--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4915,7 +4915,7 @@
         <v>14.3</v>
       </c>
       <c r="J58" t="n">
-        <v>15.06</v>
+        <v>15.05</v>
       </c>
       <c r="K58" t="n">
         <v>22.11</v>
@@ -31615,6 +31615,83 @@
         <v>154.5</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" s="3" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C413" s="3" t="n">
+        <v>101.53</v>
+      </c>
+      <c r="D413" s="3" t="n">
+        <v>105.34</v>
+      </c>
+      <c r="E413" s="3" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="F413" s="3" t="n">
+        <v>104.36</v>
+      </c>
+      <c r="G413" s="3" t="n">
+        <v>75327368</v>
+      </c>
+      <c r="H413" s="4" t="n">
+        <v>-14.33</v>
+      </c>
+      <c r="I413" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J413" s="3" t="n">
+        <v>118.11</v>
+      </c>
+      <c r="K413" s="3" t="n">
+        <v>152.42</v>
+      </c>
+      <c r="L413" s="3" t="n">
+        <v>148.87</v>
+      </c>
+      <c r="M413" s="3" t="n">
+        <v>110.93</v>
+      </c>
+      <c r="N413" s="5" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="O413" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="P413" s="3" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" s="3" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" s="3" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S413" s="3" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="U413" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V413" s="3" t="inlineStr"/>
+      <c r="W413" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -4915,7 +4915,7 @@
         <v>14.3</v>
       </c>
       <c r="J58" t="n">
-        <v>15.05</v>
+        <v>15.06</v>
       </c>
       <c r="K58" t="n">
         <v>22.11</v>
@@ -31630,37 +31630,37 @@
         <v>101.53</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>105.34</v>
+        <v>105.39</v>
       </c>
       <c r="E413" s="3" t="n">
         <v>99.87</v>
       </c>
       <c r="F413" s="3" t="n">
-        <v>104.36</v>
+        <v>101.13</v>
       </c>
       <c r="G413" s="3" t="n">
-        <v>75327368</v>
+        <v>99814009</v>
       </c>
       <c r="H413" s="4" t="n">
-        <v>-14.33</v>
+        <v>-16.98</v>
       </c>
       <c r="I413" s="3" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" s="3" t="n">
-        <v>118.11</v>
+        <v>117.95</v>
       </c>
       <c r="K413" s="3" t="n">
-        <v>152.42</v>
+        <v>152.37</v>
       </c>
       <c r="L413" s="3" t="n">
-        <v>148.87</v>
+        <v>148.84</v>
       </c>
       <c r="M413" s="3" t="n">
-        <v>110.93</v>
+        <v>110.92</v>
       </c>
       <c r="N413" s="5" t="n">
-        <v>46.02</v>
+        <v>44.35</v>
       </c>
       <c r="O413" s="3" t="n">
         <v>31</v>
@@ -31681,16 +31681,18 @@
         </is>
       </c>
       <c r="S413" s="3" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="5" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="U413" s="5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="V413" s="3" t="inlineStr"/>
-      <c r="W413" s="5" t="inlineStr"/>
+      <c r="W413" s="5" t="n">
+        <v>152.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31491,7 +31491,7 @@
         <v>121.82</v>
       </c>
       <c r="G411" t="n">
-        <v>53294900</v>
+        <v>53536100</v>
       </c>
       <c r="H411" s="6" t="n">
         <v>5.23</v>
@@ -31541,61 +31541,79 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>SOXL</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
+      <c r="A412" s="3" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="n">
-        <v>99814009</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I412" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
-      <c r="N412" s="2" t="n">
-        <v>57.83</v>
-      </c>
-      <c r="O412" t="n">
-        <v>31</v>
-      </c>
-      <c r="P412" t="inlineStr">
+      <c r="C412" s="3" t="n">
+        <v>101.53</v>
+      </c>
+      <c r="D412" s="3" t="n">
+        <v>105.39</v>
+      </c>
+      <c r="E412" s="3" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="F412" s="3" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="G412" s="3" t="n">
+        <v>100374100</v>
+      </c>
+      <c r="H412" s="4" t="n">
+        <v>-16.98</v>
+      </c>
+      <c r="I412" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J412" s="3" t="n">
+        <v>117.95</v>
+      </c>
+      <c r="K412" s="3" t="n">
+        <v>152.37</v>
+      </c>
+      <c r="L412" s="3" t="n">
+        <v>148.84</v>
+      </c>
+      <c r="M412" s="3" t="n">
+        <v>110.92</v>
+      </c>
+      <c r="N412" s="5" t="n">
+        <v>44.35</v>
+      </c>
+      <c r="O412" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="P412" s="3" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q412" t="inlineStr">
+      <c r="Q412" s="3" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
+      <c r="R412" s="3" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S412" s="3" t="n">
         <v>4.96</v>
       </c>
-      <c r="T412" s="2" t="n">
+      <c r="T412" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U412" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="n">
+      <c r="U412" s="5" t="inlineStr"/>
+      <c r="V412" s="3" t="inlineStr"/>
+      <c r="W412" s="5" t="n">
         <v>152.1</v>
       </c>
     </row>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31588,7 +31588,7 @@
         <v>44.35</v>
       </c>
       <c r="O412" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P412" s="3" t="inlineStr">
         <is>
@@ -31617,6 +31617,79 @@
         <v>152.1</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="D413" t="n">
+        <v>105.94</v>
+      </c>
+      <c r="E413" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="F413" t="n">
+        <v>101.89</v>
+      </c>
+      <c r="G413" t="n">
+        <v>45177782</v>
+      </c>
+      <c r="H413" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I413" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>115.46</v>
+      </c>
+      <c r="K413" t="n">
+        <v>149.41</v>
+      </c>
+      <c r="L413" t="n">
+        <v>149.23</v>
+      </c>
+      <c r="M413" t="n">
+        <v>111.24</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -645,9 +645,7 @@
       <c r="T2" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="1" t="n">
         <v>173.2</v>
@@ -724,9 +722,7 @@
       <c r="T3" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U3" s="5" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" s="4" t="n">
         <v>168.6</v>
@@ -799,9 +795,7 @@
       <c r="T4" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="1" t="n">
         <v>163.6</v>
@@ -874,9 +868,7 @@
       <c r="T5" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>157.4</v>
@@ -949,9 +941,7 @@
       <c r="T6" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>156.7</v>
@@ -1024,9 +1014,7 @@
       <c r="T7" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>158.5</v>
@@ -1099,9 +1087,7 @@
       <c r="T8" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>155.4</v>
@@ -1174,9 +1160,7 @@
       <c r="T9" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>159.4</v>
@@ -1249,9 +1233,7 @@
       <c r="T10" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>162.6</v>
@@ -1324,9 +1306,7 @@
       <c r="T11" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>163.6</v>
@@ -1399,9 +1379,7 @@
       <c r="T12" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U12" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>166.5</v>
@@ -1474,9 +1452,7 @@
       <c r="T13" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U13" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>166.9</v>
@@ -1553,9 +1529,7 @@
       <c r="T14" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U14" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>168.8</v>
@@ -1632,9 +1606,7 @@
       <c r="T15" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U15" s="2" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>166.1</v>
@@ -1707,9 +1679,7 @@
       <c r="T16" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U16" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>163.4</v>
@@ -1782,9 +1752,7 @@
       <c r="T17" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U17" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>168</v>
@@ -1857,9 +1825,7 @@
       <c r="T18" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U18" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>183.1</v>
@@ -1932,9 +1898,7 @@
       <c r="T19" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U19" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>175.8</v>
@@ -2007,9 +1971,7 @@
       <c r="T20" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U20" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>178.6</v>
@@ -2086,9 +2048,7 @@
       <c r="T21" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U21" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>165</v>
@@ -2165,9 +2125,7 @@
       <c r="T22" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U22" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="1" t="n">
         <v>156.9</v>
@@ -2240,9 +2198,7 @@
       <c r="T23" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U23" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="1" t="n">
         <v>157.6</v>
@@ -2315,9 +2271,7 @@
       <c r="T24" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U24" s="2" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>153.4</v>
@@ -2390,9 +2344,7 @@
       <c r="T25" s="5" t="n">
         <v>21.1</v>
       </c>
-      <c r="U25" s="5" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U25" s="5" t="inlineStr"/>
       <c r="V25" s="3" t="inlineStr"/>
       <c r="W25" s="5" t="n">
         <v>149.3</v>
@@ -2465,9 +2417,7 @@
       <c r="T26" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U26" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="1" t="n">
         <v>157.9</v>
@@ -2540,9 +2490,7 @@
       <c r="T27" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="U27" s="2" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="n">
         <v>154.3</v>
@@ -2615,9 +2563,7 @@
       <c r="T28" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U28" s="2" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>151.4</v>
@@ -2690,9 +2636,7 @@
       <c r="T29" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U29" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>138.9</v>
@@ -2769,9 +2713,7 @@
       <c r="T30" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U30" s="6" t="n">
-        <v>31.1</v>
-      </c>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="2" t="n">
         <v>137.6</v>
@@ -2844,9 +2786,7 @@
       <c r="T31" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U31" s="2" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" s="2" t="n">
         <v>139.9</v>
@@ -2923,14 +2863,8 @@
       <c r="T32" s="6" t="n">
         <v>27.9</v>
       </c>
-      <c r="U32" s="6" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" s="2" t="n">
         <v>146</v>
       </c>
@@ -3006,14 +2940,8 @@
       <c r="T33" s="6" t="n">
         <v>26.9</v>
       </c>
-      <c r="U33" s="6" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V33" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>132.8</v>
       </c>
@@ -3089,9 +3017,7 @@
       <c r="T34" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U34" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>128.7</v>
@@ -3168,9 +3094,7 @@
       <c r="T35" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U35" s="2" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>128.9</v>
@@ -3243,9 +3167,7 @@
       <c r="T36" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U36" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>130.3</v>
@@ -3318,9 +3240,7 @@
       <c r="T37" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U37" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>133.9</v>
@@ -3393,9 +3313,7 @@
       <c r="T38" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U38" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>136.8</v>
@@ -3468,9 +3386,7 @@
       <c r="T39" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U39" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>136.4</v>
@@ -3543,9 +3459,7 @@
       <c r="T40" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U40" s="2" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>140.8</v>
@@ -3618,9 +3532,7 @@
       <c r="T41" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U41" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>141.7</v>
@@ -3693,9 +3605,7 @@
       <c r="T42" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U42" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>144</v>
@@ -3768,9 +3678,7 @@
       <c r="T43" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U43" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>148.7</v>
@@ -3847,9 +3755,7 @@
       <c r="T44" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U44" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>144.8</v>
@@ -3922,9 +3828,7 @@
       <c r="T45" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U45" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>140.9</v>
@@ -3997,9 +3901,7 @@
       <c r="T46" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U46" s="6" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="2" t="n">
         <v>139</v>
@@ -4072,9 +3974,7 @@
       <c r="T47" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U47" s="2" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>148.6</v>
@@ -4147,9 +4047,7 @@
       <c r="T48" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U48" s="2" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>143</v>
@@ -4222,9 +4120,7 @@
       <c r="T49" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U49" s="6" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" s="2" t="n">
         <v>144.3</v>
@@ -4301,14 +4197,8 @@
       <c r="T50" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="U50" s="7" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="V50" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U50" s="5" t="inlineStr"/>
+      <c r="V50" s="3" t="inlineStr"/>
       <c r="W50" s="5" t="n">
         <v>139.2</v>
       </c>
@@ -4384,14 +4274,8 @@
       <c r="T51" s="7" t="n">
         <v>45.3</v>
       </c>
-      <c r="U51" s="7" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="V51" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U51" s="5" t="inlineStr"/>
+      <c r="V51" s="3" t="inlineStr"/>
       <c r="W51" s="5" t="n">
         <v>136.5</v>
       </c>
@@ -4467,14 +4351,8 @@
       <c r="T52" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="U52" s="6" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="V52" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" s="2" t="n">
         <v>133.8</v>
       </c>
@@ -4550,14 +4428,8 @@
       <c r="T53" s="6" t="n">
         <v>52.3</v>
       </c>
-      <c r="U53" s="6" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="V53" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" s="2" t="n">
         <v>135.7</v>
       </c>
@@ -4629,14 +4501,8 @@
       <c r="T54" s="6" t="n">
         <v>33.6</v>
       </c>
-      <c r="U54" s="6" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="V54" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" s="2" t="n">
         <v>142.2</v>
       </c>
@@ -4712,14 +4578,8 @@
       <c r="T55" s="7" t="n">
         <v>40.7</v>
       </c>
-      <c r="U55" s="7" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="V55" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U55" s="5" t="inlineStr"/>
+      <c r="V55" s="3" t="inlineStr"/>
       <c r="W55" s="5" t="n">
         <v>127.5</v>
       </c>
@@ -4795,14 +4655,8 @@
       <c r="T56" s="6" t="n">
         <v>37.6</v>
       </c>
-      <c r="U56" s="6" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="V56" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>128.6</v>
       </c>
@@ -4840,7 +4694,7 @@
         <v>14.3</v>
       </c>
       <c r="J57" t="n">
-        <v>15.06</v>
+        <v>15.05</v>
       </c>
       <c r="K57" t="n">
         <v>22.11</v>
@@ -4878,9 +4732,7 @@
       <c r="T57" s="6" t="n">
         <v>30.9</v>
       </c>
-      <c r="U57" s="6" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="2" t="n">
         <v>135.7</v>
@@ -4953,9 +4805,7 @@
       <c r="T58" s="6" t="n">
         <v>30.1</v>
       </c>
-      <c r="U58" s="6" t="n">
-        <v>26</v>
-      </c>
+      <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" s="2" t="n">
         <v>135.8</v>
@@ -5032,14 +4882,8 @@
       <c r="T59" s="6" t="n">
         <v>32.6</v>
       </c>
-      <c r="U59" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="V59" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" s="2" t="n">
         <v>131.3</v>
       </c>
@@ -5111,14 +4955,8 @@
       <c r="T60" s="6" t="n">
         <v>29.6</v>
       </c>
-      <c r="U60" s="6" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="V60" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" s="2" t="n">
         <v>130</v>
       </c>
@@ -5190,9 +5028,7 @@
       <c r="T61" s="6" t="n">
         <v>33.8</v>
       </c>
-      <c r="U61" s="6" t="n">
-        <v>30.6</v>
-      </c>
+      <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="6" t="n">
         <v>125.8</v>
@@ -5265,9 +5101,7 @@
       <c r="T62" s="6" t="n">
         <v>30.6</v>
       </c>
-      <c r="U62" s="6" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" s="6" t="n">
         <v>125.9</v>
@@ -5340,14 +5174,8 @@
       <c r="T63" s="6" t="n">
         <v>28.5</v>
       </c>
-      <c r="U63" s="6" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="V63" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" s="6" t="n">
         <v>126.7</v>
       </c>
@@ -5419,9 +5247,7 @@
       <c r="T64" s="6" t="n">
         <v>26.5</v>
       </c>
-      <c r="U64" s="6" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>129</v>
@@ -5494,9 +5320,7 @@
       <c r="T65" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U65" s="2" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>132.4</v>
@@ -5569,9 +5393,7 @@
       <c r="T66" s="6" t="n">
         <v>25.1</v>
       </c>
-      <c r="U66" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>131.3</v>
@@ -5644,9 +5466,7 @@
       <c r="T67" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U67" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>134.3</v>
@@ -5719,9 +5539,7 @@
       <c r="T68" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U68" s="2" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>132.7</v>
@@ -5794,9 +5612,7 @@
       <c r="T69" s="2" t="n">
         <v>24.6</v>
       </c>
-      <c r="U69" s="6" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>134.1</v>
@@ -5869,9 +5685,7 @@
       <c r="T70" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="U70" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>134.8</v>
@@ -5944,9 +5758,7 @@
       <c r="T71" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U71" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>134.1</v>
@@ -6019,9 +5831,7 @@
       <c r="T72" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U72" s="2" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>133.2</v>
@@ -6094,9 +5904,7 @@
       <c r="T73" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U73" s="2" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>132.2</v>
@@ -6169,9 +5977,7 @@
       <c r="T74" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="U74" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>131.5</v>
@@ -6244,9 +6050,7 @@
       <c r="T75" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U75" s="6" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>128.4</v>
@@ -6319,9 +6123,7 @@
       <c r="T76" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U76" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>137.7</v>
@@ -6394,9 +6196,7 @@
       <c r="T77" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U77" s="2" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>140.5</v>
@@ -6469,9 +6269,7 @@
       <c r="T78" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U78" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>138.9</v>
@@ -6544,9 +6342,7 @@
       <c r="T79" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U79" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>140.9</v>
@@ -6619,9 +6415,7 @@
       <c r="T80" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U80" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>136</v>
@@ -6694,9 +6488,7 @@
       <c r="T81" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>135.9</v>
@@ -6769,9 +6561,7 @@
       <c r="T82" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U82" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>137.3</v>
@@ -6844,9 +6634,7 @@
       <c r="T83" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="U83" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>137.3</v>
@@ -6919,9 +6707,7 @@
       <c r="T84" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U84" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>139</v>
@@ -6994,9 +6780,7 @@
       <c r="T85" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U85" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>139.3</v>
@@ -7069,9 +6853,7 @@
       <c r="T86" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U86" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>140.9</v>
@@ -7144,9 +6926,7 @@
       <c r="T87" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U87" s="2" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>137.6</v>
@@ -7219,9 +6999,7 @@
       <c r="T88" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U88" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>137.3</v>
@@ -7298,9 +7076,7 @@
       <c r="T89" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U89" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>138.2</v>
@@ -7373,9 +7149,7 @@
       <c r="T90" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U90" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="2" t="n">
         <v>141</v>
@@ -7448,9 +7222,7 @@
       <c r="T91" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U91" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="2" t="n">
         <v>141.6</v>
@@ -7523,9 +7295,7 @@
       <c r="T92" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U92" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="2" t="n">
         <v>137.5</v>
@@ -7598,9 +7368,7 @@
       <c r="T93" s="2" t="n">
         <v>18.5</v>
       </c>
-      <c r="U93" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>140.1</v>
@@ -7673,9 +7441,7 @@
       <c r="T94" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U94" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="2" t="n">
         <v>138.9</v>
@@ -7748,9 +7514,7 @@
       <c r="T95" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U95" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="2" t="n">
         <v>139.2</v>
@@ -7823,9 +7587,7 @@
       <c r="T96" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U96" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="2" t="n">
         <v>141.2</v>
@@ -7898,9 +7660,7 @@
       <c r="T97" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U97" s="2" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="2" t="n">
         <v>141.4</v>
@@ -7973,9 +7733,7 @@
       <c r="T98" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U98" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="2" t="n">
         <v>145.6</v>
@@ -8052,9 +7810,7 @@
       <c r="T99" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U99" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="2" t="n">
         <v>149.6</v>
@@ -8127,9 +7883,7 @@
       <c r="T100" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U100" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="1" t="n">
         <v>156.6</v>
@@ -8202,9 +7956,7 @@
       <c r="T101" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U101" s="2" t="n">
-        <v>21</v>
-      </c>
+      <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="2" t="n">
         <v>154.4</v>
@@ -8277,9 +8029,7 @@
       <c r="T102" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U102" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="2" t="n">
         <v>148.4</v>
@@ -8352,9 +8102,7 @@
       <c r="T103" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U103" s="2" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="2" t="n">
         <v>149.2</v>
@@ -8427,9 +8175,7 @@
       <c r="T104" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U104" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="2" t="n">
         <v>154.8</v>
@@ -8502,9 +8248,7 @@
       <c r="T105" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U105" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="1" t="n">
         <v>155</v>
@@ -8577,9 +8321,7 @@
       <c r="T106" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U106" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="2" t="n">
         <v>152.2</v>
@@ -8652,9 +8394,7 @@
       <c r="T107" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U107" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="2" t="n">
         <v>147.5</v>
@@ -8727,9 +8467,7 @@
       <c r="T108" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U108" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="2" t="n">
         <v>143.4</v>
@@ -8802,9 +8540,7 @@
       <c r="T109" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U109" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="2" t="n">
         <v>139.6</v>
@@ -8877,9 +8613,7 @@
       <c r="T110" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U110" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="2" t="n">
         <v>140.1</v>
@@ -8952,9 +8686,7 @@
       <c r="T111" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U111" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="2" t="n">
         <v>139.3</v>
@@ -9027,9 +8759,7 @@
       <c r="T112" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U112" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="2" t="n">
         <v>141.4</v>
@@ -9102,9 +8832,7 @@
       <c r="T113" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U113" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="2" t="n">
         <v>138</v>
@@ -9177,9 +8905,7 @@
       <c r="T114" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U114" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="2" t="n">
         <v>140.8</v>
@@ -9252,9 +8978,7 @@
       <c r="T115" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U115" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="2" t="n">
         <v>141.8</v>
@@ -9327,9 +9051,7 @@
       <c r="T116" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U116" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="2" t="n">
         <v>143.3</v>
@@ -9402,9 +9124,7 @@
       <c r="T117" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U117" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="2" t="n">
         <v>145</v>
@@ -9477,9 +9197,7 @@
       <c r="T118" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U118" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="2" t="n">
         <v>147</v>
@@ -9552,9 +9270,7 @@
       <c r="T119" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U119" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="2" t="n">
         <v>143.7</v>
@@ -9627,9 +9343,7 @@
       <c r="T120" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U120" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="2" t="n">
         <v>146.7</v>
@@ -9702,9 +9416,7 @@
       <c r="T121" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U121" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="2" t="n">
         <v>151.1</v>
@@ -9777,9 +9489,7 @@
       <c r="T122" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U122" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="2" t="n">
         <v>150.4</v>
@@ -9852,9 +9562,7 @@
       <c r="T123" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U123" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="2" t="n">
         <v>154.8</v>
@@ -9927,9 +9635,7 @@
       <c r="T124" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U124" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="2" t="n">
         <v>153.4</v>
@@ -10006,9 +9712,7 @@
       <c r="T125" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="1" t="n">
         <v>159.3</v>
@@ -10081,9 +9785,7 @@
       <c r="T126" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U126" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="1" t="n">
         <v>159.4</v>
@@ -10156,9 +9858,7 @@
       <c r="T127" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U127" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="2" t="n">
         <v>145.6</v>
@@ -10231,9 +9931,7 @@
       <c r="T128" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U128" s="2" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="2" t="n">
         <v>147.6</v>
@@ -10306,9 +10004,7 @@
       <c r="T129" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U129" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="2" t="n">
         <v>149.1</v>
@@ -10381,9 +10077,7 @@
       <c r="T130" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U130" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="2" t="n">
         <v>154.1</v>
@@ -10460,9 +10154,7 @@
       <c r="T131" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U131" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="2" t="n">
         <v>152.3</v>
@@ -10535,9 +10227,7 @@
       <c r="T132" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U132" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>155.5</v>
@@ -10610,9 +10300,7 @@
       <c r="T133" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U133" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="1" t="n">
         <v>159.3</v>
@@ -10685,9 +10373,7 @@
       <c r="T134" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U134" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="2" t="n">
         <v>149.9</v>
@@ -10760,9 +10446,7 @@
       <c r="T135" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U135" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U135" s="2" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="2" t="n">
         <v>149.7</v>
@@ -10835,9 +10519,7 @@
       <c r="T136" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U136" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="2" t="n">
         <v>147</v>
@@ -10910,9 +10592,7 @@
       <c r="T137" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U137" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="2" t="n">
         <v>147.5</v>
@@ -10985,9 +10665,7 @@
       <c r="T138" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U138" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="2" t="n">
         <v>148.6</v>
@@ -11060,9 +10738,7 @@
       <c r="T139" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U139" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="2" t="n">
         <v>151.4</v>
@@ -11135,9 +10811,7 @@
       <c r="T140" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U140" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="2" t="n">
         <v>153.1</v>
@@ -11210,9 +10884,7 @@
       <c r="T141" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U141" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U141" s="2" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="2" t="n">
         <v>150.6</v>
@@ -11285,9 +10957,7 @@
       <c r="T142" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U142" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="2" t="n">
         <v>153.8</v>
@@ -11360,9 +11030,7 @@
       <c r="T143" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U143" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="2" t="n">
         <v>153.9</v>
@@ -11439,9 +11107,7 @@
       <c r="T144" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U144" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="2" t="n">
         <v>153.2</v>
@@ -11514,9 +11180,7 @@
       <c r="T145" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U145" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="2" t="n">
         <v>144.6</v>
@@ -11589,9 +11253,7 @@
       <c r="T146" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U146" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="2" t="n">
         <v>144.3</v>
@@ -11664,9 +11326,7 @@
       <c r="T147" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U147" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="2" t="n">
         <v>146.4</v>
@@ -11739,9 +11399,7 @@
       <c r="T148" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U148" s="2" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="2" t="n">
         <v>150</v>
@@ -11814,9 +11472,7 @@
       <c r="T149" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U149" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U149" s="2" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="1" t="n">
         <v>156.5</v>
@@ -11889,9 +11545,7 @@
       <c r="T150" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U150" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U150" s="2" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="2" t="n">
         <v>150.9</v>
@@ -11964,9 +11618,7 @@
       <c r="T151" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U151" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="2" t="n">
         <v>152.5</v>
@@ -12043,9 +11695,7 @@
       <c r="T152" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U152" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U152" s="2" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="2" t="n">
         <v>152.1</v>
@@ -12122,9 +11772,7 @@
       <c r="T153" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U153" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U153" s="2" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="2" t="n">
         <v>151.5</v>
@@ -12197,9 +11845,7 @@
       <c r="T154" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U154" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="2" t="n">
         <v>150.2</v>
@@ -12272,9 +11918,7 @@
       <c r="T155" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U155" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="2" t="n">
         <v>154</v>
@@ -12347,9 +11991,7 @@
       <c r="T156" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U156" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U156" s="2" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="2" t="n">
         <v>148.2</v>
@@ -12422,9 +12064,7 @@
       <c r="T157" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U157" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U157" s="2" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="2" t="n">
         <v>148.8</v>
@@ -12497,9 +12137,7 @@
       <c r="T158" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U158" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U158" s="2" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="2" t="n">
         <v>150.9</v>
@@ -12572,9 +12210,7 @@
       <c r="T159" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U159" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="2" t="n">
         <v>151.9</v>
@@ -12647,9 +12283,7 @@
       <c r="T160" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U160" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U160" s="2" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="2" t="n">
         <v>147.6</v>
@@ -12722,9 +12356,7 @@
       <c r="T161" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U161" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U161" s="2" t="inlineStr"/>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="2" t="n">
         <v>149.5</v>
@@ -12797,9 +12429,7 @@
       <c r="T162" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U162" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U162" s="2" t="inlineStr"/>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="2" t="n">
         <v>152.1</v>
@@ -12872,9 +12502,7 @@
       <c r="T163" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U163" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U163" s="2" t="inlineStr"/>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="2" t="n">
         <v>148.2</v>
@@ -12947,9 +12575,7 @@
       <c r="T164" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U164" s="2" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="2" t="n">
         <v>146.4</v>
@@ -13022,9 +12648,7 @@
       <c r="T165" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U165" s="2" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="U165" s="2" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="2" t="n">
         <v>148.2</v>
@@ -13097,9 +12721,7 @@
       <c r="T166" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U166" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U166" s="2" t="inlineStr"/>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="2" t="n">
         <v>147</v>
@@ -13172,9 +12794,7 @@
       <c r="T167" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U167" s="2" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="U167" s="2" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>145.5</v>
@@ -13247,9 +12867,7 @@
       <c r="T168" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U168" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U168" s="2" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="2" t="n">
         <v>146.5</v>
@@ -13322,9 +12940,7 @@
       <c r="T169" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U169" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U169" s="2" t="inlineStr"/>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="2" t="n">
         <v>145.9</v>
@@ -13397,9 +13013,7 @@
       <c r="T170" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U170" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U170" s="2" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="2" t="n">
         <v>145.9</v>
@@ -13472,9 +13086,7 @@
       <c r="T171" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U171" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U171" s="2" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="2" t="n">
         <v>141.5</v>
@@ -13547,9 +13159,7 @@
       <c r="T172" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U172" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U172" s="2" t="inlineStr"/>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>143</v>
@@ -13622,9 +13232,7 @@
       <c r="T173" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U173" s="2" t="inlineStr"/>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="2" t="n">
         <v>143.4</v>
@@ -13697,9 +13305,7 @@
       <c r="T174" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U174" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U174" s="2" t="inlineStr"/>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="2" t="n">
         <v>143.7</v>
@@ -13772,9 +13378,7 @@
       <c r="T175" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U175" s="2" t="inlineStr"/>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="2" t="n">
         <v>145.9</v>
@@ -13847,9 +13451,7 @@
       <c r="T176" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U176" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U176" s="2" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="2" t="n">
         <v>144.6</v>
@@ -13922,9 +13524,7 @@
       <c r="T177" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U177" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U177" s="2" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="2" t="n">
         <v>142.5</v>
@@ -13966,7 +13566,7 @@
         <v>33.95</v>
       </c>
       <c r="K178" t="n">
-        <v>29</v>
+        <v>28.99</v>
       </c>
       <c r="L178" t="n">
         <v>23.73</v>
@@ -13997,9 +13597,7 @@
       <c r="T178" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U178" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U178" s="2" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="2" t="n">
         <v>145.2</v>
@@ -14072,9 +13670,7 @@
       <c r="T179" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U179" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U179" s="2" t="inlineStr"/>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="2" t="n">
         <v>145.8</v>
@@ -14147,9 +13743,7 @@
       <c r="T180" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U180" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U180" s="2" t="inlineStr"/>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="2" t="n">
         <v>145.3</v>
@@ -14226,9 +13820,7 @@
       <c r="T181" s="5" t="n">
         <v>21.7</v>
       </c>
-      <c r="U181" s="7" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U181" s="5" t="inlineStr"/>
       <c r="V181" s="3" t="inlineStr"/>
       <c r="W181" s="5" t="n">
         <v>138.9</v>
@@ -14301,9 +13893,7 @@
       <c r="T182" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U182" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U182" s="2" t="inlineStr"/>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="2" t="n">
         <v>142.8</v>
@@ -14376,9 +13966,7 @@
       <c r="T183" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U183" s="2" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="U183" s="2" t="inlineStr"/>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="2" t="n">
         <v>146.5</v>
@@ -14451,9 +14039,7 @@
       <c r="T184" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U184" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U184" s="2" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="2" t="n">
         <v>145</v>
@@ -14526,9 +14112,7 @@
       <c r="T185" s="6" t="n">
         <v>25.3</v>
       </c>
-      <c r="U185" s="2" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="U185" s="2" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="2" t="n">
         <v>147.1</v>
@@ -14601,9 +14185,7 @@
       <c r="T186" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U186" s="2" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="U186" s="2" t="inlineStr"/>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="2" t="n">
         <v>147.6</v>
@@ -14676,9 +14258,7 @@
       <c r="T187" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U187" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U187" s="2" t="inlineStr"/>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="2" t="n">
         <v>151.3</v>
@@ -14751,9 +14331,7 @@
       <c r="T188" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U188" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U188" s="2" t="inlineStr"/>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="2" t="n">
         <v>149.9</v>
@@ -14830,9 +14408,7 @@
       <c r="T189" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U189" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U189" s="2" t="inlineStr"/>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="2" t="n">
         <v>152.9</v>
@@ -14905,9 +14481,7 @@
       <c r="T190" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U190" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U190" s="2" t="inlineStr"/>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="2" t="n">
         <v>154.3</v>
@@ -14980,9 +14554,7 @@
       <c r="T191" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U191" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U191" s="2" t="inlineStr"/>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="2" t="n">
         <v>153.5</v>
@@ -15055,9 +14627,7 @@
       <c r="T192" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U192" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U192" s="2" t="inlineStr"/>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>148.5</v>
@@ -15130,9 +14700,7 @@
       <c r="T193" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U193" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U193" s="2" t="inlineStr"/>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>140.4</v>
@@ -15205,9 +14773,7 @@
       <c r="T194" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U194" s="2" t="inlineStr"/>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="2" t="n">
         <v>139.4</v>
@@ -15280,9 +14846,7 @@
       <c r="T195" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U195" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U195" s="2" t="inlineStr"/>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="2" t="n">
         <v>141.1</v>
@@ -15355,9 +14919,7 @@
       <c r="T196" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U196" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U196" s="2" t="inlineStr"/>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="2" t="n">
         <v>142.8</v>
@@ -15430,9 +14992,7 @@
       <c r="T197" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U197" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U197" s="2" t="inlineStr"/>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="2" t="n">
         <v>142</v>
@@ -15505,9 +15065,7 @@
       <c r="T198" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U198" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U198" s="2" t="inlineStr"/>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="2" t="n">
         <v>144</v>
@@ -15580,9 +15138,7 @@
       <c r="T199" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U199" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U199" s="2" t="inlineStr"/>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>143.6</v>
@@ -15655,9 +15211,7 @@
       <c r="T200" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U200" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U200" s="2" t="inlineStr"/>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>143.5</v>
@@ -15734,9 +15288,7 @@
       <c r="T201" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U201" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U201" s="2" t="inlineStr"/>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="2" t="n">
         <v>141.3</v>
@@ -15809,9 +15361,7 @@
       <c r="T202" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U202" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U202" s="2" t="inlineStr"/>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="2" t="n">
         <v>142.9</v>
@@ -15888,9 +15438,7 @@
       <c r="T203" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U203" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U203" s="2" t="inlineStr"/>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="2" t="n">
         <v>143.4</v>
@@ -15963,9 +15511,7 @@
       <c r="T204" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U204" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U204" s="2" t="inlineStr"/>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="2" t="n">
         <v>138.6</v>
@@ -16038,9 +15584,7 @@
       <c r="T205" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U205" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U205" s="2" t="inlineStr"/>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="2" t="n">
         <v>142.5</v>
@@ -16113,9 +15657,7 @@
       <c r="T206" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U206" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U206" s="2" t="inlineStr"/>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="2" t="n">
         <v>137.9</v>
@@ -16188,9 +15730,7 @@
       <c r="T207" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U207" s="2" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="U207" s="2" t="inlineStr"/>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="2" t="n">
         <v>140.9</v>
@@ -16267,9 +15807,7 @@
       <c r="T208" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U208" s="2" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="U208" s="2" t="inlineStr"/>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="2" t="n">
         <v>143</v>
@@ -16342,9 +15880,7 @@
       <c r="T209" s="2" t="n">
         <v>23.7</v>
       </c>
-      <c r="U209" s="6" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U209" s="2" t="inlineStr"/>
       <c r="V209" t="inlineStr"/>
       <c r="W209" s="2" t="n">
         <v>143.1</v>
@@ -16421,14 +15957,8 @@
       <c r="T210" s="7" t="n">
         <v>26.4</v>
       </c>
-      <c r="U210" s="7" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V210" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U210" s="5" t="inlineStr"/>
+      <c r="V210" s="3" t="inlineStr"/>
       <c r="W210" s="5" t="n">
         <v>145</v>
       </c>
@@ -16469,7 +15999,7 @@
         <v>41.98</v>
       </c>
       <c r="K211" t="n">
-        <v>37.05</v>
+        <v>37.06</v>
       </c>
       <c r="L211" t="n">
         <v>31.1</v>
@@ -16500,9 +16030,7 @@
       <c r="T211" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U211" s="2" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="U211" s="2" t="inlineStr"/>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="2" t="n">
         <v>148.3</v>
@@ -16575,9 +16103,7 @@
       <c r="T212" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U212" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U212" s="2" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="2" t="n">
         <v>148.6</v>
@@ -16650,9 +16176,7 @@
       <c r="T213" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U213" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U213" s="2" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="2" t="n">
         <v>151.7</v>
@@ -16725,9 +16249,7 @@
       <c r="T214" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U214" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U214" s="2" t="inlineStr"/>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="2" t="n">
         <v>145</v>
@@ -16800,9 +16322,7 @@
       <c r="T215" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U215" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U215" s="2" t="inlineStr"/>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="2" t="n">
         <v>143</v>
@@ -16875,9 +16395,7 @@
       <c r="T216" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U216" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U216" s="2" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>144.9</v>
@@ -16950,9 +16468,7 @@
       <c r="T217" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U217" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U217" s="2" t="inlineStr"/>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="2" t="n">
         <v>144.9</v>
@@ -17025,9 +16541,7 @@
       <c r="T218" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U218" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="U218" s="2" t="inlineStr"/>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="2" t="n">
         <v>149.2</v>
@@ -17100,9 +16614,7 @@
       <c r="T219" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U219" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U219" s="2" t="inlineStr"/>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="2" t="n">
         <v>148.9</v>
@@ -17175,9 +16687,7 @@
       <c r="T220" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U220" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U220" s="2" t="inlineStr"/>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="2" t="n">
         <v>148.8</v>
@@ -17250,9 +16760,7 @@
       <c r="T221" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U221" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U221" s="2" t="inlineStr"/>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="2" t="n">
         <v>150.6</v>
@@ -17325,9 +16833,7 @@
       <c r="T222" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U222" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U222" s="2" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="2" t="n">
         <v>150.3</v>
@@ -17400,9 +16906,7 @@
       <c r="T223" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U223" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U223" s="2" t="inlineStr"/>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="2" t="n">
         <v>147.6</v>
@@ -17475,9 +16979,7 @@
       <c r="T224" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U224" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U224" s="2" t="inlineStr"/>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="2" t="n">
         <v>148.3</v>
@@ -17550,9 +17052,7 @@
       <c r="T225" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U225" s="5" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U225" s="5" t="inlineStr"/>
       <c r="V225" s="3" t="inlineStr"/>
       <c r="W225" s="5" t="n">
         <v>153.6</v>
@@ -17625,9 +17125,7 @@
       <c r="T226" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U226" s="2" t="inlineStr"/>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>161.9</v>
@@ -17704,9 +17202,7 @@
       <c r="T227" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U227" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U227" s="2" t="inlineStr"/>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="1" t="n">
         <v>157</v>
@@ -17779,9 +17275,7 @@
       <c r="T228" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U228" s="2" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="U228" s="2" t="inlineStr"/>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="2" t="n">
         <v>153.5</v>
@@ -17854,9 +17348,7 @@
       <c r="T229" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U229" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U229" s="2" t="inlineStr"/>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>155.4</v>
@@ -17929,9 +17421,7 @@
       <c r="T230" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U230" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U230" s="2" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>155.9</v>
@@ -18004,9 +17494,7 @@
       <c r="T231" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="U231" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U231" s="2" t="inlineStr"/>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>159.9</v>
@@ -18079,9 +17567,7 @@
       <c r="T232" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="U232" s="2" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="U232" s="2" t="inlineStr"/>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>160.5</v>
@@ -18154,9 +17640,7 @@
       <c r="T233" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="U233" s="2" t="n">
-        <v>7.4</v>
-      </c>
+      <c r="U233" s="2" t="inlineStr"/>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="1" t="n">
         <v>160.5</v>
@@ -18229,9 +17713,7 @@
       <c r="T234" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="U234" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U234" s="2" t="inlineStr"/>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="2" t="n">
         <v>151.4</v>
@@ -18304,9 +17786,7 @@
       <c r="T235" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U235" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="U235" s="2" t="inlineStr"/>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="2" t="n">
         <v>150.5</v>
@@ -18383,9 +17863,7 @@
       <c r="T236" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U236" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U236" s="2" t="inlineStr"/>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="2" t="n">
         <v>148.3</v>
@@ -18458,9 +17936,7 @@
       <c r="T237" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U237" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U237" s="2" t="inlineStr"/>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="2" t="n">
         <v>148.7</v>
@@ -18533,9 +18009,7 @@
       <c r="T238" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U238" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U238" s="2" t="inlineStr"/>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="2" t="n">
         <v>141.9</v>
@@ -18608,9 +18082,7 @@
       <c r="T239" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U239" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U239" s="2" t="inlineStr"/>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="2" t="n">
         <v>142.4</v>
@@ -18683,9 +18155,7 @@
       <c r="T240" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U240" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="U240" s="2" t="inlineStr"/>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="2" t="n">
         <v>146.2</v>
@@ -18758,9 +18228,7 @@
       <c r="T241" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="U241" s="2" t="inlineStr"/>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="2" t="n">
         <v>143.6</v>
@@ -18833,9 +18301,7 @@
       <c r="T242" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U242" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U242" s="2" t="inlineStr"/>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="2" t="n">
         <v>147.1</v>
@@ -18908,9 +18374,7 @@
       <c r="T243" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U243" s="2" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="U243" s="2" t="inlineStr"/>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="2" t="n">
         <v>146</v>
@@ -18983,9 +18447,7 @@
       <c r="T244" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U244" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U244" s="2" t="inlineStr"/>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="2" t="n">
         <v>149.8</v>
@@ -19058,9 +18520,7 @@
       <c r="T245" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U245" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U245" s="2" t="inlineStr"/>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="2" t="n">
         <v>151.6</v>
@@ -19133,9 +18593,7 @@
       <c r="T246" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U246" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U246" s="2" t="inlineStr"/>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="2" t="n">
         <v>152.5</v>
@@ -19208,9 +18666,7 @@
       <c r="T247" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U247" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U247" s="2" t="inlineStr"/>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="2" t="n">
         <v>151.6</v>
@@ -19283,9 +18739,7 @@
       <c r="T248" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U248" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U248" s="2" t="inlineStr"/>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="2" t="n">
         <v>153.6</v>
@@ -19358,9 +18812,7 @@
       <c r="T249" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U249" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U249" s="2" t="inlineStr"/>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="1" t="n">
         <v>155</v>
@@ -19433,9 +18885,7 @@
       <c r="T250" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U250" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U250" s="2" t="inlineStr"/>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="2" t="n">
         <v>144.4</v>
@@ -19508,9 +18958,7 @@
       <c r="T251" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U251" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U251" s="2" t="inlineStr"/>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="2" t="n">
         <v>141.3</v>
@@ -19583,9 +19031,7 @@
       <c r="T252" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U252" s="2" t="inlineStr"/>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="2" t="n">
         <v>144</v>
@@ -19658,9 +19104,7 @@
       <c r="T253" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U253" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U253" s="2" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="2" t="n">
         <v>148.1</v>
@@ -19733,9 +19177,7 @@
       <c r="T254" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U254" s="2" t="inlineStr"/>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="2" t="n">
         <v>147.2</v>
@@ -19808,9 +19250,7 @@
       <c r="T255" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U255" s="2" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U255" s="2" t="inlineStr"/>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="2" t="n">
         <v>145</v>
@@ -19883,9 +19323,7 @@
       <c r="T256" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U256" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U256" s="2" t="inlineStr"/>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="2" t="n">
         <v>143.7</v>
@@ -19958,9 +19396,7 @@
       <c r="T257" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U257" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U257" s="2" t="inlineStr"/>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="2" t="n">
         <v>143.6</v>
@@ -20033,9 +19469,7 @@
       <c r="T258" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U258" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U258" s="2" t="inlineStr"/>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="2" t="n">
         <v>146.6</v>
@@ -20108,9 +19542,7 @@
       <c r="T259" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U259" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U259" s="2" t="inlineStr"/>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="2" t="n">
         <v>143.9</v>
@@ -20187,9 +19619,7 @@
       <c r="T260" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U260" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U260" s="2" t="inlineStr"/>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="2" t="n">
         <v>143.2</v>
@@ -20262,9 +19692,7 @@
       <c r="T261" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U261" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U261" s="2" t="inlineStr"/>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="2" t="n">
         <v>137.2</v>
@@ -20337,9 +19765,7 @@
       <c r="T262" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U262" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U262" s="2" t="inlineStr"/>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="2" t="n">
         <v>140.3</v>
@@ -20412,9 +19838,7 @@
       <c r="T263" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U263" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U263" s="2" t="inlineStr"/>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="2" t="n">
         <v>145.2</v>
@@ -20487,9 +19911,7 @@
       <c r="T264" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U264" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U264" s="2" t="inlineStr"/>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="2" t="n">
         <v>145.7</v>
@@ -20562,9 +19984,7 @@
       <c r="T265" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U265" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U265" s="2" t="inlineStr"/>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="2" t="n">
         <v>143.8</v>
@@ -20637,9 +20057,7 @@
       <c r="T266" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U266" s="2" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="U266" s="2" t="inlineStr"/>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="2" t="n">
         <v>142.5</v>
@@ -20712,9 +20130,7 @@
       <c r="T267" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U267" s="2" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="U267" s="2" t="inlineStr"/>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="2" t="n">
         <v>139.4</v>
@@ -20787,9 +20203,7 @@
       <c r="T268" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U268" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U268" s="2" t="inlineStr"/>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="2" t="n">
         <v>140.3</v>
@@ -20862,9 +20276,7 @@
       <c r="T269" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U269" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U269" s="2" t="inlineStr"/>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="2" t="n">
         <v>139.2</v>
@@ -20937,9 +20349,7 @@
       <c r="T270" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="U270" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U270" s="2" t="inlineStr"/>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="2" t="n">
         <v>141.2</v>
@@ -21012,9 +20422,7 @@
       <c r="T271" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U271" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U271" s="2" t="inlineStr"/>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="2" t="n">
         <v>145.5</v>
@@ -21087,9 +20495,7 @@
       <c r="T272" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U272" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U272" s="2" t="inlineStr"/>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="2" t="n">
         <v>141.4</v>
@@ -21162,9 +20568,7 @@
       <c r="T273" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U273" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U273" s="2" t="inlineStr"/>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="2" t="n">
         <v>141.9</v>
@@ -21237,9 +20641,7 @@
       <c r="T274" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U274" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U274" s="2" t="inlineStr"/>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="2" t="n">
         <v>146.1</v>
@@ -21312,9 +20714,7 @@
       <c r="T275" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U275" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U275" s="2" t="inlineStr"/>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="2" t="n">
         <v>146.6</v>
@@ -21391,9 +20791,7 @@
       <c r="T276" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U276" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U276" s="2" t="inlineStr"/>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="2" t="n">
         <v>146.7</v>
@@ -21466,9 +20864,7 @@
       <c r="T277" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="U277" s="2" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="U277" s="2" t="inlineStr"/>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="2" t="n">
         <v>151.8</v>
@@ -21545,9 +20941,7 @@
       <c r="T278" s="5" t="n">
         <v>23.6</v>
       </c>
-      <c r="U278" s="5" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="U278" s="5" t="inlineStr"/>
       <c r="V278" s="3" t="inlineStr"/>
       <c r="W278" s="5" t="n">
         <v>152.8</v>
@@ -21620,9 +21014,7 @@
       <c r="T279" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U279" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U279" s="2" t="inlineStr"/>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="2" t="n">
         <v>152.9</v>
@@ -21699,9 +21091,7 @@
       <c r="T280" s="2" t="n">
         <v>23.8</v>
       </c>
-      <c r="U280" s="2" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="U280" s="2" t="inlineStr"/>
       <c r="V280" t="inlineStr"/>
       <c r="W280" s="2" t="n">
         <v>153.9</v>
@@ -21774,14 +21164,8 @@
       <c r="T281" s="6" t="n">
         <v>29.5</v>
       </c>
-      <c r="U281" s="6" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="V281" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
       <c r="W281" s="2" t="n">
         <v>151.8</v>
       </c>
@@ -21853,9 +21237,7 @@
       <c r="T282" s="6" t="n">
         <v>25.5</v>
       </c>
-      <c r="U282" s="2" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="U282" s="2" t="inlineStr"/>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="1" t="n">
         <v>158</v>
@@ -21928,9 +21310,7 @@
       <c r="T283" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U283" s="2" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="U283" s="2" t="inlineStr"/>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="2" t="n">
         <v>154.5</v>
@@ -22003,9 +21383,7 @@
       <c r="T284" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U284" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U284" s="2" t="inlineStr"/>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="2" t="n">
         <v>152.4</v>
@@ -22076,9 +21454,7 @@
       <c r="T285" s="6" t="n">
         <v>27.3</v>
       </c>
-      <c r="U285" s="2" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="U285" s="2" t="inlineStr"/>
       <c r="V285" t="inlineStr"/>
       <c r="W285" s="2" t="n">
         <v>139.9</v>
@@ -22151,14 +21527,8 @@
       <c r="T286" s="6" t="n">
         <v>27.2</v>
       </c>
-      <c r="U286" s="6" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="V286" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" t="inlineStr"/>
       <c r="W286" s="2" t="n">
         <v>137.8</v>
       </c>
@@ -22230,9 +21600,7 @@
       <c r="T287" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U287" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U287" s="2" t="inlineStr"/>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="2" t="n">
         <v>141.5</v>
@@ -22305,9 +21673,7 @@
       <c r="T288" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U288" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U288" s="2" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="2" t="n">
         <v>145</v>
@@ -22380,9 +21746,7 @@
       <c r="T289" s="6" t="n">
         <v>25.1</v>
       </c>
-      <c r="U289" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U289" s="2" t="inlineStr"/>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="2" t="n">
         <v>136.5</v>
@@ -22455,9 +21819,7 @@
       <c r="T290" s="2" t="n">
         <v>24.1</v>
       </c>
-      <c r="U290" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U290" s="2" t="inlineStr"/>
       <c r="V290" t="inlineStr"/>
       <c r="W290" s="2" t="n">
         <v>138.3</v>
@@ -22530,14 +21892,8 @@
       <c r="T291" s="6" t="n">
         <v>26.8</v>
       </c>
-      <c r="U291" s="6" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="V291" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U291" s="2" t="inlineStr"/>
+      <c r="V291" t="inlineStr"/>
       <c r="W291" s="2" t="n">
         <v>139.1</v>
       </c>
@@ -22609,9 +21965,7 @@
       <c r="T292" s="6" t="n">
         <v>26.1</v>
       </c>
-      <c r="U292" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U292" s="2" t="inlineStr"/>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="2" t="n">
         <v>142</v>
@@ -22684,9 +22038,7 @@
       <c r="T293" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="U293" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U293" s="2" t="inlineStr"/>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>142.6</v>
@@ -22759,9 +22111,7 @@
       <c r="T294" s="6" t="n">
         <v>25.3</v>
       </c>
-      <c r="U294" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U294" s="2" t="inlineStr"/>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="2" t="n">
         <v>140.9</v>
@@ -22838,9 +22188,7 @@
       <c r="T295" s="6" t="n">
         <v>27.4</v>
       </c>
-      <c r="U295" s="2" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U295" s="2" t="inlineStr"/>
       <c r="V295" t="inlineStr"/>
       <c r="W295" s="2" t="n">
         <v>144</v>
@@ -22913,14 +22261,8 @@
       <c r="T296" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="U296" s="6" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="V296" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>139</v>
       </c>
@@ -22992,9 +22334,7 @@
       <c r="T297" s="6" t="n">
         <v>30.6</v>
       </c>
-      <c r="U297" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U297" s="2" t="inlineStr"/>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>142.2</v>
@@ -23067,9 +22407,7 @@
       <c r="T298" s="6" t="n">
         <v>25.2</v>
       </c>
-      <c r="U298" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U298" s="2" t="inlineStr"/>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>145.4</v>
@@ -23142,9 +22480,7 @@
       <c r="T299" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="U299" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U299" s="2" t="inlineStr"/>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>143.8</v>
@@ -23217,9 +22553,7 @@
       <c r="T300" s="2" t="n">
         <v>23.9</v>
       </c>
-      <c r="U300" s="6" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="U300" s="2" t="inlineStr"/>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>146.9</v>
@@ -23292,9 +22626,7 @@
       <c r="T301" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U301" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U301" s="2" t="inlineStr"/>
       <c r="V301" t="inlineStr"/>
       <c r="W301" s="2" t="n">
         <v>147.6</v>
@@ -23367,14 +22699,8 @@
       <c r="T302" s="6" t="n">
         <v>25.8</v>
       </c>
-      <c r="U302" s="6" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V302" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
       <c r="W302" s="2" t="n">
         <v>148.4</v>
       </c>
@@ -23446,9 +22772,7 @@
       <c r="T303" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U303" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U303" s="2" t="inlineStr"/>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="2" t="n">
         <v>150.4</v>
@@ -23521,9 +22845,7 @@
       <c r="T304" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U304" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U304" s="2" t="inlineStr"/>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="2" t="n">
         <v>143.3</v>
@@ -23596,9 +22918,7 @@
       <c r="T305" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U305" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U305" s="2" t="inlineStr"/>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="2" t="n">
         <v>144.2</v>
@@ -23671,9 +22991,7 @@
       <c r="T306" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U306" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U306" s="2" t="inlineStr"/>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="1" t="n">
         <v>156.9</v>
@@ -23746,9 +23064,7 @@
       <c r="T307" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U307" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U307" s="2" t="inlineStr"/>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="2" t="n">
         <v>149.9</v>
@@ -23821,9 +23137,7 @@
       <c r="T308" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U308" s="2" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="U308" s="2" t="inlineStr"/>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="2" t="n">
         <v>139.2</v>
@@ -23896,9 +23210,7 @@
       <c r="T309" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U309" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U309" s="2" t="inlineStr"/>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="2" t="n">
         <v>140.7</v>
@@ -23971,9 +23283,7 @@
       <c r="T310" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U310" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U310" s="2" t="inlineStr"/>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="2" t="n">
         <v>141.8</v>
@@ -24046,9 +23356,7 @@
       <c r="T311" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U311" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U311" s="2" t="inlineStr"/>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="2" t="n">
         <v>141.9</v>
@@ -24121,9 +23429,7 @@
       <c r="T312" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U312" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U312" s="2" t="inlineStr"/>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="2" t="n">
         <v>140.9</v>
@@ -24196,9 +23502,7 @@
       <c r="T313" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U313" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U313" s="2" t="inlineStr"/>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="2" t="n">
         <v>140.8</v>
@@ -24271,9 +23575,7 @@
       <c r="T314" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U314" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U314" s="2" t="inlineStr"/>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="2" t="n">
         <v>139.6</v>
@@ -24346,9 +23648,7 @@
       <c r="T315" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U315" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U315" s="2" t="inlineStr"/>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="2" t="n">
         <v>139.1</v>
@@ -24421,9 +23721,7 @@
       <c r="T316" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U316" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U316" s="2" t="inlineStr"/>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>139.6</v>
@@ -24496,9 +23794,7 @@
       <c r="T317" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U317" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U317" s="2" t="inlineStr"/>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="2" t="n">
         <v>138.2</v>
@@ -24571,9 +23867,7 @@
       <c r="T318" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U318" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U318" s="2" t="inlineStr"/>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="2" t="n">
         <v>141.9</v>
@@ -24646,9 +23940,7 @@
       <c r="T319" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U319" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U319" s="2" t="inlineStr"/>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="2" t="n">
         <v>143.3</v>
@@ -24721,9 +24013,7 @@
       <c r="T320" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U320" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U320" s="2" t="inlineStr"/>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="2" t="n">
         <v>141.4</v>
@@ -24796,9 +24086,7 @@
       <c r="T321" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U321" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U321" s="2" t="inlineStr"/>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="2" t="n">
         <v>141.7</v>
@@ -24871,9 +24159,7 @@
       <c r="T322" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U322" s="2" t="inlineStr"/>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="2" t="n">
         <v>138.7</v>
@@ -24946,9 +24232,7 @@
       <c r="T323" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U323" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U323" s="2" t="inlineStr"/>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="2" t="n">
         <v>135.4</v>
@@ -25021,9 +24305,7 @@
       <c r="T324" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U324" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U324" s="2" t="inlineStr"/>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="2" t="n">
         <v>136.1</v>
@@ -25096,9 +24378,7 @@
       <c r="T325" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U325" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U325" s="2" t="inlineStr"/>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="2" t="n">
         <v>138.2</v>
@@ -25171,9 +24451,7 @@
       <c r="T326" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U326" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U326" s="2" t="inlineStr"/>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="2" t="n">
         <v>140.2</v>
@@ -25246,9 +24524,7 @@
       <c r="T327" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U327" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U327" s="2" t="inlineStr"/>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="2" t="n">
         <v>139.4</v>
@@ -25321,9 +24597,7 @@
       <c r="T328" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U328" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U328" s="2" t="inlineStr"/>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="2" t="n">
         <v>141.5</v>
@@ -25396,9 +24670,7 @@
       <c r="T329" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U329" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U329" s="2" t="inlineStr"/>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="2" t="n">
         <v>139.3</v>
@@ -25471,9 +24743,7 @@
       <c r="T330" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U330" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U330" s="2" t="inlineStr"/>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="2" t="n">
         <v>145.8</v>
@@ -25546,9 +24816,7 @@
       <c r="T331" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U331" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U331" s="2" t="inlineStr"/>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="2" t="n">
         <v>138.4</v>
@@ -25621,9 +24889,7 @@
       <c r="T332" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U332" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U332" s="2" t="inlineStr"/>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="2" t="n">
         <v>135.5</v>
@@ -25696,9 +24962,7 @@
       <c r="T333" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U333" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U333" s="2" t="inlineStr"/>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="2" t="n">
         <v>132.3</v>
@@ -25771,9 +25035,7 @@
       <c r="T334" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U334" s="2" t="n">
-        <v>14</v>
-      </c>
+      <c r="U334" s="2" t="inlineStr"/>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="2" t="n">
         <v>137</v>
@@ -25846,9 +25108,7 @@
       <c r="T335" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U335" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U335" s="2" t="inlineStr"/>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="2" t="n">
         <v>137.4</v>
@@ -25921,9 +25181,7 @@
       <c r="T336" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U336" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U336" s="2" t="inlineStr"/>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="2" t="n">
         <v>139</v>
@@ -25996,9 +25254,7 @@
       <c r="T337" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U337" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U337" s="2" t="inlineStr"/>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="2" t="n">
         <v>138.6</v>
@@ -26071,9 +25327,7 @@
       <c r="T338" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U338" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U338" s="2" t="inlineStr"/>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="2" t="n">
         <v>139.5</v>
@@ -26146,9 +25400,7 @@
       <c r="T339" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U339" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U339" s="2" t="inlineStr"/>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="2" t="n">
         <v>144.2</v>
@@ -26221,9 +25473,7 @@
       <c r="T340" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U340" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U340" s="2" t="inlineStr"/>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="2" t="n">
         <v>142.5</v>
@@ -26296,9 +25546,7 @@
       <c r="T341" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U341" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U341" s="2" t="inlineStr"/>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="2" t="n">
         <v>143.2</v>
@@ -26371,9 +25619,7 @@
       <c r="T342" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U342" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U342" s="2" t="inlineStr"/>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="2" t="n">
         <v>136.9</v>
@@ -26446,9 +25692,7 @@
       <c r="T343" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U343" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U343" s="2" t="inlineStr"/>
       <c r="V343" t="inlineStr"/>
       <c r="W343" s="2" t="n">
         <v>142.1</v>
@@ -26525,9 +25769,7 @@
       <c r="T344" s="5" t="n">
         <v>21.5</v>
       </c>
-      <c r="U344" s="7" t="n">
-        <v>28.7</v>
-      </c>
+      <c r="U344" s="5" t="inlineStr"/>
       <c r="V344" s="3" t="inlineStr"/>
       <c r="W344" s="5" t="n">
         <v>152.2</v>
@@ -26600,9 +25842,7 @@
       <c r="T345" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U345" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U345" s="2" t="inlineStr"/>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="2" t="n">
         <v>145</v>
@@ -26679,9 +25919,7 @@
       <c r="T346" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U346" s="2" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="U346" s="2" t="inlineStr"/>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="2" t="n">
         <v>142</v>
@@ -26754,9 +25992,7 @@
       <c r="T347" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="U347" s="2" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U347" s="2" t="inlineStr"/>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="2" t="n">
         <v>143.1</v>
@@ -26829,9 +26065,7 @@
       <c r="T348" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U348" s="2" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="U348" s="2" t="inlineStr"/>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="2" t="n">
         <v>143</v>
@@ -26904,9 +26138,7 @@
       <c r="T349" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U349" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U349" s="2" t="inlineStr"/>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>142.6</v>
@@ -26979,9 +26211,7 @@
       <c r="T350" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U350" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U350" s="2" t="inlineStr"/>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="2" t="n">
         <v>144.3</v>
@@ -27054,9 +26284,7 @@
       <c r="T351" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U351" s="5" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U351" s="5" t="inlineStr"/>
       <c r="V351" s="3" t="inlineStr"/>
       <c r="W351" s="5" t="n">
         <v>142.7</v>
@@ -27129,9 +26357,7 @@
       <c r="T352" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U352" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U352" s="2" t="inlineStr"/>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="2" t="n">
         <v>142.6</v>
@@ -27204,9 +26430,7 @@
       <c r="T353" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U353" s="2" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="U353" s="2" t="inlineStr"/>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="2" t="n">
         <v>146.7</v>
@@ -27279,9 +26503,7 @@
       <c r="T354" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U354" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U354" s="2" t="inlineStr"/>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="2" t="n">
         <v>141.9</v>
@@ -27358,9 +26580,7 @@
       <c r="T355" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U355" s="5" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U355" s="5" t="inlineStr"/>
       <c r="V355" s="3" t="inlineStr"/>
       <c r="W355" s="5" t="n">
         <v>143.1</v>
@@ -27433,9 +26653,7 @@
       <c r="T356" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U356" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U356" s="2" t="inlineStr"/>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="2" t="n">
         <v>145.3</v>
@@ -27508,9 +26726,7 @@
       <c r="T357" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U357" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U357" s="2" t="inlineStr"/>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="2" t="n">
         <v>139.9</v>
@@ -27587,9 +26803,7 @@
       <c r="T358" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U358" s="5" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="U358" s="5" t="inlineStr"/>
       <c r="V358" s="3" t="inlineStr"/>
       <c r="W358" s="5" t="n">
         <v>139.4</v>
@@ -27662,9 +26876,7 @@
       <c r="T359" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U359" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U359" s="2" t="inlineStr"/>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="2" t="n">
         <v>144.5</v>
@@ -27737,9 +26949,7 @@
       <c r="T360" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U360" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U360" s="2" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="2" t="n">
         <v>149.6</v>
@@ -27816,9 +27026,7 @@
       <c r="T361" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U361" s="5" t="n">
-        <v>13</v>
-      </c>
+      <c r="U361" s="5" t="inlineStr"/>
       <c r="V361" s="3" t="inlineStr"/>
       <c r="W361" s="5" t="n">
         <v>154.8</v>
@@ -27891,9 +27099,7 @@
       <c r="T362" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U362" s="5" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U362" s="5" t="inlineStr"/>
       <c r="V362" s="3" t="inlineStr"/>
       <c r="W362" s="5" t="n">
         <v>150</v>
@@ -27966,9 +27172,7 @@
       <c r="T363" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U363" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="U363" s="2" t="inlineStr"/>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="2" t="n">
         <v>145.4</v>
@@ -28045,9 +27249,7 @@
       <c r="T364" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U364" s="5" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U364" s="5" t="inlineStr"/>
       <c r="V364" s="3" t="inlineStr"/>
       <c r="W364" s="5" t="n">
         <v>145.7</v>
@@ -28120,9 +27322,7 @@
       <c r="T365" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U365" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U365" s="2" t="inlineStr"/>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="2" t="n">
         <v>149.8</v>
@@ -28195,9 +27395,7 @@
       <c r="T366" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U366" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U366" s="2" t="inlineStr"/>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="2" t="n">
         <v>144.7</v>
@@ -28270,9 +27468,7 @@
       <c r="T367" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U367" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U367" s="2" t="inlineStr"/>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="2" t="n">
         <v>144.3</v>
@@ -28349,9 +27545,7 @@
       <c r="T368" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U368" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U368" s="2" t="inlineStr"/>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="2" t="n">
         <v>145.7</v>
@@ -28424,9 +27618,7 @@
       <c r="T369" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U369" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U369" s="2" t="inlineStr"/>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="2" t="n">
         <v>145.1</v>
@@ -28499,9 +27691,7 @@
       <c r="T370" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U370" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U370" s="2" t="inlineStr"/>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="2" t="n">
         <v>148.5</v>
@@ -28574,9 +27764,7 @@
       <c r="T371" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U371" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U371" s="2" t="inlineStr"/>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="2" t="n">
         <v>145.7</v>
@@ -28649,9 +27837,7 @@
       <c r="T372" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U372" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U372" s="2" t="inlineStr"/>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="2" t="n">
         <v>147.3</v>
@@ -31564,7 +30750,7 @@
         <v>101.13</v>
       </c>
       <c r="G412" s="3" t="n">
-        <v>100374100</v>
+        <v>101135900</v>
       </c>
       <c r="H412" s="4" t="n">
         <v>-16.98</v>
@@ -31638,31 +30824,31 @@
         <v>100.96</v>
       </c>
       <c r="F413" t="n">
-        <v>101.89</v>
+        <v>102.32</v>
       </c>
       <c r="G413" t="n">
-        <v>45177782</v>
+        <v>56370700</v>
       </c>
       <c r="H413" s="6" t="n">
-        <v>0.75</v>
+        <v>1.18</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" t="n">
-        <v>115.46</v>
+        <v>115.49</v>
       </c>
       <c r="K413" t="n">
-        <v>149.41</v>
+        <v>149.42</v>
       </c>
       <c r="L413" t="n">
-        <v>149.23</v>
+        <v>149.24</v>
       </c>
       <c r="M413" t="n">
-        <v>111.24</v>
+        <v>111.25</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>41.89</v>
+        <v>42.19</v>
       </c>
       <c r="O413" t="n">
         <v>29</v>
@@ -31679,16 +30865,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>14.8</v>
+        <v>17.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -30741,28 +30741,44 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="D412" t="n">
+        <v>105.94</v>
+      </c>
+      <c r="E412" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="F412" t="n">
+        <v>102.32</v>
+      </c>
       <c r="G412" t="n">
-        <v>56370700</v>
-      </c>
-      <c r="H412" s="5" t="n">
-        <v>0</v>
+        <v>56701600</v>
+      </c>
+      <c r="H412" s="4" t="n">
+        <v>1.18</v>
       </c>
       <c r="I412" t="n">
         <v>14.3</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>115.49</v>
+      </c>
+      <c r="K412" t="n">
+        <v>149.42</v>
+      </c>
+      <c r="L412" t="n">
+        <v>149.24</v>
+      </c>
+      <c r="M412" t="n">
+        <v>111.25</v>
+      </c>
       <c r="N412" s="5" t="n">
-        <v>41.37</v>
+        <v>42.19</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30797,13 +30797,84 @@
       <c r="T412" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="5" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U412" s="5" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="5" t="n">
         <v>146.6</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>107.44</v>
+      </c>
+      <c r="D413" t="n">
+        <v>109.32</v>
+      </c>
+      <c r="E413" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="F413" t="n">
+        <v>108.13</v>
+      </c>
+      <c r="G413" t="n">
+        <v>27412593</v>
+      </c>
+      <c r="H413" s="4" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="I413" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>114.44</v>
+      </c>
+      <c r="K413" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="L413" t="n">
+        <v>149.66</v>
+      </c>
+      <c r="M413" t="n">
+        <v>111.59</v>
+      </c>
+      <c r="N413" s="5" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T413" s="5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U413" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -30754,7 +30754,7 @@
         <v>102.32</v>
       </c>
       <c r="G412" t="n">
-        <v>56701600</v>
+        <v>57147000</v>
       </c>
       <c r="H412" s="4" t="n">
         <v>1.18</v>
@@ -30821,37 +30821,37 @@
         <v>109.32</v>
       </c>
       <c r="E413" t="n">
-        <v>106.25</v>
+        <v>101.07</v>
       </c>
       <c r="F413" t="n">
-        <v>108.13</v>
+        <v>103.31</v>
       </c>
       <c r="G413" t="n">
-        <v>27412593</v>
+        <v>65804936</v>
       </c>
       <c r="H413" s="4" t="n">
-        <v>5.68</v>
+        <v>0.97</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" t="n">
-        <v>114.44</v>
+        <v>114.2</v>
       </c>
       <c r="K413" t="n">
-        <v>146.21</v>
+        <v>146.12</v>
       </c>
       <c r="L413" t="n">
-        <v>149.66</v>
+        <v>149.62</v>
       </c>
       <c r="M413" t="n">
-        <v>111.59</v>
+        <v>111.57</v>
       </c>
       <c r="N413" s="5" t="n">
-        <v>45.31</v>
+        <v>42.23</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30865,13 +30865,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.96</v>
+        <v>5.01</v>
       </c>
       <c r="T413" s="5" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="U413" s="5" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="5" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -13493,7 +13493,7 @@
         <v>33.95</v>
       </c>
       <c r="K177" t="n">
-        <v>28.99</v>
+        <v>29</v>
       </c>
       <c r="L177" t="n">
         <v>23.73</v>
@@ -15926,7 +15926,7 @@
         <v>41.98</v>
       </c>
       <c r="K210" t="n">
-        <v>37.06</v>
+        <v>37.05</v>
       </c>
       <c r="L210" t="n">
         <v>31.1</v>
@@ -30824,31 +30824,31 @@
         <v>101.07</v>
       </c>
       <c r="F413" t="n">
-        <v>103.31</v>
+        <v>103.97</v>
       </c>
       <c r="G413" t="n">
-        <v>65804936</v>
+        <v>73053066</v>
       </c>
       <c r="H413" s="4" t="n">
-        <v>0.97</v>
+        <v>1.61</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" t="n">
-        <v>114.2</v>
+        <v>114.23</v>
       </c>
       <c r="K413" t="n">
-        <v>146.12</v>
+        <v>146.14</v>
       </c>
       <c r="L413" t="n">
-        <v>149.62</v>
+        <v>149.63</v>
       </c>
       <c r="M413" t="n">
         <v>111.57</v>
       </c>
       <c r="N413" s="5" t="n">
-        <v>42.23</v>
+        <v>42.67</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>
@@ -30868,13 +30868,15 @@
         <v>5.01</v>
       </c>
       <c r="T413" s="5" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="U413" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="5" t="inlineStr"/>
+      <c r="W413" s="5" t="n">
+        <v>145.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -30814,41 +30814,25 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>107.44</v>
-      </c>
-      <c r="D413" t="n">
-        <v>109.32</v>
-      </c>
-      <c r="E413" t="n">
-        <v>101.07</v>
-      </c>
-      <c r="F413" t="n">
-        <v>103.97</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
         <v>73053066</v>
       </c>
-      <c r="H413" s="4" t="n">
-        <v>1.61</v>
+      <c r="H413" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
-      <c r="J413" t="n">
-        <v>114.23</v>
-      </c>
-      <c r="K413" t="n">
-        <v>146.14</v>
-      </c>
-      <c r="L413" t="n">
-        <v>149.63</v>
-      </c>
-      <c r="M413" t="n">
-        <v>111.57</v>
-      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" s="5" t="n">
-        <v>42.67</v>
+        <v>41.55</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -30814,25 +30814,41 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>107.44</v>
+      </c>
+      <c r="D413" t="n">
+        <v>109.32</v>
+      </c>
+      <c r="E413" t="n">
+        <v>101.06</v>
+      </c>
+      <c r="F413" t="n">
+        <v>103.97</v>
+      </c>
       <c r="G413" t="n">
-        <v>73053066</v>
-      </c>
-      <c r="H413" s="5" t="n">
-        <v>0</v>
+        <v>73053600</v>
+      </c>
+      <c r="H413" s="4" t="n">
+        <v>1.61</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>114.23</v>
+      </c>
+      <c r="K413" t="n">
+        <v>146.14</v>
+      </c>
+      <c r="L413" t="n">
+        <v>149.63</v>
+      </c>
+      <c r="M413" t="n">
+        <v>111.57</v>
+      </c>
       <c r="N413" s="5" t="n">
-        <v>41.55</v>
+        <v>42.67</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30851,7 +30851,7 @@
         <v>42.67</v>
       </c>
       <c r="O413" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30870,13 +30870,84 @@
       <c r="T413" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="5" t="n">
-        <v>17</v>
-      </c>
+      <c r="U413" s="5" t="inlineStr"/>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="5" t="n">
         <v>145.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>113.33</v>
+      </c>
+      <c r="D414" t="n">
+        <v>115.48</v>
+      </c>
+      <c r="E414" t="n">
+        <v>112.01</v>
+      </c>
+      <c r="F414" t="n">
+        <v>115.21</v>
+      </c>
+      <c r="G414" t="n">
+        <v>41040341</v>
+      </c>
+      <c r="H414" s="4" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>113.95</v>
+      </c>
+      <c r="K414" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="L414" t="n">
+        <v>150.18</v>
+      </c>
+      <c r="M414" t="n">
+        <v>111.94</v>
+      </c>
+      <c r="N414" s="5" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T414" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U414" s="5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -30827,7 +30827,7 @@
         <v>103.97</v>
       </c>
       <c r="G413" t="n">
-        <v>73053600</v>
+        <v>74637500</v>
       </c>
       <c r="H413" s="4" t="n">
         <v>1.61</v>
@@ -30897,22 +30897,22 @@
         <v>112.01</v>
       </c>
       <c r="F414" t="n">
-        <v>115.21</v>
+        <v>114.82</v>
       </c>
       <c r="G414" t="n">
-        <v>41040341</v>
+        <v>55751188</v>
       </c>
       <c r="H414" s="4" t="n">
-        <v>10.81</v>
+        <v>10.44</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>113.95</v>
+        <v>113.93</v>
       </c>
       <c r="K414" t="n">
-        <v>144.2</v>
+        <v>144.19</v>
       </c>
       <c r="L414" t="n">
         <v>150.18</v>
@@ -30921,7 +30921,7 @@
         <v>111.94</v>
       </c>
       <c r="N414" s="5" t="n">
-        <v>45.69</v>
+        <v>45.46</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>
@@ -30941,13 +30941,15 @@
         <v>4.95</v>
       </c>
       <c r="T414" s="5" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="U414" s="5" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="5" t="inlineStr"/>
+      <c r="W414" s="5" t="n">
+        <v>145.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -30900,7 +30900,7 @@
         <v>114.82</v>
       </c>
       <c r="G414" t="n">
-        <v>55751188</v>
+        <v>56121200</v>
       </c>
       <c r="H414" s="4" t="n">
         <v>10.44</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30924,7 +30924,7 @@
         <v>45.46</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -30943,13 +30943,84 @@
       <c r="T414" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="5" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U414" s="5" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="5" t="n">
         <v>145.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>117.03</v>
+      </c>
+      <c r="D415" t="n">
+        <v>119.71</v>
+      </c>
+      <c r="E415" t="n">
+        <v>116.91</v>
+      </c>
+      <c r="F415" t="n">
+        <v>118.87</v>
+      </c>
+      <c r="G415" t="n">
+        <v>17044967</v>
+      </c>
+      <c r="H415" s="4" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I415" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>113.77</v>
+      </c>
+      <c r="K415" t="n">
+        <v>142.35</v>
+      </c>
+      <c r="L415" t="n">
+        <v>150.78</v>
+      </c>
+      <c r="M415" t="n">
+        <v>112.33</v>
+      </c>
+      <c r="N415" s="5" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="O415" t="n">
+        <v>29</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U415" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -649,7 +649,9 @@
       <c r="T2" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V2" s="1" t="inlineStr"/>
       <c r="W2" s="2" t="n">
         <v>168.6</v>
@@ -722,7 +724,9 @@
       <c r="T3" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="6" t="n">
         <v>163.6</v>
@@ -795,7 +799,9 @@
       <c r="T4" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="6" t="n">
         <v>157.4</v>
@@ -868,7 +874,9 @@
       <c r="T5" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="6" t="n">
         <v>156.7</v>
@@ -941,7 +949,9 @@
       <c r="T6" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="6" t="n">
         <v>158.5</v>
@@ -1014,7 +1024,9 @@
       <c r="T7" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="6" t="n">
         <v>155.4</v>
@@ -1087,7 +1099,9 @@
       <c r="T8" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="6" t="n">
         <v>159.4</v>
@@ -1160,7 +1174,9 @@
       <c r="T9" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="6" t="n">
         <v>162.6</v>
@@ -1233,7 +1249,9 @@
       <c r="T10" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="U10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="6" t="n">
         <v>163.6</v>
@@ -1306,7 +1324,9 @@
       <c r="T11" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="6" t="n">
         <v>166.5</v>
@@ -1379,7 +1399,9 @@
       <c r="T12" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U12" s="5" t="inlineStr"/>
+      <c r="U12" s="5" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="6" t="n">
         <v>166.9</v>
@@ -1456,7 +1478,9 @@
       <c r="T13" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U13" s="5" t="inlineStr"/>
+      <c r="U13" s="5" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="6" t="n">
         <v>168.8</v>
@@ -1533,7 +1557,9 @@
       <c r="T14" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U14" s="5" t="inlineStr"/>
+      <c r="U14" s="5" t="n">
+        <v>12.8</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="6" t="n">
         <v>166.1</v>
@@ -1606,7 +1632,9 @@
       <c r="T15" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U15" s="5" t="inlineStr"/>
+      <c r="U15" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="6" t="n">
         <v>163.4</v>
@@ -1679,7 +1707,9 @@
       <c r="T16" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="6" t="n">
         <v>168</v>
@@ -1752,7 +1782,9 @@
       <c r="T17" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="6" t="n">
         <v>183.1</v>
@@ -1825,7 +1857,9 @@
       <c r="T18" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="6" t="n">
         <v>175.8</v>
@@ -1898,7 +1932,9 @@
       <c r="T19" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U19" s="5" t="inlineStr"/>
+      <c r="U19" s="5" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="6" t="n">
         <v>178.6</v>
@@ -1975,7 +2011,9 @@
       <c r="T20" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="6" t="n">
         <v>165</v>
@@ -2052,7 +2090,9 @@
       <c r="T21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="6" t="n">
         <v>156.9</v>
@@ -2125,7 +2165,9 @@
       <c r="T22" s="5" t="n">
         <v>19.4</v>
       </c>
-      <c r="U22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="6" t="n">
         <v>157.6</v>
@@ -2198,7 +2240,9 @@
       <c r="T23" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U23" s="5" t="inlineStr"/>
+      <c r="U23" s="5" t="n">
+        <v>20.5</v>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="5" t="n">
         <v>153.4</v>
@@ -2271,7 +2315,9 @@
       <c r="T24" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="U24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V24" s="1" t="inlineStr"/>
       <c r="W24" s="3" t="n">
         <v>149.3</v>
@@ -2344,7 +2390,9 @@
       <c r="T25" s="5" t="n">
         <v>19.6</v>
       </c>
-      <c r="U25" s="5" t="inlineStr"/>
+      <c r="U25" s="5" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="6" t="n">
         <v>157.9</v>
@@ -2417,7 +2465,9 @@
       <c r="T26" s="5" t="n">
         <v>22.8</v>
       </c>
-      <c r="U26" s="5" t="inlineStr"/>
+      <c r="U26" s="5" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="5" t="n">
         <v>154.3</v>
@@ -2490,7 +2540,9 @@
       <c r="T27" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="U27" s="5" t="inlineStr"/>
+      <c r="U27" s="5" t="n">
+        <v>24.6</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="5" t="n">
         <v>151.4</v>
@@ -2563,7 +2615,9 @@
       <c r="T28" s="5" t="n">
         <v>21.9</v>
       </c>
-      <c r="U28" s="5" t="inlineStr"/>
+      <c r="U28" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="5" t="n">
         <v>138.9</v>
@@ -2640,7 +2694,9 @@
       <c r="T29" s="5" t="n">
         <v>24.9</v>
       </c>
-      <c r="U29" s="5" t="inlineStr"/>
+      <c r="U29" s="4" t="n">
+        <v>31.1</v>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="5" t="n">
         <v>137.6</v>
@@ -2713,7 +2769,9 @@
       <c r="T30" s="5" t="n">
         <v>23.4</v>
       </c>
-      <c r="U30" s="5" t="inlineStr"/>
+      <c r="U30" s="5" t="n">
+        <v>24.7</v>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="5" t="n">
         <v>139.9</v>
@@ -2790,8 +2848,14 @@
       <c r="T31" s="4" t="n">
         <v>27.9</v>
       </c>
-      <c r="U31" s="5" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" s="4" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W31" s="5" t="n">
         <v>146</v>
       </c>
@@ -2867,8 +2931,14 @@
       <c r="T32" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" s="4" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W32" s="5" t="n">
         <v>132.8</v>
       </c>
@@ -2944,7 +3014,9 @@
       <c r="T33" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U33" s="5" t="inlineStr"/>
+      <c r="U33" s="5" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" s="5" t="n">
         <v>128.7</v>
@@ -3021,7 +3093,9 @@
       <c r="T34" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="U34" s="5" t="inlineStr"/>
+      <c r="U34" s="5" t="n">
+        <v>23.4</v>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="5" t="n">
         <v>128.9</v>
@@ -3094,7 +3168,9 @@
       <c r="T35" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="U35" s="5" t="inlineStr"/>
+      <c r="U35" s="5" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="5" t="n">
         <v>130.3</v>
@@ -3167,7 +3243,9 @@
       <c r="T36" s="5" t="n">
         <v>20.5</v>
       </c>
-      <c r="U36" s="5" t="inlineStr"/>
+      <c r="U36" s="5" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="5" t="n">
         <v>133.9</v>
@@ -3240,7 +3318,9 @@
       <c r="T37" s="5" t="n">
         <v>21.7</v>
       </c>
-      <c r="U37" s="5" t="inlineStr"/>
+      <c r="U37" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="5" t="n">
         <v>136.8</v>
@@ -3313,7 +3393,9 @@
       <c r="T38" s="5" t="n">
         <v>19.9</v>
       </c>
-      <c r="U38" s="5" t="inlineStr"/>
+      <c r="U38" s="5" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="5" t="n">
         <v>136.4</v>
@@ -3386,7 +3468,9 @@
       <c r="T39" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="U39" s="5" t="inlineStr"/>
+      <c r="U39" s="5" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="5" t="n">
         <v>140.8</v>
@@ -3459,7 +3543,9 @@
       <c r="T40" s="5" t="n">
         <v>19.3</v>
       </c>
-      <c r="U40" s="5" t="inlineStr"/>
+      <c r="U40" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="5" t="n">
         <v>141.7</v>
@@ -3532,7 +3618,9 @@
       <c r="T41" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U41" s="5" t="inlineStr"/>
+      <c r="U41" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="5" t="n">
         <v>144</v>
@@ -3605,7 +3693,9 @@
       <c r="T42" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U42" s="5" t="inlineStr"/>
+      <c r="U42" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="5" t="n">
         <v>148.7</v>
@@ -3682,7 +3772,9 @@
       <c r="T43" s="5" t="n">
         <v>18.3</v>
       </c>
-      <c r="U43" s="5" t="inlineStr"/>
+      <c r="U43" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="5" t="n">
         <v>144.8</v>
@@ -3755,7 +3847,9 @@
       <c r="T44" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U44" s="5" t="inlineStr"/>
+      <c r="U44" s="5" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="5" t="n">
         <v>140.9</v>
@@ -3828,7 +3922,9 @@
       <c r="T45" s="5" t="n">
         <v>21.6</v>
       </c>
-      <c r="U45" s="5" t="inlineStr"/>
+      <c r="U45" s="4" t="n">
+        <v>25.4</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="5" t="n">
         <v>139</v>
@@ -3901,7 +3997,9 @@
       <c r="T46" s="5" t="n">
         <v>22.3</v>
       </c>
-      <c r="U46" s="5" t="inlineStr"/>
+      <c r="U46" s="5" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="5" t="n">
         <v>148.6</v>
@@ -3974,7 +4072,9 @@
       <c r="T47" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="U47" s="5" t="inlineStr"/>
+      <c r="U47" s="5" t="n">
+        <v>20.1</v>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="5" t="n">
         <v>143</v>
@@ -4047,7 +4147,9 @@
       <c r="T48" s="5" t="n">
         <v>21.5</v>
       </c>
-      <c r="U48" s="5" t="inlineStr"/>
+      <c r="U48" s="4" t="n">
+        <v>26.7</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="5" t="n">
         <v>144.3</v>
@@ -4124,8 +4226,14 @@
       <c r="T49" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="U49" s="3" t="inlineStr"/>
-      <c r="V49" s="1" t="inlineStr"/>
+      <c r="U49" s="7" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="V49" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W49" s="3" t="n">
         <v>139.2</v>
       </c>
@@ -4201,8 +4309,14 @@
       <c r="T50" s="7" t="n">
         <v>45.3</v>
       </c>
-      <c r="U50" s="3" t="inlineStr"/>
-      <c r="V50" s="1" t="inlineStr"/>
+      <c r="U50" s="7" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="V50" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W50" s="3" t="n">
         <v>136.5</v>
       </c>
@@ -4278,8 +4392,14 @@
       <c r="T51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="U51" s="5" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="U51" s="4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W51" s="5" t="n">
         <v>133.8</v>
       </c>
@@ -4355,8 +4475,14 @@
       <c r="T52" s="4" t="n">
         <v>52.3</v>
       </c>
-      <c r="U52" s="5" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" s="4" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="V52" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W52" s="5" t="n">
         <v>135.7</v>
       </c>
@@ -4428,8 +4554,14 @@
       <c r="T53" s="4" t="n">
         <v>33.6</v>
       </c>
-      <c r="U53" s="5" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="U53" s="4" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="V53" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W53" s="5" t="n">
         <v>142.2</v>
       </c>
@@ -4505,8 +4637,14 @@
       <c r="T54" s="7" t="n">
         <v>40.7</v>
       </c>
-      <c r="U54" s="3" t="inlineStr"/>
-      <c r="V54" s="1" t="inlineStr"/>
+      <c r="U54" s="7" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="V54" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W54" s="3" t="n">
         <v>127.5</v>
       </c>
@@ -4582,8 +4720,14 @@
       <c r="T55" s="4" t="n">
         <v>37.6</v>
       </c>
-      <c r="U55" s="5" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="U55" s="4" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V55" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W55" s="5" t="n">
         <v>128.6</v>
       </c>
@@ -4659,7 +4803,9 @@
       <c r="T56" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="U56" s="5" t="inlineStr"/>
+      <c r="U56" s="4" t="n">
+        <v>28.5</v>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" s="5" t="n">
         <v>135.7</v>
@@ -4732,7 +4878,9 @@
       <c r="T57" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="U57" s="5" t="inlineStr"/>
+      <c r="U57" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="5" t="n">
         <v>135.8</v>
@@ -4809,8 +4957,14 @@
       <c r="T58" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="U58" s="5" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="U58" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V58" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W58" s="5" t="n">
         <v>131.3</v>
       </c>
@@ -4882,8 +5036,14 @@
       <c r="T59" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="U59" s="5" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="U59" s="4" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V59" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W59" s="5" t="n">
         <v>130</v>
       </c>
@@ -4955,7 +5115,9 @@
       <c r="T60" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="U60" s="5" t="inlineStr"/>
+      <c r="U60" s="4" t="n">
+        <v>30.6</v>
+      </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" s="4" t="n">
         <v>125.8</v>
@@ -5028,7 +5190,9 @@
       <c r="T61" s="4" t="n">
         <v>30.6</v>
       </c>
-      <c r="U61" s="5" t="inlineStr"/>
+      <c r="U61" s="4" t="n">
+        <v>29.1</v>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="4" t="n">
         <v>125.9</v>
@@ -5101,8 +5265,14 @@
       <c r="T62" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="U62" s="5" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="U62" s="4" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="V62" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W62" s="4" t="n">
         <v>126.7</v>
       </c>
@@ -5174,7 +5344,9 @@
       <c r="T63" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="U63" s="5" t="inlineStr"/>
+      <c r="U63" s="4" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" s="5" t="n">
         <v>129</v>
@@ -5247,7 +5419,9 @@
       <c r="T64" s="5" t="n">
         <v>24.8</v>
       </c>
-      <c r="U64" s="5" t="inlineStr"/>
+      <c r="U64" s="5" t="n">
+        <v>23.6</v>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="5" t="n">
         <v>132.4</v>
@@ -5320,7 +5494,9 @@
       <c r="T65" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="U65" s="5" t="inlineStr"/>
+      <c r="U65" s="5" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="5" t="n">
         <v>131.3</v>
@@ -5393,7 +5569,9 @@
       <c r="T66" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U66" s="5" t="inlineStr"/>
+      <c r="U66" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="5" t="n">
         <v>134.3</v>
@@ -5466,7 +5644,9 @@
       <c r="T67" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="U67" s="5" t="inlineStr"/>
+      <c r="U67" s="5" t="n">
+        <v>22.9</v>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="5" t="n">
         <v>132.7</v>
@@ -5539,7 +5719,9 @@
       <c r="T68" s="5" t="n">
         <v>24.6</v>
       </c>
-      <c r="U68" s="5" t="inlineStr"/>
+      <c r="U68" s="4" t="n">
+        <v>27.5</v>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="5" t="n">
         <v>134.1</v>
@@ -5612,7 +5794,9 @@
       <c r="T69" s="5" t="n">
         <v>22.7</v>
       </c>
-      <c r="U69" s="5" t="inlineStr"/>
+      <c r="U69" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="5" t="n">
         <v>134.8</v>
@@ -5685,7 +5869,9 @@
       <c r="T70" s="5" t="n">
         <v>23.6</v>
       </c>
-      <c r="U70" s="5" t="inlineStr"/>
+      <c r="U70" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="5" t="n">
         <v>134.1</v>
@@ -5758,7 +5944,9 @@
       <c r="T71" s="5" t="n">
         <v>24.8</v>
       </c>
-      <c r="U71" s="5" t="inlineStr"/>
+      <c r="U71" s="5" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="5" t="n">
         <v>133.2</v>
@@ -5831,7 +6019,9 @@
       <c r="T72" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="U72" s="5" t="inlineStr"/>
+      <c r="U72" s="5" t="n">
+        <v>19.8</v>
+      </c>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="5" t="n">
         <v>132.2</v>
@@ -5904,7 +6094,9 @@
       <c r="T73" s="5" t="n">
         <v>22.5</v>
       </c>
-      <c r="U73" s="5" t="inlineStr"/>
+      <c r="U73" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="5" t="n">
         <v>131.5</v>
@@ -5977,7 +6169,9 @@
       <c r="T74" s="5" t="n">
         <v>21.9</v>
       </c>
-      <c r="U74" s="5" t="inlineStr"/>
+      <c r="U74" s="4" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="5" t="n">
         <v>128.4</v>
@@ -6050,7 +6244,9 @@
       <c r="T75" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U75" s="5" t="inlineStr"/>
+      <c r="U75" s="5" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="5" t="n">
         <v>137.7</v>
@@ -6123,7 +6319,9 @@
       <c r="T76" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U76" s="5" t="inlineStr"/>
+      <c r="U76" s="5" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="5" t="n">
         <v>140.5</v>
@@ -6196,7 +6394,9 @@
       <c r="T77" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U77" s="5" t="inlineStr"/>
+      <c r="U77" s="5" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="5" t="n">
         <v>138.9</v>
@@ -6269,7 +6469,9 @@
       <c r="T78" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U78" s="5" t="inlineStr"/>
+      <c r="U78" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="5" t="n">
         <v>140.9</v>
@@ -6342,7 +6544,9 @@
       <c r="T79" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U79" s="5" t="inlineStr"/>
+      <c r="U79" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="5" t="n">
         <v>136</v>
@@ -6415,7 +6619,9 @@
       <c r="T80" s="5" t="n">
         <v>18.1</v>
       </c>
-      <c r="U80" s="5" t="inlineStr"/>
+      <c r="U80" s="5" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="5" t="n">
         <v>135.9</v>
@@ -6488,7 +6694,9 @@
       <c r="T81" s="5" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="5" t="inlineStr"/>
+      <c r="U81" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="5" t="n">
         <v>137.3</v>
@@ -6561,7 +6769,9 @@
       <c r="T82" s="5" t="n">
         <v>20.9</v>
       </c>
-      <c r="U82" s="5" t="inlineStr"/>
+      <c r="U82" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="5" t="n">
         <v>137.3</v>
@@ -6634,7 +6844,9 @@
       <c r="T83" s="5" t="n">
         <v>20.3</v>
       </c>
-      <c r="U83" s="5" t="inlineStr"/>
+      <c r="U83" s="5" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="5" t="n">
         <v>139</v>
@@ -6707,7 +6919,9 @@
       <c r="T84" s="5" t="n">
         <v>22.3</v>
       </c>
-      <c r="U84" s="5" t="inlineStr"/>
+      <c r="U84" s="5" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="5" t="n">
         <v>139.3</v>
@@ -6780,7 +6994,9 @@
       <c r="T85" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U85" s="5" t="inlineStr"/>
+      <c r="U85" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="5" t="n">
         <v>140.9</v>
@@ -6853,7 +7069,9 @@
       <c r="T86" s="5" t="n">
         <v>19.3</v>
       </c>
-      <c r="U86" s="5" t="inlineStr"/>
+      <c r="U86" s="5" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="5" t="n">
         <v>137.6</v>
@@ -6926,7 +7144,9 @@
       <c r="T87" s="5" t="n">
         <v>19.2</v>
       </c>
-      <c r="U87" s="5" t="inlineStr"/>
+      <c r="U87" s="5" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="5" t="n">
         <v>137.3</v>
@@ -7003,7 +7223,9 @@
       <c r="T88" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U88" s="5" t="inlineStr"/>
+      <c r="U88" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="5" t="n">
         <v>138.2</v>
@@ -7076,7 +7298,9 @@
       <c r="T89" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U89" s="5" t="inlineStr"/>
+      <c r="U89" s="5" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="5" t="n">
         <v>141</v>
@@ -7149,7 +7373,9 @@
       <c r="T90" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U90" s="5" t="inlineStr"/>
+      <c r="U90" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="5" t="n">
         <v>141.6</v>
@@ -7222,7 +7448,9 @@
       <c r="T91" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U91" s="5" t="inlineStr"/>
+      <c r="U91" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="5" t="n">
         <v>137.5</v>
@@ -7295,7 +7523,9 @@
       <c r="T92" s="5" t="n">
         <v>18.5</v>
       </c>
-      <c r="U92" s="5" t="inlineStr"/>
+      <c r="U92" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="5" t="n">
         <v>140.1</v>
@@ -7368,7 +7598,9 @@
       <c r="T93" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U93" s="5" t="inlineStr"/>
+      <c r="U93" s="5" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="5" t="n">
         <v>138.9</v>
@@ -7441,7 +7673,9 @@
       <c r="T94" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U94" s="5" t="inlineStr"/>
+      <c r="U94" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="5" t="n">
         <v>139.2</v>
@@ -7514,7 +7748,9 @@
       <c r="T95" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U95" s="5" t="inlineStr"/>
+      <c r="U95" s="5" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="5" t="n">
         <v>141.2</v>
@@ -7587,7 +7823,9 @@
       <c r="T96" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U96" s="5" t="inlineStr"/>
+      <c r="U96" s="5" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="5" t="n">
         <v>141.4</v>
@@ -7660,7 +7898,9 @@
       <c r="T97" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U97" s="5" t="inlineStr"/>
+      <c r="U97" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="5" t="n">
         <v>145.6</v>
@@ -7737,7 +7977,9 @@
       <c r="T98" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U98" s="5" t="inlineStr"/>
+      <c r="U98" s="5" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="5" t="n">
         <v>149.6</v>
@@ -7810,7 +8052,9 @@
       <c r="T99" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U99" s="5" t="inlineStr"/>
+      <c r="U99" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="6" t="n">
         <v>156.6</v>
@@ -7883,7 +8127,9 @@
       <c r="T100" s="5" t="n">
         <v>21.6</v>
       </c>
-      <c r="U100" s="5" t="inlineStr"/>
+      <c r="U100" s="5" t="n">
+        <v>21</v>
+      </c>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="5" t="n">
         <v>154.4</v>
@@ -7956,7 +8202,9 @@
       <c r="T101" s="5" t="n">
         <v>20.1</v>
       </c>
-      <c r="U101" s="5" t="inlineStr"/>
+      <c r="U101" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="5" t="n">
         <v>148.4</v>
@@ -8029,7 +8277,9 @@
       <c r="T102" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="U102" s="5" t="inlineStr"/>
+      <c r="U102" s="5" t="n">
+        <v>18.4</v>
+      </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="5" t="n">
         <v>149.2</v>
@@ -8102,7 +8352,9 @@
       <c r="T103" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="U103" s="5" t="inlineStr"/>
+      <c r="U103" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="5" t="n">
         <v>154.8</v>
@@ -8175,7 +8427,9 @@
       <c r="T104" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U104" s="5" t="inlineStr"/>
+      <c r="U104" s="5" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="6" t="n">
         <v>155</v>
@@ -8248,7 +8502,9 @@
       <c r="T105" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U105" s="5" t="inlineStr"/>
+      <c r="U105" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="5" t="n">
         <v>152.2</v>
@@ -8321,7 +8577,9 @@
       <c r="T106" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U106" s="5" t="inlineStr"/>
+      <c r="U106" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="5" t="n">
         <v>147.5</v>
@@ -8394,7 +8652,9 @@
       <c r="T107" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U107" s="5" t="inlineStr"/>
+      <c r="U107" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="5" t="n">
         <v>143.4</v>
@@ -8467,7 +8727,9 @@
       <c r="T108" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U108" s="5" t="inlineStr"/>
+      <c r="U108" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="5" t="n">
         <v>139.6</v>
@@ -8540,7 +8802,9 @@
       <c r="T109" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U109" s="5" t="inlineStr"/>
+      <c r="U109" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="5" t="n">
         <v>140.1</v>
@@ -8613,7 +8877,9 @@
       <c r="T110" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U110" s="5" t="inlineStr"/>
+      <c r="U110" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="5" t="n">
         <v>139.3</v>
@@ -8686,7 +8952,9 @@
       <c r="T111" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U111" s="5" t="inlineStr"/>
+      <c r="U111" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="5" t="n">
         <v>141.4</v>
@@ -8759,7 +9027,9 @@
       <c r="T112" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U112" s="5" t="inlineStr"/>
+      <c r="U112" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="5" t="n">
         <v>138</v>
@@ -8832,7 +9102,9 @@
       <c r="T113" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U113" s="5" t="inlineStr"/>
+      <c r="U113" s="5" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="5" t="n">
         <v>140.8</v>
@@ -8905,7 +9177,9 @@
       <c r="T114" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U114" s="5" t="inlineStr"/>
+      <c r="U114" s="5" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="5" t="n">
         <v>141.8</v>
@@ -8978,7 +9252,9 @@
       <c r="T115" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U115" s="5" t="inlineStr"/>
+      <c r="U115" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="5" t="n">
         <v>143.3</v>
@@ -9051,7 +9327,9 @@
       <c r="T116" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U116" s="5" t="inlineStr"/>
+      <c r="U116" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="5" t="n">
         <v>145</v>
@@ -9124,7 +9402,9 @@
       <c r="T117" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U117" s="5" t="inlineStr"/>
+      <c r="U117" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="5" t="n">
         <v>147</v>
@@ -9197,7 +9477,9 @@
       <c r="T118" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U118" s="5" t="inlineStr"/>
+      <c r="U118" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="5" t="n">
         <v>143.7</v>
@@ -9270,7 +9552,9 @@
       <c r="T119" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U119" s="5" t="inlineStr"/>
+      <c r="U119" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="5" t="n">
         <v>146.7</v>
@@ -9343,7 +9627,9 @@
       <c r="T120" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U120" s="5" t="inlineStr"/>
+      <c r="U120" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="5" t="n">
         <v>151.1</v>
@@ -9416,7 +9702,9 @@
       <c r="T121" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U121" s="5" t="inlineStr"/>
+      <c r="U121" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="5" t="n">
         <v>150.4</v>
@@ -9489,7 +9777,9 @@
       <c r="T122" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U122" s="5" t="inlineStr"/>
+      <c r="U122" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="5" t="n">
         <v>154.8</v>
@@ -9562,7 +9852,9 @@
       <c r="T123" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U123" s="5" t="inlineStr"/>
+      <c r="U123" s="5" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="5" t="n">
         <v>153.4</v>
@@ -9639,7 +9931,9 @@
       <c r="T124" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U124" s="5" t="inlineStr"/>
+      <c r="U124" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="6" t="n">
         <v>159.3</v>
@@ -9712,7 +10006,9 @@
       <c r="T125" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="5" t="inlineStr"/>
+      <c r="U125" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="6" t="n">
         <v>159.4</v>
@@ -9785,7 +10081,9 @@
       <c r="T126" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U126" s="5" t="inlineStr"/>
+      <c r="U126" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="5" t="n">
         <v>145.6</v>
@@ -9858,7 +10156,9 @@
       <c r="T127" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U127" s="5" t="inlineStr"/>
+      <c r="U127" s="5" t="n">
+        <v>7.9</v>
+      </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="5" t="n">
         <v>147.6</v>
@@ -9931,7 +10231,9 @@
       <c r="T128" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U128" s="5" t="inlineStr"/>
+      <c r="U128" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="5" t="n">
         <v>149.1</v>
@@ -10004,7 +10306,9 @@
       <c r="T129" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="U129" s="5" t="inlineStr"/>
+      <c r="U129" s="5" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="5" t="n">
         <v>154.1</v>
@@ -10081,7 +10385,9 @@
       <c r="T130" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U130" s="5" t="inlineStr"/>
+      <c r="U130" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="5" t="n">
         <v>152.3</v>
@@ -10154,7 +10460,9 @@
       <c r="T131" s="5" t="n">
         <v>20.4</v>
       </c>
-      <c r="U131" s="5" t="inlineStr"/>
+      <c r="U131" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="6" t="n">
         <v>155.5</v>
@@ -10227,7 +10535,9 @@
       <c r="T132" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U132" s="5" t="inlineStr"/>
+      <c r="U132" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="6" t="n">
         <v>159.3</v>
@@ -10300,7 +10610,9 @@
       <c r="T133" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U133" s="5" t="inlineStr"/>
+      <c r="U133" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="5" t="n">
         <v>149.9</v>
@@ -10373,7 +10685,9 @@
       <c r="T134" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U134" s="5" t="inlineStr"/>
+      <c r="U134" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="5" t="n">
         <v>149.7</v>
@@ -10446,7 +10760,9 @@
       <c r="T135" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U135" s="5" t="inlineStr"/>
+      <c r="U135" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="5" t="n">
         <v>147</v>
@@ -10519,7 +10835,9 @@
       <c r="T136" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U136" s="5" t="inlineStr"/>
+      <c r="U136" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="5" t="n">
         <v>147.5</v>
@@ -10592,7 +10910,9 @@
       <c r="T137" s="5" t="n">
         <v>16.2</v>
       </c>
-      <c r="U137" s="5" t="inlineStr"/>
+      <c r="U137" s="5" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="5" t="n">
         <v>148.6</v>
@@ -10665,7 +10985,9 @@
       <c r="T138" s="5" t="n">
         <v>14.7</v>
       </c>
-      <c r="U138" s="5" t="inlineStr"/>
+      <c r="U138" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="5" t="n">
         <v>151.4</v>
@@ -10738,7 +11060,9 @@
       <c r="T139" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U139" s="5" t="inlineStr"/>
+      <c r="U139" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="5" t="n">
         <v>153.1</v>
@@ -10811,7 +11135,9 @@
       <c r="T140" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U140" s="5" t="inlineStr"/>
+      <c r="U140" s="5" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="5" t="n">
         <v>150.6</v>
@@ -10884,7 +11210,9 @@
       <c r="T141" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U141" s="5" t="inlineStr"/>
+      <c r="U141" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="5" t="n">
         <v>153.8</v>
@@ -10957,7 +11285,9 @@
       <c r="T142" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U142" s="5" t="inlineStr"/>
+      <c r="U142" s="5" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="5" t="n">
         <v>153.9</v>
@@ -11034,7 +11364,9 @@
       <c r="T143" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="U143" s="5" t="inlineStr"/>
+      <c r="U143" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="5" t="n">
         <v>153.2</v>
@@ -11107,7 +11439,9 @@
       <c r="T144" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U144" s="5" t="inlineStr"/>
+      <c r="U144" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="5" t="n">
         <v>144.6</v>
@@ -11180,7 +11514,9 @@
       <c r="T145" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U145" s="5" t="inlineStr"/>
+      <c r="U145" s="5" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="5" t="n">
         <v>144.3</v>
@@ -11253,7 +11589,9 @@
       <c r="T146" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="U146" s="5" t="inlineStr"/>
+      <c r="U146" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="5" t="n">
         <v>146.4</v>
@@ -11326,7 +11664,9 @@
       <c r="T147" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U147" s="5" t="inlineStr"/>
+      <c r="U147" s="5" t="n">
+        <v>8.1</v>
+      </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="5" t="n">
         <v>150</v>
@@ -11399,7 +11739,9 @@
       <c r="T148" s="5" t="n">
         <v>14.6</v>
       </c>
-      <c r="U148" s="5" t="inlineStr"/>
+      <c r="U148" s="5" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="6" t="n">
         <v>156.5</v>
@@ -11472,7 +11814,9 @@
       <c r="T149" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U149" s="5" t="inlineStr"/>
+      <c r="U149" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="5" t="n">
         <v>150.9</v>
@@ -11545,7 +11889,9 @@
       <c r="T150" s="5" t="n">
         <v>14.4</v>
       </c>
-      <c r="U150" s="5" t="inlineStr"/>
+      <c r="U150" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="5" t="n">
         <v>152.5</v>
@@ -11622,7 +11968,9 @@
       <c r="T151" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U151" s="5" t="inlineStr"/>
+      <c r="U151" s="5" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="5" t="n">
         <v>152.1</v>
@@ -11699,7 +12047,9 @@
       <c r="T152" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U152" s="5" t="inlineStr"/>
+      <c r="U152" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="5" t="n">
         <v>151.5</v>
@@ -11772,7 +12122,9 @@
       <c r="T153" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U153" s="5" t="inlineStr"/>
+      <c r="U153" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="5" t="n">
         <v>150.2</v>
@@ -11845,7 +12197,9 @@
       <c r="T154" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U154" s="5" t="inlineStr"/>
+      <c r="U154" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="5" t="n">
         <v>154</v>
@@ -11918,7 +12272,9 @@
       <c r="T155" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U155" s="5" t="inlineStr"/>
+      <c r="U155" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="5" t="n">
         <v>148.2</v>
@@ -11991,7 +12347,9 @@
       <c r="T156" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U156" s="5" t="inlineStr"/>
+      <c r="U156" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="5" t="n">
         <v>148.8</v>
@@ -12064,7 +12422,9 @@
       <c r="T157" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U157" s="5" t="inlineStr"/>
+      <c r="U157" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="5" t="n">
         <v>150.9</v>
@@ -12137,7 +12497,9 @@
       <c r="T158" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U158" s="5" t="inlineStr"/>
+      <c r="U158" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="5" t="n">
         <v>151.9</v>
@@ -12210,7 +12572,9 @@
       <c r="T159" s="5" t="n">
         <v>14.7</v>
       </c>
-      <c r="U159" s="5" t="inlineStr"/>
+      <c r="U159" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="5" t="n">
         <v>147.6</v>
@@ -12283,7 +12647,9 @@
       <c r="T160" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U160" s="5" t="inlineStr"/>
+      <c r="U160" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="5" t="n">
         <v>149.5</v>
@@ -12356,7 +12722,9 @@
       <c r="T161" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U161" s="5" t="inlineStr"/>
+      <c r="U161" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="5" t="n">
         <v>152.1</v>
@@ -12429,7 +12797,9 @@
       <c r="T162" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U162" s="5" t="inlineStr"/>
+      <c r="U162" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="5" t="n">
         <v>148.2</v>
@@ -12502,7 +12872,9 @@
       <c r="T163" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U163" s="5" t="inlineStr"/>
+      <c r="U163" s="5" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="5" t="n">
         <v>146.4</v>
@@ -12575,7 +12947,9 @@
       <c r="T164" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="5" t="inlineStr"/>
+      <c r="U164" s="5" t="n">
+        <v>14.4</v>
+      </c>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="5" t="n">
         <v>148.2</v>
@@ -12648,7 +13022,9 @@
       <c r="T165" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U165" s="5" t="inlineStr"/>
+      <c r="U165" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="5" t="n">
         <v>147</v>
@@ -12721,7 +13097,9 @@
       <c r="T166" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U166" s="5" t="inlineStr"/>
+      <c r="U166" s="5" t="n">
+        <v>9.1</v>
+      </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="5" t="n">
         <v>145.5</v>
@@ -12794,7 +13172,9 @@
       <c r="T167" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U167" s="5" t="inlineStr"/>
+      <c r="U167" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="5" t="n">
         <v>146.5</v>
@@ -12867,7 +13247,9 @@
       <c r="T168" s="5" t="n">
         <v>16.2</v>
       </c>
-      <c r="U168" s="5" t="inlineStr"/>
+      <c r="U168" s="5" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="5" t="n">
         <v>145.9</v>
@@ -12940,7 +13322,9 @@
       <c r="T169" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U169" s="5" t="inlineStr"/>
+      <c r="U169" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="5" t="n">
         <v>145.9</v>
@@ -13013,7 +13397,9 @@
       <c r="T170" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U170" s="5" t="inlineStr"/>
+      <c r="U170" s="5" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="5" t="n">
         <v>141.5</v>
@@ -13086,7 +13472,9 @@
       <c r="T171" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U171" s="5" t="inlineStr"/>
+      <c r="U171" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="5" t="n">
         <v>143</v>
@@ -13159,7 +13547,9 @@
       <c r="T172" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U172" s="5" t="inlineStr"/>
+      <c r="U172" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="5" t="n">
         <v>143.4</v>
@@ -13232,7 +13622,9 @@
       <c r="T173" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="5" t="inlineStr"/>
+      <c r="U173" s="5" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="5" t="n">
         <v>143.7</v>
@@ -13305,7 +13697,9 @@
       <c r="T174" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U174" s="5" t="inlineStr"/>
+      <c r="U174" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="5" t="n">
         <v>145.9</v>
@@ -13378,7 +13772,9 @@
       <c r="T175" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="5" t="inlineStr"/>
+      <c r="U175" s="5" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="5" t="n">
         <v>144.6</v>
@@ -13451,7 +13847,9 @@
       <c r="T176" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U176" s="5" t="inlineStr"/>
+      <c r="U176" s="5" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="5" t="n">
         <v>142.5</v>
@@ -13524,7 +13922,9 @@
       <c r="T177" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U177" s="5" t="inlineStr"/>
+      <c r="U177" s="5" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="5" t="n">
         <v>145.2</v>
@@ -13597,7 +13997,9 @@
       <c r="T178" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U178" s="5" t="inlineStr"/>
+      <c r="U178" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="5" t="n">
         <v>145.8</v>
@@ -13670,7 +14072,9 @@
       <c r="T179" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U179" s="5" t="inlineStr"/>
+      <c r="U179" s="5" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="5" t="n">
         <v>145.3</v>
@@ -13747,7 +14151,9 @@
       <c r="T180" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="U180" s="3" t="inlineStr"/>
+      <c r="U180" s="7" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V180" s="1" t="inlineStr"/>
       <c r="W180" s="3" t="n">
         <v>138.9</v>
@@ -13820,7 +14226,9 @@
       <c r="T181" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U181" s="5" t="inlineStr"/>
+      <c r="U181" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="5" t="n">
         <v>142.8</v>
@@ -13893,7 +14301,9 @@
       <c r="T182" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U182" s="5" t="inlineStr"/>
+      <c r="U182" s="5" t="n">
+        <v>17.7</v>
+      </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="5" t="n">
         <v>146.5</v>
@@ -13966,7 +14376,9 @@
       <c r="T183" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="U183" s="5" t="inlineStr"/>
+      <c r="U183" s="5" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="5" t="n">
         <v>145</v>
@@ -14039,7 +14451,9 @@
       <c r="T184" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="U184" s="5" t="inlineStr"/>
+      <c r="U184" s="5" t="n">
+        <v>23.8</v>
+      </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="5" t="n">
         <v>147.1</v>
@@ -14112,7 +14526,9 @@
       <c r="T185" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U185" s="5" t="inlineStr"/>
+      <c r="U185" s="5" t="n">
+        <v>17.9</v>
+      </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="5" t="n">
         <v>147.6</v>
@@ -14185,7 +14601,9 @@
       <c r="T186" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U186" s="5" t="inlineStr"/>
+      <c r="U186" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="5" t="n">
         <v>151.3</v>
@@ -14258,7 +14676,9 @@
       <c r="T187" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U187" s="5" t="inlineStr"/>
+      <c r="U187" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="5" t="n">
         <v>149.9</v>
@@ -14335,7 +14755,9 @@
       <c r="T188" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U188" s="5" t="inlineStr"/>
+      <c r="U188" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="5" t="n">
         <v>152.9</v>
@@ -14408,7 +14830,9 @@
       <c r="T189" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U189" s="5" t="inlineStr"/>
+      <c r="U189" s="5" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="5" t="n">
         <v>154.3</v>
@@ -14481,7 +14905,9 @@
       <c r="T190" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U190" s="5" t="inlineStr"/>
+      <c r="U190" s="5" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="5" t="n">
         <v>153.5</v>
@@ -14554,7 +14980,9 @@
       <c r="T191" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U191" s="5" t="inlineStr"/>
+      <c r="U191" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="5" t="n">
         <v>148.5</v>
@@ -14627,7 +15055,9 @@
       <c r="T192" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U192" s="5" t="inlineStr"/>
+      <c r="U192" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="5" t="n">
         <v>140.4</v>
@@ -14700,7 +15130,9 @@
       <c r="T193" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U193" s="5" t="inlineStr"/>
+      <c r="U193" s="5" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="5" t="n">
         <v>139.4</v>
@@ -14773,7 +15205,9 @@
       <c r="T194" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="5" t="inlineStr"/>
+      <c r="U194" s="5" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="5" t="n">
         <v>141.1</v>
@@ -14846,7 +15280,9 @@
       <c r="T195" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U195" s="5" t="inlineStr"/>
+      <c r="U195" s="5" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="5" t="n">
         <v>142.8</v>
@@ -14919,7 +15355,9 @@
       <c r="T196" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U196" s="5" t="inlineStr"/>
+      <c r="U196" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="5" t="n">
         <v>142</v>
@@ -14992,7 +15430,9 @@
       <c r="T197" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U197" s="5" t="inlineStr"/>
+      <c r="U197" s="5" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="5" t="n">
         <v>144</v>
@@ -15065,7 +15505,9 @@
       <c r="T198" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U198" s="5" t="inlineStr"/>
+      <c r="U198" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="5" t="n">
         <v>143.6</v>
@@ -15138,7 +15580,9 @@
       <c r="T199" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U199" s="5" t="inlineStr"/>
+      <c r="U199" s="5" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="5" t="n">
         <v>143.5</v>
@@ -15215,7 +15659,9 @@
       <c r="T200" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U200" s="5" t="inlineStr"/>
+      <c r="U200" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="5" t="n">
         <v>141.3</v>
@@ -15288,7 +15734,9 @@
       <c r="T201" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U201" s="5" t="inlineStr"/>
+      <c r="U201" s="5" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="5" t="n">
         <v>142.9</v>
@@ -15365,7 +15813,9 @@
       <c r="T202" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U202" s="5" t="inlineStr"/>
+      <c r="U202" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="5" t="n">
         <v>143.4</v>
@@ -15438,7 +15888,9 @@
       <c r="T203" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U203" s="5" t="inlineStr"/>
+      <c r="U203" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="5" t="n">
         <v>138.6</v>
@@ -15511,7 +15963,9 @@
       <c r="T204" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="U204" s="5" t="inlineStr"/>
+      <c r="U204" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="5" t="n">
         <v>142.5</v>
@@ -15584,7 +16038,9 @@
       <c r="T205" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="U205" s="5" t="inlineStr"/>
+      <c r="U205" s="5" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="5" t="n">
         <v>137.9</v>
@@ -15657,7 +16113,9 @@
       <c r="T206" s="5" t="n">
         <v>22.4</v>
       </c>
-      <c r="U206" s="5" t="inlineStr"/>
+      <c r="U206" s="5" t="n">
+        <v>19.4</v>
+      </c>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="5" t="n">
         <v>140.9</v>
@@ -15734,7 +16192,9 @@
       <c r="T207" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="U207" s="5" t="inlineStr"/>
+      <c r="U207" s="5" t="n">
+        <v>20.9</v>
+      </c>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="5" t="n">
         <v>143</v>
@@ -15807,7 +16267,9 @@
       <c r="T208" s="5" t="n">
         <v>23.7</v>
       </c>
-      <c r="U208" s="5" t="inlineStr"/>
+      <c r="U208" s="4" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="5" t="n">
         <v>143.1</v>
@@ -15884,8 +16346,14 @@
       <c r="T209" s="7" t="n">
         <v>26.4</v>
       </c>
-      <c r="U209" s="3" t="inlineStr"/>
-      <c r="V209" s="1" t="inlineStr"/>
+      <c r="U209" s="7" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V209" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W209" s="3" t="n">
         <v>145</v>
       </c>
@@ -15957,7 +16425,9 @@
       <c r="T210" s="5" t="n">
         <v>23.4</v>
       </c>
-      <c r="U210" s="5" t="inlineStr"/>
+      <c r="U210" s="5" t="n">
+        <v>23.3</v>
+      </c>
       <c r="V210" t="inlineStr"/>
       <c r="W210" s="5" t="n">
         <v>148.3</v>
@@ -16030,7 +16500,9 @@
       <c r="T211" s="5" t="n">
         <v>20.5</v>
       </c>
-      <c r="U211" s="5" t="inlineStr"/>
+      <c r="U211" s="5" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="5" t="n">
         <v>148.6</v>
@@ -16103,7 +16575,9 @@
       <c r="T212" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U212" s="5" t="inlineStr"/>
+      <c r="U212" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="5" t="n">
         <v>151.7</v>
@@ -16176,7 +16650,9 @@
       <c r="T213" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U213" s="5" t="inlineStr"/>
+      <c r="U213" s="5" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="5" t="n">
         <v>145</v>
@@ -16249,7 +16725,9 @@
       <c r="T214" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U214" s="5" t="inlineStr"/>
+      <c r="U214" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="5" t="n">
         <v>143</v>
@@ -16322,7 +16800,9 @@
       <c r="T215" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U215" s="5" t="inlineStr"/>
+      <c r="U215" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="5" t="n">
         <v>144.9</v>
@@ -16395,7 +16875,9 @@
       <c r="T216" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U216" s="5" t="inlineStr"/>
+      <c r="U216" s="5" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="5" t="n">
         <v>144.9</v>
@@ -16468,7 +16950,9 @@
       <c r="T217" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U217" s="5" t="inlineStr"/>
+      <c r="U217" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="5" t="n">
         <v>149.2</v>
@@ -16541,7 +17025,9 @@
       <c r="T218" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U218" s="5" t="inlineStr"/>
+      <c r="U218" s="5" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="5" t="n">
         <v>148.9</v>
@@ -16614,7 +17100,9 @@
       <c r="T219" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U219" s="5" t="inlineStr"/>
+      <c r="U219" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="5" t="n">
         <v>148.8</v>
@@ -16687,7 +17175,9 @@
       <c r="T220" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U220" s="5" t="inlineStr"/>
+      <c r="U220" s="5" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="5" t="n">
         <v>150.6</v>
@@ -16760,7 +17250,9 @@
       <c r="T221" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U221" s="5" t="inlineStr"/>
+      <c r="U221" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="5" t="n">
         <v>150.3</v>
@@ -16833,7 +17325,9 @@
       <c r="T222" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U222" s="5" t="inlineStr"/>
+      <c r="U222" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="5" t="n">
         <v>147.6</v>
@@ -16906,7 +17400,9 @@
       <c r="T223" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U223" s="5" t="inlineStr"/>
+      <c r="U223" s="5" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="5" t="n">
         <v>148.3</v>
@@ -16979,7 +17475,9 @@
       <c r="T224" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U224" s="3" t="inlineStr"/>
+      <c r="U224" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V224" s="1" t="inlineStr"/>
       <c r="W224" s="3" t="n">
         <v>153.6</v>
@@ -17052,7 +17550,9 @@
       <c r="T225" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U225" s="5" t="inlineStr"/>
+      <c r="U225" s="5" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="6" t="n">
         <v>161.9</v>
@@ -17129,7 +17629,9 @@
       <c r="T226" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="5" t="inlineStr"/>
+      <c r="U226" s="5" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="6" t="n">
         <v>157</v>
@@ -17202,7 +17704,9 @@
       <c r="T227" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U227" s="5" t="inlineStr"/>
+      <c r="U227" s="5" t="n">
+        <v>16.9</v>
+      </c>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="5" t="n">
         <v>153.5</v>
@@ -17275,7 +17779,9 @@
       <c r="T228" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U228" s="5" t="inlineStr"/>
+      <c r="U228" s="5" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="6" t="n">
         <v>155.4</v>
@@ -17348,7 +17854,9 @@
       <c r="T229" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U229" s="5" t="inlineStr"/>
+      <c r="U229" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="6" t="n">
         <v>155.9</v>
@@ -17421,7 +17929,9 @@
       <c r="T230" s="5" t="n">
         <v>14.1</v>
       </c>
-      <c r="U230" s="5" t="inlineStr"/>
+      <c r="U230" s="5" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="6" t="n">
         <v>159.9</v>
@@ -17494,7 +18004,9 @@
       <c r="T231" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="U231" s="5" t="inlineStr"/>
+      <c r="U231" s="5" t="n">
+        <v>7.6</v>
+      </c>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="6" t="n">
         <v>160.5</v>
@@ -17567,7 +18079,9 @@
       <c r="T232" s="5" t="n">
         <v>13.5</v>
       </c>
-      <c r="U232" s="5" t="inlineStr"/>
+      <c r="U232" s="5" t="n">
+        <v>7.4</v>
+      </c>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="6" t="n">
         <v>160.5</v>
@@ -17640,7 +18154,9 @@
       <c r="T233" s="5" t="n">
         <v>13.6</v>
       </c>
-      <c r="U233" s="5" t="inlineStr"/>
+      <c r="U233" s="5" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="5" t="n">
         <v>151.4</v>
@@ -17713,7 +18229,9 @@
       <c r="T234" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="U234" s="5" t="inlineStr"/>
+      <c r="U234" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="5" t="n">
         <v>150.5</v>
@@ -17790,7 +18308,9 @@
       <c r="T235" s="5" t="n">
         <v>14.3</v>
       </c>
-      <c r="U235" s="5" t="inlineStr"/>
+      <c r="U235" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="5" t="n">
         <v>148.3</v>
@@ -17863,7 +18383,9 @@
       <c r="T236" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U236" s="5" t="inlineStr"/>
+      <c r="U236" s="5" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="5" t="n">
         <v>148.7</v>
@@ -17936,7 +18458,9 @@
       <c r="T237" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U237" s="5" t="inlineStr"/>
+      <c r="U237" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="5" t="n">
         <v>141.9</v>
@@ -18009,7 +18533,9 @@
       <c r="T238" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U238" s="5" t="inlineStr"/>
+      <c r="U238" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="5" t="n">
         <v>142.4</v>
@@ -18082,7 +18608,9 @@
       <c r="T239" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U239" s="5" t="inlineStr"/>
+      <c r="U239" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="5" t="n">
         <v>146.2</v>
@@ -18155,7 +18683,9 @@
       <c r="T240" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U240" s="5" t="inlineStr"/>
+      <c r="U240" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="5" t="n">
         <v>143.6</v>
@@ -18228,7 +18758,9 @@
       <c r="T241" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="5" t="inlineStr"/>
+      <c r="U241" s="5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="5" t="n">
         <v>147.1</v>
@@ -18301,7 +18833,9 @@
       <c r="T242" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U242" s="5" t="inlineStr"/>
+      <c r="U242" s="5" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="5" t="n">
         <v>146</v>
@@ -18374,7 +18908,9 @@
       <c r="T243" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U243" s="5" t="inlineStr"/>
+      <c r="U243" s="5" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="5" t="n">
         <v>149.8</v>
@@ -18447,7 +18983,9 @@
       <c r="T244" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U244" s="5" t="inlineStr"/>
+      <c r="U244" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="5" t="n">
         <v>151.6</v>
@@ -18520,7 +19058,9 @@
       <c r="T245" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U245" s="5" t="inlineStr"/>
+      <c r="U245" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="5" t="n">
         <v>152.5</v>
@@ -18593,7 +19133,9 @@
       <c r="T246" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U246" s="5" t="inlineStr"/>
+      <c r="U246" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="5" t="n">
         <v>151.6</v>
@@ -18666,7 +19208,9 @@
       <c r="T247" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U247" s="5" t="inlineStr"/>
+      <c r="U247" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="5" t="n">
         <v>153.6</v>
@@ -18739,7 +19283,9 @@
       <c r="T248" s="5" t="n">
         <v>20.1</v>
       </c>
-      <c r="U248" s="5" t="inlineStr"/>
+      <c r="U248" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="6" t="n">
         <v>155</v>
@@ -18812,7 +19358,9 @@
       <c r="T249" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U249" s="5" t="inlineStr"/>
+      <c r="U249" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="5" t="n">
         <v>144.4</v>
@@ -18885,7 +19433,9 @@
       <c r="T250" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="U250" s="5" t="inlineStr"/>
+      <c r="U250" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="5" t="n">
         <v>141.3</v>
@@ -18958,7 +19508,9 @@
       <c r="T251" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U251" s="5" t="inlineStr"/>
+      <c r="U251" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="5" t="n">
         <v>144</v>
@@ -19031,7 +19583,9 @@
       <c r="T252" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="5" t="inlineStr"/>
+      <c r="U252" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="5" t="n">
         <v>148.1</v>
@@ -19104,7 +19658,9 @@
       <c r="T253" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U253" s="5" t="inlineStr"/>
+      <c r="U253" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="5" t="n">
         <v>147.2</v>
@@ -19177,7 +19733,9 @@
       <c r="T254" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="5" t="inlineStr"/>
+      <c r="U254" s="5" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="5" t="n">
         <v>145</v>
@@ -19250,7 +19808,9 @@
       <c r="T255" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U255" s="5" t="inlineStr"/>
+      <c r="U255" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="5" t="n">
         <v>143.7</v>
@@ -19323,7 +19883,9 @@
       <c r="T256" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U256" s="5" t="inlineStr"/>
+      <c r="U256" s="5" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="5" t="n">
         <v>143.6</v>
@@ -19396,7 +19958,9 @@
       <c r="T257" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U257" s="5" t="inlineStr"/>
+      <c r="U257" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="5" t="n">
         <v>146.6</v>
@@ -19469,7 +20033,9 @@
       <c r="T258" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U258" s="5" t="inlineStr"/>
+      <c r="U258" s="5" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="5" t="n">
         <v>143.9</v>
@@ -19546,7 +20112,9 @@
       <c r="T259" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U259" s="5" t="inlineStr"/>
+      <c r="U259" s="5" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="5" t="n">
         <v>143.2</v>
@@ -19619,7 +20187,9 @@
       <c r="T260" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="U260" s="5" t="inlineStr"/>
+      <c r="U260" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="5" t="n">
         <v>137.2</v>
@@ -19692,7 +20262,9 @@
       <c r="T261" s="5" t="n">
         <v>20.4</v>
       </c>
-      <c r="U261" s="5" t="inlineStr"/>
+      <c r="U261" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="5" t="n">
         <v>140.3</v>
@@ -19765,7 +20337,9 @@
       <c r="T262" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U262" s="5" t="inlineStr"/>
+      <c r="U262" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="5" t="n">
         <v>145.2</v>
@@ -19838,7 +20412,9 @@
       <c r="T263" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U263" s="5" t="inlineStr"/>
+      <c r="U263" s="5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="5" t="n">
         <v>145.7</v>
@@ -19911,7 +20487,9 @@
       <c r="T264" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U264" s="5" t="inlineStr"/>
+      <c r="U264" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="5" t="n">
         <v>143.8</v>
@@ -19984,7 +20562,9 @@
       <c r="T265" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U265" s="5" t="inlineStr"/>
+      <c r="U265" s="5" t="n">
+        <v>21.5</v>
+      </c>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="5" t="n">
         <v>142.5</v>
@@ -20057,7 +20637,9 @@
       <c r="T266" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="U266" s="5" t="inlineStr"/>
+      <c r="U266" s="5" t="n">
+        <v>22.4</v>
+      </c>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="5" t="n">
         <v>139.4</v>
@@ -20130,7 +20712,9 @@
       <c r="T267" s="5" t="n">
         <v>20.3</v>
       </c>
-      <c r="U267" s="5" t="inlineStr"/>
+      <c r="U267" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="5" t="n">
         <v>140.3</v>
@@ -20203,7 +20787,9 @@
       <c r="T268" s="5" t="n">
         <v>19.6</v>
       </c>
-      <c r="U268" s="5" t="inlineStr"/>
+      <c r="U268" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="5" t="n">
         <v>139.2</v>
@@ -20276,7 +20862,9 @@
       <c r="T269" s="5" t="n">
         <v>20.2</v>
       </c>
-      <c r="U269" s="5" t="inlineStr"/>
+      <c r="U269" s="5" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="5" t="n">
         <v>141.2</v>
@@ -20349,7 +20937,9 @@
       <c r="T270" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U270" s="5" t="inlineStr"/>
+      <c r="U270" s="5" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="5" t="n">
         <v>145.5</v>
@@ -20422,7 +21012,9 @@
       <c r="T271" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="U271" s="5" t="inlineStr"/>
+      <c r="U271" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="5" t="n">
         <v>141.4</v>
@@ -20495,7 +21087,9 @@
       <c r="T272" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U272" s="5" t="inlineStr"/>
+      <c r="U272" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="5" t="n">
         <v>141.9</v>
@@ -20568,7 +21162,9 @@
       <c r="T273" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U273" s="5" t="inlineStr"/>
+      <c r="U273" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="5" t="n">
         <v>146.1</v>
@@ -20641,7 +21237,9 @@
       <c r="T274" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U274" s="5" t="inlineStr"/>
+      <c r="U274" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="5" t="n">
         <v>146.6</v>
@@ -20718,7 +21316,9 @@
       <c r="T275" s="5" t="n">
         <v>19.9</v>
       </c>
-      <c r="U275" s="5" t="inlineStr"/>
+      <c r="U275" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="5" t="n">
         <v>146.7</v>
@@ -20791,7 +21391,9 @@
       <c r="T276" s="5" t="n">
         <v>21.4</v>
       </c>
-      <c r="U276" s="5" t="inlineStr"/>
+      <c r="U276" s="5" t="n">
+        <v>16.3</v>
+      </c>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="5" t="n">
         <v>151.8</v>
@@ -20868,7 +21470,9 @@
       <c r="T277" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="U277" s="3" t="inlineStr"/>
+      <c r="U277" s="3" t="n">
+        <v>20.3</v>
+      </c>
       <c r="V277" s="1" t="inlineStr"/>
       <c r="W277" s="3" t="n">
         <v>152.8</v>
@@ -20941,7 +21545,9 @@
       <c r="T278" s="5" t="n">
         <v>21.1</v>
       </c>
-      <c r="U278" s="5" t="inlineStr"/>
+      <c r="U278" s="5" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="5" t="n">
         <v>152.9</v>
@@ -21018,7 +21624,9 @@
       <c r="T279" s="5" t="n">
         <v>23.8</v>
       </c>
-      <c r="U279" s="5" t="inlineStr"/>
+      <c r="U279" s="5" t="n">
+        <v>21.9</v>
+      </c>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="5" t="n">
         <v>153.9</v>
@@ -21091,8 +21699,14 @@
       <c r="T280" s="4" t="n">
         <v>29.5</v>
       </c>
-      <c r="U280" s="5" t="inlineStr"/>
-      <c r="V280" t="inlineStr"/>
+      <c r="U280" s="4" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="V280" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W280" s="5" t="n">
         <v>151.8</v>
       </c>
@@ -21164,7 +21778,9 @@
       <c r="T281" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="U281" s="5" t="inlineStr"/>
+      <c r="U281" s="5" t="n">
+        <v>22.7</v>
+      </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" s="6" t="n">
         <v>158</v>
@@ -21237,7 +21853,9 @@
       <c r="T282" s="5" t="n">
         <v>24.9</v>
       </c>
-      <c r="U282" s="5" t="inlineStr"/>
+      <c r="U282" s="5" t="n">
+        <v>21.3</v>
+      </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="5" t="n">
         <v>154.5</v>
@@ -21310,7 +21928,9 @@
       <c r="T283" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U283" s="5" t="inlineStr"/>
+      <c r="U283" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="5" t="n">
         <v>152.4</v>
@@ -21381,7 +22001,9 @@
       <c r="T284" s="4" t="n">
         <v>27.3</v>
       </c>
-      <c r="U284" s="5" t="inlineStr"/>
+      <c r="U284" s="5" t="n">
+        <v>24.2</v>
+      </c>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="5" t="n">
         <v>139.9</v>
@@ -21454,8 +22076,14 @@
       <c r="T285" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="U285" s="5" t="inlineStr"/>
-      <c r="V285" t="inlineStr"/>
+      <c r="U285" s="4" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="V285" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W285" s="5" t="n">
         <v>137.8</v>
       </c>
@@ -21527,7 +22155,9 @@
       <c r="T286" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="U286" s="5" t="inlineStr"/>
+      <c r="U286" s="5" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V286" t="inlineStr"/>
       <c r="W286" s="5" t="n">
         <v>141.5</v>
@@ -21600,7 +22230,9 @@
       <c r="T287" s="5" t="n">
         <v>22.4</v>
       </c>
-      <c r="U287" s="5" t="inlineStr"/>
+      <c r="U287" s="5" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="5" t="n">
         <v>145</v>
@@ -21673,7 +22305,9 @@
       <c r="T288" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="U288" s="5" t="inlineStr"/>
+      <c r="U288" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="5" t="n">
         <v>136.5</v>
@@ -21746,7 +22380,9 @@
       <c r="T289" s="5" t="n">
         <v>24.1</v>
       </c>
-      <c r="U289" s="5" t="inlineStr"/>
+      <c r="U289" s="5" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="5" t="n">
         <v>138.3</v>
@@ -21819,8 +22455,14 @@
       <c r="T290" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="U290" s="5" t="inlineStr"/>
-      <c r="V290" t="inlineStr"/>
+      <c r="U290" s="4" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V290" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W290" s="5" t="n">
         <v>139.1</v>
       </c>
@@ -21892,7 +22534,9 @@
       <c r="T291" s="4" t="n">
         <v>26.1</v>
       </c>
-      <c r="U291" s="5" t="inlineStr"/>
+      <c r="U291" s="5" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V291" t="inlineStr"/>
       <c r="W291" s="5" t="n">
         <v>142</v>
@@ -21965,7 +22609,9 @@
       <c r="T292" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="U292" s="5" t="inlineStr"/>
+      <c r="U292" s="5" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="5" t="n">
         <v>142.6</v>
@@ -22038,7 +22684,9 @@
       <c r="T293" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="U293" s="5" t="inlineStr"/>
+      <c r="U293" s="5" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="5" t="n">
         <v>140.9</v>
@@ -22115,7 +22763,9 @@
       <c r="T294" s="4" t="n">
         <v>27.4</v>
       </c>
-      <c r="U294" s="5" t="inlineStr"/>
+      <c r="U294" s="5" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="5" t="n">
         <v>144</v>
@@ -22188,8 +22838,14 @@
       <c r="T295" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="U295" s="5" t="inlineStr"/>
-      <c r="V295" t="inlineStr"/>
+      <c r="U295" s="4" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="V295" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W295" s="5" t="n">
         <v>139</v>
       </c>
@@ -22261,7 +22917,9 @@
       <c r="T296" s="4" t="n">
         <v>30.6</v>
       </c>
-      <c r="U296" s="5" t="inlineStr"/>
+      <c r="U296" s="5" t="n">
+        <v>23</v>
+      </c>
       <c r="V296" t="inlineStr"/>
       <c r="W296" s="5" t="n">
         <v>142.2</v>
@@ -22334,7 +22992,9 @@
       <c r="T297" s="4" t="n">
         <v>25.2</v>
       </c>
-      <c r="U297" s="5" t="inlineStr"/>
+      <c r="U297" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="5" t="n">
         <v>145.4</v>
@@ -22407,7 +23067,9 @@
       <c r="T298" s="5" t="n">
         <v>24.5</v>
       </c>
-      <c r="U298" s="5" t="inlineStr"/>
+      <c r="U298" s="5" t="n">
+        <v>23</v>
+      </c>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="5" t="n">
         <v>143.8</v>
@@ -22480,7 +23142,9 @@
       <c r="T299" s="5" t="n">
         <v>23.9</v>
       </c>
-      <c r="U299" s="5" t="inlineStr"/>
+      <c r="U299" s="4" t="n">
+        <v>27.6</v>
+      </c>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="5" t="n">
         <v>146.9</v>
@@ -22553,7 +23217,9 @@
       <c r="T300" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U300" s="5" t="inlineStr"/>
+      <c r="U300" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="5" t="n">
         <v>147.6</v>
@@ -22626,8 +23292,14 @@
       <c r="T301" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="U301" s="5" t="inlineStr"/>
-      <c r="V301" t="inlineStr"/>
+      <c r="U301" s="4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V301" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W301" s="5" t="n">
         <v>148.4</v>
       </c>
@@ -22699,7 +23371,9 @@
       <c r="T302" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="U302" s="5" t="inlineStr"/>
+      <c r="U302" s="5" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V302" t="inlineStr"/>
       <c r="W302" s="5" t="n">
         <v>150.4</v>
@@ -22772,7 +23446,9 @@
       <c r="T303" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U303" s="5" t="inlineStr"/>
+      <c r="U303" s="5" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="5" t="n">
         <v>143.3</v>
@@ -22845,7 +23521,9 @@
       <c r="T304" s="5" t="n">
         <v>19.2</v>
       </c>
-      <c r="U304" s="5" t="inlineStr"/>
+      <c r="U304" s="5" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="5" t="n">
         <v>144.2</v>
@@ -22918,7 +23596,9 @@
       <c r="T305" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U305" s="5" t="inlineStr"/>
+      <c r="U305" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="6" t="n">
         <v>156.9</v>
@@ -22991,7 +23671,9 @@
       <c r="T306" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U306" s="5" t="inlineStr"/>
+      <c r="U306" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="5" t="n">
         <v>149.9</v>
@@ -23064,7 +23746,9 @@
       <c r="T307" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U307" s="5" t="inlineStr"/>
+      <c r="U307" s="5" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="5" t="n">
         <v>139.2</v>
@@ -23137,7 +23821,9 @@
       <c r="T308" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U308" s="5" t="inlineStr"/>
+      <c r="U308" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="5" t="n">
         <v>140.7</v>
@@ -23210,7 +23896,9 @@
       <c r="T309" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U309" s="5" t="inlineStr"/>
+      <c r="U309" s="5" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="5" t="n">
         <v>141.8</v>
@@ -23283,7 +23971,9 @@
       <c r="T310" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U310" s="5" t="inlineStr"/>
+      <c r="U310" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="5" t="n">
         <v>141.9</v>
@@ -23356,7 +24046,9 @@
       <c r="T311" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U311" s="5" t="inlineStr"/>
+      <c r="U311" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="5" t="n">
         <v>140.9</v>
@@ -23429,7 +24121,9 @@
       <c r="T312" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U312" s="5" t="inlineStr"/>
+      <c r="U312" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="5" t="n">
         <v>140.8</v>
@@ -23502,7 +24196,9 @@
       <c r="T313" s="5" t="n">
         <v>19.3</v>
       </c>
-      <c r="U313" s="5" t="inlineStr"/>
+      <c r="U313" s="5" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="5" t="n">
         <v>139.6</v>
@@ -23575,7 +24271,9 @@
       <c r="T314" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U314" s="5" t="inlineStr"/>
+      <c r="U314" s="5" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="5" t="n">
         <v>139.1</v>
@@ -23648,7 +24346,9 @@
       <c r="T315" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U315" s="5" t="inlineStr"/>
+      <c r="U315" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="5" t="n">
         <v>139.6</v>
@@ -23721,7 +24421,9 @@
       <c r="T316" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U316" s="5" t="inlineStr"/>
+      <c r="U316" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="5" t="n">
         <v>138.2</v>
@@ -23794,7 +24496,9 @@
       <c r="T317" s="5" t="n">
         <v>18.8</v>
       </c>
-      <c r="U317" s="5" t="inlineStr"/>
+      <c r="U317" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="5" t="n">
         <v>141.9</v>
@@ -23867,7 +24571,9 @@
       <c r="T318" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U318" s="5" t="inlineStr"/>
+      <c r="U318" s="5" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="5" t="n">
         <v>143.3</v>
@@ -23940,7 +24646,9 @@
       <c r="T319" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U319" s="5" t="inlineStr"/>
+      <c r="U319" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="5" t="n">
         <v>141.4</v>
@@ -24013,7 +24721,9 @@
       <c r="T320" s="5" t="n">
         <v>18.3</v>
       </c>
-      <c r="U320" s="5" t="inlineStr"/>
+      <c r="U320" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="5" t="n">
         <v>141.7</v>
@@ -24086,7 +24796,9 @@
       <c r="T321" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U321" s="5" t="inlineStr"/>
+      <c r="U321" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="5" t="n">
         <v>138.7</v>
@@ -24159,7 +24871,9 @@
       <c r="T322" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="5" t="inlineStr"/>
+      <c r="U322" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="5" t="n">
         <v>135.4</v>
@@ -24232,7 +24946,9 @@
       <c r="T323" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U323" s="5" t="inlineStr"/>
+      <c r="U323" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="5" t="n">
         <v>136.1</v>
@@ -24305,7 +25021,9 @@
       <c r="T324" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U324" s="5" t="inlineStr"/>
+      <c r="U324" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="5" t="n">
         <v>138.2</v>
@@ -24378,7 +25096,9 @@
       <c r="T325" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U325" s="5" t="inlineStr"/>
+      <c r="U325" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="5" t="n">
         <v>140.2</v>
@@ -24451,7 +25171,9 @@
       <c r="T326" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U326" s="5" t="inlineStr"/>
+      <c r="U326" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="5" t="n">
         <v>139.4</v>
@@ -24524,7 +25246,9 @@
       <c r="T327" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U327" s="5" t="inlineStr"/>
+      <c r="U327" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="5" t="n">
         <v>141.5</v>
@@ -24597,7 +25321,9 @@
       <c r="T328" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U328" s="5" t="inlineStr"/>
+      <c r="U328" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="5" t="n">
         <v>139.3</v>
@@ -24670,7 +25396,9 @@
       <c r="T329" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U329" s="5" t="inlineStr"/>
+      <c r="U329" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="5" t="n">
         <v>145.8</v>
@@ -24743,7 +25471,9 @@
       <c r="T330" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U330" s="5" t="inlineStr"/>
+      <c r="U330" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="5" t="n">
         <v>138.4</v>
@@ -24816,7 +25546,9 @@
       <c r="T331" s="5" t="n">
         <v>18.1</v>
       </c>
-      <c r="U331" s="5" t="inlineStr"/>
+      <c r="U331" s="5" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="5" t="n">
         <v>135.5</v>
@@ -24889,7 +25621,9 @@
       <c r="T332" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U332" s="5" t="inlineStr"/>
+      <c r="U332" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="5" t="n">
         <v>132.3</v>
@@ -24962,7 +25696,9 @@
       <c r="T333" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U333" s="5" t="inlineStr"/>
+      <c r="U333" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="5" t="n">
         <v>137</v>
@@ -25035,7 +25771,9 @@
       <c r="T334" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U334" s="5" t="inlineStr"/>
+      <c r="U334" s="5" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="5" t="n">
         <v>137.4</v>
@@ -25108,7 +25846,9 @@
       <c r="T335" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U335" s="5" t="inlineStr"/>
+      <c r="U335" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="5" t="n">
         <v>139</v>
@@ -25181,7 +25921,9 @@
       <c r="T336" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U336" s="5" t="inlineStr"/>
+      <c r="U336" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="5" t="n">
         <v>138.6</v>
@@ -25254,7 +25996,9 @@
       <c r="T337" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U337" s="5" t="inlineStr"/>
+      <c r="U337" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="5" t="n">
         <v>139.5</v>
@@ -25327,7 +26071,9 @@
       <c r="T338" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U338" s="5" t="inlineStr"/>
+      <c r="U338" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="5" t="n">
         <v>144.2</v>
@@ -25400,7 +26146,9 @@
       <c r="T339" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U339" s="5" t="inlineStr"/>
+      <c r="U339" s="5" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="5" t="n">
         <v>142.5</v>
@@ -25473,7 +26221,9 @@
       <c r="T340" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U340" s="5" t="inlineStr"/>
+      <c r="U340" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="5" t="n">
         <v>143.2</v>
@@ -25546,7 +26296,9 @@
       <c r="T341" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U341" s="5" t="inlineStr"/>
+      <c r="U341" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="5" t="n">
         <v>136.9</v>
@@ -25619,7 +26371,9 @@
       <c r="T342" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U342" s="5" t="inlineStr"/>
+      <c r="U342" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="5" t="n">
         <v>142.1</v>
@@ -25696,7 +26450,9 @@
       <c r="T343" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="U343" s="3" t="inlineStr"/>
+      <c r="U343" s="7" t="n">
+        <v>28.7</v>
+      </c>
       <c r="V343" s="1" t="inlineStr"/>
       <c r="W343" s="3" t="n">
         <v>152.2</v>
@@ -25769,7 +26525,9 @@
       <c r="T344" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U344" s="5" t="inlineStr"/>
+      <c r="U344" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="V344" t="inlineStr"/>
       <c r="W344" s="5" t="n">
         <v>145</v>
@@ -25846,7 +26604,9 @@
       <c r="T345" s="5" t="n">
         <v>19.9</v>
       </c>
-      <c r="U345" s="5" t="inlineStr"/>
+      <c r="U345" s="5" t="n">
+        <v>20.6</v>
+      </c>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="5" t="n">
         <v>142</v>
@@ -25919,7 +26679,9 @@
       <c r="T346" s="5" t="n">
         <v>22.2</v>
       </c>
-      <c r="U346" s="5" t="inlineStr"/>
+      <c r="U346" s="5" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="5" t="n">
         <v>143.1</v>
@@ -25992,7 +26754,9 @@
       <c r="T347" s="5" t="n">
         <v>19.4</v>
       </c>
-      <c r="U347" s="5" t="inlineStr"/>
+      <c r="U347" s="5" t="n">
+        <v>21.1</v>
+      </c>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="5" t="n">
         <v>143</v>
@@ -26065,7 +26829,9 @@
       <c r="T348" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U348" s="5" t="inlineStr"/>
+      <c r="U348" s="5" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="5" t="n">
         <v>142.6</v>
@@ -26138,7 +26904,9 @@
       <c r="T349" s="5" t="n">
         <v>16.2</v>
       </c>
-      <c r="U349" s="5" t="inlineStr"/>
+      <c r="U349" s="5" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="5" t="n">
         <v>144.3</v>
@@ -26211,7 +26979,9 @@
       <c r="T350" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U350" s="3" t="inlineStr"/>
+      <c r="U350" s="3" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V350" s="1" t="inlineStr"/>
       <c r="W350" s="3" t="n">
         <v>142.7</v>
@@ -26284,7 +27054,9 @@
       <c r="T351" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U351" s="5" t="inlineStr"/>
+      <c r="U351" s="5" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="5" t="n">
         <v>142.6</v>
@@ -26357,7 +27129,9 @@
       <c r="T352" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U352" s="5" t="inlineStr"/>
+      <c r="U352" s="5" t="n">
+        <v>15.7</v>
+      </c>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="5" t="n">
         <v>146.7</v>
@@ -26430,7 +27204,9 @@
       <c r="T353" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U353" s="5" t="inlineStr"/>
+      <c r="U353" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="5" t="n">
         <v>141.9</v>
@@ -26507,7 +27283,9 @@
       <c r="T354" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="U354" s="3" t="inlineStr"/>
+      <c r="U354" s="3" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V354" s="1" t="inlineStr"/>
       <c r="W354" s="3" t="n">
         <v>143.1</v>
@@ -26580,7 +27358,9 @@
       <c r="T355" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U355" s="5" t="inlineStr"/>
+      <c r="U355" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="5" t="n">
         <v>145.3</v>
@@ -26653,7 +27433,9 @@
       <c r="T356" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U356" s="5" t="inlineStr"/>
+      <c r="U356" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="5" t="n">
         <v>139.9</v>
@@ -26730,7 +27512,9 @@
       <c r="T357" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U357" s="3" t="inlineStr"/>
+      <c r="U357" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="V357" s="1" t="inlineStr"/>
       <c r="W357" s="3" t="n">
         <v>139.4</v>
@@ -26803,7 +27587,9 @@
       <c r="T358" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U358" s="5" t="inlineStr"/>
+      <c r="U358" s="5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="5" t="n">
         <v>144.5</v>
@@ -26876,7 +27662,9 @@
       <c r="T359" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U359" s="5" t="inlineStr"/>
+      <c r="U359" s="5" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="5" t="n">
         <v>149.6</v>
@@ -26953,7 +27741,9 @@
       <c r="T360" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U360" s="3" t="inlineStr"/>
+      <c r="U360" s="3" t="n">
+        <v>13</v>
+      </c>
       <c r="V360" s="1" t="inlineStr"/>
       <c r="W360" s="3" t="n">
         <v>154.8</v>
@@ -27026,7 +27816,9 @@
       <c r="T361" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U361" s="3" t="inlineStr"/>
+      <c r="U361" s="3" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V361" s="1" t="inlineStr"/>
       <c r="W361" s="3" t="n">
         <v>150</v>
@@ -27099,7 +27891,9 @@
       <c r="T362" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="U362" s="5" t="inlineStr"/>
+      <c r="U362" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="5" t="n">
         <v>145.4</v>
@@ -27176,7 +27970,9 @@
       <c r="T363" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U363" s="3" t="inlineStr"/>
+      <c r="U363" s="3" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V363" s="1" t="inlineStr"/>
       <c r="W363" s="3" t="n">
         <v>145.7</v>
@@ -27249,7 +28045,9 @@
       <c r="T364" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U364" s="5" t="inlineStr"/>
+      <c r="U364" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="5" t="n">
         <v>149.8</v>
@@ -27322,7 +28120,9 @@
       <c r="T365" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U365" s="5" t="inlineStr"/>
+      <c r="U365" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="5" t="n">
         <v>144.7</v>
@@ -27395,7 +28195,9 @@
       <c r="T366" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U366" s="5" t="inlineStr"/>
+      <c r="U366" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="5" t="n">
         <v>144.3</v>
@@ -27472,7 +28274,9 @@
       <c r="T367" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U367" s="5" t="inlineStr"/>
+      <c r="U367" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="5" t="n">
         <v>145.7</v>
@@ -27545,7 +28349,9 @@
       <c r="T368" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U368" s="5" t="inlineStr"/>
+      <c r="U368" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="5" t="n">
         <v>145.1</v>
@@ -27618,7 +28424,9 @@
       <c r="T369" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U369" s="5" t="inlineStr"/>
+      <c r="U369" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="5" t="n">
         <v>148.5</v>
@@ -27691,7 +28499,9 @@
       <c r="T370" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U370" s="5" t="inlineStr"/>
+      <c r="U370" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="5" t="n">
         <v>145.7</v>
@@ -27764,7 +28574,9 @@
       <c r="T371" s="5" t="n">
         <v>18.8</v>
       </c>
-      <c r="U371" s="5" t="inlineStr"/>
+      <c r="U371" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="5" t="n">
         <v>147.3</v>
@@ -27837,7 +28649,9 @@
       <c r="T372" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U372" s="5" t="inlineStr"/>
+      <c r="U372" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="5" t="n">
         <v>146.1</v>
@@ -27910,7 +28724,9 @@
       <c r="T373" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U373" s="5" t="inlineStr"/>
+      <c r="U373" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V373" t="inlineStr"/>
       <c r="W373" s="5" t="n">
         <v>151.7</v>
@@ -27983,7 +28799,9 @@
       <c r="T374" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U374" s="5" t="inlineStr"/>
+      <c r="U374" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V374" t="inlineStr"/>
       <c r="W374" s="5" t="n">
         <v>150.2</v>
@@ -28056,7 +28874,9 @@
       <c r="T375" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U375" s="5" t="inlineStr"/>
+      <c r="U375" s="5" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V375" t="inlineStr"/>
       <c r="W375" s="5" t="n">
         <v>145.9</v>
@@ -28129,7 +28949,9 @@
       <c r="T376" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U376" s="5" t="inlineStr"/>
+      <c r="U376" s="5" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" s="5" t="n">
         <v>147.3</v>
@@ -28206,7 +29028,9 @@
       <c r="T377" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U377" s="5" t="inlineStr"/>
+      <c r="U377" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V377" t="inlineStr"/>
       <c r="W377" s="5" t="n">
         <v>146.6</v>
@@ -28279,7 +29103,9 @@
       <c r="T378" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="U378" s="3" t="inlineStr"/>
+      <c r="U378" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V378" s="1" t="inlineStr"/>
       <c r="W378" s="3" t="n">
         <v>143</v>
@@ -28356,7 +29182,9 @@
       <c r="T379" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="U379" s="3" t="inlineStr"/>
+      <c r="U379" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V379" s="1" t="inlineStr"/>
       <c r="W379" s="3" t="n">
         <v>139.6</v>
@@ -28429,7 +29257,9 @@
       <c r="T380" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U380" s="5" t="inlineStr"/>
+      <c r="U380" s="5" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V380" t="inlineStr"/>
       <c r="W380" s="5" t="n">
         <v>139.9</v>
@@ -28502,7 +29332,9 @@
       <c r="T381" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U381" s="5" t="inlineStr"/>
+      <c r="U381" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V381" t="inlineStr"/>
       <c r="W381" s="5" t="n">
         <v>141.2</v>
@@ -28575,7 +29407,9 @@
       <c r="T382" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U382" s="5" t="inlineStr"/>
+      <c r="U382" s="5" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V382" t="inlineStr"/>
       <c r="W382" s="5" t="n">
         <v>140</v>
@@ -28648,7 +29482,9 @@
       <c r="T383" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U383" s="5" t="inlineStr"/>
+      <c r="U383" s="5" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V383" t="inlineStr"/>
       <c r="W383" s="4" t="n">
         <v>126.4</v>
@@ -28725,7 +29561,9 @@
       <c r="T384" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U384" s="5" t="inlineStr"/>
+      <c r="U384" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V384" t="inlineStr"/>
       <c r="W384" s="5" t="n">
         <v>133.3</v>
@@ -28798,7 +29636,9 @@
       <c r="T385" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U385" s="5" t="inlineStr"/>
+      <c r="U385" s="5" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V385" t="inlineStr"/>
       <c r="W385" s="5" t="n">
         <v>134.7</v>
@@ -28871,7 +29711,9 @@
       <c r="T386" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U386" s="5" t="inlineStr"/>
+      <c r="U386" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V386" t="inlineStr"/>
       <c r="W386" s="5" t="n">
         <v>132.6</v>
@@ -28948,7 +29790,9 @@
       <c r="T387" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="U387" s="5" t="inlineStr"/>
+      <c r="U387" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V387" t="inlineStr"/>
       <c r="W387" s="5" t="n">
         <v>137.1</v>
@@ -29021,7 +29865,9 @@
       <c r="T388" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U388" s="5" t="inlineStr"/>
+      <c r="U388" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V388" t="inlineStr"/>
       <c r="W388" s="5" t="n">
         <v>135.6</v>
@@ -29094,7 +29940,9 @@
       <c r="T389" s="5" t="n">
         <v>14.6</v>
       </c>
-      <c r="U389" s="5" t="inlineStr"/>
+      <c r="U389" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V389" t="inlineStr"/>
       <c r="W389" s="5" t="n">
         <v>136.5</v>
@@ -29167,7 +30015,9 @@
       <c r="T390" s="5" t="n">
         <v>14.6</v>
       </c>
-      <c r="U390" s="5" t="inlineStr"/>
+      <c r="U390" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V390" t="inlineStr"/>
       <c r="W390" s="5" t="n">
         <v>134.4</v>
@@ -29240,7 +30090,9 @@
       <c r="T391" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="U391" s="5" t="inlineStr"/>
+      <c r="U391" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V391" t="inlineStr"/>
       <c r="W391" s="5" t="n">
         <v>138.4</v>
@@ -29313,7 +30165,9 @@
       <c r="T392" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U392" s="5" t="inlineStr"/>
+      <c r="U392" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V392" t="inlineStr"/>
       <c r="W392" s="5" t="n">
         <v>142.9</v>
@@ -29390,7 +30244,9 @@
       <c r="T393" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U393" s="3" t="inlineStr"/>
+      <c r="U393" s="3" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V393" s="1" t="inlineStr"/>
       <c r="W393" s="3" t="n">
         <v>143.6</v>
@@ -29463,7 +30319,9 @@
       <c r="T394" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U394" s="5" t="inlineStr"/>
+      <c r="U394" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V394" t="inlineStr"/>
       <c r="W394" s="5" t="n">
         <v>142.9</v>
@@ -29536,7 +30394,9 @@
       <c r="T395" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U395" s="5" t="inlineStr"/>
+      <c r="U395" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V395" t="inlineStr"/>
       <c r="W395" s="5" t="n">
         <v>143.2</v>
@@ -29609,7 +30469,9 @@
       <c r="T396" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U396" s="5" t="inlineStr"/>
+      <c r="U396" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V396" t="inlineStr"/>
       <c r="W396" s="5" t="n">
         <v>143.9</v>
@@ -29682,7 +30544,9 @@
       <c r="T397" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U397" s="5" t="inlineStr"/>
+      <c r="U397" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V397" t="inlineStr"/>
       <c r="W397" s="5" t="n">
         <v>145.6</v>
@@ -29755,7 +30619,9 @@
       <c r="T398" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U398" s="5" t="inlineStr"/>
+      <c r="U398" s="5" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V398" t="inlineStr"/>
       <c r="W398" s="5" t="n">
         <v>143.3</v>
@@ -29828,7 +30694,9 @@
       <c r="T399" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U399" s="5" t="inlineStr"/>
+      <c r="U399" s="5" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V399" t="inlineStr"/>
       <c r="W399" s="5" t="n">
         <v>143</v>
@@ -29901,7 +30769,9 @@
       <c r="T400" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U400" s="5" t="inlineStr"/>
+      <c r="U400" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V400" t="inlineStr"/>
       <c r="W400" s="5" t="n">
         <v>144.1</v>
@@ -29974,7 +30844,9 @@
       <c r="T401" s="5" t="n">
         <v>14.4</v>
       </c>
-      <c r="U401" s="5" t="inlineStr"/>
+      <c r="U401" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V401" t="inlineStr"/>
       <c r="W401" s="5" t="n">
         <v>149.8</v>
@@ -30047,7 +30919,9 @@
       <c r="T402" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U402" s="5" t="inlineStr"/>
+      <c r="U402" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V402" t="inlineStr"/>
       <c r="W402" s="5" t="n">
         <v>148.5</v>
@@ -30124,7 +30998,9 @@
       <c r="T403" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U403" s="5" t="inlineStr"/>
+      <c r="U403" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V403" t="inlineStr"/>
       <c r="W403" s="5" t="n">
         <v>149.2</v>
@@ -30201,7 +31077,9 @@
       <c r="T404" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U404" s="5" t="inlineStr"/>
+      <c r="U404" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V404" t="inlineStr"/>
       <c r="W404" s="5" t="n">
         <v>144.1</v>
@@ -30278,7 +31156,9 @@
       <c r="T405" s="5" t="n">
         <v>14.3</v>
       </c>
-      <c r="U405" s="5" t="inlineStr"/>
+      <c r="U405" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V405" t="inlineStr"/>
       <c r="W405" s="5" t="n">
         <v>150.6</v>
@@ -30351,7 +31231,9 @@
       <c r="T406" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U406" s="5" t="inlineStr"/>
+      <c r="U406" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V406" t="inlineStr"/>
       <c r="W406" s="5" t="n">
         <v>151.6</v>
@@ -30424,7 +31306,9 @@
       <c r="T407" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U407" s="5" t="inlineStr"/>
+      <c r="U407" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V407" t="inlineStr"/>
       <c r="W407" s="5" t="n">
         <v>148.9</v>
@@ -30497,7 +31381,9 @@
       <c r="T408" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U408" s="5" t="inlineStr"/>
+      <c r="U408" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V408" t="inlineStr"/>
       <c r="W408" s="5" t="n">
         <v>149.2</v>
@@ -30574,7 +31460,9 @@
       <c r="T409" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U409" s="5" t="inlineStr"/>
+      <c r="U409" s="5" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V409" t="inlineStr"/>
       <c r="W409" s="5" t="n">
         <v>147</v>
@@ -30647,7 +31535,9 @@
       <c r="T410" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U410" s="5" t="inlineStr"/>
+      <c r="U410" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="V410" t="inlineStr"/>
       <c r="W410" s="5" t="n">
         <v>154.5</v>
@@ -30724,7 +31614,9 @@
       <c r="T411" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="U411" s="3" t="inlineStr"/>
+      <c r="U411" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="V411" s="1" t="inlineStr"/>
       <c r="W411" s="3" t="n">
         <v>152.1</v>
@@ -30797,7 +31689,9 @@
       <c r="T412" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="5" t="inlineStr"/>
+      <c r="U412" s="5" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="5" t="n">
         <v>146.6</v>
@@ -30870,7 +31764,9 @@
       <c r="T413" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="5" t="inlineStr"/>
+      <c r="U413" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="5" t="n">
         <v>145.9</v>
@@ -30943,7 +31839,9 @@
       <c r="T414" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="5" t="inlineStr"/>
+      <c r="U414" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="5" t="n">
         <v>145.7</v>
@@ -30967,34 +31865,34 @@
         <v>119.71</v>
       </c>
       <c r="E415" t="n">
-        <v>116.91</v>
+        <v>116.68</v>
       </c>
       <c r="F415" t="n">
-        <v>118.87</v>
+        <v>117.97</v>
       </c>
       <c r="G415" t="n">
-        <v>17044967</v>
+        <v>30557143</v>
       </c>
       <c r="H415" s="4" t="n">
-        <v>3.53</v>
+        <v>2.74</v>
       </c>
       <c r="I415" t="n">
         <v>14.3</v>
       </c>
       <c r="J415" t="n">
-        <v>113.77</v>
+        <v>113.72</v>
       </c>
       <c r="K415" t="n">
-        <v>142.35</v>
+        <v>142.33</v>
       </c>
       <c r="L415" t="n">
-        <v>150.78</v>
+        <v>150.77</v>
       </c>
       <c r="M415" t="n">
-        <v>112.33</v>
+        <v>112.32</v>
       </c>
       <c r="N415" s="5" t="n">
-        <v>54.54</v>
+        <v>54.04</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -31014,10 +31912,10 @@
         <v>5</v>
       </c>
       <c r="T415" s="5" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="5" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="5" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31796,7 +31796,7 @@
         <v>114.82</v>
       </c>
       <c r="G414" t="n">
-        <v>56121200</v>
+        <v>56833100</v>
       </c>
       <c r="H414" s="4" t="n">
         <v>10.44</v>
@@ -31862,37 +31862,37 @@
         <v>117.03</v>
       </c>
       <c r="D415" t="n">
-        <v>119.71</v>
+        <v>123.86</v>
       </c>
       <c r="E415" t="n">
         <v>116.68</v>
       </c>
       <c r="F415" t="n">
-        <v>117.97</v>
+        <v>123.67</v>
       </c>
       <c r="G415" t="n">
-        <v>30557143</v>
+        <v>44207841</v>
       </c>
       <c r="H415" s="4" t="n">
-        <v>2.74</v>
+        <v>7.71</v>
       </c>
       <c r="I415" t="n">
         <v>14.3</v>
       </c>
       <c r="J415" t="n">
-        <v>113.72</v>
+        <v>114.01</v>
       </c>
       <c r="K415" t="n">
-        <v>142.33</v>
+        <v>142.43</v>
       </c>
       <c r="L415" t="n">
-        <v>150.77</v>
+        <v>150.82</v>
       </c>
       <c r="M415" t="n">
-        <v>112.32</v>
+        <v>112.35</v>
       </c>
       <c r="N415" s="5" t="n">
-        <v>54.04</v>
+        <v>57.03</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -31912,13 +31912,15 @@
         <v>5</v>
       </c>
       <c r="T415" s="5" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="5" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="5" t="inlineStr"/>
+      <c r="W415" s="5" t="n">
+        <v>148.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2052,7 +2052,7 @@
         <v>14.3</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>27.27</v>
+        <v>27.26</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>28.66</v>
@@ -13662,7 +13662,7 @@
         <v>33.95</v>
       </c>
       <c r="K174" t="n">
-        <v>29</v>
+        <v>28.99</v>
       </c>
       <c r="L174" t="n">
         <v>23.73</v>
@@ -31666,7 +31666,7 @@
         <v>57.03</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31692,6 +31692,79 @@
       <c r="W412" s="2" t="n">
         <v>148.1</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>132.07</v>
+      </c>
+      <c r="D413" t="n">
+        <v>140.42</v>
+      </c>
+      <c r="E413" t="n">
+        <v>129.62</v>
+      </c>
+      <c r="F413" t="n">
+        <v>139.91</v>
+      </c>
+      <c r="G413" t="n">
+        <v>39232380</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="I413" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>114.97</v>
+      </c>
+      <c r="K413" t="n">
+        <v>140.55</v>
+      </c>
+      <c r="L413" t="n">
+        <v>151.65</v>
+      </c>
+      <c r="M413" t="n">
+        <v>112.83</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -2052,7 +2052,7 @@
         <v>14.3</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>27.26</v>
+        <v>27.27</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>28.66</v>
@@ -31708,37 +31708,37 @@
         <v>132.07</v>
       </c>
       <c r="D413" t="n">
-        <v>140.42</v>
+        <v>144</v>
       </c>
       <c r="E413" t="n">
         <v>129.62</v>
       </c>
       <c r="F413" t="n">
-        <v>139.91</v>
+        <v>141.93</v>
       </c>
       <c r="G413" t="n">
-        <v>39232380</v>
+        <v>60116064</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>13.13</v>
+        <v>14.77</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" t="n">
-        <v>114.97</v>
+        <v>115.07</v>
       </c>
       <c r="K413" t="n">
-        <v>140.55</v>
+        <v>140.58</v>
       </c>
       <c r="L413" t="n">
-        <v>151.65</v>
+        <v>151.66</v>
       </c>
       <c r="M413" t="n">
-        <v>112.83</v>
+        <v>112.84</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>63.23</v>
+        <v>63.94</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31755,13 +31755,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31717,7 +31717,7 @@
         <v>141.93</v>
       </c>
       <c r="G413" t="n">
-        <v>60116064</v>
+        <v>60567682</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>14.77</v>
@@ -31764,7 +31764,9 @@
         <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>142.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31693,6 +31693,79 @@
         <v>142.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>137.67</v>
+      </c>
+      <c r="D413" t="n">
+        <v>147.33</v>
+      </c>
+      <c r="E413" t="n">
+        <v>137.46</v>
+      </c>
+      <c r="F413" t="n">
+        <v>147.28</v>
+      </c>
+      <c r="G413" t="n">
+        <v>27178970</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I413" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>116.88</v>
+      </c>
+      <c r="K413" t="n">
+        <v>139.44</v>
+      </c>
+      <c r="L413" t="n">
+        <v>152.49</v>
+      </c>
+      <c r="M413" t="n">
+        <v>113.34</v>
+      </c>
+      <c r="N413" s="1" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="O413" t="n">
+        <v>37</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31708,40 +31708,40 @@
         <v>137.67</v>
       </c>
       <c r="D413" t="n">
-        <v>147.33</v>
+        <v>149.91</v>
       </c>
       <c r="E413" t="n">
         <v>137.46</v>
       </c>
       <c r="F413" t="n">
-        <v>147.28</v>
+        <v>149.6</v>
       </c>
       <c r="G413" t="n">
-        <v>27178970</v>
+        <v>52823392</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>3.77</v>
+        <v>5.4</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" t="n">
-        <v>116.88</v>
+        <v>116.99</v>
       </c>
       <c r="K413" t="n">
-        <v>139.44</v>
+        <v>139.48</v>
       </c>
       <c r="L413" t="n">
-        <v>152.49</v>
+        <v>152.51</v>
       </c>
       <c r="M413" t="n">
-        <v>113.34</v>
+        <v>113.36</v>
       </c>
       <c r="N413" s="1" t="n">
-        <v>70.09</v>
+        <v>70.75</v>
       </c>
       <c r="O413" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31758,10 +31758,10 @@
         <v>4.95</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31642,7 +31642,7 @@
         <v>141.93</v>
       </c>
       <c r="G412" t="n">
-        <v>61103200</v>
+        <v>62514300</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>14.77</v>
@@ -31708,40 +31708,40 @@
         <v>137.67</v>
       </c>
       <c r="D413" t="n">
-        <v>149.91</v>
+        <v>152.64</v>
       </c>
       <c r="E413" t="n">
         <v>137.46</v>
       </c>
       <c r="F413" t="n">
-        <v>149.6</v>
+        <v>151.95</v>
       </c>
       <c r="G413" t="n">
-        <v>52823392</v>
+        <v>65009024</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>5.4</v>
+        <v>7.06</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" t="n">
-        <v>116.99</v>
+        <v>117.11</v>
       </c>
       <c r="K413" t="n">
-        <v>139.48</v>
+        <v>139.52</v>
       </c>
       <c r="L413" t="n">
-        <v>152.51</v>
+        <v>152.53</v>
       </c>
       <c r="M413" t="n">
-        <v>113.36</v>
+        <v>113.37</v>
       </c>
       <c r="N413" s="1" t="n">
-        <v>70.75</v>
+        <v>71.39</v>
       </c>
       <c r="O413" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31755,16 +31755,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31634,7 +31634,7 @@
       <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
-        <v>65009024</v>
+        <v>0</v>
       </c>
       <c r="H412" s="2" t="n">
         <v>0</v>
@@ -31669,6 +31669,71 @@
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>149.89</v>
+      </c>
+      <c r="D413" t="n">
+        <v>151</v>
+      </c>
+      <c r="E413" t="n">
+        <v>139.58</v>
+      </c>
+      <c r="F413" t="n">
+        <v>142.93</v>
+      </c>
+      <c r="G413" t="n">
+        <v>37849942</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I413" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" s="2" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="O413" t="n">
+        <v>36</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31629,25 +31629,41 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>137.67</v>
+      </c>
+      <c r="D412" t="n">
+        <v>152.64</v>
+      </c>
+      <c r="E412" t="n">
+        <v>137.46</v>
+      </c>
+      <c r="F412" t="n">
+        <v>151.95</v>
+      </c>
       <c r="G412" t="n">
-        <v>0</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>66530800</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>7.13</v>
       </c>
       <c r="I412" t="n">
         <v>14.3</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
-      <c r="N412" s="2" t="n">
-        <v>68.45</v>
+      <c r="J412" t="n">
+        <v>117.04</v>
+      </c>
+      <c r="K412" t="n">
+        <v>139.43</v>
+      </c>
+      <c r="L412" t="n">
+        <v>152.43</v>
+      </c>
+      <c r="M412" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="N412" s="1" t="n">
+        <v>71.41</v>
       </c>
       <c r="O412" t="n">
         <v>35</v>
@@ -31690,26 +31706,34 @@
         <v>139.58</v>
       </c>
       <c r="F413" t="n">
-        <v>142.93</v>
+        <v>145.76</v>
       </c>
       <c r="G413" t="n">
-        <v>37849942</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>0.77</v>
+        <v>58997550</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-4.07</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>118.55</v>
+      </c>
+      <c r="K413" t="n">
+        <v>137.92</v>
+      </c>
+      <c r="L413" t="n">
+        <v>153.21</v>
+      </c>
+      <c r="M413" t="n">
+        <v>113.8</v>
+      </c>
       <c r="N413" s="2" t="n">
-        <v>68.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O413" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31723,13 +31747,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.09</v>
+        <v>5.11</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.4</v>
+        <v>10.6</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -4303,7 +4303,7 @@
         <v>14.3</v>
       </c>
       <c r="J50" t="n">
-        <v>15.56</v>
+        <v>15.55</v>
       </c>
       <c r="K50" t="n">
         <v>22.42</v>
@@ -31706,22 +31706,22 @@
         <v>139.58</v>
       </c>
       <c r="F413" t="n">
-        <v>145.76</v>
+        <v>146.25</v>
       </c>
       <c r="G413" t="n">
-        <v>58997550</v>
+        <v>61043803</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-4.07</v>
+        <v>-3.75</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" t="n">
-        <v>118.55</v>
+        <v>118.57</v>
       </c>
       <c r="K413" t="n">
-        <v>137.92</v>
+        <v>137.93</v>
       </c>
       <c r="L413" t="n">
         <v>153.21</v>
@@ -31730,7 +31730,7 @@
         <v>113.8</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>67.69</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>
@@ -31753,10 +31753,12 @@
         <v>15.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31696,41 +31696,25 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>149.89</v>
-      </c>
-      <c r="D413" t="n">
-        <v>151</v>
-      </c>
-      <c r="E413" t="n">
-        <v>139.58</v>
-      </c>
-      <c r="F413" t="n">
-        <v>146.25</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
         <v>61043803</v>
       </c>
-      <c r="H413" s="1" t="n">
-        <v>-3.75</v>
+      <c r="H413" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
-      <c r="J413" t="n">
-        <v>118.57</v>
-      </c>
-      <c r="K413" t="n">
-        <v>137.93</v>
-      </c>
-      <c r="L413" t="n">
-        <v>153.21</v>
-      </c>
-      <c r="M413" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="N413" s="2" t="n">
-        <v>67.69</v>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" s="1" t="n">
+        <v>71.29000000000001</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31696,25 +31696,41 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>149.89</v>
+      </c>
+      <c r="D413" t="n">
+        <v>151</v>
+      </c>
+      <c r="E413" t="n">
+        <v>139.58</v>
+      </c>
+      <c r="F413" t="n">
+        <v>146.25</v>
+      </c>
       <c r="G413" t="n">
-        <v>61043803</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>61503100</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-3.75</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
-      <c r="N413" s="1" t="n">
-        <v>71.29000000000001</v>
+      <c r="J413" t="n">
+        <v>118.57</v>
+      </c>
+      <c r="K413" t="n">
+        <v>137.93</v>
+      </c>
+      <c r="L413" t="n">
+        <v>153.21</v>
+      </c>
+      <c r="M413" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>67.69</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31733,7 +31733,7 @@
         <v>67.69</v>
       </c>
       <c r="O413" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31759,6 +31759,79 @@
       <c r="W413" s="2" t="n">
         <v>146.1</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>138.47</v>
+      </c>
+      <c r="D414" t="n">
+        <v>147.2</v>
+      </c>
+      <c r="E414" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="F414" t="n">
+        <v>143.51</v>
+      </c>
+      <c r="G414" t="n">
+        <v>50922051</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>119.92</v>
+      </c>
+      <c r="K414" t="n">
+        <v>135.88</v>
+      </c>
+      <c r="L414" t="n">
+        <v>153.97</v>
+      </c>
+      <c r="M414" t="n">
+        <v>114.28</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>65.98</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31709,7 +31709,7 @@
         <v>146.25</v>
       </c>
       <c r="G413" t="n">
-        <v>61503100</v>
+        <v>62051700</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-3.75</v>
@@ -31781,34 +31781,34 @@
         <v>136.9</v>
       </c>
       <c r="F414" t="n">
-        <v>143.51</v>
+        <v>146.33</v>
       </c>
       <c r="G414" t="n">
-        <v>50922051</v>
-      </c>
-      <c r="H414" s="1" t="n">
-        <v>-1.87</v>
+        <v>64553899</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>0.05</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>119.92</v>
+        <v>120.06</v>
       </c>
       <c r="K414" t="n">
-        <v>135.88</v>
+        <v>135.93</v>
       </c>
       <c r="L414" t="n">
-        <v>153.97</v>
+        <v>153.99</v>
       </c>
       <c r="M414" t="n">
-        <v>114.28</v>
+        <v>114.3</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>65.98</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31822,16 +31822,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31771,41 +31771,25 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>138.47</v>
-      </c>
-      <c r="D414" t="n">
-        <v>147.2</v>
-      </c>
-      <c r="E414" t="n">
-        <v>136.9</v>
-      </c>
-      <c r="F414" t="n">
-        <v>146.33</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>64553899</v>
       </c>
-      <c r="H414" s="3" t="n">
-        <v>0.05</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
-      <c r="J414" t="n">
-        <v>120.06</v>
-      </c>
-      <c r="K414" t="n">
-        <v>135.93</v>
-      </c>
-      <c r="L414" t="n">
-        <v>153.99</v>
-      </c>
-      <c r="M414" t="n">
-        <v>114.3</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>67.58</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31771,25 +31771,41 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>138.47</v>
+      </c>
+      <c r="D414" t="n">
+        <v>147.2</v>
+      </c>
+      <c r="E414" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="F414" t="n">
+        <v>146.33</v>
+      </c>
       <c r="G414" t="n">
-        <v>64553899</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>64854800</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>0.05</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>120.06</v>
+      </c>
+      <c r="K414" t="n">
+        <v>135.93</v>
+      </c>
+      <c r="L414" t="n">
+        <v>153.99</v>
+      </c>
+      <c r="M414" t="n">
+        <v>114.3</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>67.58</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31679,11 +31679,19 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31843,6 +31843,79 @@
         <v>146</v>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>149.24</v>
+      </c>
+      <c r="D415" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="E415" t="n">
+        <v>147.39</v>
+      </c>
+      <c r="F415" t="n">
+        <v>152.64</v>
+      </c>
+      <c r="G415" t="n">
+        <v>43277114</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="I415" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>121.55</v>
+      </c>
+      <c r="K415" t="n">
+        <v>134.85</v>
+      </c>
+      <c r="L415" t="n">
+        <v>154.81</v>
+      </c>
+      <c r="M415" t="n">
+        <v>114.82</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>66.34</v>
+      </c>
+      <c r="O415" t="n">
+        <v>38</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31792,7 +31792,7 @@
         <v>146.33</v>
       </c>
       <c r="G414" t="n">
-        <v>64854800</v>
+        <v>65335900</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>0.05</v>
@@ -31864,34 +31864,34 @@
         <v>147.39</v>
       </c>
       <c r="F415" t="n">
-        <v>152.64</v>
+        <v>151.45</v>
       </c>
       <c r="G415" t="n">
-        <v>43277114</v>
+        <v>55809520</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>4.31</v>
+        <v>3.5</v>
       </c>
       <c r="I415" t="n">
         <v>14.3</v>
       </c>
       <c r="J415" t="n">
-        <v>121.55</v>
+        <v>121.49</v>
       </c>
       <c r="K415" t="n">
-        <v>134.85</v>
+        <v>134.83</v>
       </c>
       <c r="L415" t="n">
-        <v>154.81</v>
+        <v>154.8</v>
       </c>
       <c r="M415" t="n">
         <v>114.82</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>66.34</v>
+        <v>65.97</v>
       </c>
       <c r="O415" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31905,16 +31905,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>144.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31779,25 +31779,41 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>149.24</v>
+      </c>
+      <c r="D414" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="E414" t="n">
+        <v>147.39</v>
+      </c>
+      <c r="F414" t="n">
+        <v>151.45</v>
+      </c>
       <c r="G414" t="n">
-        <v>55809520</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>56130400</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>3.5</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>121.49</v>
+      </c>
+      <c r="K414" t="n">
+        <v>134.83</v>
+      </c>
+      <c r="L414" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="M414" t="n">
+        <v>114.82</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>64.26000000000001</v>
+        <v>65.97</v>
       </c>
       <c r="O414" t="n">
         <v>37</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31693,6 +31693,79 @@
         <v>144.9</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>148.14</v>
+      </c>
+      <c r="D413" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="E413" t="n">
+        <v>135.21</v>
+      </c>
+      <c r="F413" t="n">
+        <v>137.22</v>
+      </c>
+      <c r="G413" t="n">
+        <v>35050625</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="I413" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>122.78</v>
+      </c>
+      <c r="K413" t="n">
+        <v>134.09</v>
+      </c>
+      <c r="L413" t="n">
+        <v>155.47</v>
+      </c>
+      <c r="M413" t="n">
+        <v>115.26</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31714,31 +31714,31 @@
         <v>135.21</v>
       </c>
       <c r="F413" t="n">
-        <v>137.22</v>
+        <v>142.29</v>
       </c>
       <c r="G413" t="n">
-        <v>35050625</v>
+        <v>69584851</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-9.4</v>
+        <v>-6.05</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" t="n">
-        <v>122.78</v>
+        <v>123.04</v>
       </c>
       <c r="K413" t="n">
-        <v>134.09</v>
+        <v>134.18</v>
       </c>
       <c r="L413" t="n">
-        <v>155.47</v>
+        <v>155.51</v>
       </c>
       <c r="M413" t="n">
-        <v>115.26</v>
+        <v>115.29</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>56.08</v>
+        <v>58.65</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31755,16 +31755,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -19176,7 +19176,7 @@
         <v>47.19</v>
       </c>
       <c r="L247" t="n">
-        <v>40.7</v>
+        <v>40.71</v>
       </c>
       <c r="M247" t="n">
         <v>32.48</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31693,6 +31693,79 @@
         <v>146.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>148.93</v>
+      </c>
+      <c r="D413" t="n">
+        <v>152.37</v>
+      </c>
+      <c r="E413" t="n">
+        <v>145.49</v>
+      </c>
+      <c r="F413" t="n">
+        <v>148.6</v>
+      </c>
+      <c r="G413" t="n">
+        <v>31016196</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="I413" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>124.83</v>
+      </c>
+      <c r="K413" t="n">
+        <v>133.41</v>
+      </c>
+      <c r="L413" t="n">
+        <v>156.19</v>
+      </c>
+      <c r="M413" t="n">
+        <v>115.78</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31642,7 +31642,7 @@
         <v>142.29</v>
       </c>
       <c r="G412" t="n">
-        <v>69932000</v>
+        <v>70559400</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-6.05</v>
@@ -31714,34 +31714,34 @@
         <v>145.49</v>
       </c>
       <c r="F413" t="n">
-        <v>148.6</v>
+        <v>147</v>
       </c>
       <c r="G413" t="n">
-        <v>31016196</v>
+        <v>52307538</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>4.43</v>
+        <v>3.31</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" t="n">
-        <v>124.83</v>
+        <v>124.75</v>
       </c>
       <c r="K413" t="n">
-        <v>133.41</v>
+        <v>133.38</v>
       </c>
       <c r="L413" t="n">
-        <v>156.19</v>
+        <v>156.18</v>
       </c>
       <c r="M413" t="n">
         <v>115.78</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>59.99</v>
+        <v>59.43</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31755,13 +31755,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31629,25 +31629,41 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>148.94</v>
+      </c>
+      <c r="D412" t="n">
+        <v>152.37</v>
+      </c>
+      <c r="E412" t="n">
+        <v>145.49</v>
+      </c>
+      <c r="F412" t="n">
+        <v>147</v>
+      </c>
       <c r="G412" t="n">
-        <v>52706835</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>53029800</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>3.31</v>
       </c>
       <c r="I412" t="n">
         <v>14.3</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="K412" t="n">
+        <v>133.38</v>
+      </c>
+      <c r="L412" t="n">
+        <v>156.18</v>
+      </c>
+      <c r="M412" t="n">
+        <v>115.78</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>57.65</v>
+        <v>59.43</v>
       </c>
       <c r="O412" t="n">
         <v>32</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31666,7 +31666,7 @@
         <v>59.43</v>
       </c>
       <c r="O412" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31693,6 +31693,79 @@
         <v>144.6</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>147.95</v>
+      </c>
+      <c r="D413" t="n">
+        <v>150.77</v>
+      </c>
+      <c r="E413" t="n">
+        <v>144.41</v>
+      </c>
+      <c r="F413" t="n">
+        <v>146.74</v>
+      </c>
+      <c r="G413" t="n">
+        <v>34226764</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="I413" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="K413" t="n">
+        <v>133.08</v>
+      </c>
+      <c r="L413" t="n">
+        <v>156.8</v>
+      </c>
+      <c r="M413" t="n">
+        <v>116.26</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>65.13</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31642,7 +31642,7 @@
         <v>147</v>
       </c>
       <c r="G412" t="n">
-        <v>53029800</v>
+        <v>53567600</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>3.31</v>
@@ -31714,34 +31714,34 @@
         <v>144.41</v>
       </c>
       <c r="F413" t="n">
-        <v>146.74</v>
+        <v>147.86</v>
       </c>
       <c r="G413" t="n">
-        <v>34226764</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>-0.18</v>
+        <v>46807636</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.59</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" t="n">
-        <v>126.8</v>
+        <v>126.85</v>
       </c>
       <c r="K413" t="n">
-        <v>133.08</v>
+        <v>133.1</v>
       </c>
       <c r="L413" t="n">
-        <v>156.8</v>
+        <v>156.81</v>
       </c>
       <c r="M413" t="n">
-        <v>116.26</v>
+        <v>116.27</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>65.13</v>
+        <v>65.58</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31755,16 +31755,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>141.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31717,7 +31717,7 @@
         <v>147.86</v>
       </c>
       <c r="G413" t="n">
-        <v>46807636</v>
+        <v>47769800</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>0.59</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31741,7 +31741,7 @@
         <v>65.58</v>
       </c>
       <c r="O413" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31768,6 +31768,79 @@
         <v>141.9</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>148.55</v>
+      </c>
+      <c r="D414" t="n">
+        <v>151.25</v>
+      </c>
+      <c r="E414" t="n">
+        <v>144.32</v>
+      </c>
+      <c r="F414" t="n">
+        <v>149.09</v>
+      </c>
+      <c r="G414" t="n">
+        <v>42926082</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>128.99</v>
+      </c>
+      <c r="K414" t="n">
+        <v>132.67</v>
+      </c>
+      <c r="L414" t="n">
+        <v>157.42</v>
+      </c>
+      <c r="M414" t="n">
+        <v>116.81</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>63.89</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31717,7 +31717,7 @@
         <v>147.86</v>
       </c>
       <c r="G413" t="n">
-        <v>47769800</v>
+        <v>48729500</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>0.59</v>
@@ -31783,40 +31783,40 @@
         <v>148.55</v>
       </c>
       <c r="D414" t="n">
-        <v>151.25</v>
+        <v>156.71</v>
       </c>
       <c r="E414" t="n">
         <v>144.32</v>
       </c>
       <c r="F414" t="n">
-        <v>149.09</v>
+        <v>153.69</v>
       </c>
       <c r="G414" t="n">
-        <v>42926082</v>
+        <v>72955271</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.83</v>
+        <v>3.94</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>128.99</v>
+        <v>129.22</v>
       </c>
       <c r="K414" t="n">
-        <v>132.67</v>
+        <v>132.75</v>
       </c>
       <c r="L414" t="n">
-        <v>157.42</v>
+        <v>157.45</v>
       </c>
       <c r="M414" t="n">
-        <v>116.81</v>
+        <v>116.83</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>63.89</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31830,16 +31830,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>142.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31779,41 +31779,25 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>148.55</v>
-      </c>
-      <c r="D414" t="n">
-        <v>156.71</v>
-      </c>
-      <c r="E414" t="n">
-        <v>144.32</v>
-      </c>
-      <c r="F414" t="n">
-        <v>153.69</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>72955271</v>
       </c>
-      <c r="H414" s="1" t="n">
-        <v>3.94</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
-      <c r="J414" t="n">
-        <v>129.22</v>
-      </c>
-      <c r="K414" t="n">
-        <v>132.75</v>
-      </c>
-      <c r="L414" t="n">
-        <v>157.45</v>
-      </c>
-      <c r="M414" t="n">
-        <v>116.83</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>65.51000000000001</v>
+        <v>63.44</v>
       </c>
       <c r="O414" t="n">
         <v>28</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31779,28 +31779,44 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>148.56</v>
+      </c>
+      <c r="D414" t="n">
+        <v>156.71</v>
+      </c>
+      <c r="E414" t="n">
+        <v>144.31</v>
+      </c>
+      <c r="F414" t="n">
+        <v>153.69</v>
+      </c>
       <c r="G414" t="n">
-        <v>72955271</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>73388200</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>3.94</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>129.22</v>
+      </c>
+      <c r="K414" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="L414" t="n">
+        <v>157.45</v>
+      </c>
+      <c r="M414" t="n">
+        <v>116.83</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>63.44</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31816,7 +31816,7 @@
         <v>65.51000000000001</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31842,6 +31842,79 @@
       <c r="W414" s="2" t="n">
         <v>142.8</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>165.39</v>
+      </c>
+      <c r="D415" t="n">
+        <v>169.75</v>
+      </c>
+      <c r="E415" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="F415" t="n">
+        <v>165.55</v>
+      </c>
+      <c r="G415" t="n">
+        <v>37605125</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="I415" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>132.17</v>
+      </c>
+      <c r="K415" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="L415" t="n">
+        <v>158.16</v>
+      </c>
+      <c r="M415" t="n">
+        <v>117.45</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="O415" t="n">
+        <v>31</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31792,7 +31792,7 @@
         <v>153.69</v>
       </c>
       <c r="G414" t="n">
-        <v>73388200</v>
+        <v>74003000</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>3.94</v>
@@ -31861,34 +31861,34 @@
         <v>169.75</v>
       </c>
       <c r="E415" t="n">
-        <v>162.9</v>
+        <v>162.4</v>
       </c>
       <c r="F415" t="n">
-        <v>165.55</v>
+        <v>163.71</v>
       </c>
       <c r="G415" t="n">
-        <v>37605125</v>
+        <v>61737094</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>7.72</v>
+        <v>6.52</v>
       </c>
       <c r="I415" t="n">
         <v>14.3</v>
       </c>
       <c r="J415" t="n">
-        <v>132.17</v>
+        <v>132.08</v>
       </c>
       <c r="K415" t="n">
-        <v>132.3</v>
+        <v>132.27</v>
       </c>
       <c r="L415" t="n">
-        <v>158.16</v>
+        <v>158.15</v>
       </c>
       <c r="M415" t="n">
-        <v>117.45</v>
+        <v>117.44</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>84.23</v>
+        <v>83.91</v>
       </c>
       <c r="O415" t="n">
         <v>31</v>
@@ -31905,13 +31905,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31779,25 +31779,41 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>165.39</v>
+      </c>
+      <c r="D414" t="n">
+        <v>169.75</v>
+      </c>
+      <c r="E414" t="n">
+        <v>162.4</v>
+      </c>
+      <c r="F414" t="n">
+        <v>163.71</v>
+      </c>
       <c r="G414" t="n">
-        <v>61952497</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>62325200</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>6.52</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>132.08</v>
+      </c>
+      <c r="K414" t="n">
+        <v>132.27</v>
+      </c>
+      <c r="L414" t="n">
+        <v>158.15</v>
+      </c>
+      <c r="M414" t="n">
+        <v>117.44</v>
+      </c>
       <c r="N414" s="3" t="n">
-        <v>81.95999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31658,7 +31658,7 @@
         <v>83.91</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3695,7 +3695,7 @@
         <v>14.3</v>
       </c>
       <c r="J42" t="n">
-        <v>15.55</v>
+        <v>15.56</v>
       </c>
       <c r="K42" t="n">
         <v>22.42</v>
@@ -31658,7 +31658,7 @@
         <v>83.91</v>
       </c>
       <c r="O412" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31684,6 +31684,79 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>161.66</v>
+      </c>
+      <c r="D413" t="n">
+        <v>163.86</v>
+      </c>
+      <c r="E413" t="n">
+        <v>158.08</v>
+      </c>
+      <c r="F413" t="n">
+        <v>163.62</v>
+      </c>
+      <c r="G413" t="n">
+        <v>26531351</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I413" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="K413" t="n">
+        <v>131.79</v>
+      </c>
+      <c r="L413" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="M413" t="n">
+        <v>118.06</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>83.62</v>
+      </c>
+      <c r="O413" t="n">
+        <v>44</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31559,7 +31559,7 @@
         <v>163.71</v>
       </c>
       <c r="G411" t="n">
-        <v>62325200</v>
+        <v>62660800</v>
       </c>
       <c r="H411" s="1" t="n">
         <v>6.52</v>
@@ -31621,25 +31621,41 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>161.66</v>
+      </c>
+      <c r="D412" t="n">
+        <v>164.38</v>
+      </c>
+      <c r="E412" t="n">
+        <v>158.08</v>
+      </c>
+      <c r="F412" t="n">
+        <v>164.27</v>
+      </c>
       <c r="G412" t="n">
-        <v>35904970</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>36216300</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>0.34</v>
       </c>
       <c r="I412" t="n">
         <v>14.3</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>134.43</v>
+      </c>
+      <c r="K412" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="L412" t="n">
+        <v>158.81</v>
+      </c>
+      <c r="M412" t="n">
+        <v>118.06</v>
+      </c>
       <c r="N412" s="3" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="O412" t="n">
         <v>43</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31658,7 +31658,7 @@
         <v>83.8</v>
       </c>
       <c r="O412" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31684,6 +31684,79 @@
       <c r="W412" s="2" t="n">
         <v>143</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>167.34</v>
+      </c>
+      <c r="D413" t="n">
+        <v>169.83</v>
+      </c>
+      <c r="E413" t="n">
+        <v>165.38</v>
+      </c>
+      <c r="F413" t="n">
+        <v>168.05</v>
+      </c>
+      <c r="G413" t="n">
+        <v>18955065</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I413" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>136.67</v>
+      </c>
+      <c r="K413" t="n">
+        <v>131.85</v>
+      </c>
+      <c r="L413" t="n">
+        <v>159.49</v>
+      </c>
+      <c r="M413" t="n">
+        <v>118.72</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>84.17</v>
+      </c>
+      <c r="O413" t="n">
+        <v>48</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -3620,7 +3620,7 @@
         <v>14.3</v>
       </c>
       <c r="J41" t="n">
-        <v>15.55</v>
+        <v>15.56</v>
       </c>
       <c r="K41" t="n">
         <v>22.42</v>
@@ -31634,7 +31634,7 @@
         <v>164.27</v>
       </c>
       <c r="G412" t="n">
-        <v>36216300</v>
+        <v>36723200</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>0.34</v>
@@ -31703,34 +31703,34 @@
         <v>169.83</v>
       </c>
       <c r="E413" t="n">
-        <v>165.38</v>
+        <v>163.42</v>
       </c>
       <c r="F413" t="n">
-        <v>168.05</v>
+        <v>164.21</v>
       </c>
       <c r="G413" t="n">
-        <v>18955065</v>
-      </c>
-      <c r="H413" s="1" t="n">
-        <v>2.3</v>
+        <v>43024464</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
       <c r="J413" t="n">
-        <v>136.67</v>
+        <v>136.48</v>
       </c>
       <c r="K413" t="n">
-        <v>131.85</v>
+        <v>131.79</v>
       </c>
       <c r="L413" t="n">
-        <v>159.49</v>
+        <v>159.46</v>
       </c>
       <c r="M413" t="n">
-        <v>118.72</v>
+        <v>118.7</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>84.17</v>
+        <v>83.45</v>
       </c>
       <c r="O413" t="n">
         <v>48</v>
@@ -31747,13 +31747,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31621,25 +31621,41 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>167.34</v>
+      </c>
+      <c r="D412" t="n">
+        <v>169.83</v>
+      </c>
+      <c r="E412" t="n">
+        <v>163.42</v>
+      </c>
+      <c r="F412" t="n">
+        <v>164.26</v>
+      </c>
       <c r="G412" t="n">
-        <v>44634151</v>
-      </c>
-      <c r="H412" s="3" t="n">
-        <v>0</v>
+        <v>44565100</v>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>-0.01</v>
       </c>
       <c r="I412" t="n">
         <v>14.3</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>136.48</v>
+      </c>
+      <c r="K412" t="n">
+        <v>131.79</v>
+      </c>
+      <c r="L412" t="n">
+        <v>159.46</v>
+      </c>
+      <c r="M412" t="n">
+        <v>118.7</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>83.51000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="O412" t="n">
         <v>47</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>5.01</v>
       </c>
       <c r="I2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J2" t="n">
         <v>28.28</v>
@@ -683,7 +683,7 @@
         <v>4.94</v>
       </c>
       <c r="I3" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J3" t="n">
         <v>28.16</v>
@@ -758,7 +758,7 @@
         <v>0.74</v>
       </c>
       <c r="I4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J4" t="n">
         <v>27.99</v>
@@ -833,7 +833,7 @@
         <v>-9.119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J5" t="n">
         <v>27.69</v>
@@ -912,7 +912,7 @@
         <v>-7.1</v>
       </c>
       <c r="I6" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J6" t="n">
         <v>27.4</v>
@@ -991,7 +991,7 @@
         <v>-6.32</v>
       </c>
       <c r="I7" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J7" t="n">
         <v>27.4</v>
@@ -1066,7 +1066,7 @@
         <v>4.86</v>
       </c>
       <c r="I8" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J8" t="n">
         <v>27.44</v>
@@ -1141,7 +1141,7 @@
         <v>-17.28</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>27.25</v>
@@ -1216,7 +1216,7 @@
         <v>4.54</v>
       </c>
       <c r="I10" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J10" t="n">
         <v>27.03</v>
@@ -1291,7 +1291,7 @@
         <v>-9.789999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J11" t="n">
         <v>26.7</v>
@@ -1366,7 +1366,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J12" t="n">
         <v>26.46</v>
@@ -1441,7 +1441,7 @@
         <v>6.29</v>
       </c>
       <c r="I13" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J13" t="n">
         <v>26.24</v>
@@ -1516,7 +1516,7 @@
         <v>-12.39</v>
       </c>
       <c r="I14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J14" t="n">
         <v>25.82</v>
@@ -1595,7 +1595,7 @@
         <v>8.59</v>
       </c>
       <c r="I15" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J15" t="n">
         <v>25.49</v>
@@ -1670,7 +1670,7 @@
         <v>-13.84</v>
       </c>
       <c r="I16" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J16" t="n">
         <v>25.07</v>
@@ -1753,7 +1753,7 @@
         <v>-3.19</v>
       </c>
       <c r="I17" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J17" t="n">
         <v>24.58</v>
@@ -1836,7 +1836,7 @@
         <v>5.09</v>
       </c>
       <c r="I18" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J18" t="n">
         <v>24.13</v>
@@ -1915,7 +1915,7 @@
         <v>-1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J19" t="n">
         <v>23.66</v>
@@ -1994,7 +1994,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J20" t="n">
         <v>23.23</v>
@@ -2069,7 +2069,7 @@
         <v>4.98</v>
       </c>
       <c r="I21" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J21" t="n">
         <v>22.84</v>
@@ -2144,7 +2144,7 @@
         <v>-4.12</v>
       </c>
       <c r="I22" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J22" t="n">
         <v>22.34</v>
@@ -2219,7 +2219,7 @@
         <v>2.22</v>
       </c>
       <c r="I23" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J23" t="n">
         <v>21.79</v>
@@ -2294,7 +2294,7 @@
         <v>-2.17</v>
       </c>
       <c r="I24" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J24" t="n">
         <v>21.21</v>
@@ -2369,7 +2369,7 @@
         <v>-3.28</v>
       </c>
       <c r="I25" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J25" t="n">
         <v>20.74</v>
@@ -2444,7 +2444,7 @@
         <v>8.93</v>
       </c>
       <c r="I26" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J26" t="n">
         <v>20.45</v>
@@ -2519,7 +2519,7 @@
         <v>-1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J27" t="n">
         <v>20.23</v>
@@ -2594,7 +2594,7 @@
         <v>-8.6</v>
       </c>
       <c r="I28" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J28" t="n">
         <v>19.86</v>
@@ -2673,7 +2673,7 @@
         <v>-5.45</v>
       </c>
       <c r="I29" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J29" t="n">
         <v>19.66</v>
@@ -2748,7 +2748,7 @@
         <v>-9.779999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J30" t="n">
         <v>19.33</v>
@@ -2823,7 +2823,7 @@
         <v>-0.5</v>
       </c>
       <c r="I31" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J31" t="n">
         <v>19.11</v>
@@ -2898,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J32" t="n">
         <v>18.88</v>
@@ -2973,7 +2973,7 @@
         <v>1.95</v>
       </c>
       <c r="I33" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J33" t="n">
         <v>18.6</v>
@@ -3048,7 +3048,7 @@
         <v>-29.83</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>18.21</v>
@@ -3131,7 +3131,7 @@
         <v>-23.5</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>17.61</v>
@@ -3214,7 +3214,7 @@
         <v>4.83</v>
       </c>
       <c r="I36" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J36" t="n">
         <v>17.17</v>
@@ -3297,7 +3297,7 @@
         <v>-9.77</v>
       </c>
       <c r="I37" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J37" t="n">
         <v>16.72</v>
@@ -3380,7 +3380,7 @@
         <v>54.74</v>
       </c>
       <c r="I38" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J38" t="n">
         <v>16.45</v>
@@ -3459,7 +3459,7 @@
         <v>-24.61</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>16.03</v>
@@ -3542,7 +3542,7 @@
         <v>6.26</v>
       </c>
       <c r="I40" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J40" t="n">
         <v>15.56</v>
@@ -3625,7 +3625,7 @@
         <v>2.36</v>
       </c>
       <c r="I41" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J41" t="n">
         <v>15.04</v>
@@ -3704,7 +3704,7 @@
         <v>1.25</v>
       </c>
       <c r="I42" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J42" t="n">
         <v>14.58</v>
@@ -3779,7 +3779,7 @@
         <v>-11.93</v>
       </c>
       <c r="I43" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J43" t="n">
         <v>14.04</v>
@@ -3862,7 +3862,7 @@
         <v>-1.51</v>
       </c>
       <c r="I44" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J44" t="n">
         <v>13.5</v>
@@ -3941,7 +3941,7 @@
         <v>-5.35</v>
       </c>
       <c r="I45" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J45" t="n">
         <v>12.98</v>
@@ -4016,7 +4016,7 @@
         <v>5.42</v>
       </c>
       <c r="I46" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J46" t="n">
         <v>12.4</v>
@@ -4091,7 +4091,7 @@
         <v>12.14</v>
       </c>
       <c r="I47" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J47" t="n">
         <v>11.89</v>
@@ -4170,7 +4170,7 @@
         <v>16.59</v>
       </c>
       <c r="I48" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J48" t="n">
         <v>11.55</v>
@@ -4245,7 +4245,7 @@
         <v>2.85</v>
       </c>
       <c r="I49" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J49" t="n">
         <v>11.28</v>
@@ -4320,7 +4320,7 @@
         <v>-0.41</v>
       </c>
       <c r="I50" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J50" t="n">
         <v>11.09</v>
@@ -4395,7 +4395,7 @@
         <v>-3.51</v>
       </c>
       <c r="I51" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J51" t="n">
         <v>10.89</v>
@@ -4470,7 +4470,7 @@
         <v>2.54</v>
       </c>
       <c r="I52" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J52" t="n">
         <v>10.7</v>
@@ -4545,7 +4545,7 @@
         <v>-0.5</v>
       </c>
       <c r="I53" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J53" t="n">
         <v>10.49</v>
@@ -4620,7 +4620,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J54" t="n">
         <v>10.59</v>
@@ -4695,7 +4695,7 @@
         <v>-1.81</v>
       </c>
       <c r="I55" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J55" t="n">
         <v>10.8</v>
@@ -4770,7 +4770,7 @@
         <v>-3.15</v>
       </c>
       <c r="I56" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J56" t="n">
         <v>10.98</v>
@@ -4845,7 +4845,7 @@
         <v>5.08</v>
       </c>
       <c r="I57" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J57" t="n">
         <v>11.23</v>
@@ -4920,7 +4920,7 @@
         <v>2.8</v>
       </c>
       <c r="I58" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J58" t="n">
         <v>11.27</v>
@@ -4995,7 +4995,7 @@
         <v>3.31</v>
       </c>
       <c r="I59" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J59" t="n">
         <v>11.49</v>
@@ -5070,7 +5070,7 @@
         <v>21.42</v>
       </c>
       <c r="I60" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J60" t="n">
         <v>11.84</v>
@@ -5145,7 +5145,7 @@
         <v>8.56</v>
       </c>
       <c r="I61" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J61" t="n">
         <v>12.24</v>
@@ -5220,7 +5220,7 @@
         <v>1.3</v>
       </c>
       <c r="I62" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J62" t="n">
         <v>12.65</v>
@@ -5295,7 +5295,7 @@
         <v>-1.97</v>
       </c>
       <c r="I63" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J63" t="n">
         <v>13.11</v>
@@ -5370,7 +5370,7 @@
         <v>-0.44</v>
       </c>
       <c r="I64" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J64" t="n">
         <v>13.56</v>
@@ -5445,7 +5445,7 @@
         <v>-1.75</v>
       </c>
       <c r="I65" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J65" t="n">
         <v>14.03</v>
@@ -5520,7 +5520,7 @@
         <v>-0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J66" t="n">
         <v>14.47</v>
@@ -5595,7 +5595,7 @@
         <v>-5.42</v>
       </c>
       <c r="I67" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J67" t="n">
         <v>14.8</v>
@@ -5670,7 +5670,7 @@
         <v>-2.89</v>
       </c>
       <c r="I68" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J68" t="n">
         <v>15.03</v>
@@ -5745,7 +5745,7 @@
         <v>-4.68</v>
       </c>
       <c r="I69" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J69" t="n">
         <v>15.19</v>
@@ -5820,7 +5820,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J70" t="n">
         <v>15.44</v>
@@ -5895,7 +5895,7 @@
         <v>-1.45</v>
       </c>
       <c r="I71" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J71" t="n">
         <v>15.7</v>
@@ -5970,7 +5970,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J72" t="n">
         <v>15.95</v>
@@ -6045,7 +6045,7 @@
         <v>-6.01</v>
       </c>
       <c r="I73" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J73" t="n">
         <v>16.16</v>
@@ -6124,7 +6124,7 @@
         <v>4.53</v>
       </c>
       <c r="I74" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J74" t="n">
         <v>16.33</v>
@@ -6199,7 +6199,7 @@
         <v>8.32</v>
       </c>
       <c r="I75" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J75" t="n">
         <v>16.6</v>
@@ -6274,7 +6274,7 @@
         <v>4.28</v>
       </c>
       <c r="I76" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J76" t="n">
         <v>16.92</v>
@@ -6349,7 +6349,7 @@
         <v>-1.47</v>
       </c>
       <c r="I77" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J77" t="n">
         <v>17.19</v>
@@ -6424,7 +6424,7 @@
         <v>1.98</v>
       </c>
       <c r="I78" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J78" t="n">
         <v>17.47</v>
@@ -6499,7 +6499,7 @@
         <v>7.33</v>
       </c>
       <c r="I79" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J79" t="n">
         <v>17.79</v>
@@ -6574,7 +6574,7 @@
         <v>6.34</v>
       </c>
       <c r="I80" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J80" t="n">
         <v>18.03</v>
@@ -6649,7 +6649,7 @@
         <v>-1.15</v>
       </c>
       <c r="I81" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J81" t="n">
         <v>18.18</v>
@@ -6724,7 +6724,7 @@
         <v>0.23</v>
       </c>
       <c r="I82" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J82" t="n">
         <v>18.32</v>
@@ -6799,7 +6799,7 @@
         <v>-7.59</v>
       </c>
       <c r="I83" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J83" t="n">
         <v>18.4</v>
@@ -6878,7 +6878,7 @@
         <v>9.27</v>
       </c>
       <c r="I84" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J84" t="n">
         <v>18.57</v>
@@ -6953,7 +6953,7 @@
         <v>-2.2</v>
       </c>
       <c r="I85" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J85" t="n">
         <v>18.74</v>
@@ -7028,7 +7028,7 @@
         <v>0.89</v>
       </c>
       <c r="I86" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J86" t="n">
         <v>18.92</v>
@@ -7103,7 +7103,7 @@
         <v>-1.86</v>
       </c>
       <c r="I87" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J87" t="n">
         <v>19.13</v>
@@ -7178,7 +7178,7 @@
         <v>1.75</v>
       </c>
       <c r="I88" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J88" t="n">
         <v>19.38</v>
@@ -7253,7 +7253,7 @@
         <v>11.35</v>
       </c>
       <c r="I89" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J89" t="n">
         <v>19.8</v>
@@ -7328,7 +7328,7 @@
         <v>2.63</v>
       </c>
       <c r="I90" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J90" t="n">
         <v>20.16</v>
@@ -7403,7 +7403,7 @@
         <v>2.52</v>
       </c>
       <c r="I91" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J91" t="n">
         <v>20.57</v>
@@ -7478,7 +7478,7 @@
         <v>-0.36</v>
       </c>
       <c r="I92" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J92" t="n">
         <v>20.97</v>
@@ -7553,7 +7553,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J93" t="n">
         <v>21.42</v>
@@ -7628,7 +7628,7 @@
         <v>-1.59</v>
       </c>
       <c r="I94" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J94" t="n">
         <v>21.81</v>
@@ -7703,7 +7703,7 @@
         <v>5.43</v>
       </c>
       <c r="I95" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J95" t="n">
         <v>22.2</v>
@@ -7778,7 +7778,7 @@
         <v>1.46</v>
       </c>
       <c r="I96" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J96" t="n">
         <v>22.57</v>
@@ -7853,7 +7853,7 @@
         <v>-5.53</v>
       </c>
       <c r="I97" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J97" t="n">
         <v>22.89</v>
@@ -7928,7 +7928,7 @@
         <v>5.61</v>
       </c>
       <c r="I98" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J98" t="n">
         <v>23.25</v>
@@ -8003,7 +8003,7 @@
         <v>1.02</v>
       </c>
       <c r="I99" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J99" t="n">
         <v>23.55</v>
@@ -8078,7 +8078,7 @@
         <v>2.7</v>
       </c>
       <c r="I100" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J100" t="n">
         <v>23.83</v>
@@ -8153,7 +8153,7 @@
         <v>-0.29</v>
       </c>
       <c r="I101" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J101" t="n">
         <v>24.12</v>
@@ -8228,7 +8228,7 @@
         <v>-2.9</v>
       </c>
       <c r="I102" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J102" t="n">
         <v>24.36</v>
@@ -8303,7 +8303,7 @@
         <v>2.98</v>
       </c>
       <c r="I103" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J103" t="n">
         <v>24.72</v>
@@ -8378,7 +8378,7 @@
         <v>-0.95</v>
       </c>
       <c r="I104" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J104" t="n">
         <v>24.98</v>
@@ -8453,7 +8453,7 @@
         <v>1.07</v>
       </c>
       <c r="I105" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J105" t="n">
         <v>25.28</v>
@@ -8528,7 +8528,7 @@
         <v>0.04</v>
       </c>
       <c r="I106" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J106" t="n">
         <v>25.57</v>
@@ -8603,7 +8603,7 @@
         <v>0.62</v>
       </c>
       <c r="I107" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J107" t="n">
         <v>25.89</v>
@@ -8678,7 +8678,7 @@
         <v>-4.26</v>
       </c>
       <c r="I108" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J108" t="n">
         <v>26.13</v>
@@ -8753,7 +8753,7 @@
         <v>-2.05</v>
       </c>
       <c r="I109" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J109" t="n">
         <v>26.22</v>
@@ -8832,7 +8832,7 @@
         <v>-0.62</v>
       </c>
       <c r="I110" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J110" t="n">
         <v>26.27</v>
@@ -8907,7 +8907,7 @@
         <v>-0.08</v>
       </c>
       <c r="I111" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J111" t="n">
         <v>26.29</v>
@@ -8982,7 +8982,7 @@
         <v>4.96</v>
       </c>
       <c r="I112" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J112" t="n">
         <v>26.38</v>
@@ -9057,7 +9057,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J113" t="n">
         <v>26.48</v>
@@ -9132,7 +9132,7 @@
         <v>2.15</v>
       </c>
       <c r="I114" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J114" t="n">
         <v>26.62</v>
@@ -9207,7 +9207,7 @@
         <v>-9.5</v>
       </c>
       <c r="I115" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J115" t="n">
         <v>26.57</v>
@@ -9286,7 +9286,7 @@
         <v>-3.61</v>
       </c>
       <c r="I116" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J116" t="n">
         <v>26.45</v>
@@ -9361,7 +9361,7 @@
         <v>3.82</v>
       </c>
       <c r="I117" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J117" t="n">
         <v>26.45</v>
@@ -9436,7 +9436,7 @@
         <v>-1.92</v>
       </c>
       <c r="I118" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J118" t="n">
         <v>26.36</v>
@@ -9511,7 +9511,7 @@
         <v>-2.16</v>
       </c>
       <c r="I119" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J119" t="n">
         <v>26.23</v>
@@ -9586,7 +9586,7 @@
         <v>4.21</v>
       </c>
       <c r="I120" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J120" t="n">
         <v>26.11</v>
@@ -9661,7 +9661,7 @@
         <v>2.84</v>
       </c>
       <c r="I121" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J121" t="n">
         <v>26.03</v>
@@ -9736,7 +9736,7 @@
         <v>-0.39</v>
       </c>
       <c r="I122" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J122" t="n">
         <v>25.99</v>
@@ -9811,7 +9811,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I123" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J123" t="n">
         <v>26.02</v>
@@ -9886,7 +9886,7 @@
         <v>4.54</v>
       </c>
       <c r="I124" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J124" t="n">
         <v>26.13</v>
@@ -9961,7 +9961,7 @@
         <v>0.51</v>
       </c>
       <c r="I125" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J125" t="n">
         <v>26.24</v>
@@ -10036,7 +10036,7 @@
         <v>-6.98</v>
       </c>
       <c r="I126" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J126" t="n">
         <v>26.24</v>
@@ -10111,7 +10111,7 @@
         <v>0.59</v>
       </c>
       <c r="I127" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J127" t="n">
         <v>26.24</v>
@@ -10186,7 +10186,7 @@
         <v>-4.65</v>
       </c>
       <c r="I128" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J128" t="n">
         <v>26.24</v>
@@ -10265,7 +10265,7 @@
         <v>-1.68</v>
       </c>
       <c r="I129" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J129" t="n">
         <v>26.24</v>
@@ -10340,7 +10340,7 @@
         <v>-1.75</v>
       </c>
       <c r="I130" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J130" t="n">
         <v>26.23</v>
@@ -10415,7 +10415,7 @@
         <v>8.25</v>
       </c>
       <c r="I131" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J131" t="n">
         <v>26.32</v>
@@ -10490,7 +10490,7 @@
         <v>-0.55</v>
       </c>
       <c r="I132" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J132" t="n">
         <v>26.34</v>
@@ -10565,7 +10565,7 @@
         <v>2.35</v>
       </c>
       <c r="I133" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J133" t="n">
         <v>26.38</v>
@@ -10640,7 +10640,7 @@
         <v>0.86</v>
       </c>
       <c r="I134" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J134" t="n">
         <v>26.41</v>
@@ -10715,7 +10715,7 @@
         <v>1.24</v>
       </c>
       <c r="I135" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J135" t="n">
         <v>26.59</v>
@@ -10790,7 +10790,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J136" t="n">
         <v>26.69</v>
@@ -10869,7 +10869,7 @@
         <v>-3.04</v>
       </c>
       <c r="I137" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J137" t="n">
         <v>26.7</v>
@@ -10948,7 +10948,7 @@
         <v>-1.35</v>
       </c>
       <c r="I138" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J138" t="n">
         <v>26.72</v>
@@ -11023,7 +11023,7 @@
         <v>2.97</v>
       </c>
       <c r="I139" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J139" t="n">
         <v>26.8</v>
@@ -11098,7 +11098,7 @@
         <v>3.08</v>
       </c>
       <c r="I140" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J140" t="n">
         <v>26.87</v>
@@ -11173,7 +11173,7 @@
         <v>2.38</v>
       </c>
       <c r="I141" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J141" t="n">
         <v>26.94</v>
@@ -11248,7 +11248,7 @@
         <v>0.37</v>
       </c>
       <c r="I142" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J142" t="n">
         <v>27.02</v>
@@ -11323,7 +11323,7 @@
         <v>5.23</v>
       </c>
       <c r="I143" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J143" t="n">
         <v>27.05</v>
@@ -11398,7 +11398,7 @@
         <v>2</v>
       </c>
       <c r="I144" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J144" t="n">
         <v>27.05</v>
@@ -11473,7 +11473,7 @@
         <v>0.45</v>
       </c>
       <c r="I145" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J145" t="n">
         <v>27.04</v>
@@ -11548,7 +11548,7 @@
         <v>2.39</v>
       </c>
       <c r="I146" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J146" t="n">
         <v>27.17</v>
@@ -11623,7 +11623,7 @@
         <v>1.6</v>
       </c>
       <c r="I147" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J147" t="n">
         <v>27.32</v>
@@ -11698,7 +11698,7 @@
         <v>-0.03</v>
       </c>
       <c r="I148" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J148" t="n">
         <v>27.53</v>
@@ -11773,7 +11773,7 @@
         <v>10.41</v>
       </c>
       <c r="I149" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J149" t="n">
         <v>27.92</v>
@@ -11848,7 +11848,7 @@
         <v>-1.84</v>
       </c>
       <c r="I150" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J150" t="n">
         <v>28.3</v>
@@ -11923,7 +11923,7 @@
         <v>4.27</v>
       </c>
       <c r="I151" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J151" t="n">
         <v>28.65</v>
@@ -11998,7 +11998,7 @@
         <v>-0.35</v>
       </c>
       <c r="I152" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J152" t="n">
         <v>29</v>
@@ -12073,7 +12073,7 @@
         <v>-0.29</v>
       </c>
       <c r="I153" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J153" t="n">
         <v>29.32</v>
@@ -12148,7 +12148,7 @@
         <v>-1.02</v>
       </c>
       <c r="I154" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J154" t="n">
         <v>29.6</v>
@@ -12223,7 +12223,7 @@
         <v>0.5</v>
       </c>
       <c r="I155" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J155" t="n">
         <v>29.88</v>
@@ -12298,7 +12298,7 @@
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J156" t="n">
         <v>30.28</v>
@@ -12373,7 +12373,7 @@
         <v>2.41</v>
       </c>
       <c r="I157" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J157" t="n">
         <v>30.75</v>
@@ -12448,7 +12448,7 @@
         <v>5.8</v>
       </c>
       <c r="I158" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J158" t="n">
         <v>31.35</v>
@@ -12523,7 +12523,7 @@
         <v>6</v>
       </c>
       <c r="I159" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J159" t="n">
         <v>32.02</v>
@@ -12598,7 +12598,7 @@
         <v>-2.18</v>
       </c>
       <c r="I160" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J160" t="n">
         <v>32.61</v>
@@ -12673,7 +12673,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J161" t="n">
         <v>33.34</v>
@@ -12748,7 +12748,7 @@
         <v>-6.91</v>
       </c>
       <c r="I162" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J162" t="n">
         <v>33.93</v>
@@ -12823,7 +12823,7 @@
         <v>10.18</v>
       </c>
       <c r="I163" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J163" t="n">
         <v>34.64</v>
@@ -12898,7 +12898,7 @@
         <v>-1.26</v>
       </c>
       <c r="I164" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J164" t="n">
         <v>35.29</v>
@@ -12973,7 +12973,7 @@
         <v>-19</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>35.53</v>
@@ -13052,7 +13052,7 @@
         <v>14.39</v>
       </c>
       <c r="I166" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J166" t="n">
         <v>35.99</v>
@@ -13127,7 +13127,7 @@
         <v>-6.39</v>
       </c>
       <c r="I167" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J167" t="n">
         <v>36.3</v>
@@ -13202,7 +13202,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="I168" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J168" t="n">
         <v>36.78</v>
@@ -13277,7 +13277,7 @@
         <v>1.48</v>
       </c>
       <c r="I169" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J169" t="n">
         <v>37.12</v>
@@ -13352,7 +13352,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J170" t="n">
         <v>37.48</v>
@@ -13427,7 +13427,7 @@
         <v>4.84</v>
       </c>
       <c r="I171" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J171" t="n">
         <v>37.88</v>
@@ -13502,7 +13502,7 @@
         <v>-1.73</v>
       </c>
       <c r="I172" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J172" t="n">
         <v>38.24</v>
@@ -13577,7 +13577,7 @@
         <v>-7.52</v>
       </c>
       <c r="I173" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J173" t="n">
         <v>38.44</v>
@@ -13656,7 +13656,7 @@
         <v>7.25</v>
       </c>
       <c r="I174" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J174" t="n">
         <v>38.81</v>
@@ -13731,7 +13731,7 @@
         <v>4.79</v>
       </c>
       <c r="I175" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J175" t="n">
         <v>39.27</v>
@@ -13806,7 +13806,7 @@
         <v>8.58</v>
       </c>
       <c r="I176" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J176" t="n">
         <v>39.91</v>
@@ -13881,7 +13881,7 @@
         <v>0.26</v>
       </c>
       <c r="I177" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J177" t="n">
         <v>40.51</v>
@@ -13956,7 +13956,7 @@
         <v>5.16</v>
       </c>
       <c r="I178" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J178" t="n">
         <v>41.14</v>
@@ -14031,7 +14031,7 @@
         <v>-4.03</v>
       </c>
       <c r="I179" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J179" t="n">
         <v>41.55</v>
@@ -14106,7 +14106,7 @@
         <v>0.82</v>
       </c>
       <c r="I180" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J180" t="n">
         <v>42.03</v>
@@ -14181,7 +14181,7 @@
         <v>1.68</v>
       </c>
       <c r="I181" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J181" t="n">
         <v>42.37</v>
@@ -14256,7 +14256,7 @@
         <v>-11.91</v>
       </c>
       <c r="I182" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J182" t="n">
         <v>42.57</v>
@@ -14331,7 +14331,7 @@
         <v>9.42</v>
       </c>
       <c r="I183" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J183" t="n">
         <v>42.77</v>
@@ -14406,7 +14406,7 @@
         <v>-8.16</v>
       </c>
       <c r="I184" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J184" t="n">
         <v>42.81</v>
@@ -14481,7 +14481,7 @@
         <v>-2.95</v>
       </c>
       <c r="I185" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J185" t="n">
         <v>43.19</v>
@@ -14560,7 +14560,7 @@
         <v>7.72</v>
       </c>
       <c r="I186" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J186" t="n">
         <v>43.48</v>
@@ -14635,7 +14635,7 @@
         <v>-7.01</v>
       </c>
       <c r="I187" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J187" t="n">
         <v>43.74</v>
@@ -14714,7 +14714,7 @@
         <v>4.55</v>
       </c>
       <c r="I188" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J188" t="n">
         <v>43.92</v>
@@ -14789,7 +14789,7 @@
         <v>-10.28</v>
       </c>
       <c r="I189" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J189" t="n">
         <v>43.86</v>
@@ -14864,7 +14864,7 @@
         <v>-0.92</v>
       </c>
       <c r="I190" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J190" t="n">
         <v>43.79</v>
@@ -14939,7 +14939,7 @@
         <v>-5.18</v>
       </c>
       <c r="I191" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J191" t="n">
         <v>43.52</v>
@@ -15014,7 +15014,7 @@
         <v>-6.76</v>
       </c>
       <c r="I192" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J192" t="n">
         <v>43.16</v>
@@ -15093,7 +15093,7 @@
         <v>4.69</v>
       </c>
       <c r="I193" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J193" t="n">
         <v>43.04</v>
@@ -15168,7 +15168,7 @@
         <v>-14.33</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>42.52</v>
@@ -15251,7 +15251,7 @@
         <v>2.99</v>
       </c>
       <c r="I195" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J195" t="n">
         <v>41.95</v>
@@ -15326,7 +15326,7 @@
         <v>13.02</v>
       </c>
       <c r="I196" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J196" t="n">
         <v>41.4</v>
@@ -15401,7 +15401,7 @@
         <v>0.86</v>
       </c>
       <c r="I197" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J197" t="n">
         <v>40.86</v>
@@ -15476,7 +15476,7 @@
         <v>8.33</v>
       </c>
       <c r="I198" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J198" t="n">
         <v>40.35</v>
@@ -15551,7 +15551,7 @@
         <v>5.29</v>
       </c>
       <c r="I199" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J199" t="n">
         <v>40.05</v>
@@ -15626,7 +15626,7 @@
         <v>0.12</v>
       </c>
       <c r="I200" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J200" t="n">
         <v>39.72</v>
@@ -15701,7 +15701,7 @@
         <v>6.03</v>
       </c>
       <c r="I201" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J201" t="n">
         <v>39.48</v>
@@ -15776,7 +15776,7 @@
         <v>6.35</v>
       </c>
       <c r="I202" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J202" t="n">
         <v>39.67</v>
@@ -15851,7 +15851,7 @@
         <v>-3.05</v>
       </c>
       <c r="I203" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J203" t="n">
         <v>39.59</v>
@@ -15926,7 +15926,7 @@
         <v>2.97</v>
       </c>
       <c r="I204" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J204" t="n">
         <v>39.76</v>
@@ -16001,7 +16001,7 @@
         <v>3.21</v>
       </c>
       <c r="I205" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J205" t="n">
         <v>40.08</v>
@@ -16076,7 +16076,7 @@
         <v>-0.42</v>
       </c>
       <c r="I206" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J206" t="n">
         <v>40.22</v>
@@ -16151,7 +16151,7 @@
         <v>3.89</v>
       </c>
       <c r="I207" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J207" t="n">
         <v>40.61</v>
@@ -16226,7 +16226,7 @@
         <v>-1.73</v>
       </c>
       <c r="I208" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J208" t="n">
         <v>40.86</v>
@@ -16301,7 +16301,7 @@
         <v>-14.52</v>
       </c>
       <c r="I209" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>40.99</v>
@@ -16376,7 +16376,7 @@
         <v>-1.27</v>
       </c>
       <c r="I210" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J210" t="n">
         <v>41.1</v>
@@ -16451,7 +16451,7 @@
         <v>-1.68</v>
       </c>
       <c r="I211" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J211" t="n">
         <v>41.29</v>
@@ -16530,7 +16530,7 @@
         <v>-11.05</v>
       </c>
       <c r="I212" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J212" t="n">
         <v>41.37</v>
@@ -16605,7 +16605,7 @@
         <v>7.11</v>
       </c>
       <c r="I213" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J213" t="n">
         <v>41.5</v>
@@ -16680,7 +16680,7 @@
         <v>8.15</v>
       </c>
       <c r="I214" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J214" t="n">
         <v>42.05</v>
@@ -16755,7 +16755,7 @@
         <v>3.69</v>
       </c>
       <c r="I215" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J215" t="n">
         <v>42.62</v>
@@ -16830,7 +16830,7 @@
         <v>1.02</v>
       </c>
       <c r="I216" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J216" t="n">
         <v>43.01</v>
@@ -16905,7 +16905,7 @@
         <v>1.17</v>
       </c>
       <c r="I217" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J217" t="n">
         <v>43.41</v>
@@ -16980,7 +16980,7 @@
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J218" t="n">
         <v>43.67</v>
@@ -17055,7 +17055,7 @@
         <v>-0.88</v>
       </c>
       <c r="I219" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J219" t="n">
         <v>43.79</v>
@@ -17130,7 +17130,7 @@
         <v>-0.34</v>
       </c>
       <c r="I220" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J220" t="n">
         <v>43.91</v>
@@ -17209,7 +17209,7 @@
         <v>-3.76</v>
       </c>
       <c r="I221" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J221" t="n">
         <v>43.82</v>
@@ -17284,7 +17284,7 @@
         <v>12.4</v>
       </c>
       <c r="I222" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J222" t="n">
         <v>43.86</v>
@@ -17359,7 +17359,7 @@
         <v>4.19</v>
       </c>
       <c r="I223" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J223" t="n">
         <v>44.06</v>
@@ -17434,7 +17434,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I224" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J224" t="n">
         <v>44.43</v>
@@ -17509,7 +17509,7 @@
         <v>-3.17</v>
       </c>
       <c r="I225" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J225" t="n">
         <v>44.65</v>
@@ -17584,7 +17584,7 @@
         <v>-5.05</v>
       </c>
       <c r="I226" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J226" t="n">
         <v>44.74</v>
@@ -17659,7 +17659,7 @@
         <v>8.65</v>
       </c>
       <c r="I227" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J227" t="n">
         <v>44.96</v>
@@ -17734,7 +17734,7 @@
         <v>1.3</v>
       </c>
       <c r="I228" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J228" t="n">
         <v>45.25</v>
@@ -17809,7 +17809,7 @@
         <v>2.6</v>
       </c>
       <c r="I229" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J229" t="n">
         <v>45.97</v>
@@ -17884,7 +17884,7 @@
         <v>-1.23</v>
       </c>
       <c r="I230" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J230" t="n">
         <v>46.68</v>
@@ -17959,7 +17959,7 @@
         <v>4.88</v>
       </c>
       <c r="I231" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J231" t="n">
         <v>47.56</v>
@@ -18034,7 +18034,7 @@
         <v>4.6</v>
       </c>
       <c r="I232" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J232" t="n">
         <v>48.79</v>
@@ -18109,7 +18109,7 @@
         <v>-4.63</v>
       </c>
       <c r="I233" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J233" t="n">
         <v>49.76</v>
@@ -18184,7 +18184,7 @@
         <v>9.57</v>
       </c>
       <c r="I234" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J234" t="n">
         <v>50.85</v>
@@ -18259,7 +18259,7 @@
         <v>0.38</v>
       </c>
       <c r="I235" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J235" t="n">
         <v>51.87</v>
@@ -18334,7 +18334,7 @@
         <v>-3.33</v>
       </c>
       <c r="I236" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J236" t="n">
         <v>52.76</v>
@@ -18409,7 +18409,7 @@
         <v>-1.46</v>
       </c>
       <c r="I237" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J237" t="n">
         <v>53.59</v>
@@ -18484,7 +18484,7 @@
         <v>7.02</v>
       </c>
       <c r="I238" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J238" t="n">
         <v>54.62</v>
@@ -18559,7 +18559,7 @@
         <v>7.89</v>
       </c>
       <c r="I239" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J239" t="n">
         <v>55.94</v>
@@ -18634,7 +18634,7 @@
         <v>0.54</v>
       </c>
       <c r="I240" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J240" t="n">
         <v>57.28</v>
@@ -18709,7 +18709,7 @@
         <v>-12.31</v>
       </c>
       <c r="I241" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J241" t="n">
         <v>58.26</v>
@@ -18784,7 +18784,7 @@
         <v>5.52</v>
       </c>
       <c r="I242" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J242" t="n">
         <v>59.16</v>
@@ -18859,7 +18859,7 @@
         <v>-6.14</v>
       </c>
       <c r="I243" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J243" t="n">
         <v>59.76</v>
@@ -18934,7 +18934,7 @@
         <v>-13.08</v>
       </c>
       <c r="I244" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J244" t="n">
         <v>59.72</v>
@@ -19013,7 +19013,7 @@
         <v>0.11</v>
       </c>
       <c r="I245" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J245" t="n">
         <v>59.77</v>
@@ -19088,7 +19088,7 @@
         <v>15.95</v>
       </c>
       <c r="I246" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J246" t="n">
         <v>60.37</v>
@@ -19163,7 +19163,7 @@
         <v>3.69</v>
       </c>
       <c r="I247" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J247" t="n">
         <v>60.88</v>
@@ -19238,7 +19238,7 @@
         <v>-1.08</v>
       </c>
       <c r="I248" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J248" t="n">
         <v>61.31</v>
@@ -19313,7 +19313,7 @@
         <v>7.44</v>
       </c>
       <c r="I249" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J249" t="n">
         <v>61.91</v>
@@ -19388,7 +19388,7 @@
         <v>-7.28</v>
       </c>
       <c r="I250" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J250" t="n">
         <v>62.29</v>
@@ -19463,7 +19463,7 @@
         <v>2.36</v>
       </c>
       <c r="I251" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J251" t="n">
         <v>62.62</v>
@@ -19538,7 +19538,7 @@
         <v>-0.37</v>
       </c>
       <c r="I252" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J252" t="n">
         <v>62.8</v>
@@ -19613,7 +19613,7 @@
         <v>3.02</v>
       </c>
       <c r="I253" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J253" t="n">
         <v>63.22</v>
@@ -19688,7 +19688,7 @@
         <v>-1.6</v>
       </c>
       <c r="I254" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J254" t="n">
         <v>63.31</v>
@@ -19763,7 +19763,7 @@
         <v>2.88</v>
       </c>
       <c r="I255" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J255" t="n">
         <v>63.47</v>
@@ -19838,7 +19838,7 @@
         <v>-1.86</v>
       </c>
       <c r="I256" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J256" t="n">
         <v>63.69</v>
@@ -19913,7 +19913,7 @@
         <v>4.06</v>
       </c>
       <c r="I257" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J257" t="n">
         <v>64.08</v>
@@ -19988,7 +19988,7 @@
         <v>4.85</v>
       </c>
       <c r="I258" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J258" t="n">
         <v>64.42</v>
@@ -20063,7 +20063,7 @@
         <v>-9.07</v>
       </c>
       <c r="I259" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J259" t="n">
         <v>64.19</v>
@@ -20138,7 +20138,7 @@
         <v>-3.94</v>
       </c>
       <c r="I260" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J260" t="n">
         <v>63.8</v>
@@ -20217,7 +20217,7 @@
         <v>-0.02</v>
       </c>
       <c r="I261" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J261" t="n">
         <v>63.85</v>
@@ -20292,7 +20292,7 @@
         <v>-14.89</v>
       </c>
       <c r="I262" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J262" s="4" t="n">
         <v>63.26</v>
@@ -20371,7 +20371,7 @@
         <v>5.99</v>
       </c>
       <c r="I263" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J263" t="n">
         <v>63.03</v>
@@ -20446,7 +20446,7 @@
         <v>-3.22</v>
       </c>
       <c r="I264" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J264" t="n">
         <v>63.11</v>
@@ -20525,7 +20525,7 @@
         <v>-12.6</v>
       </c>
       <c r="I265" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J265" t="n">
         <v>62.84</v>
@@ -20604,7 +20604,7 @@
         <v>11.35</v>
       </c>
       <c r="I266" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J266" t="n">
         <v>62.42</v>
@@ -20679,7 +20679,7 @@
         <v>2.36</v>
       </c>
       <c r="I267" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J267" t="n">
         <v>61.95</v>
@@ -20754,7 +20754,7 @@
         <v>2.75</v>
       </c>
       <c r="I268" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J268" t="n">
         <v>61.59</v>
@@ -20829,7 +20829,7 @@
         <v>-10.35</v>
       </c>
       <c r="I269" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J269" t="n">
         <v>60.7</v>
@@ -20902,7 +20902,7 @@
         <v>0.88</v>
       </c>
       <c r="I270" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J270" t="n">
         <v>60.08</v>
@@ -20981,7 +20981,7 @@
         <v>5.84</v>
       </c>
       <c r="I271" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J271" t="n">
         <v>59.54</v>
@@ -21056,7 +21056,7 @@
         <v>2.35</v>
       </c>
       <c r="I272" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J272" t="n">
         <v>59.07</v>
@@ -21131,7 +21131,7 @@
         <v>-1.69</v>
       </c>
       <c r="I273" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J273" t="n">
         <v>58.45</v>
@@ -21206,7 +21206,7 @@
         <v>1.54</v>
       </c>
       <c r="I274" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J274" t="n">
         <v>57.93</v>
@@ -21281,7 +21281,7 @@
         <v>-6.75</v>
       </c>
       <c r="I275" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J275" t="n">
         <v>57.14</v>
@@ -21360,7 +21360,7 @@
         <v>3.7</v>
       </c>
       <c r="I276" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J276" t="n">
         <v>56.5</v>
@@ -21435,7 +21435,7 @@
         <v>3.62</v>
       </c>
       <c r="I277" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J277" t="n">
         <v>55.82</v>
@@ -21510,7 +21510,7 @@
         <v>3.79</v>
       </c>
       <c r="I278" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J278" t="n">
         <v>55.08</v>
@@ -21585,7 +21585,7 @@
         <v>-14.14</v>
       </c>
       <c r="I279" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J279" t="n">
         <v>54.26</v>
@@ -21664,7 +21664,7 @@
         <v>-4.82</v>
       </c>
       <c r="I280" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J280" t="n">
         <v>53.45</v>
@@ -21743,7 +21743,7 @@
         <v>-12.86</v>
       </c>
       <c r="I281" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J281" t="n">
         <v>52.34</v>
@@ -21818,7 +21818,7 @@
         <v>17.96</v>
       </c>
       <c r="I282" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J282" t="n">
         <v>52.07</v>
@@ -21893,7 +21893,7 @@
         <v>9.09</v>
       </c>
       <c r="I283" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J283" t="n">
         <v>51.85</v>
@@ -21968,7 +21968,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I284" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J284" t="n">
         <v>51.75</v>
@@ -22043,7 +22043,7 @@
         <v>3.89</v>
       </c>
       <c r="I285" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J285" t="n">
         <v>52.1</v>
@@ -22118,7 +22118,7 @@
         <v>3.18</v>
       </c>
       <c r="I286" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J286" t="n">
         <v>52.26</v>
@@ -22197,7 +22197,7 @@
         <v>19.38</v>
       </c>
       <c r="I287" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J287" t="n">
         <v>52.9</v>
@@ -22272,7 +22272,7 @@
         <v>6.63</v>
       </c>
       <c r="I288" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J288" t="n">
         <v>53.7</v>
@@ -22347,7 +22347,7 @@
         <v>6.13</v>
       </c>
       <c r="I289" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J289" t="n">
         <v>55</v>
@@ -22422,7 +22422,7 @@
         <v>5.46</v>
       </c>
       <c r="I290" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J290" t="n">
         <v>56.49</v>
@@ -22497,7 +22497,7 @@
         <v>5.89</v>
       </c>
       <c r="I291" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J291" t="n">
         <v>58.07</v>
@@ -22572,7 +22572,7 @@
         <v>0.76</v>
       </c>
       <c r="I292" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J292" t="n">
         <v>59.62</v>
@@ -22647,7 +22647,7 @@
         <v>2.81</v>
       </c>
       <c r="I293" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J293" t="n">
         <v>61.34</v>
@@ -22722,7 +22722,7 @@
         <v>7.15</v>
       </c>
       <c r="I294" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J294" t="n">
         <v>63.33</v>
@@ -22797,7 +22797,7 @@
         <v>1.33</v>
       </c>
       <c r="I295" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J295" t="n">
         <v>65.56999999999999</v>
@@ -22872,7 +22872,7 @@
         <v>2.24</v>
       </c>
       <c r="I296" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J296" t="n">
         <v>67.81999999999999</v>
@@ -22947,7 +22947,7 @@
         <v>7.69</v>
       </c>
       <c r="I297" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J297" t="n">
         <v>70.34999999999999</v>
@@ -23022,7 +23022,7 @@
         <v>6.75</v>
       </c>
       <c r="I298" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J298" t="n">
         <v>73.14</v>
@@ -23097,7 +23097,7 @@
         <v>13.79</v>
       </c>
       <c r="I299" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J299" t="n">
         <v>77.09999999999999</v>
@@ -23172,7 +23172,7 @@
         <v>-3.84</v>
       </c>
       <c r="I300" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J300" t="n">
         <v>80.94</v>
@@ -23247,7 +23247,7 @@
         <v>-11.21</v>
       </c>
       <c r="I301" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J301" t="n">
         <v>84.38</v>
@@ -23322,7 +23322,7 @@
         <v>7.67</v>
       </c>
       <c r="I302" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J302" t="n">
         <v>87.88</v>
@@ -23397,7 +23397,7 @@
         <v>7.64</v>
       </c>
       <c r="I303" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J303" t="n">
         <v>91.62</v>
@@ -23472,7 +23472,7 @@
         <v>2.69</v>
       </c>
       <c r="I304" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J304" t="n">
         <v>95.5</v>
@@ -23547,7 +23547,7 @@
         <v>-2.18</v>
       </c>
       <c r="I305" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J305" t="n">
         <v>99.13</v>
@@ -23622,7 +23622,7 @@
         <v>13.02</v>
       </c>
       <c r="I306" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J306" t="n">
         <v>103.51</v>
@@ -23697,7 +23697,7 @@
         <v>15.04</v>
       </c>
       <c r="I307" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J307" t="n">
         <v>108.42</v>
@@ -23772,7 +23772,7 @@
         <v>-8.289999999999999</v>
       </c>
       <c r="I308" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J308" t="n">
         <v>112.43</v>
@@ -23847,7 +23847,7 @@
         <v>16.33</v>
       </c>
       <c r="I309" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J309" t="n">
         <v>117.45</v>
@@ -23922,7 +23922,7 @@
         <v>7.62</v>
       </c>
       <c r="I310" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J310" t="n">
         <v>122.94</v>
@@ -23997,7 +23997,7 @@
         <v>-9.4</v>
       </c>
       <c r="I311" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J311" t="n">
         <v>127.3</v>
@@ -24072,7 +24072,7 @@
         <v>6.79</v>
       </c>
       <c r="I312" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J312" t="n">
         <v>132.21</v>
@@ -24147,7 +24147,7 @@
         <v>1.06</v>
       </c>
       <c r="I313" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J313" t="n">
         <v>137.1</v>
@@ -24222,7 +24222,7 @@
         <v>-11.82</v>
       </c>
       <c r="I314" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J314" t="n">
         <v>140.57</v>
@@ -24297,7 +24297,7 @@
         <v>-7.57</v>
       </c>
       <c r="I315" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J315" t="n">
         <v>143.36</v>
@@ -24372,7 +24372,7 @@
         <v>0.09</v>
       </c>
       <c r="I316" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J316" t="n">
         <v>146.05</v>
@@ -24447,7 +24447,7 @@
         <v>14.03</v>
       </c>
       <c r="I317" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J317" t="n">
         <v>149.42</v>
@@ -24522,7 +24522,7 @@
         <v>2.99</v>
       </c>
       <c r="I318" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J318" t="n">
         <v>152.7</v>
@@ -24597,7 +24597,7 @@
         <v>6.83</v>
       </c>
       <c r="I319" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J319" t="n">
         <v>155.81</v>
@@ -24672,7 +24672,7 @@
         <v>18.48</v>
       </c>
       <c r="I320" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J320" t="n">
         <v>160.93</v>
@@ -24747,7 +24747,7 @@
         <v>-3.46</v>
       </c>
       <c r="I321" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J321" t="n">
         <v>166.34</v>
@@ -24822,7 +24822,7 @@
         <v>3.05</v>
       </c>
       <c r="I322" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J322" t="n">
         <v>171.67</v>
@@ -24897,7 +24897,7 @@
         <v>-0.13</v>
       </c>
       <c r="I323" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J323" t="n">
         <v>176.54</v>
@@ -24972,7 +24972,7 @@
         <v>1.2</v>
       </c>
       <c r="I324" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J324" t="n">
         <v>181.37</v>
@@ -25047,7 +25047,7 @@
         <v>17.31</v>
       </c>
       <c r="I325" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J325" t="n">
         <v>188.3</v>
@@ -25122,7 +25122,7 @@
         <v>5.34</v>
       </c>
       <c r="I326" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J326" t="n">
         <v>195.12</v>
@@ -25197,7 +25197,7 @@
         <v>-6.36</v>
       </c>
       <c r="I327" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J327" t="n">
         <v>199.96</v>
@@ -25272,7 +25272,7 @@
         <v>-30.51</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J328" s="4" t="n">
         <v>201.48</v>
@@ -25351,7 +25351,7 @@
         <v>15.83</v>
       </c>
       <c r="I329" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J329" t="n">
         <v>203.2</v>
@@ -25426,7 +25426,7 @@
         <v>-4.61</v>
       </c>
       <c r="I330" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J330" t="n">
         <v>203.76</v>
@@ -25505,7 +25505,7 @@
         <v>-10.43</v>
       </c>
       <c r="I331" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J331" t="n">
         <v>204.17</v>
@@ -25580,7 +25580,7 @@
         <v>23.99</v>
       </c>
       <c r="I332" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J332" t="n">
         <v>206.15</v>
@@ -25655,7 +25655,7 @@
         <v>4.78</v>
       </c>
       <c r="I333" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J333" t="n">
         <v>208.58</v>
@@ -25730,7 +25730,7 @@
         <v>16.11</v>
       </c>
       <c r="I334" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J334" t="n">
         <v>213.99</v>
@@ -25805,7 +25805,7 @@
         <v>-16.99</v>
       </c>
       <c r="I335" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J335" s="4" t="n">
         <v>217.71</v>
@@ -25880,7 +25880,7 @@
         <v>3.39</v>
       </c>
       <c r="I336" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J336" t="n">
         <v>221.81</v>
@@ -25955,7 +25955,7 @@
         <v>19.43</v>
       </c>
       <c r="I337" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J337" t="n">
         <v>227.11</v>
@@ -26030,7 +26030,7 @@
         <v>7.69</v>
       </c>
       <c r="I338" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J338" t="n">
         <v>233.22</v>
@@ -26105,7 +26105,7 @@
         <v>-23.06</v>
       </c>
       <c r="I339" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J339" s="4" t="n">
         <v>235.26</v>
@@ -26184,7 +26184,7 @@
         <v>-0.8</v>
       </c>
       <c r="I340" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J340" t="n">
         <v>235.45</v>
@@ -26259,7 +26259,7 @@
         <v>10.03</v>
       </c>
       <c r="I341" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J341" t="n">
         <v>237.18</v>
@@ -26334,7 +26334,7 @@
         <v>-14.65</v>
       </c>
       <c r="I342" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J342" s="4" t="n">
         <v>236.73</v>
@@ -26413,7 +26413,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I343" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J343" t="n">
         <v>237.34</v>
@@ -26488,7 +26488,7 @@
         <v>12.76</v>
       </c>
       <c r="I344" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J344" t="n">
         <v>239.32</v>
@@ -26563,7 +26563,7 @@
         <v>-18.43</v>
       </c>
       <c r="I345" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J345" s="4" t="n">
         <v>236.89</v>
@@ -26642,7 +26642,7 @@
         <v>-16.59</v>
       </c>
       <c r="I346" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J346" s="4" t="n">
         <v>231.94</v>
@@ -26717,7 +26717,7 @@
         <v>7.26</v>
       </c>
       <c r="I347" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J347" t="n">
         <v>228.54</v>
@@ -26792,7 +26792,7 @@
         <v>-15.09</v>
       </c>
       <c r="I348" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J348" s="4" t="n">
         <v>227.67</v>
@@ -26871,7 +26871,7 @@
         <v>5.78</v>
       </c>
       <c r="I349" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J349" t="n">
         <v>225.84</v>
@@ -26946,7 +26946,7 @@
         <v>10.08</v>
       </c>
       <c r="I350" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J350" t="n">
         <v>225.38</v>
@@ -27021,7 +27021,7 @@
         <v>-0.1</v>
       </c>
       <c r="I351" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J351" t="n">
         <v>225.96</v>
@@ -27096,7 +27096,7 @@
         <v>-13.99</v>
       </c>
       <c r="I352" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J352" t="n">
         <v>223.03</v>
@@ -27175,7 +27175,7 @@
         <v>6.83</v>
       </c>
       <c r="I353" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J353" t="n">
         <v>220.13</v>
@@ -27250,7 +27250,7 @@
         <v>-6.29</v>
       </c>
       <c r="I354" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J354" t="n">
         <v>214.79</v>
@@ -27325,7 +27325,7 @@
         <v>-13.93</v>
       </c>
       <c r="I355" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J355" t="n">
         <v>210.61</v>
@@ -27400,7 +27400,7 @@
         <v>-4.92</v>
       </c>
       <c r="I356" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J356" t="n">
         <v>205.69</v>
@@ -27475,7 +27475,7 @@
         <v>0.99</v>
       </c>
       <c r="I357" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J357" t="n">
         <v>198.57</v>
@@ -27550,7 +27550,7 @@
         <v>15.89</v>
       </c>
       <c r="I358" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J358" t="n">
         <v>191.46</v>
@@ -27625,7 +27625,7 @@
         <v>1.54</v>
       </c>
       <c r="I359" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J359" t="n">
         <v>187.94</v>
@@ -27700,7 +27700,7 @@
         <v>-2.16</v>
       </c>
       <c r="I360" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J360" t="n">
         <v>184.34</v>
@@ -27775,7 +27775,7 @@
         <v>-13.14</v>
       </c>
       <c r="I361" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J361" t="n">
         <v>178.56</v>
@@ -27850,7 +27850,7 @@
         <v>-6.33</v>
       </c>
       <c r="I362" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J362" t="n">
         <v>174.19</v>
@@ -27929,7 +27929,7 @@
         <v>-14.52</v>
       </c>
       <c r="I363" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J363" s="4" t="n">
         <v>167.84</v>
@@ -28004,7 +28004,7 @@
         <v>-16.02</v>
       </c>
       <c r="I364" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J364" s="4" t="n">
         <v>159.11</v>
@@ -28083,7 +28083,7 @@
         <v>24.7</v>
       </c>
       <c r="I365" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J365" t="n">
         <v>153.97</v>
@@ -28158,7 +28158,7 @@
         <v>0</v>
       </c>
       <c r="I366" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J366" t="n">
         <v>150.64</v>
@@ -28233,7 +28233,7 @@
         <v>1.74</v>
       </c>
       <c r="I367" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J367" t="n">
         <v>146.74</v>
@@ -28308,7 +28308,7 @@
         <v>19.87</v>
       </c>
       <c r="I368" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J368" t="n">
         <v>145.48</v>
@@ -28383,7 +28383,7 @@
         <v>-5.6</v>
       </c>
       <c r="I369" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J369" t="n">
         <v>143.34</v>
@@ -28462,7 +28462,7 @@
         <v>0.2</v>
       </c>
       <c r="I370" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J370" t="n">
         <v>140.34</v>
@@ -28537,7 +28537,7 @@
         <v>5.99</v>
       </c>
       <c r="I371" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J371" t="n">
         <v>137.74</v>
@@ -28612,7 +28612,7 @@
         <v>-7.31</v>
       </c>
       <c r="I372" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J372" t="n">
         <v>135.97</v>
@@ -28691,7 +28691,7 @@
         <v>2.31</v>
       </c>
       <c r="I373" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J373" t="n">
         <v>133.79</v>
@@ -28766,7 +28766,7 @@
         <v>6.89</v>
       </c>
       <c r="I374" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J374" t="n">
         <v>132.62</v>
@@ -28841,7 +28841,7 @@
         <v>2.25</v>
       </c>
       <c r="I375" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J375" t="n">
         <v>132.76</v>
@@ -28916,7 +28916,7 @@
         <v>-0.28</v>
       </c>
       <c r="I376" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J376" t="n">
         <v>133.24</v>
@@ -28991,7 +28991,7 @@
         <v>4.54</v>
       </c>
       <c r="I377" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J377" t="n">
         <v>133.97</v>
@@ -29066,7 +29066,7 @@
         <v>-14.8</v>
       </c>
       <c r="I378" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J378" s="4" t="n">
         <v>132.5</v>
@@ -29145,7 +29145,7 @@
         <v>-6.48</v>
       </c>
       <c r="I379" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J379" t="n">
         <v>130.49</v>
@@ -29220,7 +29220,7 @@
         <v>1.22</v>
       </c>
       <c r="I380" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J380" t="n">
         <v>128.73</v>
@@ -29295,7 +29295,7 @@
         <v>-1.32</v>
       </c>
       <c r="I381" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J381" t="n">
         <v>127.92</v>
@@ -29370,7 +29370,7 @@
         <v>-7.82</v>
       </c>
       <c r="I382" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J382" t="n">
         <v>127.07</v>
@@ -29445,7 +29445,7 @@
         <v>4.05</v>
       </c>
       <c r="I383" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J383" t="n">
         <v>127.37</v>
@@ -29520,7 +29520,7 @@
         <v>0.8</v>
       </c>
       <c r="I384" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J384" t="n">
         <v>128.6</v>
@@ -29595,7 +29595,7 @@
         <v>5.54</v>
       </c>
       <c r="I385" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J385" t="n">
         <v>129.02</v>
@@ -29670,7 +29670,7 @@
         <v>-9.51</v>
       </c>
       <c r="I386" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J386" t="n">
         <v>128.85</v>
@@ -29745,7 +29745,7 @@
         <v>1.3</v>
       </c>
       <c r="I387" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J387" t="n">
         <v>128.66</v>
@@ -29820,7 +29820,7 @@
         <v>-6.1</v>
       </c>
       <c r="I388" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J388" t="n">
         <v>126.96</v>
@@ -29899,7 +29899,7 @@
         <v>0.42</v>
       </c>
       <c r="I389" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J389" t="n">
         <v>125.67</v>
@@ -29978,7 +29978,7 @@
         <v>0.37</v>
       </c>
       <c r="I390" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J390" t="n">
         <v>124.39</v>
@@ -30057,7 +30057,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="I391" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J391" t="n">
         <v>123.25</v>
@@ -30132,7 +30132,7 @@
         <v>5.11</v>
       </c>
       <c r="I392" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J392" t="n">
         <v>122.91</v>
@@ -30207,7 +30207,7 @@
         <v>2.11</v>
       </c>
       <c r="I393" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J393" t="n">
         <v>122.55</v>
@@ -30282,7 +30282,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="I394" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J394" t="n">
         <v>121.23</v>
@@ -30361,7 +30361,7 @@
         <v>5.24</v>
       </c>
       <c r="I395" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J395" t="n">
         <v>120.06</v>
@@ -30436,7 +30436,7 @@
         <v>-16.99</v>
       </c>
       <c r="I396" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J396" s="4" t="n">
         <v>117.87</v>
@@ -30515,7 +30515,7 @@
         <v>1.18</v>
       </c>
       <c r="I397" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J397" t="n">
         <v>115.41</v>
@@ -30590,7 +30590,7 @@
         <v>1.61</v>
       </c>
       <c r="I398" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J398" t="n">
         <v>114.15</v>
@@ -30665,7 +30665,7 @@
         <v>10.43</v>
       </c>
       <c r="I399" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J399" t="n">
         <v>113.86</v>
@@ -30740,7 +30740,7 @@
         <v>7.71</v>
       </c>
       <c r="I400" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J400" t="n">
         <v>113.93</v>
@@ -30815,7 +30815,7 @@
         <v>14.77</v>
       </c>
       <c r="I401" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J401" t="n">
         <v>115</v>
@@ -30890,7 +30890,7 @@
         <v>7.13</v>
       </c>
       <c r="I402" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J402" t="n">
         <v>117.04</v>
@@ -30965,7 +30965,7 @@
         <v>-3.75</v>
       </c>
       <c r="I403" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J403" t="n">
         <v>118.57</v>
@@ -31040,7 +31040,7 @@
         <v>0.05</v>
       </c>
       <c r="I404" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J404" t="n">
         <v>120.06</v>
@@ -31115,7 +31115,7 @@
         <v>3.5</v>
       </c>
       <c r="I405" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J405" t="n">
         <v>121.49</v>
@@ -31190,7 +31190,7 @@
         <v>-6.05</v>
       </c>
       <c r="I406" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J406" t="n">
         <v>123.04</v>
@@ -31265,7 +31265,7 @@
         <v>3.31</v>
       </c>
       <c r="I407" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J407" t="n">
         <v>124.75</v>
@@ -31340,7 +31340,7 @@
         <v>0.59</v>
       </c>
       <c r="I408" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J408" t="n">
         <v>126.85</v>
@@ -31415,7 +31415,7 @@
         <v>3.94</v>
       </c>
       <c r="I409" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J409" t="n">
         <v>129.22</v>
@@ -31490,7 +31490,7 @@
         <v>6.52</v>
       </c>
       <c r="I410" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J410" t="n">
         <v>132.08</v>
@@ -31565,7 +31565,7 @@
         <v>0.34</v>
       </c>
       <c r="I411" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J411" t="n">
         <v>134.43</v>
@@ -31640,7 +31640,7 @@
         <v>-0.01</v>
       </c>
       <c r="I412" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J412" t="n">
         <v>136.48</v>
@@ -31684,6 +31684,83 @@
       <c r="W412" s="3" t="n">
         <v>141.2</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>153.7</v>
+      </c>
+      <c r="D413" t="n">
+        <v>156.41</v>
+      </c>
+      <c r="E413" t="n">
+        <v>151.42</v>
+      </c>
+      <c r="F413" t="n">
+        <v>156.32</v>
+      </c>
+      <c r="G413" t="n">
+        <v>20509888</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>-4.83</v>
+      </c>
+      <c r="I413" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J413" t="n">
+        <v>138.01</v>
+      </c>
+      <c r="K413" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="L413" t="n">
+        <v>160.03</v>
+      </c>
+      <c r="M413" t="n">
+        <v>119.29</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="O413" t="n">
+        <v>42</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -3545,7 +3545,7 @@
         <v>14.2</v>
       </c>
       <c r="J40" t="n">
-        <v>15.56</v>
+        <v>15.55</v>
       </c>
       <c r="K40" t="n">
         <v>22.42</v>
@@ -31634,7 +31634,7 @@
         <v>164.26</v>
       </c>
       <c r="G412" t="n">
-        <v>44565100</v>
+        <v>45120400</v>
       </c>
       <c r="H412" s="2" t="n">
         <v>-0.01</v>
@@ -31700,40 +31700,40 @@
         <v>153.7</v>
       </c>
       <c r="D413" t="n">
-        <v>156.41</v>
+        <v>159.49</v>
       </c>
       <c r="E413" t="n">
         <v>151.42</v>
       </c>
       <c r="F413" t="n">
-        <v>156.32</v>
+        <v>158.91</v>
       </c>
       <c r="G413" t="n">
-        <v>20509888</v>
+        <v>50318638</v>
       </c>
       <c r="H413" s="2" t="n">
-        <v>-4.83</v>
+        <v>-3.26</v>
       </c>
       <c r="I413" t="n">
         <v>14.2</v>
       </c>
       <c r="J413" t="n">
-        <v>138.01</v>
+        <v>138.14</v>
       </c>
       <c r="K413" t="n">
-        <v>131.45</v>
+        <v>131.49</v>
       </c>
       <c r="L413" t="n">
-        <v>160.03</v>
+        <v>160.05</v>
       </c>
       <c r="M413" t="n">
-        <v>119.29</v>
+        <v>119.31</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>73.84</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="O413" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31751,13 +31751,13 @@
         </is>
       </c>
       <c r="S413" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="T413" s="3" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="3" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31696,41 +31696,25 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>153.7</v>
-      </c>
-      <c r="D413" t="n">
-        <v>159.49</v>
-      </c>
-      <c r="E413" t="n">
-        <v>151.42</v>
-      </c>
-      <c r="F413" t="n">
-        <v>158.91</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>50318638</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>-3.26</v>
+        <v>50470974</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>14.2</v>
       </c>
-      <c r="J413" t="n">
-        <v>138.14</v>
-      </c>
-      <c r="K413" t="n">
-        <v>131.49</v>
-      </c>
-      <c r="L413" t="n">
-        <v>160.05</v>
-      </c>
-      <c r="M413" t="n">
-        <v>119.31</v>
-      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>
@@ -31745,11 +31729,7 @@
           <t>BUY STOP</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr">
-        <is>
-          <t>3rd: MA120, 50% cash, 5d</t>
-        </is>
-      </c>
+      <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
         <v>5.28</v>
       </c>
@@ -31760,7 +31740,9 @@
         <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="3" t="inlineStr"/>
+      <c r="W413" s="3" t="n">
+        <v>141.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31696,25 +31696,41 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>153.7</v>
+      </c>
+      <c r="D413" t="n">
+        <v>159.49</v>
+      </c>
+      <c r="E413" t="n">
+        <v>151.42</v>
+      </c>
+      <c r="F413" t="n">
+        <v>158.91</v>
+      </c>
       <c r="G413" t="n">
-        <v>50470974</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>0</v>
+        <v>50770700</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>-3.26</v>
       </c>
       <c r="I413" t="n">
         <v>14.2</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>138.14</v>
+      </c>
+      <c r="K413" t="n">
+        <v>131.49</v>
+      </c>
+      <c r="L413" t="n">
+        <v>160.05</v>
+      </c>
+      <c r="M413" t="n">
+        <v>119.31</v>
+      </c>
       <c r="N413" s="2" t="n">
-        <v>81.23999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>
@@ -31729,7 +31745,11 @@
           <t>BUY STOP</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S413" t="n">
         <v>5.28</v>
       </c>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31733,7 +31733,7 @@
         <v>76.09999999999999</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31763,6 +31763,79 @@
       <c r="W413" s="3" t="n">
         <v>141.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>150.48</v>
+      </c>
+      <c r="D414" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="E414" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="F414" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="G414" t="n">
+        <v>33067080</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>139.93</v>
+      </c>
+      <c r="K414" t="n">
+        <v>131.26</v>
+      </c>
+      <c r="L414" t="n">
+        <v>160.52</v>
+      </c>
+      <c r="M414" t="n">
+        <v>119.85</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>66.78</v>
+      </c>
+      <c r="O414" t="n">
+        <v>41</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31709,7 +31709,7 @@
         <v>158.91</v>
       </c>
       <c r="G413" t="n">
-        <v>50770700</v>
+        <v>51367100</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>-3.26</v>
@@ -31782,37 +31782,37 @@
         <v>155.5</v>
       </c>
       <c r="E414" t="n">
-        <v>146.4</v>
+        <v>136.32</v>
       </c>
       <c r="F414" t="n">
-        <v>151.5</v>
+        <v>142.52</v>
       </c>
       <c r="G414" t="n">
-        <v>33067080</v>
+        <v>100232380</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>-4.66</v>
+        <v>-10.31</v>
       </c>
       <c r="I414" t="n">
         <v>14.2</v>
       </c>
       <c r="J414" t="n">
-        <v>139.93</v>
+        <v>139.48</v>
       </c>
       <c r="K414" t="n">
-        <v>131.26</v>
+        <v>131.11</v>
       </c>
       <c r="L414" t="n">
-        <v>160.52</v>
+        <v>160.45</v>
       </c>
       <c r="M414" t="n">
-        <v>119.85</v>
+        <v>119.81</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>66.78</v>
+        <v>60.27</v>
       </c>
       <c r="O414" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31826,13 +31826,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
       <c r="T414" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="3" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31788,7 +31788,7 @@
         <v>142.52</v>
       </c>
       <c r="G414" t="n">
-        <v>100232380</v>
+        <v>100692500</v>
       </c>
       <c r="H414" s="2" t="n">
         <v>-10.31</v>
@@ -31835,7 +31835,9 @@
         <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31812,7 +31812,7 @@
         <v>60.27</v>
       </c>
       <c r="O414" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31838,6 +31838,83 @@
       <c r="W414" s="3" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>148.18</v>
+      </c>
+      <c r="D415" t="n">
+        <v>148.13</v>
+      </c>
+      <c r="E415" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="F415" t="n">
+        <v>139.18</v>
+      </c>
+      <c r="G415" t="n">
+        <v>35484312</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="I415" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>140.35</v>
+      </c>
+      <c r="K415" t="n">
+        <v>131.06</v>
+      </c>
+      <c r="L415" t="n">
+        <v>160.81</v>
+      </c>
+      <c r="M415" t="n">
+        <v>120.29</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="O415" t="n">
+        <v>44</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T415" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U415" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31788,7 +31788,7 @@
         <v>142.52</v>
       </c>
       <c r="G414" t="n">
-        <v>100692500</v>
+        <v>101636900</v>
       </c>
       <c r="H414" s="2" t="n">
         <v>-10.31</v>
@@ -31857,25 +31857,25 @@
         <v>148.13</v>
       </c>
       <c r="E415" t="n">
-        <v>138.4</v>
+        <v>137.71</v>
       </c>
       <c r="F415" t="n">
-        <v>139.18</v>
+        <v>139.76</v>
       </c>
       <c r="G415" t="n">
-        <v>35484312</v>
+        <v>58589540</v>
       </c>
       <c r="H415" s="2" t="n">
-        <v>-2.34</v>
+        <v>-1.94</v>
       </c>
       <c r="I415" t="n">
         <v>14.2</v>
       </c>
       <c r="J415" t="n">
-        <v>140.35</v>
+        <v>140.38</v>
       </c>
       <c r="K415" t="n">
-        <v>131.06</v>
+        <v>131.07</v>
       </c>
       <c r="L415" t="n">
         <v>160.81</v>
@@ -31884,10 +31884,10 @@
         <v>120.29</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>48.28</v>
+        <v>48.64</v>
       </c>
       <c r="O415" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31905,13 +31905,13 @@
         </is>
       </c>
       <c r="S415" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T415" s="3" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="3" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="3" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31850,41 +31850,25 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>148.18</v>
-      </c>
-      <c r="D415" t="n">
-        <v>148.13</v>
-      </c>
-      <c r="E415" t="n">
-        <v>137.71</v>
-      </c>
-      <c r="F415" t="n">
-        <v>139.76</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>58589540</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>-1.94</v>
+        <v>58824798</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>14.2</v>
       </c>
-      <c r="J415" t="n">
-        <v>140.38</v>
-      </c>
-      <c r="K415" t="n">
-        <v>131.07</v>
-      </c>
-      <c r="L415" t="n">
-        <v>160.81</v>
-      </c>
-      <c r="M415" t="n">
-        <v>120.29</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" s="3" t="n">
-        <v>48.64</v>
+        <v>50.46</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>
@@ -31899,11 +31883,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>1st: MA20, 10% cash</t>
-        </is>
-      </c>
+      <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
         <v>5.24</v>
       </c>
@@ -31914,7 +31894,9 @@
         <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="3" t="inlineStr"/>
+      <c r="W415" s="3" t="n">
+        <v>154.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31850,25 +31850,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>148.18</v>
+      </c>
+      <c r="D415" t="n">
+        <v>148.18</v>
+      </c>
+      <c r="E415" t="n">
+        <v>137.71</v>
+      </c>
+      <c r="F415" t="n">
+        <v>139.76</v>
+      </c>
       <c r="G415" t="n">
-        <v>58824798</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>0</v>
+        <v>59031400</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>-1.94</v>
       </c>
       <c r="I415" t="n">
         <v>14.2</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>140.38</v>
+      </c>
+      <c r="K415" t="n">
+        <v>131.07</v>
+      </c>
+      <c r="L415" t="n">
+        <v>160.81</v>
+      </c>
+      <c r="M415" t="n">
+        <v>120.29</v>
+      </c>
       <c r="N415" s="3" t="n">
-        <v>50.46</v>
+        <v>48.64</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>
@@ -31883,7 +31899,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
       <c r="S415" t="n">
         <v>5.24</v>
       </c>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -18568,7 +18568,7 @@
         <v>47.19</v>
       </c>
       <c r="L239" t="n">
-        <v>40.71</v>
+        <v>40.7</v>
       </c>
       <c r="M239" t="n">
         <v>32.48</v>
@@ -31737,11 +31737,11 @@
         <v>48.64</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31766,6 +31766,85 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="3" t="n">
         <v>154.3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>134.43</v>
+      </c>
+      <c r="D414" t="n">
+        <v>134.54</v>
+      </c>
+      <c r="E414" t="n">
+        <v>127.27</v>
+      </c>
+      <c r="F414" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="G414" t="n">
+        <v>57087700</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>141.75</v>
+      </c>
+      <c r="K414" t="n">
+        <v>130.95</v>
+      </c>
+      <c r="L414" t="n">
+        <v>161.07</v>
+      </c>
+      <c r="M414" t="n">
+        <v>120.72</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>34.89</v>
+      </c>
+      <c r="O414" t="n">
+        <v>46</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>155.1</v>
       </c>
     </row>
   </sheetData>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -18493,7 +18493,7 @@
         <v>47.19</v>
       </c>
       <c r="L238" t="n">
-        <v>40.71</v>
+        <v>40.7</v>
       </c>
       <c r="M238" t="n">
         <v>32.48</v>
@@ -31771,6 +31771,79 @@
       <c r="W413" s="1" t="n">
         <v>155.1</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>118.42</v>
+      </c>
+      <c r="D414" t="n">
+        <v>126.45</v>
+      </c>
+      <c r="E414" t="n">
+        <v>115.84</v>
+      </c>
+      <c r="F414" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="G414" t="n">
+        <v>59592010</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>142.81</v>
+      </c>
+      <c r="K414" t="n">
+        <v>130.73</v>
+      </c>
+      <c r="L414" t="n">
+        <v>161.22</v>
+      </c>
+      <c r="M414" t="n">
+        <v>121.11</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="O414" t="n">
+        <v>44</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -3320,7 +3320,7 @@
         <v>14.2</v>
       </c>
       <c r="J37" t="n">
-        <v>15.55</v>
+        <v>15.56</v>
       </c>
       <c r="K37" t="n">
         <v>22.42</v>
@@ -18493,7 +18493,7 @@
         <v>47.19</v>
       </c>
       <c r="L238" t="n">
-        <v>40.7</v>
+        <v>40.71</v>
       </c>
       <c r="M238" t="n">
         <v>32.48</v>
@@ -31717,7 +31717,7 @@
         <v>128.4</v>
       </c>
       <c r="G413" t="n">
-        <v>57428800</v>
+        <v>58727700</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-8.130000000000001</v>
@@ -31787,40 +31787,40 @@
         <v>118.42</v>
       </c>
       <c r="D414" t="n">
-        <v>126.45</v>
+        <v>127.92</v>
       </c>
       <c r="E414" t="n">
         <v>115.84</v>
       </c>
       <c r="F414" t="n">
-        <v>123.5</v>
+        <v>127.57</v>
       </c>
       <c r="G414" t="n">
-        <v>59592010</v>
+        <v>78523250</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-3.82</v>
+        <v>-0.65</v>
       </c>
       <c r="I414" t="n">
         <v>14.2</v>
       </c>
       <c r="J414" t="n">
-        <v>142.81</v>
+        <v>143.01</v>
       </c>
       <c r="K414" t="n">
-        <v>130.73</v>
+        <v>130.8</v>
       </c>
       <c r="L414" t="n">
-        <v>161.22</v>
+        <v>161.25</v>
       </c>
       <c r="M414" t="n">
-        <v>121.11</v>
+        <v>121.13</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>35.25</v>
+        <v>37.21</v>
       </c>
       <c r="O414" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31836,12 +31836,8 @@
       <c r="S414" t="n">
         <v>5.22</v>
       </c>
-      <c r="T414" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U414" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="T414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31745,7 +31745,7 @@
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31741,11 +31741,11 @@
         <v>37.21</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31767,6 +31767,79 @@
       <c r="W413" s="2" t="n">
         <v>154.7</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>119.02</v>
+      </c>
+      <c r="D414" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="E414" t="n">
+        <v>117</v>
+      </c>
+      <c r="F414" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="G414" t="n">
+        <v>32079673</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-6.95</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>143.75</v>
+      </c>
+      <c r="K414" t="n">
+        <v>130.14</v>
+      </c>
+      <c r="L414" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="M414" t="n">
+        <v>121.51</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>33.12</v>
+      </c>
+      <c r="O414" t="n">
+        <v>37</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31786,37 +31786,37 @@
         <v>120.9</v>
       </c>
       <c r="E414" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F414" t="n">
-        <v>118.7</v>
+        <v>109.54</v>
       </c>
       <c r="G414" t="n">
-        <v>32079673</v>
+        <v>81598737</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-6.95</v>
+        <v>-14.13</v>
       </c>
       <c r="I414" t="n">
         <v>14.2</v>
       </c>
       <c r="J414" t="n">
-        <v>143.75</v>
+        <v>143.3</v>
       </c>
       <c r="K414" t="n">
-        <v>130.14</v>
+        <v>129.98</v>
       </c>
       <c r="L414" t="n">
-        <v>161.3</v>
+        <v>161.22</v>
       </c>
       <c r="M414" t="n">
-        <v>121.51</v>
-      </c>
-      <c r="N414" s="2" t="n">
-        <v>33.12</v>
+        <v>121.46</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>29.78</v>
       </c>
       <c r="O414" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31828,15 +31828,19 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr"/>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S414" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.7</v>
+        <v>17.2</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.1</v>
+        <v>14</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31717,7 +31717,7 @@
         <v>127.57</v>
       </c>
       <c r="G413" t="n">
-        <v>78255400</v>
+        <v>79220200</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.65</v>
@@ -31789,34 +31789,34 @@
         <v>109</v>
       </c>
       <c r="F414" t="n">
-        <v>109.54</v>
+        <v>110.54</v>
       </c>
       <c r="G414" t="n">
-        <v>81598737</v>
+        <v>102344094</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-14.13</v>
+        <v>-13.35</v>
       </c>
       <c r="I414" t="n">
         <v>14.2</v>
       </c>
       <c r="J414" t="n">
-        <v>143.3</v>
+        <v>143.35</v>
       </c>
       <c r="K414" t="n">
-        <v>129.98</v>
+        <v>130</v>
       </c>
       <c r="L414" t="n">
-        <v>161.22</v>
+        <v>161.23</v>
       </c>
       <c r="M414" t="n">
         <v>121.46</v>
       </c>
-      <c r="N414" s="3" t="n">
-        <v>29.78</v>
+      <c r="N414" s="2" t="n">
+        <v>30.11</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31828,22 +31828,20 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
+      <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
         <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>157.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31792,7 +31792,7 @@
         <v>110.54</v>
       </c>
       <c r="G414" t="n">
-        <v>102344094</v>
+        <v>102288200</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-13.35</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31816,7 +31816,7 @@
         <v>30.11</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>-7.1</v>
       </c>
       <c r="I2" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J2" t="n">
         <v>27.4</v>
@@ -687,7 +687,7 @@
         <v>-6.32</v>
       </c>
       <c r="I3" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J3" t="n">
         <v>27.4</v>
@@ -762,7 +762,7 @@
         <v>4.86</v>
       </c>
       <c r="I4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J4" t="n">
         <v>27.44</v>
@@ -837,7 +837,7 @@
         <v>-17.28</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>27.25</v>
@@ -912,7 +912,7 @@
         <v>4.54</v>
       </c>
       <c r="I6" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J6" t="n">
         <v>27.03</v>
@@ -987,7 +987,7 @@
         <v>-9.789999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J7" t="n">
         <v>26.7</v>
@@ -1062,7 +1062,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J8" t="n">
         <v>26.46</v>
@@ -1137,7 +1137,7 @@
         <v>6.29</v>
       </c>
       <c r="I9" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J9" t="n">
         <v>26.24</v>
@@ -1212,7 +1212,7 @@
         <v>-12.39</v>
       </c>
       <c r="I10" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J10" t="n">
         <v>25.82</v>
@@ -1291,7 +1291,7 @@
         <v>8.59</v>
       </c>
       <c r="I11" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J11" t="n">
         <v>25.49</v>
@@ -1366,7 +1366,7 @@
         <v>-13.84</v>
       </c>
       <c r="I12" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J12" t="n">
         <v>25.07</v>
@@ -1449,7 +1449,7 @@
         <v>-3.19</v>
       </c>
       <c r="I13" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J13" t="n">
         <v>24.58</v>
@@ -1532,7 +1532,7 @@
         <v>5.09</v>
       </c>
       <c r="I14" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J14" t="n">
         <v>24.13</v>
@@ -1611,7 +1611,7 @@
         <v>-1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J15" t="n">
         <v>23.66</v>
@@ -1690,7 +1690,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J16" t="n">
         <v>23.23</v>
@@ -1765,7 +1765,7 @@
         <v>4.98</v>
       </c>
       <c r="I17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J17" t="n">
         <v>22.84</v>
@@ -1840,7 +1840,7 @@
         <v>-4.12</v>
       </c>
       <c r="I18" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J18" t="n">
         <v>22.34</v>
@@ -1915,7 +1915,7 @@
         <v>2.22</v>
       </c>
       <c r="I19" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J19" t="n">
         <v>21.79</v>
@@ -1990,7 +1990,7 @@
         <v>-2.17</v>
       </c>
       <c r="I20" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J20" t="n">
         <v>21.21</v>
@@ -2065,7 +2065,7 @@
         <v>-3.28</v>
       </c>
       <c r="I21" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J21" t="n">
         <v>20.74</v>
@@ -2140,7 +2140,7 @@
         <v>8.93</v>
       </c>
       <c r="I22" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J22" t="n">
         <v>20.45</v>
@@ -2215,7 +2215,7 @@
         <v>-1.82</v>
       </c>
       <c r="I23" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J23" t="n">
         <v>20.23</v>
@@ -2290,7 +2290,7 @@
         <v>-8.6</v>
       </c>
       <c r="I24" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J24" t="n">
         <v>19.86</v>
@@ -2369,7 +2369,7 @@
         <v>-5.45</v>
       </c>
       <c r="I25" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J25" t="n">
         <v>19.66</v>
@@ -2444,7 +2444,7 @@
         <v>-9.779999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J26" t="n">
         <v>19.33</v>
@@ -2519,7 +2519,7 @@
         <v>-0.5</v>
       </c>
       <c r="I27" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J27" t="n">
         <v>19.11</v>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J28" t="n">
         <v>18.88</v>
@@ -2669,7 +2669,7 @@
         <v>1.95</v>
       </c>
       <c r="I29" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J29" t="n">
         <v>18.6</v>
@@ -2744,7 +2744,7 @@
         <v>-29.83</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>18.21</v>
@@ -2827,7 +2827,7 @@
         <v>-23.5</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>17.61</v>
@@ -2910,7 +2910,7 @@
         <v>4.83</v>
       </c>
       <c r="I32" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J32" t="n">
         <v>17.17</v>
@@ -2993,7 +2993,7 @@
         <v>-9.77</v>
       </c>
       <c r="I33" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J33" t="n">
         <v>16.72</v>
@@ -3076,7 +3076,7 @@
         <v>54.74</v>
       </c>
       <c r="I34" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J34" t="n">
         <v>16.45</v>
@@ -3155,7 +3155,7 @@
         <v>-24.61</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>16.03</v>
@@ -3238,7 +3238,7 @@
         <v>6.26</v>
       </c>
       <c r="I36" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J36" t="n">
         <v>15.56</v>
@@ -3321,7 +3321,7 @@
         <v>2.36</v>
       </c>
       <c r="I37" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J37" t="n">
         <v>15.04</v>
@@ -3400,7 +3400,7 @@
         <v>1.25</v>
       </c>
       <c r="I38" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J38" t="n">
         <v>14.58</v>
@@ -3475,7 +3475,7 @@
         <v>-11.93</v>
       </c>
       <c r="I39" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J39" t="n">
         <v>14.04</v>
@@ -3558,7 +3558,7 @@
         <v>-1.51</v>
       </c>
       <c r="I40" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J40" t="n">
         <v>13.5</v>
@@ -3637,7 +3637,7 @@
         <v>-5.35</v>
       </c>
       <c r="I41" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J41" t="n">
         <v>12.98</v>
@@ -3712,7 +3712,7 @@
         <v>5.42</v>
       </c>
       <c r="I42" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J42" t="n">
         <v>12.4</v>
@@ -3787,7 +3787,7 @@
         <v>12.14</v>
       </c>
       <c r="I43" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J43" t="n">
         <v>11.89</v>
@@ -3866,7 +3866,7 @@
         <v>16.59</v>
       </c>
       <c r="I44" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J44" t="n">
         <v>11.55</v>
@@ -3941,7 +3941,7 @@
         <v>2.85</v>
       </c>
       <c r="I45" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J45" t="n">
         <v>11.28</v>
@@ -4016,7 +4016,7 @@
         <v>-0.41</v>
       </c>
       <c r="I46" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J46" t="n">
         <v>11.09</v>
@@ -4091,7 +4091,7 @@
         <v>-3.51</v>
       </c>
       <c r="I47" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J47" t="n">
         <v>10.89</v>
@@ -4166,7 +4166,7 @@
         <v>2.54</v>
       </c>
       <c r="I48" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J48" t="n">
         <v>10.7</v>
@@ -4241,7 +4241,7 @@
         <v>-0.5</v>
       </c>
       <c r="I49" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J49" t="n">
         <v>10.49</v>
@@ -4316,7 +4316,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J50" t="n">
         <v>10.59</v>
@@ -4391,7 +4391,7 @@
         <v>-1.81</v>
       </c>
       <c r="I51" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J51" t="n">
         <v>10.8</v>
@@ -4466,7 +4466,7 @@
         <v>-3.15</v>
       </c>
       <c r="I52" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J52" t="n">
         <v>10.98</v>
@@ -4541,7 +4541,7 @@
         <v>5.08</v>
       </c>
       <c r="I53" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J53" t="n">
         <v>11.23</v>
@@ -4616,7 +4616,7 @@
         <v>2.8</v>
       </c>
       <c r="I54" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J54" t="n">
         <v>11.27</v>
@@ -4691,7 +4691,7 @@
         <v>3.31</v>
       </c>
       <c r="I55" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J55" t="n">
         <v>11.49</v>
@@ -4766,7 +4766,7 @@
         <v>21.42</v>
       </c>
       <c r="I56" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J56" t="n">
         <v>11.84</v>
@@ -4841,7 +4841,7 @@
         <v>8.56</v>
       </c>
       <c r="I57" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J57" t="n">
         <v>12.24</v>
@@ -4916,7 +4916,7 @@
         <v>1.3</v>
       </c>
       <c r="I58" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J58" t="n">
         <v>12.65</v>
@@ -4991,7 +4991,7 @@
         <v>-1.97</v>
       </c>
       <c r="I59" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J59" t="n">
         <v>13.11</v>
@@ -5066,7 +5066,7 @@
         <v>-0.44</v>
       </c>
       <c r="I60" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J60" t="n">
         <v>13.56</v>
@@ -5141,7 +5141,7 @@
         <v>-1.75</v>
       </c>
       <c r="I61" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J61" t="n">
         <v>14.03</v>
@@ -5216,7 +5216,7 @@
         <v>-0.5</v>
       </c>
       <c r="I62" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J62" t="n">
         <v>14.47</v>
@@ -5291,7 +5291,7 @@
         <v>-5.42</v>
       </c>
       <c r="I63" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J63" t="n">
         <v>14.8</v>
@@ -5366,7 +5366,7 @@
         <v>-2.89</v>
       </c>
       <c r="I64" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J64" t="n">
         <v>15.03</v>
@@ -5441,7 +5441,7 @@
         <v>-4.68</v>
       </c>
       <c r="I65" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J65" t="n">
         <v>15.19</v>
@@ -5516,7 +5516,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J66" t="n">
         <v>15.44</v>
@@ -5591,7 +5591,7 @@
         <v>-1.45</v>
       </c>
       <c r="I67" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J67" t="n">
         <v>15.7</v>
@@ -5666,7 +5666,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J68" t="n">
         <v>15.95</v>
@@ -5741,7 +5741,7 @@
         <v>-6.01</v>
       </c>
       <c r="I69" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J69" t="n">
         <v>16.16</v>
@@ -5820,7 +5820,7 @@
         <v>4.53</v>
       </c>
       <c r="I70" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J70" t="n">
         <v>16.33</v>
@@ -5895,7 +5895,7 @@
         <v>8.32</v>
       </c>
       <c r="I71" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J71" t="n">
         <v>16.6</v>
@@ -5970,7 +5970,7 @@
         <v>4.28</v>
       </c>
       <c r="I72" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J72" t="n">
         <v>16.92</v>
@@ -6045,7 +6045,7 @@
         <v>-1.47</v>
       </c>
       <c r="I73" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J73" t="n">
         <v>17.19</v>
@@ -6120,7 +6120,7 @@
         <v>1.98</v>
       </c>
       <c r="I74" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J74" t="n">
         <v>17.47</v>
@@ -6195,7 +6195,7 @@
         <v>7.33</v>
       </c>
       <c r="I75" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J75" t="n">
         <v>17.79</v>
@@ -6270,7 +6270,7 @@
         <v>6.34</v>
       </c>
       <c r="I76" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J76" t="n">
         <v>18.03</v>
@@ -6345,7 +6345,7 @@
         <v>-1.15</v>
       </c>
       <c r="I77" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J77" t="n">
         <v>18.18</v>
@@ -6420,7 +6420,7 @@
         <v>0.23</v>
       </c>
       <c r="I78" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J78" t="n">
         <v>18.32</v>
@@ -6495,7 +6495,7 @@
         <v>-7.59</v>
       </c>
       <c r="I79" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J79" t="n">
         <v>18.4</v>
@@ -6574,7 +6574,7 @@
         <v>9.27</v>
       </c>
       <c r="I80" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J80" t="n">
         <v>18.57</v>
@@ -6649,7 +6649,7 @@
         <v>-2.2</v>
       </c>
       <c r="I81" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J81" t="n">
         <v>18.74</v>
@@ -6724,7 +6724,7 @@
         <v>0.89</v>
       </c>
       <c r="I82" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J82" t="n">
         <v>18.92</v>
@@ -6799,7 +6799,7 @@
         <v>-1.86</v>
       </c>
       <c r="I83" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J83" t="n">
         <v>19.13</v>
@@ -6874,7 +6874,7 @@
         <v>1.75</v>
       </c>
       <c r="I84" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J84" t="n">
         <v>19.38</v>
@@ -6949,7 +6949,7 @@
         <v>11.35</v>
       </c>
       <c r="I85" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J85" t="n">
         <v>19.8</v>
@@ -7024,7 +7024,7 @@
         <v>2.63</v>
       </c>
       <c r="I86" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J86" t="n">
         <v>20.16</v>
@@ -7099,7 +7099,7 @@
         <v>2.52</v>
       </c>
       <c r="I87" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J87" t="n">
         <v>20.57</v>
@@ -7174,7 +7174,7 @@
         <v>-0.36</v>
       </c>
       <c r="I88" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J88" t="n">
         <v>20.97</v>
@@ -7249,7 +7249,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J89" t="n">
         <v>21.42</v>
@@ -7324,7 +7324,7 @@
         <v>-1.59</v>
       </c>
       <c r="I90" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J90" t="n">
         <v>21.81</v>
@@ -7399,7 +7399,7 @@
         <v>5.43</v>
       </c>
       <c r="I91" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J91" t="n">
         <v>22.2</v>
@@ -7474,7 +7474,7 @@
         <v>1.46</v>
       </c>
       <c r="I92" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J92" t="n">
         <v>22.57</v>
@@ -7549,7 +7549,7 @@
         <v>-5.53</v>
       </c>
       <c r="I93" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J93" t="n">
         <v>22.89</v>
@@ -7624,7 +7624,7 @@
         <v>5.61</v>
       </c>
       <c r="I94" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J94" t="n">
         <v>23.25</v>
@@ -7699,7 +7699,7 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J95" t="n">
         <v>23.55</v>
@@ -7774,7 +7774,7 @@
         <v>2.7</v>
       </c>
       <c r="I96" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J96" t="n">
         <v>23.83</v>
@@ -7849,7 +7849,7 @@
         <v>-0.29</v>
       </c>
       <c r="I97" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J97" t="n">
         <v>24.12</v>
@@ -7924,7 +7924,7 @@
         <v>-2.9</v>
       </c>
       <c r="I98" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J98" t="n">
         <v>24.36</v>
@@ -7999,7 +7999,7 @@
         <v>2.98</v>
       </c>
       <c r="I99" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J99" t="n">
         <v>24.72</v>
@@ -8074,7 +8074,7 @@
         <v>-0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J100" t="n">
         <v>24.98</v>
@@ -8149,7 +8149,7 @@
         <v>1.07</v>
       </c>
       <c r="I101" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J101" t="n">
         <v>25.28</v>
@@ -8224,7 +8224,7 @@
         <v>0.04</v>
       </c>
       <c r="I102" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J102" t="n">
         <v>25.57</v>
@@ -8299,7 +8299,7 @@
         <v>0.62</v>
       </c>
       <c r="I103" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J103" t="n">
         <v>25.89</v>
@@ -8374,7 +8374,7 @@
         <v>-4.26</v>
       </c>
       <c r="I104" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J104" t="n">
         <v>26.13</v>
@@ -8449,7 +8449,7 @@
         <v>-2.05</v>
       </c>
       <c r="I105" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J105" t="n">
         <v>26.22</v>
@@ -8528,7 +8528,7 @@
         <v>-0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J106" t="n">
         <v>26.27</v>
@@ -8603,7 +8603,7 @@
         <v>-0.08</v>
       </c>
       <c r="I107" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J107" t="n">
         <v>26.29</v>
@@ -8678,7 +8678,7 @@
         <v>4.96</v>
       </c>
       <c r="I108" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J108" t="n">
         <v>26.38</v>
@@ -8753,7 +8753,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J109" t="n">
         <v>26.48</v>
@@ -8828,7 +8828,7 @@
         <v>2.15</v>
       </c>
       <c r="I110" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J110" t="n">
         <v>26.62</v>
@@ -8903,7 +8903,7 @@
         <v>-9.5</v>
       </c>
       <c r="I111" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J111" t="n">
         <v>26.57</v>
@@ -8982,7 +8982,7 @@
         <v>-3.61</v>
       </c>
       <c r="I112" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J112" t="n">
         <v>26.45</v>
@@ -9057,7 +9057,7 @@
         <v>3.82</v>
       </c>
       <c r="I113" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J113" t="n">
         <v>26.45</v>
@@ -9132,7 +9132,7 @@
         <v>-1.92</v>
       </c>
       <c r="I114" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J114" t="n">
         <v>26.36</v>
@@ -9207,7 +9207,7 @@
         <v>-2.16</v>
       </c>
       <c r="I115" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J115" t="n">
         <v>26.23</v>
@@ -9282,7 +9282,7 @@
         <v>4.21</v>
       </c>
       <c r="I116" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J116" t="n">
         <v>26.11</v>
@@ -9357,7 +9357,7 @@
         <v>2.84</v>
       </c>
       <c r="I117" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J117" t="n">
         <v>26.03</v>
@@ -9432,7 +9432,7 @@
         <v>-0.39</v>
       </c>
       <c r="I118" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J118" t="n">
         <v>25.99</v>
@@ -9507,7 +9507,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J119" t="n">
         <v>26.02</v>
@@ -9582,7 +9582,7 @@
         <v>4.54</v>
       </c>
       <c r="I120" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J120" t="n">
         <v>26.13</v>
@@ -9657,7 +9657,7 @@
         <v>0.51</v>
       </c>
       <c r="I121" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J121" t="n">
         <v>26.24</v>
@@ -9732,7 +9732,7 @@
         <v>-6.98</v>
       </c>
       <c r="I122" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J122" t="n">
         <v>26.24</v>
@@ -9807,7 +9807,7 @@
         <v>0.59</v>
       </c>
       <c r="I123" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J123" t="n">
         <v>26.24</v>
@@ -9882,7 +9882,7 @@
         <v>-4.65</v>
       </c>
       <c r="I124" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J124" t="n">
         <v>26.24</v>
@@ -9961,7 +9961,7 @@
         <v>-1.68</v>
       </c>
       <c r="I125" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J125" t="n">
         <v>26.24</v>
@@ -10036,7 +10036,7 @@
         <v>-1.75</v>
       </c>
       <c r="I126" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J126" t="n">
         <v>26.23</v>
@@ -10111,7 +10111,7 @@
         <v>8.25</v>
       </c>
       <c r="I127" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J127" t="n">
         <v>26.32</v>
@@ -10186,7 +10186,7 @@
         <v>-0.55</v>
       </c>
       <c r="I128" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J128" t="n">
         <v>26.34</v>
@@ -10261,7 +10261,7 @@
         <v>2.35</v>
       </c>
       <c r="I129" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J129" t="n">
         <v>26.38</v>
@@ -10336,7 +10336,7 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J130" t="n">
         <v>26.41</v>
@@ -10411,7 +10411,7 @@
         <v>1.24</v>
       </c>
       <c r="I131" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J131" t="n">
         <v>26.59</v>
@@ -10486,7 +10486,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="I132" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J132" t="n">
         <v>26.69</v>
@@ -10565,7 +10565,7 @@
         <v>-3.04</v>
       </c>
       <c r="I133" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J133" t="n">
         <v>26.7</v>
@@ -10644,7 +10644,7 @@
         <v>-1.35</v>
       </c>
       <c r="I134" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J134" t="n">
         <v>26.72</v>
@@ -10719,7 +10719,7 @@
         <v>2.97</v>
       </c>
       <c r="I135" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J135" t="n">
         <v>26.8</v>
@@ -10794,7 +10794,7 @@
         <v>3.08</v>
       </c>
       <c r="I136" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J136" t="n">
         <v>26.87</v>
@@ -10869,7 +10869,7 @@
         <v>2.38</v>
       </c>
       <c r="I137" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J137" t="n">
         <v>26.94</v>
@@ -10944,7 +10944,7 @@
         <v>0.37</v>
       </c>
       <c r="I138" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J138" t="n">
         <v>27.02</v>
@@ -11019,7 +11019,7 @@
         <v>5.23</v>
       </c>
       <c r="I139" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J139" t="n">
         <v>27.05</v>
@@ -11094,7 +11094,7 @@
         <v>2</v>
       </c>
       <c r="I140" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J140" t="n">
         <v>27.05</v>
@@ -11169,7 +11169,7 @@
         <v>0.45</v>
       </c>
       <c r="I141" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J141" t="n">
         <v>27.04</v>
@@ -11244,7 +11244,7 @@
         <v>2.39</v>
       </c>
       <c r="I142" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J142" t="n">
         <v>27.17</v>
@@ -11319,7 +11319,7 @@
         <v>1.6</v>
       </c>
       <c r="I143" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J143" t="n">
         <v>27.32</v>
@@ -11394,7 +11394,7 @@
         <v>-0.03</v>
       </c>
       <c r="I144" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J144" t="n">
         <v>27.53</v>
@@ -11469,7 +11469,7 @@
         <v>10.41</v>
       </c>
       <c r="I145" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J145" t="n">
         <v>27.92</v>
@@ -11544,7 +11544,7 @@
         <v>-1.84</v>
       </c>
       <c r="I146" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J146" t="n">
         <v>28.3</v>
@@ -11619,7 +11619,7 @@
         <v>4.27</v>
       </c>
       <c r="I147" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J147" t="n">
         <v>28.65</v>
@@ -11694,7 +11694,7 @@
         <v>-0.35</v>
       </c>
       <c r="I148" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J148" t="n">
         <v>29</v>
@@ -11769,7 +11769,7 @@
         <v>-0.29</v>
       </c>
       <c r="I149" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J149" t="n">
         <v>29.32</v>
@@ -11844,7 +11844,7 @@
         <v>-1.02</v>
       </c>
       <c r="I150" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J150" t="n">
         <v>29.6</v>
@@ -11919,7 +11919,7 @@
         <v>0.5</v>
       </c>
       <c r="I151" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J151" t="n">
         <v>29.88</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J152" t="n">
         <v>30.28</v>
@@ -12069,7 +12069,7 @@
         <v>2.41</v>
       </c>
       <c r="I153" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J153" t="n">
         <v>30.75</v>
@@ -12144,7 +12144,7 @@
         <v>5.8</v>
       </c>
       <c r="I154" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J154" t="n">
         <v>31.35</v>
@@ -12219,7 +12219,7 @@
         <v>6</v>
       </c>
       <c r="I155" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J155" t="n">
         <v>32.02</v>
@@ -12294,7 +12294,7 @@
         <v>-2.18</v>
       </c>
       <c r="I156" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J156" t="n">
         <v>32.61</v>
@@ -12369,7 +12369,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="I157" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J157" t="n">
         <v>33.34</v>
@@ -12444,7 +12444,7 @@
         <v>-6.91</v>
       </c>
       <c r="I158" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J158" t="n">
         <v>33.93</v>
@@ -12519,7 +12519,7 @@
         <v>10.18</v>
       </c>
       <c r="I159" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J159" t="n">
         <v>34.64</v>
@@ -12594,7 +12594,7 @@
         <v>-1.26</v>
       </c>
       <c r="I160" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J160" t="n">
         <v>35.29</v>
@@ -12669,7 +12669,7 @@
         <v>-19</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>35.53</v>
@@ -12748,7 +12748,7 @@
         <v>14.39</v>
       </c>
       <c r="I162" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J162" t="n">
         <v>35.99</v>
@@ -12823,7 +12823,7 @@
         <v>-6.39</v>
       </c>
       <c r="I163" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J163" t="n">
         <v>36.3</v>
@@ -12898,7 +12898,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="I164" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J164" t="n">
         <v>36.78</v>
@@ -12973,7 +12973,7 @@
         <v>1.48</v>
       </c>
       <c r="I165" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J165" t="n">
         <v>37.12</v>
@@ -13048,7 +13048,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J166" t="n">
         <v>37.48</v>
@@ -13123,7 +13123,7 @@
         <v>4.84</v>
       </c>
       <c r="I167" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J167" t="n">
         <v>37.88</v>
@@ -13198,7 +13198,7 @@
         <v>-1.73</v>
       </c>
       <c r="I168" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J168" t="n">
         <v>38.24</v>
@@ -13273,7 +13273,7 @@
         <v>-7.52</v>
       </c>
       <c r="I169" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J169" t="n">
         <v>38.44</v>
@@ -13352,7 +13352,7 @@
         <v>7.25</v>
       </c>
       <c r="I170" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J170" t="n">
         <v>38.81</v>
@@ -13427,7 +13427,7 @@
         <v>4.79</v>
       </c>
       <c r="I171" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J171" t="n">
         <v>39.27</v>
@@ -13502,7 +13502,7 @@
         <v>8.58</v>
       </c>
       <c r="I172" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J172" t="n">
         <v>39.91</v>
@@ -13577,7 +13577,7 @@
         <v>0.26</v>
       </c>
       <c r="I173" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J173" t="n">
         <v>40.51</v>
@@ -13652,7 +13652,7 @@
         <v>5.16</v>
       </c>
       <c r="I174" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J174" t="n">
         <v>41.14</v>
@@ -13727,7 +13727,7 @@
         <v>-4.03</v>
       </c>
       <c r="I175" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J175" t="n">
         <v>41.55</v>
@@ -13802,7 +13802,7 @@
         <v>0.82</v>
       </c>
       <c r="I176" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J176" t="n">
         <v>42.03</v>
@@ -13877,7 +13877,7 @@
         <v>1.68</v>
       </c>
       <c r="I177" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J177" t="n">
         <v>42.37</v>
@@ -13952,7 +13952,7 @@
         <v>-11.91</v>
       </c>
       <c r="I178" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J178" t="n">
         <v>42.57</v>
@@ -14027,7 +14027,7 @@
         <v>9.42</v>
       </c>
       <c r="I179" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J179" t="n">
         <v>42.77</v>
@@ -14102,7 +14102,7 @@
         <v>-8.16</v>
       </c>
       <c r="I180" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J180" t="n">
         <v>42.81</v>
@@ -14177,7 +14177,7 @@
         <v>-2.95</v>
       </c>
       <c r="I181" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J181" t="n">
         <v>43.19</v>
@@ -14256,7 +14256,7 @@
         <v>7.72</v>
       </c>
       <c r="I182" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J182" t="n">
         <v>43.48</v>
@@ -14331,7 +14331,7 @@
         <v>-7.01</v>
       </c>
       <c r="I183" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J183" t="n">
         <v>43.74</v>
@@ -14410,7 +14410,7 @@
         <v>4.55</v>
       </c>
       <c r="I184" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J184" t="n">
         <v>43.92</v>
@@ -14485,7 +14485,7 @@
         <v>-10.28</v>
       </c>
       <c r="I185" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J185" t="n">
         <v>43.86</v>
@@ -14560,7 +14560,7 @@
         <v>-0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J186" t="n">
         <v>43.79</v>
@@ -14635,7 +14635,7 @@
         <v>-5.18</v>
       </c>
       <c r="I187" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J187" t="n">
         <v>43.52</v>
@@ -14710,7 +14710,7 @@
         <v>-6.76</v>
       </c>
       <c r="I188" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J188" t="n">
         <v>43.16</v>
@@ -14789,7 +14789,7 @@
         <v>4.69</v>
       </c>
       <c r="I189" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J189" t="n">
         <v>43.04</v>
@@ -14864,7 +14864,7 @@
         <v>-14.33</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>42.52</v>
@@ -14947,7 +14947,7 @@
         <v>2.99</v>
       </c>
       <c r="I191" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J191" t="n">
         <v>41.95</v>
@@ -15022,7 +15022,7 @@
         <v>13.02</v>
       </c>
       <c r="I192" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J192" t="n">
         <v>41.4</v>
@@ -15097,7 +15097,7 @@
         <v>0.86</v>
       </c>
       <c r="I193" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J193" t="n">
         <v>40.86</v>
@@ -15172,7 +15172,7 @@
         <v>8.33</v>
       </c>
       <c r="I194" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J194" t="n">
         <v>40.35</v>
@@ -15247,7 +15247,7 @@
         <v>5.29</v>
       </c>
       <c r="I195" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J195" t="n">
         <v>40.05</v>
@@ -15322,7 +15322,7 @@
         <v>0.12</v>
       </c>
       <c r="I196" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J196" t="n">
         <v>39.72</v>
@@ -15397,7 +15397,7 @@
         <v>6.03</v>
       </c>
       <c r="I197" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J197" t="n">
         <v>39.48</v>
@@ -15472,7 +15472,7 @@
         <v>6.35</v>
       </c>
       <c r="I198" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J198" t="n">
         <v>39.67</v>
@@ -15547,7 +15547,7 @@
         <v>-3.05</v>
       </c>
       <c r="I199" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J199" t="n">
         <v>39.59</v>
@@ -15622,7 +15622,7 @@
         <v>2.97</v>
       </c>
       <c r="I200" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J200" t="n">
         <v>39.76</v>
@@ -15697,7 +15697,7 @@
         <v>3.21</v>
       </c>
       <c r="I201" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J201" t="n">
         <v>40.08</v>
@@ -15772,7 +15772,7 @@
         <v>-0.42</v>
       </c>
       <c r="I202" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J202" t="n">
         <v>40.22</v>
@@ -15847,7 +15847,7 @@
         <v>3.89</v>
       </c>
       <c r="I203" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J203" t="n">
         <v>40.61</v>
@@ -15922,7 +15922,7 @@
         <v>-1.73</v>
       </c>
       <c r="I204" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J204" t="n">
         <v>40.86</v>
@@ -15997,7 +15997,7 @@
         <v>-14.52</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>40.99</v>
@@ -16072,7 +16072,7 @@
         <v>-1.27</v>
       </c>
       <c r="I206" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J206" t="n">
         <v>41.1</v>
@@ -16147,7 +16147,7 @@
         <v>-1.68</v>
       </c>
       <c r="I207" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J207" t="n">
         <v>41.29</v>
@@ -16226,7 +16226,7 @@
         <v>-11.05</v>
       </c>
       <c r="I208" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J208" t="n">
         <v>41.37</v>
@@ -16301,7 +16301,7 @@
         <v>7.11</v>
       </c>
       <c r="I209" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J209" t="n">
         <v>41.5</v>
@@ -16376,7 +16376,7 @@
         <v>8.15</v>
       </c>
       <c r="I210" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J210" t="n">
         <v>42.05</v>
@@ -16451,7 +16451,7 @@
         <v>3.69</v>
       </c>
       <c r="I211" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J211" t="n">
         <v>42.62</v>
@@ -16526,7 +16526,7 @@
         <v>1.02</v>
       </c>
       <c r="I212" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J212" t="n">
         <v>43.01</v>
@@ -16601,7 +16601,7 @@
         <v>1.17</v>
       </c>
       <c r="I213" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J213" t="n">
         <v>43.41</v>
@@ -16676,7 +16676,7 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J214" t="n">
         <v>43.67</v>
@@ -16751,7 +16751,7 @@
         <v>-0.88</v>
       </c>
       <c r="I215" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J215" t="n">
         <v>43.79</v>
@@ -16826,7 +16826,7 @@
         <v>-0.34</v>
       </c>
       <c r="I216" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J216" t="n">
         <v>43.91</v>
@@ -16905,7 +16905,7 @@
         <v>-3.76</v>
       </c>
       <c r="I217" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J217" t="n">
         <v>43.82</v>
@@ -16980,7 +16980,7 @@
         <v>12.4</v>
       </c>
       <c r="I218" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J218" t="n">
         <v>43.86</v>
@@ -17055,7 +17055,7 @@
         <v>4.19</v>
       </c>
       <c r="I219" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J219" t="n">
         <v>44.06</v>
@@ -17130,7 +17130,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J220" t="n">
         <v>44.43</v>
@@ -17205,7 +17205,7 @@
         <v>-3.17</v>
       </c>
       <c r="I221" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J221" t="n">
         <v>44.65</v>
@@ -17280,7 +17280,7 @@
         <v>-5.05</v>
       </c>
       <c r="I222" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J222" t="n">
         <v>44.74</v>
@@ -17355,7 +17355,7 @@
         <v>8.65</v>
       </c>
       <c r="I223" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J223" t="n">
         <v>44.96</v>
@@ -17430,7 +17430,7 @@
         <v>1.3</v>
       </c>
       <c r="I224" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J224" t="n">
         <v>45.25</v>
@@ -17505,7 +17505,7 @@
         <v>2.6</v>
       </c>
       <c r="I225" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J225" t="n">
         <v>45.97</v>
@@ -17580,7 +17580,7 @@
         <v>-1.23</v>
       </c>
       <c r="I226" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J226" t="n">
         <v>46.68</v>
@@ -17655,7 +17655,7 @@
         <v>4.88</v>
       </c>
       <c r="I227" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J227" t="n">
         <v>47.56</v>
@@ -17730,7 +17730,7 @@
         <v>4.6</v>
       </c>
       <c r="I228" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J228" t="n">
         <v>48.79</v>
@@ -17805,7 +17805,7 @@
         <v>-4.63</v>
       </c>
       <c r="I229" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J229" t="n">
         <v>49.76</v>
@@ -17880,7 +17880,7 @@
         <v>9.57</v>
       </c>
       <c r="I230" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J230" t="n">
         <v>50.85</v>
@@ -17955,7 +17955,7 @@
         <v>0.38</v>
       </c>
       <c r="I231" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J231" t="n">
         <v>51.87</v>
@@ -18030,7 +18030,7 @@
         <v>-3.33</v>
       </c>
       <c r="I232" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J232" t="n">
         <v>52.76</v>
@@ -18105,7 +18105,7 @@
         <v>-1.46</v>
       </c>
       <c r="I233" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J233" t="n">
         <v>53.59</v>
@@ -18180,7 +18180,7 @@
         <v>7.02</v>
       </c>
       <c r="I234" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J234" t="n">
         <v>54.62</v>
@@ -18255,7 +18255,7 @@
         <v>7.89</v>
       </c>
       <c r="I235" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J235" t="n">
         <v>55.94</v>
@@ -18330,7 +18330,7 @@
         <v>0.54</v>
       </c>
       <c r="I236" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J236" t="n">
         <v>57.28</v>
@@ -18405,7 +18405,7 @@
         <v>-12.31</v>
       </c>
       <c r="I237" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J237" t="n">
         <v>58.26</v>
@@ -18480,7 +18480,7 @@
         <v>5.52</v>
       </c>
       <c r="I238" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J238" t="n">
         <v>59.16</v>
@@ -18555,7 +18555,7 @@
         <v>-6.14</v>
       </c>
       <c r="I239" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J239" t="n">
         <v>59.76</v>
@@ -18630,7 +18630,7 @@
         <v>-13.08</v>
       </c>
       <c r="I240" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J240" t="n">
         <v>59.72</v>
@@ -18709,7 +18709,7 @@
         <v>0.11</v>
       </c>
       <c r="I241" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J241" t="n">
         <v>59.77</v>
@@ -18784,7 +18784,7 @@
         <v>15.95</v>
       </c>
       <c r="I242" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J242" t="n">
         <v>60.37</v>
@@ -18859,7 +18859,7 @@
         <v>3.69</v>
       </c>
       <c r="I243" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J243" t="n">
         <v>60.88</v>
@@ -18934,7 +18934,7 @@
         <v>-1.08</v>
       </c>
       <c r="I244" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J244" t="n">
         <v>61.31</v>
@@ -19009,7 +19009,7 @@
         <v>7.44</v>
       </c>
       <c r="I245" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J245" t="n">
         <v>61.91</v>
@@ -19084,7 +19084,7 @@
         <v>-7.28</v>
       </c>
       <c r="I246" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J246" t="n">
         <v>62.29</v>
@@ -19159,7 +19159,7 @@
         <v>2.36</v>
       </c>
       <c r="I247" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J247" t="n">
         <v>62.62</v>
@@ -19234,7 +19234,7 @@
         <v>-0.37</v>
       </c>
       <c r="I248" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J248" t="n">
         <v>62.8</v>
@@ -19309,7 +19309,7 @@
         <v>3.02</v>
       </c>
       <c r="I249" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J249" t="n">
         <v>63.22</v>
@@ -19384,7 +19384,7 @@
         <v>-1.6</v>
       </c>
       <c r="I250" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J250" t="n">
         <v>63.31</v>
@@ -19459,7 +19459,7 @@
         <v>2.88</v>
       </c>
       <c r="I251" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J251" t="n">
         <v>63.47</v>
@@ -19534,7 +19534,7 @@
         <v>-1.86</v>
       </c>
       <c r="I252" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J252" t="n">
         <v>63.69</v>
@@ -19609,7 +19609,7 @@
         <v>4.06</v>
       </c>
       <c r="I253" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J253" t="n">
         <v>64.08</v>
@@ -19684,7 +19684,7 @@
         <v>4.85</v>
       </c>
       <c r="I254" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J254" t="n">
         <v>64.42</v>
@@ -19759,7 +19759,7 @@
         <v>-9.07</v>
       </c>
       <c r="I255" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J255" t="n">
         <v>64.19</v>
@@ -19834,7 +19834,7 @@
         <v>-3.94</v>
       </c>
       <c r="I256" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J256" t="n">
         <v>63.8</v>
@@ -19913,7 +19913,7 @@
         <v>-0.02</v>
       </c>
       <c r="I257" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J257" t="n">
         <v>63.85</v>
@@ -19988,7 +19988,7 @@
         <v>-14.89</v>
       </c>
       <c r="I258" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J258" s="4" t="n">
         <v>63.26</v>
@@ -20067,7 +20067,7 @@
         <v>5.99</v>
       </c>
       <c r="I259" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J259" t="n">
         <v>63.03</v>
@@ -20142,7 +20142,7 @@
         <v>-3.22</v>
       </c>
       <c r="I260" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J260" t="n">
         <v>63.11</v>
@@ -20221,7 +20221,7 @@
         <v>-12.6</v>
       </c>
       <c r="I261" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J261" t="n">
         <v>62.84</v>
@@ -20300,7 +20300,7 @@
         <v>11.35</v>
       </c>
       <c r="I262" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J262" t="n">
         <v>62.42</v>
@@ -20375,7 +20375,7 @@
         <v>2.36</v>
       </c>
       <c r="I263" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J263" t="n">
         <v>61.95</v>
@@ -20450,7 +20450,7 @@
         <v>2.75</v>
       </c>
       <c r="I264" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J264" t="n">
         <v>61.59</v>
@@ -20525,7 +20525,7 @@
         <v>-10.35</v>
       </c>
       <c r="I265" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J265" t="n">
         <v>60.7</v>
@@ -20598,7 +20598,7 @@
         <v>0.88</v>
       </c>
       <c r="I266" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J266" t="n">
         <v>60.08</v>
@@ -20677,7 +20677,7 @@
         <v>5.84</v>
       </c>
       <c r="I267" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J267" t="n">
         <v>59.54</v>
@@ -20752,7 +20752,7 @@
         <v>2.35</v>
       </c>
       <c r="I268" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J268" t="n">
         <v>59.07</v>
@@ -20827,7 +20827,7 @@
         <v>-1.69</v>
       </c>
       <c r="I269" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J269" t="n">
         <v>58.45</v>
@@ -20902,7 +20902,7 @@
         <v>1.54</v>
       </c>
       <c r="I270" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J270" t="n">
         <v>57.93</v>
@@ -20977,7 +20977,7 @@
         <v>-6.75</v>
       </c>
       <c r="I271" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J271" t="n">
         <v>57.14</v>
@@ -21056,7 +21056,7 @@
         <v>3.7</v>
       </c>
       <c r="I272" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J272" t="n">
         <v>56.5</v>
@@ -21131,7 +21131,7 @@
         <v>3.62</v>
       </c>
       <c r="I273" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J273" t="n">
         <v>55.82</v>
@@ -21206,7 +21206,7 @@
         <v>3.79</v>
       </c>
       <c r="I274" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J274" t="n">
         <v>55.08</v>
@@ -21281,7 +21281,7 @@
         <v>-14.14</v>
       </c>
       <c r="I275" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J275" t="n">
         <v>54.26</v>
@@ -21360,7 +21360,7 @@
         <v>-4.82</v>
       </c>
       <c r="I276" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J276" t="n">
         <v>53.45</v>
@@ -21439,7 +21439,7 @@
         <v>-12.86</v>
       </c>
       <c r="I277" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J277" t="n">
         <v>52.34</v>
@@ -21514,7 +21514,7 @@
         <v>17.96</v>
       </c>
       <c r="I278" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J278" t="n">
         <v>52.07</v>
@@ -21589,7 +21589,7 @@
         <v>9.09</v>
       </c>
       <c r="I279" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J279" t="n">
         <v>51.85</v>
@@ -21664,7 +21664,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I280" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J280" t="n">
         <v>51.75</v>
@@ -21739,7 +21739,7 @@
         <v>3.89</v>
       </c>
       <c r="I281" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J281" t="n">
         <v>52.1</v>
@@ -21814,7 +21814,7 @@
         <v>3.18</v>
       </c>
       <c r="I282" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J282" t="n">
         <v>52.26</v>
@@ -21893,7 +21893,7 @@
         <v>19.38</v>
       </c>
       <c r="I283" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J283" t="n">
         <v>52.9</v>
@@ -21968,7 +21968,7 @@
         <v>6.63</v>
       </c>
       <c r="I284" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J284" t="n">
         <v>53.7</v>
@@ -22043,7 +22043,7 @@
         <v>6.13</v>
       </c>
       <c r="I285" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J285" t="n">
         <v>55</v>
@@ -22118,7 +22118,7 @@
         <v>5.46</v>
       </c>
       <c r="I286" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J286" t="n">
         <v>56.49</v>
@@ -22193,7 +22193,7 @@
         <v>5.89</v>
       </c>
       <c r="I287" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J287" t="n">
         <v>58.07</v>
@@ -22268,7 +22268,7 @@
         <v>0.76</v>
       </c>
       <c r="I288" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J288" t="n">
         <v>59.62</v>
@@ -22343,7 +22343,7 @@
         <v>2.81</v>
       </c>
       <c r="I289" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J289" t="n">
         <v>61.34</v>
@@ -22418,7 +22418,7 @@
         <v>7.15</v>
       </c>
       <c r="I290" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J290" t="n">
         <v>63.33</v>
@@ -22493,7 +22493,7 @@
         <v>1.33</v>
       </c>
       <c r="I291" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J291" t="n">
         <v>65.56999999999999</v>
@@ -22568,7 +22568,7 @@
         <v>2.24</v>
       </c>
       <c r="I292" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J292" t="n">
         <v>67.81999999999999</v>
@@ -22643,7 +22643,7 @@
         <v>7.69</v>
       </c>
       <c r="I293" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J293" t="n">
         <v>70.34999999999999</v>
@@ -22718,7 +22718,7 @@
         <v>6.75</v>
       </c>
       <c r="I294" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J294" t="n">
         <v>73.14</v>
@@ -22793,7 +22793,7 @@
         <v>13.79</v>
       </c>
       <c r="I295" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J295" t="n">
         <v>77.09999999999999</v>
@@ -22868,7 +22868,7 @@
         <v>-3.84</v>
       </c>
       <c r="I296" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J296" t="n">
         <v>80.94</v>
@@ -22943,7 +22943,7 @@
         <v>-11.21</v>
       </c>
       <c r="I297" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J297" t="n">
         <v>84.38</v>
@@ -23018,7 +23018,7 @@
         <v>7.67</v>
       </c>
       <c r="I298" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J298" t="n">
         <v>87.88</v>
@@ -23093,7 +23093,7 @@
         <v>7.64</v>
       </c>
       <c r="I299" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J299" t="n">
         <v>91.62</v>
@@ -23168,7 +23168,7 @@
         <v>2.69</v>
       </c>
       <c r="I300" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J300" t="n">
         <v>95.5</v>
@@ -23243,7 +23243,7 @@
         <v>-2.18</v>
       </c>
       <c r="I301" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J301" t="n">
         <v>99.13</v>
@@ -23318,7 +23318,7 @@
         <v>13.02</v>
       </c>
       <c r="I302" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J302" t="n">
         <v>103.51</v>
@@ -23393,7 +23393,7 @@
         <v>15.04</v>
       </c>
       <c r="I303" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J303" t="n">
         <v>108.42</v>
@@ -23468,7 +23468,7 @@
         <v>-8.289999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J304" t="n">
         <v>112.43</v>
@@ -23543,7 +23543,7 @@
         <v>16.33</v>
       </c>
       <c r="I305" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J305" t="n">
         <v>117.45</v>
@@ -23618,7 +23618,7 @@
         <v>7.62</v>
       </c>
       <c r="I306" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J306" t="n">
         <v>122.94</v>
@@ -23693,7 +23693,7 @@
         <v>-9.4</v>
       </c>
       <c r="I307" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J307" t="n">
         <v>127.3</v>
@@ -23768,7 +23768,7 @@
         <v>6.79</v>
       </c>
       <c r="I308" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J308" t="n">
         <v>132.21</v>
@@ -23843,7 +23843,7 @@
         <v>1.06</v>
       </c>
       <c r="I309" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J309" t="n">
         <v>137.1</v>
@@ -23918,7 +23918,7 @@
         <v>-11.82</v>
       </c>
       <c r="I310" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J310" t="n">
         <v>140.57</v>
@@ -23993,7 +23993,7 @@
         <v>-7.57</v>
       </c>
       <c r="I311" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J311" t="n">
         <v>143.36</v>
@@ -24068,7 +24068,7 @@
         <v>0.09</v>
       </c>
       <c r="I312" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J312" t="n">
         <v>146.05</v>
@@ -24143,7 +24143,7 @@
         <v>14.03</v>
       </c>
       <c r="I313" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J313" t="n">
         <v>149.42</v>
@@ -24218,7 +24218,7 @@
         <v>2.99</v>
       </c>
       <c r="I314" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J314" t="n">
         <v>152.7</v>
@@ -24293,7 +24293,7 @@
         <v>6.83</v>
       </c>
       <c r="I315" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J315" t="n">
         <v>155.81</v>
@@ -24368,7 +24368,7 @@
         <v>18.48</v>
       </c>
       <c r="I316" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J316" t="n">
         <v>160.93</v>
@@ -24443,7 +24443,7 @@
         <v>-3.46</v>
       </c>
       <c r="I317" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J317" t="n">
         <v>166.34</v>
@@ -24518,7 +24518,7 @@
         <v>3.05</v>
       </c>
       <c r="I318" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J318" t="n">
         <v>171.67</v>
@@ -24593,7 +24593,7 @@
         <v>-0.13</v>
       </c>
       <c r="I319" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J319" t="n">
         <v>176.54</v>
@@ -24668,7 +24668,7 @@
         <v>1.2</v>
       </c>
       <c r="I320" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J320" t="n">
         <v>181.37</v>
@@ -24743,7 +24743,7 @@
         <v>17.31</v>
       </c>
       <c r="I321" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J321" t="n">
         <v>188.3</v>
@@ -24818,7 +24818,7 @@
         <v>5.34</v>
       </c>
       <c r="I322" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J322" t="n">
         <v>195.12</v>
@@ -24893,7 +24893,7 @@
         <v>-6.36</v>
       </c>
       <c r="I323" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J323" t="n">
         <v>199.96</v>
@@ -24968,7 +24968,7 @@
         <v>-30.51</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>201.48</v>
@@ -25047,7 +25047,7 @@
         <v>15.83</v>
       </c>
       <c r="I325" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J325" t="n">
         <v>203.2</v>
@@ -25122,7 +25122,7 @@
         <v>-4.61</v>
       </c>
       <c r="I326" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J326" t="n">
         <v>203.76</v>
@@ -25201,7 +25201,7 @@
         <v>-10.43</v>
       </c>
       <c r="I327" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J327" t="n">
         <v>204.17</v>
@@ -25276,7 +25276,7 @@
         <v>23.99</v>
       </c>
       <c r="I328" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J328" t="n">
         <v>206.15</v>
@@ -25351,7 +25351,7 @@
         <v>4.78</v>
       </c>
       <c r="I329" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J329" t="n">
         <v>208.58</v>
@@ -25426,7 +25426,7 @@
         <v>16.11</v>
       </c>
       <c r="I330" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J330" t="n">
         <v>213.99</v>
@@ -25501,7 +25501,7 @@
         <v>-16.99</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>217.71</v>
@@ -25576,7 +25576,7 @@
         <v>3.39</v>
       </c>
       <c r="I332" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J332" t="n">
         <v>221.81</v>
@@ -25651,7 +25651,7 @@
         <v>19.43</v>
       </c>
       <c r="I333" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J333" t="n">
         <v>227.11</v>
@@ -25726,7 +25726,7 @@
         <v>7.69</v>
       </c>
       <c r="I334" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J334" t="n">
         <v>233.22</v>
@@ -25801,7 +25801,7 @@
         <v>-23.06</v>
       </c>
       <c r="I335" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J335" s="4" t="n">
         <v>235.26</v>
@@ -25880,7 +25880,7 @@
         <v>-0.8</v>
       </c>
       <c r="I336" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J336" t="n">
         <v>235.45</v>
@@ -25955,7 +25955,7 @@
         <v>10.03</v>
       </c>
       <c r="I337" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J337" t="n">
         <v>237.18</v>
@@ -26030,7 +26030,7 @@
         <v>-14.65</v>
       </c>
       <c r="I338" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>236.73</v>
@@ -26109,7 +26109,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I339" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J339" t="n">
         <v>237.34</v>
@@ -26184,7 +26184,7 @@
         <v>12.76</v>
       </c>
       <c r="I340" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J340" t="n">
         <v>239.32</v>
@@ -26259,7 +26259,7 @@
         <v>-18.43</v>
       </c>
       <c r="I341" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>236.89</v>
@@ -26338,7 +26338,7 @@
         <v>-16.59</v>
       </c>
       <c r="I342" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J342" s="4" t="n">
         <v>231.94</v>
@@ -26413,7 +26413,7 @@
         <v>7.26</v>
       </c>
       <c r="I343" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J343" t="n">
         <v>228.54</v>
@@ -26488,7 +26488,7 @@
         <v>-15.09</v>
       </c>
       <c r="I344" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>227.67</v>
@@ -26567,7 +26567,7 @@
         <v>5.78</v>
       </c>
       <c r="I345" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J345" t="n">
         <v>225.84</v>
@@ -26642,7 +26642,7 @@
         <v>10.08</v>
       </c>
       <c r="I346" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J346" t="n">
         <v>225.38</v>
@@ -26717,7 +26717,7 @@
         <v>-0.1</v>
       </c>
       <c r="I347" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J347" t="n">
         <v>225.96</v>
@@ -26792,7 +26792,7 @@
         <v>-13.99</v>
       </c>
       <c r="I348" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J348" t="n">
         <v>223.03</v>
@@ -26871,7 +26871,7 @@
         <v>6.83</v>
       </c>
       <c r="I349" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J349" t="n">
         <v>220.13</v>
@@ -26946,7 +26946,7 @@
         <v>-6.29</v>
       </c>
       <c r="I350" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J350" t="n">
         <v>214.79</v>
@@ -27021,7 +27021,7 @@
         <v>-13.93</v>
       </c>
       <c r="I351" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J351" t="n">
         <v>210.61</v>
@@ -27096,7 +27096,7 @@
         <v>-4.92</v>
       </c>
       <c r="I352" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J352" t="n">
         <v>205.69</v>
@@ -27171,7 +27171,7 @@
         <v>0.99</v>
       </c>
       <c r="I353" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J353" t="n">
         <v>198.57</v>
@@ -27246,7 +27246,7 @@
         <v>15.89</v>
       </c>
       <c r="I354" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J354" t="n">
         <v>191.46</v>
@@ -27321,7 +27321,7 @@
         <v>1.54</v>
       </c>
       <c r="I355" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J355" t="n">
         <v>187.94</v>
@@ -27396,7 +27396,7 @@
         <v>-2.16</v>
       </c>
       <c r="I356" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J356" t="n">
         <v>184.34</v>
@@ -27471,7 +27471,7 @@
         <v>-13.14</v>
       </c>
       <c r="I357" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J357" t="n">
         <v>178.56</v>
@@ -27546,7 +27546,7 @@
         <v>-6.33</v>
       </c>
       <c r="I358" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J358" t="n">
         <v>174.19</v>
@@ -27625,7 +27625,7 @@
         <v>-14.52</v>
       </c>
       <c r="I359" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J359" s="4" t="n">
         <v>167.84</v>
@@ -27700,7 +27700,7 @@
         <v>-16.02</v>
       </c>
       <c r="I360" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J360" s="4" t="n">
         <v>159.11</v>
@@ -27779,7 +27779,7 @@
         <v>24.7</v>
       </c>
       <c r="I361" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J361" t="n">
         <v>153.97</v>
@@ -27854,7 +27854,7 @@
         <v>0</v>
       </c>
       <c r="I362" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J362" t="n">
         <v>150.64</v>
@@ -27929,7 +27929,7 @@
         <v>1.74</v>
       </c>
       <c r="I363" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J363" t="n">
         <v>146.74</v>
@@ -28004,7 +28004,7 @@
         <v>19.87</v>
       </c>
       <c r="I364" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J364" t="n">
         <v>145.48</v>
@@ -28079,7 +28079,7 @@
         <v>-5.6</v>
       </c>
       <c r="I365" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J365" t="n">
         <v>143.34</v>
@@ -28158,7 +28158,7 @@
         <v>0.2</v>
       </c>
       <c r="I366" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J366" t="n">
         <v>140.34</v>
@@ -28233,7 +28233,7 @@
         <v>5.99</v>
       </c>
       <c r="I367" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J367" t="n">
         <v>137.74</v>
@@ -28308,7 +28308,7 @@
         <v>-7.31</v>
       </c>
       <c r="I368" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J368" t="n">
         <v>135.97</v>
@@ -28387,7 +28387,7 @@
         <v>2.31</v>
       </c>
       <c r="I369" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J369" t="n">
         <v>133.79</v>
@@ -28462,7 +28462,7 @@
         <v>6.89</v>
       </c>
       <c r="I370" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J370" t="n">
         <v>132.62</v>
@@ -28537,7 +28537,7 @@
         <v>2.25</v>
       </c>
       <c r="I371" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J371" t="n">
         <v>132.76</v>
@@ -28612,7 +28612,7 @@
         <v>-0.28</v>
       </c>
       <c r="I372" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J372" t="n">
         <v>133.24</v>
@@ -28687,7 +28687,7 @@
         <v>4.54</v>
       </c>
       <c r="I373" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J373" t="n">
         <v>133.97</v>
@@ -28762,7 +28762,7 @@
         <v>-14.8</v>
       </c>
       <c r="I374" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J374" s="4" t="n">
         <v>132.5</v>
@@ -28841,7 +28841,7 @@
         <v>-6.48</v>
       </c>
       <c r="I375" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J375" t="n">
         <v>130.49</v>
@@ -28916,7 +28916,7 @@
         <v>1.22</v>
       </c>
       <c r="I376" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J376" t="n">
         <v>128.73</v>
@@ -28991,7 +28991,7 @@
         <v>-1.32</v>
       </c>
       <c r="I377" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J377" t="n">
         <v>127.92</v>
@@ -29066,7 +29066,7 @@
         <v>-7.82</v>
       </c>
       <c r="I378" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J378" t="n">
         <v>127.07</v>
@@ -29141,7 +29141,7 @@
         <v>4.05</v>
       </c>
       <c r="I379" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J379" t="n">
         <v>127.37</v>
@@ -29216,7 +29216,7 @@
         <v>0.8</v>
       </c>
       <c r="I380" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J380" t="n">
         <v>128.6</v>
@@ -29291,7 +29291,7 @@
         <v>5.54</v>
       </c>
       <c r="I381" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J381" t="n">
         <v>129.02</v>
@@ -29366,7 +29366,7 @@
         <v>-9.51</v>
       </c>
       <c r="I382" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J382" t="n">
         <v>128.85</v>
@@ -29441,7 +29441,7 @@
         <v>1.3</v>
       </c>
       <c r="I383" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J383" t="n">
         <v>128.66</v>
@@ -29516,7 +29516,7 @@
         <v>-6.1</v>
       </c>
       <c r="I384" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J384" t="n">
         <v>126.96</v>
@@ -29595,7 +29595,7 @@
         <v>0.42</v>
       </c>
       <c r="I385" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J385" t="n">
         <v>125.67</v>
@@ -29674,7 +29674,7 @@
         <v>0.37</v>
       </c>
       <c r="I386" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J386" t="n">
         <v>124.39</v>
@@ -29753,7 +29753,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="I387" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J387" t="n">
         <v>123.25</v>
@@ -29828,7 +29828,7 @@
         <v>5.11</v>
       </c>
       <c r="I388" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J388" t="n">
         <v>122.91</v>
@@ -29903,7 +29903,7 @@
         <v>2.11</v>
       </c>
       <c r="I389" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J389" t="n">
         <v>122.55</v>
@@ -29978,7 +29978,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="I390" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J390" t="n">
         <v>121.23</v>
@@ -30057,7 +30057,7 @@
         <v>5.24</v>
       </c>
       <c r="I391" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J391" t="n">
         <v>120.06</v>
@@ -30132,7 +30132,7 @@
         <v>-16.99</v>
       </c>
       <c r="I392" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J392" s="4" t="n">
         <v>117.87</v>
@@ -30211,7 +30211,7 @@
         <v>1.18</v>
       </c>
       <c r="I393" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J393" t="n">
         <v>115.41</v>
@@ -30286,7 +30286,7 @@
         <v>1.61</v>
       </c>
       <c r="I394" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J394" t="n">
         <v>114.15</v>
@@ -30361,7 +30361,7 @@
         <v>10.43</v>
       </c>
       <c r="I395" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J395" t="n">
         <v>113.86</v>
@@ -30436,7 +30436,7 @@
         <v>7.71</v>
       </c>
       <c r="I396" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J396" t="n">
         <v>113.93</v>
@@ -30511,7 +30511,7 @@
         <v>14.77</v>
       </c>
       <c r="I397" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J397" t="n">
         <v>115</v>
@@ -30586,7 +30586,7 @@
         <v>7.13</v>
       </c>
       <c r="I398" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J398" t="n">
         <v>117.04</v>
@@ -30661,7 +30661,7 @@
         <v>-3.75</v>
       </c>
       <c r="I399" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J399" t="n">
         <v>118.57</v>
@@ -30736,7 +30736,7 @@
         <v>0.05</v>
       </c>
       <c r="I400" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J400" t="n">
         <v>120.06</v>
@@ -30811,7 +30811,7 @@
         <v>3.5</v>
       </c>
       <c r="I401" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J401" t="n">
         <v>121.49</v>
@@ -30886,7 +30886,7 @@
         <v>-6.05</v>
       </c>
       <c r="I402" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J402" t="n">
         <v>123.04</v>
@@ -30961,7 +30961,7 @@
         <v>3.31</v>
       </c>
       <c r="I403" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J403" t="n">
         <v>124.75</v>
@@ -31036,7 +31036,7 @@
         <v>0.59</v>
       </c>
       <c r="I404" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J404" t="n">
         <v>126.85</v>
@@ -31111,7 +31111,7 @@
         <v>3.94</v>
       </c>
       <c r="I405" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J405" t="n">
         <v>129.22</v>
@@ -31186,7 +31186,7 @@
         <v>6.52</v>
       </c>
       <c r="I406" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J406" t="n">
         <v>132.08</v>
@@ -31261,7 +31261,7 @@
         <v>0.34</v>
       </c>
       <c r="I407" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J407" t="n">
         <v>134.43</v>
@@ -31336,7 +31336,7 @@
         <v>-0.01</v>
       </c>
       <c r="I408" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J408" t="n">
         <v>136.48</v>
@@ -31411,7 +31411,7 @@
         <v>-3.26</v>
       </c>
       <c r="I409" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J409" t="n">
         <v>138.14</v>
@@ -31490,7 +31490,7 @@
         <v>-10.31</v>
       </c>
       <c r="I410" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J410" t="n">
         <v>139.48</v>
@@ -31565,7 +31565,7 @@
         <v>-1.94</v>
       </c>
       <c r="I411" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J411" t="n">
         <v>140.38</v>
@@ -31644,7 +31644,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="I412" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J412" t="n">
         <v>141.75</v>
@@ -31723,7 +31723,7 @@
         <v>-0.65</v>
       </c>
       <c r="I413" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J413" t="n">
         <v>143.01</v>
@@ -31798,7 +31798,7 @@
         <v>-13.35</v>
       </c>
       <c r="I414" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J414" t="n">
         <v>143.35</v>
@@ -31816,7 +31816,7 @@
         <v>30.11</v>
       </c>
       <c r="O414" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31842,6 +31842,83 @@
       <c r="W414" s="1" t="n">
         <v>157.3</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="D415" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="E415" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="F415" t="n">
+        <v>97.70999999999999</v>
+      </c>
+      <c r="G415" t="n">
+        <v>56816997</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-11.61</v>
+      </c>
+      <c r="I415" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="K415" t="n">
+        <v>128.95</v>
+      </c>
+      <c r="L415" t="n">
+        <v>160.98</v>
+      </c>
+      <c r="M415" t="n">
+        <v>121.73</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="O415" t="n">
+        <v>24</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -608,7 +608,7 @@
         <v>-7.1</v>
       </c>
       <c r="I2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J2" t="n">
         <v>27.4</v>
@@ -687,7 +687,7 @@
         <v>-6.32</v>
       </c>
       <c r="I3" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J3" t="n">
         <v>27.4</v>
@@ -762,7 +762,7 @@
         <v>4.86</v>
       </c>
       <c r="I4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J4" t="n">
         <v>27.44</v>
@@ -837,7 +837,7 @@
         <v>-17.28</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>27.25</v>
@@ -912,7 +912,7 @@
         <v>4.54</v>
       </c>
       <c r="I6" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J6" t="n">
         <v>27.03</v>
@@ -987,7 +987,7 @@
         <v>-9.789999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J7" t="n">
         <v>26.7</v>
@@ -1062,7 +1062,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J8" t="n">
         <v>26.46</v>
@@ -1137,7 +1137,7 @@
         <v>6.29</v>
       </c>
       <c r="I9" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J9" t="n">
         <v>26.24</v>
@@ -1212,7 +1212,7 @@
         <v>-12.39</v>
       </c>
       <c r="I10" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J10" t="n">
         <v>25.82</v>
@@ -1291,7 +1291,7 @@
         <v>8.59</v>
       </c>
       <c r="I11" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J11" t="n">
         <v>25.49</v>
@@ -1366,7 +1366,7 @@
         <v>-13.84</v>
       </c>
       <c r="I12" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J12" t="n">
         <v>25.07</v>
@@ -1449,7 +1449,7 @@
         <v>-3.19</v>
       </c>
       <c r="I13" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J13" t="n">
         <v>24.58</v>
@@ -1532,7 +1532,7 @@
         <v>5.09</v>
       </c>
       <c r="I14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J14" t="n">
         <v>24.13</v>
@@ -1611,7 +1611,7 @@
         <v>-1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J15" t="n">
         <v>23.66</v>
@@ -1690,7 +1690,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J16" t="n">
         <v>23.23</v>
@@ -1765,7 +1765,7 @@
         <v>4.98</v>
       </c>
       <c r="I17" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J17" t="n">
         <v>22.84</v>
@@ -1840,7 +1840,7 @@
         <v>-4.12</v>
       </c>
       <c r="I18" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J18" t="n">
         <v>22.34</v>
@@ -1915,7 +1915,7 @@
         <v>2.22</v>
       </c>
       <c r="I19" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J19" t="n">
         <v>21.79</v>
@@ -1990,7 +1990,7 @@
         <v>-2.17</v>
       </c>
       <c r="I20" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J20" t="n">
         <v>21.21</v>
@@ -2065,7 +2065,7 @@
         <v>-3.28</v>
       </c>
       <c r="I21" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J21" t="n">
         <v>20.74</v>
@@ -2140,7 +2140,7 @@
         <v>8.93</v>
       </c>
       <c r="I22" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J22" t="n">
         <v>20.45</v>
@@ -2215,7 +2215,7 @@
         <v>-1.82</v>
       </c>
       <c r="I23" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J23" t="n">
         <v>20.23</v>
@@ -2290,7 +2290,7 @@
         <v>-8.6</v>
       </c>
       <c r="I24" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J24" t="n">
         <v>19.86</v>
@@ -2369,7 +2369,7 @@
         <v>-5.45</v>
       </c>
       <c r="I25" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J25" t="n">
         <v>19.66</v>
@@ -2444,7 +2444,7 @@
         <v>-9.779999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J26" t="n">
         <v>19.33</v>
@@ -2519,7 +2519,7 @@
         <v>-0.5</v>
       </c>
       <c r="I27" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J27" t="n">
         <v>19.11</v>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J28" t="n">
         <v>18.88</v>
@@ -2669,7 +2669,7 @@
         <v>1.95</v>
       </c>
       <c r="I29" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J29" t="n">
         <v>18.6</v>
@@ -2744,7 +2744,7 @@
         <v>-29.83</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>18.21</v>
@@ -2827,7 +2827,7 @@
         <v>-23.5</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>17.61</v>
@@ -2910,7 +2910,7 @@
         <v>4.83</v>
       </c>
       <c r="I32" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J32" t="n">
         <v>17.17</v>
@@ -2993,7 +2993,7 @@
         <v>-9.77</v>
       </c>
       <c r="I33" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J33" t="n">
         <v>16.72</v>
@@ -3076,7 +3076,7 @@
         <v>54.74</v>
       </c>
       <c r="I34" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J34" t="n">
         <v>16.45</v>
@@ -3155,7 +3155,7 @@
         <v>-24.61</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>16.03</v>
@@ -3238,7 +3238,7 @@
         <v>6.26</v>
       </c>
       <c r="I36" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J36" t="n">
         <v>15.56</v>
@@ -3321,7 +3321,7 @@
         <v>2.36</v>
       </c>
       <c r="I37" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J37" t="n">
         <v>15.04</v>
@@ -3400,7 +3400,7 @@
         <v>1.25</v>
       </c>
       <c r="I38" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J38" t="n">
         <v>14.58</v>
@@ -3475,7 +3475,7 @@
         <v>-11.93</v>
       </c>
       <c r="I39" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J39" t="n">
         <v>14.04</v>
@@ -3558,7 +3558,7 @@
         <v>-1.51</v>
       </c>
       <c r="I40" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J40" t="n">
         <v>13.5</v>
@@ -3637,7 +3637,7 @@
         <v>-5.35</v>
       </c>
       <c r="I41" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J41" t="n">
         <v>12.98</v>
@@ -3712,7 +3712,7 @@
         <v>5.42</v>
       </c>
       <c r="I42" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J42" t="n">
         <v>12.4</v>
@@ -3787,7 +3787,7 @@
         <v>12.14</v>
       </c>
       <c r="I43" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J43" t="n">
         <v>11.89</v>
@@ -3866,7 +3866,7 @@
         <v>16.59</v>
       </c>
       <c r="I44" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J44" t="n">
         <v>11.55</v>
@@ -3941,7 +3941,7 @@
         <v>2.85</v>
       </c>
       <c r="I45" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J45" t="n">
         <v>11.28</v>
@@ -4016,7 +4016,7 @@
         <v>-0.41</v>
       </c>
       <c r="I46" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J46" t="n">
         <v>11.09</v>
@@ -4091,7 +4091,7 @@
         <v>-3.51</v>
       </c>
       <c r="I47" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J47" t="n">
         <v>10.89</v>
@@ -4166,7 +4166,7 @@
         <v>2.54</v>
       </c>
       <c r="I48" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J48" t="n">
         <v>10.7</v>
@@ -4241,7 +4241,7 @@
         <v>-0.5</v>
       </c>
       <c r="I49" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J49" t="n">
         <v>10.49</v>
@@ -4316,7 +4316,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J50" t="n">
         <v>10.59</v>
@@ -4391,7 +4391,7 @@
         <v>-1.81</v>
       </c>
       <c r="I51" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J51" t="n">
         <v>10.8</v>
@@ -4466,7 +4466,7 @@
         <v>-3.15</v>
       </c>
       <c r="I52" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J52" t="n">
         <v>10.98</v>
@@ -4541,7 +4541,7 @@
         <v>5.08</v>
       </c>
       <c r="I53" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J53" t="n">
         <v>11.23</v>
@@ -4616,7 +4616,7 @@
         <v>2.8</v>
       </c>
       <c r="I54" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J54" t="n">
         <v>11.27</v>
@@ -4691,7 +4691,7 @@
         <v>3.31</v>
       </c>
       <c r="I55" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J55" t="n">
         <v>11.49</v>
@@ -4766,7 +4766,7 @@
         <v>21.42</v>
       </c>
       <c r="I56" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J56" t="n">
         <v>11.84</v>
@@ -4841,7 +4841,7 @@
         <v>8.56</v>
       </c>
       <c r="I57" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J57" t="n">
         <v>12.24</v>
@@ -4916,7 +4916,7 @@
         <v>1.3</v>
       </c>
       <c r="I58" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J58" t="n">
         <v>12.65</v>
@@ -4991,7 +4991,7 @@
         <v>-1.97</v>
       </c>
       <c r="I59" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J59" t="n">
         <v>13.11</v>
@@ -5066,7 +5066,7 @@
         <v>-0.44</v>
       </c>
       <c r="I60" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J60" t="n">
         <v>13.56</v>
@@ -5141,7 +5141,7 @@
         <v>-1.75</v>
       </c>
       <c r="I61" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J61" t="n">
         <v>14.03</v>
@@ -5216,7 +5216,7 @@
         <v>-0.5</v>
       </c>
       <c r="I62" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J62" t="n">
         <v>14.47</v>
@@ -5291,7 +5291,7 @@
         <v>-5.42</v>
       </c>
       <c r="I63" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J63" t="n">
         <v>14.8</v>
@@ -5366,7 +5366,7 @@
         <v>-2.89</v>
       </c>
       <c r="I64" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J64" t="n">
         <v>15.03</v>
@@ -5441,7 +5441,7 @@
         <v>-4.68</v>
       </c>
       <c r="I65" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J65" t="n">
         <v>15.19</v>
@@ -5516,7 +5516,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J66" t="n">
         <v>15.44</v>
@@ -5591,7 +5591,7 @@
         <v>-1.45</v>
       </c>
       <c r="I67" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J67" t="n">
         <v>15.7</v>
@@ -5666,7 +5666,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J68" t="n">
         <v>15.95</v>
@@ -5741,7 +5741,7 @@
         <v>-6.01</v>
       </c>
       <c r="I69" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J69" t="n">
         <v>16.16</v>
@@ -5820,7 +5820,7 @@
         <v>4.53</v>
       </c>
       <c r="I70" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J70" t="n">
         <v>16.33</v>
@@ -5895,7 +5895,7 @@
         <v>8.32</v>
       </c>
       <c r="I71" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J71" t="n">
         <v>16.6</v>
@@ -5970,7 +5970,7 @@
         <v>4.28</v>
       </c>
       <c r="I72" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J72" t="n">
         <v>16.92</v>
@@ -6045,7 +6045,7 @@
         <v>-1.47</v>
       </c>
       <c r="I73" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J73" t="n">
         <v>17.19</v>
@@ -6120,7 +6120,7 @@
         <v>1.98</v>
       </c>
       <c r="I74" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J74" t="n">
         <v>17.47</v>
@@ -6195,7 +6195,7 @@
         <v>7.33</v>
       </c>
       <c r="I75" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J75" t="n">
         <v>17.79</v>
@@ -6270,7 +6270,7 @@
         <v>6.34</v>
       </c>
       <c r="I76" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J76" t="n">
         <v>18.03</v>
@@ -6345,7 +6345,7 @@
         <v>-1.15</v>
       </c>
       <c r="I77" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J77" t="n">
         <v>18.18</v>
@@ -6420,7 +6420,7 @@
         <v>0.23</v>
       </c>
       <c r="I78" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J78" t="n">
         <v>18.32</v>
@@ -6495,7 +6495,7 @@
         <v>-7.59</v>
       </c>
       <c r="I79" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J79" t="n">
         <v>18.4</v>
@@ -6574,7 +6574,7 @@
         <v>9.27</v>
       </c>
       <c r="I80" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J80" t="n">
         <v>18.57</v>
@@ -6649,7 +6649,7 @@
         <v>-2.2</v>
       </c>
       <c r="I81" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J81" t="n">
         <v>18.74</v>
@@ -6724,7 +6724,7 @@
         <v>0.89</v>
       </c>
       <c r="I82" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J82" t="n">
         <v>18.92</v>
@@ -6799,7 +6799,7 @@
         <v>-1.86</v>
       </c>
       <c r="I83" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J83" t="n">
         <v>19.13</v>
@@ -6874,7 +6874,7 @@
         <v>1.75</v>
       </c>
       <c r="I84" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J84" t="n">
         <v>19.38</v>
@@ -6949,7 +6949,7 @@
         <v>11.35</v>
       </c>
       <c r="I85" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J85" t="n">
         <v>19.8</v>
@@ -7024,7 +7024,7 @@
         <v>2.63</v>
       </c>
       <c r="I86" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J86" t="n">
         <v>20.16</v>
@@ -7099,7 +7099,7 @@
         <v>2.52</v>
       </c>
       <c r="I87" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J87" t="n">
         <v>20.57</v>
@@ -7174,7 +7174,7 @@
         <v>-0.36</v>
       </c>
       <c r="I88" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J88" t="n">
         <v>20.97</v>
@@ -7249,7 +7249,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J89" t="n">
         <v>21.42</v>
@@ -7324,7 +7324,7 @@
         <v>-1.59</v>
       </c>
       <c r="I90" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J90" t="n">
         <v>21.81</v>
@@ -7399,7 +7399,7 @@
         <v>5.43</v>
       </c>
       <c r="I91" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J91" t="n">
         <v>22.2</v>
@@ -7474,7 +7474,7 @@
         <v>1.46</v>
       </c>
       <c r="I92" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J92" t="n">
         <v>22.57</v>
@@ -7549,7 +7549,7 @@
         <v>-5.53</v>
       </c>
       <c r="I93" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J93" t="n">
         <v>22.89</v>
@@ -7624,7 +7624,7 @@
         <v>5.61</v>
       </c>
       <c r="I94" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J94" t="n">
         <v>23.25</v>
@@ -7699,7 +7699,7 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J95" t="n">
         <v>23.55</v>
@@ -7774,7 +7774,7 @@
         <v>2.7</v>
       </c>
       <c r="I96" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J96" t="n">
         <v>23.83</v>
@@ -7849,7 +7849,7 @@
         <v>-0.29</v>
       </c>
       <c r="I97" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J97" t="n">
         <v>24.12</v>
@@ -7924,7 +7924,7 @@
         <v>-2.9</v>
       </c>
       <c r="I98" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J98" t="n">
         <v>24.36</v>
@@ -7999,7 +7999,7 @@
         <v>2.98</v>
       </c>
       <c r="I99" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J99" t="n">
         <v>24.72</v>
@@ -8074,7 +8074,7 @@
         <v>-0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J100" t="n">
         <v>24.98</v>
@@ -8149,7 +8149,7 @@
         <v>1.07</v>
       </c>
       <c r="I101" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J101" t="n">
         <v>25.28</v>
@@ -8224,7 +8224,7 @@
         <v>0.04</v>
       </c>
       <c r="I102" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J102" t="n">
         <v>25.57</v>
@@ -8299,7 +8299,7 @@
         <v>0.62</v>
       </c>
       <c r="I103" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J103" t="n">
         <v>25.89</v>
@@ -8374,7 +8374,7 @@
         <v>-4.26</v>
       </c>
       <c r="I104" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J104" t="n">
         <v>26.13</v>
@@ -8449,7 +8449,7 @@
         <v>-2.05</v>
       </c>
       <c r="I105" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J105" t="n">
         <v>26.22</v>
@@ -8528,7 +8528,7 @@
         <v>-0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J106" t="n">
         <v>26.27</v>
@@ -8603,7 +8603,7 @@
         <v>-0.08</v>
       </c>
       <c r="I107" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J107" t="n">
         <v>26.29</v>
@@ -8678,7 +8678,7 @@
         <v>4.96</v>
       </c>
       <c r="I108" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J108" t="n">
         <v>26.38</v>
@@ -8753,7 +8753,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J109" t="n">
         <v>26.48</v>
@@ -8828,7 +8828,7 @@
         <v>2.15</v>
       </c>
       <c r="I110" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J110" t="n">
         <v>26.62</v>
@@ -8903,7 +8903,7 @@
         <v>-9.5</v>
       </c>
       <c r="I111" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J111" t="n">
         <v>26.57</v>
@@ -8982,7 +8982,7 @@
         <v>-3.61</v>
       </c>
       <c r="I112" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J112" t="n">
         <v>26.45</v>
@@ -9057,7 +9057,7 @@
         <v>3.82</v>
       </c>
       <c r="I113" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J113" t="n">
         <v>26.45</v>
@@ -9132,7 +9132,7 @@
         <v>-1.92</v>
       </c>
       <c r="I114" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J114" t="n">
         <v>26.36</v>
@@ -9207,7 +9207,7 @@
         <v>-2.16</v>
       </c>
       <c r="I115" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J115" t="n">
         <v>26.23</v>
@@ -9282,7 +9282,7 @@
         <v>4.21</v>
       </c>
       <c r="I116" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J116" t="n">
         <v>26.11</v>
@@ -9357,7 +9357,7 @@
         <v>2.84</v>
       </c>
       <c r="I117" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J117" t="n">
         <v>26.03</v>
@@ -9432,7 +9432,7 @@
         <v>-0.39</v>
       </c>
       <c r="I118" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J118" t="n">
         <v>25.99</v>
@@ -9507,7 +9507,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J119" t="n">
         <v>26.02</v>
@@ -9582,7 +9582,7 @@
         <v>4.54</v>
       </c>
       <c r="I120" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J120" t="n">
         <v>26.13</v>
@@ -9657,7 +9657,7 @@
         <v>0.51</v>
       </c>
       <c r="I121" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J121" t="n">
         <v>26.24</v>
@@ -9732,7 +9732,7 @@
         <v>-6.98</v>
       </c>
       <c r="I122" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J122" t="n">
         <v>26.24</v>
@@ -9807,7 +9807,7 @@
         <v>0.59</v>
       </c>
       <c r="I123" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J123" t="n">
         <v>26.24</v>
@@ -9882,7 +9882,7 @@
         <v>-4.65</v>
       </c>
       <c r="I124" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J124" t="n">
         <v>26.24</v>
@@ -9961,7 +9961,7 @@
         <v>-1.68</v>
       </c>
       <c r="I125" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J125" t="n">
         <v>26.24</v>
@@ -10036,7 +10036,7 @@
         <v>-1.75</v>
       </c>
       <c r="I126" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J126" t="n">
         <v>26.23</v>
@@ -10111,7 +10111,7 @@
         <v>8.25</v>
       </c>
       <c r="I127" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J127" t="n">
         <v>26.32</v>
@@ -10186,7 +10186,7 @@
         <v>-0.55</v>
       </c>
       <c r="I128" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J128" t="n">
         <v>26.34</v>
@@ -10261,7 +10261,7 @@
         <v>2.35</v>
       </c>
       <c r="I129" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J129" t="n">
         <v>26.38</v>
@@ -10336,7 +10336,7 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J130" t="n">
         <v>26.41</v>
@@ -10411,7 +10411,7 @@
         <v>1.24</v>
       </c>
       <c r="I131" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J131" t="n">
         <v>26.59</v>
@@ -10486,7 +10486,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="I132" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J132" t="n">
         <v>26.69</v>
@@ -10565,7 +10565,7 @@
         <v>-3.04</v>
       </c>
       <c r="I133" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J133" t="n">
         <v>26.7</v>
@@ -10644,7 +10644,7 @@
         <v>-1.35</v>
       </c>
       <c r="I134" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J134" t="n">
         <v>26.72</v>
@@ -10719,7 +10719,7 @@
         <v>2.97</v>
       </c>
       <c r="I135" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J135" t="n">
         <v>26.8</v>
@@ -10794,7 +10794,7 @@
         <v>3.08</v>
       </c>
       <c r="I136" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J136" t="n">
         <v>26.87</v>
@@ -10869,7 +10869,7 @@
         <v>2.38</v>
       </c>
       <c r="I137" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J137" t="n">
         <v>26.94</v>
@@ -10944,7 +10944,7 @@
         <v>0.37</v>
       </c>
       <c r="I138" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J138" t="n">
         <v>27.02</v>
@@ -11019,7 +11019,7 @@
         <v>5.23</v>
       </c>
       <c r="I139" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J139" t="n">
         <v>27.05</v>
@@ -11094,7 +11094,7 @@
         <v>2</v>
       </c>
       <c r="I140" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J140" t="n">
         <v>27.05</v>
@@ -11169,7 +11169,7 @@
         <v>0.45</v>
       </c>
       <c r="I141" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J141" t="n">
         <v>27.04</v>
@@ -11244,7 +11244,7 @@
         <v>2.39</v>
       </c>
       <c r="I142" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J142" t="n">
         <v>27.17</v>
@@ -11319,7 +11319,7 @@
         <v>1.6</v>
       </c>
       <c r="I143" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J143" t="n">
         <v>27.32</v>
@@ -11394,7 +11394,7 @@
         <v>-0.03</v>
       </c>
       <c r="I144" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J144" t="n">
         <v>27.53</v>
@@ -11469,7 +11469,7 @@
         <v>10.41</v>
       </c>
       <c r="I145" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J145" t="n">
         <v>27.92</v>
@@ -11544,7 +11544,7 @@
         <v>-1.84</v>
       </c>
       <c r="I146" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J146" t="n">
         <v>28.3</v>
@@ -11619,7 +11619,7 @@
         <v>4.27</v>
       </c>
       <c r="I147" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J147" t="n">
         <v>28.65</v>
@@ -11694,7 +11694,7 @@
         <v>-0.35</v>
       </c>
       <c r="I148" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J148" t="n">
         <v>29</v>
@@ -11769,7 +11769,7 @@
         <v>-0.29</v>
       </c>
       <c r="I149" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J149" t="n">
         <v>29.32</v>
@@ -11844,7 +11844,7 @@
         <v>-1.02</v>
       </c>
       <c r="I150" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J150" t="n">
         <v>29.6</v>
@@ -11919,7 +11919,7 @@
         <v>0.5</v>
       </c>
       <c r="I151" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J151" t="n">
         <v>29.88</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J152" t="n">
         <v>30.28</v>
@@ -12069,7 +12069,7 @@
         <v>2.41</v>
       </c>
       <c r="I153" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J153" t="n">
         <v>30.75</v>
@@ -12144,7 +12144,7 @@
         <v>5.8</v>
       </c>
       <c r="I154" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J154" t="n">
         <v>31.35</v>
@@ -12219,7 +12219,7 @@
         <v>6</v>
       </c>
       <c r="I155" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J155" t="n">
         <v>32.02</v>
@@ -12294,7 +12294,7 @@
         <v>-2.18</v>
       </c>
       <c r="I156" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J156" t="n">
         <v>32.61</v>
@@ -12369,7 +12369,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="I157" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J157" t="n">
         <v>33.34</v>
@@ -12444,7 +12444,7 @@
         <v>-6.91</v>
       </c>
       <c r="I158" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J158" t="n">
         <v>33.93</v>
@@ -12519,7 +12519,7 @@
         <v>10.18</v>
       </c>
       <c r="I159" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J159" t="n">
         <v>34.64</v>
@@ -12594,7 +12594,7 @@
         <v>-1.26</v>
       </c>
       <c r="I160" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J160" t="n">
         <v>35.29</v>
@@ -12669,7 +12669,7 @@
         <v>-19</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>35.53</v>
@@ -12748,7 +12748,7 @@
         <v>14.39</v>
       </c>
       <c r="I162" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J162" t="n">
         <v>35.99</v>
@@ -12823,7 +12823,7 @@
         <v>-6.39</v>
       </c>
       <c r="I163" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J163" t="n">
         <v>36.3</v>
@@ -12898,7 +12898,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="I164" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J164" t="n">
         <v>36.78</v>
@@ -12973,7 +12973,7 @@
         <v>1.48</v>
       </c>
       <c r="I165" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J165" t="n">
         <v>37.12</v>
@@ -13048,7 +13048,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J166" t="n">
         <v>37.48</v>
@@ -13123,7 +13123,7 @@
         <v>4.84</v>
       </c>
       <c r="I167" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J167" t="n">
         <v>37.88</v>
@@ -13198,7 +13198,7 @@
         <v>-1.73</v>
       </c>
       <c r="I168" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J168" t="n">
         <v>38.24</v>
@@ -13273,7 +13273,7 @@
         <v>-7.52</v>
       </c>
       <c r="I169" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J169" t="n">
         <v>38.44</v>
@@ -13352,7 +13352,7 @@
         <v>7.25</v>
       </c>
       <c r="I170" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J170" t="n">
         <v>38.81</v>
@@ -13427,7 +13427,7 @@
         <v>4.79</v>
       </c>
       <c r="I171" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J171" t="n">
         <v>39.27</v>
@@ -13502,7 +13502,7 @@
         <v>8.58</v>
       </c>
       <c r="I172" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J172" t="n">
         <v>39.91</v>
@@ -13577,7 +13577,7 @@
         <v>0.26</v>
       </c>
       <c r="I173" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J173" t="n">
         <v>40.51</v>
@@ -13652,7 +13652,7 @@
         <v>5.16</v>
       </c>
       <c r="I174" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J174" t="n">
         <v>41.14</v>
@@ -13727,7 +13727,7 @@
         <v>-4.03</v>
       </c>
       <c r="I175" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J175" t="n">
         <v>41.55</v>
@@ -13802,7 +13802,7 @@
         <v>0.82</v>
       </c>
       <c r="I176" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J176" t="n">
         <v>42.03</v>
@@ -13877,7 +13877,7 @@
         <v>1.68</v>
       </c>
       <c r="I177" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J177" t="n">
         <v>42.37</v>
@@ -13952,7 +13952,7 @@
         <v>-11.91</v>
       </c>
       <c r="I178" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J178" t="n">
         <v>42.57</v>
@@ -14027,7 +14027,7 @@
         <v>9.42</v>
       </c>
       <c r="I179" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J179" t="n">
         <v>42.77</v>
@@ -14102,7 +14102,7 @@
         <v>-8.16</v>
       </c>
       <c r="I180" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J180" t="n">
         <v>42.81</v>
@@ -14177,7 +14177,7 @@
         <v>-2.95</v>
       </c>
       <c r="I181" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J181" t="n">
         <v>43.19</v>
@@ -14256,7 +14256,7 @@
         <v>7.72</v>
       </c>
       <c r="I182" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J182" t="n">
         <v>43.48</v>
@@ -14331,7 +14331,7 @@
         <v>-7.01</v>
       </c>
       <c r="I183" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J183" t="n">
         <v>43.74</v>
@@ -14410,7 +14410,7 @@
         <v>4.55</v>
       </c>
       <c r="I184" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J184" t="n">
         <v>43.92</v>
@@ -14485,7 +14485,7 @@
         <v>-10.28</v>
       </c>
       <c r="I185" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J185" t="n">
         <v>43.86</v>
@@ -14560,7 +14560,7 @@
         <v>-0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J186" t="n">
         <v>43.79</v>
@@ -14635,7 +14635,7 @@
         <v>-5.18</v>
       </c>
       <c r="I187" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J187" t="n">
         <v>43.52</v>
@@ -14710,7 +14710,7 @@
         <v>-6.76</v>
       </c>
       <c r="I188" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J188" t="n">
         <v>43.16</v>
@@ -14789,7 +14789,7 @@
         <v>4.69</v>
       </c>
       <c r="I189" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J189" t="n">
         <v>43.04</v>
@@ -14864,7 +14864,7 @@
         <v>-14.33</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>42.52</v>
@@ -14947,7 +14947,7 @@
         <v>2.99</v>
       </c>
       <c r="I191" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J191" t="n">
         <v>41.95</v>
@@ -15022,7 +15022,7 @@
         <v>13.02</v>
       </c>
       <c r="I192" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J192" t="n">
         <v>41.4</v>
@@ -15097,7 +15097,7 @@
         <v>0.86</v>
       </c>
       <c r="I193" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J193" t="n">
         <v>40.86</v>
@@ -15172,7 +15172,7 @@
         <v>8.33</v>
       </c>
       <c r="I194" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J194" t="n">
         <v>40.35</v>
@@ -15247,7 +15247,7 @@
         <v>5.29</v>
       </c>
       <c r="I195" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J195" t="n">
         <v>40.05</v>
@@ -15322,7 +15322,7 @@
         <v>0.12</v>
       </c>
       <c r="I196" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J196" t="n">
         <v>39.72</v>
@@ -15397,7 +15397,7 @@
         <v>6.03</v>
       </c>
       <c r="I197" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J197" t="n">
         <v>39.48</v>
@@ -15472,7 +15472,7 @@
         <v>6.35</v>
       </c>
       <c r="I198" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J198" t="n">
         <v>39.67</v>
@@ -15547,7 +15547,7 @@
         <v>-3.05</v>
       </c>
       <c r="I199" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J199" t="n">
         <v>39.59</v>
@@ -15622,7 +15622,7 @@
         <v>2.97</v>
       </c>
       <c r="I200" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J200" t="n">
         <v>39.76</v>
@@ -15697,7 +15697,7 @@
         <v>3.21</v>
       </c>
       <c r="I201" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J201" t="n">
         <v>40.08</v>
@@ -15772,7 +15772,7 @@
         <v>-0.42</v>
       </c>
       <c r="I202" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J202" t="n">
         <v>40.22</v>
@@ -15847,7 +15847,7 @@
         <v>3.89</v>
       </c>
       <c r="I203" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J203" t="n">
         <v>40.61</v>
@@ -15922,7 +15922,7 @@
         <v>-1.73</v>
       </c>
       <c r="I204" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J204" t="n">
         <v>40.86</v>
@@ -15997,7 +15997,7 @@
         <v>-14.52</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>40.99</v>
@@ -16072,7 +16072,7 @@
         <v>-1.27</v>
       </c>
       <c r="I206" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J206" t="n">
         <v>41.1</v>
@@ -16147,7 +16147,7 @@
         <v>-1.68</v>
       </c>
       <c r="I207" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J207" t="n">
         <v>41.29</v>
@@ -16226,7 +16226,7 @@
         <v>-11.05</v>
       </c>
       <c r="I208" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J208" t="n">
         <v>41.37</v>
@@ -16301,7 +16301,7 @@
         <v>7.11</v>
       </c>
       <c r="I209" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J209" t="n">
         <v>41.5</v>
@@ -16376,7 +16376,7 @@
         <v>8.15</v>
       </c>
       <c r="I210" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J210" t="n">
         <v>42.05</v>
@@ -16451,7 +16451,7 @@
         <v>3.69</v>
       </c>
       <c r="I211" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J211" t="n">
         <v>42.62</v>
@@ -16526,7 +16526,7 @@
         <v>1.02</v>
       </c>
       <c r="I212" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J212" t="n">
         <v>43.01</v>
@@ -16601,7 +16601,7 @@
         <v>1.17</v>
       </c>
       <c r="I213" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J213" t="n">
         <v>43.41</v>
@@ -16676,7 +16676,7 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J214" t="n">
         <v>43.67</v>
@@ -16751,7 +16751,7 @@
         <v>-0.88</v>
       </c>
       <c r="I215" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J215" t="n">
         <v>43.79</v>
@@ -16826,7 +16826,7 @@
         <v>-0.34</v>
       </c>
       <c r="I216" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J216" t="n">
         <v>43.91</v>
@@ -16905,7 +16905,7 @@
         <v>-3.76</v>
       </c>
       <c r="I217" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J217" t="n">
         <v>43.82</v>
@@ -16980,7 +16980,7 @@
         <v>12.4</v>
       </c>
       <c r="I218" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J218" t="n">
         <v>43.86</v>
@@ -17055,7 +17055,7 @@
         <v>4.19</v>
       </c>
       <c r="I219" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J219" t="n">
         <v>44.06</v>
@@ -17130,7 +17130,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J220" t="n">
         <v>44.43</v>
@@ -17205,7 +17205,7 @@
         <v>-3.17</v>
       </c>
       <c r="I221" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J221" t="n">
         <v>44.65</v>
@@ -17280,7 +17280,7 @@
         <v>-5.05</v>
       </c>
       <c r="I222" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J222" t="n">
         <v>44.74</v>
@@ -17355,7 +17355,7 @@
         <v>8.65</v>
       </c>
       <c r="I223" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J223" t="n">
         <v>44.96</v>
@@ -17430,7 +17430,7 @@
         <v>1.3</v>
       </c>
       <c r="I224" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J224" t="n">
         <v>45.25</v>
@@ -17505,7 +17505,7 @@
         <v>2.6</v>
       </c>
       <c r="I225" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J225" t="n">
         <v>45.97</v>
@@ -17580,7 +17580,7 @@
         <v>-1.23</v>
       </c>
       <c r="I226" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J226" t="n">
         <v>46.68</v>
@@ -17655,7 +17655,7 @@
         <v>4.88</v>
       </c>
       <c r="I227" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J227" t="n">
         <v>47.56</v>
@@ -17730,7 +17730,7 @@
         <v>4.6</v>
       </c>
       <c r="I228" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J228" t="n">
         <v>48.79</v>
@@ -17805,7 +17805,7 @@
         <v>-4.63</v>
       </c>
       <c r="I229" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J229" t="n">
         <v>49.76</v>
@@ -17880,7 +17880,7 @@
         <v>9.57</v>
       </c>
       <c r="I230" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J230" t="n">
         <v>50.85</v>
@@ -17955,7 +17955,7 @@
         <v>0.38</v>
       </c>
       <c r="I231" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J231" t="n">
         <v>51.87</v>
@@ -18030,7 +18030,7 @@
         <v>-3.33</v>
       </c>
       <c r="I232" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J232" t="n">
         <v>52.76</v>
@@ -18105,7 +18105,7 @@
         <v>-1.46</v>
       </c>
       <c r="I233" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J233" t="n">
         <v>53.59</v>
@@ -18180,7 +18180,7 @@
         <v>7.02</v>
       </c>
       <c r="I234" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J234" t="n">
         <v>54.62</v>
@@ -18255,7 +18255,7 @@
         <v>7.89</v>
       </c>
       <c r="I235" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J235" t="n">
         <v>55.94</v>
@@ -18330,7 +18330,7 @@
         <v>0.54</v>
       </c>
       <c r="I236" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J236" t="n">
         <v>57.28</v>
@@ -18405,7 +18405,7 @@
         <v>-12.31</v>
       </c>
       <c r="I237" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J237" t="n">
         <v>58.26</v>
@@ -18480,7 +18480,7 @@
         <v>5.52</v>
       </c>
       <c r="I238" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J238" t="n">
         <v>59.16</v>
@@ -18555,7 +18555,7 @@
         <v>-6.14</v>
       </c>
       <c r="I239" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J239" t="n">
         <v>59.76</v>
@@ -18630,7 +18630,7 @@
         <v>-13.08</v>
       </c>
       <c r="I240" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J240" t="n">
         <v>59.72</v>
@@ -18709,7 +18709,7 @@
         <v>0.11</v>
       </c>
       <c r="I241" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J241" t="n">
         <v>59.77</v>
@@ -18784,7 +18784,7 @@
         <v>15.95</v>
       </c>
       <c r="I242" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J242" t="n">
         <v>60.37</v>
@@ -18859,7 +18859,7 @@
         <v>3.69</v>
       </c>
       <c r="I243" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J243" t="n">
         <v>60.88</v>
@@ -18934,7 +18934,7 @@
         <v>-1.08</v>
       </c>
       <c r="I244" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J244" t="n">
         <v>61.31</v>
@@ -19009,7 +19009,7 @@
         <v>7.44</v>
       </c>
       <c r="I245" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J245" t="n">
         <v>61.91</v>
@@ -19084,7 +19084,7 @@
         <v>-7.28</v>
       </c>
       <c r="I246" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J246" t="n">
         <v>62.29</v>
@@ -19159,7 +19159,7 @@
         <v>2.36</v>
       </c>
       <c r="I247" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J247" t="n">
         <v>62.62</v>
@@ -19234,7 +19234,7 @@
         <v>-0.37</v>
       </c>
       <c r="I248" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J248" t="n">
         <v>62.8</v>
@@ -19309,7 +19309,7 @@
         <v>3.02</v>
       </c>
       <c r="I249" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J249" t="n">
         <v>63.22</v>
@@ -19384,7 +19384,7 @@
         <v>-1.6</v>
       </c>
       <c r="I250" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J250" t="n">
         <v>63.31</v>
@@ -19459,7 +19459,7 @@
         <v>2.88</v>
       </c>
       <c r="I251" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J251" t="n">
         <v>63.47</v>
@@ -19534,7 +19534,7 @@
         <v>-1.86</v>
       </c>
       <c r="I252" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J252" t="n">
         <v>63.69</v>
@@ -19609,7 +19609,7 @@
         <v>4.06</v>
       </c>
       <c r="I253" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J253" t="n">
         <v>64.08</v>
@@ -19684,7 +19684,7 @@
         <v>4.85</v>
       </c>
       <c r="I254" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J254" t="n">
         <v>64.42</v>
@@ -19759,7 +19759,7 @@
         <v>-9.07</v>
       </c>
       <c r="I255" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J255" t="n">
         <v>64.19</v>
@@ -19834,7 +19834,7 @@
         <v>-3.94</v>
       </c>
       <c r="I256" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J256" t="n">
         <v>63.8</v>
@@ -19913,7 +19913,7 @@
         <v>-0.02</v>
       </c>
       <c r="I257" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J257" t="n">
         <v>63.85</v>
@@ -19988,7 +19988,7 @@
         <v>-14.89</v>
       </c>
       <c r="I258" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J258" s="4" t="n">
         <v>63.26</v>
@@ -20067,7 +20067,7 @@
         <v>5.99</v>
       </c>
       <c r="I259" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J259" t="n">
         <v>63.03</v>
@@ -20142,7 +20142,7 @@
         <v>-3.22</v>
       </c>
       <c r="I260" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J260" t="n">
         <v>63.11</v>
@@ -20221,7 +20221,7 @@
         <v>-12.6</v>
       </c>
       <c r="I261" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J261" t="n">
         <v>62.84</v>
@@ -20300,7 +20300,7 @@
         <v>11.35</v>
       </c>
       <c r="I262" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J262" t="n">
         <v>62.42</v>
@@ -20375,7 +20375,7 @@
         <v>2.36</v>
       </c>
       <c r="I263" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J263" t="n">
         <v>61.95</v>
@@ -20450,7 +20450,7 @@
         <v>2.75</v>
       </c>
       <c r="I264" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J264" t="n">
         <v>61.59</v>
@@ -20525,7 +20525,7 @@
         <v>-10.35</v>
       </c>
       <c r="I265" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J265" t="n">
         <v>60.7</v>
@@ -20598,7 +20598,7 @@
         <v>0.88</v>
       </c>
       <c r="I266" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J266" t="n">
         <v>60.08</v>
@@ -20677,7 +20677,7 @@
         <v>5.84</v>
       </c>
       <c r="I267" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J267" t="n">
         <v>59.54</v>
@@ -20752,7 +20752,7 @@
         <v>2.35</v>
       </c>
       <c r="I268" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J268" t="n">
         <v>59.07</v>
@@ -20827,7 +20827,7 @@
         <v>-1.69</v>
       </c>
       <c r="I269" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J269" t="n">
         <v>58.45</v>
@@ -20902,7 +20902,7 @@
         <v>1.54</v>
       </c>
       <c r="I270" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J270" t="n">
         <v>57.93</v>
@@ -20977,7 +20977,7 @@
         <v>-6.75</v>
       </c>
       <c r="I271" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J271" t="n">
         <v>57.14</v>
@@ -21056,7 +21056,7 @@
         <v>3.7</v>
       </c>
       <c r="I272" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J272" t="n">
         <v>56.5</v>
@@ -21131,7 +21131,7 @@
         <v>3.62</v>
       </c>
       <c r="I273" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J273" t="n">
         <v>55.82</v>
@@ -21206,7 +21206,7 @@
         <v>3.79</v>
       </c>
       <c r="I274" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J274" t="n">
         <v>55.08</v>
@@ -21281,7 +21281,7 @@
         <v>-14.14</v>
       </c>
       <c r="I275" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J275" t="n">
         <v>54.26</v>
@@ -21360,7 +21360,7 @@
         <v>-4.82</v>
       </c>
       <c r="I276" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J276" t="n">
         <v>53.45</v>
@@ -21439,7 +21439,7 @@
         <v>-12.86</v>
       </c>
       <c r="I277" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J277" t="n">
         <v>52.34</v>
@@ -21514,7 +21514,7 @@
         <v>17.96</v>
       </c>
       <c r="I278" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J278" t="n">
         <v>52.07</v>
@@ -21589,7 +21589,7 @@
         <v>9.09</v>
       </c>
       <c r="I279" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J279" t="n">
         <v>51.85</v>
@@ -21664,7 +21664,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I280" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J280" t="n">
         <v>51.75</v>
@@ -21739,7 +21739,7 @@
         <v>3.89</v>
       </c>
       <c r="I281" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J281" t="n">
         <v>52.1</v>
@@ -21814,7 +21814,7 @@
         <v>3.18</v>
       </c>
       <c r="I282" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J282" t="n">
         <v>52.26</v>
@@ -21893,7 +21893,7 @@
         <v>19.38</v>
       </c>
       <c r="I283" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J283" t="n">
         <v>52.9</v>
@@ -21968,7 +21968,7 @@
         <v>6.63</v>
       </c>
       <c r="I284" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J284" t="n">
         <v>53.7</v>
@@ -22043,7 +22043,7 @@
         <v>6.13</v>
       </c>
       <c r="I285" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J285" t="n">
         <v>55</v>
@@ -22118,7 +22118,7 @@
         <v>5.46</v>
       </c>
       <c r="I286" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J286" t="n">
         <v>56.49</v>
@@ -22193,7 +22193,7 @@
         <v>5.89</v>
       </c>
       <c r="I287" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J287" t="n">
         <v>58.07</v>
@@ -22268,7 +22268,7 @@
         <v>0.76</v>
       </c>
       <c r="I288" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J288" t="n">
         <v>59.62</v>
@@ -22343,7 +22343,7 @@
         <v>2.81</v>
       </c>
       <c r="I289" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J289" t="n">
         <v>61.34</v>
@@ -22418,7 +22418,7 @@
         <v>7.15</v>
       </c>
       <c r="I290" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J290" t="n">
         <v>63.33</v>
@@ -22493,7 +22493,7 @@
         <v>1.33</v>
       </c>
       <c r="I291" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J291" t="n">
         <v>65.56999999999999</v>
@@ -22568,7 +22568,7 @@
         <v>2.24</v>
       </c>
       <c r="I292" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J292" t="n">
         <v>67.81999999999999</v>
@@ -22643,7 +22643,7 @@
         <v>7.69</v>
       </c>
       <c r="I293" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J293" t="n">
         <v>70.34999999999999</v>
@@ -22718,7 +22718,7 @@
         <v>6.75</v>
       </c>
       <c r="I294" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J294" t="n">
         <v>73.14</v>
@@ -22793,7 +22793,7 @@
         <v>13.79</v>
       </c>
       <c r="I295" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J295" t="n">
         <v>77.09999999999999</v>
@@ -22868,7 +22868,7 @@
         <v>-3.84</v>
       </c>
       <c r="I296" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J296" t="n">
         <v>80.94</v>
@@ -22943,7 +22943,7 @@
         <v>-11.21</v>
       </c>
       <c r="I297" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J297" t="n">
         <v>84.38</v>
@@ -23018,7 +23018,7 @@
         <v>7.67</v>
       </c>
       <c r="I298" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J298" t="n">
         <v>87.88</v>
@@ -23093,7 +23093,7 @@
         <v>7.64</v>
       </c>
       <c r="I299" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J299" t="n">
         <v>91.62</v>
@@ -23168,7 +23168,7 @@
         <v>2.69</v>
       </c>
       <c r="I300" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J300" t="n">
         <v>95.5</v>
@@ -23243,7 +23243,7 @@
         <v>-2.18</v>
       </c>
       <c r="I301" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J301" t="n">
         <v>99.13</v>
@@ -23318,7 +23318,7 @@
         <v>13.02</v>
       </c>
       <c r="I302" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J302" t="n">
         <v>103.51</v>
@@ -23393,7 +23393,7 @@
         <v>15.04</v>
       </c>
       <c r="I303" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J303" t="n">
         <v>108.42</v>
@@ -23468,7 +23468,7 @@
         <v>-8.289999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J304" t="n">
         <v>112.43</v>
@@ -23543,7 +23543,7 @@
         <v>16.33</v>
       </c>
       <c r="I305" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J305" t="n">
         <v>117.45</v>
@@ -23618,7 +23618,7 @@
         <v>7.62</v>
       </c>
       <c r="I306" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J306" t="n">
         <v>122.94</v>
@@ -23693,7 +23693,7 @@
         <v>-9.4</v>
       </c>
       <c r="I307" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J307" t="n">
         <v>127.3</v>
@@ -23768,7 +23768,7 @@
         <v>6.79</v>
       </c>
       <c r="I308" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J308" t="n">
         <v>132.21</v>
@@ -23843,7 +23843,7 @@
         <v>1.06</v>
       </c>
       <c r="I309" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J309" t="n">
         <v>137.1</v>
@@ -23918,7 +23918,7 @@
         <v>-11.82</v>
       </c>
       <c r="I310" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J310" t="n">
         <v>140.57</v>
@@ -23993,7 +23993,7 @@
         <v>-7.57</v>
       </c>
       <c r="I311" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J311" t="n">
         <v>143.36</v>
@@ -24068,7 +24068,7 @@
         <v>0.09</v>
       </c>
       <c r="I312" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J312" t="n">
         <v>146.05</v>
@@ -24143,7 +24143,7 @@
         <v>14.03</v>
       </c>
       <c r="I313" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J313" t="n">
         <v>149.42</v>
@@ -24218,7 +24218,7 @@
         <v>2.99</v>
       </c>
       <c r="I314" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J314" t="n">
         <v>152.7</v>
@@ -24293,7 +24293,7 @@
         <v>6.83</v>
       </c>
       <c r="I315" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J315" t="n">
         <v>155.81</v>
@@ -24368,7 +24368,7 @@
         <v>18.48</v>
       </c>
       <c r="I316" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J316" t="n">
         <v>160.93</v>
@@ -24443,7 +24443,7 @@
         <v>-3.46</v>
       </c>
       <c r="I317" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J317" t="n">
         <v>166.34</v>
@@ -24518,7 +24518,7 @@
         <v>3.05</v>
       </c>
       <c r="I318" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J318" t="n">
         <v>171.67</v>
@@ -24593,7 +24593,7 @@
         <v>-0.13</v>
       </c>
       <c r="I319" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J319" t="n">
         <v>176.54</v>
@@ -24668,7 +24668,7 @@
         <v>1.2</v>
       </c>
       <c r="I320" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J320" t="n">
         <v>181.37</v>
@@ -24743,7 +24743,7 @@
         <v>17.31</v>
       </c>
       <c r="I321" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J321" t="n">
         <v>188.3</v>
@@ -24818,7 +24818,7 @@
         <v>5.34</v>
       </c>
       <c r="I322" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J322" t="n">
         <v>195.12</v>
@@ -24893,7 +24893,7 @@
         <v>-6.36</v>
       </c>
       <c r="I323" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J323" t="n">
         <v>199.96</v>
@@ -24968,7 +24968,7 @@
         <v>-30.51</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>201.48</v>
@@ -25047,7 +25047,7 @@
         <v>15.83</v>
       </c>
       <c r="I325" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J325" t="n">
         <v>203.2</v>
@@ -25122,7 +25122,7 @@
         <v>-4.61</v>
       </c>
       <c r="I326" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J326" t="n">
         <v>203.76</v>
@@ -25201,7 +25201,7 @@
         <v>-10.43</v>
       </c>
       <c r="I327" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J327" t="n">
         <v>204.17</v>
@@ -25276,7 +25276,7 @@
         <v>23.99</v>
       </c>
       <c r="I328" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J328" t="n">
         <v>206.15</v>
@@ -25351,7 +25351,7 @@
         <v>4.78</v>
       </c>
       <c r="I329" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J329" t="n">
         <v>208.58</v>
@@ -25426,7 +25426,7 @@
         <v>16.11</v>
       </c>
       <c r="I330" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J330" t="n">
         <v>213.99</v>
@@ -25501,7 +25501,7 @@
         <v>-16.99</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>217.71</v>
@@ -25576,7 +25576,7 @@
         <v>3.39</v>
       </c>
       <c r="I332" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J332" t="n">
         <v>221.81</v>
@@ -25651,7 +25651,7 @@
         <v>19.43</v>
       </c>
       <c r="I333" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J333" t="n">
         <v>227.11</v>
@@ -25726,7 +25726,7 @@
         <v>7.69</v>
       </c>
       <c r="I334" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J334" t="n">
         <v>233.22</v>
@@ -25801,7 +25801,7 @@
         <v>-23.06</v>
       </c>
       <c r="I335" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J335" s="4" t="n">
         <v>235.26</v>
@@ -25880,7 +25880,7 @@
         <v>-0.8</v>
       </c>
       <c r="I336" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J336" t="n">
         <v>235.45</v>
@@ -25955,7 +25955,7 @@
         <v>10.03</v>
       </c>
       <c r="I337" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J337" t="n">
         <v>237.18</v>
@@ -26030,7 +26030,7 @@
         <v>-14.65</v>
       </c>
       <c r="I338" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>236.73</v>
@@ -26109,7 +26109,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I339" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J339" t="n">
         <v>237.34</v>
@@ -26184,7 +26184,7 @@
         <v>12.76</v>
       </c>
       <c r="I340" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J340" t="n">
         <v>239.32</v>
@@ -26259,7 +26259,7 @@
         <v>-18.43</v>
       </c>
       <c r="I341" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>236.89</v>
@@ -26338,7 +26338,7 @@
         <v>-16.59</v>
       </c>
       <c r="I342" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J342" s="4" t="n">
         <v>231.94</v>
@@ -26413,7 +26413,7 @@
         <v>7.26</v>
       </c>
       <c r="I343" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J343" t="n">
         <v>228.54</v>
@@ -26488,7 +26488,7 @@
         <v>-15.09</v>
       </c>
       <c r="I344" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>227.67</v>
@@ -26567,7 +26567,7 @@
         <v>5.78</v>
       </c>
       <c r="I345" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J345" t="n">
         <v>225.84</v>
@@ -26642,7 +26642,7 @@
         <v>10.08</v>
       </c>
       <c r="I346" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J346" t="n">
         <v>225.38</v>
@@ -26717,7 +26717,7 @@
         <v>-0.1</v>
       </c>
       <c r="I347" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J347" t="n">
         <v>225.96</v>
@@ -26792,7 +26792,7 @@
         <v>-13.99</v>
       </c>
       <c r="I348" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J348" t="n">
         <v>223.03</v>
@@ -26871,7 +26871,7 @@
         <v>6.83</v>
       </c>
       <c r="I349" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J349" t="n">
         <v>220.13</v>
@@ -26946,7 +26946,7 @@
         <v>-6.29</v>
       </c>
       <c r="I350" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J350" t="n">
         <v>214.79</v>
@@ -27021,7 +27021,7 @@
         <v>-13.93</v>
       </c>
       <c r="I351" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J351" t="n">
         <v>210.61</v>
@@ -27096,7 +27096,7 @@
         <v>-4.92</v>
       </c>
       <c r="I352" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J352" t="n">
         <v>205.69</v>
@@ -27171,7 +27171,7 @@
         <v>0.99</v>
       </c>
       <c r="I353" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J353" t="n">
         <v>198.57</v>
@@ -27246,7 +27246,7 @@
         <v>15.89</v>
       </c>
       <c r="I354" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J354" t="n">
         <v>191.46</v>
@@ -27321,7 +27321,7 @@
         <v>1.54</v>
       </c>
       <c r="I355" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J355" t="n">
         <v>187.94</v>
@@ -27396,7 +27396,7 @@
         <v>-2.16</v>
       </c>
       <c r="I356" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J356" t="n">
         <v>184.34</v>
@@ -27471,7 +27471,7 @@
         <v>-13.14</v>
       </c>
       <c r="I357" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J357" t="n">
         <v>178.56</v>
@@ -27546,7 +27546,7 @@
         <v>-6.33</v>
       </c>
       <c r="I358" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J358" t="n">
         <v>174.19</v>
@@ -27625,7 +27625,7 @@
         <v>-14.52</v>
       </c>
       <c r="I359" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J359" s="4" t="n">
         <v>167.84</v>
@@ -27700,7 +27700,7 @@
         <v>-16.02</v>
       </c>
       <c r="I360" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J360" s="4" t="n">
         <v>159.11</v>
@@ -27779,7 +27779,7 @@
         <v>24.7</v>
       </c>
       <c r="I361" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J361" t="n">
         <v>153.97</v>
@@ -27854,7 +27854,7 @@
         <v>0</v>
       </c>
       <c r="I362" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J362" t="n">
         <v>150.64</v>
@@ -27929,7 +27929,7 @@
         <v>1.74</v>
       </c>
       <c r="I363" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J363" t="n">
         <v>146.74</v>
@@ -28004,7 +28004,7 @@
         <v>19.87</v>
       </c>
       <c r="I364" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J364" t="n">
         <v>145.48</v>
@@ -28079,7 +28079,7 @@
         <v>-5.6</v>
       </c>
       <c r="I365" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J365" t="n">
         <v>143.34</v>
@@ -28158,7 +28158,7 @@
         <v>0.2</v>
       </c>
       <c r="I366" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J366" t="n">
         <v>140.34</v>
@@ -28233,7 +28233,7 @@
         <v>5.99</v>
       </c>
       <c r="I367" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J367" t="n">
         <v>137.74</v>
@@ -28308,7 +28308,7 @@
         <v>-7.31</v>
       </c>
       <c r="I368" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J368" t="n">
         <v>135.97</v>
@@ -28387,7 +28387,7 @@
         <v>2.31</v>
       </c>
       <c r="I369" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J369" t="n">
         <v>133.79</v>
@@ -28462,7 +28462,7 @@
         <v>6.89</v>
       </c>
       <c r="I370" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J370" t="n">
         <v>132.62</v>
@@ -28537,7 +28537,7 @@
         <v>2.25</v>
       </c>
       <c r="I371" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J371" t="n">
         <v>132.76</v>
@@ -28612,7 +28612,7 @@
         <v>-0.28</v>
       </c>
       <c r="I372" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J372" t="n">
         <v>133.24</v>
@@ -28687,7 +28687,7 @@
         <v>4.54</v>
       </c>
       <c r="I373" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J373" t="n">
         <v>133.97</v>
@@ -28762,7 +28762,7 @@
         <v>-14.8</v>
       </c>
       <c r="I374" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J374" s="4" t="n">
         <v>132.5</v>
@@ -28841,7 +28841,7 @@
         <v>-6.48</v>
       </c>
       <c r="I375" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J375" t="n">
         <v>130.49</v>
@@ -28916,7 +28916,7 @@
         <v>1.22</v>
       </c>
       <c r="I376" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J376" t="n">
         <v>128.73</v>
@@ -28991,7 +28991,7 @@
         <v>-1.32</v>
       </c>
       <c r="I377" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J377" t="n">
         <v>127.92</v>
@@ -29066,7 +29066,7 @@
         <v>-7.82</v>
       </c>
       <c r="I378" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J378" t="n">
         <v>127.07</v>
@@ -29141,7 +29141,7 @@
         <v>4.05</v>
       </c>
       <c r="I379" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J379" t="n">
         <v>127.37</v>
@@ -29216,7 +29216,7 @@
         <v>0.8</v>
       </c>
       <c r="I380" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J380" t="n">
         <v>128.6</v>
@@ -29291,7 +29291,7 @@
         <v>5.54</v>
       </c>
       <c r="I381" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J381" t="n">
         <v>129.02</v>
@@ -29366,7 +29366,7 @@
         <v>-9.51</v>
       </c>
       <c r="I382" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J382" t="n">
         <v>128.85</v>
@@ -29441,7 +29441,7 @@
         <v>1.3</v>
       </c>
       <c r="I383" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J383" t="n">
         <v>128.66</v>
@@ -29516,7 +29516,7 @@
         <v>-6.1</v>
       </c>
       <c r="I384" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J384" t="n">
         <v>126.96</v>
@@ -29595,7 +29595,7 @@
         <v>0.42</v>
       </c>
       <c r="I385" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J385" t="n">
         <v>125.67</v>
@@ -29674,7 +29674,7 @@
         <v>0.37</v>
       </c>
       <c r="I386" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J386" t="n">
         <v>124.39</v>
@@ -29753,7 +29753,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="I387" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J387" t="n">
         <v>123.25</v>
@@ -29828,7 +29828,7 @@
         <v>5.11</v>
       </c>
       <c r="I388" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J388" t="n">
         <v>122.91</v>
@@ -29903,7 +29903,7 @@
         <v>2.11</v>
       </c>
       <c r="I389" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J389" t="n">
         <v>122.55</v>
@@ -29978,7 +29978,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="I390" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J390" t="n">
         <v>121.23</v>
@@ -30057,7 +30057,7 @@
         <v>5.24</v>
       </c>
       <c r="I391" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J391" t="n">
         <v>120.06</v>
@@ -30132,7 +30132,7 @@
         <v>-16.99</v>
       </c>
       <c r="I392" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J392" s="4" t="n">
         <v>117.87</v>
@@ -30211,7 +30211,7 @@
         <v>1.18</v>
       </c>
       <c r="I393" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J393" t="n">
         <v>115.41</v>
@@ -30286,7 +30286,7 @@
         <v>1.61</v>
       </c>
       <c r="I394" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J394" t="n">
         <v>114.15</v>
@@ -30361,7 +30361,7 @@
         <v>10.43</v>
       </c>
       <c r="I395" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J395" t="n">
         <v>113.86</v>
@@ -30436,7 +30436,7 @@
         <v>7.71</v>
       </c>
       <c r="I396" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J396" t="n">
         <v>113.93</v>
@@ -30511,7 +30511,7 @@
         <v>14.77</v>
       </c>
       <c r="I397" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J397" t="n">
         <v>115</v>
@@ -30586,7 +30586,7 @@
         <v>7.13</v>
       </c>
       <c r="I398" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J398" t="n">
         <v>117.04</v>
@@ -30661,7 +30661,7 @@
         <v>-3.75</v>
       </c>
       <c r="I399" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J399" t="n">
         <v>118.57</v>
@@ -30736,7 +30736,7 @@
         <v>0.05</v>
       </c>
       <c r="I400" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J400" t="n">
         <v>120.06</v>
@@ -30811,7 +30811,7 @@
         <v>3.5</v>
       </c>
       <c r="I401" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J401" t="n">
         <v>121.49</v>
@@ -30886,7 +30886,7 @@
         <v>-6.05</v>
       </c>
       <c r="I402" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J402" t="n">
         <v>123.04</v>
@@ -30961,7 +30961,7 @@
         <v>3.31</v>
       </c>
       <c r="I403" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J403" t="n">
         <v>124.75</v>
@@ -31036,7 +31036,7 @@
         <v>0.59</v>
       </c>
       <c r="I404" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J404" t="n">
         <v>126.85</v>
@@ -31111,7 +31111,7 @@
         <v>3.94</v>
       </c>
       <c r="I405" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J405" t="n">
         <v>129.22</v>
@@ -31186,7 +31186,7 @@
         <v>6.52</v>
       </c>
       <c r="I406" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J406" t="n">
         <v>132.08</v>
@@ -31261,7 +31261,7 @@
         <v>0.34</v>
       </c>
       <c r="I407" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J407" t="n">
         <v>134.43</v>
@@ -31336,7 +31336,7 @@
         <v>-0.01</v>
       </c>
       <c r="I408" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J408" t="n">
         <v>136.48</v>
@@ -31411,7 +31411,7 @@
         <v>-3.26</v>
       </c>
       <c r="I409" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J409" t="n">
         <v>138.14</v>
@@ -31490,7 +31490,7 @@
         <v>-10.31</v>
       </c>
       <c r="I410" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J410" t="n">
         <v>139.48</v>
@@ -31565,7 +31565,7 @@
         <v>-1.94</v>
       </c>
       <c r="I411" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J411" t="n">
         <v>140.38</v>
@@ -31644,7 +31644,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="I412" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J412" t="n">
         <v>141.75</v>
@@ -31723,7 +31723,7 @@
         <v>-0.65</v>
       </c>
       <c r="I413" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J413" t="n">
         <v>143.01</v>
@@ -31798,7 +31798,7 @@
         <v>-13.35</v>
       </c>
       <c r="I414" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J414" t="n">
         <v>143.35</v>
@@ -31858,44 +31858,44 @@
         <v>98.34999999999999</v>
       </c>
       <c r="D415" t="n">
-        <v>102.45</v>
+        <v>104.95</v>
       </c>
       <c r="E415" t="n">
-        <v>95.23999999999999</v>
+        <v>95.23</v>
       </c>
       <c r="F415" t="n">
-        <v>97.70999999999999</v>
+        <v>102.99</v>
       </c>
       <c r="G415" t="n">
-        <v>56816997</v>
+        <v>113411825</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-11.61</v>
+        <v>-6.83</v>
       </c>
       <c r="I415" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J415" t="n">
-        <v>142.5</v>
+        <v>142.76</v>
       </c>
       <c r="K415" t="n">
-        <v>128.95</v>
+        <v>129.04</v>
       </c>
       <c r="L415" t="n">
-        <v>160.98</v>
+        <v>161.02</v>
       </c>
       <c r="M415" t="n">
-        <v>121.73</v>
+        <v>121.76</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>22.5</v>
+        <v>23.78</v>
       </c>
       <c r="O415" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>extreme fear</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
@@ -31909,13 +31909,13 @@
         </is>
       </c>
       <c r="S415" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31792,7 +31792,7 @@
         <v>110.54</v>
       </c>
       <c r="G414" t="n">
-        <v>102288200</v>
+        <v>107400700</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-13.35</v>
@@ -31858,40 +31858,40 @@
         <v>98.34999999999999</v>
       </c>
       <c r="D415" t="n">
-        <v>104.95</v>
+        <v>108.8</v>
       </c>
       <c r="E415" t="n">
         <v>95.23</v>
       </c>
       <c r="F415" t="n">
-        <v>102.99</v>
+        <v>107.35</v>
       </c>
       <c r="G415" t="n">
-        <v>113411825</v>
+        <v>136485535</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-6.83</v>
+        <v>-2.89</v>
       </c>
       <c r="I415" t="n">
         <v>14.2</v>
       </c>
       <c r="J415" t="n">
-        <v>142.76</v>
+        <v>142.98</v>
       </c>
       <c r="K415" t="n">
-        <v>129.04</v>
+        <v>129.11</v>
       </c>
       <c r="L415" t="n">
-        <v>161.02</v>
+        <v>161.06</v>
       </c>
       <c r="M415" t="n">
-        <v>121.76</v>
+        <v>121.78</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>23.78</v>
+        <v>24.96</v>
       </c>
       <c r="O415" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31909,16 +31909,18 @@
         </is>
       </c>
       <c r="S415" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="1" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31854,41 +31854,25 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>98.34999999999999</v>
-      </c>
-      <c r="D415" t="n">
-        <v>108.8</v>
-      </c>
-      <c r="E415" t="n">
-        <v>95.23</v>
-      </c>
-      <c r="F415" t="n">
-        <v>107.35</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
         <v>136485535</v>
       </c>
-      <c r="H415" s="1" t="n">
-        <v>-2.89</v>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>14.2</v>
       </c>
-      <c r="J415" t="n">
-        <v>142.98</v>
-      </c>
-      <c r="K415" t="n">
-        <v>129.11</v>
-      </c>
-      <c r="L415" t="n">
-        <v>161.06</v>
-      </c>
-      <c r="M415" t="n">
-        <v>121.78</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" s="3" t="n">
-        <v>24.96</v>
+        <v>25.9</v>
       </c>
       <c r="O415" t="n">
         <v>32</v>
@@ -31903,11 +31887,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
+      <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
         <v>5.09</v>
       </c>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31854,28 +31854,44 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="D415" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="E415" t="n">
+        <v>95.23</v>
+      </c>
+      <c r="F415" t="n">
+        <v>107.35</v>
+      </c>
       <c r="G415" t="n">
-        <v>136485535</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>138394200</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-2.89</v>
       </c>
       <c r="I415" t="n">
         <v>14.2</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>142.98</v>
+      </c>
+      <c r="K415" t="n">
+        <v>129.11</v>
+      </c>
+      <c r="L415" t="n">
+        <v>161.06</v>
+      </c>
+      <c r="M415" t="n">
+        <v>121.78</v>
+      </c>
       <c r="N415" s="3" t="n">
-        <v>25.9</v>
+        <v>24.96</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31887,7 +31903,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S415" t="n">
         <v>5.09</v>
       </c>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31891,7 +31891,7 @@
         <v>24.96</v>
       </c>
       <c r="O415" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31891,7 +31891,7 @@
         <v>24.96</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31921,6 +31921,83 @@
       <c r="W415" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="D416" t="n">
+        <v>103.92</v>
+      </c>
+      <c r="E416" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="F416" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G416" t="n">
+        <v>45975761</v>
+      </c>
+      <c r="H416" s="1" t="n">
+        <v>-6.66</v>
+      </c>
+      <c r="I416" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J416" t="n">
+        <v>141.81</v>
+      </c>
+      <c r="K416" t="n">
+        <v>128.16</v>
+      </c>
+      <c r="L416" t="n">
+        <v>160.86</v>
+      </c>
+      <c r="M416" t="n">
+        <v>122.07</v>
+      </c>
+      <c r="N416" s="3" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="O416" t="n">
+        <v>30</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S416" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31940,41 +31940,41 @@
         <v>103.92</v>
       </c>
       <c r="E416" t="n">
-        <v>98.55</v>
+        <v>93.44</v>
       </c>
       <c r="F416" t="n">
-        <v>100.2</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="G416" t="n">
-        <v>45975761</v>
+        <v>95229341</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-6.66</v>
+        <v>-10.35</v>
       </c>
       <c r="I416" t="n">
         <v>14.2</v>
       </c>
       <c r="J416" t="n">
-        <v>141.81</v>
+        <v>141.61</v>
       </c>
       <c r="K416" t="n">
-        <v>128.16</v>
+        <v>128.09</v>
       </c>
       <c r="L416" t="n">
-        <v>160.86</v>
+        <v>160.83</v>
       </c>
       <c r="M416" t="n">
-        <v>122.07</v>
+        <v>122.05</v>
       </c>
       <c r="N416" s="3" t="n">
-        <v>25.54</v>
+        <v>24.42</v>
       </c>
       <c r="O416" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q416" t="inlineStr">
@@ -31988,13 +31988,13 @@
         </is>
       </c>
       <c r="S416" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>15.9</v>
+        <v>21.3</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>8.1</v>
+        <v>22</v>
       </c>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="2" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -608,7 +608,7 @@
         <v>-7.1</v>
       </c>
       <c r="I2" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J2" t="n">
         <v>27.4</v>
@@ -687,7 +687,7 @@
         <v>-6.32</v>
       </c>
       <c r="I3" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J3" t="n">
         <v>27.4</v>
@@ -762,7 +762,7 @@
         <v>4.86</v>
       </c>
       <c r="I4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J4" t="n">
         <v>27.44</v>
@@ -837,7 +837,7 @@
         <v>-17.28</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>27.25</v>
@@ -912,7 +912,7 @@
         <v>4.54</v>
       </c>
       <c r="I6" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J6" t="n">
         <v>27.03</v>
@@ -987,7 +987,7 @@
         <v>-9.789999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J7" t="n">
         <v>26.7</v>
@@ -1062,7 +1062,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J8" t="n">
         <v>26.46</v>
@@ -1137,7 +1137,7 @@
         <v>6.29</v>
       </c>
       <c r="I9" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J9" t="n">
         <v>26.24</v>
@@ -1212,7 +1212,7 @@
         <v>-12.39</v>
       </c>
       <c r="I10" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J10" t="n">
         <v>25.82</v>
@@ -1291,7 +1291,7 @@
         <v>8.59</v>
       </c>
       <c r="I11" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J11" t="n">
         <v>25.49</v>
@@ -1366,7 +1366,7 @@
         <v>-13.84</v>
       </c>
       <c r="I12" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J12" t="n">
         <v>25.07</v>
@@ -1449,7 +1449,7 @@
         <v>-3.19</v>
       </c>
       <c r="I13" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J13" t="n">
         <v>24.58</v>
@@ -1532,7 +1532,7 @@
         <v>5.09</v>
       </c>
       <c r="I14" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J14" t="n">
         <v>24.13</v>
@@ -1611,7 +1611,7 @@
         <v>-1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J15" t="n">
         <v>23.66</v>
@@ -1690,7 +1690,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J16" t="n">
         <v>23.23</v>
@@ -1765,7 +1765,7 @@
         <v>4.98</v>
       </c>
       <c r="I17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J17" t="n">
         <v>22.84</v>
@@ -1840,7 +1840,7 @@
         <v>-4.12</v>
       </c>
       <c r="I18" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J18" t="n">
         <v>22.34</v>
@@ -1915,7 +1915,7 @@
         <v>2.22</v>
       </c>
       <c r="I19" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J19" t="n">
         <v>21.79</v>
@@ -1990,7 +1990,7 @@
         <v>-2.17</v>
       </c>
       <c r="I20" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J20" t="n">
         <v>21.21</v>
@@ -2065,7 +2065,7 @@
         <v>-3.28</v>
       </c>
       <c r="I21" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J21" t="n">
         <v>20.74</v>
@@ -2140,7 +2140,7 @@
         <v>8.93</v>
       </c>
       <c r="I22" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J22" t="n">
         <v>20.45</v>
@@ -2215,7 +2215,7 @@
         <v>-1.82</v>
       </c>
       <c r="I23" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J23" t="n">
         <v>20.23</v>
@@ -2290,7 +2290,7 @@
         <v>-8.6</v>
       </c>
       <c r="I24" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J24" t="n">
         <v>19.86</v>
@@ -2369,7 +2369,7 @@
         <v>-5.45</v>
       </c>
       <c r="I25" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J25" t="n">
         <v>19.66</v>
@@ -2444,7 +2444,7 @@
         <v>-9.779999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J26" t="n">
         <v>19.33</v>
@@ -2519,7 +2519,7 @@
         <v>-0.5</v>
       </c>
       <c r="I27" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J27" t="n">
         <v>19.11</v>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J28" t="n">
         <v>18.88</v>
@@ -2669,7 +2669,7 @@
         <v>1.95</v>
       </c>
       <c r="I29" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J29" t="n">
         <v>18.6</v>
@@ -2744,7 +2744,7 @@
         <v>-29.83</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>18.21</v>
@@ -2827,7 +2827,7 @@
         <v>-23.5</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>17.61</v>
@@ -2910,7 +2910,7 @@
         <v>4.83</v>
       </c>
       <c r="I32" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J32" t="n">
         <v>17.17</v>
@@ -2993,7 +2993,7 @@
         <v>-9.77</v>
       </c>
       <c r="I33" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J33" t="n">
         <v>16.72</v>
@@ -3076,7 +3076,7 @@
         <v>54.74</v>
       </c>
       <c r="I34" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J34" t="n">
         <v>16.45</v>
@@ -3155,7 +3155,7 @@
         <v>-24.61</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>16.03</v>
@@ -3238,7 +3238,7 @@
         <v>6.26</v>
       </c>
       <c r="I36" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J36" t="n">
         <v>15.56</v>
@@ -3321,7 +3321,7 @@
         <v>2.36</v>
       </c>
       <c r="I37" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J37" t="n">
         <v>15.04</v>
@@ -3400,7 +3400,7 @@
         <v>1.25</v>
       </c>
       <c r="I38" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J38" t="n">
         <v>14.58</v>
@@ -3475,7 +3475,7 @@
         <v>-11.93</v>
       </c>
       <c r="I39" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J39" t="n">
         <v>14.04</v>
@@ -3558,7 +3558,7 @@
         <v>-1.51</v>
       </c>
       <c r="I40" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J40" t="n">
         <v>13.5</v>
@@ -3637,7 +3637,7 @@
         <v>-5.35</v>
       </c>
       <c r="I41" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J41" t="n">
         <v>12.98</v>
@@ -3712,7 +3712,7 @@
         <v>5.42</v>
       </c>
       <c r="I42" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J42" t="n">
         <v>12.4</v>
@@ -3787,7 +3787,7 @@
         <v>12.14</v>
       </c>
       <c r="I43" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J43" t="n">
         <v>11.89</v>
@@ -3866,7 +3866,7 @@
         <v>16.59</v>
       </c>
       <c r="I44" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J44" t="n">
         <v>11.55</v>
@@ -3941,7 +3941,7 @@
         <v>2.85</v>
       </c>
       <c r="I45" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J45" t="n">
         <v>11.28</v>
@@ -4016,7 +4016,7 @@
         <v>-0.41</v>
       </c>
       <c r="I46" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J46" t="n">
         <v>11.09</v>
@@ -4091,7 +4091,7 @@
         <v>-3.51</v>
       </c>
       <c r="I47" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J47" t="n">
         <v>10.89</v>
@@ -4166,7 +4166,7 @@
         <v>2.54</v>
       </c>
       <c r="I48" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J48" t="n">
         <v>10.7</v>
@@ -4241,7 +4241,7 @@
         <v>-0.5</v>
       </c>
       <c r="I49" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J49" t="n">
         <v>10.49</v>
@@ -4316,7 +4316,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J50" t="n">
         <v>10.59</v>
@@ -4391,7 +4391,7 @@
         <v>-1.81</v>
       </c>
       <c r="I51" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J51" t="n">
         <v>10.8</v>
@@ -4466,7 +4466,7 @@
         <v>-3.15</v>
       </c>
       <c r="I52" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J52" t="n">
         <v>10.98</v>
@@ -4541,7 +4541,7 @@
         <v>5.08</v>
       </c>
       <c r="I53" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J53" t="n">
         <v>11.23</v>
@@ -4616,7 +4616,7 @@
         <v>2.8</v>
       </c>
       <c r="I54" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J54" t="n">
         <v>11.27</v>
@@ -4691,7 +4691,7 @@
         <v>3.31</v>
       </c>
       <c r="I55" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J55" t="n">
         <v>11.49</v>
@@ -4766,7 +4766,7 @@
         <v>21.42</v>
       </c>
       <c r="I56" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J56" t="n">
         <v>11.84</v>
@@ -4841,7 +4841,7 @@
         <v>8.56</v>
       </c>
       <c r="I57" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J57" t="n">
         <v>12.24</v>
@@ -4916,7 +4916,7 @@
         <v>1.3</v>
       </c>
       <c r="I58" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J58" t="n">
         <v>12.65</v>
@@ -4991,7 +4991,7 @@
         <v>-1.97</v>
       </c>
       <c r="I59" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J59" t="n">
         <v>13.11</v>
@@ -5066,7 +5066,7 @@
         <v>-0.44</v>
       </c>
       <c r="I60" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J60" t="n">
         <v>13.56</v>
@@ -5141,7 +5141,7 @@
         <v>-1.75</v>
       </c>
       <c r="I61" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J61" t="n">
         <v>14.03</v>
@@ -5216,7 +5216,7 @@
         <v>-0.5</v>
       </c>
       <c r="I62" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J62" t="n">
         <v>14.47</v>
@@ -5291,7 +5291,7 @@
         <v>-5.42</v>
       </c>
       <c r="I63" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J63" t="n">
         <v>14.8</v>
@@ -5366,7 +5366,7 @@
         <v>-2.89</v>
       </c>
       <c r="I64" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J64" t="n">
         <v>15.03</v>
@@ -5441,7 +5441,7 @@
         <v>-4.68</v>
       </c>
       <c r="I65" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J65" t="n">
         <v>15.19</v>
@@ -5516,7 +5516,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J66" t="n">
         <v>15.44</v>
@@ -5591,7 +5591,7 @@
         <v>-1.45</v>
       </c>
       <c r="I67" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J67" t="n">
         <v>15.7</v>
@@ -5666,7 +5666,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J68" t="n">
         <v>15.95</v>
@@ -5741,7 +5741,7 @@
         <v>-6.01</v>
       </c>
       <c r="I69" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J69" t="n">
         <v>16.16</v>
@@ -5820,7 +5820,7 @@
         <v>4.53</v>
       </c>
       <c r="I70" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J70" t="n">
         <v>16.33</v>
@@ -5895,7 +5895,7 @@
         <v>8.32</v>
       </c>
       <c r="I71" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J71" t="n">
         <v>16.6</v>
@@ -5970,7 +5970,7 @@
         <v>4.28</v>
       </c>
       <c r="I72" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J72" t="n">
         <v>16.92</v>
@@ -6045,7 +6045,7 @@
         <v>-1.47</v>
       </c>
       <c r="I73" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J73" t="n">
         <v>17.19</v>
@@ -6120,7 +6120,7 @@
         <v>1.98</v>
       </c>
       <c r="I74" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J74" t="n">
         <v>17.47</v>
@@ -6195,7 +6195,7 @@
         <v>7.33</v>
       </c>
       <c r="I75" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J75" t="n">
         <v>17.79</v>
@@ -6270,7 +6270,7 @@
         <v>6.34</v>
       </c>
       <c r="I76" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J76" t="n">
         <v>18.03</v>
@@ -6345,7 +6345,7 @@
         <v>-1.15</v>
       </c>
       <c r="I77" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J77" t="n">
         <v>18.18</v>
@@ -6420,7 +6420,7 @@
         <v>0.23</v>
       </c>
       <c r="I78" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J78" t="n">
         <v>18.32</v>
@@ -6495,7 +6495,7 @@
         <v>-7.59</v>
       </c>
       <c r="I79" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J79" t="n">
         <v>18.4</v>
@@ -6574,7 +6574,7 @@
         <v>9.27</v>
       </c>
       <c r="I80" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J80" t="n">
         <v>18.57</v>
@@ -6649,7 +6649,7 @@
         <v>-2.2</v>
       </c>
       <c r="I81" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J81" t="n">
         <v>18.74</v>
@@ -6724,7 +6724,7 @@
         <v>0.89</v>
       </c>
       <c r="I82" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J82" t="n">
         <v>18.92</v>
@@ -6799,7 +6799,7 @@
         <v>-1.86</v>
       </c>
       <c r="I83" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J83" t="n">
         <v>19.13</v>
@@ -6874,7 +6874,7 @@
         <v>1.75</v>
       </c>
       <c r="I84" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J84" t="n">
         <v>19.38</v>
@@ -6949,7 +6949,7 @@
         <v>11.35</v>
       </c>
       <c r="I85" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J85" t="n">
         <v>19.8</v>
@@ -7024,7 +7024,7 @@
         <v>2.63</v>
       </c>
       <c r="I86" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J86" t="n">
         <v>20.16</v>
@@ -7099,7 +7099,7 @@
         <v>2.52</v>
       </c>
       <c r="I87" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J87" t="n">
         <v>20.57</v>
@@ -7174,7 +7174,7 @@
         <v>-0.36</v>
       </c>
       <c r="I88" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J88" t="n">
         <v>20.97</v>
@@ -7249,7 +7249,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J89" t="n">
         <v>21.42</v>
@@ -7324,7 +7324,7 @@
         <v>-1.59</v>
       </c>
       <c r="I90" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J90" t="n">
         <v>21.81</v>
@@ -7399,7 +7399,7 @@
         <v>5.43</v>
       </c>
       <c r="I91" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J91" t="n">
         <v>22.2</v>
@@ -7474,7 +7474,7 @@
         <v>1.46</v>
       </c>
       <c r="I92" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J92" t="n">
         <v>22.57</v>
@@ -7549,7 +7549,7 @@
         <v>-5.53</v>
       </c>
       <c r="I93" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J93" t="n">
         <v>22.89</v>
@@ -7624,7 +7624,7 @@
         <v>5.61</v>
       </c>
       <c r="I94" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J94" t="n">
         <v>23.25</v>
@@ -7699,7 +7699,7 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J95" t="n">
         <v>23.55</v>
@@ -7774,7 +7774,7 @@
         <v>2.7</v>
       </c>
       <c r="I96" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J96" t="n">
         <v>23.83</v>
@@ -7849,7 +7849,7 @@
         <v>-0.29</v>
       </c>
       <c r="I97" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J97" t="n">
         <v>24.12</v>
@@ -7924,7 +7924,7 @@
         <v>-2.9</v>
       </c>
       <c r="I98" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J98" t="n">
         <v>24.36</v>
@@ -7999,7 +7999,7 @@
         <v>2.98</v>
       </c>
       <c r="I99" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J99" t="n">
         <v>24.72</v>
@@ -8074,7 +8074,7 @@
         <v>-0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J100" t="n">
         <v>24.98</v>
@@ -8149,7 +8149,7 @@
         <v>1.07</v>
       </c>
       <c r="I101" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J101" t="n">
         <v>25.28</v>
@@ -8224,7 +8224,7 @@
         <v>0.04</v>
       </c>
       <c r="I102" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J102" t="n">
         <v>25.57</v>
@@ -8299,7 +8299,7 @@
         <v>0.62</v>
       </c>
       <c r="I103" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J103" t="n">
         <v>25.89</v>
@@ -8374,7 +8374,7 @@
         <v>-4.26</v>
       </c>
       <c r="I104" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J104" t="n">
         <v>26.13</v>
@@ -8449,7 +8449,7 @@
         <v>-2.05</v>
       </c>
       <c r="I105" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J105" t="n">
         <v>26.22</v>
@@ -8528,7 +8528,7 @@
         <v>-0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J106" t="n">
         <v>26.27</v>
@@ -8603,7 +8603,7 @@
         <v>-0.08</v>
       </c>
       <c r="I107" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J107" t="n">
         <v>26.29</v>
@@ -8678,7 +8678,7 @@
         <v>4.96</v>
       </c>
       <c r="I108" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J108" t="n">
         <v>26.38</v>
@@ -8753,7 +8753,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J109" t="n">
         <v>26.48</v>
@@ -8828,7 +8828,7 @@
         <v>2.15</v>
       </c>
       <c r="I110" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J110" t="n">
         <v>26.62</v>
@@ -8903,7 +8903,7 @@
         <v>-9.5</v>
       </c>
       <c r="I111" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J111" t="n">
         <v>26.57</v>
@@ -8982,7 +8982,7 @@
         <v>-3.61</v>
       </c>
       <c r="I112" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J112" t="n">
         <v>26.45</v>
@@ -9057,7 +9057,7 @@
         <v>3.82</v>
       </c>
       <c r="I113" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J113" t="n">
         <v>26.45</v>
@@ -9132,7 +9132,7 @@
         <v>-1.92</v>
       </c>
       <c r="I114" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J114" t="n">
         <v>26.36</v>
@@ -9207,7 +9207,7 @@
         <v>-2.16</v>
       </c>
       <c r="I115" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J115" t="n">
         <v>26.23</v>
@@ -9282,7 +9282,7 @@
         <v>4.21</v>
       </c>
       <c r="I116" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J116" t="n">
         <v>26.11</v>
@@ -9357,7 +9357,7 @@
         <v>2.84</v>
       </c>
       <c r="I117" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J117" t="n">
         <v>26.03</v>
@@ -9432,7 +9432,7 @@
         <v>-0.39</v>
       </c>
       <c r="I118" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J118" t="n">
         <v>25.99</v>
@@ -9507,7 +9507,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J119" t="n">
         <v>26.02</v>
@@ -9582,7 +9582,7 @@
         <v>4.54</v>
       </c>
       <c r="I120" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J120" t="n">
         <v>26.13</v>
@@ -9657,7 +9657,7 @@
         <v>0.51</v>
       </c>
       <c r="I121" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J121" t="n">
         <v>26.24</v>
@@ -9732,7 +9732,7 @@
         <v>-6.98</v>
       </c>
       <c r="I122" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J122" t="n">
         <v>26.24</v>
@@ -9807,7 +9807,7 @@
         <v>0.59</v>
       </c>
       <c r="I123" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J123" t="n">
         <v>26.24</v>
@@ -9882,7 +9882,7 @@
         <v>-4.65</v>
       </c>
       <c r="I124" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J124" t="n">
         <v>26.24</v>
@@ -9961,7 +9961,7 @@
         <v>-1.68</v>
       </c>
       <c r="I125" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J125" t="n">
         <v>26.24</v>
@@ -10036,7 +10036,7 @@
         <v>-1.75</v>
       </c>
       <c r="I126" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J126" t="n">
         <v>26.23</v>
@@ -10111,7 +10111,7 @@
         <v>8.25</v>
       </c>
       <c r="I127" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J127" t="n">
         <v>26.32</v>
@@ -10186,7 +10186,7 @@
         <v>-0.55</v>
       </c>
       <c r="I128" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J128" t="n">
         <v>26.34</v>
@@ -10261,7 +10261,7 @@
         <v>2.35</v>
       </c>
       <c r="I129" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J129" t="n">
         <v>26.38</v>
@@ -10336,7 +10336,7 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J130" t="n">
         <v>26.41</v>
@@ -10411,7 +10411,7 @@
         <v>1.24</v>
       </c>
       <c r="I131" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J131" t="n">
         <v>26.59</v>
@@ -10486,7 +10486,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="I132" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J132" t="n">
         <v>26.69</v>
@@ -10565,7 +10565,7 @@
         <v>-3.04</v>
       </c>
       <c r="I133" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J133" t="n">
         <v>26.7</v>
@@ -10644,7 +10644,7 @@
         <v>-1.35</v>
       </c>
       <c r="I134" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J134" t="n">
         <v>26.72</v>
@@ -10719,7 +10719,7 @@
         <v>2.97</v>
       </c>
       <c r="I135" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J135" t="n">
         <v>26.8</v>
@@ -10794,7 +10794,7 @@
         <v>3.08</v>
       </c>
       <c r="I136" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J136" t="n">
         <v>26.87</v>
@@ -10869,7 +10869,7 @@
         <v>2.38</v>
       </c>
       <c r="I137" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J137" t="n">
         <v>26.94</v>
@@ -10944,7 +10944,7 @@
         <v>0.37</v>
       </c>
       <c r="I138" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J138" t="n">
         <v>27.02</v>
@@ -11019,7 +11019,7 @@
         <v>5.23</v>
       </c>
       <c r="I139" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J139" t="n">
         <v>27.05</v>
@@ -11094,7 +11094,7 @@
         <v>2</v>
       </c>
       <c r="I140" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J140" t="n">
         <v>27.05</v>
@@ -11169,7 +11169,7 @@
         <v>0.45</v>
       </c>
       <c r="I141" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J141" t="n">
         <v>27.04</v>
@@ -11244,7 +11244,7 @@
         <v>2.39</v>
       </c>
       <c r="I142" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J142" t="n">
         <v>27.17</v>
@@ -11319,7 +11319,7 @@
         <v>1.6</v>
       </c>
       <c r="I143" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J143" t="n">
         <v>27.32</v>
@@ -11394,7 +11394,7 @@
         <v>-0.03</v>
       </c>
       <c r="I144" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J144" t="n">
         <v>27.53</v>
@@ -11469,7 +11469,7 @@
         <v>10.41</v>
       </c>
       <c r="I145" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J145" t="n">
         <v>27.92</v>
@@ -11544,7 +11544,7 @@
         <v>-1.84</v>
       </c>
       <c r="I146" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J146" t="n">
         <v>28.3</v>
@@ -11619,7 +11619,7 @@
         <v>4.27</v>
       </c>
       <c r="I147" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J147" t="n">
         <v>28.65</v>
@@ -11694,7 +11694,7 @@
         <v>-0.35</v>
       </c>
       <c r="I148" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J148" t="n">
         <v>29</v>
@@ -11769,7 +11769,7 @@
         <v>-0.29</v>
       </c>
       <c r="I149" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J149" t="n">
         <v>29.32</v>
@@ -11844,7 +11844,7 @@
         <v>-1.02</v>
       </c>
       <c r="I150" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J150" t="n">
         <v>29.6</v>
@@ -11919,7 +11919,7 @@
         <v>0.5</v>
       </c>
       <c r="I151" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J151" t="n">
         <v>29.88</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J152" t="n">
         <v>30.28</v>
@@ -12069,7 +12069,7 @@
         <v>2.41</v>
       </c>
       <c r="I153" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J153" t="n">
         <v>30.75</v>
@@ -12144,7 +12144,7 @@
         <v>5.8</v>
       </c>
       <c r="I154" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J154" t="n">
         <v>31.35</v>
@@ -12219,7 +12219,7 @@
         <v>6</v>
       </c>
       <c r="I155" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J155" t="n">
         <v>32.02</v>
@@ -12294,7 +12294,7 @@
         <v>-2.18</v>
       </c>
       <c r="I156" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J156" t="n">
         <v>32.61</v>
@@ -12369,7 +12369,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="I157" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J157" t="n">
         <v>33.34</v>
@@ -12444,7 +12444,7 @@
         <v>-6.91</v>
       </c>
       <c r="I158" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J158" t="n">
         <v>33.93</v>
@@ -12519,7 +12519,7 @@
         <v>10.18</v>
       </c>
       <c r="I159" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J159" t="n">
         <v>34.64</v>
@@ -12594,7 +12594,7 @@
         <v>-1.26</v>
       </c>
       <c r="I160" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J160" t="n">
         <v>35.29</v>
@@ -12669,7 +12669,7 @@
         <v>-19</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>35.53</v>
@@ -12748,7 +12748,7 @@
         <v>14.39</v>
       </c>
       <c r="I162" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J162" t="n">
         <v>35.99</v>
@@ -12823,7 +12823,7 @@
         <v>-6.39</v>
       </c>
       <c r="I163" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J163" t="n">
         <v>36.3</v>
@@ -12898,7 +12898,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="I164" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J164" t="n">
         <v>36.78</v>
@@ -12973,7 +12973,7 @@
         <v>1.48</v>
       </c>
       <c r="I165" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J165" t="n">
         <v>37.12</v>
@@ -13048,7 +13048,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J166" t="n">
         <v>37.48</v>
@@ -13123,7 +13123,7 @@
         <v>4.84</v>
       </c>
       <c r="I167" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J167" t="n">
         <v>37.88</v>
@@ -13198,7 +13198,7 @@
         <v>-1.73</v>
       </c>
       <c r="I168" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J168" t="n">
         <v>38.24</v>
@@ -13273,7 +13273,7 @@
         <v>-7.52</v>
       </c>
       <c r="I169" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J169" t="n">
         <v>38.44</v>
@@ -13352,7 +13352,7 @@
         <v>7.25</v>
       </c>
       <c r="I170" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J170" t="n">
         <v>38.81</v>
@@ -13427,7 +13427,7 @@
         <v>4.79</v>
       </c>
       <c r="I171" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J171" t="n">
         <v>39.27</v>
@@ -13502,7 +13502,7 @@
         <v>8.58</v>
       </c>
       <c r="I172" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J172" t="n">
         <v>39.91</v>
@@ -13577,7 +13577,7 @@
         <v>0.26</v>
       </c>
       <c r="I173" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J173" t="n">
         <v>40.51</v>
@@ -13652,7 +13652,7 @@
         <v>5.16</v>
       </c>
       <c r="I174" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J174" t="n">
         <v>41.14</v>
@@ -13727,7 +13727,7 @@
         <v>-4.03</v>
       </c>
       <c r="I175" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J175" t="n">
         <v>41.55</v>
@@ -13802,7 +13802,7 @@
         <v>0.82</v>
       </c>
       <c r="I176" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J176" t="n">
         <v>42.03</v>
@@ -13877,7 +13877,7 @@
         <v>1.68</v>
       </c>
       <c r="I177" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J177" t="n">
         <v>42.37</v>
@@ -13952,7 +13952,7 @@
         <v>-11.91</v>
       </c>
       <c r="I178" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J178" t="n">
         <v>42.57</v>
@@ -14027,7 +14027,7 @@
         <v>9.42</v>
       </c>
       <c r="I179" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J179" t="n">
         <v>42.77</v>
@@ -14102,7 +14102,7 @@
         <v>-8.16</v>
       </c>
       <c r="I180" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J180" t="n">
         <v>42.81</v>
@@ -14177,7 +14177,7 @@
         <v>-2.95</v>
       </c>
       <c r="I181" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J181" t="n">
         <v>43.19</v>
@@ -14256,7 +14256,7 @@
         <v>7.72</v>
       </c>
       <c r="I182" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J182" t="n">
         <v>43.48</v>
@@ -14331,7 +14331,7 @@
         <v>-7.01</v>
       </c>
       <c r="I183" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J183" t="n">
         <v>43.74</v>
@@ -14410,7 +14410,7 @@
         <v>4.55</v>
       </c>
       <c r="I184" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J184" t="n">
         <v>43.92</v>
@@ -14485,7 +14485,7 @@
         <v>-10.28</v>
       </c>
       <c r="I185" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J185" t="n">
         <v>43.86</v>
@@ -14560,7 +14560,7 @@
         <v>-0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J186" t="n">
         <v>43.79</v>
@@ -14635,7 +14635,7 @@
         <v>-5.18</v>
       </c>
       <c r="I187" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J187" t="n">
         <v>43.52</v>
@@ -14710,7 +14710,7 @@
         <v>-6.76</v>
       </c>
       <c r="I188" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J188" t="n">
         <v>43.16</v>
@@ -14789,7 +14789,7 @@
         <v>4.69</v>
       </c>
       <c r="I189" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J189" t="n">
         <v>43.04</v>
@@ -14864,7 +14864,7 @@
         <v>-14.33</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>42.52</v>
@@ -14947,7 +14947,7 @@
         <v>2.99</v>
       </c>
       <c r="I191" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J191" t="n">
         <v>41.95</v>
@@ -15022,7 +15022,7 @@
         <v>13.02</v>
       </c>
       <c r="I192" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J192" t="n">
         <v>41.4</v>
@@ -15097,7 +15097,7 @@
         <v>0.86</v>
       </c>
       <c r="I193" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J193" t="n">
         <v>40.86</v>
@@ -15172,7 +15172,7 @@
         <v>8.33</v>
       </c>
       <c r="I194" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J194" t="n">
         <v>40.35</v>
@@ -15247,7 +15247,7 @@
         <v>5.29</v>
       </c>
       <c r="I195" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J195" t="n">
         <v>40.05</v>
@@ -15322,7 +15322,7 @@
         <v>0.12</v>
       </c>
       <c r="I196" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J196" t="n">
         <v>39.72</v>
@@ -15397,7 +15397,7 @@
         <v>6.03</v>
       </c>
       <c r="I197" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J197" t="n">
         <v>39.48</v>
@@ -15472,7 +15472,7 @@
         <v>6.35</v>
       </c>
       <c r="I198" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J198" t="n">
         <v>39.67</v>
@@ -15547,7 +15547,7 @@
         <v>-3.05</v>
       </c>
       <c r="I199" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J199" t="n">
         <v>39.59</v>
@@ -15622,7 +15622,7 @@
         <v>2.97</v>
       </c>
       <c r="I200" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J200" t="n">
         <v>39.76</v>
@@ -15697,7 +15697,7 @@
         <v>3.21</v>
       </c>
       <c r="I201" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J201" t="n">
         <v>40.08</v>
@@ -15772,7 +15772,7 @@
         <v>-0.42</v>
       </c>
       <c r="I202" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J202" t="n">
         <v>40.22</v>
@@ -15847,7 +15847,7 @@
         <v>3.89</v>
       </c>
       <c r="I203" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J203" t="n">
         <v>40.61</v>
@@ -15922,7 +15922,7 @@
         <v>-1.73</v>
       </c>
       <c r="I204" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J204" t="n">
         <v>40.86</v>
@@ -15997,7 +15997,7 @@
         <v>-14.52</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>40.99</v>
@@ -16072,7 +16072,7 @@
         <v>-1.27</v>
       </c>
       <c r="I206" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J206" t="n">
         <v>41.1</v>
@@ -16147,7 +16147,7 @@
         <v>-1.68</v>
       </c>
       <c r="I207" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J207" t="n">
         <v>41.29</v>
@@ -16226,7 +16226,7 @@
         <v>-11.05</v>
       </c>
       <c r="I208" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J208" t="n">
         <v>41.37</v>
@@ -16301,7 +16301,7 @@
         <v>7.11</v>
       </c>
       <c r="I209" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J209" t="n">
         <v>41.5</v>
@@ -16376,7 +16376,7 @@
         <v>8.15</v>
       </c>
       <c r="I210" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J210" t="n">
         <v>42.05</v>
@@ -16451,7 +16451,7 @@
         <v>3.69</v>
       </c>
       <c r="I211" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J211" t="n">
         <v>42.62</v>
@@ -16526,7 +16526,7 @@
         <v>1.02</v>
       </c>
       <c r="I212" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J212" t="n">
         <v>43.01</v>
@@ -16601,7 +16601,7 @@
         <v>1.17</v>
       </c>
       <c r="I213" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J213" t="n">
         <v>43.41</v>
@@ -16676,7 +16676,7 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J214" t="n">
         <v>43.67</v>
@@ -16751,7 +16751,7 @@
         <v>-0.88</v>
       </c>
       <c r="I215" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J215" t="n">
         <v>43.79</v>
@@ -16826,7 +16826,7 @@
         <v>-0.34</v>
       </c>
       <c r="I216" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J216" t="n">
         <v>43.91</v>
@@ -16905,7 +16905,7 @@
         <v>-3.76</v>
       </c>
       <c r="I217" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J217" t="n">
         <v>43.82</v>
@@ -16980,7 +16980,7 @@
         <v>12.4</v>
       </c>
       <c r="I218" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J218" t="n">
         <v>43.86</v>
@@ -17055,7 +17055,7 @@
         <v>4.19</v>
       </c>
       <c r="I219" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J219" t="n">
         <v>44.06</v>
@@ -17130,7 +17130,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J220" t="n">
         <v>44.43</v>
@@ -17205,7 +17205,7 @@
         <v>-3.17</v>
       </c>
       <c r="I221" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J221" t="n">
         <v>44.65</v>
@@ -17280,7 +17280,7 @@
         <v>-5.05</v>
       </c>
       <c r="I222" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J222" t="n">
         <v>44.74</v>
@@ -17355,7 +17355,7 @@
         <v>8.65</v>
       </c>
       <c r="I223" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J223" t="n">
         <v>44.96</v>
@@ -17430,7 +17430,7 @@
         <v>1.3</v>
       </c>
       <c r="I224" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J224" t="n">
         <v>45.25</v>
@@ -17505,7 +17505,7 @@
         <v>2.6</v>
       </c>
       <c r="I225" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J225" t="n">
         <v>45.97</v>
@@ -17580,7 +17580,7 @@
         <v>-1.23</v>
       </c>
       <c r="I226" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J226" t="n">
         <v>46.68</v>
@@ -17655,7 +17655,7 @@
         <v>4.88</v>
       </c>
       <c r="I227" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J227" t="n">
         <v>47.56</v>
@@ -17730,7 +17730,7 @@
         <v>4.6</v>
       </c>
       <c r="I228" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J228" t="n">
         <v>48.79</v>
@@ -17805,7 +17805,7 @@
         <v>-4.63</v>
       </c>
       <c r="I229" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J229" t="n">
         <v>49.76</v>
@@ -17880,7 +17880,7 @@
         <v>9.57</v>
       </c>
       <c r="I230" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J230" t="n">
         <v>50.85</v>
@@ -17955,7 +17955,7 @@
         <v>0.38</v>
       </c>
       <c r="I231" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J231" t="n">
         <v>51.87</v>
@@ -18030,7 +18030,7 @@
         <v>-3.33</v>
       </c>
       <c r="I232" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J232" t="n">
         <v>52.76</v>
@@ -18105,7 +18105,7 @@
         <v>-1.46</v>
       </c>
       <c r="I233" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J233" t="n">
         <v>53.59</v>
@@ -18180,7 +18180,7 @@
         <v>7.02</v>
       </c>
       <c r="I234" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J234" t="n">
         <v>54.62</v>
@@ -18255,7 +18255,7 @@
         <v>7.89</v>
       </c>
       <c r="I235" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J235" t="n">
         <v>55.94</v>
@@ -18330,7 +18330,7 @@
         <v>0.54</v>
       </c>
       <c r="I236" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J236" t="n">
         <v>57.28</v>
@@ -18405,7 +18405,7 @@
         <v>-12.31</v>
       </c>
       <c r="I237" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J237" t="n">
         <v>58.26</v>
@@ -18480,7 +18480,7 @@
         <v>5.52</v>
       </c>
       <c r="I238" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J238" t="n">
         <v>59.16</v>
@@ -18555,7 +18555,7 @@
         <v>-6.14</v>
       </c>
       <c r="I239" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J239" t="n">
         <v>59.76</v>
@@ -18630,7 +18630,7 @@
         <v>-13.08</v>
       </c>
       <c r="I240" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J240" t="n">
         <v>59.72</v>
@@ -18709,7 +18709,7 @@
         <v>0.11</v>
       </c>
       <c r="I241" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J241" t="n">
         <v>59.77</v>
@@ -18784,7 +18784,7 @@
         <v>15.95</v>
       </c>
       <c r="I242" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J242" t="n">
         <v>60.37</v>
@@ -18859,7 +18859,7 @@
         <v>3.69</v>
       </c>
       <c r="I243" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J243" t="n">
         <v>60.88</v>
@@ -18934,7 +18934,7 @@
         <v>-1.08</v>
       </c>
       <c r="I244" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J244" t="n">
         <v>61.31</v>
@@ -19009,7 +19009,7 @@
         <v>7.44</v>
       </c>
       <c r="I245" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J245" t="n">
         <v>61.91</v>
@@ -19084,7 +19084,7 @@
         <v>-7.28</v>
       </c>
       <c r="I246" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J246" t="n">
         <v>62.29</v>
@@ -19159,7 +19159,7 @@
         <v>2.36</v>
       </c>
       <c r="I247" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J247" t="n">
         <v>62.62</v>
@@ -19234,7 +19234,7 @@
         <v>-0.37</v>
       </c>
       <c r="I248" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J248" t="n">
         <v>62.8</v>
@@ -19309,7 +19309,7 @@
         <v>3.02</v>
       </c>
       <c r="I249" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J249" t="n">
         <v>63.22</v>
@@ -19384,7 +19384,7 @@
         <v>-1.6</v>
       </c>
       <c r="I250" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J250" t="n">
         <v>63.31</v>
@@ -19459,7 +19459,7 @@
         <v>2.88</v>
       </c>
       <c r="I251" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J251" t="n">
         <v>63.47</v>
@@ -19534,7 +19534,7 @@
         <v>-1.86</v>
       </c>
       <c r="I252" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J252" t="n">
         <v>63.69</v>
@@ -19609,7 +19609,7 @@
         <v>4.06</v>
       </c>
       <c r="I253" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J253" t="n">
         <v>64.08</v>
@@ -19684,7 +19684,7 @@
         <v>4.85</v>
       </c>
       <c r="I254" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J254" t="n">
         <v>64.42</v>
@@ -19759,7 +19759,7 @@
         <v>-9.07</v>
       </c>
       <c r="I255" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J255" t="n">
         <v>64.19</v>
@@ -19834,7 +19834,7 @@
         <v>-3.94</v>
       </c>
       <c r="I256" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J256" t="n">
         <v>63.8</v>
@@ -19913,7 +19913,7 @@
         <v>-0.02</v>
       </c>
       <c r="I257" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J257" t="n">
         <v>63.85</v>
@@ -19988,7 +19988,7 @@
         <v>-14.89</v>
       </c>
       <c r="I258" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J258" s="4" t="n">
         <v>63.26</v>
@@ -20067,7 +20067,7 @@
         <v>5.99</v>
       </c>
       <c r="I259" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J259" t="n">
         <v>63.03</v>
@@ -20142,7 +20142,7 @@
         <v>-3.22</v>
       </c>
       <c r="I260" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J260" t="n">
         <v>63.11</v>
@@ -20221,7 +20221,7 @@
         <v>-12.6</v>
       </c>
       <c r="I261" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J261" t="n">
         <v>62.84</v>
@@ -20300,7 +20300,7 @@
         <v>11.35</v>
       </c>
       <c r="I262" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J262" t="n">
         <v>62.42</v>
@@ -20375,7 +20375,7 @@
         <v>2.36</v>
       </c>
       <c r="I263" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J263" t="n">
         <v>61.95</v>
@@ -20450,7 +20450,7 @@
         <v>2.75</v>
       </c>
       <c r="I264" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J264" t="n">
         <v>61.59</v>
@@ -20525,7 +20525,7 @@
         <v>-10.35</v>
       </c>
       <c r="I265" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J265" t="n">
         <v>60.7</v>
@@ -20598,7 +20598,7 @@
         <v>0.88</v>
       </c>
       <c r="I266" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J266" t="n">
         <v>60.08</v>
@@ -20677,7 +20677,7 @@
         <v>5.84</v>
       </c>
       <c r="I267" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J267" t="n">
         <v>59.54</v>
@@ -20752,7 +20752,7 @@
         <v>2.35</v>
       </c>
       <c r="I268" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J268" t="n">
         <v>59.07</v>
@@ -20827,7 +20827,7 @@
         <v>-1.69</v>
       </c>
       <c r="I269" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J269" t="n">
         <v>58.45</v>
@@ -20902,7 +20902,7 @@
         <v>1.54</v>
       </c>
       <c r="I270" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J270" t="n">
         <v>57.93</v>
@@ -20977,7 +20977,7 @@
         <v>-6.75</v>
       </c>
       <c r="I271" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J271" t="n">
         <v>57.14</v>
@@ -21056,7 +21056,7 @@
         <v>3.7</v>
       </c>
       <c r="I272" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J272" t="n">
         <v>56.5</v>
@@ -21131,7 +21131,7 @@
         <v>3.62</v>
       </c>
       <c r="I273" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J273" t="n">
         <v>55.82</v>
@@ -21206,7 +21206,7 @@
         <v>3.79</v>
       </c>
       <c r="I274" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J274" t="n">
         <v>55.08</v>
@@ -21281,7 +21281,7 @@
         <v>-14.14</v>
       </c>
       <c r="I275" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J275" t="n">
         <v>54.26</v>
@@ -21360,7 +21360,7 @@
         <v>-4.82</v>
       </c>
       <c r="I276" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J276" t="n">
         <v>53.45</v>
@@ -21439,7 +21439,7 @@
         <v>-12.86</v>
       </c>
       <c r="I277" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J277" t="n">
         <v>52.34</v>
@@ -21514,7 +21514,7 @@
         <v>17.96</v>
       </c>
       <c r="I278" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J278" t="n">
         <v>52.07</v>
@@ -21589,7 +21589,7 @@
         <v>9.09</v>
       </c>
       <c r="I279" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J279" t="n">
         <v>51.85</v>
@@ -21664,7 +21664,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I280" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J280" t="n">
         <v>51.75</v>
@@ -21739,7 +21739,7 @@
         <v>3.89</v>
       </c>
       <c r="I281" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J281" t="n">
         <v>52.1</v>
@@ -21814,7 +21814,7 @@
         <v>3.18</v>
       </c>
       <c r="I282" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J282" t="n">
         <v>52.26</v>
@@ -21893,7 +21893,7 @@
         <v>19.38</v>
       </c>
       <c r="I283" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J283" t="n">
         <v>52.9</v>
@@ -21968,7 +21968,7 @@
         <v>6.63</v>
       </c>
       <c r="I284" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J284" t="n">
         <v>53.7</v>
@@ -22043,7 +22043,7 @@
         <v>6.13</v>
       </c>
       <c r="I285" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J285" t="n">
         <v>55</v>
@@ -22118,7 +22118,7 @@
         <v>5.46</v>
       </c>
       <c r="I286" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J286" t="n">
         <v>56.49</v>
@@ -22193,7 +22193,7 @@
         <v>5.89</v>
       </c>
       <c r="I287" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J287" t="n">
         <v>58.07</v>
@@ -22268,7 +22268,7 @@
         <v>0.76</v>
       </c>
       <c r="I288" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J288" t="n">
         <v>59.62</v>
@@ -22343,7 +22343,7 @@
         <v>2.81</v>
       </c>
       <c r="I289" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J289" t="n">
         <v>61.34</v>
@@ -22418,7 +22418,7 @@
         <v>7.15</v>
       </c>
       <c r="I290" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J290" t="n">
         <v>63.33</v>
@@ -22493,7 +22493,7 @@
         <v>1.33</v>
       </c>
       <c r="I291" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J291" t="n">
         <v>65.56999999999999</v>
@@ -22568,7 +22568,7 @@
         <v>2.24</v>
       </c>
       <c r="I292" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J292" t="n">
         <v>67.81999999999999</v>
@@ -22643,7 +22643,7 @@
         <v>7.69</v>
       </c>
       <c r="I293" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J293" t="n">
         <v>70.34999999999999</v>
@@ -22718,7 +22718,7 @@
         <v>6.75</v>
       </c>
       <c r="I294" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J294" t="n">
         <v>73.14</v>
@@ -22793,7 +22793,7 @@
         <v>13.79</v>
       </c>
       <c r="I295" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J295" t="n">
         <v>77.09999999999999</v>
@@ -22868,7 +22868,7 @@
         <v>-3.84</v>
       </c>
       <c r="I296" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J296" t="n">
         <v>80.94</v>
@@ -22943,7 +22943,7 @@
         <v>-11.21</v>
       </c>
       <c r="I297" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J297" t="n">
         <v>84.38</v>
@@ -23018,7 +23018,7 @@
         <v>7.67</v>
       </c>
       <c r="I298" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J298" t="n">
         <v>87.88</v>
@@ -23093,7 +23093,7 @@
         <v>7.64</v>
       </c>
       <c r="I299" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J299" t="n">
         <v>91.62</v>
@@ -23168,7 +23168,7 @@
         <v>2.69</v>
       </c>
       <c r="I300" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J300" t="n">
         <v>95.5</v>
@@ -23243,7 +23243,7 @@
         <v>-2.18</v>
       </c>
       <c r="I301" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J301" t="n">
         <v>99.13</v>
@@ -23318,7 +23318,7 @@
         <v>13.02</v>
       </c>
       <c r="I302" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J302" t="n">
         <v>103.51</v>
@@ -23393,7 +23393,7 @@
         <v>15.04</v>
       </c>
       <c r="I303" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J303" t="n">
         <v>108.42</v>
@@ -23468,7 +23468,7 @@
         <v>-8.289999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J304" t="n">
         <v>112.43</v>
@@ -23543,7 +23543,7 @@
         <v>16.33</v>
       </c>
       <c r="I305" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J305" t="n">
         <v>117.45</v>
@@ -23618,7 +23618,7 @@
         <v>7.62</v>
       </c>
       <c r="I306" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J306" t="n">
         <v>122.94</v>
@@ -23693,7 +23693,7 @@
         <v>-9.4</v>
       </c>
       <c r="I307" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J307" t="n">
         <v>127.3</v>
@@ -23768,7 +23768,7 @@
         <v>6.79</v>
       </c>
       <c r="I308" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J308" t="n">
         <v>132.21</v>
@@ -23843,7 +23843,7 @@
         <v>1.06</v>
       </c>
       <c r="I309" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J309" t="n">
         <v>137.1</v>
@@ -23918,7 +23918,7 @@
         <v>-11.82</v>
       </c>
       <c r="I310" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J310" t="n">
         <v>140.57</v>
@@ -23993,7 +23993,7 @@
         <v>-7.57</v>
       </c>
       <c r="I311" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J311" t="n">
         <v>143.36</v>
@@ -24068,7 +24068,7 @@
         <v>0.09</v>
       </c>
       <c r="I312" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J312" t="n">
         <v>146.05</v>
@@ -24143,7 +24143,7 @@
         <v>14.03</v>
       </c>
       <c r="I313" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J313" t="n">
         <v>149.42</v>
@@ -24218,7 +24218,7 @@
         <v>2.99</v>
       </c>
       <c r="I314" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J314" t="n">
         <v>152.7</v>
@@ -24293,7 +24293,7 @@
         <v>6.83</v>
       </c>
       <c r="I315" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J315" t="n">
         <v>155.81</v>
@@ -24368,7 +24368,7 @@
         <v>18.48</v>
       </c>
       <c r="I316" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J316" t="n">
         <v>160.93</v>
@@ -24443,7 +24443,7 @@
         <v>-3.46</v>
       </c>
       <c r="I317" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J317" t="n">
         <v>166.34</v>
@@ -24518,7 +24518,7 @@
         <v>3.05</v>
       </c>
       <c r="I318" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J318" t="n">
         <v>171.67</v>
@@ -24593,7 +24593,7 @@
         <v>-0.13</v>
       </c>
       <c r="I319" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J319" t="n">
         <v>176.54</v>
@@ -24668,7 +24668,7 @@
         <v>1.2</v>
       </c>
       <c r="I320" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J320" t="n">
         <v>181.37</v>
@@ -24743,7 +24743,7 @@
         <v>17.31</v>
       </c>
       <c r="I321" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J321" t="n">
         <v>188.3</v>
@@ -24818,7 +24818,7 @@
         <v>5.34</v>
       </c>
       <c r="I322" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J322" t="n">
         <v>195.12</v>
@@ -24893,7 +24893,7 @@
         <v>-6.36</v>
       </c>
       <c r="I323" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J323" t="n">
         <v>199.96</v>
@@ -24968,7 +24968,7 @@
         <v>-30.51</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>201.48</v>
@@ -25047,7 +25047,7 @@
         <v>15.83</v>
       </c>
       <c r="I325" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J325" t="n">
         <v>203.2</v>
@@ -25122,7 +25122,7 @@
         <v>-4.61</v>
       </c>
       <c r="I326" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J326" t="n">
         <v>203.76</v>
@@ -25201,7 +25201,7 @@
         <v>-10.43</v>
       </c>
       <c r="I327" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J327" t="n">
         <v>204.17</v>
@@ -25276,7 +25276,7 @@
         <v>23.99</v>
       </c>
       <c r="I328" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J328" t="n">
         <v>206.15</v>
@@ -25351,7 +25351,7 @@
         <v>4.78</v>
       </c>
       <c r="I329" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J329" t="n">
         <v>208.58</v>
@@ -25426,7 +25426,7 @@
         <v>16.11</v>
       </c>
       <c r="I330" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J330" t="n">
         <v>213.99</v>
@@ -25501,7 +25501,7 @@
         <v>-16.99</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>217.71</v>
@@ -25576,7 +25576,7 @@
         <v>3.39</v>
       </c>
       <c r="I332" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J332" t="n">
         <v>221.81</v>
@@ -25651,7 +25651,7 @@
         <v>19.43</v>
       </c>
       <c r="I333" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J333" t="n">
         <v>227.11</v>
@@ -25726,7 +25726,7 @@
         <v>7.69</v>
       </c>
       <c r="I334" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J334" t="n">
         <v>233.22</v>
@@ -25801,7 +25801,7 @@
         <v>-23.06</v>
       </c>
       <c r="I335" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J335" s="4" t="n">
         <v>235.26</v>
@@ -25880,7 +25880,7 @@
         <v>-0.8</v>
       </c>
       <c r="I336" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J336" t="n">
         <v>235.45</v>
@@ -25955,7 +25955,7 @@
         <v>10.03</v>
       </c>
       <c r="I337" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J337" t="n">
         <v>237.18</v>
@@ -26030,7 +26030,7 @@
         <v>-14.65</v>
       </c>
       <c r="I338" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>236.73</v>
@@ -26109,7 +26109,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I339" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J339" t="n">
         <v>237.34</v>
@@ -26184,7 +26184,7 @@
         <v>12.76</v>
       </c>
       <c r="I340" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J340" t="n">
         <v>239.32</v>
@@ -26259,7 +26259,7 @@
         <v>-18.43</v>
       </c>
       <c r="I341" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>236.89</v>
@@ -26338,7 +26338,7 @@
         <v>-16.59</v>
       </c>
       <c r="I342" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J342" s="4" t="n">
         <v>231.94</v>
@@ -26413,7 +26413,7 @@
         <v>7.26</v>
       </c>
       <c r="I343" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J343" t="n">
         <v>228.54</v>
@@ -26488,7 +26488,7 @@
         <v>-15.09</v>
       </c>
       <c r="I344" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>227.67</v>
@@ -26567,7 +26567,7 @@
         <v>5.78</v>
       </c>
       <c r="I345" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J345" t="n">
         <v>225.84</v>
@@ -26642,7 +26642,7 @@
         <v>10.08</v>
       </c>
       <c r="I346" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J346" t="n">
         <v>225.38</v>
@@ -26717,7 +26717,7 @@
         <v>-0.1</v>
       </c>
       <c r="I347" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J347" t="n">
         <v>225.96</v>
@@ -26792,7 +26792,7 @@
         <v>-13.99</v>
       </c>
       <c r="I348" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J348" t="n">
         <v>223.03</v>
@@ -26871,7 +26871,7 @@
         <v>6.83</v>
       </c>
       <c r="I349" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J349" t="n">
         <v>220.13</v>
@@ -26946,7 +26946,7 @@
         <v>-6.29</v>
       </c>
       <c r="I350" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J350" t="n">
         <v>214.79</v>
@@ -27021,7 +27021,7 @@
         <v>-13.93</v>
       </c>
       <c r="I351" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J351" t="n">
         <v>210.61</v>
@@ -27096,7 +27096,7 @@
         <v>-4.92</v>
       </c>
       <c r="I352" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J352" t="n">
         <v>205.69</v>
@@ -27171,7 +27171,7 @@
         <v>0.99</v>
       </c>
       <c r="I353" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J353" t="n">
         <v>198.57</v>
@@ -27246,7 +27246,7 @@
         <v>15.89</v>
       </c>
       <c r="I354" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J354" t="n">
         <v>191.46</v>
@@ -27321,7 +27321,7 @@
         <v>1.54</v>
       </c>
       <c r="I355" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J355" t="n">
         <v>187.94</v>
@@ -27396,7 +27396,7 @@
         <v>-2.16</v>
       </c>
       <c r="I356" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J356" t="n">
         <v>184.34</v>
@@ -27471,7 +27471,7 @@
         <v>-13.14</v>
       </c>
       <c r="I357" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J357" t="n">
         <v>178.56</v>
@@ -27546,7 +27546,7 @@
         <v>-6.33</v>
       </c>
       <c r="I358" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J358" t="n">
         <v>174.19</v>
@@ -27625,7 +27625,7 @@
         <v>-14.52</v>
       </c>
       <c r="I359" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J359" s="4" t="n">
         <v>167.84</v>
@@ -27700,7 +27700,7 @@
         <v>-16.02</v>
       </c>
       <c r="I360" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J360" s="4" t="n">
         <v>159.11</v>
@@ -27779,7 +27779,7 @@
         <v>24.7</v>
       </c>
       <c r="I361" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J361" t="n">
         <v>153.97</v>
@@ -27854,7 +27854,7 @@
         <v>0</v>
       </c>
       <c r="I362" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J362" t="n">
         <v>150.64</v>
@@ -27929,7 +27929,7 @@
         <v>1.74</v>
       </c>
       <c r="I363" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J363" t="n">
         <v>146.74</v>
@@ -28004,7 +28004,7 @@
         <v>19.87</v>
       </c>
       <c r="I364" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J364" t="n">
         <v>145.48</v>
@@ -28079,7 +28079,7 @@
         <v>-5.6</v>
       </c>
       <c r="I365" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J365" t="n">
         <v>143.34</v>
@@ -28158,7 +28158,7 @@
         <v>0.2</v>
       </c>
       <c r="I366" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J366" t="n">
         <v>140.34</v>
@@ -28233,7 +28233,7 @@
         <v>5.99</v>
       </c>
       <c r="I367" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J367" t="n">
         <v>137.74</v>
@@ -28308,7 +28308,7 @@
         <v>-7.31</v>
       </c>
       <c r="I368" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J368" t="n">
         <v>135.97</v>
@@ -28387,7 +28387,7 @@
         <v>2.31</v>
       </c>
       <c r="I369" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J369" t="n">
         <v>133.79</v>
@@ -28462,7 +28462,7 @@
         <v>6.89</v>
       </c>
       <c r="I370" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J370" t="n">
         <v>132.62</v>
@@ -28537,7 +28537,7 @@
         <v>2.25</v>
       </c>
       <c r="I371" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J371" t="n">
         <v>132.76</v>
@@ -28612,7 +28612,7 @@
         <v>-0.28</v>
       </c>
       <c r="I372" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J372" t="n">
         <v>133.24</v>
@@ -28687,7 +28687,7 @@
         <v>4.54</v>
       </c>
       <c r="I373" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J373" t="n">
         <v>133.97</v>
@@ -28762,7 +28762,7 @@
         <v>-14.8</v>
       </c>
       <c r="I374" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J374" s="4" t="n">
         <v>132.5</v>
@@ -28841,7 +28841,7 @@
         <v>-6.48</v>
       </c>
       <c r="I375" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J375" t="n">
         <v>130.49</v>
@@ -28916,7 +28916,7 @@
         <v>1.22</v>
       </c>
       <c r="I376" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J376" t="n">
         <v>128.73</v>
@@ -28991,7 +28991,7 @@
         <v>-1.32</v>
       </c>
       <c r="I377" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J377" t="n">
         <v>127.92</v>
@@ -29066,7 +29066,7 @@
         <v>-7.82</v>
       </c>
       <c r="I378" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J378" t="n">
         <v>127.07</v>
@@ -29141,7 +29141,7 @@
         <v>4.05</v>
       </c>
       <c r="I379" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J379" t="n">
         <v>127.37</v>
@@ -29216,7 +29216,7 @@
         <v>0.8</v>
       </c>
       <c r="I380" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J380" t="n">
         <v>128.6</v>
@@ -29291,7 +29291,7 @@
         <v>5.54</v>
       </c>
       <c r="I381" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J381" t="n">
         <v>129.02</v>
@@ -29366,7 +29366,7 @@
         <v>-9.51</v>
       </c>
       <c r="I382" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J382" t="n">
         <v>128.85</v>
@@ -29441,7 +29441,7 @@
         <v>1.3</v>
       </c>
       <c r="I383" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J383" t="n">
         <v>128.66</v>
@@ -29516,7 +29516,7 @@
         <v>-6.1</v>
       </c>
       <c r="I384" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J384" t="n">
         <v>126.96</v>
@@ -29595,7 +29595,7 @@
         <v>0.42</v>
       </c>
       <c r="I385" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J385" t="n">
         <v>125.67</v>
@@ -29674,7 +29674,7 @@
         <v>0.37</v>
       </c>
       <c r="I386" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J386" t="n">
         <v>124.39</v>
@@ -29753,7 +29753,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="I387" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J387" t="n">
         <v>123.25</v>
@@ -29828,7 +29828,7 @@
         <v>5.11</v>
       </c>
       <c r="I388" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J388" t="n">
         <v>122.91</v>
@@ -29903,7 +29903,7 @@
         <v>2.11</v>
       </c>
       <c r="I389" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J389" t="n">
         <v>122.55</v>
@@ -29978,7 +29978,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="I390" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J390" t="n">
         <v>121.23</v>
@@ -30057,7 +30057,7 @@
         <v>5.24</v>
       </c>
       <c r="I391" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J391" t="n">
         <v>120.06</v>
@@ -30132,7 +30132,7 @@
         <v>-16.99</v>
       </c>
       <c r="I392" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J392" s="4" t="n">
         <v>117.87</v>
@@ -30211,7 +30211,7 @@
         <v>1.18</v>
       </c>
       <c r="I393" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J393" t="n">
         <v>115.41</v>
@@ -30286,7 +30286,7 @@
         <v>1.61</v>
       </c>
       <c r="I394" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J394" t="n">
         <v>114.15</v>
@@ -30361,7 +30361,7 @@
         <v>10.43</v>
       </c>
       <c r="I395" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J395" t="n">
         <v>113.86</v>
@@ -30436,7 +30436,7 @@
         <v>7.71</v>
       </c>
       <c r="I396" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J396" t="n">
         <v>113.93</v>
@@ -30511,7 +30511,7 @@
         <v>14.77</v>
       </c>
       <c r="I397" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J397" t="n">
         <v>115</v>
@@ -30586,7 +30586,7 @@
         <v>7.13</v>
       </c>
       <c r="I398" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J398" t="n">
         <v>117.04</v>
@@ -30661,7 +30661,7 @@
         <v>-3.75</v>
       </c>
       <c r="I399" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J399" t="n">
         <v>118.57</v>
@@ -30736,7 +30736,7 @@
         <v>0.05</v>
       </c>
       <c r="I400" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J400" t="n">
         <v>120.06</v>
@@ -30811,7 +30811,7 @@
         <v>3.5</v>
       </c>
       <c r="I401" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J401" t="n">
         <v>121.49</v>
@@ -30886,7 +30886,7 @@
         <v>-6.05</v>
       </c>
       <c r="I402" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J402" t="n">
         <v>123.04</v>
@@ -30961,7 +30961,7 @@
         <v>3.31</v>
       </c>
       <c r="I403" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J403" t="n">
         <v>124.75</v>
@@ -31036,7 +31036,7 @@
         <v>0.59</v>
       </c>
       <c r="I404" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J404" t="n">
         <v>126.85</v>
@@ -31111,7 +31111,7 @@
         <v>3.94</v>
       </c>
       <c r="I405" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J405" t="n">
         <v>129.22</v>
@@ -31186,7 +31186,7 @@
         <v>6.52</v>
       </c>
       <c r="I406" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J406" t="n">
         <v>132.08</v>
@@ -31261,7 +31261,7 @@
         <v>0.34</v>
       </c>
       <c r="I407" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J407" t="n">
         <v>134.43</v>
@@ -31336,7 +31336,7 @@
         <v>-0.01</v>
       </c>
       <c r="I408" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J408" t="n">
         <v>136.48</v>
@@ -31411,7 +31411,7 @@
         <v>-3.26</v>
       </c>
       <c r="I409" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J409" t="n">
         <v>138.14</v>
@@ -31490,7 +31490,7 @@
         <v>-10.31</v>
       </c>
       <c r="I410" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J410" t="n">
         <v>139.48</v>
@@ -31565,7 +31565,7 @@
         <v>-1.94</v>
       </c>
       <c r="I411" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J411" t="n">
         <v>140.38</v>
@@ -31644,7 +31644,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="I412" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J412" t="n">
         <v>141.75</v>
@@ -31723,7 +31723,7 @@
         <v>-0.65</v>
       </c>
       <c r="I413" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J413" t="n">
         <v>143.01</v>
@@ -31798,7 +31798,7 @@
         <v>-13.35</v>
       </c>
       <c r="I414" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J414" t="n">
         <v>143.35</v>
@@ -31867,13 +31867,13 @@
         <v>107.35</v>
       </c>
       <c r="G415" t="n">
-        <v>138394200</v>
+        <v>139897300</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-2.89</v>
       </c>
       <c r="I415" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J415" t="n">
         <v>142.98</v>
@@ -31943,31 +31943,31 @@
         <v>93.44</v>
       </c>
       <c r="F416" t="n">
-        <v>96.23999999999999</v>
+        <v>93.67</v>
       </c>
       <c r="G416" t="n">
-        <v>95229341</v>
+        <v>112826432</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-10.35</v>
+        <v>-12.74</v>
       </c>
       <c r="I416" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J416" t="n">
-        <v>141.61</v>
+        <v>141.48</v>
       </c>
       <c r="K416" t="n">
-        <v>128.09</v>
+        <v>128.05</v>
       </c>
       <c r="L416" t="n">
-        <v>160.83</v>
+        <v>160.81</v>
       </c>
       <c r="M416" t="n">
-        <v>122.05</v>
+        <v>122.03</v>
       </c>
       <c r="N416" s="3" t="n">
-        <v>24.42</v>
+        <v>23.74</v>
       </c>
       <c r="O416" t="n">
         <v>18</v>
@@ -31991,13 +31991,15 @@
         <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="1" t="n">
+        <v>168.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -608,7 +608,7 @@
         <v>-6.32</v>
       </c>
       <c r="I2" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J2" t="n">
         <v>27.4</v>
@@ -683,7 +683,7 @@
         <v>4.86</v>
       </c>
       <c r="I3" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J3" t="n">
         <v>27.44</v>
@@ -758,7 +758,7 @@
         <v>-17.28</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>27.25</v>
@@ -833,7 +833,7 @@
         <v>4.54</v>
       </c>
       <c r="I5" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J5" t="n">
         <v>27.03</v>
@@ -908,7 +908,7 @@
         <v>-9.789999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J6" t="n">
         <v>26.7</v>
@@ -983,7 +983,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J7" t="n">
         <v>26.46</v>
@@ -1058,7 +1058,7 @@
         <v>6.29</v>
       </c>
       <c r="I8" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J8" t="n">
         <v>26.24</v>
@@ -1133,7 +1133,7 @@
         <v>-12.39</v>
       </c>
       <c r="I9" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J9" t="n">
         <v>25.82</v>
@@ -1212,7 +1212,7 @@
         <v>8.59</v>
       </c>
       <c r="I10" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J10" t="n">
         <v>25.49</v>
@@ -1287,7 +1287,7 @@
         <v>-13.84</v>
       </c>
       <c r="I11" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J11" t="n">
         <v>25.07</v>
@@ -1370,7 +1370,7 @@
         <v>-3.19</v>
       </c>
       <c r="I12" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J12" t="n">
         <v>24.58</v>
@@ -1453,7 +1453,7 @@
         <v>5.09</v>
       </c>
       <c r="I13" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J13" t="n">
         <v>24.13</v>
@@ -1532,7 +1532,7 @@
         <v>-1.16</v>
       </c>
       <c r="I14" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J14" t="n">
         <v>23.66</v>
@@ -1611,7 +1611,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J15" t="n">
         <v>23.23</v>
@@ -1686,7 +1686,7 @@
         <v>4.98</v>
       </c>
       <c r="I16" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J16" t="n">
         <v>22.84</v>
@@ -1761,7 +1761,7 @@
         <v>-4.12</v>
       </c>
       <c r="I17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J17" t="n">
         <v>22.34</v>
@@ -1836,7 +1836,7 @@
         <v>2.22</v>
       </c>
       <c r="I18" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J18" t="n">
         <v>21.79</v>
@@ -1911,7 +1911,7 @@
         <v>-2.17</v>
       </c>
       <c r="I19" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J19" t="n">
         <v>21.21</v>
@@ -1986,7 +1986,7 @@
         <v>-3.28</v>
       </c>
       <c r="I20" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J20" t="n">
         <v>20.74</v>
@@ -2061,7 +2061,7 @@
         <v>8.93</v>
       </c>
       <c r="I21" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J21" t="n">
         <v>20.45</v>
@@ -2136,7 +2136,7 @@
         <v>-1.82</v>
       </c>
       <c r="I22" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J22" t="n">
         <v>20.23</v>
@@ -2211,7 +2211,7 @@
         <v>-8.6</v>
       </c>
       <c r="I23" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J23" t="n">
         <v>19.86</v>
@@ -2290,7 +2290,7 @@
         <v>-5.45</v>
       </c>
       <c r="I24" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J24" t="n">
         <v>19.66</v>
@@ -2365,7 +2365,7 @@
         <v>-9.779999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J25" t="n">
         <v>19.33</v>
@@ -2440,7 +2440,7 @@
         <v>-0.5</v>
       </c>
       <c r="I26" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J26" t="n">
         <v>19.11</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J27" t="n">
         <v>18.88</v>
@@ -2590,7 +2590,7 @@
         <v>1.95</v>
       </c>
       <c r="I28" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J28" t="n">
         <v>18.6</v>
@@ -2665,7 +2665,7 @@
         <v>-29.83</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>18.21</v>
@@ -2748,7 +2748,7 @@
         <v>-23.5</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>17.61</v>
@@ -2831,7 +2831,7 @@
         <v>4.83</v>
       </c>
       <c r="I31" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J31" t="n">
         <v>17.17</v>
@@ -2914,7 +2914,7 @@
         <v>-9.77</v>
       </c>
       <c r="I32" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J32" t="n">
         <v>16.72</v>
@@ -2997,7 +2997,7 @@
         <v>54.74</v>
       </c>
       <c r="I33" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J33" t="n">
         <v>16.45</v>
@@ -3076,7 +3076,7 @@
         <v>-24.61</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>16.03</v>
@@ -3159,7 +3159,7 @@
         <v>6.26</v>
       </c>
       <c r="I35" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J35" t="n">
         <v>15.56</v>
@@ -3242,7 +3242,7 @@
         <v>2.36</v>
       </c>
       <c r="I36" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J36" t="n">
         <v>15.04</v>
@@ -3321,7 +3321,7 @@
         <v>1.25</v>
       </c>
       <c r="I37" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J37" t="n">
         <v>14.58</v>
@@ -3396,7 +3396,7 @@
         <v>-11.93</v>
       </c>
       <c r="I38" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J38" t="n">
         <v>14.04</v>
@@ -3479,7 +3479,7 @@
         <v>-1.51</v>
       </c>
       <c r="I39" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J39" t="n">
         <v>13.5</v>
@@ -3558,7 +3558,7 @@
         <v>-5.35</v>
       </c>
       <c r="I40" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J40" t="n">
         <v>12.98</v>
@@ -3633,7 +3633,7 @@
         <v>5.42</v>
       </c>
       <c r="I41" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J41" t="n">
         <v>12.4</v>
@@ -3708,7 +3708,7 @@
         <v>12.14</v>
       </c>
       <c r="I42" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J42" t="n">
         <v>11.89</v>
@@ -3787,7 +3787,7 @@
         <v>16.59</v>
       </c>
       <c r="I43" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J43" t="n">
         <v>11.55</v>
@@ -3862,7 +3862,7 @@
         <v>2.85</v>
       </c>
       <c r="I44" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J44" t="n">
         <v>11.28</v>
@@ -3937,7 +3937,7 @@
         <v>-0.41</v>
       </c>
       <c r="I45" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J45" t="n">
         <v>11.09</v>
@@ -4012,7 +4012,7 @@
         <v>-3.51</v>
       </c>
       <c r="I46" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J46" t="n">
         <v>10.89</v>
@@ -4087,7 +4087,7 @@
         <v>2.54</v>
       </c>
       <c r="I47" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J47" t="n">
         <v>10.7</v>
@@ -4162,7 +4162,7 @@
         <v>-0.5</v>
       </c>
       <c r="I48" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J48" t="n">
         <v>10.49</v>
@@ -4237,7 +4237,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J49" t="n">
         <v>10.59</v>
@@ -4312,7 +4312,7 @@
         <v>-1.81</v>
       </c>
       <c r="I50" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J50" t="n">
         <v>10.8</v>
@@ -4387,7 +4387,7 @@
         <v>-3.15</v>
       </c>
       <c r="I51" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J51" t="n">
         <v>10.98</v>
@@ -4462,7 +4462,7 @@
         <v>5.08</v>
       </c>
       <c r="I52" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J52" t="n">
         <v>11.23</v>
@@ -4537,7 +4537,7 @@
         <v>2.8</v>
       </c>
       <c r="I53" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J53" t="n">
         <v>11.27</v>
@@ -4612,7 +4612,7 @@
         <v>3.31</v>
       </c>
       <c r="I54" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J54" t="n">
         <v>11.49</v>
@@ -4687,7 +4687,7 @@
         <v>21.42</v>
       </c>
       <c r="I55" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J55" t="n">
         <v>11.84</v>
@@ -4762,7 +4762,7 @@
         <v>8.56</v>
       </c>
       <c r="I56" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J56" t="n">
         <v>12.24</v>
@@ -4837,7 +4837,7 @@
         <v>1.3</v>
       </c>
       <c r="I57" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J57" t="n">
         <v>12.65</v>
@@ -4912,7 +4912,7 @@
         <v>-1.97</v>
       </c>
       <c r="I58" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J58" t="n">
         <v>13.11</v>
@@ -4987,7 +4987,7 @@
         <v>-0.44</v>
       </c>
       <c r="I59" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J59" t="n">
         <v>13.56</v>
@@ -5062,7 +5062,7 @@
         <v>-1.75</v>
       </c>
       <c r="I60" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J60" t="n">
         <v>14.03</v>
@@ -5137,7 +5137,7 @@
         <v>-0.5</v>
       </c>
       <c r="I61" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J61" t="n">
         <v>14.47</v>
@@ -5212,7 +5212,7 @@
         <v>-5.42</v>
       </c>
       <c r="I62" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J62" t="n">
         <v>14.8</v>
@@ -5287,7 +5287,7 @@
         <v>-2.89</v>
       </c>
       <c r="I63" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J63" t="n">
         <v>15.03</v>
@@ -5362,7 +5362,7 @@
         <v>-4.68</v>
       </c>
       <c r="I64" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J64" t="n">
         <v>15.19</v>
@@ -5437,7 +5437,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J65" t="n">
         <v>15.44</v>
@@ -5512,7 +5512,7 @@
         <v>-1.45</v>
       </c>
       <c r="I66" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J66" t="n">
         <v>15.7</v>
@@ -5587,7 +5587,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J67" t="n">
         <v>15.95</v>
@@ -5662,7 +5662,7 @@
         <v>-6.01</v>
       </c>
       <c r="I68" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J68" t="n">
         <v>16.16</v>
@@ -5741,7 +5741,7 @@
         <v>4.53</v>
       </c>
       <c r="I69" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J69" t="n">
         <v>16.33</v>
@@ -5816,7 +5816,7 @@
         <v>8.32</v>
       </c>
       <c r="I70" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J70" t="n">
         <v>16.6</v>
@@ -5891,7 +5891,7 @@
         <v>4.28</v>
       </c>
       <c r="I71" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J71" t="n">
         <v>16.92</v>
@@ -5966,7 +5966,7 @@
         <v>-1.47</v>
       </c>
       <c r="I72" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J72" t="n">
         <v>17.19</v>
@@ -6041,7 +6041,7 @@
         <v>1.98</v>
       </c>
       <c r="I73" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J73" t="n">
         <v>17.47</v>
@@ -6116,7 +6116,7 @@
         <v>7.33</v>
       </c>
       <c r="I74" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J74" t="n">
         <v>17.79</v>
@@ -6191,7 +6191,7 @@
         <v>6.34</v>
       </c>
       <c r="I75" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J75" t="n">
         <v>18.03</v>
@@ -6266,7 +6266,7 @@
         <v>-1.15</v>
       </c>
       <c r="I76" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J76" t="n">
         <v>18.18</v>
@@ -6341,7 +6341,7 @@
         <v>0.23</v>
       </c>
       <c r="I77" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J77" t="n">
         <v>18.32</v>
@@ -6416,7 +6416,7 @@
         <v>-7.59</v>
       </c>
       <c r="I78" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J78" t="n">
         <v>18.4</v>
@@ -6495,7 +6495,7 @@
         <v>9.27</v>
       </c>
       <c r="I79" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J79" t="n">
         <v>18.57</v>
@@ -6570,7 +6570,7 @@
         <v>-2.2</v>
       </c>
       <c r="I80" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J80" t="n">
         <v>18.74</v>
@@ -6645,7 +6645,7 @@
         <v>0.89</v>
       </c>
       <c r="I81" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J81" t="n">
         <v>18.92</v>
@@ -6720,7 +6720,7 @@
         <v>-1.86</v>
       </c>
       <c r="I82" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J82" t="n">
         <v>19.13</v>
@@ -6795,7 +6795,7 @@
         <v>1.75</v>
       </c>
       <c r="I83" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J83" t="n">
         <v>19.38</v>
@@ -6870,7 +6870,7 @@
         <v>11.35</v>
       </c>
       <c r="I84" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J84" t="n">
         <v>19.8</v>
@@ -6945,7 +6945,7 @@
         <v>2.63</v>
       </c>
       <c r="I85" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J85" t="n">
         <v>20.16</v>
@@ -7020,7 +7020,7 @@
         <v>2.52</v>
       </c>
       <c r="I86" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J86" t="n">
         <v>20.57</v>
@@ -7095,7 +7095,7 @@
         <v>-0.36</v>
       </c>
       <c r="I87" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J87" t="n">
         <v>20.97</v>
@@ -7170,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J88" t="n">
         <v>21.42</v>
@@ -7245,7 +7245,7 @@
         <v>-1.59</v>
       </c>
       <c r="I89" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J89" t="n">
         <v>21.81</v>
@@ -7320,7 +7320,7 @@
         <v>5.43</v>
       </c>
       <c r="I90" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J90" t="n">
         <v>22.2</v>
@@ -7395,7 +7395,7 @@
         <v>1.46</v>
       </c>
       <c r="I91" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J91" t="n">
         <v>22.57</v>
@@ -7470,7 +7470,7 @@
         <v>-5.53</v>
       </c>
       <c r="I92" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J92" t="n">
         <v>22.89</v>
@@ -7545,7 +7545,7 @@
         <v>5.61</v>
       </c>
       <c r="I93" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J93" t="n">
         <v>23.25</v>
@@ -7620,7 +7620,7 @@
         <v>1.02</v>
       </c>
       <c r="I94" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J94" t="n">
         <v>23.55</v>
@@ -7695,7 +7695,7 @@
         <v>2.7</v>
       </c>
       <c r="I95" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J95" t="n">
         <v>23.83</v>
@@ -7770,7 +7770,7 @@
         <v>-0.29</v>
       </c>
       <c r="I96" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J96" t="n">
         <v>24.12</v>
@@ -7845,7 +7845,7 @@
         <v>-2.9</v>
       </c>
       <c r="I97" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J97" t="n">
         <v>24.36</v>
@@ -7920,7 +7920,7 @@
         <v>2.98</v>
       </c>
       <c r="I98" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J98" t="n">
         <v>24.72</v>
@@ -7995,7 +7995,7 @@
         <v>-0.95</v>
       </c>
       <c r="I99" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J99" t="n">
         <v>24.98</v>
@@ -8070,7 +8070,7 @@
         <v>1.07</v>
       </c>
       <c r="I100" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J100" t="n">
         <v>25.28</v>
@@ -8145,7 +8145,7 @@
         <v>0.04</v>
       </c>
       <c r="I101" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J101" t="n">
         <v>25.57</v>
@@ -8220,7 +8220,7 @@
         <v>0.62</v>
       </c>
       <c r="I102" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J102" t="n">
         <v>25.89</v>
@@ -8295,7 +8295,7 @@
         <v>-4.26</v>
       </c>
       <c r="I103" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J103" t="n">
         <v>26.13</v>
@@ -8370,7 +8370,7 @@
         <v>-2.05</v>
       </c>
       <c r="I104" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J104" t="n">
         <v>26.22</v>
@@ -8449,7 +8449,7 @@
         <v>-0.62</v>
       </c>
       <c r="I105" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J105" t="n">
         <v>26.27</v>
@@ -8524,7 +8524,7 @@
         <v>-0.08</v>
       </c>
       <c r="I106" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J106" t="n">
         <v>26.29</v>
@@ -8599,7 +8599,7 @@
         <v>4.96</v>
       </c>
       <c r="I107" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J107" t="n">
         <v>26.38</v>
@@ -8674,7 +8674,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I108" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J108" t="n">
         <v>26.48</v>
@@ -8749,7 +8749,7 @@
         <v>2.15</v>
       </c>
       <c r="I109" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J109" t="n">
         <v>26.62</v>
@@ -8824,7 +8824,7 @@
         <v>-9.5</v>
       </c>
       <c r="I110" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J110" t="n">
         <v>26.57</v>
@@ -8903,7 +8903,7 @@
         <v>-3.61</v>
       </c>
       <c r="I111" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J111" t="n">
         <v>26.45</v>
@@ -8978,7 +8978,7 @@
         <v>3.82</v>
       </c>
       <c r="I112" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J112" t="n">
         <v>26.45</v>
@@ -9053,7 +9053,7 @@
         <v>-1.92</v>
       </c>
       <c r="I113" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J113" t="n">
         <v>26.36</v>
@@ -9128,7 +9128,7 @@
         <v>-2.16</v>
       </c>
       <c r="I114" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J114" t="n">
         <v>26.23</v>
@@ -9203,7 +9203,7 @@
         <v>4.21</v>
       </c>
       <c r="I115" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J115" t="n">
         <v>26.11</v>
@@ -9278,7 +9278,7 @@
         <v>2.84</v>
       </c>
       <c r="I116" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J116" t="n">
         <v>26.03</v>
@@ -9353,7 +9353,7 @@
         <v>-0.39</v>
       </c>
       <c r="I117" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J117" t="n">
         <v>25.99</v>
@@ -9428,7 +9428,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I118" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J118" t="n">
         <v>26.02</v>
@@ -9503,7 +9503,7 @@
         <v>4.54</v>
       </c>
       <c r="I119" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J119" t="n">
         <v>26.13</v>
@@ -9578,7 +9578,7 @@
         <v>0.51</v>
       </c>
       <c r="I120" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J120" t="n">
         <v>26.24</v>
@@ -9653,7 +9653,7 @@
         <v>-6.98</v>
       </c>
       <c r="I121" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J121" t="n">
         <v>26.24</v>
@@ -9728,7 +9728,7 @@
         <v>0.59</v>
       </c>
       <c r="I122" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J122" t="n">
         <v>26.24</v>
@@ -9803,7 +9803,7 @@
         <v>-4.65</v>
       </c>
       <c r="I123" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J123" t="n">
         <v>26.24</v>
@@ -9882,7 +9882,7 @@
         <v>-1.68</v>
       </c>
       <c r="I124" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J124" t="n">
         <v>26.24</v>
@@ -9957,7 +9957,7 @@
         <v>-1.75</v>
       </c>
       <c r="I125" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J125" t="n">
         <v>26.23</v>
@@ -10032,7 +10032,7 @@
         <v>8.25</v>
       </c>
       <c r="I126" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J126" t="n">
         <v>26.32</v>
@@ -10107,7 +10107,7 @@
         <v>-0.55</v>
       </c>
       <c r="I127" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J127" t="n">
         <v>26.34</v>
@@ -10182,7 +10182,7 @@
         <v>2.35</v>
       </c>
       <c r="I128" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J128" t="n">
         <v>26.38</v>
@@ -10257,7 +10257,7 @@
         <v>0.86</v>
       </c>
       <c r="I129" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J129" t="n">
         <v>26.41</v>
@@ -10332,7 +10332,7 @@
         <v>1.24</v>
       </c>
       <c r="I130" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J130" t="n">
         <v>26.59</v>
@@ -10407,7 +10407,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J131" t="n">
         <v>26.69</v>
@@ -10486,7 +10486,7 @@
         <v>-3.04</v>
       </c>
       <c r="I132" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J132" t="n">
         <v>26.7</v>
@@ -10565,7 +10565,7 @@
         <v>-1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J133" t="n">
         <v>26.72</v>
@@ -10640,7 +10640,7 @@
         <v>2.97</v>
       </c>
       <c r="I134" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J134" t="n">
         <v>26.8</v>
@@ -10715,7 +10715,7 @@
         <v>3.08</v>
       </c>
       <c r="I135" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J135" t="n">
         <v>26.87</v>
@@ -10790,7 +10790,7 @@
         <v>2.38</v>
       </c>
       <c r="I136" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J136" t="n">
         <v>26.94</v>
@@ -10865,7 +10865,7 @@
         <v>0.37</v>
       </c>
       <c r="I137" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J137" t="n">
         <v>27.02</v>
@@ -10940,7 +10940,7 @@
         <v>5.23</v>
       </c>
       <c r="I138" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J138" t="n">
         <v>27.05</v>
@@ -11015,7 +11015,7 @@
         <v>2</v>
       </c>
       <c r="I139" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J139" t="n">
         <v>27.05</v>
@@ -11090,7 +11090,7 @@
         <v>0.45</v>
       </c>
       <c r="I140" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J140" t="n">
         <v>27.04</v>
@@ -11165,7 +11165,7 @@
         <v>2.39</v>
       </c>
       <c r="I141" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J141" t="n">
         <v>27.17</v>
@@ -11240,7 +11240,7 @@
         <v>1.6</v>
       </c>
       <c r="I142" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J142" t="n">
         <v>27.32</v>
@@ -11315,7 +11315,7 @@
         <v>-0.03</v>
       </c>
       <c r="I143" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J143" t="n">
         <v>27.53</v>
@@ -11390,7 +11390,7 @@
         <v>10.41</v>
       </c>
       <c r="I144" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J144" t="n">
         <v>27.92</v>
@@ -11465,7 +11465,7 @@
         <v>-1.84</v>
       </c>
       <c r="I145" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J145" t="n">
         <v>28.3</v>
@@ -11540,7 +11540,7 @@
         <v>4.27</v>
       </c>
       <c r="I146" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J146" t="n">
         <v>28.65</v>
@@ -11615,7 +11615,7 @@
         <v>-0.35</v>
       </c>
       <c r="I147" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J147" t="n">
         <v>29</v>
@@ -11690,7 +11690,7 @@
         <v>-0.29</v>
       </c>
       <c r="I148" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J148" t="n">
         <v>29.32</v>
@@ -11765,7 +11765,7 @@
         <v>-1.02</v>
       </c>
       <c r="I149" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J149" t="n">
         <v>29.6</v>
@@ -11840,7 +11840,7 @@
         <v>0.5</v>
       </c>
       <c r="I150" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J150" t="n">
         <v>29.88</v>
@@ -11915,7 +11915,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J151" t="n">
         <v>30.28</v>
@@ -11990,7 +11990,7 @@
         <v>2.41</v>
       </c>
       <c r="I152" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J152" t="n">
         <v>30.75</v>
@@ -12065,7 +12065,7 @@
         <v>5.8</v>
       </c>
       <c r="I153" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J153" t="n">
         <v>31.35</v>
@@ -12140,7 +12140,7 @@
         <v>6</v>
       </c>
       <c r="I154" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J154" t="n">
         <v>32.02</v>
@@ -12215,7 +12215,7 @@
         <v>-2.18</v>
       </c>
       <c r="I155" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J155" t="n">
         <v>32.61</v>
@@ -12290,7 +12290,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J156" t="n">
         <v>33.34</v>
@@ -12365,7 +12365,7 @@
         <v>-6.91</v>
       </c>
       <c r="I157" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J157" t="n">
         <v>33.93</v>
@@ -12440,7 +12440,7 @@
         <v>10.18</v>
       </c>
       <c r="I158" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J158" t="n">
         <v>34.64</v>
@@ -12515,7 +12515,7 @@
         <v>-1.26</v>
       </c>
       <c r="I159" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J159" t="n">
         <v>35.29</v>
@@ -12590,7 +12590,7 @@
         <v>-19</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>35.53</v>
@@ -12669,7 +12669,7 @@
         <v>14.39</v>
       </c>
       <c r="I161" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J161" t="n">
         <v>35.99</v>
@@ -12744,7 +12744,7 @@
         <v>-6.39</v>
       </c>
       <c r="I162" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J162" t="n">
         <v>36.3</v>
@@ -12819,7 +12819,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="I163" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J163" t="n">
         <v>36.78</v>
@@ -12894,7 +12894,7 @@
         <v>1.48</v>
       </c>
       <c r="I164" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J164" t="n">
         <v>37.12</v>
@@ -12969,7 +12969,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J165" t="n">
         <v>37.48</v>
@@ -13044,7 +13044,7 @@
         <v>4.84</v>
       </c>
       <c r="I166" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J166" t="n">
         <v>37.88</v>
@@ -13119,7 +13119,7 @@
         <v>-1.73</v>
       </c>
       <c r="I167" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J167" t="n">
         <v>38.24</v>
@@ -13194,7 +13194,7 @@
         <v>-7.52</v>
       </c>
       <c r="I168" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J168" t="n">
         <v>38.44</v>
@@ -13273,7 +13273,7 @@
         <v>7.25</v>
       </c>
       <c r="I169" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J169" t="n">
         <v>38.81</v>
@@ -13348,7 +13348,7 @@
         <v>4.79</v>
       </c>
       <c r="I170" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J170" t="n">
         <v>39.27</v>
@@ -13423,7 +13423,7 @@
         <v>8.58</v>
       </c>
       <c r="I171" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J171" t="n">
         <v>39.91</v>
@@ -13498,7 +13498,7 @@
         <v>0.26</v>
       </c>
       <c r="I172" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J172" t="n">
         <v>40.51</v>
@@ -13573,7 +13573,7 @@
         <v>5.16</v>
       </c>
       <c r="I173" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J173" t="n">
         <v>41.14</v>
@@ -13648,7 +13648,7 @@
         <v>-4.03</v>
       </c>
       <c r="I174" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J174" t="n">
         <v>41.55</v>
@@ -13723,7 +13723,7 @@
         <v>0.82</v>
       </c>
       <c r="I175" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J175" t="n">
         <v>42.03</v>
@@ -13798,7 +13798,7 @@
         <v>1.68</v>
       </c>
       <c r="I176" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J176" t="n">
         <v>42.37</v>
@@ -13873,7 +13873,7 @@
         <v>-11.91</v>
       </c>
       <c r="I177" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J177" t="n">
         <v>42.57</v>
@@ -13948,7 +13948,7 @@
         <v>9.42</v>
       </c>
       <c r="I178" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J178" t="n">
         <v>42.77</v>
@@ -14023,7 +14023,7 @@
         <v>-8.16</v>
       </c>
       <c r="I179" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J179" t="n">
         <v>42.81</v>
@@ -14098,7 +14098,7 @@
         <v>-2.95</v>
       </c>
       <c r="I180" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J180" t="n">
         <v>43.19</v>
@@ -14177,7 +14177,7 @@
         <v>7.72</v>
       </c>
       <c r="I181" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J181" t="n">
         <v>43.48</v>
@@ -14252,7 +14252,7 @@
         <v>-7.01</v>
       </c>
       <c r="I182" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J182" t="n">
         <v>43.74</v>
@@ -14331,7 +14331,7 @@
         <v>4.55</v>
       </c>
       <c r="I183" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J183" t="n">
         <v>43.92</v>
@@ -14406,7 +14406,7 @@
         <v>-10.28</v>
       </c>
       <c r="I184" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J184" t="n">
         <v>43.86</v>
@@ -14481,7 +14481,7 @@
         <v>-0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J185" t="n">
         <v>43.79</v>
@@ -14556,7 +14556,7 @@
         <v>-5.18</v>
       </c>
       <c r="I186" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J186" t="n">
         <v>43.52</v>
@@ -14631,7 +14631,7 @@
         <v>-6.76</v>
       </c>
       <c r="I187" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J187" t="n">
         <v>43.16</v>
@@ -14710,7 +14710,7 @@
         <v>4.69</v>
       </c>
       <c r="I188" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J188" t="n">
         <v>43.04</v>
@@ -14785,7 +14785,7 @@
         <v>-14.33</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>42.52</v>
@@ -14868,7 +14868,7 @@
         <v>2.99</v>
       </c>
       <c r="I190" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J190" t="n">
         <v>41.95</v>
@@ -14943,7 +14943,7 @@
         <v>13.02</v>
       </c>
       <c r="I191" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J191" t="n">
         <v>41.4</v>
@@ -15018,7 +15018,7 @@
         <v>0.86</v>
       </c>
       <c r="I192" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J192" t="n">
         <v>40.86</v>
@@ -15093,7 +15093,7 @@
         <v>8.33</v>
       </c>
       <c r="I193" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J193" t="n">
         <v>40.35</v>
@@ -15168,7 +15168,7 @@
         <v>5.29</v>
       </c>
       <c r="I194" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J194" t="n">
         <v>40.05</v>
@@ -15243,7 +15243,7 @@
         <v>0.12</v>
       </c>
       <c r="I195" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J195" t="n">
         <v>39.72</v>
@@ -15318,7 +15318,7 @@
         <v>6.03</v>
       </c>
       <c r="I196" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J196" t="n">
         <v>39.48</v>
@@ -15393,7 +15393,7 @@
         <v>6.35</v>
       </c>
       <c r="I197" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J197" t="n">
         <v>39.67</v>
@@ -15468,7 +15468,7 @@
         <v>-3.05</v>
       </c>
       <c r="I198" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J198" t="n">
         <v>39.59</v>
@@ -15543,7 +15543,7 @@
         <v>2.97</v>
       </c>
       <c r="I199" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J199" t="n">
         <v>39.76</v>
@@ -15618,7 +15618,7 @@
         <v>3.21</v>
       </c>
       <c r="I200" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J200" t="n">
         <v>40.08</v>
@@ -15693,7 +15693,7 @@
         <v>-0.42</v>
       </c>
       <c r="I201" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J201" t="n">
         <v>40.22</v>
@@ -15768,7 +15768,7 @@
         <v>3.89</v>
       </c>
       <c r="I202" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J202" t="n">
         <v>40.61</v>
@@ -15843,7 +15843,7 @@
         <v>-1.73</v>
       </c>
       <c r="I203" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J203" t="n">
         <v>40.86</v>
@@ -15918,7 +15918,7 @@
         <v>-14.52</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>40.99</v>
@@ -15993,7 +15993,7 @@
         <v>-1.27</v>
       </c>
       <c r="I205" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J205" t="n">
         <v>41.1</v>
@@ -16068,7 +16068,7 @@
         <v>-1.68</v>
       </c>
       <c r="I206" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J206" t="n">
         <v>41.29</v>
@@ -16147,7 +16147,7 @@
         <v>-11.05</v>
       </c>
       <c r="I207" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J207" t="n">
         <v>41.37</v>
@@ -16222,7 +16222,7 @@
         <v>7.11</v>
       </c>
       <c r="I208" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J208" t="n">
         <v>41.5</v>
@@ -16297,7 +16297,7 @@
         <v>8.15</v>
       </c>
       <c r="I209" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J209" t="n">
         <v>42.05</v>
@@ -16372,7 +16372,7 @@
         <v>3.69</v>
       </c>
       <c r="I210" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J210" t="n">
         <v>42.62</v>
@@ -16447,7 +16447,7 @@
         <v>1.02</v>
       </c>
       <c r="I211" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J211" t="n">
         <v>43.01</v>
@@ -16522,7 +16522,7 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J212" t="n">
         <v>43.41</v>
@@ -16597,7 +16597,7 @@
         <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J213" t="n">
         <v>43.67</v>
@@ -16672,7 +16672,7 @@
         <v>-0.88</v>
       </c>
       <c r="I214" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J214" t="n">
         <v>43.79</v>
@@ -16747,7 +16747,7 @@
         <v>-0.34</v>
       </c>
       <c r="I215" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J215" t="n">
         <v>43.91</v>
@@ -16826,7 +16826,7 @@
         <v>-3.76</v>
       </c>
       <c r="I216" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J216" t="n">
         <v>43.82</v>
@@ -16901,7 +16901,7 @@
         <v>12.4</v>
       </c>
       <c r="I217" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J217" t="n">
         <v>43.86</v>
@@ -16976,7 +16976,7 @@
         <v>4.19</v>
       </c>
       <c r="I218" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J218" t="n">
         <v>44.06</v>
@@ -17051,7 +17051,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I219" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J219" t="n">
         <v>44.43</v>
@@ -17126,7 +17126,7 @@
         <v>-3.17</v>
       </c>
       <c r="I220" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J220" t="n">
         <v>44.65</v>
@@ -17201,7 +17201,7 @@
         <v>-5.05</v>
       </c>
       <c r="I221" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J221" t="n">
         <v>44.74</v>
@@ -17276,7 +17276,7 @@
         <v>8.65</v>
       </c>
       <c r="I222" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J222" t="n">
         <v>44.96</v>
@@ -17351,7 +17351,7 @@
         <v>1.3</v>
       </c>
       <c r="I223" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J223" t="n">
         <v>45.25</v>
@@ -17426,7 +17426,7 @@
         <v>2.6</v>
       </c>
       <c r="I224" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J224" t="n">
         <v>45.97</v>
@@ -17501,7 +17501,7 @@
         <v>-1.23</v>
       </c>
       <c r="I225" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J225" t="n">
         <v>46.68</v>
@@ -17576,7 +17576,7 @@
         <v>4.88</v>
       </c>
       <c r="I226" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J226" t="n">
         <v>47.56</v>
@@ -17651,7 +17651,7 @@
         <v>4.6</v>
       </c>
       <c r="I227" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J227" t="n">
         <v>48.79</v>
@@ -17726,7 +17726,7 @@
         <v>-4.63</v>
       </c>
       <c r="I228" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J228" t="n">
         <v>49.76</v>
@@ -17801,7 +17801,7 @@
         <v>9.57</v>
       </c>
       <c r="I229" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J229" t="n">
         <v>50.85</v>
@@ -17876,7 +17876,7 @@
         <v>0.38</v>
       </c>
       <c r="I230" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J230" t="n">
         <v>51.87</v>
@@ -17951,7 +17951,7 @@
         <v>-3.33</v>
       </c>
       <c r="I231" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J231" t="n">
         <v>52.76</v>
@@ -18026,7 +18026,7 @@
         <v>-1.46</v>
       </c>
       <c r="I232" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J232" t="n">
         <v>53.59</v>
@@ -18101,7 +18101,7 @@
         <v>7.02</v>
       </c>
       <c r="I233" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J233" t="n">
         <v>54.62</v>
@@ -18176,7 +18176,7 @@
         <v>7.89</v>
       </c>
       <c r="I234" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J234" t="n">
         <v>55.94</v>
@@ -18251,7 +18251,7 @@
         <v>0.54</v>
       </c>
       <c r="I235" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J235" t="n">
         <v>57.28</v>
@@ -18326,7 +18326,7 @@
         <v>-12.31</v>
       </c>
       <c r="I236" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J236" t="n">
         <v>58.26</v>
@@ -18401,7 +18401,7 @@
         <v>5.52</v>
       </c>
       <c r="I237" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J237" t="n">
         <v>59.16</v>
@@ -18476,7 +18476,7 @@
         <v>-6.14</v>
       </c>
       <c r="I238" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J238" t="n">
         <v>59.76</v>
@@ -18551,7 +18551,7 @@
         <v>-13.08</v>
       </c>
       <c r="I239" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J239" t="n">
         <v>59.72</v>
@@ -18630,7 +18630,7 @@
         <v>0.11</v>
       </c>
       <c r="I240" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J240" t="n">
         <v>59.77</v>
@@ -18705,7 +18705,7 @@
         <v>15.95</v>
       </c>
       <c r="I241" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J241" t="n">
         <v>60.37</v>
@@ -18780,7 +18780,7 @@
         <v>3.69</v>
       </c>
       <c r="I242" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J242" t="n">
         <v>60.88</v>
@@ -18855,7 +18855,7 @@
         <v>-1.08</v>
       </c>
       <c r="I243" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J243" t="n">
         <v>61.31</v>
@@ -18930,7 +18930,7 @@
         <v>7.44</v>
       </c>
       <c r="I244" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J244" t="n">
         <v>61.91</v>
@@ -19005,7 +19005,7 @@
         <v>-7.28</v>
       </c>
       <c r="I245" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J245" t="n">
         <v>62.29</v>
@@ -19080,7 +19080,7 @@
         <v>2.36</v>
       </c>
       <c r="I246" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J246" t="n">
         <v>62.62</v>
@@ -19155,7 +19155,7 @@
         <v>-0.37</v>
       </c>
       <c r="I247" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J247" t="n">
         <v>62.8</v>
@@ -19230,7 +19230,7 @@
         <v>3.02</v>
       </c>
       <c r="I248" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J248" t="n">
         <v>63.22</v>
@@ -19305,7 +19305,7 @@
         <v>-1.6</v>
       </c>
       <c r="I249" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J249" t="n">
         <v>63.31</v>
@@ -19380,7 +19380,7 @@
         <v>2.88</v>
       </c>
       <c r="I250" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J250" t="n">
         <v>63.47</v>
@@ -19455,7 +19455,7 @@
         <v>-1.86</v>
       </c>
       <c r="I251" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J251" t="n">
         <v>63.69</v>
@@ -19530,7 +19530,7 @@
         <v>4.06</v>
       </c>
       <c r="I252" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J252" t="n">
         <v>64.08</v>
@@ -19605,7 +19605,7 @@
         <v>4.85</v>
       </c>
       <c r="I253" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J253" t="n">
         <v>64.42</v>
@@ -19680,7 +19680,7 @@
         <v>-9.07</v>
       </c>
       <c r="I254" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J254" t="n">
         <v>64.19</v>
@@ -19755,7 +19755,7 @@
         <v>-3.94</v>
       </c>
       <c r="I255" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J255" t="n">
         <v>63.8</v>
@@ -19834,7 +19834,7 @@
         <v>-0.02</v>
       </c>
       <c r="I256" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J256" t="n">
         <v>63.85</v>
@@ -19909,7 +19909,7 @@
         <v>-14.89</v>
       </c>
       <c r="I257" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J257" s="4" t="n">
         <v>63.26</v>
@@ -19988,7 +19988,7 @@
         <v>5.99</v>
       </c>
       <c r="I258" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J258" t="n">
         <v>63.03</v>
@@ -20063,7 +20063,7 @@
         <v>-3.22</v>
       </c>
       <c r="I259" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J259" t="n">
         <v>63.11</v>
@@ -20142,7 +20142,7 @@
         <v>-12.6</v>
       </c>
       <c r="I260" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J260" t="n">
         <v>62.84</v>
@@ -20221,7 +20221,7 @@
         <v>11.35</v>
       </c>
       <c r="I261" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J261" t="n">
         <v>62.42</v>
@@ -20296,7 +20296,7 @@
         <v>2.36</v>
       </c>
       <c r="I262" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J262" t="n">
         <v>61.95</v>
@@ -20371,7 +20371,7 @@
         <v>2.75</v>
       </c>
       <c r="I263" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J263" t="n">
         <v>61.59</v>
@@ -20446,7 +20446,7 @@
         <v>-10.35</v>
       </c>
       <c r="I264" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J264" t="n">
         <v>60.7</v>
@@ -20519,7 +20519,7 @@
         <v>0.88</v>
       </c>
       <c r="I265" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J265" t="n">
         <v>60.08</v>
@@ -20598,7 +20598,7 @@
         <v>5.84</v>
       </c>
       <c r="I266" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J266" t="n">
         <v>59.54</v>
@@ -20673,7 +20673,7 @@
         <v>2.35</v>
       </c>
       <c r="I267" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J267" t="n">
         <v>59.07</v>
@@ -20748,7 +20748,7 @@
         <v>-1.69</v>
       </c>
       <c r="I268" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J268" t="n">
         <v>58.45</v>
@@ -20823,7 +20823,7 @@
         <v>1.54</v>
       </c>
       <c r="I269" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J269" t="n">
         <v>57.93</v>
@@ -20898,7 +20898,7 @@
         <v>-6.75</v>
       </c>
       <c r="I270" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J270" t="n">
         <v>57.14</v>
@@ -20977,7 +20977,7 @@
         <v>3.7</v>
       </c>
       <c r="I271" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J271" t="n">
         <v>56.5</v>
@@ -21052,7 +21052,7 @@
         <v>3.62</v>
       </c>
       <c r="I272" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J272" t="n">
         <v>55.82</v>
@@ -21127,7 +21127,7 @@
         <v>3.79</v>
       </c>
       <c r="I273" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J273" t="n">
         <v>55.08</v>
@@ -21202,7 +21202,7 @@
         <v>-14.14</v>
       </c>
       <c r="I274" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J274" t="n">
         <v>54.26</v>
@@ -21281,7 +21281,7 @@
         <v>-4.82</v>
       </c>
       <c r="I275" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J275" t="n">
         <v>53.45</v>
@@ -21360,7 +21360,7 @@
         <v>-12.86</v>
       </c>
       <c r="I276" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J276" t="n">
         <v>52.34</v>
@@ -21435,7 +21435,7 @@
         <v>17.96</v>
       </c>
       <c r="I277" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J277" t="n">
         <v>52.07</v>
@@ -21510,7 +21510,7 @@
         <v>9.09</v>
       </c>
       <c r="I278" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J278" t="n">
         <v>51.85</v>
@@ -21585,7 +21585,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J279" t="n">
         <v>51.75</v>
@@ -21660,7 +21660,7 @@
         <v>3.89</v>
       </c>
       <c r="I280" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J280" t="n">
         <v>52.1</v>
@@ -21735,7 +21735,7 @@
         <v>3.18</v>
       </c>
       <c r="I281" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J281" t="n">
         <v>52.26</v>
@@ -21814,7 +21814,7 @@
         <v>19.38</v>
       </c>
       <c r="I282" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J282" t="n">
         <v>52.9</v>
@@ -21889,7 +21889,7 @@
         <v>6.63</v>
       </c>
       <c r="I283" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J283" t="n">
         <v>53.7</v>
@@ -21964,7 +21964,7 @@
         <v>6.13</v>
       </c>
       <c r="I284" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J284" t="n">
         <v>55</v>
@@ -22039,7 +22039,7 @@
         <v>5.46</v>
       </c>
       <c r="I285" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J285" t="n">
         <v>56.49</v>
@@ -22114,7 +22114,7 @@
         <v>5.89</v>
       </c>
       <c r="I286" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J286" t="n">
         <v>58.07</v>
@@ -22189,7 +22189,7 @@
         <v>0.76</v>
       </c>
       <c r="I287" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J287" t="n">
         <v>59.62</v>
@@ -22264,7 +22264,7 @@
         <v>2.81</v>
       </c>
       <c r="I288" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J288" t="n">
         <v>61.34</v>
@@ -22339,7 +22339,7 @@
         <v>7.15</v>
       </c>
       <c r="I289" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J289" t="n">
         <v>63.33</v>
@@ -22414,7 +22414,7 @@
         <v>1.33</v>
       </c>
       <c r="I290" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J290" t="n">
         <v>65.56999999999999</v>
@@ -22489,7 +22489,7 @@
         <v>2.24</v>
       </c>
       <c r="I291" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J291" t="n">
         <v>67.81999999999999</v>
@@ -22564,7 +22564,7 @@
         <v>7.69</v>
       </c>
       <c r="I292" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J292" t="n">
         <v>70.34999999999999</v>
@@ -22639,7 +22639,7 @@
         <v>6.75</v>
       </c>
       <c r="I293" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J293" t="n">
         <v>73.14</v>
@@ -22714,7 +22714,7 @@
         <v>13.79</v>
       </c>
       <c r="I294" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J294" t="n">
         <v>77.09999999999999</v>
@@ -22789,7 +22789,7 @@
         <v>-3.84</v>
       </c>
       <c r="I295" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J295" t="n">
         <v>80.94</v>
@@ -22864,7 +22864,7 @@
         <v>-11.21</v>
       </c>
       <c r="I296" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J296" t="n">
         <v>84.38</v>
@@ -22939,7 +22939,7 @@
         <v>7.67</v>
       </c>
       <c r="I297" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J297" t="n">
         <v>87.88</v>
@@ -23014,7 +23014,7 @@
         <v>7.64</v>
       </c>
       <c r="I298" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J298" t="n">
         <v>91.62</v>
@@ -23089,7 +23089,7 @@
         <v>2.69</v>
       </c>
       <c r="I299" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J299" t="n">
         <v>95.5</v>
@@ -23164,7 +23164,7 @@
         <v>-2.18</v>
       </c>
       <c r="I300" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J300" t="n">
         <v>99.13</v>
@@ -23239,7 +23239,7 @@
         <v>13.02</v>
       </c>
       <c r="I301" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J301" t="n">
         <v>103.51</v>
@@ -23314,7 +23314,7 @@
         <v>15.04</v>
       </c>
       <c r="I302" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J302" t="n">
         <v>108.42</v>
@@ -23389,7 +23389,7 @@
         <v>-8.289999999999999</v>
       </c>
       <c r="I303" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J303" t="n">
         <v>112.43</v>
@@ -23464,7 +23464,7 @@
         <v>16.33</v>
       </c>
       <c r="I304" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J304" t="n">
         <v>117.45</v>
@@ -23539,7 +23539,7 @@
         <v>7.62</v>
       </c>
       <c r="I305" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J305" t="n">
         <v>122.94</v>
@@ -23614,7 +23614,7 @@
         <v>-9.4</v>
       </c>
       <c r="I306" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J306" t="n">
         <v>127.3</v>
@@ -23689,7 +23689,7 @@
         <v>6.79</v>
       </c>
       <c r="I307" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J307" t="n">
         <v>132.21</v>
@@ -23764,7 +23764,7 @@
         <v>1.06</v>
       </c>
       <c r="I308" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J308" t="n">
         <v>137.1</v>
@@ -23839,7 +23839,7 @@
         <v>-11.82</v>
       </c>
       <c r="I309" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J309" t="n">
         <v>140.57</v>
@@ -23914,7 +23914,7 @@
         <v>-7.57</v>
       </c>
       <c r="I310" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J310" t="n">
         <v>143.36</v>
@@ -23989,7 +23989,7 @@
         <v>0.09</v>
       </c>
       <c r="I311" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J311" t="n">
         <v>146.05</v>
@@ -24064,7 +24064,7 @@
         <v>14.03</v>
       </c>
       <c r="I312" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J312" t="n">
         <v>149.42</v>
@@ -24139,7 +24139,7 @@
         <v>2.99</v>
       </c>
       <c r="I313" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J313" t="n">
         <v>152.7</v>
@@ -24214,7 +24214,7 @@
         <v>6.83</v>
       </c>
       <c r="I314" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J314" t="n">
         <v>155.81</v>
@@ -24289,7 +24289,7 @@
         <v>18.48</v>
       </c>
       <c r="I315" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J315" t="n">
         <v>160.93</v>
@@ -24364,7 +24364,7 @@
         <v>-3.46</v>
       </c>
       <c r="I316" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J316" t="n">
         <v>166.34</v>
@@ -24439,7 +24439,7 @@
         <v>3.05</v>
       </c>
       <c r="I317" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J317" t="n">
         <v>171.67</v>
@@ -24514,7 +24514,7 @@
         <v>-0.13</v>
       </c>
       <c r="I318" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J318" t="n">
         <v>176.54</v>
@@ -24589,7 +24589,7 @@
         <v>1.2</v>
       </c>
       <c r="I319" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J319" t="n">
         <v>181.37</v>
@@ -24664,7 +24664,7 @@
         <v>17.31</v>
       </c>
       <c r="I320" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J320" t="n">
         <v>188.3</v>
@@ -24739,7 +24739,7 @@
         <v>5.34</v>
       </c>
       <c r="I321" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J321" t="n">
         <v>195.12</v>
@@ -24814,7 +24814,7 @@
         <v>-6.36</v>
       </c>
       <c r="I322" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J322" t="n">
         <v>199.96</v>
@@ -24889,7 +24889,7 @@
         <v>-30.51</v>
       </c>
       <c r="I323" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J323" s="4" t="n">
         <v>201.48</v>
@@ -24968,7 +24968,7 @@
         <v>15.83</v>
       </c>
       <c r="I324" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J324" t="n">
         <v>203.2</v>
@@ -25043,7 +25043,7 @@
         <v>-4.61</v>
       </c>
       <c r="I325" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J325" t="n">
         <v>203.76</v>
@@ -25122,7 +25122,7 @@
         <v>-10.43</v>
       </c>
       <c r="I326" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J326" t="n">
         <v>204.17</v>
@@ -25197,7 +25197,7 @@
         <v>23.99</v>
       </c>
       <c r="I327" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J327" t="n">
         <v>206.15</v>
@@ -25272,7 +25272,7 @@
         <v>4.78</v>
       </c>
       <c r="I328" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J328" t="n">
         <v>208.58</v>
@@ -25347,7 +25347,7 @@
         <v>16.11</v>
       </c>
       <c r="I329" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J329" t="n">
         <v>213.99</v>
@@ -25422,7 +25422,7 @@
         <v>-16.99</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>217.71</v>
@@ -25497,7 +25497,7 @@
         <v>3.39</v>
       </c>
       <c r="I331" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J331" t="n">
         <v>221.81</v>
@@ -25572,7 +25572,7 @@
         <v>19.43</v>
       </c>
       <c r="I332" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J332" t="n">
         <v>227.11</v>
@@ -25647,7 +25647,7 @@
         <v>7.69</v>
       </c>
       <c r="I333" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J333" t="n">
         <v>233.22</v>
@@ -25722,7 +25722,7 @@
         <v>-23.06</v>
       </c>
       <c r="I334" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J334" s="4" t="n">
         <v>235.26</v>
@@ -25801,7 +25801,7 @@
         <v>-0.8</v>
       </c>
       <c r="I335" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J335" t="n">
         <v>235.45</v>
@@ -25876,7 +25876,7 @@
         <v>10.03</v>
       </c>
       <c r="I336" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J336" t="n">
         <v>237.18</v>
@@ -25951,7 +25951,7 @@
         <v>-14.65</v>
       </c>
       <c r="I337" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J337" s="4" t="n">
         <v>236.73</v>
@@ -26030,7 +26030,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I338" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J338" t="n">
         <v>237.34</v>
@@ -26105,7 +26105,7 @@
         <v>12.76</v>
       </c>
       <c r="I339" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J339" t="n">
         <v>239.32</v>
@@ -26180,7 +26180,7 @@
         <v>-18.43</v>
       </c>
       <c r="I340" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J340" s="4" t="n">
         <v>236.89</v>
@@ -26259,7 +26259,7 @@
         <v>-16.59</v>
       </c>
       <c r="I341" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>231.94</v>
@@ -26334,7 +26334,7 @@
         <v>7.26</v>
       </c>
       <c r="I342" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J342" t="n">
         <v>228.54</v>
@@ -26409,7 +26409,7 @@
         <v>-15.09</v>
       </c>
       <c r="I343" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J343" s="4" t="n">
         <v>227.67</v>
@@ -26488,7 +26488,7 @@
         <v>5.78</v>
       </c>
       <c r="I344" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J344" t="n">
         <v>225.84</v>
@@ -26563,7 +26563,7 @@
         <v>10.08</v>
       </c>
       <c r="I345" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J345" t="n">
         <v>225.38</v>
@@ -26638,7 +26638,7 @@
         <v>-0.1</v>
       </c>
       <c r="I346" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J346" t="n">
         <v>225.96</v>
@@ -26713,7 +26713,7 @@
         <v>-13.99</v>
       </c>
       <c r="I347" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J347" t="n">
         <v>223.03</v>
@@ -26792,7 +26792,7 @@
         <v>6.83</v>
       </c>
       <c r="I348" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J348" t="n">
         <v>220.13</v>
@@ -26867,7 +26867,7 @@
         <v>-6.29</v>
       </c>
       <c r="I349" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J349" t="n">
         <v>214.79</v>
@@ -26942,7 +26942,7 @@
         <v>-13.93</v>
       </c>
       <c r="I350" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J350" t="n">
         <v>210.61</v>
@@ -27017,7 +27017,7 @@
         <v>-4.92</v>
       </c>
       <c r="I351" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J351" t="n">
         <v>205.69</v>
@@ -27092,7 +27092,7 @@
         <v>0.99</v>
       </c>
       <c r="I352" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J352" t="n">
         <v>198.57</v>
@@ -27167,7 +27167,7 @@
         <v>15.89</v>
       </c>
       <c r="I353" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J353" t="n">
         <v>191.46</v>
@@ -27242,7 +27242,7 @@
         <v>1.54</v>
       </c>
       <c r="I354" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J354" t="n">
         <v>187.94</v>
@@ -27317,7 +27317,7 @@
         <v>-2.16</v>
       </c>
       <c r="I355" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J355" t="n">
         <v>184.34</v>
@@ -27392,7 +27392,7 @@
         <v>-13.14</v>
       </c>
       <c r="I356" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J356" t="n">
         <v>178.56</v>
@@ -27467,7 +27467,7 @@
         <v>-6.33</v>
       </c>
       <c r="I357" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J357" t="n">
         <v>174.19</v>
@@ -27546,7 +27546,7 @@
         <v>-14.52</v>
       </c>
       <c r="I358" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J358" s="4" t="n">
         <v>167.84</v>
@@ -27621,7 +27621,7 @@
         <v>-16.02</v>
       </c>
       <c r="I359" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J359" s="4" t="n">
         <v>159.11</v>
@@ -27700,7 +27700,7 @@
         <v>24.7</v>
       </c>
       <c r="I360" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J360" t="n">
         <v>153.97</v>
@@ -27775,7 +27775,7 @@
         <v>0</v>
       </c>
       <c r="I361" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J361" t="n">
         <v>150.64</v>
@@ -27850,7 +27850,7 @@
         <v>1.74</v>
       </c>
       <c r="I362" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J362" t="n">
         <v>146.74</v>
@@ -27925,7 +27925,7 @@
         <v>19.87</v>
       </c>
       <c r="I363" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J363" t="n">
         <v>145.48</v>
@@ -28000,7 +28000,7 @@
         <v>-5.6</v>
       </c>
       <c r="I364" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J364" t="n">
         <v>143.34</v>
@@ -28079,7 +28079,7 @@
         <v>0.2</v>
       </c>
       <c r="I365" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J365" t="n">
         <v>140.34</v>
@@ -28154,7 +28154,7 @@
         <v>5.99</v>
       </c>
       <c r="I366" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J366" t="n">
         <v>137.74</v>
@@ -28229,7 +28229,7 @@
         <v>-7.31</v>
       </c>
       <c r="I367" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J367" t="n">
         <v>135.97</v>
@@ -28308,7 +28308,7 @@
         <v>2.31</v>
       </c>
       <c r="I368" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J368" t="n">
         <v>133.79</v>
@@ -28383,7 +28383,7 @@
         <v>6.89</v>
       </c>
       <c r="I369" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J369" t="n">
         <v>132.62</v>
@@ -28458,7 +28458,7 @@
         <v>2.25</v>
       </c>
       <c r="I370" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J370" t="n">
         <v>132.76</v>
@@ -28533,7 +28533,7 @@
         <v>-0.28</v>
       </c>
       <c r="I371" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J371" t="n">
         <v>133.24</v>
@@ -28608,7 +28608,7 @@
         <v>4.54</v>
       </c>
       <c r="I372" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J372" t="n">
         <v>133.97</v>
@@ -28683,7 +28683,7 @@
         <v>-14.8</v>
       </c>
       <c r="I373" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J373" s="4" t="n">
         <v>132.5</v>
@@ -28762,7 +28762,7 @@
         <v>-6.48</v>
       </c>
       <c r="I374" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J374" t="n">
         <v>130.49</v>
@@ -28837,7 +28837,7 @@
         <v>1.22</v>
       </c>
       <c r="I375" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J375" t="n">
         <v>128.73</v>
@@ -28912,7 +28912,7 @@
         <v>-1.32</v>
       </c>
       <c r="I376" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J376" t="n">
         <v>127.92</v>
@@ -28987,7 +28987,7 @@
         <v>-7.82</v>
       </c>
       <c r="I377" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J377" t="n">
         <v>127.07</v>
@@ -29062,7 +29062,7 @@
         <v>4.05</v>
       </c>
       <c r="I378" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J378" t="n">
         <v>127.37</v>
@@ -29137,7 +29137,7 @@
         <v>0.8</v>
       </c>
       <c r="I379" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J379" t="n">
         <v>128.6</v>
@@ -29212,7 +29212,7 @@
         <v>5.54</v>
       </c>
       <c r="I380" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J380" t="n">
         <v>129.02</v>
@@ -29287,7 +29287,7 @@
         <v>-9.51</v>
       </c>
       <c r="I381" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J381" t="n">
         <v>128.85</v>
@@ -29362,7 +29362,7 @@
         <v>1.3</v>
       </c>
       <c r="I382" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J382" t="n">
         <v>128.66</v>
@@ -29437,7 +29437,7 @@
         <v>-6.1</v>
       </c>
       <c r="I383" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J383" t="n">
         <v>126.96</v>
@@ -29516,7 +29516,7 @@
         <v>0.42</v>
       </c>
       <c r="I384" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J384" t="n">
         <v>125.67</v>
@@ -29595,7 +29595,7 @@
         <v>0.37</v>
       </c>
       <c r="I385" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J385" t="n">
         <v>124.39</v>
@@ -29674,7 +29674,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="I386" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J386" t="n">
         <v>123.25</v>
@@ -29749,7 +29749,7 @@
         <v>5.11</v>
       </c>
       <c r="I387" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J387" t="n">
         <v>122.91</v>
@@ -29824,7 +29824,7 @@
         <v>2.11</v>
       </c>
       <c r="I388" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J388" t="n">
         <v>122.55</v>
@@ -29899,7 +29899,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="I389" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J389" t="n">
         <v>121.23</v>
@@ -29978,7 +29978,7 @@
         <v>5.24</v>
       </c>
       <c r="I390" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J390" t="n">
         <v>120.06</v>
@@ -30053,7 +30053,7 @@
         <v>-16.99</v>
       </c>
       <c r="I391" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J391" s="4" t="n">
         <v>117.87</v>
@@ -30132,7 +30132,7 @@
         <v>1.18</v>
       </c>
       <c r="I392" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J392" t="n">
         <v>115.41</v>
@@ -30207,7 +30207,7 @@
         <v>1.61</v>
       </c>
       <c r="I393" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J393" t="n">
         <v>114.15</v>
@@ -30282,7 +30282,7 @@
         <v>10.43</v>
       </c>
       <c r="I394" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J394" t="n">
         <v>113.86</v>
@@ -30357,7 +30357,7 @@
         <v>7.71</v>
       </c>
       <c r="I395" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J395" t="n">
         <v>113.93</v>
@@ -30432,7 +30432,7 @@
         <v>14.77</v>
       </c>
       <c r="I396" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J396" t="n">
         <v>115</v>
@@ -30507,7 +30507,7 @@
         <v>7.13</v>
       </c>
       <c r="I397" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J397" t="n">
         <v>117.04</v>
@@ -30582,7 +30582,7 @@
         <v>-3.75</v>
       </c>
       <c r="I398" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J398" t="n">
         <v>118.57</v>
@@ -30657,7 +30657,7 @@
         <v>0.05</v>
       </c>
       <c r="I399" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J399" t="n">
         <v>120.06</v>
@@ -30732,7 +30732,7 @@
         <v>3.5</v>
       </c>
       <c r="I400" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J400" t="n">
         <v>121.49</v>
@@ -30807,7 +30807,7 @@
         <v>-6.05</v>
       </c>
       <c r="I401" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J401" t="n">
         <v>123.04</v>
@@ -30882,7 +30882,7 @@
         <v>3.31</v>
       </c>
       <c r="I402" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J402" t="n">
         <v>124.75</v>
@@ -30957,7 +30957,7 @@
         <v>0.59</v>
       </c>
       <c r="I403" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J403" t="n">
         <v>126.85</v>
@@ -31032,7 +31032,7 @@
         <v>3.94</v>
       </c>
       <c r="I404" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J404" t="n">
         <v>129.22</v>
@@ -31107,7 +31107,7 @@
         <v>6.52</v>
       </c>
       <c r="I405" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J405" t="n">
         <v>132.08</v>
@@ -31182,7 +31182,7 @@
         <v>0.34</v>
       </c>
       <c r="I406" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J406" t="n">
         <v>134.43</v>
@@ -31257,7 +31257,7 @@
         <v>-0.01</v>
       </c>
       <c r="I407" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J407" t="n">
         <v>136.48</v>
@@ -31332,7 +31332,7 @@
         <v>-3.26</v>
       </c>
       <c r="I408" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J408" t="n">
         <v>138.14</v>
@@ -31411,7 +31411,7 @@
         <v>-10.31</v>
       </c>
       <c r="I409" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J409" t="n">
         <v>139.48</v>
@@ -31486,7 +31486,7 @@
         <v>-1.94</v>
       </c>
       <c r="I410" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J410" t="n">
         <v>140.38</v>
@@ -31565,7 +31565,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="I411" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J411" t="n">
         <v>141.75</v>
@@ -31644,7 +31644,7 @@
         <v>-0.65</v>
       </c>
       <c r="I412" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J412" t="n">
         <v>143.01</v>
@@ -31719,7 +31719,7 @@
         <v>-13.35</v>
       </c>
       <c r="I413" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J413" t="n">
         <v>143.35</v>
@@ -31794,7 +31794,7 @@
         <v>-2.89</v>
       </c>
       <c r="I414" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J414" t="n">
         <v>142.98</v>
@@ -31854,25 +31854,41 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>101.19</v>
+      </c>
+      <c r="D415" t="n">
+        <v>103.93</v>
+      </c>
+      <c r="E415" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="F415" t="n">
+        <v>93.67</v>
+      </c>
       <c r="G415" t="n">
-        <v>112826432</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>113810400</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-12.74</v>
       </c>
       <c r="I415" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+        <v>14.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>141.48</v>
+      </c>
+      <c r="K415" t="n">
+        <v>128.05</v>
+      </c>
+      <c r="L415" t="n">
+        <v>160.81</v>
+      </c>
+      <c r="M415" t="n">
+        <v>122.03</v>
+      </c>
       <c r="N415" s="3" t="n">
-        <v>27.86</v>
+        <v>23.74</v>
       </c>
       <c r="O415" t="n">
         <v>18</v>
@@ -31887,7 +31903,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S415" t="n">
         <v>5.1</v>
       </c>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31741,7 +31741,7 @@
         <v>23.74</v>
       </c>
       <c r="O413" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3012,7 +3012,7 @@
         <v>14.3</v>
       </c>
       <c r="J33" t="n">
-        <v>15.56</v>
+        <v>15.55</v>
       </c>
       <c r="K33" t="n">
         <v>22.42</v>
@@ -31741,7 +31741,7 @@
         <v>23.74</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31771,6 +31771,83 @@
       <c r="W413" s="6" t="n">
         <v>168.6</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="D414" t="n">
+        <v>104.98</v>
+      </c>
+      <c r="E414" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="F414" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="G414" t="n">
+        <v>80201632</v>
+      </c>
+      <c r="H414" s="4" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>139.36</v>
+      </c>
+      <c r="K414" t="n">
+        <v>127.43</v>
+      </c>
+      <c r="L414" t="n">
+        <v>160.73</v>
+      </c>
+      <c r="M414" t="n">
+        <v>122.32</v>
+      </c>
+      <c r="N414" s="4" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="O414" t="n">
+        <v>24</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T414" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U414" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31793,34 +31793,34 @@
         <v>97.8</v>
       </c>
       <c r="F414" t="n">
-        <v>99.48999999999999</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="G414" t="n">
-        <v>80201632</v>
+        <v>94053446</v>
       </c>
       <c r="H414" s="4" t="n">
-        <v>6.21</v>
+        <v>5.32</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>139.36</v>
+        <v>139.32</v>
       </c>
       <c r="K414" t="n">
-        <v>127.43</v>
+        <v>127.41</v>
       </c>
       <c r="L414" t="n">
-        <v>160.73</v>
+        <v>160.72</v>
       </c>
       <c r="M414" t="n">
         <v>122.32</v>
       </c>
       <c r="N414" s="4" t="n">
-        <v>24.65</v>
+        <v>23.96</v>
       </c>
       <c r="O414" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31838,16 +31838,18 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="T414" s="5" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="U414" s="5" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="5" t="inlineStr"/>
+      <c r="W414" s="6" t="n">
+        <v>161.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31745,7 +31745,7 @@
         <v>23.96</v>
       </c>
       <c r="O413" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31775,6 +31775,83 @@
       <c r="W413" s="3" t="n">
         <v>161.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>94.51000000000001</v>
+      </c>
+      <c r="D414" t="n">
+        <v>102.62</v>
+      </c>
+      <c r="E414" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="F414" t="n">
+        <v>100.96</v>
+      </c>
+      <c r="G414" t="n">
+        <v>51198403</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>136.77</v>
+      </c>
+      <c r="K414" t="n">
+        <v>126.96</v>
+      </c>
+      <c r="L414" t="n">
+        <v>160.58</v>
+      </c>
+      <c r="M414" t="n">
+        <v>122.58</v>
+      </c>
+      <c r="N414" s="1" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="O414" t="n">
+        <v>28</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31797,34 +31797,34 @@
         <v>91.34999999999999</v>
       </c>
       <c r="F414" t="n">
-        <v>100.96</v>
+        <v>99.59</v>
       </c>
       <c r="G414" t="n">
-        <v>51198403</v>
+        <v>82308201</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>2.34</v>
+        <v>0.95</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>136.77</v>
+        <v>136.7</v>
       </c>
       <c r="K414" t="n">
-        <v>126.96</v>
+        <v>126.94</v>
       </c>
       <c r="L414" t="n">
-        <v>160.58</v>
+        <v>160.57</v>
       </c>
       <c r="M414" t="n">
         <v>122.58</v>
       </c>
       <c r="N414" s="1" t="n">
-        <v>25.13</v>
+        <v>24.03</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31842,13 +31842,13 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31721,7 +31721,7 @@
         <v>98.65000000000001</v>
       </c>
       <c r="G413" t="n">
-        <v>94573000</v>
+        <v>95625900</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>5.32</v>
@@ -31797,31 +31797,31 @@
         <v>91.34999999999999</v>
       </c>
       <c r="F414" t="n">
-        <v>99.59</v>
+        <v>97.55</v>
       </c>
       <c r="G414" t="n">
-        <v>82308201</v>
-      </c>
-      <c r="H414" s="1" t="n">
-        <v>0.95</v>
+        <v>94282304</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-1.12</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>136.7</v>
+        <v>136.6</v>
       </c>
       <c r="K414" t="n">
-        <v>126.94</v>
+        <v>126.9</v>
       </c>
       <c r="L414" t="n">
-        <v>160.57</v>
+        <v>160.55</v>
       </c>
       <c r="M414" t="n">
-        <v>122.58</v>
+        <v>122.57</v>
       </c>
       <c r="N414" s="1" t="n">
-        <v>24.03</v>
+        <v>22.98</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31845,13 +31845,15 @@
         <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31749,7 +31749,7 @@
         <v>22.98</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>-9.789999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J2" t="n">
         <v>26.7</v>
@@ -683,7 +683,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J3" t="n">
         <v>26.46</v>
@@ -758,7 +758,7 @@
         <v>6.29</v>
       </c>
       <c r="I4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J4" t="n">
         <v>26.24</v>
@@ -833,7 +833,7 @@
         <v>-12.39</v>
       </c>
       <c r="I5" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J5" t="n">
         <v>25.82</v>
@@ -912,7 +912,7 @@
         <v>8.59</v>
       </c>
       <c r="I6" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J6" t="n">
         <v>25.49</v>
@@ -987,7 +987,7 @@
         <v>-13.84</v>
       </c>
       <c r="I7" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J7" t="n">
         <v>25.07</v>
@@ -1070,7 +1070,7 @@
         <v>-3.19</v>
       </c>
       <c r="I8" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J8" t="n">
         <v>24.58</v>
@@ -1153,7 +1153,7 @@
         <v>5.09</v>
       </c>
       <c r="I9" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J9" t="n">
         <v>24.13</v>
@@ -1232,7 +1232,7 @@
         <v>-1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J10" t="n">
         <v>23.66</v>
@@ -1311,7 +1311,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J11" t="n">
         <v>23.23</v>
@@ -1386,7 +1386,7 @@
         <v>4.98</v>
       </c>
       <c r="I12" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J12" t="n">
         <v>22.84</v>
@@ -1461,7 +1461,7 @@
         <v>-4.12</v>
       </c>
       <c r="I13" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J13" t="n">
         <v>22.34</v>
@@ -1536,7 +1536,7 @@
         <v>2.22</v>
       </c>
       <c r="I14" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J14" t="n">
         <v>21.79</v>
@@ -1611,7 +1611,7 @@
         <v>-2.17</v>
       </c>
       <c r="I15" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J15" t="n">
         <v>21.21</v>
@@ -1686,7 +1686,7 @@
         <v>-3.28</v>
       </c>
       <c r="I16" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J16" t="n">
         <v>20.74</v>
@@ -1761,7 +1761,7 @@
         <v>8.93</v>
       </c>
       <c r="I17" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J17" t="n">
         <v>20.45</v>
@@ -1836,7 +1836,7 @@
         <v>-1.82</v>
       </c>
       <c r="I18" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J18" t="n">
         <v>20.23</v>
@@ -1911,7 +1911,7 @@
         <v>-8.6</v>
       </c>
       <c r="I19" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J19" t="n">
         <v>19.86</v>
@@ -1990,7 +1990,7 @@
         <v>-5.45</v>
       </c>
       <c r="I20" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J20" t="n">
         <v>19.66</v>
@@ -2065,7 +2065,7 @@
         <v>-9.779999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J21" t="n">
         <v>19.33</v>
@@ -2140,7 +2140,7 @@
         <v>-0.5</v>
       </c>
       <c r="I22" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J22" t="n">
         <v>19.11</v>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J23" t="n">
         <v>18.88</v>
@@ -2290,7 +2290,7 @@
         <v>1.95</v>
       </c>
       <c r="I24" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J24" t="n">
         <v>18.6</v>
@@ -2365,7 +2365,7 @@
         <v>-29.83</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>18.21</v>
@@ -2448,7 +2448,7 @@
         <v>-23.5</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>17.61</v>
@@ -2531,7 +2531,7 @@
         <v>4.83</v>
       </c>
       <c r="I27" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J27" t="n">
         <v>17.17</v>
@@ -2614,7 +2614,7 @@
         <v>-9.77</v>
       </c>
       <c r="I28" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J28" t="n">
         <v>16.72</v>
@@ -2697,7 +2697,7 @@
         <v>54.74</v>
       </c>
       <c r="I29" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J29" t="n">
         <v>16.45</v>
@@ -2776,7 +2776,7 @@
         <v>-24.61</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>16.03</v>
@@ -2859,7 +2859,7 @@
         <v>6.26</v>
       </c>
       <c r="I31" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J31" t="n">
         <v>15.55</v>
@@ -2942,7 +2942,7 @@
         <v>2.36</v>
       </c>
       <c r="I32" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J32" t="n">
         <v>15.04</v>
@@ -3021,7 +3021,7 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J33" t="n">
         <v>14.58</v>
@@ -3096,7 +3096,7 @@
         <v>-11.93</v>
       </c>
       <c r="I34" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J34" t="n">
         <v>14.04</v>
@@ -3179,7 +3179,7 @@
         <v>-1.51</v>
       </c>
       <c r="I35" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J35" t="n">
         <v>13.5</v>
@@ -3258,7 +3258,7 @@
         <v>-5.35</v>
       </c>
       <c r="I36" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J36" t="n">
         <v>12.98</v>
@@ -3333,7 +3333,7 @@
         <v>5.42</v>
       </c>
       <c r="I37" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J37" t="n">
         <v>12.4</v>
@@ -3408,7 +3408,7 @@
         <v>12.14</v>
       </c>
       <c r="I38" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J38" t="n">
         <v>11.89</v>
@@ -3487,7 +3487,7 @@
         <v>16.59</v>
       </c>
       <c r="I39" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J39" t="n">
         <v>11.55</v>
@@ -3562,7 +3562,7 @@
         <v>2.85</v>
       </c>
       <c r="I40" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J40" t="n">
         <v>11.28</v>
@@ -3637,7 +3637,7 @@
         <v>-0.41</v>
       </c>
       <c r="I41" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J41" t="n">
         <v>11.09</v>
@@ -3712,7 +3712,7 @@
         <v>-3.51</v>
       </c>
       <c r="I42" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J42" t="n">
         <v>10.89</v>
@@ -3787,7 +3787,7 @@
         <v>2.54</v>
       </c>
       <c r="I43" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J43" t="n">
         <v>10.7</v>
@@ -3862,7 +3862,7 @@
         <v>-0.5</v>
       </c>
       <c r="I44" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J44" t="n">
         <v>10.49</v>
@@ -3937,7 +3937,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J45" t="n">
         <v>10.59</v>
@@ -4012,7 +4012,7 @@
         <v>-1.81</v>
       </c>
       <c r="I46" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J46" t="n">
         <v>10.8</v>
@@ -4087,7 +4087,7 @@
         <v>-3.15</v>
       </c>
       <c r="I47" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J47" t="n">
         <v>10.98</v>
@@ -4162,7 +4162,7 @@
         <v>5.08</v>
       </c>
       <c r="I48" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J48" t="n">
         <v>11.23</v>
@@ -4237,7 +4237,7 @@
         <v>2.8</v>
       </c>
       <c r="I49" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J49" t="n">
         <v>11.27</v>
@@ -4312,7 +4312,7 @@
         <v>3.31</v>
       </c>
       <c r="I50" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J50" t="n">
         <v>11.49</v>
@@ -4387,7 +4387,7 @@
         <v>21.42</v>
       </c>
       <c r="I51" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J51" t="n">
         <v>11.84</v>
@@ -4462,7 +4462,7 @@
         <v>8.56</v>
       </c>
       <c r="I52" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J52" t="n">
         <v>12.24</v>
@@ -4537,7 +4537,7 @@
         <v>1.3</v>
       </c>
       <c r="I53" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J53" t="n">
         <v>12.65</v>
@@ -4612,7 +4612,7 @@
         <v>-1.97</v>
       </c>
       <c r="I54" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J54" t="n">
         <v>13.11</v>
@@ -4687,7 +4687,7 @@
         <v>-0.44</v>
       </c>
       <c r="I55" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J55" t="n">
         <v>13.56</v>
@@ -4762,7 +4762,7 @@
         <v>-1.75</v>
       </c>
       <c r="I56" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J56" t="n">
         <v>14.03</v>
@@ -4837,7 +4837,7 @@
         <v>-0.5</v>
       </c>
       <c r="I57" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J57" t="n">
         <v>14.47</v>
@@ -4912,7 +4912,7 @@
         <v>-5.42</v>
       </c>
       <c r="I58" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J58" t="n">
         <v>14.8</v>
@@ -4987,7 +4987,7 @@
         <v>-2.89</v>
       </c>
       <c r="I59" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J59" t="n">
         <v>15.03</v>
@@ -5062,7 +5062,7 @@
         <v>-4.68</v>
       </c>
       <c r="I60" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J60" t="n">
         <v>15.19</v>
@@ -5137,7 +5137,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J61" t="n">
         <v>15.44</v>
@@ -5212,7 +5212,7 @@
         <v>-1.45</v>
       </c>
       <c r="I62" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J62" t="n">
         <v>15.7</v>
@@ -5287,7 +5287,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J63" t="n">
         <v>15.95</v>
@@ -5362,7 +5362,7 @@
         <v>-6.01</v>
       </c>
       <c r="I64" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J64" t="n">
         <v>16.16</v>
@@ -5441,7 +5441,7 @@
         <v>4.53</v>
       </c>
       <c r="I65" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J65" t="n">
         <v>16.33</v>
@@ -5516,7 +5516,7 @@
         <v>8.32</v>
       </c>
       <c r="I66" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J66" t="n">
         <v>16.6</v>
@@ -5591,7 +5591,7 @@
         <v>4.28</v>
       </c>
       <c r="I67" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J67" t="n">
         <v>16.92</v>
@@ -5666,7 +5666,7 @@
         <v>-1.47</v>
       </c>
       <c r="I68" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J68" t="n">
         <v>17.19</v>
@@ -5741,7 +5741,7 @@
         <v>1.98</v>
       </c>
       <c r="I69" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J69" t="n">
         <v>17.47</v>
@@ -5816,7 +5816,7 @@
         <v>7.33</v>
       </c>
       <c r="I70" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J70" t="n">
         <v>17.79</v>
@@ -5891,7 +5891,7 @@
         <v>6.34</v>
       </c>
       <c r="I71" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J71" t="n">
         <v>18.03</v>
@@ -5966,7 +5966,7 @@
         <v>-1.15</v>
       </c>
       <c r="I72" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J72" t="n">
         <v>18.18</v>
@@ -6041,7 +6041,7 @@
         <v>0.23</v>
       </c>
       <c r="I73" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J73" t="n">
         <v>18.32</v>
@@ -6116,7 +6116,7 @@
         <v>-7.59</v>
       </c>
       <c r="I74" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J74" t="n">
         <v>18.4</v>
@@ -6195,7 +6195,7 @@
         <v>9.27</v>
       </c>
       <c r="I75" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J75" t="n">
         <v>18.57</v>
@@ -6270,7 +6270,7 @@
         <v>-2.2</v>
       </c>
       <c r="I76" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J76" t="n">
         <v>18.74</v>
@@ -6345,7 +6345,7 @@
         <v>0.89</v>
       </c>
       <c r="I77" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J77" t="n">
         <v>18.92</v>
@@ -6420,7 +6420,7 @@
         <v>-1.86</v>
       </c>
       <c r="I78" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J78" t="n">
         <v>19.13</v>
@@ -6495,7 +6495,7 @@
         <v>1.75</v>
       </c>
       <c r="I79" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J79" t="n">
         <v>19.38</v>
@@ -6570,7 +6570,7 @@
         <v>11.35</v>
       </c>
       <c r="I80" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J80" t="n">
         <v>19.8</v>
@@ -6645,7 +6645,7 @@
         <v>2.63</v>
       </c>
       <c r="I81" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J81" t="n">
         <v>20.16</v>
@@ -6720,7 +6720,7 @@
         <v>2.52</v>
       </c>
       <c r="I82" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J82" t="n">
         <v>20.57</v>
@@ -6795,7 +6795,7 @@
         <v>-0.36</v>
       </c>
       <c r="I83" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J83" t="n">
         <v>20.97</v>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J84" t="n">
         <v>21.42</v>
@@ -6945,7 +6945,7 @@
         <v>-1.59</v>
       </c>
       <c r="I85" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J85" t="n">
         <v>21.81</v>
@@ -7020,7 +7020,7 @@
         <v>5.43</v>
       </c>
       <c r="I86" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J86" t="n">
         <v>22.2</v>
@@ -7095,7 +7095,7 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J87" t="n">
         <v>22.57</v>
@@ -7170,7 +7170,7 @@
         <v>-5.53</v>
       </c>
       <c r="I88" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J88" t="n">
         <v>22.89</v>
@@ -7245,7 +7245,7 @@
         <v>5.61</v>
       </c>
       <c r="I89" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J89" t="n">
         <v>23.25</v>
@@ -7320,7 +7320,7 @@
         <v>1.02</v>
       </c>
       <c r="I90" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J90" t="n">
         <v>23.55</v>
@@ -7395,7 +7395,7 @@
         <v>2.7</v>
       </c>
       <c r="I91" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J91" t="n">
         <v>23.83</v>
@@ -7470,7 +7470,7 @@
         <v>-0.29</v>
       </c>
       <c r="I92" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J92" t="n">
         <v>24.12</v>
@@ -7545,7 +7545,7 @@
         <v>-2.9</v>
       </c>
       <c r="I93" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J93" t="n">
         <v>24.36</v>
@@ -7620,7 +7620,7 @@
         <v>2.98</v>
       </c>
       <c r="I94" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J94" t="n">
         <v>24.72</v>
@@ -7695,7 +7695,7 @@
         <v>-0.95</v>
       </c>
       <c r="I95" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J95" t="n">
         <v>24.98</v>
@@ -7770,7 +7770,7 @@
         <v>1.07</v>
       </c>
       <c r="I96" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J96" t="n">
         <v>25.28</v>
@@ -7845,7 +7845,7 @@
         <v>0.04</v>
       </c>
       <c r="I97" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J97" t="n">
         <v>25.57</v>
@@ -7920,7 +7920,7 @@
         <v>0.62</v>
       </c>
       <c r="I98" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J98" t="n">
         <v>25.89</v>
@@ -7995,7 +7995,7 @@
         <v>-4.26</v>
       </c>
       <c r="I99" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J99" t="n">
         <v>26.13</v>
@@ -8070,7 +8070,7 @@
         <v>-2.05</v>
       </c>
       <c r="I100" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J100" t="n">
         <v>26.22</v>
@@ -8149,7 +8149,7 @@
         <v>-0.62</v>
       </c>
       <c r="I101" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J101" t="n">
         <v>26.27</v>
@@ -8224,7 +8224,7 @@
         <v>-0.08</v>
       </c>
       <c r="I102" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J102" t="n">
         <v>26.29</v>
@@ -8299,7 +8299,7 @@
         <v>4.96</v>
       </c>
       <c r="I103" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J103" t="n">
         <v>26.38</v>
@@ -8374,7 +8374,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J104" t="n">
         <v>26.48</v>
@@ -8449,7 +8449,7 @@
         <v>2.15</v>
       </c>
       <c r="I105" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J105" t="n">
         <v>26.62</v>
@@ -8524,7 +8524,7 @@
         <v>-9.5</v>
       </c>
       <c r="I106" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J106" t="n">
         <v>26.57</v>
@@ -8603,7 +8603,7 @@
         <v>-3.61</v>
       </c>
       <c r="I107" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J107" t="n">
         <v>26.45</v>
@@ -8678,7 +8678,7 @@
         <v>3.82</v>
       </c>
       <c r="I108" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J108" t="n">
         <v>26.45</v>
@@ -8753,7 +8753,7 @@
         <v>-1.92</v>
       </c>
       <c r="I109" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J109" t="n">
         <v>26.36</v>
@@ -8828,7 +8828,7 @@
         <v>-2.16</v>
       </c>
       <c r="I110" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J110" t="n">
         <v>26.23</v>
@@ -8903,7 +8903,7 @@
         <v>4.21</v>
       </c>
       <c r="I111" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J111" t="n">
         <v>26.11</v>
@@ -8978,7 +8978,7 @@
         <v>2.84</v>
       </c>
       <c r="I112" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J112" t="n">
         <v>26.03</v>
@@ -9053,7 +9053,7 @@
         <v>-0.39</v>
       </c>
       <c r="I113" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J113" t="n">
         <v>25.99</v>
@@ -9128,7 +9128,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I114" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J114" t="n">
         <v>26.02</v>
@@ -9203,7 +9203,7 @@
         <v>4.54</v>
       </c>
       <c r="I115" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J115" t="n">
         <v>26.13</v>
@@ -9278,7 +9278,7 @@
         <v>0.51</v>
       </c>
       <c r="I116" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J116" t="n">
         <v>26.24</v>
@@ -9353,7 +9353,7 @@
         <v>-6.98</v>
       </c>
       <c r="I117" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J117" t="n">
         <v>26.24</v>
@@ -9428,7 +9428,7 @@
         <v>0.59</v>
       </c>
       <c r="I118" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J118" t="n">
         <v>26.24</v>
@@ -9503,7 +9503,7 @@
         <v>-4.65</v>
       </c>
       <c r="I119" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J119" t="n">
         <v>26.24</v>
@@ -9582,7 +9582,7 @@
         <v>-1.68</v>
       </c>
       <c r="I120" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J120" t="n">
         <v>26.24</v>
@@ -9657,7 +9657,7 @@
         <v>-1.75</v>
       </c>
       <c r="I121" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J121" t="n">
         <v>26.23</v>
@@ -9732,7 +9732,7 @@
         <v>8.25</v>
       </c>
       <c r="I122" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J122" t="n">
         <v>26.32</v>
@@ -9807,7 +9807,7 @@
         <v>-0.55</v>
       </c>
       <c r="I123" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J123" t="n">
         <v>26.34</v>
@@ -9882,7 +9882,7 @@
         <v>2.35</v>
       </c>
       <c r="I124" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J124" t="n">
         <v>26.38</v>
@@ -9957,7 +9957,7 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J125" t="n">
         <v>26.41</v>
@@ -10032,7 +10032,7 @@
         <v>1.24</v>
       </c>
       <c r="I126" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J126" t="n">
         <v>26.59</v>
@@ -10107,7 +10107,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J127" t="n">
         <v>26.69</v>
@@ -10186,7 +10186,7 @@
         <v>-3.04</v>
       </c>
       <c r="I128" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J128" t="n">
         <v>26.7</v>
@@ -10265,7 +10265,7 @@
         <v>-1.35</v>
       </c>
       <c r="I129" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J129" t="n">
         <v>26.72</v>
@@ -10340,7 +10340,7 @@
         <v>2.97</v>
       </c>
       <c r="I130" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J130" t="n">
         <v>26.8</v>
@@ -10415,7 +10415,7 @@
         <v>3.08</v>
       </c>
       <c r="I131" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J131" t="n">
         <v>26.87</v>
@@ -10490,7 +10490,7 @@
         <v>2.38</v>
       </c>
       <c r="I132" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J132" t="n">
         <v>26.94</v>
@@ -10565,7 +10565,7 @@
         <v>0.37</v>
       </c>
       <c r="I133" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J133" t="n">
         <v>27.02</v>
@@ -10640,7 +10640,7 @@
         <v>5.23</v>
       </c>
       <c r="I134" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J134" t="n">
         <v>27.05</v>
@@ -10715,7 +10715,7 @@
         <v>2</v>
       </c>
       <c r="I135" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J135" t="n">
         <v>27.05</v>
@@ -10790,7 +10790,7 @@
         <v>0.45</v>
       </c>
       <c r="I136" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J136" t="n">
         <v>27.04</v>
@@ -10865,7 +10865,7 @@
         <v>2.39</v>
       </c>
       <c r="I137" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J137" t="n">
         <v>27.17</v>
@@ -10940,7 +10940,7 @@
         <v>1.6</v>
       </c>
       <c r="I138" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J138" t="n">
         <v>27.32</v>
@@ -11015,7 +11015,7 @@
         <v>-0.03</v>
       </c>
       <c r="I139" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J139" t="n">
         <v>27.53</v>
@@ -11090,7 +11090,7 @@
         <v>10.41</v>
       </c>
       <c r="I140" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J140" t="n">
         <v>27.92</v>
@@ -11165,7 +11165,7 @@
         <v>-1.84</v>
       </c>
       <c r="I141" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J141" t="n">
         <v>28.3</v>
@@ -11240,7 +11240,7 @@
         <v>4.27</v>
       </c>
       <c r="I142" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J142" t="n">
         <v>28.65</v>
@@ -11315,7 +11315,7 @@
         <v>-0.35</v>
       </c>
       <c r="I143" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J143" t="n">
         <v>29</v>
@@ -11390,7 +11390,7 @@
         <v>-0.29</v>
       </c>
       <c r="I144" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J144" t="n">
         <v>29.32</v>
@@ -11465,7 +11465,7 @@
         <v>-1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J145" t="n">
         <v>29.6</v>
@@ -11540,7 +11540,7 @@
         <v>0.5</v>
       </c>
       <c r="I146" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J146" t="n">
         <v>29.88</v>
@@ -11615,7 +11615,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J147" t="n">
         <v>30.28</v>
@@ -11690,7 +11690,7 @@
         <v>2.41</v>
       </c>
       <c r="I148" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J148" t="n">
         <v>30.75</v>
@@ -11765,7 +11765,7 @@
         <v>5.8</v>
       </c>
       <c r="I149" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J149" t="n">
         <v>31.35</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="I150" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J150" t="n">
         <v>32.02</v>
@@ -11915,7 +11915,7 @@
         <v>-2.18</v>
       </c>
       <c r="I151" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J151" t="n">
         <v>32.61</v>
@@ -11990,7 +11990,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="I152" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J152" t="n">
         <v>33.34</v>
@@ -12065,7 +12065,7 @@
         <v>-6.91</v>
       </c>
       <c r="I153" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J153" t="n">
         <v>33.93</v>
@@ -12140,7 +12140,7 @@
         <v>10.18</v>
       </c>
       <c r="I154" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J154" t="n">
         <v>34.64</v>
@@ -12215,7 +12215,7 @@
         <v>-1.26</v>
       </c>
       <c r="I155" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J155" t="n">
         <v>35.29</v>
@@ -12290,7 +12290,7 @@
         <v>-19</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>35.53</v>
@@ -12369,7 +12369,7 @@
         <v>14.39</v>
       </c>
       <c r="I157" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J157" t="n">
         <v>35.99</v>
@@ -12444,7 +12444,7 @@
         <v>-6.39</v>
       </c>
       <c r="I158" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J158" t="n">
         <v>36.3</v>
@@ -12519,7 +12519,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J159" t="n">
         <v>36.78</v>
@@ -12594,7 +12594,7 @@
         <v>1.48</v>
       </c>
       <c r="I160" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J160" t="n">
         <v>37.12</v>
@@ -12669,7 +12669,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J161" t="n">
         <v>37.48</v>
@@ -12744,7 +12744,7 @@
         <v>4.84</v>
       </c>
       <c r="I162" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J162" t="n">
         <v>37.88</v>
@@ -12819,7 +12819,7 @@
         <v>-1.73</v>
       </c>
       <c r="I163" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J163" t="n">
         <v>38.24</v>
@@ -12894,7 +12894,7 @@
         <v>-7.52</v>
       </c>
       <c r="I164" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J164" t="n">
         <v>38.44</v>
@@ -12973,7 +12973,7 @@
         <v>7.25</v>
       </c>
       <c r="I165" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J165" t="n">
         <v>38.81</v>
@@ -13048,7 +13048,7 @@
         <v>4.79</v>
       </c>
       <c r="I166" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J166" t="n">
         <v>39.27</v>
@@ -13123,7 +13123,7 @@
         <v>8.58</v>
       </c>
       <c r="I167" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J167" t="n">
         <v>39.91</v>
@@ -13198,7 +13198,7 @@
         <v>0.26</v>
       </c>
       <c r="I168" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J168" t="n">
         <v>40.51</v>
@@ -13273,7 +13273,7 @@
         <v>5.16</v>
       </c>
       <c r="I169" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J169" t="n">
         <v>41.14</v>
@@ -13348,7 +13348,7 @@
         <v>-4.03</v>
       </c>
       <c r="I170" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J170" t="n">
         <v>41.55</v>
@@ -13423,7 +13423,7 @@
         <v>0.82</v>
       </c>
       <c r="I171" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J171" t="n">
         <v>42.03</v>
@@ -13498,7 +13498,7 @@
         <v>1.68</v>
       </c>
       <c r="I172" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J172" t="n">
         <v>42.37</v>
@@ -13573,7 +13573,7 @@
         <v>-11.91</v>
       </c>
       <c r="I173" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J173" t="n">
         <v>42.57</v>
@@ -13648,7 +13648,7 @@
         <v>9.42</v>
       </c>
       <c r="I174" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J174" t="n">
         <v>42.77</v>
@@ -13723,7 +13723,7 @@
         <v>-8.16</v>
       </c>
       <c r="I175" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J175" t="n">
         <v>42.81</v>
@@ -13798,7 +13798,7 @@
         <v>-2.95</v>
       </c>
       <c r="I176" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J176" t="n">
         <v>43.19</v>
@@ -13877,7 +13877,7 @@
         <v>7.72</v>
       </c>
       <c r="I177" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J177" t="n">
         <v>43.48</v>
@@ -13952,7 +13952,7 @@
         <v>-7.01</v>
       </c>
       <c r="I178" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J178" t="n">
         <v>43.74</v>
@@ -14031,7 +14031,7 @@
         <v>4.55</v>
       </c>
       <c r="I179" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J179" t="n">
         <v>43.92</v>
@@ -14106,7 +14106,7 @@
         <v>-10.28</v>
       </c>
       <c r="I180" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J180" t="n">
         <v>43.86</v>
@@ -14181,7 +14181,7 @@
         <v>-0.92</v>
       </c>
       <c r="I181" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J181" t="n">
         <v>43.79</v>
@@ -14256,7 +14256,7 @@
         <v>-5.18</v>
       </c>
       <c r="I182" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J182" t="n">
         <v>43.52</v>
@@ -14331,7 +14331,7 @@
         <v>-6.76</v>
       </c>
       <c r="I183" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J183" t="n">
         <v>43.16</v>
@@ -14410,7 +14410,7 @@
         <v>4.69</v>
       </c>
       <c r="I184" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J184" t="n">
         <v>43.04</v>
@@ -14485,7 +14485,7 @@
         <v>-14.33</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>42.52</v>
@@ -14568,7 +14568,7 @@
         <v>2.99</v>
       </c>
       <c r="I186" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J186" t="n">
         <v>41.95</v>
@@ -14643,7 +14643,7 @@
         <v>13.02</v>
       </c>
       <c r="I187" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J187" t="n">
         <v>41.4</v>
@@ -14718,7 +14718,7 @@
         <v>0.86</v>
       </c>
       <c r="I188" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J188" t="n">
         <v>40.86</v>
@@ -14793,7 +14793,7 @@
         <v>8.33</v>
       </c>
       <c r="I189" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J189" t="n">
         <v>40.35</v>
@@ -14868,7 +14868,7 @@
         <v>5.29</v>
       </c>
       <c r="I190" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J190" t="n">
         <v>40.05</v>
@@ -14943,7 +14943,7 @@
         <v>0.12</v>
       </c>
       <c r="I191" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J191" t="n">
         <v>39.72</v>
@@ -15018,7 +15018,7 @@
         <v>6.03</v>
       </c>
       <c r="I192" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J192" t="n">
         <v>39.48</v>
@@ -15093,7 +15093,7 @@
         <v>6.35</v>
       </c>
       <c r="I193" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J193" t="n">
         <v>39.67</v>
@@ -15168,7 +15168,7 @@
         <v>-3.05</v>
       </c>
       <c r="I194" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J194" t="n">
         <v>39.59</v>
@@ -15243,7 +15243,7 @@
         <v>2.97</v>
       </c>
       <c r="I195" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J195" t="n">
         <v>39.76</v>
@@ -15318,7 +15318,7 @@
         <v>3.21</v>
       </c>
       <c r="I196" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J196" t="n">
         <v>40.08</v>
@@ -15393,7 +15393,7 @@
         <v>-0.42</v>
       </c>
       <c r="I197" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J197" t="n">
         <v>40.22</v>
@@ -15468,7 +15468,7 @@
         <v>3.89</v>
       </c>
       <c r="I198" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J198" t="n">
         <v>40.61</v>
@@ -15543,7 +15543,7 @@
         <v>-1.73</v>
       </c>
       <c r="I199" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J199" t="n">
         <v>40.86</v>
@@ -15618,7 +15618,7 @@
         <v>-14.52</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>40.99</v>
@@ -15693,7 +15693,7 @@
         <v>-1.27</v>
       </c>
       <c r="I201" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J201" t="n">
         <v>41.1</v>
@@ -15768,7 +15768,7 @@
         <v>-1.68</v>
       </c>
       <c r="I202" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J202" t="n">
         <v>41.29</v>
@@ -15847,7 +15847,7 @@
         <v>-11.05</v>
       </c>
       <c r="I203" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J203" t="n">
         <v>41.37</v>
@@ -15922,7 +15922,7 @@
         <v>7.11</v>
       </c>
       <c r="I204" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J204" t="n">
         <v>41.5</v>
@@ -15997,7 +15997,7 @@
         <v>8.15</v>
       </c>
       <c r="I205" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J205" t="n">
         <v>42.05</v>
@@ -16072,7 +16072,7 @@
         <v>3.69</v>
       </c>
       <c r="I206" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J206" t="n">
         <v>42.62</v>
@@ -16147,7 +16147,7 @@
         <v>1.02</v>
       </c>
       <c r="I207" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J207" t="n">
         <v>43.01</v>
@@ -16222,7 +16222,7 @@
         <v>1.17</v>
       </c>
       <c r="I208" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J208" t="n">
         <v>43.41</v>
@@ -16297,7 +16297,7 @@
         <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J209" t="n">
         <v>43.67</v>
@@ -16372,7 +16372,7 @@
         <v>-0.88</v>
       </c>
       <c r="I210" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J210" t="n">
         <v>43.79</v>
@@ -16447,7 +16447,7 @@
         <v>-0.34</v>
       </c>
       <c r="I211" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J211" t="n">
         <v>43.91</v>
@@ -16526,7 +16526,7 @@
         <v>-3.76</v>
       </c>
       <c r="I212" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J212" t="n">
         <v>43.82</v>
@@ -16601,7 +16601,7 @@
         <v>12.4</v>
       </c>
       <c r="I213" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J213" t="n">
         <v>43.86</v>
@@ -16676,7 +16676,7 @@
         <v>4.19</v>
       </c>
       <c r="I214" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J214" t="n">
         <v>44.06</v>
@@ -16751,7 +16751,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J215" t="n">
         <v>44.43</v>
@@ -16826,7 +16826,7 @@
         <v>-3.17</v>
       </c>
       <c r="I216" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J216" t="n">
         <v>44.65</v>
@@ -16901,7 +16901,7 @@
         <v>-5.05</v>
       </c>
       <c r="I217" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J217" t="n">
         <v>44.74</v>
@@ -16976,7 +16976,7 @@
         <v>8.65</v>
       </c>
       <c r="I218" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J218" t="n">
         <v>44.96</v>
@@ -17051,7 +17051,7 @@
         <v>1.3</v>
       </c>
       <c r="I219" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J219" t="n">
         <v>45.25</v>
@@ -17126,7 +17126,7 @@
         <v>2.6</v>
       </c>
       <c r="I220" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J220" t="n">
         <v>45.97</v>
@@ -17201,7 +17201,7 @@
         <v>-1.23</v>
       </c>
       <c r="I221" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J221" t="n">
         <v>46.68</v>
@@ -17276,7 +17276,7 @@
         <v>4.88</v>
       </c>
       <c r="I222" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J222" t="n">
         <v>47.56</v>
@@ -17351,7 +17351,7 @@
         <v>4.6</v>
       </c>
       <c r="I223" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J223" t="n">
         <v>48.79</v>
@@ -17426,7 +17426,7 @@
         <v>-4.63</v>
       </c>
       <c r="I224" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J224" t="n">
         <v>49.76</v>
@@ -17501,7 +17501,7 @@
         <v>9.57</v>
       </c>
       <c r="I225" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J225" t="n">
         <v>50.85</v>
@@ -17576,7 +17576,7 @@
         <v>0.38</v>
       </c>
       <c r="I226" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J226" t="n">
         <v>51.87</v>
@@ -17651,7 +17651,7 @@
         <v>-3.33</v>
       </c>
       <c r="I227" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J227" t="n">
         <v>52.76</v>
@@ -17726,7 +17726,7 @@
         <v>-1.46</v>
       </c>
       <c r="I228" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J228" t="n">
         <v>53.59</v>
@@ -17801,7 +17801,7 @@
         <v>7.02</v>
       </c>
       <c r="I229" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J229" t="n">
         <v>54.62</v>
@@ -17876,7 +17876,7 @@
         <v>7.89</v>
       </c>
       <c r="I230" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J230" t="n">
         <v>55.94</v>
@@ -17951,7 +17951,7 @@
         <v>0.54</v>
       </c>
       <c r="I231" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J231" t="n">
         <v>57.28</v>
@@ -18026,7 +18026,7 @@
         <v>-12.31</v>
       </c>
       <c r="I232" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J232" t="n">
         <v>58.26</v>
@@ -18101,7 +18101,7 @@
         <v>5.52</v>
       </c>
       <c r="I233" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J233" t="n">
         <v>59.16</v>
@@ -18176,7 +18176,7 @@
         <v>-6.14</v>
       </c>
       <c r="I234" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J234" t="n">
         <v>59.76</v>
@@ -18251,7 +18251,7 @@
         <v>-13.08</v>
       </c>
       <c r="I235" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J235" t="n">
         <v>59.72</v>
@@ -18330,7 +18330,7 @@
         <v>0.11</v>
       </c>
       <c r="I236" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J236" t="n">
         <v>59.77</v>
@@ -18405,7 +18405,7 @@
         <v>15.95</v>
       </c>
       <c r="I237" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J237" t="n">
         <v>60.37</v>
@@ -18480,7 +18480,7 @@
         <v>3.69</v>
       </c>
       <c r="I238" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J238" t="n">
         <v>60.88</v>
@@ -18555,7 +18555,7 @@
         <v>-1.08</v>
       </c>
       <c r="I239" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J239" t="n">
         <v>61.31</v>
@@ -18630,7 +18630,7 @@
         <v>7.44</v>
       </c>
       <c r="I240" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J240" t="n">
         <v>61.91</v>
@@ -18705,7 +18705,7 @@
         <v>-7.28</v>
       </c>
       <c r="I241" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J241" t="n">
         <v>62.29</v>
@@ -18780,7 +18780,7 @@
         <v>2.36</v>
       </c>
       <c r="I242" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J242" t="n">
         <v>62.62</v>
@@ -18855,7 +18855,7 @@
         <v>-0.37</v>
       </c>
       <c r="I243" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J243" t="n">
         <v>62.8</v>
@@ -18930,7 +18930,7 @@
         <v>3.02</v>
       </c>
       <c r="I244" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J244" t="n">
         <v>63.22</v>
@@ -19005,7 +19005,7 @@
         <v>-1.6</v>
       </c>
       <c r="I245" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J245" t="n">
         <v>63.31</v>
@@ -19080,7 +19080,7 @@
         <v>2.88</v>
       </c>
       <c r="I246" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J246" t="n">
         <v>63.47</v>
@@ -19155,7 +19155,7 @@
         <v>-1.86</v>
       </c>
       <c r="I247" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J247" t="n">
         <v>63.69</v>
@@ -19230,7 +19230,7 @@
         <v>4.06</v>
       </c>
       <c r="I248" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J248" t="n">
         <v>64.08</v>
@@ -19305,7 +19305,7 @@
         <v>4.85</v>
       </c>
       <c r="I249" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J249" t="n">
         <v>64.42</v>
@@ -19380,7 +19380,7 @@
         <v>-9.07</v>
       </c>
       <c r="I250" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J250" t="n">
         <v>64.19</v>
@@ -19455,7 +19455,7 @@
         <v>-3.94</v>
       </c>
       <c r="I251" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J251" t="n">
         <v>63.8</v>
@@ -19534,7 +19534,7 @@
         <v>-0.02</v>
       </c>
       <c r="I252" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J252" t="n">
         <v>63.85</v>
@@ -19609,7 +19609,7 @@
         <v>-14.89</v>
       </c>
       <c r="I253" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>63.26</v>
@@ -19688,7 +19688,7 @@
         <v>5.99</v>
       </c>
       <c r="I254" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J254" t="n">
         <v>63.03</v>
@@ -19763,7 +19763,7 @@
         <v>-3.22</v>
       </c>
       <c r="I255" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J255" t="n">
         <v>63.11</v>
@@ -19842,7 +19842,7 @@
         <v>-12.6</v>
       </c>
       <c r="I256" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J256" t="n">
         <v>62.84</v>
@@ -19921,7 +19921,7 @@
         <v>11.35</v>
       </c>
       <c r="I257" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J257" t="n">
         <v>62.42</v>
@@ -19996,7 +19996,7 @@
         <v>2.36</v>
       </c>
       <c r="I258" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J258" t="n">
         <v>61.95</v>
@@ -20071,7 +20071,7 @@
         <v>2.75</v>
       </c>
       <c r="I259" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J259" t="n">
         <v>61.59</v>
@@ -20146,7 +20146,7 @@
         <v>-10.35</v>
       </c>
       <c r="I260" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J260" t="n">
         <v>60.7</v>
@@ -20219,7 +20219,7 @@
         <v>0.88</v>
       </c>
       <c r="I261" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J261" t="n">
         <v>60.08</v>
@@ -20298,7 +20298,7 @@
         <v>5.84</v>
       </c>
       <c r="I262" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J262" t="n">
         <v>59.54</v>
@@ -20373,7 +20373,7 @@
         <v>2.35</v>
       </c>
       <c r="I263" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J263" t="n">
         <v>59.07</v>
@@ -20448,7 +20448,7 @@
         <v>-1.69</v>
       </c>
       <c r="I264" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J264" t="n">
         <v>58.45</v>
@@ -20523,7 +20523,7 @@
         <v>1.54</v>
       </c>
       <c r="I265" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J265" t="n">
         <v>57.93</v>
@@ -20598,7 +20598,7 @@
         <v>-6.75</v>
       </c>
       <c r="I266" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J266" t="n">
         <v>57.14</v>
@@ -20677,7 +20677,7 @@
         <v>3.7</v>
       </c>
       <c r="I267" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J267" t="n">
         <v>56.5</v>
@@ -20752,7 +20752,7 @@
         <v>3.62</v>
       </c>
       <c r="I268" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J268" t="n">
         <v>55.82</v>
@@ -20827,7 +20827,7 @@
         <v>3.79</v>
       </c>
       <c r="I269" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J269" t="n">
         <v>55.08</v>
@@ -20902,7 +20902,7 @@
         <v>-14.14</v>
       </c>
       <c r="I270" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J270" t="n">
         <v>54.26</v>
@@ -20981,7 +20981,7 @@
         <v>-4.82</v>
       </c>
       <c r="I271" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J271" t="n">
         <v>53.45</v>
@@ -21060,7 +21060,7 @@
         <v>-12.86</v>
       </c>
       <c r="I272" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J272" t="n">
         <v>52.34</v>
@@ -21135,7 +21135,7 @@
         <v>17.96</v>
       </c>
       <c r="I273" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J273" t="n">
         <v>52.07</v>
@@ -21210,7 +21210,7 @@
         <v>9.09</v>
       </c>
       <c r="I274" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J274" t="n">
         <v>51.85</v>
@@ -21285,7 +21285,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I275" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J275" t="n">
         <v>51.75</v>
@@ -21360,7 +21360,7 @@
         <v>3.89</v>
       </c>
       <c r="I276" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J276" t="n">
         <v>52.1</v>
@@ -21435,7 +21435,7 @@
         <v>3.18</v>
       </c>
       <c r="I277" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J277" t="n">
         <v>52.26</v>
@@ -21514,7 +21514,7 @@
         <v>19.38</v>
       </c>
       <c r="I278" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J278" t="n">
         <v>52.9</v>
@@ -21589,7 +21589,7 @@
         <v>6.63</v>
       </c>
       <c r="I279" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J279" t="n">
         <v>53.7</v>
@@ -21664,7 +21664,7 @@
         <v>6.13</v>
       </c>
       <c r="I280" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J280" t="n">
         <v>55</v>
@@ -21739,7 +21739,7 @@
         <v>5.46</v>
       </c>
       <c r="I281" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J281" t="n">
         <v>56.49</v>
@@ -21814,7 +21814,7 @@
         <v>5.89</v>
       </c>
       <c r="I282" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J282" t="n">
         <v>58.07</v>
@@ -21889,7 +21889,7 @@
         <v>0.76</v>
       </c>
       <c r="I283" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J283" t="n">
         <v>59.62</v>
@@ -21964,7 +21964,7 @@
         <v>2.81</v>
       </c>
       <c r="I284" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J284" t="n">
         <v>61.34</v>
@@ -22039,7 +22039,7 @@
         <v>7.15</v>
       </c>
       <c r="I285" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J285" t="n">
         <v>63.33</v>
@@ -22114,7 +22114,7 @@
         <v>1.33</v>
       </c>
       <c r="I286" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J286" t="n">
         <v>65.56999999999999</v>
@@ -22189,7 +22189,7 @@
         <v>2.24</v>
       </c>
       <c r="I287" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J287" t="n">
         <v>67.81999999999999</v>
@@ -22264,7 +22264,7 @@
         <v>7.69</v>
       </c>
       <c r="I288" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J288" t="n">
         <v>70.34999999999999</v>
@@ -22339,7 +22339,7 @@
         <v>6.75</v>
       </c>
       <c r="I289" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J289" t="n">
         <v>73.14</v>
@@ -22414,7 +22414,7 @@
         <v>13.79</v>
       </c>
       <c r="I290" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J290" t="n">
         <v>77.09999999999999</v>
@@ -22489,7 +22489,7 @@
         <v>-3.84</v>
       </c>
       <c r="I291" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J291" t="n">
         <v>80.94</v>
@@ -22564,7 +22564,7 @@
         <v>-11.21</v>
       </c>
       <c r="I292" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J292" t="n">
         <v>84.38</v>
@@ -22639,7 +22639,7 @@
         <v>7.67</v>
       </c>
       <c r="I293" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J293" t="n">
         <v>87.88</v>
@@ -22714,7 +22714,7 @@
         <v>7.64</v>
       </c>
       <c r="I294" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J294" t="n">
         <v>91.62</v>
@@ -22789,7 +22789,7 @@
         <v>2.69</v>
       </c>
       <c r="I295" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J295" t="n">
         <v>95.5</v>
@@ -22864,7 +22864,7 @@
         <v>-2.18</v>
       </c>
       <c r="I296" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J296" t="n">
         <v>99.13</v>
@@ -22939,7 +22939,7 @@
         <v>13.02</v>
       </c>
       <c r="I297" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J297" t="n">
         <v>103.51</v>
@@ -23014,7 +23014,7 @@
         <v>15.04</v>
       </c>
       <c r="I298" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J298" t="n">
         <v>108.42</v>
@@ -23089,7 +23089,7 @@
         <v>-8.289999999999999</v>
       </c>
       <c r="I299" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J299" t="n">
         <v>112.43</v>
@@ -23164,7 +23164,7 @@
         <v>16.33</v>
       </c>
       <c r="I300" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J300" t="n">
         <v>117.45</v>
@@ -23239,7 +23239,7 @@
         <v>7.62</v>
       </c>
       <c r="I301" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J301" t="n">
         <v>122.94</v>
@@ -23314,7 +23314,7 @@
         <v>-9.4</v>
       </c>
       <c r="I302" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J302" t="n">
         <v>127.3</v>
@@ -23389,7 +23389,7 @@
         <v>6.79</v>
       </c>
       <c r="I303" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J303" t="n">
         <v>132.21</v>
@@ -23464,7 +23464,7 @@
         <v>1.06</v>
       </c>
       <c r="I304" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J304" t="n">
         <v>137.1</v>
@@ -23539,7 +23539,7 @@
         <v>-11.82</v>
       </c>
       <c r="I305" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J305" t="n">
         <v>140.57</v>
@@ -23614,7 +23614,7 @@
         <v>-7.57</v>
       </c>
       <c r="I306" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J306" t="n">
         <v>143.36</v>
@@ -23689,7 +23689,7 @@
         <v>0.09</v>
       </c>
       <c r="I307" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J307" t="n">
         <v>146.05</v>
@@ -23764,7 +23764,7 @@
         <v>14.03</v>
       </c>
       <c r="I308" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J308" t="n">
         <v>149.42</v>
@@ -23839,7 +23839,7 @@
         <v>2.99</v>
       </c>
       <c r="I309" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J309" t="n">
         <v>152.7</v>
@@ -23914,7 +23914,7 @@
         <v>6.83</v>
       </c>
       <c r="I310" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J310" t="n">
         <v>155.81</v>
@@ -23989,7 +23989,7 @@
         <v>18.48</v>
       </c>
       <c r="I311" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J311" t="n">
         <v>160.93</v>
@@ -24064,7 +24064,7 @@
         <v>-3.46</v>
       </c>
       <c r="I312" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J312" t="n">
         <v>166.34</v>
@@ -24139,7 +24139,7 @@
         <v>3.05</v>
       </c>
       <c r="I313" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J313" t="n">
         <v>171.67</v>
@@ -24214,7 +24214,7 @@
         <v>-0.13</v>
       </c>
       <c r="I314" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J314" t="n">
         <v>176.54</v>
@@ -24289,7 +24289,7 @@
         <v>1.2</v>
       </c>
       <c r="I315" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J315" t="n">
         <v>181.37</v>
@@ -24364,7 +24364,7 @@
         <v>17.31</v>
       </c>
       <c r="I316" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J316" t="n">
         <v>188.3</v>
@@ -24439,7 +24439,7 @@
         <v>5.34</v>
       </c>
       <c r="I317" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J317" t="n">
         <v>195.12</v>
@@ -24514,7 +24514,7 @@
         <v>-6.36</v>
       </c>
       <c r="I318" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J318" t="n">
         <v>199.96</v>
@@ -24589,7 +24589,7 @@
         <v>-30.51</v>
       </c>
       <c r="I319" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J319" s="4" t="n">
         <v>201.48</v>
@@ -24668,7 +24668,7 @@
         <v>15.83</v>
       </c>
       <c r="I320" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J320" t="n">
         <v>203.2</v>
@@ -24743,7 +24743,7 @@
         <v>-4.61</v>
       </c>
       <c r="I321" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J321" t="n">
         <v>203.76</v>
@@ -24822,7 +24822,7 @@
         <v>-10.43</v>
       </c>
       <c r="I322" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J322" t="n">
         <v>204.17</v>
@@ -24897,7 +24897,7 @@
         <v>23.99</v>
       </c>
       <c r="I323" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J323" t="n">
         <v>206.15</v>
@@ -24972,7 +24972,7 @@
         <v>4.78</v>
       </c>
       <c r="I324" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J324" t="n">
         <v>208.58</v>
@@ -25047,7 +25047,7 @@
         <v>16.11</v>
       </c>
       <c r="I325" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J325" t="n">
         <v>213.99</v>
@@ -25122,7 +25122,7 @@
         <v>-16.99</v>
       </c>
       <c r="I326" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J326" s="4" t="n">
         <v>217.71</v>
@@ -25197,7 +25197,7 @@
         <v>3.39</v>
       </c>
       <c r="I327" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J327" t="n">
         <v>221.81</v>
@@ -25272,7 +25272,7 @@
         <v>19.43</v>
       </c>
       <c r="I328" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J328" t="n">
         <v>227.11</v>
@@ -25347,7 +25347,7 @@
         <v>7.69</v>
       </c>
       <c r="I329" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J329" t="n">
         <v>233.22</v>
@@ -25422,7 +25422,7 @@
         <v>-23.06</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>235.26</v>
@@ -25501,7 +25501,7 @@
         <v>-0.8</v>
       </c>
       <c r="I331" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J331" t="n">
         <v>235.45</v>
@@ -25576,7 +25576,7 @@
         <v>10.03</v>
       </c>
       <c r="I332" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J332" t="n">
         <v>237.18</v>
@@ -25651,7 +25651,7 @@
         <v>-14.65</v>
       </c>
       <c r="I333" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J333" s="4" t="n">
         <v>236.73</v>
@@ -25730,7 +25730,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I334" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J334" t="n">
         <v>237.34</v>
@@ -25805,7 +25805,7 @@
         <v>12.76</v>
       </c>
       <c r="I335" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J335" t="n">
         <v>239.32</v>
@@ -25880,7 +25880,7 @@
         <v>-18.43</v>
       </c>
       <c r="I336" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J336" s="4" t="n">
         <v>236.89</v>
@@ -25959,7 +25959,7 @@
         <v>-16.59</v>
       </c>
       <c r="I337" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J337" s="4" t="n">
         <v>231.94</v>
@@ -26034,7 +26034,7 @@
         <v>7.26</v>
       </c>
       <c r="I338" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J338" t="n">
         <v>228.54</v>
@@ -26109,7 +26109,7 @@
         <v>-15.09</v>
       </c>
       <c r="I339" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J339" s="4" t="n">
         <v>227.67</v>
@@ -26188,7 +26188,7 @@
         <v>5.78</v>
       </c>
       <c r="I340" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J340" t="n">
         <v>225.84</v>
@@ -26263,7 +26263,7 @@
         <v>10.08</v>
       </c>
       <c r="I341" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J341" t="n">
         <v>225.38</v>
@@ -26338,7 +26338,7 @@
         <v>-0.1</v>
       </c>
       <c r="I342" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J342" t="n">
         <v>225.96</v>
@@ -26413,7 +26413,7 @@
         <v>-13.99</v>
       </c>
       <c r="I343" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J343" t="n">
         <v>223.03</v>
@@ -26492,7 +26492,7 @@
         <v>6.83</v>
       </c>
       <c r="I344" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J344" t="n">
         <v>220.13</v>
@@ -26567,7 +26567,7 @@
         <v>-6.29</v>
       </c>
       <c r="I345" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J345" t="n">
         <v>214.79</v>
@@ -26642,7 +26642,7 @@
         <v>-13.93</v>
       </c>
       <c r="I346" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J346" t="n">
         <v>210.61</v>
@@ -26717,7 +26717,7 @@
         <v>-4.92</v>
       </c>
       <c r="I347" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J347" t="n">
         <v>205.69</v>
@@ -26792,7 +26792,7 @@
         <v>0.99</v>
       </c>
       <c r="I348" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J348" t="n">
         <v>198.57</v>
@@ -26867,7 +26867,7 @@
         <v>15.89</v>
       </c>
       <c r="I349" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J349" t="n">
         <v>191.46</v>
@@ -26942,7 +26942,7 @@
         <v>1.54</v>
       </c>
       <c r="I350" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J350" t="n">
         <v>187.94</v>
@@ -27017,7 +27017,7 @@
         <v>-2.16</v>
       </c>
       <c r="I351" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J351" t="n">
         <v>184.34</v>
@@ -27092,7 +27092,7 @@
         <v>-13.14</v>
       </c>
       <c r="I352" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J352" t="n">
         <v>178.56</v>
@@ -27167,7 +27167,7 @@
         <v>-6.33</v>
       </c>
       <c r="I353" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J353" t="n">
         <v>174.19</v>
@@ -27246,7 +27246,7 @@
         <v>-14.52</v>
       </c>
       <c r="I354" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>167.84</v>
@@ -27321,7 +27321,7 @@
         <v>-16.02</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>159.11</v>
@@ -27400,7 +27400,7 @@
         <v>24.7</v>
       </c>
       <c r="I356" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J356" t="n">
         <v>153.97</v>
@@ -27475,7 +27475,7 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J357" t="n">
         <v>150.64</v>
@@ -27550,7 +27550,7 @@
         <v>1.74</v>
       </c>
       <c r="I358" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J358" t="n">
         <v>146.74</v>
@@ -27625,7 +27625,7 @@
         <v>19.87</v>
       </c>
       <c r="I359" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J359" t="n">
         <v>145.48</v>
@@ -27700,7 +27700,7 @@
         <v>-5.6</v>
       </c>
       <c r="I360" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J360" t="n">
         <v>143.34</v>
@@ -27779,7 +27779,7 @@
         <v>0.2</v>
       </c>
       <c r="I361" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J361" t="n">
         <v>140.34</v>
@@ -27854,7 +27854,7 @@
         <v>5.99</v>
       </c>
       <c r="I362" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J362" t="n">
         <v>137.74</v>
@@ -27929,7 +27929,7 @@
         <v>-7.31</v>
       </c>
       <c r="I363" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J363" t="n">
         <v>135.97</v>
@@ -28008,7 +28008,7 @@
         <v>2.31</v>
       </c>
       <c r="I364" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J364" t="n">
         <v>133.79</v>
@@ -28083,7 +28083,7 @@
         <v>6.89</v>
       </c>
       <c r="I365" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J365" t="n">
         <v>132.62</v>
@@ -28158,7 +28158,7 @@
         <v>2.25</v>
       </c>
       <c r="I366" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J366" t="n">
         <v>132.76</v>
@@ -28233,7 +28233,7 @@
         <v>-0.28</v>
       </c>
       <c r="I367" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J367" t="n">
         <v>133.24</v>
@@ -28308,7 +28308,7 @@
         <v>4.54</v>
       </c>
       <c r="I368" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J368" t="n">
         <v>133.97</v>
@@ -28383,7 +28383,7 @@
         <v>-14.8</v>
       </c>
       <c r="I369" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>132.5</v>
@@ -28462,7 +28462,7 @@
         <v>-6.48</v>
       </c>
       <c r="I370" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J370" t="n">
         <v>130.49</v>
@@ -28537,7 +28537,7 @@
         <v>1.22</v>
       </c>
       <c r="I371" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J371" t="n">
         <v>128.73</v>
@@ -28612,7 +28612,7 @@
         <v>-1.32</v>
       </c>
       <c r="I372" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J372" t="n">
         <v>127.92</v>
@@ -28687,7 +28687,7 @@
         <v>-7.82</v>
       </c>
       <c r="I373" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J373" t="n">
         <v>127.07</v>
@@ -28762,7 +28762,7 @@
         <v>4.05</v>
       </c>
       <c r="I374" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J374" t="n">
         <v>127.37</v>
@@ -28837,7 +28837,7 @@
         <v>0.8</v>
       </c>
       <c r="I375" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J375" t="n">
         <v>128.6</v>
@@ -28912,7 +28912,7 @@
         <v>5.54</v>
       </c>
       <c r="I376" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J376" t="n">
         <v>129.02</v>
@@ -28987,7 +28987,7 @@
         <v>-9.51</v>
       </c>
       <c r="I377" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J377" t="n">
         <v>128.85</v>
@@ -29062,7 +29062,7 @@
         <v>1.3</v>
       </c>
       <c r="I378" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J378" t="n">
         <v>128.66</v>
@@ -29137,7 +29137,7 @@
         <v>-6.1</v>
       </c>
       <c r="I379" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J379" t="n">
         <v>126.96</v>
@@ -29216,7 +29216,7 @@
         <v>0.42</v>
       </c>
       <c r="I380" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J380" t="n">
         <v>125.67</v>
@@ -29295,7 +29295,7 @@
         <v>0.37</v>
       </c>
       <c r="I381" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J381" t="n">
         <v>124.39</v>
@@ -29374,7 +29374,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="I382" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J382" t="n">
         <v>123.25</v>
@@ -29449,7 +29449,7 @@
         <v>5.11</v>
       </c>
       <c r="I383" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J383" t="n">
         <v>122.91</v>
@@ -29524,7 +29524,7 @@
         <v>2.11</v>
       </c>
       <c r="I384" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J384" t="n">
         <v>122.55</v>
@@ -29599,7 +29599,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="I385" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J385" t="n">
         <v>121.23</v>
@@ -29678,7 +29678,7 @@
         <v>5.24</v>
       </c>
       <c r="I386" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J386" t="n">
         <v>120.06</v>
@@ -29753,7 +29753,7 @@
         <v>-16.99</v>
       </c>
       <c r="I387" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>117.87</v>
@@ -29832,7 +29832,7 @@
         <v>1.18</v>
       </c>
       <c r="I388" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J388" t="n">
         <v>115.41</v>
@@ -29907,7 +29907,7 @@
         <v>1.61</v>
       </c>
       <c r="I389" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J389" t="n">
         <v>114.15</v>
@@ -29982,7 +29982,7 @@
         <v>10.43</v>
       </c>
       <c r="I390" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J390" t="n">
         <v>113.86</v>
@@ -30057,7 +30057,7 @@
         <v>7.71</v>
       </c>
       <c r="I391" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J391" t="n">
         <v>113.93</v>
@@ -30132,7 +30132,7 @@
         <v>14.77</v>
       </c>
       <c r="I392" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J392" t="n">
         <v>115</v>
@@ -30207,7 +30207,7 @@
         <v>7.13</v>
       </c>
       <c r="I393" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J393" t="n">
         <v>117.04</v>
@@ -30282,7 +30282,7 @@
         <v>-3.75</v>
       </c>
       <c r="I394" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J394" t="n">
         <v>118.57</v>
@@ -30357,7 +30357,7 @@
         <v>0.05</v>
       </c>
       <c r="I395" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J395" t="n">
         <v>120.06</v>
@@ -30432,7 +30432,7 @@
         <v>3.5</v>
       </c>
       <c r="I396" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J396" t="n">
         <v>121.49</v>
@@ -30507,7 +30507,7 @@
         <v>-6.05</v>
       </c>
       <c r="I397" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J397" t="n">
         <v>123.04</v>
@@ -30582,7 +30582,7 @@
         <v>3.31</v>
       </c>
       <c r="I398" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J398" t="n">
         <v>124.75</v>
@@ -30657,7 +30657,7 @@
         <v>0.59</v>
       </c>
       <c r="I399" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J399" t="n">
         <v>126.85</v>
@@ -30732,7 +30732,7 @@
         <v>3.94</v>
       </c>
       <c r="I400" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J400" t="n">
         <v>129.22</v>
@@ -30807,7 +30807,7 @@
         <v>6.52</v>
       </c>
       <c r="I401" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J401" t="n">
         <v>132.08</v>
@@ -30882,7 +30882,7 @@
         <v>0.34</v>
       </c>
       <c r="I402" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J402" t="n">
         <v>134.43</v>
@@ -30957,7 +30957,7 @@
         <v>-0.01</v>
       </c>
       <c r="I403" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J403" t="n">
         <v>136.48</v>
@@ -31032,7 +31032,7 @@
         <v>-3.26</v>
       </c>
       <c r="I404" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J404" t="n">
         <v>138.14</v>
@@ -31111,7 +31111,7 @@
         <v>-10.31</v>
       </c>
       <c r="I405" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J405" t="n">
         <v>139.48</v>
@@ -31186,7 +31186,7 @@
         <v>-1.94</v>
       </c>
       <c r="I406" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J406" t="n">
         <v>140.38</v>
@@ -31265,7 +31265,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="I407" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J407" t="n">
         <v>141.75</v>
@@ -31344,7 +31344,7 @@
         <v>-0.65</v>
       </c>
       <c r="I408" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J408" t="n">
         <v>143.01</v>
@@ -31419,7 +31419,7 @@
         <v>-13.35</v>
       </c>
       <c r="I409" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J409" t="n">
         <v>143.35</v>
@@ -31494,7 +31494,7 @@
         <v>-2.89</v>
       </c>
       <c r="I410" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J410" t="n">
         <v>142.98</v>
@@ -31573,7 +31573,7 @@
         <v>-12.74</v>
       </c>
       <c r="I411" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J411" t="n">
         <v>141.48</v>
@@ -31652,7 +31652,7 @@
         <v>5.32</v>
       </c>
       <c r="I412" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J412" t="n">
         <v>139.32</v>
@@ -31731,7 +31731,7 @@
         <v>-1.12</v>
       </c>
       <c r="I413" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="J413" t="n">
         <v>136.6</v>
@@ -31749,7 +31749,7 @@
         <v>22.98</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31779,6 +31779,81 @@
       <c r="W413" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>94.51000000000001</v>
+      </c>
+      <c r="D414" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="E414" t="n">
+        <v>102.44</v>
+      </c>
+      <c r="F414" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="G414" t="n">
+        <v>12094285</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>134.43</v>
+      </c>
+      <c r="K414" t="n">
+        <v>126.79</v>
+      </c>
+      <c r="L414" t="n">
+        <v>160.35</v>
+      </c>
+      <c r="M414" t="n">
+        <v>122.84</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -608,7 +608,7 @@
         <v>-9.789999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J2" t="n">
         <v>26.7</v>
@@ -683,7 +683,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J3" t="n">
         <v>26.46</v>
@@ -758,7 +758,7 @@
         <v>6.29</v>
       </c>
       <c r="I4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J4" t="n">
         <v>26.24</v>
@@ -833,7 +833,7 @@
         <v>-12.39</v>
       </c>
       <c r="I5" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J5" t="n">
         <v>25.82</v>
@@ -912,7 +912,7 @@
         <v>8.59</v>
       </c>
       <c r="I6" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J6" t="n">
         <v>25.49</v>
@@ -987,7 +987,7 @@
         <v>-13.84</v>
       </c>
       <c r="I7" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J7" t="n">
         <v>25.07</v>
@@ -1070,7 +1070,7 @@
         <v>-3.19</v>
       </c>
       <c r="I8" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J8" t="n">
         <v>24.58</v>
@@ -1153,7 +1153,7 @@
         <v>5.09</v>
       </c>
       <c r="I9" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J9" t="n">
         <v>24.13</v>
@@ -1232,7 +1232,7 @@
         <v>-1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J10" t="n">
         <v>23.66</v>
@@ -1311,7 +1311,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J11" t="n">
         <v>23.23</v>
@@ -1386,7 +1386,7 @@
         <v>4.98</v>
       </c>
       <c r="I12" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J12" t="n">
         <v>22.84</v>
@@ -1461,7 +1461,7 @@
         <v>-4.12</v>
       </c>
       <c r="I13" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J13" t="n">
         <v>22.34</v>
@@ -1536,7 +1536,7 @@
         <v>2.22</v>
       </c>
       <c r="I14" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J14" t="n">
         <v>21.79</v>
@@ -1611,7 +1611,7 @@
         <v>-2.17</v>
       </c>
       <c r="I15" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J15" t="n">
         <v>21.21</v>
@@ -1686,7 +1686,7 @@
         <v>-3.28</v>
       </c>
       <c r="I16" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J16" t="n">
         <v>20.74</v>
@@ -1761,7 +1761,7 @@
         <v>8.93</v>
       </c>
       <c r="I17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J17" t="n">
         <v>20.45</v>
@@ -1836,7 +1836,7 @@
         <v>-1.82</v>
       </c>
       <c r="I18" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J18" t="n">
         <v>20.23</v>
@@ -1911,7 +1911,7 @@
         <v>-8.6</v>
       </c>
       <c r="I19" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J19" t="n">
         <v>19.86</v>
@@ -1990,7 +1990,7 @@
         <v>-5.45</v>
       </c>
       <c r="I20" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J20" t="n">
         <v>19.66</v>
@@ -2065,7 +2065,7 @@
         <v>-9.779999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J21" t="n">
         <v>19.33</v>
@@ -2140,7 +2140,7 @@
         <v>-0.5</v>
       </c>
       <c r="I22" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J22" t="n">
         <v>19.11</v>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J23" t="n">
         <v>18.88</v>
@@ -2290,7 +2290,7 @@
         <v>1.95</v>
       </c>
       <c r="I24" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J24" t="n">
         <v>18.6</v>
@@ -2365,7 +2365,7 @@
         <v>-29.83</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>18.21</v>
@@ -2448,7 +2448,7 @@
         <v>-23.5</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>17.61</v>
@@ -2531,7 +2531,7 @@
         <v>4.83</v>
       </c>
       <c r="I27" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J27" t="n">
         <v>17.17</v>
@@ -2614,7 +2614,7 @@
         <v>-9.77</v>
       </c>
       <c r="I28" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J28" t="n">
         <v>16.72</v>
@@ -2697,7 +2697,7 @@
         <v>54.74</v>
       </c>
       <c r="I29" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J29" t="n">
         <v>16.45</v>
@@ -2776,7 +2776,7 @@
         <v>-24.61</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>16.03</v>
@@ -2859,7 +2859,7 @@
         <v>6.26</v>
       </c>
       <c r="I31" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J31" t="n">
         <v>15.55</v>
@@ -2942,7 +2942,7 @@
         <v>2.36</v>
       </c>
       <c r="I32" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J32" t="n">
         <v>15.04</v>
@@ -3021,7 +3021,7 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J33" t="n">
         <v>14.58</v>
@@ -3096,7 +3096,7 @@
         <v>-11.93</v>
       </c>
       <c r="I34" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J34" t="n">
         <v>14.04</v>
@@ -3179,7 +3179,7 @@
         <v>-1.51</v>
       </c>
       <c r="I35" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J35" t="n">
         <v>13.5</v>
@@ -3258,7 +3258,7 @@
         <v>-5.35</v>
       </c>
       <c r="I36" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J36" t="n">
         <v>12.98</v>
@@ -3333,7 +3333,7 @@
         <v>5.42</v>
       </c>
       <c r="I37" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J37" t="n">
         <v>12.4</v>
@@ -3408,7 +3408,7 @@
         <v>12.14</v>
       </c>
       <c r="I38" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J38" t="n">
         <v>11.89</v>
@@ -3487,7 +3487,7 @@
         <v>16.59</v>
       </c>
       <c r="I39" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J39" t="n">
         <v>11.55</v>
@@ -3562,7 +3562,7 @@
         <v>2.85</v>
       </c>
       <c r="I40" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J40" t="n">
         <v>11.28</v>
@@ -3637,7 +3637,7 @@
         <v>-0.41</v>
       </c>
       <c r="I41" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J41" t="n">
         <v>11.09</v>
@@ -3712,7 +3712,7 @@
         <v>-3.51</v>
       </c>
       <c r="I42" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J42" t="n">
         <v>10.89</v>
@@ -3787,7 +3787,7 @@
         <v>2.54</v>
       </c>
       <c r="I43" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J43" t="n">
         <v>10.7</v>
@@ -3862,7 +3862,7 @@
         <v>-0.5</v>
       </c>
       <c r="I44" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J44" t="n">
         <v>10.49</v>
@@ -3937,7 +3937,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J45" t="n">
         <v>10.59</v>
@@ -4012,7 +4012,7 @@
         <v>-1.81</v>
       </c>
       <c r="I46" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J46" t="n">
         <v>10.8</v>
@@ -4087,7 +4087,7 @@
         <v>-3.15</v>
       </c>
       <c r="I47" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J47" t="n">
         <v>10.98</v>
@@ -4162,7 +4162,7 @@
         <v>5.08</v>
       </c>
       <c r="I48" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J48" t="n">
         <v>11.23</v>
@@ -4237,7 +4237,7 @@
         <v>2.8</v>
       </c>
       <c r="I49" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J49" t="n">
         <v>11.27</v>
@@ -4312,7 +4312,7 @@
         <v>3.31</v>
       </c>
       <c r="I50" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J50" t="n">
         <v>11.49</v>
@@ -4387,7 +4387,7 @@
         <v>21.42</v>
       </c>
       <c r="I51" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J51" t="n">
         <v>11.84</v>
@@ -4462,7 +4462,7 @@
         <v>8.56</v>
       </c>
       <c r="I52" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J52" t="n">
         <v>12.24</v>
@@ -4537,7 +4537,7 @@
         <v>1.3</v>
       </c>
       <c r="I53" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J53" t="n">
         <v>12.65</v>
@@ -4612,7 +4612,7 @@
         <v>-1.97</v>
       </c>
       <c r="I54" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J54" t="n">
         <v>13.11</v>
@@ -4687,7 +4687,7 @@
         <v>-0.44</v>
       </c>
       <c r="I55" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J55" t="n">
         <v>13.56</v>
@@ -4762,7 +4762,7 @@
         <v>-1.75</v>
       </c>
       <c r="I56" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J56" t="n">
         <v>14.03</v>
@@ -4837,7 +4837,7 @@
         <v>-0.5</v>
       </c>
       <c r="I57" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J57" t="n">
         <v>14.47</v>
@@ -4912,7 +4912,7 @@
         <v>-5.42</v>
       </c>
       <c r="I58" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J58" t="n">
         <v>14.8</v>
@@ -4987,7 +4987,7 @@
         <v>-2.89</v>
       </c>
       <c r="I59" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J59" t="n">
         <v>15.03</v>
@@ -5062,7 +5062,7 @@
         <v>-4.68</v>
       </c>
       <c r="I60" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J60" t="n">
         <v>15.19</v>
@@ -5137,7 +5137,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J61" t="n">
         <v>15.44</v>
@@ -5212,7 +5212,7 @@
         <v>-1.45</v>
       </c>
       <c r="I62" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J62" t="n">
         <v>15.7</v>
@@ -5287,7 +5287,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J63" t="n">
         <v>15.95</v>
@@ -5362,7 +5362,7 @@
         <v>-6.01</v>
       </c>
       <c r="I64" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J64" t="n">
         <v>16.16</v>
@@ -5441,7 +5441,7 @@
         <v>4.53</v>
       </c>
       <c r="I65" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J65" t="n">
         <v>16.33</v>
@@ -5516,7 +5516,7 @@
         <v>8.32</v>
       </c>
       <c r="I66" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J66" t="n">
         <v>16.6</v>
@@ -5591,7 +5591,7 @@
         <v>4.28</v>
       </c>
       <c r="I67" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J67" t="n">
         <v>16.92</v>
@@ -5666,7 +5666,7 @@
         <v>-1.47</v>
       </c>
       <c r="I68" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J68" t="n">
         <v>17.19</v>
@@ -5741,7 +5741,7 @@
         <v>1.98</v>
       </c>
       <c r="I69" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J69" t="n">
         <v>17.47</v>
@@ -5816,7 +5816,7 @@
         <v>7.33</v>
       </c>
       <c r="I70" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J70" t="n">
         <v>17.79</v>
@@ -5891,7 +5891,7 @@
         <v>6.34</v>
       </c>
       <c r="I71" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J71" t="n">
         <v>18.03</v>
@@ -5966,7 +5966,7 @@
         <v>-1.15</v>
       </c>
       <c r="I72" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J72" t="n">
         <v>18.18</v>
@@ -6041,7 +6041,7 @@
         <v>0.23</v>
       </c>
       <c r="I73" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J73" t="n">
         <v>18.32</v>
@@ -6116,7 +6116,7 @@
         <v>-7.59</v>
       </c>
       <c r="I74" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J74" t="n">
         <v>18.4</v>
@@ -6195,7 +6195,7 @@
         <v>9.27</v>
       </c>
       <c r="I75" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J75" t="n">
         <v>18.57</v>
@@ -6270,7 +6270,7 @@
         <v>-2.2</v>
       </c>
       <c r="I76" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J76" t="n">
         <v>18.74</v>
@@ -6345,7 +6345,7 @@
         <v>0.89</v>
       </c>
       <c r="I77" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J77" t="n">
         <v>18.92</v>
@@ -6420,7 +6420,7 @@
         <v>-1.86</v>
       </c>
       <c r="I78" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J78" t="n">
         <v>19.13</v>
@@ -6495,7 +6495,7 @@
         <v>1.75</v>
       </c>
       <c r="I79" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J79" t="n">
         <v>19.38</v>
@@ -6570,7 +6570,7 @@
         <v>11.35</v>
       </c>
       <c r="I80" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J80" t="n">
         <v>19.8</v>
@@ -6645,7 +6645,7 @@
         <v>2.63</v>
       </c>
       <c r="I81" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J81" t="n">
         <v>20.16</v>
@@ -6720,7 +6720,7 @@
         <v>2.52</v>
       </c>
       <c r="I82" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J82" t="n">
         <v>20.57</v>
@@ -6795,7 +6795,7 @@
         <v>-0.36</v>
       </c>
       <c r="I83" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J83" t="n">
         <v>20.97</v>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J84" t="n">
         <v>21.42</v>
@@ -6945,7 +6945,7 @@
         <v>-1.59</v>
       </c>
       <c r="I85" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J85" t="n">
         <v>21.81</v>
@@ -7020,7 +7020,7 @@
         <v>5.43</v>
       </c>
       <c r="I86" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J86" t="n">
         <v>22.2</v>
@@ -7095,7 +7095,7 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J87" t="n">
         <v>22.57</v>
@@ -7170,7 +7170,7 @@
         <v>-5.53</v>
       </c>
       <c r="I88" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J88" t="n">
         <v>22.89</v>
@@ -7245,7 +7245,7 @@
         <v>5.61</v>
       </c>
       <c r="I89" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J89" t="n">
         <v>23.25</v>
@@ -7320,7 +7320,7 @@
         <v>1.02</v>
       </c>
       <c r="I90" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J90" t="n">
         <v>23.55</v>
@@ -7395,7 +7395,7 @@
         <v>2.7</v>
       </c>
       <c r="I91" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J91" t="n">
         <v>23.83</v>
@@ -7470,7 +7470,7 @@
         <v>-0.29</v>
       </c>
       <c r="I92" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J92" t="n">
         <v>24.12</v>
@@ -7545,7 +7545,7 @@
         <v>-2.9</v>
       </c>
       <c r="I93" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J93" t="n">
         <v>24.36</v>
@@ -7620,7 +7620,7 @@
         <v>2.98</v>
       </c>
       <c r="I94" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J94" t="n">
         <v>24.72</v>
@@ -7695,7 +7695,7 @@
         <v>-0.95</v>
       </c>
       <c r="I95" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J95" t="n">
         <v>24.98</v>
@@ -7770,7 +7770,7 @@
         <v>1.07</v>
       </c>
       <c r="I96" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J96" t="n">
         <v>25.28</v>
@@ -7845,7 +7845,7 @@
         <v>0.04</v>
       </c>
       <c r="I97" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J97" t="n">
         <v>25.57</v>
@@ -7920,7 +7920,7 @@
         <v>0.62</v>
       </c>
       <c r="I98" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J98" t="n">
         <v>25.89</v>
@@ -7995,7 +7995,7 @@
         <v>-4.26</v>
       </c>
       <c r="I99" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J99" t="n">
         <v>26.13</v>
@@ -8070,7 +8070,7 @@
         <v>-2.05</v>
       </c>
       <c r="I100" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J100" t="n">
         <v>26.22</v>
@@ -8149,7 +8149,7 @@
         <v>-0.62</v>
       </c>
       <c r="I101" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J101" t="n">
         <v>26.27</v>
@@ -8224,7 +8224,7 @@
         <v>-0.08</v>
       </c>
       <c r="I102" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J102" t="n">
         <v>26.29</v>
@@ -8299,7 +8299,7 @@
         <v>4.96</v>
       </c>
       <c r="I103" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J103" t="n">
         <v>26.38</v>
@@ -8374,7 +8374,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J104" t="n">
         <v>26.48</v>
@@ -8449,7 +8449,7 @@
         <v>2.15</v>
       </c>
       <c r="I105" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J105" t="n">
         <v>26.62</v>
@@ -8524,7 +8524,7 @@
         <v>-9.5</v>
       </c>
       <c r="I106" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J106" t="n">
         <v>26.57</v>
@@ -8603,7 +8603,7 @@
         <v>-3.61</v>
       </c>
       <c r="I107" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J107" t="n">
         <v>26.45</v>
@@ -8678,7 +8678,7 @@
         <v>3.82</v>
       </c>
       <c r="I108" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J108" t="n">
         <v>26.45</v>
@@ -8753,7 +8753,7 @@
         <v>-1.92</v>
       </c>
       <c r="I109" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J109" t="n">
         <v>26.36</v>
@@ -8828,7 +8828,7 @@
         <v>-2.16</v>
       </c>
       <c r="I110" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J110" t="n">
         <v>26.23</v>
@@ -8903,7 +8903,7 @@
         <v>4.21</v>
       </c>
       <c r="I111" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J111" t="n">
         <v>26.11</v>
@@ -8978,7 +8978,7 @@
         <v>2.84</v>
       </c>
       <c r="I112" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J112" t="n">
         <v>26.03</v>
@@ -9053,7 +9053,7 @@
         <v>-0.39</v>
       </c>
       <c r="I113" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J113" t="n">
         <v>25.99</v>
@@ -9128,7 +9128,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I114" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J114" t="n">
         <v>26.02</v>
@@ -9203,7 +9203,7 @@
         <v>4.54</v>
       </c>
       <c r="I115" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J115" t="n">
         <v>26.13</v>
@@ -9278,7 +9278,7 @@
         <v>0.51</v>
       </c>
       <c r="I116" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J116" t="n">
         <v>26.24</v>
@@ -9353,7 +9353,7 @@
         <v>-6.98</v>
       </c>
       <c r="I117" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J117" t="n">
         <v>26.24</v>
@@ -9428,7 +9428,7 @@
         <v>0.59</v>
       </c>
       <c r="I118" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J118" t="n">
         <v>26.24</v>
@@ -9503,7 +9503,7 @@
         <v>-4.65</v>
       </c>
       <c r="I119" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J119" t="n">
         <v>26.24</v>
@@ -9582,7 +9582,7 @@
         <v>-1.68</v>
       </c>
       <c r="I120" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J120" t="n">
         <v>26.24</v>
@@ -9657,7 +9657,7 @@
         <v>-1.75</v>
       </c>
       <c r="I121" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J121" t="n">
         <v>26.23</v>
@@ -9732,7 +9732,7 @@
         <v>8.25</v>
       </c>
       <c r="I122" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J122" t="n">
         <v>26.32</v>
@@ -9807,7 +9807,7 @@
         <v>-0.55</v>
       </c>
       <c r="I123" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J123" t="n">
         <v>26.34</v>
@@ -9882,7 +9882,7 @@
         <v>2.35</v>
       </c>
       <c r="I124" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J124" t="n">
         <v>26.38</v>
@@ -9957,7 +9957,7 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J125" t="n">
         <v>26.41</v>
@@ -10032,7 +10032,7 @@
         <v>1.24</v>
       </c>
       <c r="I126" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J126" t="n">
         <v>26.59</v>
@@ -10107,7 +10107,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J127" t="n">
         <v>26.69</v>
@@ -10186,7 +10186,7 @@
         <v>-3.04</v>
       </c>
       <c r="I128" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J128" t="n">
         <v>26.7</v>
@@ -10265,7 +10265,7 @@
         <v>-1.35</v>
       </c>
       <c r="I129" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J129" t="n">
         <v>26.72</v>
@@ -10340,7 +10340,7 @@
         <v>2.97</v>
       </c>
       <c r="I130" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J130" t="n">
         <v>26.8</v>
@@ -10415,7 +10415,7 @@
         <v>3.08</v>
       </c>
       <c r="I131" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J131" t="n">
         <v>26.87</v>
@@ -10490,7 +10490,7 @@
         <v>2.38</v>
       </c>
       <c r="I132" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J132" t="n">
         <v>26.94</v>
@@ -10565,7 +10565,7 @@
         <v>0.37</v>
       </c>
       <c r="I133" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J133" t="n">
         <v>27.02</v>
@@ -10640,7 +10640,7 @@
         <v>5.23</v>
       </c>
       <c r="I134" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J134" t="n">
         <v>27.05</v>
@@ -10715,7 +10715,7 @@
         <v>2</v>
       </c>
       <c r="I135" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J135" t="n">
         <v>27.05</v>
@@ -10790,7 +10790,7 @@
         <v>0.45</v>
       </c>
       <c r="I136" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J136" t="n">
         <v>27.04</v>
@@ -10865,7 +10865,7 @@
         <v>2.39</v>
       </c>
       <c r="I137" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J137" t="n">
         <v>27.17</v>
@@ -10940,7 +10940,7 @@
         <v>1.6</v>
       </c>
       <c r="I138" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J138" t="n">
         <v>27.32</v>
@@ -11015,7 +11015,7 @@
         <v>-0.03</v>
       </c>
       <c r="I139" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J139" t="n">
         <v>27.53</v>
@@ -11090,7 +11090,7 @@
         <v>10.41</v>
       </c>
       <c r="I140" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J140" t="n">
         <v>27.92</v>
@@ -11165,7 +11165,7 @@
         <v>-1.84</v>
       </c>
       <c r="I141" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J141" t="n">
         <v>28.3</v>
@@ -11240,7 +11240,7 @@
         <v>4.27</v>
       </c>
       <c r="I142" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J142" t="n">
         <v>28.65</v>
@@ -11315,7 +11315,7 @@
         <v>-0.35</v>
       </c>
       <c r="I143" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J143" t="n">
         <v>29</v>
@@ -11390,7 +11390,7 @@
         <v>-0.29</v>
       </c>
       <c r="I144" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J144" t="n">
         <v>29.32</v>
@@ -11465,7 +11465,7 @@
         <v>-1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J145" t="n">
         <v>29.6</v>
@@ -11540,7 +11540,7 @@
         <v>0.5</v>
       </c>
       <c r="I146" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J146" t="n">
         <v>29.88</v>
@@ -11615,7 +11615,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J147" t="n">
         <v>30.28</v>
@@ -11690,7 +11690,7 @@
         <v>2.41</v>
       </c>
       <c r="I148" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J148" t="n">
         <v>30.75</v>
@@ -11765,7 +11765,7 @@
         <v>5.8</v>
       </c>
       <c r="I149" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J149" t="n">
         <v>31.35</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="I150" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J150" t="n">
         <v>32.02</v>
@@ -11915,7 +11915,7 @@
         <v>-2.18</v>
       </c>
       <c r="I151" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J151" t="n">
         <v>32.61</v>
@@ -11990,7 +11990,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="I152" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J152" t="n">
         <v>33.34</v>
@@ -12065,7 +12065,7 @@
         <v>-6.91</v>
       </c>
       <c r="I153" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J153" t="n">
         <v>33.93</v>
@@ -12140,7 +12140,7 @@
         <v>10.18</v>
       </c>
       <c r="I154" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J154" t="n">
         <v>34.64</v>
@@ -12215,7 +12215,7 @@
         <v>-1.26</v>
       </c>
       <c r="I155" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J155" t="n">
         <v>35.29</v>
@@ -12290,7 +12290,7 @@
         <v>-19</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>35.53</v>
@@ -12369,7 +12369,7 @@
         <v>14.39</v>
       </c>
       <c r="I157" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J157" t="n">
         <v>35.99</v>
@@ -12444,7 +12444,7 @@
         <v>-6.39</v>
       </c>
       <c r="I158" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J158" t="n">
         <v>36.3</v>
@@ -12519,7 +12519,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J159" t="n">
         <v>36.78</v>
@@ -12594,7 +12594,7 @@
         <v>1.48</v>
       </c>
       <c r="I160" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J160" t="n">
         <v>37.12</v>
@@ -12669,7 +12669,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J161" t="n">
         <v>37.48</v>
@@ -12744,7 +12744,7 @@
         <v>4.84</v>
       </c>
       <c r="I162" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J162" t="n">
         <v>37.88</v>
@@ -12819,7 +12819,7 @@
         <v>-1.73</v>
       </c>
       <c r="I163" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J163" t="n">
         <v>38.24</v>
@@ -12894,7 +12894,7 @@
         <v>-7.52</v>
       </c>
       <c r="I164" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J164" t="n">
         <v>38.44</v>
@@ -12973,7 +12973,7 @@
         <v>7.25</v>
       </c>
       <c r="I165" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J165" t="n">
         <v>38.81</v>
@@ -13048,7 +13048,7 @@
         <v>4.79</v>
       </c>
       <c r="I166" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J166" t="n">
         <v>39.27</v>
@@ -13123,7 +13123,7 @@
         <v>8.58</v>
       </c>
       <c r="I167" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J167" t="n">
         <v>39.91</v>
@@ -13198,7 +13198,7 @@
         <v>0.26</v>
       </c>
       <c r="I168" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J168" t="n">
         <v>40.51</v>
@@ -13273,7 +13273,7 @@
         <v>5.16</v>
       </c>
       <c r="I169" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J169" t="n">
         <v>41.14</v>
@@ -13348,7 +13348,7 @@
         <v>-4.03</v>
       </c>
       <c r="I170" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J170" t="n">
         <v>41.55</v>
@@ -13423,7 +13423,7 @@
         <v>0.82</v>
       </c>
       <c r="I171" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J171" t="n">
         <v>42.03</v>
@@ -13498,7 +13498,7 @@
         <v>1.68</v>
       </c>
       <c r="I172" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J172" t="n">
         <v>42.37</v>
@@ -13573,7 +13573,7 @@
         <v>-11.91</v>
       </c>
       <c r="I173" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J173" t="n">
         <v>42.57</v>
@@ -13648,7 +13648,7 @@
         <v>9.42</v>
       </c>
       <c r="I174" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J174" t="n">
         <v>42.77</v>
@@ -13723,7 +13723,7 @@
         <v>-8.16</v>
       </c>
       <c r="I175" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J175" t="n">
         <v>42.81</v>
@@ -13798,7 +13798,7 @@
         <v>-2.95</v>
       </c>
       <c r="I176" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J176" t="n">
         <v>43.19</v>
@@ -13877,7 +13877,7 @@
         <v>7.72</v>
       </c>
       <c r="I177" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J177" t="n">
         <v>43.48</v>
@@ -13952,7 +13952,7 @@
         <v>-7.01</v>
       </c>
       <c r="I178" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J178" t="n">
         <v>43.74</v>
@@ -14031,7 +14031,7 @@
         <v>4.55</v>
       </c>
       <c r="I179" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J179" t="n">
         <v>43.92</v>
@@ -14106,7 +14106,7 @@
         <v>-10.28</v>
       </c>
       <c r="I180" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J180" t="n">
         <v>43.86</v>
@@ -14181,7 +14181,7 @@
         <v>-0.92</v>
       </c>
       <c r="I181" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J181" t="n">
         <v>43.79</v>
@@ -14256,7 +14256,7 @@
         <v>-5.18</v>
       </c>
       <c r="I182" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J182" t="n">
         <v>43.52</v>
@@ -14331,7 +14331,7 @@
         <v>-6.76</v>
       </c>
       <c r="I183" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J183" t="n">
         <v>43.16</v>
@@ -14410,7 +14410,7 @@
         <v>4.69</v>
       </c>
       <c r="I184" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J184" t="n">
         <v>43.04</v>
@@ -14485,7 +14485,7 @@
         <v>-14.33</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>42.52</v>
@@ -14568,7 +14568,7 @@
         <v>2.99</v>
       </c>
       <c r="I186" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J186" t="n">
         <v>41.95</v>
@@ -14643,7 +14643,7 @@
         <v>13.02</v>
       </c>
       <c r="I187" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J187" t="n">
         <v>41.4</v>
@@ -14718,7 +14718,7 @@
         <v>0.86</v>
       </c>
       <c r="I188" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J188" t="n">
         <v>40.86</v>
@@ -14793,7 +14793,7 @@
         <v>8.33</v>
       </c>
       <c r="I189" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J189" t="n">
         <v>40.35</v>
@@ -14868,7 +14868,7 @@
         <v>5.29</v>
       </c>
       <c r="I190" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J190" t="n">
         <v>40.05</v>
@@ -14943,7 +14943,7 @@
         <v>0.12</v>
       </c>
       <c r="I191" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J191" t="n">
         <v>39.72</v>
@@ -15018,7 +15018,7 @@
         <v>6.03</v>
       </c>
       <c r="I192" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J192" t="n">
         <v>39.48</v>
@@ -15093,7 +15093,7 @@
         <v>6.35</v>
       </c>
       <c r="I193" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J193" t="n">
         <v>39.67</v>
@@ -15168,7 +15168,7 @@
         <v>-3.05</v>
       </c>
       <c r="I194" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J194" t="n">
         <v>39.59</v>
@@ -15243,7 +15243,7 @@
         <v>2.97</v>
       </c>
       <c r="I195" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J195" t="n">
         <v>39.76</v>
@@ -15318,7 +15318,7 @@
         <v>3.21</v>
       </c>
       <c r="I196" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J196" t="n">
         <v>40.08</v>
@@ -15393,7 +15393,7 @@
         <v>-0.42</v>
       </c>
       <c r="I197" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J197" t="n">
         <v>40.22</v>
@@ -15468,7 +15468,7 @@
         <v>3.89</v>
       </c>
       <c r="I198" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J198" t="n">
         <v>40.61</v>
@@ -15543,7 +15543,7 @@
         <v>-1.73</v>
       </c>
       <c r="I199" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J199" t="n">
         <v>40.86</v>
@@ -15618,7 +15618,7 @@
         <v>-14.52</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>40.99</v>
@@ -15693,7 +15693,7 @@
         <v>-1.27</v>
       </c>
       <c r="I201" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J201" t="n">
         <v>41.1</v>
@@ -15768,7 +15768,7 @@
         <v>-1.68</v>
       </c>
       <c r="I202" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J202" t="n">
         <v>41.29</v>
@@ -15847,7 +15847,7 @@
         <v>-11.05</v>
       </c>
       <c r="I203" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J203" t="n">
         <v>41.37</v>
@@ -15922,7 +15922,7 @@
         <v>7.11</v>
       </c>
       <c r="I204" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J204" t="n">
         <v>41.5</v>
@@ -15997,7 +15997,7 @@
         <v>8.15</v>
       </c>
       <c r="I205" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J205" t="n">
         <v>42.05</v>
@@ -16072,7 +16072,7 @@
         <v>3.69</v>
       </c>
       <c r="I206" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J206" t="n">
         <v>42.62</v>
@@ -16147,7 +16147,7 @@
         <v>1.02</v>
       </c>
       <c r="I207" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J207" t="n">
         <v>43.01</v>
@@ -16222,7 +16222,7 @@
         <v>1.17</v>
       </c>
       <c r="I208" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J208" t="n">
         <v>43.41</v>
@@ -16297,7 +16297,7 @@
         <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J209" t="n">
         <v>43.67</v>
@@ -16372,7 +16372,7 @@
         <v>-0.88</v>
       </c>
       <c r="I210" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J210" t="n">
         <v>43.79</v>
@@ -16447,7 +16447,7 @@
         <v>-0.34</v>
       </c>
       <c r="I211" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J211" t="n">
         <v>43.91</v>
@@ -16526,7 +16526,7 @@
         <v>-3.76</v>
       </c>
       <c r="I212" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J212" t="n">
         <v>43.82</v>
@@ -16601,7 +16601,7 @@
         <v>12.4</v>
       </c>
       <c r="I213" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J213" t="n">
         <v>43.86</v>
@@ -16676,7 +16676,7 @@
         <v>4.19</v>
       </c>
       <c r="I214" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J214" t="n">
         <v>44.06</v>
@@ -16751,7 +16751,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J215" t="n">
         <v>44.43</v>
@@ -16826,7 +16826,7 @@
         <v>-3.17</v>
       </c>
       <c r="I216" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J216" t="n">
         <v>44.65</v>
@@ -16901,7 +16901,7 @@
         <v>-5.05</v>
       </c>
       <c r="I217" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J217" t="n">
         <v>44.74</v>
@@ -16976,7 +16976,7 @@
         <v>8.65</v>
       </c>
       <c r="I218" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J218" t="n">
         <v>44.96</v>
@@ -17051,7 +17051,7 @@
         <v>1.3</v>
       </c>
       <c r="I219" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J219" t="n">
         <v>45.25</v>
@@ -17126,7 +17126,7 @@
         <v>2.6</v>
       </c>
       <c r="I220" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J220" t="n">
         <v>45.97</v>
@@ -17201,7 +17201,7 @@
         <v>-1.23</v>
       </c>
       <c r="I221" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J221" t="n">
         <v>46.68</v>
@@ -17276,7 +17276,7 @@
         <v>4.88</v>
       </c>
       <c r="I222" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J222" t="n">
         <v>47.56</v>
@@ -17351,7 +17351,7 @@
         <v>4.6</v>
       </c>
       <c r="I223" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J223" t="n">
         <v>48.79</v>
@@ -17426,7 +17426,7 @@
         <v>-4.63</v>
       </c>
       <c r="I224" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J224" t="n">
         <v>49.76</v>
@@ -17501,7 +17501,7 @@
         <v>9.57</v>
       </c>
       <c r="I225" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J225" t="n">
         <v>50.85</v>
@@ -17576,7 +17576,7 @@
         <v>0.38</v>
       </c>
       <c r="I226" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J226" t="n">
         <v>51.87</v>
@@ -17651,7 +17651,7 @@
         <v>-3.33</v>
       </c>
       <c r="I227" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J227" t="n">
         <v>52.76</v>
@@ -17726,7 +17726,7 @@
         <v>-1.46</v>
       </c>
       <c r="I228" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J228" t="n">
         <v>53.59</v>
@@ -17801,7 +17801,7 @@
         <v>7.02</v>
       </c>
       <c r="I229" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J229" t="n">
         <v>54.62</v>
@@ -17876,7 +17876,7 @@
         <v>7.89</v>
       </c>
       <c r="I230" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J230" t="n">
         <v>55.94</v>
@@ -17951,7 +17951,7 @@
         <v>0.54</v>
       </c>
       <c r="I231" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J231" t="n">
         <v>57.28</v>
@@ -18026,7 +18026,7 @@
         <v>-12.31</v>
       </c>
       <c r="I232" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J232" t="n">
         <v>58.26</v>
@@ -18101,7 +18101,7 @@
         <v>5.52</v>
       </c>
       <c r="I233" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J233" t="n">
         <v>59.16</v>
@@ -18176,7 +18176,7 @@
         <v>-6.14</v>
       </c>
       <c r="I234" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J234" t="n">
         <v>59.76</v>
@@ -18251,7 +18251,7 @@
         <v>-13.08</v>
       </c>
       <c r="I235" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J235" t="n">
         <v>59.72</v>
@@ -18330,7 +18330,7 @@
         <v>0.11</v>
       </c>
       <c r="I236" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J236" t="n">
         <v>59.77</v>
@@ -18405,7 +18405,7 @@
         <v>15.95</v>
       </c>
       <c r="I237" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J237" t="n">
         <v>60.37</v>
@@ -18480,7 +18480,7 @@
         <v>3.69</v>
       </c>
       <c r="I238" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J238" t="n">
         <v>60.88</v>
@@ -18555,7 +18555,7 @@
         <v>-1.08</v>
       </c>
       <c r="I239" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J239" t="n">
         <v>61.31</v>
@@ -18630,7 +18630,7 @@
         <v>7.44</v>
       </c>
       <c r="I240" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J240" t="n">
         <v>61.91</v>
@@ -18705,7 +18705,7 @@
         <v>-7.28</v>
       </c>
       <c r="I241" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J241" t="n">
         <v>62.29</v>
@@ -18780,7 +18780,7 @@
         <v>2.36</v>
       </c>
       <c r="I242" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J242" t="n">
         <v>62.62</v>
@@ -18855,7 +18855,7 @@
         <v>-0.37</v>
       </c>
       <c r="I243" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J243" t="n">
         <v>62.8</v>
@@ -18930,7 +18930,7 @@
         <v>3.02</v>
       </c>
       <c r="I244" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J244" t="n">
         <v>63.22</v>
@@ -19005,7 +19005,7 @@
         <v>-1.6</v>
       </c>
       <c r="I245" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J245" t="n">
         <v>63.31</v>
@@ -19080,7 +19080,7 @@
         <v>2.88</v>
       </c>
       <c r="I246" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J246" t="n">
         <v>63.47</v>
@@ -19155,7 +19155,7 @@
         <v>-1.86</v>
       </c>
       <c r="I247" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J247" t="n">
         <v>63.69</v>
@@ -19230,7 +19230,7 @@
         <v>4.06</v>
       </c>
       <c r="I248" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J248" t="n">
         <v>64.08</v>
@@ -19305,7 +19305,7 @@
         <v>4.85</v>
       </c>
       <c r="I249" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J249" t="n">
         <v>64.42</v>
@@ -19380,7 +19380,7 @@
         <v>-9.07</v>
       </c>
       <c r="I250" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J250" t="n">
         <v>64.19</v>
@@ -19455,7 +19455,7 @@
         <v>-3.94</v>
       </c>
       <c r="I251" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J251" t="n">
         <v>63.8</v>
@@ -19534,7 +19534,7 @@
         <v>-0.02</v>
       </c>
       <c r="I252" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J252" t="n">
         <v>63.85</v>
@@ -19609,7 +19609,7 @@
         <v>-14.89</v>
       </c>
       <c r="I253" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>63.26</v>
@@ -19688,7 +19688,7 @@
         <v>5.99</v>
       </c>
       <c r="I254" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J254" t="n">
         <v>63.03</v>
@@ -19763,7 +19763,7 @@
         <v>-3.22</v>
       </c>
       <c r="I255" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J255" t="n">
         <v>63.11</v>
@@ -19842,7 +19842,7 @@
         <v>-12.6</v>
       </c>
       <c r="I256" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J256" t="n">
         <v>62.84</v>
@@ -19921,7 +19921,7 @@
         <v>11.35</v>
       </c>
       <c r="I257" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J257" t="n">
         <v>62.42</v>
@@ -19996,7 +19996,7 @@
         <v>2.36</v>
       </c>
       <c r="I258" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J258" t="n">
         <v>61.95</v>
@@ -20071,7 +20071,7 @@
         <v>2.75</v>
       </c>
       <c r="I259" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J259" t="n">
         <v>61.59</v>
@@ -20146,7 +20146,7 @@
         <v>-10.35</v>
       </c>
       <c r="I260" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J260" t="n">
         <v>60.7</v>
@@ -20219,7 +20219,7 @@
         <v>0.88</v>
       </c>
       <c r="I261" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J261" t="n">
         <v>60.08</v>
@@ -20298,7 +20298,7 @@
         <v>5.84</v>
       </c>
       <c r="I262" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J262" t="n">
         <v>59.54</v>
@@ -20373,7 +20373,7 @@
         <v>2.35</v>
       </c>
       <c r="I263" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J263" t="n">
         <v>59.07</v>
@@ -20448,7 +20448,7 @@
         <v>-1.69</v>
       </c>
       <c r="I264" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J264" t="n">
         <v>58.45</v>
@@ -20523,7 +20523,7 @@
         <v>1.54</v>
       </c>
       <c r="I265" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J265" t="n">
         <v>57.93</v>
@@ -20598,7 +20598,7 @@
         <v>-6.75</v>
       </c>
       <c r="I266" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J266" t="n">
         <v>57.14</v>
@@ -20677,7 +20677,7 @@
         <v>3.7</v>
       </c>
       <c r="I267" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J267" t="n">
         <v>56.5</v>
@@ -20752,7 +20752,7 @@
         <v>3.62</v>
       </c>
       <c r="I268" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J268" t="n">
         <v>55.82</v>
@@ -20827,7 +20827,7 @@
         <v>3.79</v>
       </c>
       <c r="I269" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J269" t="n">
         <v>55.08</v>
@@ -20902,7 +20902,7 @@
         <v>-14.14</v>
       </c>
       <c r="I270" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J270" t="n">
         <v>54.26</v>
@@ -20981,7 +20981,7 @@
         <v>-4.82</v>
       </c>
       <c r="I271" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J271" t="n">
         <v>53.45</v>
@@ -21060,7 +21060,7 @@
         <v>-12.86</v>
       </c>
       <c r="I272" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J272" t="n">
         <v>52.34</v>
@@ -21135,7 +21135,7 @@
         <v>17.96</v>
       </c>
       <c r="I273" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J273" t="n">
         <v>52.07</v>
@@ -21210,7 +21210,7 @@
         <v>9.09</v>
       </c>
       <c r="I274" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J274" t="n">
         <v>51.85</v>
@@ -21285,7 +21285,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I275" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J275" t="n">
         <v>51.75</v>
@@ -21360,7 +21360,7 @@
         <v>3.89</v>
       </c>
       <c r="I276" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J276" t="n">
         <v>52.1</v>
@@ -21435,7 +21435,7 @@
         <v>3.18</v>
       </c>
       <c r="I277" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J277" t="n">
         <v>52.26</v>
@@ -21514,7 +21514,7 @@
         <v>19.38</v>
       </c>
       <c r="I278" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J278" t="n">
         <v>52.9</v>
@@ -21589,7 +21589,7 @@
         <v>6.63</v>
       </c>
       <c r="I279" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J279" t="n">
         <v>53.7</v>
@@ -21664,7 +21664,7 @@
         <v>6.13</v>
       </c>
       <c r="I280" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J280" t="n">
         <v>55</v>
@@ -21739,7 +21739,7 @@
         <v>5.46</v>
       </c>
       <c r="I281" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J281" t="n">
         <v>56.49</v>
@@ -21814,7 +21814,7 @@
         <v>5.89</v>
       </c>
       <c r="I282" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J282" t="n">
         <v>58.07</v>
@@ -21889,7 +21889,7 @@
         <v>0.76</v>
       </c>
       <c r="I283" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J283" t="n">
         <v>59.62</v>
@@ -21964,7 +21964,7 @@
         <v>2.81</v>
       </c>
       <c r="I284" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J284" t="n">
         <v>61.34</v>
@@ -22039,7 +22039,7 @@
         <v>7.15</v>
       </c>
       <c r="I285" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J285" t="n">
         <v>63.33</v>
@@ -22114,7 +22114,7 @@
         <v>1.33</v>
       </c>
       <c r="I286" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J286" t="n">
         <v>65.56999999999999</v>
@@ -22189,7 +22189,7 @@
         <v>2.24</v>
       </c>
       <c r="I287" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J287" t="n">
         <v>67.81999999999999</v>
@@ -22264,7 +22264,7 @@
         <v>7.69</v>
       </c>
       <c r="I288" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J288" t="n">
         <v>70.34999999999999</v>
@@ -22339,7 +22339,7 @@
         <v>6.75</v>
       </c>
       <c r="I289" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J289" t="n">
         <v>73.14</v>
@@ -22414,7 +22414,7 @@
         <v>13.79</v>
       </c>
       <c r="I290" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J290" t="n">
         <v>77.09999999999999</v>
@@ -22489,7 +22489,7 @@
         <v>-3.84</v>
       </c>
       <c r="I291" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J291" t="n">
         <v>80.94</v>
@@ -22564,7 +22564,7 @@
         <v>-11.21</v>
       </c>
       <c r="I292" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J292" t="n">
         <v>84.38</v>
@@ -22639,7 +22639,7 @@
         <v>7.67</v>
       </c>
       <c r="I293" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J293" t="n">
         <v>87.88</v>
@@ -22714,7 +22714,7 @@
         <v>7.64</v>
       </c>
       <c r="I294" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J294" t="n">
         <v>91.62</v>
@@ -22789,7 +22789,7 @@
         <v>2.69</v>
       </c>
       <c r="I295" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J295" t="n">
         <v>95.5</v>
@@ -22864,7 +22864,7 @@
         <v>-2.18</v>
       </c>
       <c r="I296" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J296" t="n">
         <v>99.13</v>
@@ -22939,7 +22939,7 @@
         <v>13.02</v>
       </c>
       <c r="I297" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J297" t="n">
         <v>103.51</v>
@@ -23014,7 +23014,7 @@
         <v>15.04</v>
       </c>
       <c r="I298" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J298" t="n">
         <v>108.42</v>
@@ -23089,7 +23089,7 @@
         <v>-8.289999999999999</v>
       </c>
       <c r="I299" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J299" t="n">
         <v>112.43</v>
@@ -23164,7 +23164,7 @@
         <v>16.33</v>
       </c>
       <c r="I300" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J300" t="n">
         <v>117.45</v>
@@ -23239,7 +23239,7 @@
         <v>7.62</v>
       </c>
       <c r="I301" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J301" t="n">
         <v>122.94</v>
@@ -23314,7 +23314,7 @@
         <v>-9.4</v>
       </c>
       <c r="I302" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J302" t="n">
         <v>127.3</v>
@@ -23389,7 +23389,7 @@
         <v>6.79</v>
       </c>
       <c r="I303" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J303" t="n">
         <v>132.21</v>
@@ -23464,7 +23464,7 @@
         <v>1.06</v>
       </c>
       <c r="I304" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J304" t="n">
         <v>137.1</v>
@@ -23539,7 +23539,7 @@
         <v>-11.82</v>
       </c>
       <c r="I305" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J305" t="n">
         <v>140.57</v>
@@ -23614,7 +23614,7 @@
         <v>-7.57</v>
       </c>
       <c r="I306" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J306" t="n">
         <v>143.36</v>
@@ -23689,7 +23689,7 @@
         <v>0.09</v>
       </c>
       <c r="I307" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J307" t="n">
         <v>146.05</v>
@@ -23764,7 +23764,7 @@
         <v>14.03</v>
       </c>
       <c r="I308" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J308" t="n">
         <v>149.42</v>
@@ -23839,7 +23839,7 @@
         <v>2.99</v>
       </c>
       <c r="I309" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J309" t="n">
         <v>152.7</v>
@@ -23914,7 +23914,7 @@
         <v>6.83</v>
       </c>
       <c r="I310" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J310" t="n">
         <v>155.81</v>
@@ -23989,7 +23989,7 @@
         <v>18.48</v>
       </c>
       <c r="I311" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J311" t="n">
         <v>160.93</v>
@@ -24064,7 +24064,7 @@
         <v>-3.46</v>
       </c>
       <c r="I312" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J312" t="n">
         <v>166.34</v>
@@ -24139,7 +24139,7 @@
         <v>3.05</v>
       </c>
       <c r="I313" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J313" t="n">
         <v>171.67</v>
@@ -24214,7 +24214,7 @@
         <v>-0.13</v>
       </c>
       <c r="I314" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J314" t="n">
         <v>176.54</v>
@@ -24289,7 +24289,7 @@
         <v>1.2</v>
       </c>
       <c r="I315" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J315" t="n">
         <v>181.37</v>
@@ -24364,7 +24364,7 @@
         <v>17.31</v>
       </c>
       <c r="I316" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J316" t="n">
         <v>188.3</v>
@@ -24439,7 +24439,7 @@
         <v>5.34</v>
       </c>
       <c r="I317" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J317" t="n">
         <v>195.12</v>
@@ -24514,7 +24514,7 @@
         <v>-6.36</v>
       </c>
       <c r="I318" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J318" t="n">
         <v>199.96</v>
@@ -24589,7 +24589,7 @@
         <v>-30.51</v>
       </c>
       <c r="I319" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J319" s="4" t="n">
         <v>201.48</v>
@@ -24668,7 +24668,7 @@
         <v>15.83</v>
       </c>
       <c r="I320" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J320" t="n">
         <v>203.2</v>
@@ -24743,7 +24743,7 @@
         <v>-4.61</v>
       </c>
       <c r="I321" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J321" t="n">
         <v>203.76</v>
@@ -24822,7 +24822,7 @@
         <v>-10.43</v>
       </c>
       <c r="I322" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J322" t="n">
         <v>204.17</v>
@@ -24897,7 +24897,7 @@
         <v>23.99</v>
       </c>
       <c r="I323" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J323" t="n">
         <v>206.15</v>
@@ -24972,7 +24972,7 @@
         <v>4.78</v>
       </c>
       <c r="I324" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J324" t="n">
         <v>208.58</v>
@@ -25047,7 +25047,7 @@
         <v>16.11</v>
       </c>
       <c r="I325" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J325" t="n">
         <v>213.99</v>
@@ -25122,7 +25122,7 @@
         <v>-16.99</v>
       </c>
       <c r="I326" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J326" s="4" t="n">
         <v>217.71</v>
@@ -25197,7 +25197,7 @@
         <v>3.39</v>
       </c>
       <c r="I327" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J327" t="n">
         <v>221.81</v>
@@ -25272,7 +25272,7 @@
         <v>19.43</v>
       </c>
       <c r="I328" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J328" t="n">
         <v>227.11</v>
@@ -25347,7 +25347,7 @@
         <v>7.69</v>
       </c>
       <c r="I329" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J329" t="n">
         <v>233.22</v>
@@ -25422,7 +25422,7 @@
         <v>-23.06</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>235.26</v>
@@ -25501,7 +25501,7 @@
         <v>-0.8</v>
       </c>
       <c r="I331" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J331" t="n">
         <v>235.45</v>
@@ -25576,7 +25576,7 @@
         <v>10.03</v>
       </c>
       <c r="I332" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J332" t="n">
         <v>237.18</v>
@@ -25651,7 +25651,7 @@
         <v>-14.65</v>
       </c>
       <c r="I333" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J333" s="4" t="n">
         <v>236.73</v>
@@ -25730,7 +25730,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I334" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J334" t="n">
         <v>237.34</v>
@@ -25805,7 +25805,7 @@
         <v>12.76</v>
       </c>
       <c r="I335" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J335" t="n">
         <v>239.32</v>
@@ -25880,7 +25880,7 @@
         <v>-18.43</v>
       </c>
       <c r="I336" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J336" s="4" t="n">
         <v>236.89</v>
@@ -25959,7 +25959,7 @@
         <v>-16.59</v>
       </c>
       <c r="I337" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J337" s="4" t="n">
         <v>231.94</v>
@@ -26034,7 +26034,7 @@
         <v>7.26</v>
       </c>
       <c r="I338" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J338" t="n">
         <v>228.54</v>
@@ -26109,7 +26109,7 @@
         <v>-15.09</v>
       </c>
       <c r="I339" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J339" s="4" t="n">
         <v>227.67</v>
@@ -26188,7 +26188,7 @@
         <v>5.78</v>
       </c>
       <c r="I340" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J340" t="n">
         <v>225.84</v>
@@ -26263,7 +26263,7 @@
         <v>10.08</v>
       </c>
       <c r="I341" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J341" t="n">
         <v>225.38</v>
@@ -26338,7 +26338,7 @@
         <v>-0.1</v>
       </c>
       <c r="I342" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J342" t="n">
         <v>225.96</v>
@@ -26413,7 +26413,7 @@
         <v>-13.99</v>
       </c>
       <c r="I343" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J343" t="n">
         <v>223.03</v>
@@ -26492,7 +26492,7 @@
         <v>6.83</v>
       </c>
       <c r="I344" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J344" t="n">
         <v>220.13</v>
@@ -26567,7 +26567,7 @@
         <v>-6.29</v>
       </c>
       <c r="I345" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J345" t="n">
         <v>214.79</v>
@@ -26642,7 +26642,7 @@
         <v>-13.93</v>
       </c>
       <c r="I346" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J346" t="n">
         <v>210.61</v>
@@ -26717,7 +26717,7 @@
         <v>-4.92</v>
       </c>
       <c r="I347" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J347" t="n">
         <v>205.69</v>
@@ -26792,7 +26792,7 @@
         <v>0.99</v>
       </c>
       <c r="I348" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J348" t="n">
         <v>198.57</v>
@@ -26867,7 +26867,7 @@
         <v>15.89</v>
       </c>
       <c r="I349" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J349" t="n">
         <v>191.46</v>
@@ -26942,7 +26942,7 @@
         <v>1.54</v>
       </c>
       <c r="I350" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J350" t="n">
         <v>187.94</v>
@@ -27017,7 +27017,7 @@
         <v>-2.16</v>
       </c>
       <c r="I351" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J351" t="n">
         <v>184.34</v>
@@ -27092,7 +27092,7 @@
         <v>-13.14</v>
       </c>
       <c r="I352" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J352" t="n">
         <v>178.56</v>
@@ -27167,7 +27167,7 @@
         <v>-6.33</v>
       </c>
       <c r="I353" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J353" t="n">
         <v>174.19</v>
@@ -27246,7 +27246,7 @@
         <v>-14.52</v>
       </c>
       <c r="I354" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>167.84</v>
@@ -27321,7 +27321,7 @@
         <v>-16.02</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>159.11</v>
@@ -27400,7 +27400,7 @@
         <v>24.7</v>
       </c>
       <c r="I356" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J356" t="n">
         <v>153.97</v>
@@ -27475,7 +27475,7 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J357" t="n">
         <v>150.64</v>
@@ -27550,7 +27550,7 @@
         <v>1.74</v>
       </c>
       <c r="I358" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J358" t="n">
         <v>146.74</v>
@@ -27625,7 +27625,7 @@
         <v>19.87</v>
       </c>
       <c r="I359" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J359" t="n">
         <v>145.48</v>
@@ -27700,7 +27700,7 @@
         <v>-5.6</v>
       </c>
       <c r="I360" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J360" t="n">
         <v>143.34</v>
@@ -27779,7 +27779,7 @@
         <v>0.2</v>
       </c>
       <c r="I361" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J361" t="n">
         <v>140.34</v>
@@ -27854,7 +27854,7 @@
         <v>5.99</v>
       </c>
       <c r="I362" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J362" t="n">
         <v>137.74</v>
@@ -27929,7 +27929,7 @@
         <v>-7.31</v>
       </c>
       <c r="I363" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J363" t="n">
         <v>135.97</v>
@@ -28008,7 +28008,7 @@
         <v>2.31</v>
       </c>
       <c r="I364" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J364" t="n">
         <v>133.79</v>
@@ -28083,7 +28083,7 @@
         <v>6.89</v>
       </c>
       <c r="I365" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J365" t="n">
         <v>132.62</v>
@@ -28158,7 +28158,7 @@
         <v>2.25</v>
       </c>
       <c r="I366" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J366" t="n">
         <v>132.76</v>
@@ -28233,7 +28233,7 @@
         <v>-0.28</v>
       </c>
       <c r="I367" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J367" t="n">
         <v>133.24</v>
@@ -28308,7 +28308,7 @@
         <v>4.54</v>
       </c>
       <c r="I368" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J368" t="n">
         <v>133.97</v>
@@ -28383,7 +28383,7 @@
         <v>-14.8</v>
       </c>
       <c r="I369" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>132.5</v>
@@ -28462,7 +28462,7 @@
         <v>-6.48</v>
       </c>
       <c r="I370" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J370" t="n">
         <v>130.49</v>
@@ -28537,7 +28537,7 @@
         <v>1.22</v>
       </c>
       <c r="I371" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J371" t="n">
         <v>128.73</v>
@@ -28612,7 +28612,7 @@
         <v>-1.32</v>
       </c>
       <c r="I372" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J372" t="n">
         <v>127.92</v>
@@ -28687,7 +28687,7 @@
         <v>-7.82</v>
       </c>
       <c r="I373" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J373" t="n">
         <v>127.07</v>
@@ -28762,7 +28762,7 @@
         <v>4.05</v>
       </c>
       <c r="I374" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J374" t="n">
         <v>127.37</v>
@@ -28837,7 +28837,7 @@
         <v>0.8</v>
       </c>
       <c r="I375" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J375" t="n">
         <v>128.6</v>
@@ -28912,7 +28912,7 @@
         <v>5.54</v>
       </c>
       <c r="I376" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J376" t="n">
         <v>129.02</v>
@@ -28987,7 +28987,7 @@
         <v>-9.51</v>
       </c>
       <c r="I377" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J377" t="n">
         <v>128.85</v>
@@ -29062,7 +29062,7 @@
         <v>1.3</v>
       </c>
       <c r="I378" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J378" t="n">
         <v>128.66</v>
@@ -29137,7 +29137,7 @@
         <v>-6.1</v>
       </c>
       <c r="I379" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J379" t="n">
         <v>126.96</v>
@@ -29216,7 +29216,7 @@
         <v>0.42</v>
       </c>
       <c r="I380" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J380" t="n">
         <v>125.67</v>
@@ -29295,7 +29295,7 @@
         <v>0.37</v>
       </c>
       <c r="I381" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J381" t="n">
         <v>124.39</v>
@@ -29374,7 +29374,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="I382" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J382" t="n">
         <v>123.25</v>
@@ -29449,7 +29449,7 @@
         <v>5.11</v>
       </c>
       <c r="I383" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J383" t="n">
         <v>122.91</v>
@@ -29524,7 +29524,7 @@
         <v>2.11</v>
       </c>
       <c r="I384" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J384" t="n">
         <v>122.55</v>
@@ -29599,7 +29599,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="I385" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J385" t="n">
         <v>121.23</v>
@@ -29678,7 +29678,7 @@
         <v>5.24</v>
       </c>
       <c r="I386" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J386" t="n">
         <v>120.06</v>
@@ -29753,7 +29753,7 @@
         <v>-16.99</v>
       </c>
       <c r="I387" s="4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>117.87</v>
@@ -29832,7 +29832,7 @@
         <v>1.18</v>
       </c>
       <c r="I388" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J388" t="n">
         <v>115.41</v>
@@ -29907,7 +29907,7 @@
         <v>1.61</v>
       </c>
       <c r="I389" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J389" t="n">
         <v>114.15</v>
@@ -29982,7 +29982,7 @@
         <v>10.43</v>
       </c>
       <c r="I390" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J390" t="n">
         <v>113.86</v>
@@ -30057,7 +30057,7 @@
         <v>7.71</v>
       </c>
       <c r="I391" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J391" t="n">
         <v>113.93</v>
@@ -30132,7 +30132,7 @@
         <v>14.77</v>
       </c>
       <c r="I392" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J392" t="n">
         <v>115</v>
@@ -30207,7 +30207,7 @@
         <v>7.13</v>
       </c>
       <c r="I393" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J393" t="n">
         <v>117.04</v>
@@ -30282,7 +30282,7 @@
         <v>-3.75</v>
       </c>
       <c r="I394" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J394" t="n">
         <v>118.57</v>
@@ -30357,7 +30357,7 @@
         <v>0.05</v>
       </c>
       <c r="I395" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J395" t="n">
         <v>120.06</v>
@@ -30432,7 +30432,7 @@
         <v>3.5</v>
       </c>
       <c r="I396" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J396" t="n">
         <v>121.49</v>
@@ -30507,7 +30507,7 @@
         <v>-6.05</v>
       </c>
       <c r="I397" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J397" t="n">
         <v>123.04</v>
@@ -30582,7 +30582,7 @@
         <v>3.31</v>
       </c>
       <c r="I398" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J398" t="n">
         <v>124.75</v>
@@ -30657,7 +30657,7 @@
         <v>0.59</v>
       </c>
       <c r="I399" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J399" t="n">
         <v>126.85</v>
@@ -30732,7 +30732,7 @@
         <v>3.94</v>
       </c>
       <c r="I400" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J400" t="n">
         <v>129.22</v>
@@ -30807,7 +30807,7 @@
         <v>6.52</v>
       </c>
       <c r="I401" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J401" t="n">
         <v>132.08</v>
@@ -30882,7 +30882,7 @@
         <v>0.34</v>
       </c>
       <c r="I402" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J402" t="n">
         <v>134.43</v>
@@ -30957,7 +30957,7 @@
         <v>-0.01</v>
       </c>
       <c r="I403" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J403" t="n">
         <v>136.48</v>
@@ -31032,7 +31032,7 @@
         <v>-3.26</v>
       </c>
       <c r="I404" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J404" t="n">
         <v>138.14</v>
@@ -31111,7 +31111,7 @@
         <v>-10.31</v>
       </c>
       <c r="I405" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J405" t="n">
         <v>139.48</v>
@@ -31186,7 +31186,7 @@
         <v>-1.94</v>
       </c>
       <c r="I406" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J406" t="n">
         <v>140.38</v>
@@ -31265,7 +31265,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="I407" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J407" t="n">
         <v>141.75</v>
@@ -31344,7 +31344,7 @@
         <v>-0.65</v>
       </c>
       <c r="I408" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J408" t="n">
         <v>143.01</v>
@@ -31419,7 +31419,7 @@
         <v>-13.35</v>
       </c>
       <c r="I409" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J409" t="n">
         <v>143.35</v>
@@ -31494,7 +31494,7 @@
         <v>-2.89</v>
       </c>
       <c r="I410" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J410" t="n">
         <v>142.98</v>
@@ -31573,7 +31573,7 @@
         <v>-12.74</v>
       </c>
       <c r="I411" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J411" t="n">
         <v>141.48</v>
@@ -31652,7 +31652,7 @@
         <v>5.32</v>
       </c>
       <c r="I412" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J412" t="n">
         <v>139.32</v>
@@ -31731,7 +31731,7 @@
         <v>-1.12</v>
       </c>
       <c r="I413" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J413" t="n">
         <v>136.6</v>
@@ -31749,7 +31749,7 @@
         <v>22.98</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31792,43 +31792,43 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>94.51000000000001</v>
+        <v>102.86</v>
       </c>
       <c r="D414" t="n">
-        <v>104.35</v>
+        <v>104.96</v>
       </c>
       <c r="E414" t="n">
-        <v>102.44</v>
+        <v>99.31</v>
       </c>
       <c r="F414" t="n">
-        <v>102.9</v>
+        <v>104.21</v>
       </c>
       <c r="G414" t="n">
-        <v>12094285</v>
+        <v>57754094</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>5.48</v>
+        <v>6.83</v>
       </c>
       <c r="I414" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>134.43</v>
+        <v>134.5</v>
       </c>
       <c r="K414" t="n">
-        <v>126.79</v>
+        <v>126.82</v>
       </c>
       <c r="L414" t="n">
-        <v>160.35</v>
+        <v>160.36</v>
       </c>
       <c r="M414" t="n">
         <v>122.84</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>22.58</v>
+        <v>23.66</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31846,12 +31846,14 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U414" s="2" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -2862,7 +2862,7 @@
         <v>14.3</v>
       </c>
       <c r="J31" t="n">
-        <v>15.55</v>
+        <v>15.56</v>
       </c>
       <c r="K31" t="n">
         <v>22.42</v>
@@ -31725,7 +31725,7 @@
         <v>97.55</v>
       </c>
       <c r="G413" t="n">
-        <v>97546400</v>
+        <v>100094100</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-1.12</v>
@@ -31801,34 +31801,34 @@
         <v>99.31</v>
       </c>
       <c r="F414" t="n">
-        <v>104.21</v>
+        <v>103.24</v>
       </c>
       <c r="G414" t="n">
-        <v>57754094</v>
+        <v>76314129</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>6.83</v>
+        <v>5.83</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>134.5</v>
+        <v>134.45</v>
       </c>
       <c r="K414" t="n">
-        <v>126.82</v>
+        <v>126.8</v>
       </c>
       <c r="L414" t="n">
-        <v>160.36</v>
+        <v>160.35</v>
       </c>
       <c r="M414" t="n">
         <v>122.84</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>23.66</v>
+        <v>22.86</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31846,16 +31846,18 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>150.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31791,41 +31791,25 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>102.86</v>
-      </c>
-      <c r="D414" t="n">
-        <v>104.96</v>
-      </c>
-      <c r="E414" t="n">
-        <v>99.31</v>
-      </c>
-      <c r="F414" t="n">
-        <v>103.24</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>76314129</v>
       </c>
-      <c r="H414" s="3" t="n">
-        <v>5.83</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
-      <c r="J414" t="n">
-        <v>134.45</v>
-      </c>
-      <c r="K414" t="n">
-        <v>126.8</v>
-      </c>
-      <c r="L414" t="n">
-        <v>160.35</v>
-      </c>
-      <c r="M414" t="n">
-        <v>122.84</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="3" t="n">
-        <v>22.86</v>
+        <v>17.83</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>
@@ -31840,11 +31824,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
+      <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
         <v>5.15</v>
       </c>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31791,28 +31791,44 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>102.86</v>
+      </c>
+      <c r="D414" t="n">
+        <v>106.13</v>
+      </c>
+      <c r="E414" t="n">
+        <v>99.31</v>
+      </c>
+      <c r="F414" t="n">
+        <v>103.24</v>
+      </c>
       <c r="G414" t="n">
-        <v>76314129</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>77344000</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>5.83</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>134.45</v>
+      </c>
+      <c r="K414" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="L414" t="n">
+        <v>160.35</v>
+      </c>
+      <c r="M414" t="n">
+        <v>122.84</v>
+      </c>
       <c r="N414" s="3" t="n">
-        <v>17.83</v>
+        <v>22.86</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31824,7 +31840,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr"/>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S414" t="n">
         <v>5.15</v>
       </c>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31828,7 +31828,7 @@
         <v>22.86</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31858,6 +31858,81 @@
       <c r="W414" s="2" t="n">
         <v>150.4</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>102.86</v>
+      </c>
+      <c r="D415" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="E415" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="F415" t="n">
+        <v>90.66</v>
+      </c>
+      <c r="G415" t="n">
+        <v>26333346</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-12.19</v>
+      </c>
+      <c r="I415" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>131.67</v>
+      </c>
+      <c r="K415" t="n">
+        <v>126.78</v>
+      </c>
+      <c r="L415" t="n">
+        <v>160.02</v>
+      </c>
+      <c r="M415" t="n">
+        <v>123.02</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="O415" t="n">
+        <v>28</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31828,7 +31828,7 @@
         <v>22.86</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31860,79 +31860,81 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>SOXL</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>102.86</v>
-      </c>
-      <c r="D415" t="n">
-        <v>91.42</v>
-      </c>
-      <c r="E415" t="n">
-        <v>89.34999999999999</v>
-      </c>
-      <c r="F415" t="n">
-        <v>90.66</v>
-      </c>
-      <c r="G415" t="n">
-        <v>26333346</v>
-      </c>
-      <c r="H415" s="1" t="n">
-        <v>-12.19</v>
-      </c>
-      <c r="I415" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J415" t="n">
-        <v>131.67</v>
-      </c>
-      <c r="K415" t="n">
-        <v>126.78</v>
-      </c>
-      <c r="L415" t="n">
-        <v>160.02</v>
-      </c>
-      <c r="M415" t="n">
-        <v>123.02</v>
-      </c>
-      <c r="N415" s="3" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="O415" t="n">
-        <v>28</v>
-      </c>
-      <c r="P415" t="inlineStr">
-        <is>
-          <t>fear</t>
-        </is>
-      </c>
-      <c r="Q415" t="inlineStr">
+      <c r="C415" s="4" t="n">
+        <v>90.59</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>82.26000000000001</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>83.92</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>136017849</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-18.71</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>131.33</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>159.97</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="N415" s="6" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="O415" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="P415" s="4" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr">
+      <c r="R415" s="4" t="inlineStr">
         <is>
           <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
         </is>
       </c>
-      <c r="S415" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="T415" s="2" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="U415" s="2" t="inlineStr"/>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="S415" s="4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T415" s="7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="U415" s="7" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31804,7 +31804,7 @@
         <v>103.24</v>
       </c>
       <c r="G414" t="n">
-        <v>77344000</v>
+        <v>79757000</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>5.83</v>
@@ -31877,37 +31877,37 @@
         <v>93.40000000000001</v>
       </c>
       <c r="E415" s="4" t="n">
-        <v>82.26000000000001</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F415" s="4" t="n">
-        <v>83.92</v>
+        <v>82.11</v>
       </c>
       <c r="G415" s="4" t="n">
-        <v>136017849</v>
+        <v>177468148</v>
       </c>
       <c r="H415" s="5" t="n">
-        <v>-18.71</v>
+        <v>-20.47</v>
       </c>
       <c r="I415" s="4" t="n">
         <v>14.3</v>
       </c>
       <c r="J415" s="4" t="n">
-        <v>131.33</v>
+        <v>131.24</v>
       </c>
       <c r="K415" s="4" t="n">
-        <v>126.67</v>
+        <v>126.64</v>
       </c>
       <c r="L415" s="4" t="n">
-        <v>159.97</v>
+        <v>159.95</v>
       </c>
       <c r="M415" s="4" t="n">
-        <v>122.99</v>
+        <v>122.98</v>
       </c>
       <c r="N415" s="6" t="n">
-        <v>10.98</v>
+        <v>10.79</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
@@ -31928,13 +31928,15 @@
         <v>4.95</v>
       </c>
       <c r="T415" s="7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="U415" s="7" t="n">
-        <v>14.7</v>
+        <v>15.2</v>
       </c>
       <c r="V415" s="4" t="inlineStr"/>
-      <c r="W415" s="7" t="inlineStr"/>
+      <c r="W415" s="7" t="n">
+        <v>152.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31860,81 +31860,61 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="4" t="inlineStr">
-        <is>
-          <t>SOXL</t>
-        </is>
-      </c>
-      <c r="B415" s="4" t="inlineStr">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" s="4" t="n">
-        <v>90.59</v>
-      </c>
-      <c r="D415" s="4" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="E415" s="4" t="n">
-        <v>80.20999999999999</v>
-      </c>
-      <c r="F415" s="4" t="n">
-        <v>82.11</v>
-      </c>
-      <c r="G415" s="4" t="n">
-        <v>177468148</v>
-      </c>
-      <c r="H415" s="5" t="n">
-        <v>-20.47</v>
-      </c>
-      <c r="I415" s="4" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J415" s="4" t="n">
-        <v>131.24</v>
-      </c>
-      <c r="K415" s="4" t="n">
-        <v>126.64</v>
-      </c>
-      <c r="L415" s="4" t="n">
-        <v>159.95</v>
-      </c>
-      <c r="M415" s="4" t="n">
-        <v>122.98</v>
-      </c>
-      <c r="N415" s="6" t="n">
-        <v>10.79</v>
-      </c>
-      <c r="O415" s="4" t="n">
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="n">
+        <v>177999401</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I415" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" s="3" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="O415" t="n">
         <v>20</v>
       </c>
-      <c r="P415" s="4" t="inlineStr">
+      <c r="P415" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q415" s="4" t="inlineStr">
+      <c r="Q415" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" s="4" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
-      <c r="S415" s="4" t="n">
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
         <v>4.95</v>
       </c>
-      <c r="T415" s="7" t="n">
+      <c r="T415" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U415" s="7" t="n">
+      <c r="U415" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="V415" s="4" t="inlineStr"/>
-      <c r="W415" s="7" t="n">
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
         <v>152.4</v>
       </c>
     </row>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31860,61 +31860,81 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>SOXL</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="n">
-        <v>177999401</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I415" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="3" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="C415" s="4" t="n">
+        <v>90.59</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>80.22</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>82.11</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>178037300</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-20.47</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>131.24</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>126.64</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>159.95</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>122.98</v>
+      </c>
+      <c r="N415" s="6" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="O415" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="P415" t="inlineStr">
+      <c r="P415" s="4" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q415" t="inlineStr">
+      <c r="Q415" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
+      <c r="R415" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" s="4" t="n">
         <v>4.95</v>
       </c>
-      <c r="T415" s="2" t="n">
+      <c r="T415" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="U415" s="2" t="n">
+      <c r="U415" s="7" t="n">
         <v>15.2</v>
       </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="n">
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="7" t="n">
         <v>152.4</v>
       </c>
     </row>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31907,7 +31907,7 @@
         <v>10.79</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31907,7 +31907,7 @@
         <v>10.79</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
@@ -31937,6 +31937,83 @@
       <c r="W415" s="7" t="n">
         <v>152.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>81.64</v>
+      </c>
+      <c r="D416" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="E416" t="n">
+        <v>80.83</v>
+      </c>
+      <c r="F416" t="n">
+        <v>84.56</v>
+      </c>
+      <c r="G416" t="n">
+        <v>72365561</v>
+      </c>
+      <c r="H416" s="3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I416" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J416" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="K416" t="n">
+        <v>126.13</v>
+      </c>
+      <c r="L416" t="n">
+        <v>159.59</v>
+      </c>
+      <c r="M416" t="n">
+        <v>123.14</v>
+      </c>
+      <c r="N416" s="3" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="O416" t="n">
+        <v>20</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S416" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31883,7 +31883,7 @@
         <v>82.11</v>
       </c>
       <c r="G415" s="4" t="n">
-        <v>178037300</v>
+        <v>180752900</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-20.47</v>
@@ -31959,22 +31959,22 @@
         <v>80.83</v>
       </c>
       <c r="F416" t="n">
-        <v>84.56</v>
+        <v>83.56</v>
       </c>
       <c r="G416" t="n">
-        <v>72365561</v>
+        <v>91390844</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>2.98</v>
+        <v>1.77</v>
       </c>
       <c r="I416" t="n">
         <v>14.3</v>
       </c>
       <c r="J416" t="n">
-        <v>127.9</v>
+        <v>127.85</v>
       </c>
       <c r="K416" t="n">
-        <v>126.13</v>
+        <v>126.12</v>
       </c>
       <c r="L416" t="n">
         <v>159.59</v>
@@ -31983,10 +31983,10 @@
         <v>123.14</v>
       </c>
       <c r="N416" s="3" t="n">
-        <v>12.38</v>
+        <v>11.55</v>
       </c>
       <c r="O416" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -32004,16 +32004,18 @@
         </is>
       </c>
       <c r="S416" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="2" t="n">
+        <v>151.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31874,25 +31874,41 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>81.64</v>
+      </c>
+      <c r="D415" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="E415" t="n">
+        <v>80.83</v>
+      </c>
+      <c r="F415" t="n">
+        <v>83.56</v>
+      </c>
       <c r="G415" t="n">
-        <v>91390844</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>91648900</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>1.77</v>
       </c>
       <c r="I415" t="n">
         <v>14.3</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>127.85</v>
+      </c>
+      <c r="K415" t="n">
+        <v>126.12</v>
+      </c>
+      <c r="L415" t="n">
+        <v>159.59</v>
+      </c>
+      <c r="M415" t="n">
+        <v>123.14</v>
+      </c>
       <c r="N415" s="1" t="n">
-        <v>10.31</v>
+        <v>11.55</v>
       </c>
       <c r="O415" t="n">
         <v>21</v>
@@ -31907,7 +31923,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S415" t="n">
         <v>4.99</v>
       </c>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2637,7 +2637,7 @@
         <v>14.3</v>
       </c>
       <c r="J28" t="n">
-        <v>15.56</v>
+        <v>15.55</v>
       </c>
       <c r="K28" t="n">
         <v>22.42</v>
@@ -31761,7 +31761,7 @@
         <v>11.55</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31791,6 +31791,83 @@
       <c r="W413" s="3" t="n">
         <v>151.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>85.88</v>
+      </c>
+      <c r="D414" t="n">
+        <v>92.45999999999999</v>
+      </c>
+      <c r="E414" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="F414" t="n">
+        <v>91.03</v>
+      </c>
+      <c r="G414" t="n">
+        <v>67155031</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>125.28</v>
+      </c>
+      <c r="K414" t="n">
+        <v>125.72</v>
+      </c>
+      <c r="L414" t="n">
+        <v>159.14</v>
+      </c>
+      <c r="M414" t="n">
+        <v>123.34</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31807,25 +31807,25 @@
         <v>85.88</v>
       </c>
       <c r="D414" t="n">
-        <v>92.45999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="E414" t="n">
         <v>84.23</v>
       </c>
       <c r="F414" t="n">
-        <v>91.03</v>
+        <v>90.5</v>
       </c>
       <c r="G414" t="n">
-        <v>67155031</v>
+        <v>99055593</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>8.94</v>
+        <v>8.31</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>125.28</v>
+        <v>125.26</v>
       </c>
       <c r="K414" t="n">
         <v>125.72</v>
@@ -31837,7 +31837,7 @@
         <v>123.34</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>17.43</v>
+        <v>17.04</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31858,16 +31858,18 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31658,7 +31658,7 @@
         <v>83.56</v>
       </c>
       <c r="G412" t="n">
-        <v>91648900</v>
+        <v>92699400</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>1.77</v>
@@ -31724,28 +31724,44 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>85.88</v>
+      </c>
+      <c r="D413" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="E413" t="n">
+        <v>84.22</v>
+      </c>
+      <c r="F413" t="n">
+        <v>90.5</v>
+      </c>
       <c r="G413" t="n">
-        <v>99055593</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>99727100</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>8.31</v>
       </c>
       <c r="I413" t="n">
         <v>14.3</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>125.26</v>
+      </c>
+      <c r="K413" t="n">
+        <v>125.72</v>
+      </c>
+      <c r="L413" t="n">
+        <v>159.14</v>
+      </c>
+      <c r="M413" t="n">
+        <v>123.34</v>
+      </c>
       <c r="N413" s="1" t="n">
-        <v>11.55</v>
+        <v>17.04</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31757,7 +31773,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S413" t="n">
         <v>4.99</v>
       </c>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31761,7 +31761,7 @@
         <v>17.04</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31791,6 +31791,83 @@
       <c r="W413" s="2" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="D414" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="E414" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F414" t="n">
+        <v>95.52</v>
+      </c>
+      <c r="G414" t="n">
+        <v>34519009</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>122.68</v>
+      </c>
+      <c r="K414" t="n">
+        <v>125.36</v>
+      </c>
+      <c r="L414" t="n">
+        <v>158.55</v>
+      </c>
+      <c r="M414" t="n">
+        <v>123.55</v>
+      </c>
+      <c r="N414" s="1" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="O414" t="n">
+        <v>32</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31737,7 +31737,7 @@
         <v>90.5</v>
       </c>
       <c r="G413" t="n">
-        <v>99727100</v>
+        <v>101281500</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>8.31</v>
@@ -31807,40 +31807,40 @@
         <v>95.04000000000001</v>
       </c>
       <c r="D414" t="n">
-        <v>97.98</v>
+        <v>102.2</v>
       </c>
       <c r="E414" t="n">
         <v>94.09999999999999</v>
       </c>
       <c r="F414" t="n">
-        <v>95.52</v>
+        <v>100.65</v>
       </c>
       <c r="G414" t="n">
-        <v>34519009</v>
+        <v>87409487</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>5.55</v>
+        <v>11.22</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>122.68</v>
+        <v>122.94</v>
       </c>
       <c r="K414" t="n">
-        <v>125.36</v>
+        <v>125.45</v>
       </c>
       <c r="L414" t="n">
-        <v>158.55</v>
+        <v>158.6</v>
       </c>
       <c r="M414" t="n">
-        <v>123.55</v>
+        <v>123.57</v>
       </c>
       <c r="N414" s="1" t="n">
-        <v>21.59</v>
+        <v>25.03</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31858,13 +31858,13 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -2558,7 +2558,7 @@
         <v>14.3</v>
       </c>
       <c r="J27" t="n">
-        <v>15.55</v>
+        <v>15.56</v>
       </c>
       <c r="K27" t="n">
         <v>22.42</v>
@@ -29467,7 +29467,7 @@
         <v>44.35</v>
       </c>
       <c r="O383" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>42.19</v>
       </c>
       <c r="O384" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45.45</v>
       </c>
       <c r="O386" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>57.03</v>
       </c>
       <c r="O387" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>67.69</v>
       </c>
       <c r="O390" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P390" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="O391" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>58.65</v>
       </c>
       <c r="O393" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P393" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>59.43</v>
       </c>
       <c r="O394" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P394" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>83.91</v>
       </c>
       <c r="O397" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P397" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>83.8</v>
       </c>
       <c r="O398" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P398" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>76.09999999999999</v>
       </c>
       <c r="O400" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P400" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>60.27</v>
       </c>
       <c r="O401" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P401" t="inlineStr">
         <is>
@@ -30900,11 +30900,11 @@
         <v>48.64</v>
       </c>
       <c r="O402" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
@@ -30979,7 +30979,7 @@
         <v>34.89</v>
       </c>
       <c r="O403" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P403" t="inlineStr">
         <is>
@@ -31058,11 +31058,11 @@
         <v>37.21</v>
       </c>
       <c r="O404" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
@@ -31133,7 +31133,7 @@
         <v>30.11</v>
       </c>
       <c r="O405" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P405" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>24.96</v>
       </c>
       <c r="O406" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P406" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>23.74</v>
       </c>
       <c r="O407" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P407" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>23.96</v>
       </c>
       <c r="O408" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P408" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>22.98</v>
       </c>
       <c r="O409" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P409" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>22.86</v>
       </c>
       <c r="O410" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P410" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>10.79</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>11.55</v>
       </c>
       <c r="O412" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>17.04</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31813,34 +31813,34 @@
         <v>94.09999999999999</v>
       </c>
       <c r="F414" t="n">
-        <v>100.65</v>
+        <v>101.08</v>
       </c>
       <c r="G414" t="n">
-        <v>87409487</v>
+        <v>92548877</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>11.22</v>
+        <v>11.69</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>122.94</v>
+        <v>122.96</v>
       </c>
       <c r="K414" t="n">
-        <v>125.45</v>
+        <v>125.46</v>
       </c>
       <c r="L414" t="n">
         <v>158.6</v>
       </c>
       <c r="M414" t="n">
-        <v>123.57</v>
+        <v>123.58</v>
       </c>
       <c r="N414" s="1" t="n">
-        <v>25.03</v>
+        <v>25.31</v>
       </c>
       <c r="O414" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31867,7 +31867,9 @@
         <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31765,7 +31765,7 @@
         <v>25.31</v>
       </c>
       <c r="O413" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31795,6 +31795,79 @@
       <c r="W413" s="3" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>103.97</v>
+      </c>
+      <c r="D414" t="n">
+        <v>105.84</v>
+      </c>
+      <c r="E414" t="n">
+        <v>101.32</v>
+      </c>
+      <c r="F414" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="G414" t="n">
+        <v>49585287</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="I414" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="K414" t="n">
+        <v>124.87</v>
+      </c>
+      <c r="L414" t="n">
+        <v>158.21</v>
+      </c>
+      <c r="M414" t="n">
+        <v>123.83</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31741,7 +31741,7 @@
         <v>101.08</v>
       </c>
       <c r="G413" t="n">
-        <v>93476100</v>
+        <v>95217400</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>11.69</v>
@@ -31811,40 +31811,40 @@
         <v>103.97</v>
       </c>
       <c r="D414" t="n">
-        <v>105.84</v>
+        <v>108.6</v>
       </c>
       <c r="E414" t="n">
         <v>101.32</v>
       </c>
       <c r="F414" t="n">
-        <v>104.7</v>
+        <v>107.35</v>
       </c>
       <c r="G414" t="n">
-        <v>49585287</v>
+        <v>87485240</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>3.58</v>
+        <v>6.2</v>
       </c>
       <c r="I414" t="n">
         <v>14.3</v>
       </c>
       <c r="J414" t="n">
-        <v>120.8</v>
+        <v>120.93</v>
       </c>
       <c r="K414" t="n">
-        <v>124.87</v>
+        <v>124.92</v>
       </c>
       <c r="L414" t="n">
-        <v>158.21</v>
+        <v>158.23</v>
       </c>
       <c r="M414" t="n">
-        <v>123.83</v>
+        <v>123.84</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>31.88</v>
+        <v>33.56</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31858,16 +31858,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>148.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31820,7 +31820,7 @@
         <v>107.35</v>
       </c>
       <c r="G414" t="n">
-        <v>87485240</v>
+        <v>86904900</v>
       </c>
       <c r="H414" s="2" t="n">
         <v>6.2</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31844,7 +31844,7 @@
         <v>33.56</v>
       </c>
       <c r="O414" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31870,6 +31870,79 @@
       <c r="W414" s="3" t="n">
         <v>148.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>101.36</v>
+      </c>
+      <c r="D415" t="n">
+        <v>105.44</v>
+      </c>
+      <c r="E415" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="F415" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="G415" t="n">
+        <v>51520306</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="I415" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>118.39</v>
+      </c>
+      <c r="K415" t="n">
+        <v>124.43</v>
+      </c>
+      <c r="L415" t="n">
+        <v>157.61</v>
+      </c>
+      <c r="M415" t="n">
+        <v>124.07</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O415" t="n">
+        <v>35</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="U415" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31820,7 +31820,7 @@
         <v>107.35</v>
       </c>
       <c r="G414" t="n">
-        <v>86904900</v>
+        <v>89591100</v>
       </c>
       <c r="H414" s="2" t="n">
         <v>6.2</v>
@@ -31892,22 +31892,22 @@
         <v>97.98999999999999</v>
       </c>
       <c r="F415" t="n">
-        <v>102.75</v>
+        <v>102.39</v>
       </c>
       <c r="G415" t="n">
-        <v>51520306</v>
+        <v>89163620</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-4.29</v>
+        <v>-4.62</v>
       </c>
       <c r="I415" t="n">
         <v>14.3</v>
       </c>
       <c r="J415" t="n">
-        <v>118.39</v>
+        <v>118.37</v>
       </c>
       <c r="K415" t="n">
-        <v>124.43</v>
+        <v>124.42</v>
       </c>
       <c r="L415" t="n">
         <v>157.61</v>
@@ -31916,7 +31916,7 @@
         <v>124.07</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>33</v>
+        <v>32.89</v>
       </c>
       <c r="O415" t="n">
         <v>35</v>
@@ -31933,16 +31933,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T415" s="3" t="n">
-        <v>16.3</v>
+        <v>17.2</v>
       </c>
       <c r="U415" s="3" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="3" t="inlineStr"/>
+      <c r="W415" s="3" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31889,13 +31889,13 @@
         <v>105.44</v>
       </c>
       <c r="E415" t="n">
-        <v>97.98999999999999</v>
+        <v>97.95</v>
       </c>
       <c r="F415" t="n">
         <v>102.39</v>
       </c>
       <c r="G415" t="n">
-        <v>89163620</v>
+        <v>94028800</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-4.62</v>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -31919,7 +31919,7 @@
         <v>32.89</v>
       </c>
       <c r="O415" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>-13.84</v>
       </c>
       <c r="I2" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J2" t="n">
         <v>25.07</v>
@@ -691,7 +691,7 @@
         <v>-3.19</v>
       </c>
       <c r="I3" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J3" t="n">
         <v>24.58</v>
@@ -774,7 +774,7 @@
         <v>5.09</v>
       </c>
       <c r="I4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J4" t="n">
         <v>24.13</v>
@@ -853,7 +853,7 @@
         <v>-1.16</v>
       </c>
       <c r="I5" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J5" t="n">
         <v>23.66</v>
@@ -932,7 +932,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J6" t="n">
         <v>23.23</v>
@@ -1007,7 +1007,7 @@
         <v>4.98</v>
       </c>
       <c r="I7" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J7" t="n">
         <v>22.84</v>
@@ -1082,7 +1082,7 @@
         <v>-4.12</v>
       </c>
       <c r="I8" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J8" t="n">
         <v>22.34</v>
@@ -1157,7 +1157,7 @@
         <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J9" t="n">
         <v>21.79</v>
@@ -1232,7 +1232,7 @@
         <v>-2.17</v>
       </c>
       <c r="I10" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J10" t="n">
         <v>21.21</v>
@@ -1307,7 +1307,7 @@
         <v>-3.28</v>
       </c>
       <c r="I11" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J11" t="n">
         <v>20.74</v>
@@ -1382,7 +1382,7 @@
         <v>8.93</v>
       </c>
       <c r="I12" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
         <v>20.45</v>
@@ -1457,7 +1457,7 @@
         <v>-1.82</v>
       </c>
       <c r="I13" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J13" t="n">
         <v>20.23</v>
@@ -1532,7 +1532,7 @@
         <v>-8.6</v>
       </c>
       <c r="I14" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J14" t="n">
         <v>19.86</v>
@@ -1611,7 +1611,7 @@
         <v>-5.45</v>
       </c>
       <c r="I15" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J15" t="n">
         <v>19.66</v>
@@ -1686,7 +1686,7 @@
         <v>-9.779999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J16" t="n">
         <v>19.33</v>
@@ -1761,7 +1761,7 @@
         <v>-0.5</v>
       </c>
       <c r="I17" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J17" t="n">
         <v>19.11</v>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J18" t="n">
         <v>18.88</v>
@@ -1911,7 +1911,7 @@
         <v>1.95</v>
       </c>
       <c r="I19" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J19" t="n">
         <v>18.6</v>
@@ -1986,7 +1986,7 @@
         <v>-29.83</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>18.21</v>
@@ -2069,7 +2069,7 @@
         <v>-23.5</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>17.61</v>
@@ -2152,7 +2152,7 @@
         <v>4.83</v>
       </c>
       <c r="I22" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J22" t="n">
         <v>17.17</v>
@@ -2235,7 +2235,7 @@
         <v>-9.77</v>
       </c>
       <c r="I23" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J23" t="n">
         <v>16.72</v>
@@ -2318,7 +2318,7 @@
         <v>54.74</v>
       </c>
       <c r="I24" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J24" t="n">
         <v>16.45</v>
@@ -2397,7 +2397,7 @@
         <v>-24.61</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>16.03</v>
@@ -2480,7 +2480,7 @@
         <v>6.26</v>
       </c>
       <c r="I26" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J26" t="n">
         <v>15.56</v>
@@ -2563,7 +2563,7 @@
         <v>2.36</v>
       </c>
       <c r="I27" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J27" t="n">
         <v>15.04</v>
@@ -2642,7 +2642,7 @@
         <v>1.25</v>
       </c>
       <c r="I28" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J28" t="n">
         <v>14.58</v>
@@ -2717,7 +2717,7 @@
         <v>-11.93</v>
       </c>
       <c r="I29" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J29" t="n">
         <v>14.04</v>
@@ -2800,7 +2800,7 @@
         <v>-1.51</v>
       </c>
       <c r="I30" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J30" t="n">
         <v>13.5</v>
@@ -2879,7 +2879,7 @@
         <v>-5.35</v>
       </c>
       <c r="I31" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J31" t="n">
         <v>12.98</v>
@@ -2954,7 +2954,7 @@
         <v>5.42</v>
       </c>
       <c r="I32" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J32" t="n">
         <v>12.4</v>
@@ -3029,7 +3029,7 @@
         <v>12.14</v>
       </c>
       <c r="I33" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J33" t="n">
         <v>11.89</v>
@@ -3108,7 +3108,7 @@
         <v>16.59</v>
       </c>
       <c r="I34" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J34" t="n">
         <v>11.55</v>
@@ -3183,7 +3183,7 @@
         <v>2.85</v>
       </c>
       <c r="I35" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J35" t="n">
         <v>11.28</v>
@@ -3258,7 +3258,7 @@
         <v>-0.41</v>
       </c>
       <c r="I36" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J36" t="n">
         <v>11.09</v>
@@ -3333,7 +3333,7 @@
         <v>-3.51</v>
       </c>
       <c r="I37" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J37" t="n">
         <v>10.89</v>
@@ -3408,7 +3408,7 @@
         <v>2.54</v>
       </c>
       <c r="I38" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J38" t="n">
         <v>10.7</v>
@@ -3483,7 +3483,7 @@
         <v>-0.5</v>
       </c>
       <c r="I39" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J39" t="n">
         <v>10.49</v>
@@ -3558,7 +3558,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J40" t="n">
         <v>10.59</v>
@@ -3633,7 +3633,7 @@
         <v>-1.81</v>
       </c>
       <c r="I41" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J41" t="n">
         <v>10.8</v>
@@ -3708,7 +3708,7 @@
         <v>-3.15</v>
       </c>
       <c r="I42" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J42" t="n">
         <v>10.98</v>
@@ -3783,7 +3783,7 @@
         <v>5.08</v>
       </c>
       <c r="I43" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J43" t="n">
         <v>11.23</v>
@@ -3858,7 +3858,7 @@
         <v>2.8</v>
       </c>
       <c r="I44" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J44" t="n">
         <v>11.27</v>
@@ -3933,7 +3933,7 @@
         <v>3.31</v>
       </c>
       <c r="I45" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J45" t="n">
         <v>11.49</v>
@@ -4008,7 +4008,7 @@
         <v>21.42</v>
       </c>
       <c r="I46" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J46" t="n">
         <v>11.84</v>
@@ -4083,7 +4083,7 @@
         <v>8.56</v>
       </c>
       <c r="I47" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J47" t="n">
         <v>12.24</v>
@@ -4158,7 +4158,7 @@
         <v>1.3</v>
       </c>
       <c r="I48" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J48" t="n">
         <v>12.65</v>
@@ -4233,7 +4233,7 @@
         <v>-1.97</v>
       </c>
       <c r="I49" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J49" t="n">
         <v>13.11</v>
@@ -4308,7 +4308,7 @@
         <v>-0.44</v>
       </c>
       <c r="I50" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J50" t="n">
         <v>13.56</v>
@@ -4383,7 +4383,7 @@
         <v>-1.75</v>
       </c>
       <c r="I51" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J51" t="n">
         <v>14.03</v>
@@ -4458,7 +4458,7 @@
         <v>-0.5</v>
       </c>
       <c r="I52" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J52" t="n">
         <v>14.47</v>
@@ -4533,7 +4533,7 @@
         <v>-5.42</v>
       </c>
       <c r="I53" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J53" t="n">
         <v>14.8</v>
@@ -4608,7 +4608,7 @@
         <v>-2.89</v>
       </c>
       <c r="I54" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J54" t="n">
         <v>15.03</v>
@@ -4683,7 +4683,7 @@
         <v>-4.68</v>
       </c>
       <c r="I55" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J55" t="n">
         <v>15.19</v>
@@ -4758,7 +4758,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J56" t="n">
         <v>15.44</v>
@@ -4833,7 +4833,7 @@
         <v>-1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J57" t="n">
         <v>15.7</v>
@@ -4908,7 +4908,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J58" t="n">
         <v>15.95</v>
@@ -4983,7 +4983,7 @@
         <v>-6.01</v>
       </c>
       <c r="I59" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J59" t="n">
         <v>16.16</v>
@@ -5062,7 +5062,7 @@
         <v>4.53</v>
       </c>
       <c r="I60" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J60" t="n">
         <v>16.33</v>
@@ -5137,7 +5137,7 @@
         <v>8.32</v>
       </c>
       <c r="I61" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J61" t="n">
         <v>16.6</v>
@@ -5212,7 +5212,7 @@
         <v>4.28</v>
       </c>
       <c r="I62" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J62" t="n">
         <v>16.92</v>
@@ -5287,7 +5287,7 @@
         <v>-1.47</v>
       </c>
       <c r="I63" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J63" t="n">
         <v>17.19</v>
@@ -5362,7 +5362,7 @@
         <v>1.98</v>
       </c>
       <c r="I64" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J64" t="n">
         <v>17.47</v>
@@ -5437,7 +5437,7 @@
         <v>7.33</v>
       </c>
       <c r="I65" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J65" t="n">
         <v>17.79</v>
@@ -5512,7 +5512,7 @@
         <v>6.34</v>
       </c>
       <c r="I66" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J66" t="n">
         <v>18.03</v>
@@ -5587,7 +5587,7 @@
         <v>-1.15</v>
       </c>
       <c r="I67" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J67" t="n">
         <v>18.18</v>
@@ -5662,7 +5662,7 @@
         <v>0.23</v>
       </c>
       <c r="I68" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J68" t="n">
         <v>18.32</v>
@@ -5737,7 +5737,7 @@
         <v>-7.59</v>
       </c>
       <c r="I69" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J69" t="n">
         <v>18.4</v>
@@ -5816,7 +5816,7 @@
         <v>9.27</v>
       </c>
       <c r="I70" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J70" t="n">
         <v>18.57</v>
@@ -5891,7 +5891,7 @@
         <v>-2.2</v>
       </c>
       <c r="I71" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J71" t="n">
         <v>18.74</v>
@@ -5966,7 +5966,7 @@
         <v>0.89</v>
       </c>
       <c r="I72" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J72" t="n">
         <v>18.92</v>
@@ -6041,7 +6041,7 @@
         <v>-1.86</v>
       </c>
       <c r="I73" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J73" t="n">
         <v>19.13</v>
@@ -6116,7 +6116,7 @@
         <v>1.75</v>
       </c>
       <c r="I74" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J74" t="n">
         <v>19.38</v>
@@ -6191,7 +6191,7 @@
         <v>11.35</v>
       </c>
       <c r="I75" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J75" t="n">
         <v>19.8</v>
@@ -6266,7 +6266,7 @@
         <v>2.63</v>
       </c>
       <c r="I76" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J76" t="n">
         <v>20.16</v>
@@ -6341,7 +6341,7 @@
         <v>2.52</v>
       </c>
       <c r="I77" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J77" t="n">
         <v>20.57</v>
@@ -6416,7 +6416,7 @@
         <v>-0.36</v>
       </c>
       <c r="I78" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J78" t="n">
         <v>20.97</v>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J79" t="n">
         <v>21.42</v>
@@ -6566,7 +6566,7 @@
         <v>-1.59</v>
       </c>
       <c r="I80" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J80" t="n">
         <v>21.81</v>
@@ -6641,7 +6641,7 @@
         <v>5.43</v>
       </c>
       <c r="I81" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J81" t="n">
         <v>22.2</v>
@@ -6716,7 +6716,7 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J82" t="n">
         <v>22.57</v>
@@ -6791,7 +6791,7 @@
         <v>-5.53</v>
       </c>
       <c r="I83" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J83" t="n">
         <v>22.89</v>
@@ -6866,7 +6866,7 @@
         <v>5.61</v>
       </c>
       <c r="I84" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J84" t="n">
         <v>23.25</v>
@@ -6941,7 +6941,7 @@
         <v>1.02</v>
       </c>
       <c r="I85" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J85" t="n">
         <v>23.55</v>
@@ -7016,7 +7016,7 @@
         <v>2.7</v>
       </c>
       <c r="I86" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J86" t="n">
         <v>23.83</v>
@@ -7091,7 +7091,7 @@
         <v>-0.29</v>
       </c>
       <c r="I87" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J87" t="n">
         <v>24.12</v>
@@ -7166,7 +7166,7 @@
         <v>-2.9</v>
       </c>
       <c r="I88" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J88" t="n">
         <v>24.36</v>
@@ -7241,7 +7241,7 @@
         <v>2.98</v>
       </c>
       <c r="I89" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J89" t="n">
         <v>24.72</v>
@@ -7316,7 +7316,7 @@
         <v>-0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J90" t="n">
         <v>24.98</v>
@@ -7391,7 +7391,7 @@
         <v>1.07</v>
       </c>
       <c r="I91" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J91" t="n">
         <v>25.28</v>
@@ -7466,7 +7466,7 @@
         <v>0.04</v>
       </c>
       <c r="I92" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J92" t="n">
         <v>25.57</v>
@@ -7541,7 +7541,7 @@
         <v>0.62</v>
       </c>
       <c r="I93" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J93" t="n">
         <v>25.89</v>
@@ -7616,7 +7616,7 @@
         <v>-4.26</v>
       </c>
       <c r="I94" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J94" t="n">
         <v>26.13</v>
@@ -7691,7 +7691,7 @@
         <v>-2.05</v>
       </c>
       <c r="I95" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J95" t="n">
         <v>26.22</v>
@@ -7770,7 +7770,7 @@
         <v>-0.62</v>
       </c>
       <c r="I96" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J96" t="n">
         <v>26.27</v>
@@ -7845,7 +7845,7 @@
         <v>-0.08</v>
       </c>
       <c r="I97" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J97" t="n">
         <v>26.29</v>
@@ -7920,7 +7920,7 @@
         <v>4.96</v>
       </c>
       <c r="I98" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J98" t="n">
         <v>26.38</v>
@@ -7995,7 +7995,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I99" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J99" t="n">
         <v>26.48</v>
@@ -8070,7 +8070,7 @@
         <v>2.15</v>
       </c>
       <c r="I100" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J100" t="n">
         <v>26.62</v>
@@ -8145,7 +8145,7 @@
         <v>-9.5</v>
       </c>
       <c r="I101" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J101" t="n">
         <v>26.57</v>
@@ -8224,7 +8224,7 @@
         <v>-3.61</v>
       </c>
       <c r="I102" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J102" t="n">
         <v>26.45</v>
@@ -8299,7 +8299,7 @@
         <v>3.82</v>
       </c>
       <c r="I103" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J103" t="n">
         <v>26.45</v>
@@ -8374,7 +8374,7 @@
         <v>-1.92</v>
       </c>
       <c r="I104" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J104" t="n">
         <v>26.36</v>
@@ -8449,7 +8449,7 @@
         <v>-2.16</v>
       </c>
       <c r="I105" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J105" t="n">
         <v>26.23</v>
@@ -8524,7 +8524,7 @@
         <v>4.21</v>
       </c>
       <c r="I106" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J106" t="n">
         <v>26.11</v>
@@ -8599,7 +8599,7 @@
         <v>2.84</v>
       </c>
       <c r="I107" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J107" t="n">
         <v>26.03</v>
@@ -8674,7 +8674,7 @@
         <v>-0.39</v>
       </c>
       <c r="I108" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J108" t="n">
         <v>25.99</v>
@@ -8749,7 +8749,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J109" t="n">
         <v>26.02</v>
@@ -8824,7 +8824,7 @@
         <v>4.54</v>
       </c>
       <c r="I110" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J110" t="n">
         <v>26.13</v>
@@ -8899,7 +8899,7 @@
         <v>0.51</v>
       </c>
       <c r="I111" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J111" t="n">
         <v>26.24</v>
@@ -8974,7 +8974,7 @@
         <v>-6.98</v>
       </c>
       <c r="I112" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J112" t="n">
         <v>26.24</v>
@@ -9049,7 +9049,7 @@
         <v>0.59</v>
       </c>
       <c r="I113" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J113" t="n">
         <v>26.24</v>
@@ -9124,7 +9124,7 @@
         <v>-4.65</v>
       </c>
       <c r="I114" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J114" t="n">
         <v>26.24</v>
@@ -9203,7 +9203,7 @@
         <v>-1.68</v>
       </c>
       <c r="I115" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J115" t="n">
         <v>26.24</v>
@@ -9278,7 +9278,7 @@
         <v>-1.75</v>
       </c>
       <c r="I116" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J116" t="n">
         <v>26.23</v>
@@ -9353,7 +9353,7 @@
         <v>8.25</v>
       </c>
       <c r="I117" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J117" t="n">
         <v>26.32</v>
@@ -9428,7 +9428,7 @@
         <v>-0.55</v>
       </c>
       <c r="I118" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J118" t="n">
         <v>26.34</v>
@@ -9503,7 +9503,7 @@
         <v>2.35</v>
       </c>
       <c r="I119" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J119" t="n">
         <v>26.38</v>
@@ -9578,7 +9578,7 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J120" t="n">
         <v>26.41</v>
@@ -9653,7 +9653,7 @@
         <v>1.24</v>
       </c>
       <c r="I121" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J121" t="n">
         <v>26.59</v>
@@ -9728,7 +9728,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="I122" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J122" t="n">
         <v>26.69</v>
@@ -9807,7 +9807,7 @@
         <v>-3.04</v>
       </c>
       <c r="I123" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J123" t="n">
         <v>26.7</v>
@@ -9886,7 +9886,7 @@
         <v>-1.35</v>
       </c>
       <c r="I124" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J124" t="n">
         <v>26.72</v>
@@ -9961,7 +9961,7 @@
         <v>2.97</v>
       </c>
       <c r="I125" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J125" t="n">
         <v>26.8</v>
@@ -10036,7 +10036,7 @@
         <v>3.08</v>
       </c>
       <c r="I126" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J126" t="n">
         <v>26.87</v>
@@ -10111,7 +10111,7 @@
         <v>2.38</v>
       </c>
       <c r="I127" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J127" t="n">
         <v>26.94</v>
@@ -10186,7 +10186,7 @@
         <v>0.37</v>
       </c>
       <c r="I128" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J128" t="n">
         <v>27.02</v>
@@ -10261,7 +10261,7 @@
         <v>5.23</v>
       </c>
       <c r="I129" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J129" t="n">
         <v>27.05</v>
@@ -10336,7 +10336,7 @@
         <v>2</v>
       </c>
       <c r="I130" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J130" t="n">
         <v>27.05</v>
@@ -10411,7 +10411,7 @@
         <v>0.45</v>
       </c>
       <c r="I131" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J131" t="n">
         <v>27.04</v>
@@ -10486,7 +10486,7 @@
         <v>2.39</v>
       </c>
       <c r="I132" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J132" t="n">
         <v>27.17</v>
@@ -10561,7 +10561,7 @@
         <v>1.6</v>
       </c>
       <c r="I133" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J133" t="n">
         <v>27.32</v>
@@ -10636,7 +10636,7 @@
         <v>-0.03</v>
       </c>
       <c r="I134" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J134" t="n">
         <v>27.53</v>
@@ -10711,7 +10711,7 @@
         <v>10.41</v>
       </c>
       <c r="I135" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J135" t="n">
         <v>27.92</v>
@@ -10786,7 +10786,7 @@
         <v>-1.84</v>
       </c>
       <c r="I136" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J136" t="n">
         <v>28.3</v>
@@ -10861,7 +10861,7 @@
         <v>4.27</v>
       </c>
       <c r="I137" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J137" t="n">
         <v>28.65</v>
@@ -10936,7 +10936,7 @@
         <v>-0.35</v>
       </c>
       <c r="I138" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J138" t="n">
         <v>29</v>
@@ -11011,7 +11011,7 @@
         <v>-0.29</v>
       </c>
       <c r="I139" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J139" t="n">
         <v>29.32</v>
@@ -11086,7 +11086,7 @@
         <v>-1.02</v>
       </c>
       <c r="I140" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J140" t="n">
         <v>29.6</v>
@@ -11161,7 +11161,7 @@
         <v>0.5</v>
       </c>
       <c r="I141" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J141" t="n">
         <v>29.88</v>
@@ -11236,7 +11236,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J142" t="n">
         <v>30.28</v>
@@ -11311,7 +11311,7 @@
         <v>2.41</v>
       </c>
       <c r="I143" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J143" t="n">
         <v>30.75</v>
@@ -11386,7 +11386,7 @@
         <v>5.8</v>
       </c>
       <c r="I144" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J144" t="n">
         <v>31.35</v>
@@ -11461,7 +11461,7 @@
         <v>6</v>
       </c>
       <c r="I145" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J145" t="n">
         <v>32.02</v>
@@ -11536,7 +11536,7 @@
         <v>-2.18</v>
       </c>
       <c r="I146" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J146" t="n">
         <v>32.61</v>
@@ -11611,7 +11611,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="I147" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J147" t="n">
         <v>33.34</v>
@@ -11686,7 +11686,7 @@
         <v>-6.91</v>
       </c>
       <c r="I148" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J148" t="n">
         <v>33.93</v>
@@ -11761,7 +11761,7 @@
         <v>10.18</v>
       </c>
       <c r="I149" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J149" t="n">
         <v>34.64</v>
@@ -11836,7 +11836,7 @@
         <v>-1.26</v>
       </c>
       <c r="I150" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J150" t="n">
         <v>35.29</v>
@@ -11911,7 +11911,7 @@
         <v>-19</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>35.53</v>
@@ -11990,7 +11990,7 @@
         <v>14.39</v>
       </c>
       <c r="I152" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J152" t="n">
         <v>35.99</v>
@@ -12065,7 +12065,7 @@
         <v>-6.39</v>
       </c>
       <c r="I153" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J153" t="n">
         <v>36.3</v>
@@ -12140,7 +12140,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="I154" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J154" t="n">
         <v>36.78</v>
@@ -12215,7 +12215,7 @@
         <v>1.48</v>
       </c>
       <c r="I155" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J155" t="n">
         <v>37.12</v>
@@ -12290,7 +12290,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J156" t="n">
         <v>37.48</v>
@@ -12365,7 +12365,7 @@
         <v>4.84</v>
       </c>
       <c r="I157" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J157" t="n">
         <v>37.88</v>
@@ -12440,7 +12440,7 @@
         <v>-1.73</v>
       </c>
       <c r="I158" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J158" t="n">
         <v>38.24</v>
@@ -12515,7 +12515,7 @@
         <v>-7.52</v>
       </c>
       <c r="I159" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J159" t="n">
         <v>38.44</v>
@@ -12594,7 +12594,7 @@
         <v>7.25</v>
       </c>
       <c r="I160" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J160" t="n">
         <v>38.81</v>
@@ -12669,7 +12669,7 @@
         <v>4.79</v>
       </c>
       <c r="I161" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J161" t="n">
         <v>39.27</v>
@@ -12744,7 +12744,7 @@
         <v>8.58</v>
       </c>
       <c r="I162" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J162" t="n">
         <v>39.91</v>
@@ -12819,7 +12819,7 @@
         <v>0.26</v>
       </c>
       <c r="I163" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J163" t="n">
         <v>40.51</v>
@@ -12894,7 +12894,7 @@
         <v>5.16</v>
       </c>
       <c r="I164" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J164" t="n">
         <v>41.14</v>
@@ -12969,7 +12969,7 @@
         <v>-4.03</v>
       </c>
       <c r="I165" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J165" t="n">
         <v>41.55</v>
@@ -13044,7 +13044,7 @@
         <v>0.82</v>
       </c>
       <c r="I166" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J166" t="n">
         <v>42.03</v>
@@ -13119,7 +13119,7 @@
         <v>1.68</v>
       </c>
       <c r="I167" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J167" t="n">
         <v>42.37</v>
@@ -13194,7 +13194,7 @@
         <v>-11.91</v>
       </c>
       <c r="I168" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J168" t="n">
         <v>42.57</v>
@@ -13269,7 +13269,7 @@
         <v>9.42</v>
       </c>
       <c r="I169" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J169" t="n">
         <v>42.77</v>
@@ -13344,7 +13344,7 @@
         <v>-8.16</v>
       </c>
       <c r="I170" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J170" t="n">
         <v>42.81</v>
@@ -13419,7 +13419,7 @@
         <v>-2.95</v>
       </c>
       <c r="I171" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J171" t="n">
         <v>43.19</v>
@@ -13498,7 +13498,7 @@
         <v>7.72</v>
       </c>
       <c r="I172" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J172" t="n">
         <v>43.48</v>
@@ -13573,7 +13573,7 @@
         <v>-7.01</v>
       </c>
       <c r="I173" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J173" t="n">
         <v>43.74</v>
@@ -13652,7 +13652,7 @@
         <v>4.55</v>
       </c>
       <c r="I174" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J174" t="n">
         <v>43.92</v>
@@ -13727,7 +13727,7 @@
         <v>-10.28</v>
       </c>
       <c r="I175" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J175" t="n">
         <v>43.86</v>
@@ -13802,7 +13802,7 @@
         <v>-0.92</v>
       </c>
       <c r="I176" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J176" t="n">
         <v>43.79</v>
@@ -13877,7 +13877,7 @@
         <v>-5.18</v>
       </c>
       <c r="I177" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J177" t="n">
         <v>43.52</v>
@@ -13952,7 +13952,7 @@
         <v>-6.76</v>
       </c>
       <c r="I178" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J178" t="n">
         <v>43.16</v>
@@ -14031,7 +14031,7 @@
         <v>4.69</v>
       </c>
       <c r="I179" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J179" t="n">
         <v>43.04</v>
@@ -14077,85 +14077,85 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>SOXL</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
         <is>
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="C180" s="4" t="n">
+      <c r="C180" t="n">
         <v>38.76</v>
       </c>
-      <c r="D180" s="4" t="n">
+      <c r="D180" t="n">
         <v>39.16</v>
       </c>
-      <c r="E180" s="4" t="n">
+      <c r="E180" t="n">
         <v>30.39</v>
       </c>
-      <c r="F180" s="4" t="n">
+      <c r="F180" t="n">
         <v>30.79</v>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" t="n">
         <v>228883600</v>
       </c>
-      <c r="H180" s="5" t="n">
+      <c r="H180" s="1" t="n">
         <v>-14.33</v>
       </c>
-      <c r="I180" s="4" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J180" s="4" t="n">
+      <c r="I180" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J180" t="n">
         <v>42.52</v>
       </c>
-      <c r="K180" s="4" t="n">
+      <c r="K180" t="n">
         <v>36.98</v>
       </c>
-      <c r="L180" s="4" t="n">
+      <c r="L180" t="n">
         <v>30.96</v>
       </c>
-      <c r="M180" s="4" t="n">
+      <c r="M180" t="n">
         <v>25.67</v>
       </c>
-      <c r="N180" s="6" t="n">
+      <c r="N180" s="2" t="n">
         <v>28.84</v>
       </c>
-      <c r="O180" s="4" t="n">
+      <c r="O180" t="n">
         <v>5</v>
       </c>
-      <c r="P180" s="4" t="inlineStr">
+      <c r="P180" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q180" s="4" t="inlineStr">
+      <c r="Q180" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R180" s="4" t="inlineStr">
+      <c r="R180" t="inlineStr">
         <is>
           <t>3rd: MA120, 50% cash, 5d</t>
         </is>
       </c>
-      <c r="S180" s="4" t="n">
+      <c r="S180" t="n">
         <v>4.11</v>
       </c>
-      <c r="T180" s="6" t="n">
+      <c r="T180" s="2" t="n">
         <v>26.4</v>
       </c>
-      <c r="U180" s="6" t="n">
+      <c r="U180" s="2" t="n">
         <v>29.2</v>
       </c>
-      <c r="V180" s="6" t="inlineStr">
+      <c r="V180" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="W180" s="7" t="n">
+      <c r="W180" s="3" t="n">
         <v>145</v>
       </c>
     </row>
@@ -14189,7 +14189,7 @@
         <v>2.99</v>
       </c>
       <c r="I181" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J181" t="n">
         <v>41.95</v>
@@ -14264,7 +14264,7 @@
         <v>13.02</v>
       </c>
       <c r="I182" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J182" t="n">
         <v>41.4</v>
@@ -14339,7 +14339,7 @@
         <v>0.86</v>
       </c>
       <c r="I183" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J183" t="n">
         <v>40.86</v>
@@ -14414,7 +14414,7 @@
         <v>8.33</v>
       </c>
       <c r="I184" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J184" t="n">
         <v>40.35</v>
@@ -14489,7 +14489,7 @@
         <v>5.29</v>
       </c>
       <c r="I185" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J185" t="n">
         <v>40.05</v>
@@ -14564,7 +14564,7 @@
         <v>0.12</v>
       </c>
       <c r="I186" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J186" t="n">
         <v>39.72</v>
@@ -14639,7 +14639,7 @@
         <v>6.03</v>
       </c>
       <c r="I187" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J187" t="n">
         <v>39.48</v>
@@ -14714,7 +14714,7 @@
         <v>6.35</v>
       </c>
       <c r="I188" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J188" t="n">
         <v>39.67</v>
@@ -14789,7 +14789,7 @@
         <v>-3.05</v>
       </c>
       <c r="I189" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J189" t="n">
         <v>39.59</v>
@@ -14864,7 +14864,7 @@
         <v>2.97</v>
       </c>
       <c r="I190" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J190" t="n">
         <v>39.76</v>
@@ -14939,7 +14939,7 @@
         <v>3.21</v>
       </c>
       <c r="I191" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J191" t="n">
         <v>40.08</v>
@@ -15014,7 +15014,7 @@
         <v>-0.42</v>
       </c>
       <c r="I192" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J192" t="n">
         <v>40.22</v>
@@ -15089,7 +15089,7 @@
         <v>3.89</v>
       </c>
       <c r="I193" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J193" t="n">
         <v>40.61</v>
@@ -15164,7 +15164,7 @@
         <v>-1.73</v>
       </c>
       <c r="I194" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J194" t="n">
         <v>40.86</v>
@@ -15239,7 +15239,7 @@
         <v>-14.52</v>
       </c>
       <c r="I195" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>40.99</v>
@@ -15314,7 +15314,7 @@
         <v>-1.27</v>
       </c>
       <c r="I196" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J196" t="n">
         <v>41.1</v>
@@ -15389,7 +15389,7 @@
         <v>-1.68</v>
       </c>
       <c r="I197" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J197" t="n">
         <v>41.29</v>
@@ -15468,7 +15468,7 @@
         <v>-11.05</v>
       </c>
       <c r="I198" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J198" t="n">
         <v>41.37</v>
@@ -15543,7 +15543,7 @@
         <v>7.11</v>
       </c>
       <c r="I199" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J199" t="n">
         <v>41.5</v>
@@ -15618,7 +15618,7 @@
         <v>8.15</v>
       </c>
       <c r="I200" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J200" t="n">
         <v>42.05</v>
@@ -15693,7 +15693,7 @@
         <v>3.69</v>
       </c>
       <c r="I201" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J201" t="n">
         <v>42.62</v>
@@ -15768,7 +15768,7 @@
         <v>1.02</v>
       </c>
       <c r="I202" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J202" t="n">
         <v>43.01</v>
@@ -15843,7 +15843,7 @@
         <v>1.17</v>
       </c>
       <c r="I203" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J203" t="n">
         <v>43.41</v>
@@ -15918,7 +15918,7 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J204" t="n">
         <v>43.67</v>
@@ -15993,7 +15993,7 @@
         <v>-0.88</v>
       </c>
       <c r="I205" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J205" t="n">
         <v>43.79</v>
@@ -16068,7 +16068,7 @@
         <v>-0.34</v>
       </c>
       <c r="I206" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J206" t="n">
         <v>43.91</v>
@@ -16147,7 +16147,7 @@
         <v>-3.76</v>
       </c>
       <c r="I207" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J207" t="n">
         <v>43.82</v>
@@ -16222,7 +16222,7 @@
         <v>12.4</v>
       </c>
       <c r="I208" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J208" t="n">
         <v>43.86</v>
@@ -16297,7 +16297,7 @@
         <v>4.19</v>
       </c>
       <c r="I209" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J209" t="n">
         <v>44.06</v>
@@ -16372,7 +16372,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J210" t="n">
         <v>44.43</v>
@@ -16447,7 +16447,7 @@
         <v>-3.17</v>
       </c>
       <c r="I211" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J211" t="n">
         <v>44.65</v>
@@ -16522,7 +16522,7 @@
         <v>-5.05</v>
       </c>
       <c r="I212" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J212" t="n">
         <v>44.74</v>
@@ -16597,7 +16597,7 @@
         <v>8.65</v>
       </c>
       <c r="I213" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J213" t="n">
         <v>44.96</v>
@@ -16672,7 +16672,7 @@
         <v>1.3</v>
       </c>
       <c r="I214" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J214" t="n">
         <v>45.25</v>
@@ -16747,7 +16747,7 @@
         <v>2.6</v>
       </c>
       <c r="I215" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J215" t="n">
         <v>45.97</v>
@@ -16822,7 +16822,7 @@
         <v>-1.23</v>
       </c>
       <c r="I216" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J216" t="n">
         <v>46.68</v>
@@ -16897,7 +16897,7 @@
         <v>4.88</v>
       </c>
       <c r="I217" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J217" t="n">
         <v>47.56</v>
@@ -16972,7 +16972,7 @@
         <v>4.6</v>
       </c>
       <c r="I218" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J218" t="n">
         <v>48.79</v>
@@ -17047,7 +17047,7 @@
         <v>-4.63</v>
       </c>
       <c r="I219" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J219" t="n">
         <v>49.76</v>
@@ -17122,7 +17122,7 @@
         <v>9.57</v>
       </c>
       <c r="I220" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J220" t="n">
         <v>50.85</v>
@@ -17197,7 +17197,7 @@
         <v>0.38</v>
       </c>
       <c r="I221" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J221" t="n">
         <v>51.87</v>
@@ -17272,7 +17272,7 @@
         <v>-3.33</v>
       </c>
       <c r="I222" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J222" t="n">
         <v>52.76</v>
@@ -17347,7 +17347,7 @@
         <v>-1.46</v>
       </c>
       <c r="I223" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J223" t="n">
         <v>53.59</v>
@@ -17422,7 +17422,7 @@
         <v>7.02</v>
       </c>
       <c r="I224" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J224" t="n">
         <v>54.62</v>
@@ -17497,7 +17497,7 @@
         <v>7.89</v>
       </c>
       <c r="I225" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J225" t="n">
         <v>55.94</v>
@@ -17572,7 +17572,7 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J226" t="n">
         <v>57.28</v>
@@ -17647,7 +17647,7 @@
         <v>-12.31</v>
       </c>
       <c r="I227" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J227" t="n">
         <v>58.26</v>
@@ -17722,7 +17722,7 @@
         <v>5.52</v>
       </c>
       <c r="I228" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J228" t="n">
         <v>59.16</v>
@@ -17797,7 +17797,7 @@
         <v>-6.14</v>
       </c>
       <c r="I229" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J229" t="n">
         <v>59.76</v>
@@ -17872,7 +17872,7 @@
         <v>-13.08</v>
       </c>
       <c r="I230" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J230" t="n">
         <v>59.72</v>
@@ -17951,7 +17951,7 @@
         <v>0.11</v>
       </c>
       <c r="I231" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J231" t="n">
         <v>59.77</v>
@@ -18026,7 +18026,7 @@
         <v>15.95</v>
       </c>
       <c r="I232" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J232" t="n">
         <v>60.37</v>
@@ -18101,7 +18101,7 @@
         <v>3.69</v>
       </c>
       <c r="I233" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J233" t="n">
         <v>60.88</v>
@@ -18176,7 +18176,7 @@
         <v>-1.08</v>
       </c>
       <c r="I234" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J234" t="n">
         <v>61.31</v>
@@ -18251,7 +18251,7 @@
         <v>7.44</v>
       </c>
       <c r="I235" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J235" t="n">
         <v>61.91</v>
@@ -18326,7 +18326,7 @@
         <v>-7.28</v>
       </c>
       <c r="I236" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J236" t="n">
         <v>62.29</v>
@@ -18401,7 +18401,7 @@
         <v>2.36</v>
       </c>
       <c r="I237" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J237" t="n">
         <v>62.62</v>
@@ -18476,7 +18476,7 @@
         <v>-0.37</v>
       </c>
       <c r="I238" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J238" t="n">
         <v>62.8</v>
@@ -18551,7 +18551,7 @@
         <v>3.02</v>
       </c>
       <c r="I239" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J239" t="n">
         <v>63.22</v>
@@ -18626,7 +18626,7 @@
         <v>-1.6</v>
       </c>
       <c r="I240" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J240" t="n">
         <v>63.31</v>
@@ -18701,7 +18701,7 @@
         <v>2.88</v>
       </c>
       <c r="I241" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J241" t="n">
         <v>63.47</v>
@@ -18776,7 +18776,7 @@
         <v>-1.86</v>
       </c>
       <c r="I242" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J242" t="n">
         <v>63.69</v>
@@ -18851,7 +18851,7 @@
         <v>4.06</v>
       </c>
       <c r="I243" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J243" t="n">
         <v>64.08</v>
@@ -18926,7 +18926,7 @@
         <v>4.85</v>
       </c>
       <c r="I244" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J244" t="n">
         <v>64.42</v>
@@ -19001,7 +19001,7 @@
         <v>-9.07</v>
       </c>
       <c r="I245" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J245" t="n">
         <v>64.19</v>
@@ -19076,7 +19076,7 @@
         <v>-3.94</v>
       </c>
       <c r="I246" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J246" t="n">
         <v>63.8</v>
@@ -19155,7 +19155,7 @@
         <v>-0.02</v>
       </c>
       <c r="I247" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J247" t="n">
         <v>63.85</v>
@@ -19230,7 +19230,7 @@
         <v>-14.89</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>63.26</v>
@@ -19309,7 +19309,7 @@
         <v>5.99</v>
       </c>
       <c r="I249" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J249" t="n">
         <v>63.03</v>
@@ -19384,7 +19384,7 @@
         <v>-3.22</v>
       </c>
       <c r="I250" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J250" t="n">
         <v>63.11</v>
@@ -19463,7 +19463,7 @@
         <v>-12.6</v>
       </c>
       <c r="I251" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J251" t="n">
         <v>62.84</v>
@@ -19542,7 +19542,7 @@
         <v>11.35</v>
       </c>
       <c r="I252" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J252" t="n">
         <v>62.42</v>
@@ -19617,7 +19617,7 @@
         <v>2.36</v>
       </c>
       <c r="I253" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J253" t="n">
         <v>61.95</v>
@@ -19692,7 +19692,7 @@
         <v>2.75</v>
       </c>
       <c r="I254" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J254" t="n">
         <v>61.59</v>
@@ -19767,7 +19767,7 @@
         <v>-10.35</v>
       </c>
       <c r="I255" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J255" t="n">
         <v>60.7</v>
@@ -19840,7 +19840,7 @@
         <v>0.88</v>
       </c>
       <c r="I256" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J256" t="n">
         <v>60.08</v>
@@ -19919,7 +19919,7 @@
         <v>5.84</v>
       </c>
       <c r="I257" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J257" t="n">
         <v>59.54</v>
@@ -19994,7 +19994,7 @@
         <v>2.35</v>
       </c>
       <c r="I258" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J258" t="n">
         <v>59.07</v>
@@ -20069,7 +20069,7 @@
         <v>-1.69</v>
       </c>
       <c r="I259" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J259" t="n">
         <v>58.45</v>
@@ -20144,7 +20144,7 @@
         <v>1.54</v>
       </c>
       <c r="I260" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J260" t="n">
         <v>57.93</v>
@@ -20219,7 +20219,7 @@
         <v>-6.75</v>
       </c>
       <c r="I261" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J261" t="n">
         <v>57.14</v>
@@ -20298,7 +20298,7 @@
         <v>3.7</v>
       </c>
       <c r="I262" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J262" t="n">
         <v>56.5</v>
@@ -20373,7 +20373,7 @@
         <v>3.62</v>
       </c>
       <c r="I263" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J263" t="n">
         <v>55.82</v>
@@ -20448,7 +20448,7 @@
         <v>3.79</v>
       </c>
       <c r="I264" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J264" t="n">
         <v>55.08</v>
@@ -20523,7 +20523,7 @@
         <v>-14.14</v>
       </c>
       <c r="I265" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J265" t="n">
         <v>54.26</v>
@@ -20602,7 +20602,7 @@
         <v>-4.82</v>
       </c>
       <c r="I266" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J266" t="n">
         <v>53.45</v>
@@ -20681,7 +20681,7 @@
         <v>-12.86</v>
       </c>
       <c r="I267" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J267" t="n">
         <v>52.34</v>
@@ -20756,7 +20756,7 @@
         <v>17.96</v>
       </c>
       <c r="I268" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J268" t="n">
         <v>52.07</v>
@@ -20831,7 +20831,7 @@
         <v>9.09</v>
       </c>
       <c r="I269" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J269" t="n">
         <v>51.85</v>
@@ -20906,7 +20906,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J270" t="n">
         <v>51.75</v>
@@ -20981,7 +20981,7 @@
         <v>3.89</v>
       </c>
       <c r="I271" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J271" t="n">
         <v>52.1</v>
@@ -21056,7 +21056,7 @@
         <v>3.18</v>
       </c>
       <c r="I272" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J272" t="n">
         <v>52.26</v>
@@ -21135,7 +21135,7 @@
         <v>19.38</v>
       </c>
       <c r="I273" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J273" t="n">
         <v>52.9</v>
@@ -21210,7 +21210,7 @@
         <v>6.63</v>
       </c>
       <c r="I274" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J274" t="n">
         <v>53.7</v>
@@ -21285,7 +21285,7 @@
         <v>6.13</v>
       </c>
       <c r="I275" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J275" t="n">
         <v>55</v>
@@ -21360,7 +21360,7 @@
         <v>5.46</v>
       </c>
       <c r="I276" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J276" t="n">
         <v>56.49</v>
@@ -21435,7 +21435,7 @@
         <v>5.89</v>
       </c>
       <c r="I277" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J277" t="n">
         <v>58.07</v>
@@ -21510,7 +21510,7 @@
         <v>0.76</v>
       </c>
       <c r="I278" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J278" t="n">
         <v>59.62</v>
@@ -21585,7 +21585,7 @@
         <v>2.81</v>
       </c>
       <c r="I279" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J279" t="n">
         <v>61.34</v>
@@ -21660,7 +21660,7 @@
         <v>7.15</v>
       </c>
       <c r="I280" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J280" t="n">
         <v>63.33</v>
@@ -21735,7 +21735,7 @@
         <v>1.33</v>
       </c>
       <c r="I281" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J281" t="n">
         <v>65.56999999999999</v>
@@ -21810,7 +21810,7 @@
         <v>2.24</v>
       </c>
       <c r="I282" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J282" t="n">
         <v>67.81999999999999</v>
@@ -21885,7 +21885,7 @@
         <v>7.69</v>
       </c>
       <c r="I283" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J283" t="n">
         <v>70.34999999999999</v>
@@ -21960,7 +21960,7 @@
         <v>6.75</v>
       </c>
       <c r="I284" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J284" t="n">
         <v>73.14</v>
@@ -22035,7 +22035,7 @@
         <v>13.79</v>
       </c>
       <c r="I285" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J285" t="n">
         <v>77.09999999999999</v>
@@ -22110,7 +22110,7 @@
         <v>-3.84</v>
       </c>
       <c r="I286" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J286" t="n">
         <v>80.94</v>
@@ -22185,7 +22185,7 @@
         <v>-11.21</v>
       </c>
       <c r="I287" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J287" t="n">
         <v>84.38</v>
@@ -22260,7 +22260,7 @@
         <v>7.67</v>
       </c>
       <c r="I288" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J288" t="n">
         <v>87.88</v>
@@ -22335,7 +22335,7 @@
         <v>7.64</v>
       </c>
       <c r="I289" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J289" t="n">
         <v>91.62</v>
@@ -22410,7 +22410,7 @@
         <v>2.69</v>
       </c>
       <c r="I290" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J290" t="n">
         <v>95.5</v>
@@ -22485,7 +22485,7 @@
         <v>-2.18</v>
       </c>
       <c r="I291" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J291" t="n">
         <v>99.13</v>
@@ -22560,7 +22560,7 @@
         <v>13.02</v>
       </c>
       <c r="I292" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J292" t="n">
         <v>103.51</v>
@@ -22635,7 +22635,7 @@
         <v>15.04</v>
       </c>
       <c r="I293" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J293" t="n">
         <v>108.42</v>
@@ -22710,7 +22710,7 @@
         <v>-8.289999999999999</v>
       </c>
       <c r="I294" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J294" t="n">
         <v>112.43</v>
@@ -22785,7 +22785,7 @@
         <v>16.33</v>
       </c>
       <c r="I295" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J295" t="n">
         <v>117.45</v>
@@ -22860,7 +22860,7 @@
         <v>7.62</v>
       </c>
       <c r="I296" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J296" t="n">
         <v>122.94</v>
@@ -22935,7 +22935,7 @@
         <v>-9.4</v>
       </c>
       <c r="I297" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J297" t="n">
         <v>127.3</v>
@@ -23010,7 +23010,7 @@
         <v>6.79</v>
       </c>
       <c r="I298" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J298" t="n">
         <v>132.21</v>
@@ -23085,7 +23085,7 @@
         <v>1.06</v>
       </c>
       <c r="I299" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J299" t="n">
         <v>137.1</v>
@@ -23160,7 +23160,7 @@
         <v>-11.82</v>
       </c>
       <c r="I300" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J300" t="n">
         <v>140.57</v>
@@ -23235,7 +23235,7 @@
         <v>-7.57</v>
       </c>
       <c r="I301" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J301" t="n">
         <v>143.36</v>
@@ -23310,7 +23310,7 @@
         <v>0.09</v>
       </c>
       <c r="I302" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J302" t="n">
         <v>146.05</v>
@@ -23385,7 +23385,7 @@
         <v>14.03</v>
       </c>
       <c r="I303" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J303" t="n">
         <v>149.42</v>
@@ -23460,7 +23460,7 @@
         <v>2.99</v>
       </c>
       <c r="I304" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J304" t="n">
         <v>152.7</v>
@@ -23535,7 +23535,7 @@
         <v>6.83</v>
       </c>
       <c r="I305" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J305" t="n">
         <v>155.81</v>
@@ -23610,7 +23610,7 @@
         <v>18.48</v>
       </c>
       <c r="I306" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J306" t="n">
         <v>160.93</v>
@@ -23685,7 +23685,7 @@
         <v>-3.46</v>
       </c>
       <c r="I307" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J307" t="n">
         <v>166.34</v>
@@ -23760,7 +23760,7 @@
         <v>3.05</v>
       </c>
       <c r="I308" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J308" t="n">
         <v>171.67</v>
@@ -23835,7 +23835,7 @@
         <v>-0.13</v>
       </c>
       <c r="I309" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J309" t="n">
         <v>176.54</v>
@@ -23910,7 +23910,7 @@
         <v>1.2</v>
       </c>
       <c r="I310" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J310" t="n">
         <v>181.37</v>
@@ -23985,7 +23985,7 @@
         <v>17.31</v>
       </c>
       <c r="I311" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J311" t="n">
         <v>188.3</v>
@@ -24060,7 +24060,7 @@
         <v>5.34</v>
       </c>
       <c r="I312" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J312" t="n">
         <v>195.12</v>
@@ -24135,7 +24135,7 @@
         <v>-6.36</v>
       </c>
       <c r="I313" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J313" t="n">
         <v>199.96</v>
@@ -24210,7 +24210,7 @@
         <v>-30.51</v>
       </c>
       <c r="I314" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J314" s="4" t="n">
         <v>201.48</v>
@@ -24289,7 +24289,7 @@
         <v>15.83</v>
       </c>
       <c r="I315" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J315" t="n">
         <v>203.2</v>
@@ -24364,7 +24364,7 @@
         <v>-4.61</v>
       </c>
       <c r="I316" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J316" t="n">
         <v>203.76</v>
@@ -24443,7 +24443,7 @@
         <v>-10.43</v>
       </c>
       <c r="I317" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J317" t="n">
         <v>204.17</v>
@@ -24518,7 +24518,7 @@
         <v>23.99</v>
       </c>
       <c r="I318" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J318" t="n">
         <v>206.15</v>
@@ -24593,7 +24593,7 @@
         <v>4.78</v>
       </c>
       <c r="I319" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J319" t="n">
         <v>208.58</v>
@@ -24668,7 +24668,7 @@
         <v>16.11</v>
       </c>
       <c r="I320" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J320" t="n">
         <v>213.99</v>
@@ -24743,7 +24743,7 @@
         <v>-16.99</v>
       </c>
       <c r="I321" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J321" s="4" t="n">
         <v>217.71</v>
@@ -24818,7 +24818,7 @@
         <v>3.39</v>
       </c>
       <c r="I322" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J322" t="n">
         <v>221.81</v>
@@ -24893,7 +24893,7 @@
         <v>19.43</v>
       </c>
       <c r="I323" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J323" t="n">
         <v>227.11</v>
@@ -24968,7 +24968,7 @@
         <v>7.69</v>
       </c>
       <c r="I324" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J324" t="n">
         <v>233.22</v>
@@ -25043,7 +25043,7 @@
         <v>-23.06</v>
       </c>
       <c r="I325" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J325" s="4" t="n">
         <v>235.26</v>
@@ -25122,7 +25122,7 @@
         <v>-0.8</v>
       </c>
       <c r="I326" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J326" t="n">
         <v>235.45</v>
@@ -25197,7 +25197,7 @@
         <v>10.03</v>
       </c>
       <c r="I327" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J327" t="n">
         <v>237.18</v>
@@ -25272,7 +25272,7 @@
         <v>-14.65</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J328" s="4" t="n">
         <v>236.73</v>
@@ -25351,7 +25351,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I329" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J329" t="n">
         <v>237.34</v>
@@ -25426,7 +25426,7 @@
         <v>12.76</v>
       </c>
       <c r="I330" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J330" t="n">
         <v>239.32</v>
@@ -25501,7 +25501,7 @@
         <v>-18.43</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>236.89</v>
@@ -25580,7 +25580,7 @@
         <v>-16.59</v>
       </c>
       <c r="I332" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J332" s="4" t="n">
         <v>231.94</v>
@@ -25655,7 +25655,7 @@
         <v>7.26</v>
       </c>
       <c r="I333" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J333" t="n">
         <v>228.54</v>
@@ -25730,7 +25730,7 @@
         <v>-15.09</v>
       </c>
       <c r="I334" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J334" s="4" t="n">
         <v>227.67</v>
@@ -25809,7 +25809,7 @@
         <v>5.78</v>
       </c>
       <c r="I335" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J335" t="n">
         <v>225.84</v>
@@ -25884,7 +25884,7 @@
         <v>10.08</v>
       </c>
       <c r="I336" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J336" t="n">
         <v>225.38</v>
@@ -25959,7 +25959,7 @@
         <v>-0.1</v>
       </c>
       <c r="I337" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J337" t="n">
         <v>225.96</v>
@@ -26034,7 +26034,7 @@
         <v>-13.99</v>
       </c>
       <c r="I338" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J338" t="n">
         <v>223.03</v>
@@ -26113,7 +26113,7 @@
         <v>6.83</v>
       </c>
       <c r="I339" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J339" t="n">
         <v>220.13</v>
@@ -26188,7 +26188,7 @@
         <v>-6.29</v>
       </c>
       <c r="I340" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J340" t="n">
         <v>214.79</v>
@@ -26263,7 +26263,7 @@
         <v>-13.93</v>
       </c>
       <c r="I341" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J341" t="n">
         <v>210.61</v>
@@ -26338,7 +26338,7 @@
         <v>-4.92</v>
       </c>
       <c r="I342" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J342" t="n">
         <v>205.69</v>
@@ -26413,7 +26413,7 @@
         <v>0.99</v>
       </c>
       <c r="I343" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J343" t="n">
         <v>198.57</v>
@@ -26488,7 +26488,7 @@
         <v>15.89</v>
       </c>
       <c r="I344" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J344" t="n">
         <v>191.46</v>
@@ -26563,7 +26563,7 @@
         <v>1.54</v>
       </c>
       <c r="I345" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J345" t="n">
         <v>187.94</v>
@@ -26638,7 +26638,7 @@
         <v>-2.16</v>
       </c>
       <c r="I346" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J346" t="n">
         <v>184.34</v>
@@ -26713,7 +26713,7 @@
         <v>-13.14</v>
       </c>
       <c r="I347" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J347" t="n">
         <v>178.56</v>
@@ -26788,7 +26788,7 @@
         <v>-6.33</v>
       </c>
       <c r="I348" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J348" t="n">
         <v>174.19</v>
@@ -26867,7 +26867,7 @@
         <v>-14.52</v>
       </c>
       <c r="I349" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>167.84</v>
@@ -26942,7 +26942,7 @@
         <v>-16.02</v>
       </c>
       <c r="I350" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>159.11</v>
@@ -27021,7 +27021,7 @@
         <v>24.7</v>
       </c>
       <c r="I351" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J351" t="n">
         <v>153.97</v>
@@ -27096,7 +27096,7 @@
         <v>0</v>
       </c>
       <c r="I352" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J352" t="n">
         <v>150.64</v>
@@ -27171,7 +27171,7 @@
         <v>1.74</v>
       </c>
       <c r="I353" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J353" t="n">
         <v>146.74</v>
@@ -27246,7 +27246,7 @@
         <v>19.87</v>
       </c>
       <c r="I354" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J354" t="n">
         <v>145.48</v>
@@ -27321,7 +27321,7 @@
         <v>-5.6</v>
       </c>
       <c r="I355" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J355" t="n">
         <v>143.34</v>
@@ -27400,7 +27400,7 @@
         <v>0.2</v>
       </c>
       <c r="I356" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J356" t="n">
         <v>140.34</v>
@@ -27475,7 +27475,7 @@
         <v>5.99</v>
       </c>
       <c r="I357" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J357" t="n">
         <v>137.74</v>
@@ -27550,7 +27550,7 @@
         <v>-7.31</v>
       </c>
       <c r="I358" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J358" t="n">
         <v>135.97</v>
@@ -27629,7 +27629,7 @@
         <v>2.31</v>
       </c>
       <c r="I359" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J359" t="n">
         <v>133.79</v>
@@ -27704,7 +27704,7 @@
         <v>6.89</v>
       </c>
       <c r="I360" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J360" t="n">
         <v>132.62</v>
@@ -27779,7 +27779,7 @@
         <v>2.25</v>
       </c>
       <c r="I361" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J361" t="n">
         <v>132.76</v>
@@ -27854,7 +27854,7 @@
         <v>-0.28</v>
       </c>
       <c r="I362" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J362" t="n">
         <v>133.24</v>
@@ -27929,7 +27929,7 @@
         <v>4.54</v>
       </c>
       <c r="I363" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J363" t="n">
         <v>133.97</v>
@@ -28004,7 +28004,7 @@
         <v>-14.8</v>
       </c>
       <c r="I364" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J364" s="4" t="n">
         <v>132.5</v>
@@ -28083,7 +28083,7 @@
         <v>-6.48</v>
       </c>
       <c r="I365" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J365" t="n">
         <v>130.49</v>
@@ -28158,7 +28158,7 @@
         <v>1.22</v>
       </c>
       <c r="I366" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J366" t="n">
         <v>128.73</v>
@@ -28233,7 +28233,7 @@
         <v>-1.32</v>
       </c>
       <c r="I367" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J367" t="n">
         <v>127.92</v>
@@ -28308,7 +28308,7 @@
         <v>-7.82</v>
       </c>
       <c r="I368" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J368" t="n">
         <v>127.07</v>
@@ -28383,7 +28383,7 @@
         <v>4.05</v>
       </c>
       <c r="I369" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J369" t="n">
         <v>127.37</v>
@@ -28458,7 +28458,7 @@
         <v>0.8</v>
       </c>
       <c r="I370" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J370" t="n">
         <v>128.6</v>
@@ -28533,7 +28533,7 @@
         <v>5.54</v>
       </c>
       <c r="I371" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J371" t="n">
         <v>129.02</v>
@@ -28608,7 +28608,7 @@
         <v>-9.51</v>
       </c>
       <c r="I372" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J372" t="n">
         <v>128.85</v>
@@ -28683,7 +28683,7 @@
         <v>1.3</v>
       </c>
       <c r="I373" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J373" t="n">
         <v>128.66</v>
@@ -28758,7 +28758,7 @@
         <v>-6.1</v>
       </c>
       <c r="I374" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J374" t="n">
         <v>126.96</v>
@@ -28837,7 +28837,7 @@
         <v>0.42</v>
       </c>
       <c r="I375" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J375" t="n">
         <v>125.67</v>
@@ -28916,7 +28916,7 @@
         <v>0.37</v>
       </c>
       <c r="I376" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J376" t="n">
         <v>124.39</v>
@@ -28995,7 +28995,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="I377" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J377" t="n">
         <v>123.25</v>
@@ -29070,7 +29070,7 @@
         <v>5.11</v>
       </c>
       <c r="I378" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J378" t="n">
         <v>122.91</v>
@@ -29145,7 +29145,7 @@
         <v>2.11</v>
       </c>
       <c r="I379" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J379" t="n">
         <v>122.55</v>
@@ -29220,7 +29220,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="I380" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J380" t="n">
         <v>121.23</v>
@@ -29299,7 +29299,7 @@
         <v>5.24</v>
       </c>
       <c r="I381" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J381" t="n">
         <v>120.06</v>
@@ -29374,7 +29374,7 @@
         <v>-16.99</v>
       </c>
       <c r="I382" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J382" s="4" t="n">
         <v>117.87</v>
@@ -29453,7 +29453,7 @@
         <v>1.18</v>
       </c>
       <c r="I383" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J383" t="n">
         <v>115.41</v>
@@ -29528,7 +29528,7 @@
         <v>1.61</v>
       </c>
       <c r="I384" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J384" t="n">
         <v>114.15</v>
@@ -29603,7 +29603,7 @@
         <v>10.43</v>
       </c>
       <c r="I385" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J385" t="n">
         <v>113.86</v>
@@ -29678,7 +29678,7 @@
         <v>7.71</v>
       </c>
       <c r="I386" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J386" t="n">
         <v>113.93</v>
@@ -29753,7 +29753,7 @@
         <v>14.77</v>
       </c>
       <c r="I387" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J387" t="n">
         <v>115</v>
@@ -29828,7 +29828,7 @@
         <v>7.13</v>
       </c>
       <c r="I388" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J388" t="n">
         <v>117.04</v>
@@ -29903,7 +29903,7 @@
         <v>-3.75</v>
       </c>
       <c r="I389" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J389" t="n">
         <v>118.57</v>
@@ -29978,7 +29978,7 @@
         <v>0.05</v>
       </c>
       <c r="I390" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J390" t="n">
         <v>120.06</v>
@@ -30053,7 +30053,7 @@
         <v>3.5</v>
       </c>
       <c r="I391" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J391" t="n">
         <v>121.49</v>
@@ -30128,7 +30128,7 @@
         <v>-6.05</v>
       </c>
       <c r="I392" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J392" t="n">
         <v>123.04</v>
@@ -30203,7 +30203,7 @@
         <v>3.31</v>
       </c>
       <c r="I393" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J393" t="n">
         <v>124.75</v>
@@ -30278,7 +30278,7 @@
         <v>0.59</v>
       </c>
       <c r="I394" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J394" t="n">
         <v>126.85</v>
@@ -30353,7 +30353,7 @@
         <v>3.94</v>
       </c>
       <c r="I395" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J395" t="n">
         <v>129.22</v>
@@ -30428,7 +30428,7 @@
         <v>6.52</v>
       </c>
       <c r="I396" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J396" t="n">
         <v>132.08</v>
@@ -30503,7 +30503,7 @@
         <v>0.34</v>
       </c>
       <c r="I397" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J397" t="n">
         <v>134.43</v>
@@ -30578,7 +30578,7 @@
         <v>-0.01</v>
       </c>
       <c r="I398" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J398" t="n">
         <v>136.48</v>
@@ -30653,7 +30653,7 @@
         <v>-3.26</v>
       </c>
       <c r="I399" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J399" t="n">
         <v>138.14</v>
@@ -30732,7 +30732,7 @@
         <v>-10.31</v>
       </c>
       <c r="I400" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J400" t="n">
         <v>139.48</v>
@@ -30807,7 +30807,7 @@
         <v>-1.94</v>
       </c>
       <c r="I401" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J401" t="n">
         <v>140.38</v>
@@ -30886,7 +30886,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="I402" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J402" t="n">
         <v>141.75</v>
@@ -30965,7 +30965,7 @@
         <v>-0.65</v>
       </c>
       <c r="I403" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J403" t="n">
         <v>143.01</v>
@@ -31040,7 +31040,7 @@
         <v>-13.35</v>
       </c>
       <c r="I404" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J404" t="n">
         <v>143.35</v>
@@ -31115,7 +31115,7 @@
         <v>-2.89</v>
       </c>
       <c r="I405" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J405" t="n">
         <v>142.98</v>
@@ -31194,7 +31194,7 @@
         <v>-12.74</v>
       </c>
       <c r="I406" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J406" t="n">
         <v>141.48</v>
@@ -31273,7 +31273,7 @@
         <v>5.32</v>
       </c>
       <c r="I407" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J407" t="n">
         <v>139.32</v>
@@ -31352,7 +31352,7 @@
         <v>-1.12</v>
       </c>
       <c r="I408" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J408" t="n">
         <v>136.6</v>
@@ -31431,7 +31431,7 @@
         <v>5.83</v>
       </c>
       <c r="I409" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J409" t="n">
         <v>134.45</v>
@@ -31510,7 +31510,7 @@
         <v>-20.47</v>
       </c>
       <c r="I410" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>131.24</v>
@@ -31589,7 +31589,7 @@
         <v>1.77</v>
       </c>
       <c r="I411" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J411" t="n">
         <v>127.85</v>
@@ -31668,7 +31668,7 @@
         <v>8.31</v>
       </c>
       <c r="I412" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J412" t="n">
         <v>125.26</v>
@@ -31747,7 +31747,7 @@
         <v>11.69</v>
       </c>
       <c r="I413" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J413" t="n">
         <v>122.96</v>
@@ -31826,7 +31826,7 @@
         <v>6.2</v>
       </c>
       <c r="I414" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J414" t="n">
         <v>120.93</v>
@@ -31901,7 +31901,7 @@
         <v>-4.62</v>
       </c>
       <c r="I415" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J415" t="n">
         <v>118.37</v>
@@ -31919,7 +31919,7 @@
         <v>32.89</v>
       </c>
       <c r="O415" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31945,6 +31945,83 @@
       <c r="W415" s="3" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="4" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B416" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C416" s="4" t="n">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="D416" s="4" t="n">
+        <v>84.19</v>
+      </c>
+      <c r="E416" s="4" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="F416" s="4" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="G416" s="4" t="n">
+        <v>84356090</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>-24.66</v>
+      </c>
+      <c r="I416" s="4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J416" s="4" t="n">
+        <v>114.04</v>
+      </c>
+      <c r="K416" s="4" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="L416" s="4" t="n">
+        <v>156.67</v>
+      </c>
+      <c r="M416" s="4" t="n">
+        <v>124.18</v>
+      </c>
+      <c r="N416" s="6" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="O416" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="P416" s="4" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S416" s="4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T416" s="7" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="U416" s="7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V416" s="4" t="inlineStr"/>
+      <c r="W416" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -608,7 +608,7 @@
         <v>-13.84</v>
       </c>
       <c r="I2" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J2" t="n">
         <v>25.07</v>
@@ -691,7 +691,7 @@
         <v>-3.19</v>
       </c>
       <c r="I3" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J3" t="n">
         <v>24.58</v>
@@ -774,7 +774,7 @@
         <v>5.09</v>
       </c>
       <c r="I4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J4" t="n">
         <v>24.13</v>
@@ -853,7 +853,7 @@
         <v>-1.16</v>
       </c>
       <c r="I5" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J5" t="n">
         <v>23.66</v>
@@ -932,7 +932,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J6" t="n">
         <v>23.23</v>
@@ -1007,7 +1007,7 @@
         <v>4.98</v>
       </c>
       <c r="I7" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J7" t="n">
         <v>22.84</v>
@@ -1082,7 +1082,7 @@
         <v>-4.12</v>
       </c>
       <c r="I8" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J8" t="n">
         <v>22.34</v>
@@ -1157,7 +1157,7 @@
         <v>2.22</v>
       </c>
       <c r="I9" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J9" t="n">
         <v>21.79</v>
@@ -1232,7 +1232,7 @@
         <v>-2.17</v>
       </c>
       <c r="I10" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J10" t="n">
         <v>21.21</v>
@@ -1307,7 +1307,7 @@
         <v>-3.28</v>
       </c>
       <c r="I11" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J11" t="n">
         <v>20.74</v>
@@ -1382,7 +1382,7 @@
         <v>8.93</v>
       </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J12" t="n">
         <v>20.45</v>
@@ -1457,7 +1457,7 @@
         <v>-1.82</v>
       </c>
       <c r="I13" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J13" t="n">
         <v>20.23</v>
@@ -1532,7 +1532,7 @@
         <v>-8.6</v>
       </c>
       <c r="I14" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J14" t="n">
         <v>19.86</v>
@@ -1611,7 +1611,7 @@
         <v>-5.45</v>
       </c>
       <c r="I15" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J15" t="n">
         <v>19.66</v>
@@ -1686,7 +1686,7 @@
         <v>-9.779999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J16" t="n">
         <v>19.33</v>
@@ -1761,7 +1761,7 @@
         <v>-0.5</v>
       </c>
       <c r="I17" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J17" t="n">
         <v>19.11</v>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J18" t="n">
         <v>18.88</v>
@@ -1911,7 +1911,7 @@
         <v>1.95</v>
       </c>
       <c r="I19" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J19" t="n">
         <v>18.6</v>
@@ -1986,7 +1986,7 @@
         <v>-29.83</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>18.21</v>
@@ -2069,7 +2069,7 @@
         <v>-23.5</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>17.61</v>
@@ -2152,7 +2152,7 @@
         <v>4.83</v>
       </c>
       <c r="I22" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J22" t="n">
         <v>17.17</v>
@@ -2235,7 +2235,7 @@
         <v>-9.77</v>
       </c>
       <c r="I23" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J23" t="n">
         <v>16.72</v>
@@ -2318,7 +2318,7 @@
         <v>54.74</v>
       </c>
       <c r="I24" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J24" t="n">
         <v>16.45</v>
@@ -2397,7 +2397,7 @@
         <v>-24.61</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>16.03</v>
@@ -2480,7 +2480,7 @@
         <v>6.26</v>
       </c>
       <c r="I26" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J26" t="n">
         <v>15.56</v>
@@ -2563,7 +2563,7 @@
         <v>2.36</v>
       </c>
       <c r="I27" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J27" t="n">
         <v>15.04</v>
@@ -2642,7 +2642,7 @@
         <v>1.25</v>
       </c>
       <c r="I28" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J28" t="n">
         <v>14.58</v>
@@ -2717,7 +2717,7 @@
         <v>-11.93</v>
       </c>
       <c r="I29" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J29" t="n">
         <v>14.04</v>
@@ -2800,7 +2800,7 @@
         <v>-1.51</v>
       </c>
       <c r="I30" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J30" t="n">
         <v>13.5</v>
@@ -2879,7 +2879,7 @@
         <v>-5.35</v>
       </c>
       <c r="I31" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J31" t="n">
         <v>12.98</v>
@@ -2954,7 +2954,7 @@
         <v>5.42</v>
       </c>
       <c r="I32" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J32" t="n">
         <v>12.4</v>
@@ -3029,7 +3029,7 @@
         <v>12.14</v>
       </c>
       <c r="I33" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J33" t="n">
         <v>11.89</v>
@@ -3108,7 +3108,7 @@
         <v>16.59</v>
       </c>
       <c r="I34" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J34" t="n">
         <v>11.55</v>
@@ -3183,7 +3183,7 @@
         <v>2.85</v>
       </c>
       <c r="I35" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J35" t="n">
         <v>11.28</v>
@@ -3258,7 +3258,7 @@
         <v>-0.41</v>
       </c>
       <c r="I36" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J36" t="n">
         <v>11.09</v>
@@ -3333,7 +3333,7 @@
         <v>-3.51</v>
       </c>
       <c r="I37" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J37" t="n">
         <v>10.89</v>
@@ -3408,7 +3408,7 @@
         <v>2.54</v>
       </c>
       <c r="I38" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J38" t="n">
         <v>10.7</v>
@@ -3483,7 +3483,7 @@
         <v>-0.5</v>
       </c>
       <c r="I39" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J39" t="n">
         <v>10.49</v>
@@ -3558,7 +3558,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J40" t="n">
         <v>10.59</v>
@@ -3633,7 +3633,7 @@
         <v>-1.81</v>
       </c>
       <c r="I41" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J41" t="n">
         <v>10.8</v>
@@ -3708,7 +3708,7 @@
         <v>-3.15</v>
       </c>
       <c r="I42" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J42" t="n">
         <v>10.98</v>
@@ -3783,7 +3783,7 @@
         <v>5.08</v>
       </c>
       <c r="I43" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J43" t="n">
         <v>11.23</v>
@@ -3858,7 +3858,7 @@
         <v>2.8</v>
       </c>
       <c r="I44" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J44" t="n">
         <v>11.27</v>
@@ -3933,7 +3933,7 @@
         <v>3.31</v>
       </c>
       <c r="I45" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J45" t="n">
         <v>11.49</v>
@@ -4008,7 +4008,7 @@
         <v>21.42</v>
       </c>
       <c r="I46" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J46" t="n">
         <v>11.84</v>
@@ -4083,7 +4083,7 @@
         <v>8.56</v>
       </c>
       <c r="I47" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J47" t="n">
         <v>12.24</v>
@@ -4158,7 +4158,7 @@
         <v>1.3</v>
       </c>
       <c r="I48" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J48" t="n">
         <v>12.65</v>
@@ -4233,7 +4233,7 @@
         <v>-1.97</v>
       </c>
       <c r="I49" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J49" t="n">
         <v>13.11</v>
@@ -4308,7 +4308,7 @@
         <v>-0.44</v>
       </c>
       <c r="I50" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J50" t="n">
         <v>13.56</v>
@@ -4383,7 +4383,7 @@
         <v>-1.75</v>
       </c>
       <c r="I51" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J51" t="n">
         <v>14.03</v>
@@ -4458,7 +4458,7 @@
         <v>-0.5</v>
       </c>
       <c r="I52" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J52" t="n">
         <v>14.47</v>
@@ -4533,7 +4533,7 @@
         <v>-5.42</v>
       </c>
       <c r="I53" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J53" t="n">
         <v>14.8</v>
@@ -4608,7 +4608,7 @@
         <v>-2.89</v>
       </c>
       <c r="I54" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J54" t="n">
         <v>15.03</v>
@@ -4683,7 +4683,7 @@
         <v>-4.68</v>
       </c>
       <c r="I55" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J55" t="n">
         <v>15.19</v>
@@ -4758,7 +4758,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J56" t="n">
         <v>15.44</v>
@@ -4833,7 +4833,7 @@
         <v>-1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J57" t="n">
         <v>15.7</v>
@@ -4908,7 +4908,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J58" t="n">
         <v>15.95</v>
@@ -4983,7 +4983,7 @@
         <v>-6.01</v>
       </c>
       <c r="I59" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J59" t="n">
         <v>16.16</v>
@@ -5062,7 +5062,7 @@
         <v>4.53</v>
       </c>
       <c r="I60" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J60" t="n">
         <v>16.33</v>
@@ -5137,7 +5137,7 @@
         <v>8.32</v>
       </c>
       <c r="I61" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J61" t="n">
         <v>16.6</v>
@@ -5212,7 +5212,7 @@
         <v>4.28</v>
       </c>
       <c r="I62" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J62" t="n">
         <v>16.92</v>
@@ -5287,7 +5287,7 @@
         <v>-1.47</v>
       </c>
       <c r="I63" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J63" t="n">
         <v>17.19</v>
@@ -5362,7 +5362,7 @@
         <v>1.98</v>
       </c>
       <c r="I64" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J64" t="n">
         <v>17.47</v>
@@ -5437,7 +5437,7 @@
         <v>7.33</v>
       </c>
       <c r="I65" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J65" t="n">
         <v>17.79</v>
@@ -5512,7 +5512,7 @@
         <v>6.34</v>
       </c>
       <c r="I66" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J66" t="n">
         <v>18.03</v>
@@ -5587,7 +5587,7 @@
         <v>-1.15</v>
       </c>
       <c r="I67" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J67" t="n">
         <v>18.18</v>
@@ -5662,7 +5662,7 @@
         <v>0.23</v>
       </c>
       <c r="I68" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J68" t="n">
         <v>18.32</v>
@@ -5737,7 +5737,7 @@
         <v>-7.59</v>
       </c>
       <c r="I69" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J69" t="n">
         <v>18.4</v>
@@ -5816,7 +5816,7 @@
         <v>9.27</v>
       </c>
       <c r="I70" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J70" t="n">
         <v>18.57</v>
@@ -5891,7 +5891,7 @@
         <v>-2.2</v>
       </c>
       <c r="I71" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J71" t="n">
         <v>18.74</v>
@@ -5966,7 +5966,7 @@
         <v>0.89</v>
       </c>
       <c r="I72" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J72" t="n">
         <v>18.92</v>
@@ -6041,7 +6041,7 @@
         <v>-1.86</v>
       </c>
       <c r="I73" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J73" t="n">
         <v>19.13</v>
@@ -6116,7 +6116,7 @@
         <v>1.75</v>
       </c>
       <c r="I74" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J74" t="n">
         <v>19.38</v>
@@ -6191,7 +6191,7 @@
         <v>11.35</v>
       </c>
       <c r="I75" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J75" t="n">
         <v>19.8</v>
@@ -6266,7 +6266,7 @@
         <v>2.63</v>
       </c>
       <c r="I76" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J76" t="n">
         <v>20.16</v>
@@ -6341,7 +6341,7 @@
         <v>2.52</v>
       </c>
       <c r="I77" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J77" t="n">
         <v>20.57</v>
@@ -6416,7 +6416,7 @@
         <v>-0.36</v>
       </c>
       <c r="I78" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J78" t="n">
         <v>20.97</v>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J79" t="n">
         <v>21.42</v>
@@ -6566,7 +6566,7 @@
         <v>-1.59</v>
       </c>
       <c r="I80" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J80" t="n">
         <v>21.81</v>
@@ -6641,7 +6641,7 @@
         <v>5.43</v>
       </c>
       <c r="I81" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J81" t="n">
         <v>22.2</v>
@@ -6716,7 +6716,7 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J82" t="n">
         <v>22.57</v>
@@ -6791,7 +6791,7 @@
         <v>-5.53</v>
       </c>
       <c r="I83" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J83" t="n">
         <v>22.89</v>
@@ -6866,7 +6866,7 @@
         <v>5.61</v>
       </c>
       <c r="I84" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J84" t="n">
         <v>23.25</v>
@@ -6941,7 +6941,7 @@
         <v>1.02</v>
       </c>
       <c r="I85" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J85" t="n">
         <v>23.55</v>
@@ -7016,7 +7016,7 @@
         <v>2.7</v>
       </c>
       <c r="I86" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J86" t="n">
         <v>23.83</v>
@@ -7091,7 +7091,7 @@
         <v>-0.29</v>
       </c>
       <c r="I87" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J87" t="n">
         <v>24.12</v>
@@ -7166,7 +7166,7 @@
         <v>-2.9</v>
       </c>
       <c r="I88" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J88" t="n">
         <v>24.36</v>
@@ -7241,7 +7241,7 @@
         <v>2.98</v>
       </c>
       <c r="I89" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J89" t="n">
         <v>24.72</v>
@@ -7316,7 +7316,7 @@
         <v>-0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J90" t="n">
         <v>24.98</v>
@@ -7391,7 +7391,7 @@
         <v>1.07</v>
       </c>
       <c r="I91" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J91" t="n">
         <v>25.28</v>
@@ -7466,7 +7466,7 @@
         <v>0.04</v>
       </c>
       <c r="I92" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J92" t="n">
         <v>25.57</v>
@@ -7541,7 +7541,7 @@
         <v>0.62</v>
       </c>
       <c r="I93" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J93" t="n">
         <v>25.89</v>
@@ -7616,7 +7616,7 @@
         <v>-4.26</v>
       </c>
       <c r="I94" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J94" t="n">
         <v>26.13</v>
@@ -7691,7 +7691,7 @@
         <v>-2.05</v>
       </c>
       <c r="I95" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J95" t="n">
         <v>26.22</v>
@@ -7770,7 +7770,7 @@
         <v>-0.62</v>
       </c>
       <c r="I96" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J96" t="n">
         <v>26.27</v>
@@ -7845,7 +7845,7 @@
         <v>-0.08</v>
       </c>
       <c r="I97" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J97" t="n">
         <v>26.29</v>
@@ -7920,7 +7920,7 @@
         <v>4.96</v>
       </c>
       <c r="I98" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J98" t="n">
         <v>26.38</v>
@@ -7995,7 +7995,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I99" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J99" t="n">
         <v>26.48</v>
@@ -8070,7 +8070,7 @@
         <v>2.15</v>
       </c>
       <c r="I100" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J100" t="n">
         <v>26.62</v>
@@ -8145,7 +8145,7 @@
         <v>-9.5</v>
       </c>
       <c r="I101" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J101" t="n">
         <v>26.57</v>
@@ -8224,7 +8224,7 @@
         <v>-3.61</v>
       </c>
       <c r="I102" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J102" t="n">
         <v>26.45</v>
@@ -8299,7 +8299,7 @@
         <v>3.82</v>
       </c>
       <c r="I103" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J103" t="n">
         <v>26.45</v>
@@ -8374,7 +8374,7 @@
         <v>-1.92</v>
       </c>
       <c r="I104" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J104" t="n">
         <v>26.36</v>
@@ -8449,7 +8449,7 @@
         <v>-2.16</v>
       </c>
       <c r="I105" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J105" t="n">
         <v>26.23</v>
@@ -8524,7 +8524,7 @@
         <v>4.21</v>
       </c>
       <c r="I106" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J106" t="n">
         <v>26.11</v>
@@ -8599,7 +8599,7 @@
         <v>2.84</v>
       </c>
       <c r="I107" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J107" t="n">
         <v>26.03</v>
@@ -8674,7 +8674,7 @@
         <v>-0.39</v>
       </c>
       <c r="I108" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J108" t="n">
         <v>25.99</v>
@@ -8749,7 +8749,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J109" t="n">
         <v>26.02</v>
@@ -8824,7 +8824,7 @@
         <v>4.54</v>
       </c>
       <c r="I110" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J110" t="n">
         <v>26.13</v>
@@ -8899,7 +8899,7 @@
         <v>0.51</v>
       </c>
       <c r="I111" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J111" t="n">
         <v>26.24</v>
@@ -8974,7 +8974,7 @@
         <v>-6.98</v>
       </c>
       <c r="I112" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J112" t="n">
         <v>26.24</v>
@@ -9049,7 +9049,7 @@
         <v>0.59</v>
       </c>
       <c r="I113" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J113" t="n">
         <v>26.24</v>
@@ -9124,7 +9124,7 @@
         <v>-4.65</v>
       </c>
       <c r="I114" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J114" t="n">
         <v>26.24</v>
@@ -9203,7 +9203,7 @@
         <v>-1.68</v>
       </c>
       <c r="I115" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J115" t="n">
         <v>26.24</v>
@@ -9278,7 +9278,7 @@
         <v>-1.75</v>
       </c>
       <c r="I116" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J116" t="n">
         <v>26.23</v>
@@ -9353,7 +9353,7 @@
         <v>8.25</v>
       </c>
       <c r="I117" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J117" t="n">
         <v>26.32</v>
@@ -9428,7 +9428,7 @@
         <v>-0.55</v>
       </c>
       <c r="I118" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J118" t="n">
         <v>26.34</v>
@@ -9503,7 +9503,7 @@
         <v>2.35</v>
       </c>
       <c r="I119" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J119" t="n">
         <v>26.38</v>
@@ -9578,7 +9578,7 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J120" t="n">
         <v>26.41</v>
@@ -9653,7 +9653,7 @@
         <v>1.24</v>
       </c>
       <c r="I121" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J121" t="n">
         <v>26.59</v>
@@ -9728,7 +9728,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="I122" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J122" t="n">
         <v>26.69</v>
@@ -9807,7 +9807,7 @@
         <v>-3.04</v>
       </c>
       <c r="I123" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J123" t="n">
         <v>26.7</v>
@@ -9886,7 +9886,7 @@
         <v>-1.35</v>
       </c>
       <c r="I124" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J124" t="n">
         <v>26.72</v>
@@ -9961,7 +9961,7 @@
         <v>2.97</v>
       </c>
       <c r="I125" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J125" t="n">
         <v>26.8</v>
@@ -10036,7 +10036,7 @@
         <v>3.08</v>
       </c>
       <c r="I126" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J126" t="n">
         <v>26.87</v>
@@ -10111,7 +10111,7 @@
         <v>2.38</v>
       </c>
       <c r="I127" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J127" t="n">
         <v>26.94</v>
@@ -10186,7 +10186,7 @@
         <v>0.37</v>
       </c>
       <c r="I128" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J128" t="n">
         <v>27.02</v>
@@ -10261,7 +10261,7 @@
         <v>5.23</v>
       </c>
       <c r="I129" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J129" t="n">
         <v>27.05</v>
@@ -10336,7 +10336,7 @@
         <v>2</v>
       </c>
       <c r="I130" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J130" t="n">
         <v>27.05</v>
@@ -10411,7 +10411,7 @@
         <v>0.45</v>
       </c>
       <c r="I131" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J131" t="n">
         <v>27.04</v>
@@ -10486,7 +10486,7 @@
         <v>2.39</v>
       </c>
       <c r="I132" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J132" t="n">
         <v>27.17</v>
@@ -10561,7 +10561,7 @@
         <v>1.6</v>
       </c>
       <c r="I133" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J133" t="n">
         <v>27.32</v>
@@ -10636,7 +10636,7 @@
         <v>-0.03</v>
       </c>
       <c r="I134" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J134" t="n">
         <v>27.53</v>
@@ -10711,7 +10711,7 @@
         <v>10.41</v>
       </c>
       <c r="I135" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J135" t="n">
         <v>27.92</v>
@@ -10786,7 +10786,7 @@
         <v>-1.84</v>
       </c>
       <c r="I136" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J136" t="n">
         <v>28.3</v>
@@ -10861,7 +10861,7 @@
         <v>4.27</v>
       </c>
       <c r="I137" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J137" t="n">
         <v>28.65</v>
@@ -10936,7 +10936,7 @@
         <v>-0.35</v>
       </c>
       <c r="I138" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J138" t="n">
         <v>29</v>
@@ -11011,7 +11011,7 @@
         <v>-0.29</v>
       </c>
       <c r="I139" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J139" t="n">
         <v>29.32</v>
@@ -11086,7 +11086,7 @@
         <v>-1.02</v>
       </c>
       <c r="I140" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J140" t="n">
         <v>29.6</v>
@@ -11161,7 +11161,7 @@
         <v>0.5</v>
       </c>
       <c r="I141" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J141" t="n">
         <v>29.88</v>
@@ -11236,7 +11236,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J142" t="n">
         <v>30.28</v>
@@ -11311,7 +11311,7 @@
         <v>2.41</v>
       </c>
       <c r="I143" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J143" t="n">
         <v>30.75</v>
@@ -11386,7 +11386,7 @@
         <v>5.8</v>
       </c>
       <c r="I144" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J144" t="n">
         <v>31.35</v>
@@ -11461,7 +11461,7 @@
         <v>6</v>
       </c>
       <c r="I145" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J145" t="n">
         <v>32.02</v>
@@ -11536,7 +11536,7 @@
         <v>-2.18</v>
       </c>
       <c r="I146" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J146" t="n">
         <v>32.61</v>
@@ -11611,7 +11611,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="I147" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J147" t="n">
         <v>33.34</v>
@@ -11686,7 +11686,7 @@
         <v>-6.91</v>
       </c>
       <c r="I148" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J148" t="n">
         <v>33.93</v>
@@ -11761,7 +11761,7 @@
         <v>10.18</v>
       </c>
       <c r="I149" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J149" t="n">
         <v>34.64</v>
@@ -11836,7 +11836,7 @@
         <v>-1.26</v>
       </c>
       <c r="I150" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J150" t="n">
         <v>35.29</v>
@@ -11911,7 +11911,7 @@
         <v>-19</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>35.53</v>
@@ -11990,7 +11990,7 @@
         <v>14.39</v>
       </c>
       <c r="I152" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J152" t="n">
         <v>35.99</v>
@@ -12065,7 +12065,7 @@
         <v>-6.39</v>
       </c>
       <c r="I153" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J153" t="n">
         <v>36.3</v>
@@ -12140,7 +12140,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="I154" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J154" t="n">
         <v>36.78</v>
@@ -12215,7 +12215,7 @@
         <v>1.48</v>
       </c>
       <c r="I155" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J155" t="n">
         <v>37.12</v>
@@ -12290,7 +12290,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J156" t="n">
         <v>37.48</v>
@@ -12365,7 +12365,7 @@
         <v>4.84</v>
       </c>
       <c r="I157" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J157" t="n">
         <v>37.88</v>
@@ -12440,7 +12440,7 @@
         <v>-1.73</v>
       </c>
       <c r="I158" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J158" t="n">
         <v>38.24</v>
@@ -12515,7 +12515,7 @@
         <v>-7.52</v>
       </c>
       <c r="I159" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J159" t="n">
         <v>38.44</v>
@@ -12594,7 +12594,7 @@
         <v>7.25</v>
       </c>
       <c r="I160" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J160" t="n">
         <v>38.81</v>
@@ -12669,7 +12669,7 @@
         <v>4.79</v>
       </c>
       <c r="I161" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J161" t="n">
         <v>39.27</v>
@@ -12744,7 +12744,7 @@
         <v>8.58</v>
       </c>
       <c r="I162" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J162" t="n">
         <v>39.91</v>
@@ -12819,7 +12819,7 @@
         <v>0.26</v>
       </c>
       <c r="I163" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J163" t="n">
         <v>40.51</v>
@@ -12894,7 +12894,7 @@
         <v>5.16</v>
       </c>
       <c r="I164" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J164" t="n">
         <v>41.14</v>
@@ -12969,7 +12969,7 @@
         <v>-4.03</v>
       </c>
       <c r="I165" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J165" t="n">
         <v>41.55</v>
@@ -13044,7 +13044,7 @@
         <v>0.82</v>
       </c>
       <c r="I166" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J166" t="n">
         <v>42.03</v>
@@ -13119,7 +13119,7 @@
         <v>1.68</v>
       </c>
       <c r="I167" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J167" t="n">
         <v>42.37</v>
@@ -13194,7 +13194,7 @@
         <v>-11.91</v>
       </c>
       <c r="I168" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J168" t="n">
         <v>42.57</v>
@@ -13269,7 +13269,7 @@
         <v>9.42</v>
       </c>
       <c r="I169" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J169" t="n">
         <v>42.77</v>
@@ -13344,7 +13344,7 @@
         <v>-8.16</v>
       </c>
       <c r="I170" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J170" t="n">
         <v>42.81</v>
@@ -13419,7 +13419,7 @@
         <v>-2.95</v>
       </c>
       <c r="I171" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J171" t="n">
         <v>43.19</v>
@@ -13498,7 +13498,7 @@
         <v>7.72</v>
       </c>
       <c r="I172" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J172" t="n">
         <v>43.48</v>
@@ -13573,7 +13573,7 @@
         <v>-7.01</v>
       </c>
       <c r="I173" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J173" t="n">
         <v>43.74</v>
@@ -13652,7 +13652,7 @@
         <v>4.55</v>
       </c>
       <c r="I174" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J174" t="n">
         <v>43.92</v>
@@ -13727,7 +13727,7 @@
         <v>-10.28</v>
       </c>
       <c r="I175" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J175" t="n">
         <v>43.86</v>
@@ -13802,7 +13802,7 @@
         <v>-0.92</v>
       </c>
       <c r="I176" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J176" t="n">
         <v>43.79</v>
@@ -13877,7 +13877,7 @@
         <v>-5.18</v>
       </c>
       <c r="I177" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J177" t="n">
         <v>43.52</v>
@@ -13952,7 +13952,7 @@
         <v>-6.76</v>
       </c>
       <c r="I178" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J178" t="n">
         <v>43.16</v>
@@ -14031,7 +14031,7 @@
         <v>4.69</v>
       </c>
       <c r="I179" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J179" t="n">
         <v>43.04</v>
@@ -14106,7 +14106,7 @@
         <v>-14.33</v>
       </c>
       <c r="I180" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J180" t="n">
         <v>42.52</v>
@@ -14189,7 +14189,7 @@
         <v>2.99</v>
       </c>
       <c r="I181" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J181" t="n">
         <v>41.95</v>
@@ -14264,7 +14264,7 @@
         <v>13.02</v>
       </c>
       <c r="I182" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J182" t="n">
         <v>41.4</v>
@@ -14339,7 +14339,7 @@
         <v>0.86</v>
       </c>
       <c r="I183" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J183" t="n">
         <v>40.86</v>
@@ -14414,7 +14414,7 @@
         <v>8.33</v>
       </c>
       <c r="I184" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J184" t="n">
         <v>40.35</v>
@@ -14489,7 +14489,7 @@
         <v>5.29</v>
       </c>
       <c r="I185" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J185" t="n">
         <v>40.05</v>
@@ -14564,7 +14564,7 @@
         <v>0.12</v>
       </c>
       <c r="I186" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J186" t="n">
         <v>39.72</v>
@@ -14639,7 +14639,7 @@
         <v>6.03</v>
       </c>
       <c r="I187" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J187" t="n">
         <v>39.48</v>
@@ -14714,7 +14714,7 @@
         <v>6.35</v>
       </c>
       <c r="I188" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J188" t="n">
         <v>39.67</v>
@@ -14789,7 +14789,7 @@
         <v>-3.05</v>
       </c>
       <c r="I189" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J189" t="n">
         <v>39.59</v>
@@ -14864,7 +14864,7 @@
         <v>2.97</v>
       </c>
       <c r="I190" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J190" t="n">
         <v>39.76</v>
@@ -14939,7 +14939,7 @@
         <v>3.21</v>
       </c>
       <c r="I191" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J191" t="n">
         <v>40.08</v>
@@ -15014,7 +15014,7 @@
         <v>-0.42</v>
       </c>
       <c r="I192" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J192" t="n">
         <v>40.22</v>
@@ -15089,7 +15089,7 @@
         <v>3.89</v>
       </c>
       <c r="I193" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J193" t="n">
         <v>40.61</v>
@@ -15164,7 +15164,7 @@
         <v>-1.73</v>
       </c>
       <c r="I194" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J194" t="n">
         <v>40.86</v>
@@ -15239,7 +15239,7 @@
         <v>-14.52</v>
       </c>
       <c r="I195" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>40.99</v>
@@ -15314,7 +15314,7 @@
         <v>-1.27</v>
       </c>
       <c r="I196" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J196" t="n">
         <v>41.1</v>
@@ -15389,7 +15389,7 @@
         <v>-1.68</v>
       </c>
       <c r="I197" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J197" t="n">
         <v>41.29</v>
@@ -15468,7 +15468,7 @@
         <v>-11.05</v>
       </c>
       <c r="I198" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J198" t="n">
         <v>41.37</v>
@@ -15543,7 +15543,7 @@
         <v>7.11</v>
       </c>
       <c r="I199" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J199" t="n">
         <v>41.5</v>
@@ -15618,7 +15618,7 @@
         <v>8.15</v>
       </c>
       <c r="I200" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J200" t="n">
         <v>42.05</v>
@@ -15693,7 +15693,7 @@
         <v>3.69</v>
       </c>
       <c r="I201" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J201" t="n">
         <v>42.62</v>
@@ -15768,7 +15768,7 @@
         <v>1.02</v>
       </c>
       <c r="I202" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J202" t="n">
         <v>43.01</v>
@@ -15843,7 +15843,7 @@
         <v>1.17</v>
       </c>
       <c r="I203" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J203" t="n">
         <v>43.41</v>
@@ -15918,7 +15918,7 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J204" t="n">
         <v>43.67</v>
@@ -15993,7 +15993,7 @@
         <v>-0.88</v>
       </c>
       <c r="I205" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J205" t="n">
         <v>43.79</v>
@@ -16068,7 +16068,7 @@
         <v>-0.34</v>
       </c>
       <c r="I206" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J206" t="n">
         <v>43.91</v>
@@ -16147,7 +16147,7 @@
         <v>-3.76</v>
       </c>
       <c r="I207" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J207" t="n">
         <v>43.82</v>
@@ -16222,7 +16222,7 @@
         <v>12.4</v>
       </c>
       <c r="I208" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J208" t="n">
         <v>43.86</v>
@@ -16297,7 +16297,7 @@
         <v>4.19</v>
       </c>
       <c r="I209" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J209" t="n">
         <v>44.06</v>
@@ -16372,7 +16372,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J210" t="n">
         <v>44.43</v>
@@ -16447,7 +16447,7 @@
         <v>-3.17</v>
       </c>
       <c r="I211" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J211" t="n">
         <v>44.65</v>
@@ -16522,7 +16522,7 @@
         <v>-5.05</v>
       </c>
       <c r="I212" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J212" t="n">
         <v>44.74</v>
@@ -16597,7 +16597,7 @@
         <v>8.65</v>
       </c>
       <c r="I213" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J213" t="n">
         <v>44.96</v>
@@ -16672,7 +16672,7 @@
         <v>1.3</v>
       </c>
       <c r="I214" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J214" t="n">
         <v>45.25</v>
@@ -16747,7 +16747,7 @@
         <v>2.6</v>
       </c>
       <c r="I215" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J215" t="n">
         <v>45.97</v>
@@ -16822,7 +16822,7 @@
         <v>-1.23</v>
       </c>
       <c r="I216" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J216" t="n">
         <v>46.68</v>
@@ -16897,7 +16897,7 @@
         <v>4.88</v>
       </c>
       <c r="I217" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J217" t="n">
         <v>47.56</v>
@@ -16972,7 +16972,7 @@
         <v>4.6</v>
       </c>
       <c r="I218" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J218" t="n">
         <v>48.79</v>
@@ -17047,7 +17047,7 @@
         <v>-4.63</v>
       </c>
       <c r="I219" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J219" t="n">
         <v>49.76</v>
@@ -17122,7 +17122,7 @@
         <v>9.57</v>
       </c>
       <c r="I220" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J220" t="n">
         <v>50.85</v>
@@ -17197,7 +17197,7 @@
         <v>0.38</v>
       </c>
       <c r="I221" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J221" t="n">
         <v>51.87</v>
@@ -17272,7 +17272,7 @@
         <v>-3.33</v>
       </c>
       <c r="I222" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J222" t="n">
         <v>52.76</v>
@@ -17347,7 +17347,7 @@
         <v>-1.46</v>
       </c>
       <c r="I223" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J223" t="n">
         <v>53.59</v>
@@ -17422,7 +17422,7 @@
         <v>7.02</v>
       </c>
       <c r="I224" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J224" t="n">
         <v>54.62</v>
@@ -17497,7 +17497,7 @@
         <v>7.89</v>
       </c>
       <c r="I225" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J225" t="n">
         <v>55.94</v>
@@ -17572,7 +17572,7 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J226" t="n">
         <v>57.28</v>
@@ -17647,7 +17647,7 @@
         <v>-12.31</v>
       </c>
       <c r="I227" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J227" t="n">
         <v>58.26</v>
@@ -17722,7 +17722,7 @@
         <v>5.52</v>
       </c>
       <c r="I228" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J228" t="n">
         <v>59.16</v>
@@ -17797,7 +17797,7 @@
         <v>-6.14</v>
       </c>
       <c r="I229" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J229" t="n">
         <v>59.76</v>
@@ -17872,7 +17872,7 @@
         <v>-13.08</v>
       </c>
       <c r="I230" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J230" t="n">
         <v>59.72</v>
@@ -17951,7 +17951,7 @@
         <v>0.11</v>
       </c>
       <c r="I231" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J231" t="n">
         <v>59.77</v>
@@ -18026,7 +18026,7 @@
         <v>15.95</v>
       </c>
       <c r="I232" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J232" t="n">
         <v>60.37</v>
@@ -18101,7 +18101,7 @@
         <v>3.69</v>
       </c>
       <c r="I233" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J233" t="n">
         <v>60.88</v>
@@ -18176,7 +18176,7 @@
         <v>-1.08</v>
       </c>
       <c r="I234" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J234" t="n">
         <v>61.31</v>
@@ -18251,7 +18251,7 @@
         <v>7.44</v>
       </c>
       <c r="I235" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J235" t="n">
         <v>61.91</v>
@@ -18326,7 +18326,7 @@
         <v>-7.28</v>
       </c>
       <c r="I236" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J236" t="n">
         <v>62.29</v>
@@ -18401,7 +18401,7 @@
         <v>2.36</v>
       </c>
       <c r="I237" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J237" t="n">
         <v>62.62</v>
@@ -18476,7 +18476,7 @@
         <v>-0.37</v>
       </c>
       <c r="I238" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J238" t="n">
         <v>62.8</v>
@@ -18551,7 +18551,7 @@
         <v>3.02</v>
       </c>
       <c r="I239" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J239" t="n">
         <v>63.22</v>
@@ -18626,7 +18626,7 @@
         <v>-1.6</v>
       </c>
       <c r="I240" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J240" t="n">
         <v>63.31</v>
@@ -18701,7 +18701,7 @@
         <v>2.88</v>
       </c>
       <c r="I241" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J241" t="n">
         <v>63.47</v>
@@ -18776,7 +18776,7 @@
         <v>-1.86</v>
       </c>
       <c r="I242" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J242" t="n">
         <v>63.69</v>
@@ -18851,7 +18851,7 @@
         <v>4.06</v>
       </c>
       <c r="I243" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J243" t="n">
         <v>64.08</v>
@@ -18926,7 +18926,7 @@
         <v>4.85</v>
       </c>
       <c r="I244" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J244" t="n">
         <v>64.42</v>
@@ -19001,7 +19001,7 @@
         <v>-9.07</v>
       </c>
       <c r="I245" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J245" t="n">
         <v>64.19</v>
@@ -19076,7 +19076,7 @@
         <v>-3.94</v>
       </c>
       <c r="I246" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J246" t="n">
         <v>63.8</v>
@@ -19155,7 +19155,7 @@
         <v>-0.02</v>
       </c>
       <c r="I247" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J247" t="n">
         <v>63.85</v>
@@ -19230,7 +19230,7 @@
         <v>-14.89</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>63.26</v>
@@ -19309,7 +19309,7 @@
         <v>5.99</v>
       </c>
       <c r="I249" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J249" t="n">
         <v>63.03</v>
@@ -19384,7 +19384,7 @@
         <v>-3.22</v>
       </c>
       <c r="I250" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J250" t="n">
         <v>63.11</v>
@@ -19463,7 +19463,7 @@
         <v>-12.6</v>
       </c>
       <c r="I251" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J251" t="n">
         <v>62.84</v>
@@ -19542,7 +19542,7 @@
         <v>11.35</v>
       </c>
       <c r="I252" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J252" t="n">
         <v>62.42</v>
@@ -19617,7 +19617,7 @@
         <v>2.36</v>
       </c>
       <c r="I253" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J253" t="n">
         <v>61.95</v>
@@ -19692,7 +19692,7 @@
         <v>2.75</v>
       </c>
       <c r="I254" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J254" t="n">
         <v>61.59</v>
@@ -19767,7 +19767,7 @@
         <v>-10.35</v>
       </c>
       <c r="I255" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J255" t="n">
         <v>60.7</v>
@@ -19840,7 +19840,7 @@
         <v>0.88</v>
       </c>
       <c r="I256" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J256" t="n">
         <v>60.08</v>
@@ -19919,7 +19919,7 @@
         <v>5.84</v>
       </c>
       <c r="I257" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J257" t="n">
         <v>59.54</v>
@@ -19994,7 +19994,7 @@
         <v>2.35</v>
       </c>
       <c r="I258" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J258" t="n">
         <v>59.07</v>
@@ -20069,7 +20069,7 @@
         <v>-1.69</v>
       </c>
       <c r="I259" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J259" t="n">
         <v>58.45</v>
@@ -20144,7 +20144,7 @@
         <v>1.54</v>
       </c>
       <c r="I260" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J260" t="n">
         <v>57.93</v>
@@ -20219,7 +20219,7 @@
         <v>-6.75</v>
       </c>
       <c r="I261" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J261" t="n">
         <v>57.14</v>
@@ -20298,7 +20298,7 @@
         <v>3.7</v>
       </c>
       <c r="I262" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J262" t="n">
         <v>56.5</v>
@@ -20373,7 +20373,7 @@
         <v>3.62</v>
       </c>
       <c r="I263" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J263" t="n">
         <v>55.82</v>
@@ -20448,7 +20448,7 @@
         <v>3.79</v>
       </c>
       <c r="I264" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J264" t="n">
         <v>55.08</v>
@@ -20523,7 +20523,7 @@
         <v>-14.14</v>
       </c>
       <c r="I265" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J265" t="n">
         <v>54.26</v>
@@ -20602,7 +20602,7 @@
         <v>-4.82</v>
       </c>
       <c r="I266" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J266" t="n">
         <v>53.45</v>
@@ -20681,7 +20681,7 @@
         <v>-12.86</v>
       </c>
       <c r="I267" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J267" t="n">
         <v>52.34</v>
@@ -20756,7 +20756,7 @@
         <v>17.96</v>
       </c>
       <c r="I268" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J268" t="n">
         <v>52.07</v>
@@ -20831,7 +20831,7 @@
         <v>9.09</v>
       </c>
       <c r="I269" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J269" t="n">
         <v>51.85</v>
@@ -20906,7 +20906,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J270" t="n">
         <v>51.75</v>
@@ -20981,7 +20981,7 @@
         <v>3.89</v>
       </c>
       <c r="I271" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J271" t="n">
         <v>52.1</v>
@@ -21056,7 +21056,7 @@
         <v>3.18</v>
       </c>
       <c r="I272" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J272" t="n">
         <v>52.26</v>
@@ -21135,7 +21135,7 @@
         <v>19.38</v>
       </c>
       <c r="I273" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J273" t="n">
         <v>52.9</v>
@@ -21210,7 +21210,7 @@
         <v>6.63</v>
       </c>
       <c r="I274" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J274" t="n">
         <v>53.7</v>
@@ -21285,7 +21285,7 @@
         <v>6.13</v>
       </c>
       <c r="I275" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J275" t="n">
         <v>55</v>
@@ -21360,7 +21360,7 @@
         <v>5.46</v>
       </c>
       <c r="I276" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J276" t="n">
         <v>56.49</v>
@@ -21435,7 +21435,7 @@
         <v>5.89</v>
       </c>
       <c r="I277" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J277" t="n">
         <v>58.07</v>
@@ -21510,7 +21510,7 @@
         <v>0.76</v>
       </c>
       <c r="I278" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J278" t="n">
         <v>59.62</v>
@@ -21585,7 +21585,7 @@
         <v>2.81</v>
       </c>
       <c r="I279" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J279" t="n">
         <v>61.34</v>
@@ -21660,7 +21660,7 @@
         <v>7.15</v>
       </c>
       <c r="I280" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J280" t="n">
         <v>63.33</v>
@@ -21735,7 +21735,7 @@
         <v>1.33</v>
       </c>
       <c r="I281" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J281" t="n">
         <v>65.56999999999999</v>
@@ -21810,7 +21810,7 @@
         <v>2.24</v>
       </c>
       <c r="I282" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J282" t="n">
         <v>67.81999999999999</v>
@@ -21885,7 +21885,7 @@
         <v>7.69</v>
       </c>
       <c r="I283" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J283" t="n">
         <v>70.34999999999999</v>
@@ -21960,7 +21960,7 @@
         <v>6.75</v>
       </c>
       <c r="I284" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J284" t="n">
         <v>73.14</v>
@@ -22035,7 +22035,7 @@
         <v>13.79</v>
       </c>
       <c r="I285" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J285" t="n">
         <v>77.09999999999999</v>
@@ -22110,7 +22110,7 @@
         <v>-3.84</v>
       </c>
       <c r="I286" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J286" t="n">
         <v>80.94</v>
@@ -22185,7 +22185,7 @@
         <v>-11.21</v>
       </c>
       <c r="I287" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J287" t="n">
         <v>84.38</v>
@@ -22260,7 +22260,7 @@
         <v>7.67</v>
       </c>
       <c r="I288" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J288" t="n">
         <v>87.88</v>
@@ -22335,7 +22335,7 @@
         <v>7.64</v>
       </c>
       <c r="I289" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J289" t="n">
         <v>91.62</v>
@@ -22410,7 +22410,7 @@
         <v>2.69</v>
       </c>
       <c r="I290" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J290" t="n">
         <v>95.5</v>
@@ -22485,7 +22485,7 @@
         <v>-2.18</v>
       </c>
       <c r="I291" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J291" t="n">
         <v>99.13</v>
@@ -22560,7 +22560,7 @@
         <v>13.02</v>
       </c>
       <c r="I292" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J292" t="n">
         <v>103.51</v>
@@ -22635,7 +22635,7 @@
         <v>15.04</v>
       </c>
       <c r="I293" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J293" t="n">
         <v>108.42</v>
@@ -22710,7 +22710,7 @@
         <v>-8.289999999999999</v>
       </c>
       <c r="I294" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J294" t="n">
         <v>112.43</v>
@@ -22785,7 +22785,7 @@
         <v>16.33</v>
       </c>
       <c r="I295" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J295" t="n">
         <v>117.45</v>
@@ -22860,7 +22860,7 @@
         <v>7.62</v>
       </c>
       <c r="I296" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J296" t="n">
         <v>122.94</v>
@@ -22935,7 +22935,7 @@
         <v>-9.4</v>
       </c>
       <c r="I297" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J297" t="n">
         <v>127.3</v>
@@ -23010,7 +23010,7 @@
         <v>6.79</v>
       </c>
       <c r="I298" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J298" t="n">
         <v>132.21</v>
@@ -23085,7 +23085,7 @@
         <v>1.06</v>
       </c>
       <c r="I299" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J299" t="n">
         <v>137.1</v>
@@ -23160,7 +23160,7 @@
         <v>-11.82</v>
       </c>
       <c r="I300" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J300" t="n">
         <v>140.57</v>
@@ -23235,7 +23235,7 @@
         <v>-7.57</v>
       </c>
       <c r="I301" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J301" t="n">
         <v>143.36</v>
@@ -23310,7 +23310,7 @@
         <v>0.09</v>
       </c>
       <c r="I302" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J302" t="n">
         <v>146.05</v>
@@ -23385,7 +23385,7 @@
         <v>14.03</v>
       </c>
       <c r="I303" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J303" t="n">
         <v>149.42</v>
@@ -23460,7 +23460,7 @@
         <v>2.99</v>
       </c>
       <c r="I304" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J304" t="n">
         <v>152.7</v>
@@ -23535,7 +23535,7 @@
         <v>6.83</v>
       </c>
       <c r="I305" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J305" t="n">
         <v>155.81</v>
@@ -23610,7 +23610,7 @@
         <v>18.48</v>
       </c>
       <c r="I306" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J306" t="n">
         <v>160.93</v>
@@ -23685,7 +23685,7 @@
         <v>-3.46</v>
       </c>
       <c r="I307" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J307" t="n">
         <v>166.34</v>
@@ -23760,7 +23760,7 @@
         <v>3.05</v>
       </c>
       <c r="I308" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J308" t="n">
         <v>171.67</v>
@@ -23835,7 +23835,7 @@
         <v>-0.13</v>
       </c>
       <c r="I309" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J309" t="n">
         <v>176.54</v>
@@ -23910,7 +23910,7 @@
         <v>1.2</v>
       </c>
       <c r="I310" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J310" t="n">
         <v>181.37</v>
@@ -23985,7 +23985,7 @@
         <v>17.31</v>
       </c>
       <c r="I311" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J311" t="n">
         <v>188.3</v>
@@ -24060,7 +24060,7 @@
         <v>5.34</v>
       </c>
       <c r="I312" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J312" t="n">
         <v>195.12</v>
@@ -24135,7 +24135,7 @@
         <v>-6.36</v>
       </c>
       <c r="I313" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J313" t="n">
         <v>199.96</v>
@@ -24210,7 +24210,7 @@
         <v>-30.51</v>
       </c>
       <c r="I314" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J314" s="4" t="n">
         <v>201.48</v>
@@ -24289,7 +24289,7 @@
         <v>15.83</v>
       </c>
       <c r="I315" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J315" t="n">
         <v>203.2</v>
@@ -24364,7 +24364,7 @@
         <v>-4.61</v>
       </c>
       <c r="I316" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J316" t="n">
         <v>203.76</v>
@@ -24443,7 +24443,7 @@
         <v>-10.43</v>
       </c>
       <c r="I317" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J317" t="n">
         <v>204.17</v>
@@ -24518,7 +24518,7 @@
         <v>23.99</v>
       </c>
       <c r="I318" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J318" t="n">
         <v>206.15</v>
@@ -24593,7 +24593,7 @@
         <v>4.78</v>
       </c>
       <c r="I319" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J319" t="n">
         <v>208.58</v>
@@ -24668,7 +24668,7 @@
         <v>16.11</v>
       </c>
       <c r="I320" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J320" t="n">
         <v>213.99</v>
@@ -24743,7 +24743,7 @@
         <v>-16.99</v>
       </c>
       <c r="I321" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J321" s="4" t="n">
         <v>217.71</v>
@@ -24818,7 +24818,7 @@
         <v>3.39</v>
       </c>
       <c r="I322" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J322" t="n">
         <v>221.81</v>
@@ -24893,7 +24893,7 @@
         <v>19.43</v>
       </c>
       <c r="I323" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J323" t="n">
         <v>227.11</v>
@@ -24968,7 +24968,7 @@
         <v>7.69</v>
       </c>
       <c r="I324" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J324" t="n">
         <v>233.22</v>
@@ -25043,7 +25043,7 @@
         <v>-23.06</v>
       </c>
       <c r="I325" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J325" s="4" t="n">
         <v>235.26</v>
@@ -25122,7 +25122,7 @@
         <v>-0.8</v>
       </c>
       <c r="I326" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J326" t="n">
         <v>235.45</v>
@@ -25197,7 +25197,7 @@
         <v>10.03</v>
       </c>
       <c r="I327" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J327" t="n">
         <v>237.18</v>
@@ -25272,7 +25272,7 @@
         <v>-14.65</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J328" s="4" t="n">
         <v>236.73</v>
@@ -25351,7 +25351,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I329" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J329" t="n">
         <v>237.34</v>
@@ -25426,7 +25426,7 @@
         <v>12.76</v>
       </c>
       <c r="I330" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J330" t="n">
         <v>239.32</v>
@@ -25501,7 +25501,7 @@
         <v>-18.43</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>236.89</v>
@@ -25580,7 +25580,7 @@
         <v>-16.59</v>
       </c>
       <c r="I332" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J332" s="4" t="n">
         <v>231.94</v>
@@ -25655,7 +25655,7 @@
         <v>7.26</v>
       </c>
       <c r="I333" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J333" t="n">
         <v>228.54</v>
@@ -25730,7 +25730,7 @@
         <v>-15.09</v>
       </c>
       <c r="I334" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J334" s="4" t="n">
         <v>227.67</v>
@@ -25809,7 +25809,7 @@
         <v>5.78</v>
       </c>
       <c r="I335" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J335" t="n">
         <v>225.84</v>
@@ -25884,7 +25884,7 @@
         <v>10.08</v>
       </c>
       <c r="I336" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J336" t="n">
         <v>225.38</v>
@@ -25959,7 +25959,7 @@
         <v>-0.1</v>
       </c>
       <c r="I337" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J337" t="n">
         <v>225.96</v>
@@ -26034,7 +26034,7 @@
         <v>-13.99</v>
       </c>
       <c r="I338" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J338" t="n">
         <v>223.03</v>
@@ -26113,7 +26113,7 @@
         <v>6.83</v>
       </c>
       <c r="I339" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J339" t="n">
         <v>220.13</v>
@@ -26188,7 +26188,7 @@
         <v>-6.29</v>
       </c>
       <c r="I340" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J340" t="n">
         <v>214.79</v>
@@ -26263,7 +26263,7 @@
         <v>-13.93</v>
       </c>
       <c r="I341" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J341" t="n">
         <v>210.61</v>
@@ -26338,7 +26338,7 @@
         <v>-4.92</v>
       </c>
       <c r="I342" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J342" t="n">
         <v>205.69</v>
@@ -26413,7 +26413,7 @@
         <v>0.99</v>
       </c>
       <c r="I343" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J343" t="n">
         <v>198.57</v>
@@ -26488,7 +26488,7 @@
         <v>15.89</v>
       </c>
       <c r="I344" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J344" t="n">
         <v>191.46</v>
@@ -26563,7 +26563,7 @@
         <v>1.54</v>
       </c>
       <c r="I345" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J345" t="n">
         <v>187.94</v>
@@ -26638,7 +26638,7 @@
         <v>-2.16</v>
       </c>
       <c r="I346" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J346" t="n">
         <v>184.34</v>
@@ -26713,7 +26713,7 @@
         <v>-13.14</v>
       </c>
       <c r="I347" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J347" t="n">
         <v>178.56</v>
@@ -26788,7 +26788,7 @@
         <v>-6.33</v>
       </c>
       <c r="I348" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J348" t="n">
         <v>174.19</v>
@@ -26867,7 +26867,7 @@
         <v>-14.52</v>
       </c>
       <c r="I349" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>167.84</v>
@@ -26942,7 +26942,7 @@
         <v>-16.02</v>
       </c>
       <c r="I350" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>159.11</v>
@@ -27021,7 +27021,7 @@
         <v>24.7</v>
       </c>
       <c r="I351" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J351" t="n">
         <v>153.97</v>
@@ -27096,7 +27096,7 @@
         <v>0</v>
       </c>
       <c r="I352" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J352" t="n">
         <v>150.64</v>
@@ -27171,7 +27171,7 @@
         <v>1.74</v>
       </c>
       <c r="I353" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J353" t="n">
         <v>146.74</v>
@@ -27246,7 +27246,7 @@
         <v>19.87</v>
       </c>
       <c r="I354" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J354" t="n">
         <v>145.48</v>
@@ -27321,7 +27321,7 @@
         <v>-5.6</v>
       </c>
       <c r="I355" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J355" t="n">
         <v>143.34</v>
@@ -27400,7 +27400,7 @@
         <v>0.2</v>
       </c>
       <c r="I356" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J356" t="n">
         <v>140.34</v>
@@ -27475,7 +27475,7 @@
         <v>5.99</v>
       </c>
       <c r="I357" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J357" t="n">
         <v>137.74</v>
@@ -27550,7 +27550,7 @@
         <v>-7.31</v>
       </c>
       <c r="I358" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J358" t="n">
         <v>135.97</v>
@@ -27629,7 +27629,7 @@
         <v>2.31</v>
       </c>
       <c r="I359" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J359" t="n">
         <v>133.79</v>
@@ -27704,7 +27704,7 @@
         <v>6.89</v>
       </c>
       <c r="I360" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J360" t="n">
         <v>132.62</v>
@@ -27779,7 +27779,7 @@
         <v>2.25</v>
       </c>
       <c r="I361" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J361" t="n">
         <v>132.76</v>
@@ -27854,7 +27854,7 @@
         <v>-0.28</v>
       </c>
       <c r="I362" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J362" t="n">
         <v>133.24</v>
@@ -27929,7 +27929,7 @@
         <v>4.54</v>
       </c>
       <c r="I363" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J363" t="n">
         <v>133.97</v>
@@ -28004,7 +28004,7 @@
         <v>-14.8</v>
       </c>
       <c r="I364" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J364" s="4" t="n">
         <v>132.5</v>
@@ -28083,7 +28083,7 @@
         <v>-6.48</v>
       </c>
       <c r="I365" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J365" t="n">
         <v>130.49</v>
@@ -28158,7 +28158,7 @@
         <v>1.22</v>
       </c>
       <c r="I366" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J366" t="n">
         <v>128.73</v>
@@ -28233,7 +28233,7 @@
         <v>-1.32</v>
       </c>
       <c r="I367" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J367" t="n">
         <v>127.92</v>
@@ -28308,7 +28308,7 @@
         <v>-7.82</v>
       </c>
       <c r="I368" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J368" t="n">
         <v>127.07</v>
@@ -28383,7 +28383,7 @@
         <v>4.05</v>
       </c>
       <c r="I369" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J369" t="n">
         <v>127.37</v>
@@ -28458,7 +28458,7 @@
         <v>0.8</v>
       </c>
       <c r="I370" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J370" t="n">
         <v>128.6</v>
@@ -28533,7 +28533,7 @@
         <v>5.54</v>
       </c>
       <c r="I371" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J371" t="n">
         <v>129.02</v>
@@ -28608,7 +28608,7 @@
         <v>-9.51</v>
       </c>
       <c r="I372" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J372" t="n">
         <v>128.85</v>
@@ -28683,7 +28683,7 @@
         <v>1.3</v>
       </c>
       <c r="I373" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J373" t="n">
         <v>128.66</v>
@@ -28758,7 +28758,7 @@
         <v>-6.1</v>
       </c>
       <c r="I374" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J374" t="n">
         <v>126.96</v>
@@ -28837,7 +28837,7 @@
         <v>0.42</v>
       </c>
       <c r="I375" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J375" t="n">
         <v>125.67</v>
@@ -28916,7 +28916,7 @@
         <v>0.37</v>
       </c>
       <c r="I376" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J376" t="n">
         <v>124.39</v>
@@ -28995,7 +28995,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="I377" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J377" t="n">
         <v>123.25</v>
@@ -29070,7 +29070,7 @@
         <v>5.11</v>
       </c>
       <c r="I378" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J378" t="n">
         <v>122.91</v>
@@ -29145,7 +29145,7 @@
         <v>2.11</v>
       </c>
       <c r="I379" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J379" t="n">
         <v>122.55</v>
@@ -29220,7 +29220,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="I380" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J380" t="n">
         <v>121.23</v>
@@ -29299,7 +29299,7 @@
         <v>5.24</v>
       </c>
       <c r="I381" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J381" t="n">
         <v>120.06</v>
@@ -29374,7 +29374,7 @@
         <v>-16.99</v>
       </c>
       <c r="I382" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J382" s="4" t="n">
         <v>117.87</v>
@@ -29453,7 +29453,7 @@
         <v>1.18</v>
       </c>
       <c r="I383" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J383" t="n">
         <v>115.41</v>
@@ -29528,7 +29528,7 @@
         <v>1.61</v>
       </c>
       <c r="I384" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J384" t="n">
         <v>114.15</v>
@@ -29603,7 +29603,7 @@
         <v>10.43</v>
       </c>
       <c r="I385" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J385" t="n">
         <v>113.86</v>
@@ -29678,7 +29678,7 @@
         <v>7.71</v>
       </c>
       <c r="I386" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J386" t="n">
         <v>113.93</v>
@@ -29753,7 +29753,7 @@
         <v>14.77</v>
       </c>
       <c r="I387" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J387" t="n">
         <v>115</v>
@@ -29828,7 +29828,7 @@
         <v>7.13</v>
       </c>
       <c r="I388" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J388" t="n">
         <v>117.04</v>
@@ -29903,7 +29903,7 @@
         <v>-3.75</v>
       </c>
       <c r="I389" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J389" t="n">
         <v>118.57</v>
@@ -29978,7 +29978,7 @@
         <v>0.05</v>
       </c>
       <c r="I390" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J390" t="n">
         <v>120.06</v>
@@ -30053,7 +30053,7 @@
         <v>3.5</v>
       </c>
       <c r="I391" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J391" t="n">
         <v>121.49</v>
@@ -30128,7 +30128,7 @@
         <v>-6.05</v>
       </c>
       <c r="I392" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J392" t="n">
         <v>123.04</v>
@@ -30203,7 +30203,7 @@
         <v>3.31</v>
       </c>
       <c r="I393" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J393" t="n">
         <v>124.75</v>
@@ -30278,7 +30278,7 @@
         <v>0.59</v>
       </c>
       <c r="I394" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J394" t="n">
         <v>126.85</v>
@@ -30353,7 +30353,7 @@
         <v>3.94</v>
       </c>
       <c r="I395" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J395" t="n">
         <v>129.22</v>
@@ -30428,7 +30428,7 @@
         <v>6.52</v>
       </c>
       <c r="I396" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J396" t="n">
         <v>132.08</v>
@@ -30503,7 +30503,7 @@
         <v>0.34</v>
       </c>
       <c r="I397" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J397" t="n">
         <v>134.43</v>
@@ -30578,7 +30578,7 @@
         <v>-0.01</v>
       </c>
       <c r="I398" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J398" t="n">
         <v>136.48</v>
@@ -30653,7 +30653,7 @@
         <v>-3.26</v>
       </c>
       <c r="I399" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J399" t="n">
         <v>138.14</v>
@@ -30732,7 +30732,7 @@
         <v>-10.31</v>
       </c>
       <c r="I400" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J400" t="n">
         <v>139.48</v>
@@ -30807,7 +30807,7 @@
         <v>-1.94</v>
       </c>
       <c r="I401" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J401" t="n">
         <v>140.38</v>
@@ -30886,7 +30886,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="I402" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J402" t="n">
         <v>141.75</v>
@@ -30965,7 +30965,7 @@
         <v>-0.65</v>
       </c>
       <c r="I403" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J403" t="n">
         <v>143.01</v>
@@ -31040,7 +31040,7 @@
         <v>-13.35</v>
       </c>
       <c r="I404" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J404" t="n">
         <v>143.35</v>
@@ -31115,7 +31115,7 @@
         <v>-2.89</v>
       </c>
       <c r="I405" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J405" t="n">
         <v>142.98</v>
@@ -31194,7 +31194,7 @@
         <v>-12.74</v>
       </c>
       <c r="I406" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J406" t="n">
         <v>141.48</v>
@@ -31273,7 +31273,7 @@
         <v>5.32</v>
       </c>
       <c r="I407" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J407" t="n">
         <v>139.32</v>
@@ -31352,7 +31352,7 @@
         <v>-1.12</v>
       </c>
       <c r="I408" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J408" t="n">
         <v>136.6</v>
@@ -31431,7 +31431,7 @@
         <v>5.83</v>
       </c>
       <c r="I409" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J409" t="n">
         <v>134.45</v>
@@ -31510,7 +31510,7 @@
         <v>-20.47</v>
       </c>
       <c r="I410" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>131.24</v>
@@ -31589,7 +31589,7 @@
         <v>1.77</v>
       </c>
       <c r="I411" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J411" t="n">
         <v>127.85</v>
@@ -31668,7 +31668,7 @@
         <v>8.31</v>
       </c>
       <c r="I412" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J412" t="n">
         <v>125.26</v>
@@ -31747,7 +31747,7 @@
         <v>11.69</v>
       </c>
       <c r="I413" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J413" t="n">
         <v>122.96</v>
@@ -31826,7 +31826,7 @@
         <v>6.2</v>
       </c>
       <c r="I414" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J414" t="n">
         <v>120.93</v>
@@ -31895,13 +31895,13 @@
         <v>102.39</v>
       </c>
       <c r="G415" t="n">
-        <v>94028800</v>
+        <v>98115000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-4.62</v>
       </c>
       <c r="I415" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J415" t="n">
         <v>118.37</v>
@@ -31964,37 +31964,37 @@
         <v>84.19</v>
       </c>
       <c r="E416" s="4" t="n">
-        <v>76.81</v>
+        <v>70.23</v>
       </c>
       <c r="F416" s="4" t="n">
-        <v>77.14</v>
+        <v>74.41</v>
       </c>
       <c r="G416" s="4" t="n">
-        <v>84356090</v>
+        <v>179962967</v>
       </c>
       <c r="H416" s="5" t="n">
-        <v>-24.66</v>
+        <v>-27.33</v>
       </c>
       <c r="I416" s="4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="J416" s="4" t="n">
-        <v>114.04</v>
+        <v>113.9</v>
       </c>
       <c r="K416" s="4" t="n">
-        <v>123.5</v>
+        <v>123.46</v>
       </c>
       <c r="L416" s="4" t="n">
-        <v>156.67</v>
+        <v>156.64</v>
       </c>
       <c r="M416" s="4" t="n">
-        <v>124.18</v>
+        <v>124.17</v>
       </c>
       <c r="N416" s="6" t="n">
-        <v>29.18</v>
+        <v>28.54</v>
       </c>
       <c r="O416" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
@@ -32012,13 +32012,13 @@
         </is>
       </c>
       <c r="S416" s="4" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="T416" s="7" t="n">
         <v>19.4</v>
       </c>
       <c r="U416" s="7" t="n">
-        <v>12.7</v>
+        <v>19.3</v>
       </c>
       <c r="V416" s="4" t="inlineStr"/>
       <c r="W416" s="7" t="inlineStr"/>

--- a/US_stock/SOXL_table.xlsx
+++ b/US_stock/SOXL_table.xlsx
@@ -608,7 +608,7 @@
         <v>-3.19</v>
       </c>
       <c r="I2" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J2" t="n">
         <v>24.58</v>
@@ -691,7 +691,7 @@
         <v>5.09</v>
       </c>
       <c r="I3" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J3" t="n">
         <v>24.13</v>
@@ -770,7 +770,7 @@
         <v>-1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J4" t="n">
         <v>23.66</v>
@@ -849,7 +849,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J5" t="n">
         <v>23.23</v>
@@ -924,7 +924,7 @@
         <v>4.98</v>
       </c>
       <c r="I6" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J6" t="n">
         <v>22.84</v>
@@ -999,7 +999,7 @@
         <v>-4.12</v>
       </c>
       <c r="I7" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J7" t="n">
         <v>22.34</v>
@@ -1074,7 +1074,7 @@
         <v>2.22</v>
       </c>
       <c r="I8" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J8" t="n">
         <v>21.79</v>
@@ -1149,7 +1149,7 @@
         <v>-2.17</v>
       </c>
       <c r="I9" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J9" t="n">
         <v>21.21</v>
@@ -1224,7 +1224,7 @@
         <v>-3.28</v>
       </c>
       <c r="I10" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J10" t="n">
         <v>20.74</v>
@@ -1299,7 +1299,7 @@
         <v>8.93</v>
       </c>
       <c r="I11" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J11" t="n">
         <v>20.45</v>
@@ -1374,7 +1374,7 @@
         <v>-1.82</v>
       </c>
       <c r="I12" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
         <v>20.23</v>
@@ -1449,7 +1449,7 @@
         <v>-8.6</v>
       </c>
       <c r="I13" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J13" t="n">
         <v>19.86</v>
@@ -1528,7 +1528,7 @@
         <v>-5.45</v>
       </c>
       <c r="I14" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J14" t="n">
         <v>19.66</v>
@@ -1603,7 +1603,7 @@
         <v>-9.779999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J15" t="n">
         <v>19.33</v>
@@ -1678,7 +1678,7 @@
         <v>-0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J16" t="n">
         <v>19.11</v>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J17" t="n">
         <v>18.88</v>
@@ -1828,7 +1828,7 @@
         <v>1.95</v>
       </c>
       <c r="I18" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J18" t="n">
         <v>18.6</v>
@@ -1903,7 +1903,7 @@
         <v>-29.83</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>18.21</v>
@@ -1986,7 +1986,7 @@
         <v>-23.5</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>17.61</v>
@@ -2069,7 +2069,7 @@
         <v>4.83</v>
       </c>
       <c r="I21" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J21" t="n">
         <v>17.17</v>
@@ -2152,7 +2152,7 @@
         <v>-9.77</v>
       </c>
       <c r="I22" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J22" t="n">
         <v>16.72</v>
@@ -2235,7 +2235,7 @@
         <v>54.74</v>
       </c>
       <c r="I23" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J23" t="n">
         <v>16.45</v>
@@ -2314,7 +2314,7 @@
         <v>-24.61</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>16.03</v>
@@ -2397,7 +2397,7 @@
         <v>6.26</v>
       </c>
       <c r="I25" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J25" t="n">
         <v>15.56</v>
@@ -2480,7 +2480,7 @@
         <v>2.36</v>
       </c>
       <c r="I26" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J26" t="n">
         <v>15.04</v>
@@ -2559,7 +2559,7 @@
         <v>1.25</v>
       </c>
       <c r="I27" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J27" t="n">
         <v>14.58</v>
@@ -2634,7 +2634,7 @@
         <v>-11.93</v>
       </c>
       <c r="I28" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J28" t="n">
         <v>14.04</v>
@@ -2717,7 +2717,7 @@
         <v>-1.51</v>
       </c>
       <c r="I29" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J29" t="n">
         <v>13.5</v>
@@ -2796,7 +2796,7 @@
         <v>-5.35</v>
       </c>
       <c r="I30" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J30" t="n">
         <v>12.98</v>
@@ -2871,7 +2871,7 @@
         <v>5.42</v>
       </c>
       <c r="I31" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J31" t="n">
         <v>12.4</v>
@@ -2946,7 +2946,7 @@
         <v>12.14</v>
       </c>
       <c r="I32" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J32" t="n">
         <v>11.89</v>
@@ -3025,7 +3025,7 @@
         <v>16.59</v>
       </c>
       <c r="I33" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J33" t="n">
         <v>11.55</v>
@@ -3100,7 +3100,7 @@
         <v>2.85</v>
       </c>
       <c r="I34" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J34" t="n">
         <v>11.28</v>
@@ -3175,7 +3175,7 @@
         <v>-0.41</v>
       </c>
       <c r="I35" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J35" t="n">
         <v>11.09</v>
@@ -3250,7 +3250,7 @@
         <v>-3.51</v>
       </c>
       <c r="I36" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J36" t="n">
         <v>10.89</v>
@@ -3325,7 +3325,7 @@
         <v>2.54</v>
       </c>
       <c r="I37" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J37" t="n">
         <v>10.7</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5</v>
       </c>
       <c r="I38" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J38" t="n">
         <v>10.49</v>
@@ -3475,7 +3475,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J39" t="n">
         <v>10.59</v>
@@ -3550,7 +3550,7 @@
         <v>-1.81</v>
       </c>
       <c r="I40" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J40" t="n">
         <v>10.8</v>
@@ -3625,7 +3625,7 @@
         <v>-3.15</v>
       </c>
       <c r="I41" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J41" t="n">
         <v>10.98</v>
@@ -3700,7 +3700,7 @@
         <v>5.08</v>
       </c>
       <c r="I42" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J42" t="n">
         <v>11.23</v>
@@ -3775,7 +3775,7 @@
         <v>2.8</v>
       </c>
       <c r="I43" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J43" t="n">
         <v>11.27</v>
@@ -3850,7 +3850,7 @@
         <v>3.31</v>
       </c>
       <c r="I44" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J44" t="n">
         <v>11.49</v>
@@ -3925,7 +3925,7 @@
         <v>21.42</v>
       </c>
       <c r="I45" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J45" t="n">
         <v>11.84</v>
@@ -4000,7 +4000,7 @@
         <v>8.56</v>
       </c>
       <c r="I46" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J46" t="n">
         <v>12.24</v>
@@ -4075,7 +4075,7 @@
         <v>1.3</v>
       </c>
       <c r="I47" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J47" t="n">
         <v>12.65</v>
@@ -4150,7 +4150,7 @@
         <v>-1.97</v>
       </c>
       <c r="I48" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J48" t="n">
         <v>13.11</v>
@@ -4225,7 +4225,7 @@
         <v>-0.44</v>
       </c>
       <c r="I49" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J49" t="n">
         <v>13.56</v>
@@ -4300,7 +4300,7 @@
         <v>-1.75</v>
       </c>
       <c r="I50" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J50" t="n">
         <v>14.03</v>
@@ -4375,7 +4375,7 @@
         <v>-0.5</v>
       </c>
       <c r="I51" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J51" t="n">
         <v>14.47</v>
@@ -4450,7 +4450,7 @@
         <v>-5.42</v>
       </c>
       <c r="I52" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J52" t="n">
         <v>14.8</v>
@@ -4525,7 +4525,7 @@
         <v>-2.89</v>
       </c>
       <c r="I53" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J53" t="n">
         <v>15.03</v>
@@ -4600,7 +4600,7 @@
         <v>-4.68</v>
       </c>
       <c r="I54" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J54" t="n">
         <v>15.19</v>
@@ -4675,7 +4675,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J55" t="n">
         <v>15.44</v>
@@ -4750,7 +4750,7 @@
         <v>-1.45</v>
       </c>
       <c r="I56" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J56" t="n">
         <v>15.7</v>
@@ -4825,7 +4825,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J57" t="n">
         <v>15.95</v>
@@ -4900,7 +4900,7 @@
         <v>-6.01</v>
       </c>
       <c r="I58" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J58" t="n">
         <v>16.16</v>
@@ -4979,7 +4979,7 @@
         <v>4.53</v>
       </c>
       <c r="I59" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J59" t="n">
         <v>16.33</v>
@@ -5054,7 +5054,7 @@
         <v>8.32</v>
       </c>
       <c r="I60" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J60" t="n">
         <v>16.6</v>
@@ -5129,7 +5129,7 @@
         <v>4.28</v>
       </c>
       <c r="I61" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J61" t="n">
         <v>16.92</v>
@@ -5204,7 +5204,7 @@
         <v>-1.47</v>
       </c>
       <c r="I62" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J62" t="n">
         <v>17.19</v>
@@ -5279,7 +5279,7 @@
         <v>1.98</v>
       </c>
       <c r="I63" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J63" t="n">
         <v>17.47</v>
@@ -5354,7 +5354,7 @@
         <v>7.33</v>
       </c>
       <c r="I64" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J64" t="n">
         <v>17.79</v>
@@ -5429,7 +5429,7 @@
         <v>6.34</v>
       </c>
       <c r="I65" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J65" t="n">
         <v>18.03</v>
@@ -5504,7 +5504,7 @@
         <v>-1.15</v>
       </c>
       <c r="I66" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J66" t="n">
         <v>18.18</v>
@@ -5579,7 +5579,7 @@
         <v>0.23</v>
       </c>
       <c r="I67" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J67" t="n">
         <v>18.32</v>
@@ -5654,7 +5654,7 @@
         <v>-7.59</v>
       </c>
       <c r="I68" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J68" t="n">
         <v>18.4</v>
@@ -5733,7 +5733,7 @@
         <v>9.27</v>
       </c>
       <c r="I69" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J69" t="n">
         <v>18.57</v>
@@ -5808,7 +5808,7 @@
         <v>-2.2</v>
       </c>
       <c r="I70" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J70" t="n">
         <v>18.74</v>
@@ -5883,7 +5883,7 @@
         <v>0.89</v>
       </c>
       <c r="I71" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J71" t="n">
         <v>18.92</v>
@@ -5958,7 +5958,7 @@
         <v>-1.86</v>
       </c>
       <c r="I72" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J72" t="n">
         <v>19.13</v>
@@ -6033,7 +6033,7 @@
         <v>1.75</v>
       </c>
       <c r="I73" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J73" t="n">
         <v>19.38</v>
@@ -6108,7 +6108,7 @@
         <v>11.35</v>
       </c>
       <c r="I74" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J74" t="n">
         <v>19.8</v>
@@ -6183,7 +6183,7 @@
         <v>2.63</v>
       </c>
       <c r="I75" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J75" t="n">
         <v>20.16</v>
@@ -6258,7 +6258,7 @@
         <v>2.52</v>
       </c>
       <c r="I76" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J76" t="n">
         <v>20.57</v>
@@ -6333,7 +6333,7 @@
         <v>-0.36</v>
       </c>
       <c r="I77" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J77" t="n">
         <v>20.97</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J78" t="n">
         <v>21.42</v>
@@ -6483,7 +6483,7 @@
         <v>-1.59</v>
       </c>
       <c r="I79" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J79" t="n">
         <v>21.81</v>
@@ -6558,7 +6558,7 @@
         <v>5.43</v>
       </c>
       <c r="I80" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J80" t="n">
         <v>22.2</v>
@@ -6633,7 +6633,7 @@
         <v>1.46</v>
       </c>
       <c r="I81" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J81" t="n">
         <v>22.57</v>
@@ -6708,7 +6708,7 @@
         <v>-5.53</v>
       </c>
       <c r="I82" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J82" t="n">
         <v>22.89</v>
@@ -6783,7 +6783,7 @@
         <v>5.61</v>
       </c>
       <c r="I83" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J83" t="n">
         <v>23.25</v>
@@ -6858,7 +6858,7 @@
         <v>1.02</v>
       </c>
       <c r="I84" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J84" t="n">
         <v>23.55</v>
@@ -6933,7 +6933,7 @@
         <v>2.7</v>
       </c>
       <c r="I85" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J85" t="n">
         <v>23.83</v>
@@ -7008,7 +7008,7 @@
         <v>-0.29</v>
       </c>
       <c r="I86" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J86" t="n">
         <v>24.12</v>
@@ -7083,7 +7083,7 @@
         <v>-2.9</v>
       </c>
       <c r="I87" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J87" t="n">
         <v>24.36</v>
@@ -7158,7 +7158,7 @@
         <v>2.98</v>
       </c>
       <c r="I88" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J88" t="n">
         <v>24.72</v>
@@ -7233,7 +7233,7 @@
         <v>-0.95</v>
       </c>
       <c r="I89" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J89" t="n">
         <v>24.98</v>
@@ -7308,7 +7308,7 @@
         <v>1.07</v>
       </c>
       <c r="I90" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J90" t="n">
         <v>25.28</v>
@@ -7383,7 +7383,7 @@
         <v>0.04</v>
       </c>
       <c r="I91" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J91" t="n">
         <v>25.57</v>
@@ -7458,7 +7458,7 @@
         <v>0.62</v>
       </c>
       <c r="I92" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J92" t="n">
         <v>25.89</v>
@@ -7533,7 +7533,7 @@
         <v>-4.26</v>
       </c>
       <c r="I93" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J93" t="n">
         <v>26.13</v>
@@ -7608,7 +7608,7 @@
         <v>-2.05</v>
       </c>
       <c r="I94" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J94" t="n">
         <v>26.22</v>
@@ -7687,7 +7687,7 @@
         <v>-0.62</v>
       </c>
       <c r="I95" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J95" t="n">
         <v>26.27</v>
@@ -7762,7 +7762,7 @@
         <v>-0.08</v>
       </c>
       <c r="I96" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J96" t="n">
         <v>26.29</v>
@@ -7837,7 +7837,7 @@
         <v>4.96</v>
       </c>
       <c r="I97" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J97" t="n">
         <v>26.38</v>
@@ -7912,7 +7912,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I98" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J98" t="n">
         <v>26.48</v>
@@ -7987,7 +7987,7 @@
         <v>2.15</v>
       </c>
       <c r="I99" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J99" t="n">
         <v>26.62</v>
@@ -8062,7 +8062,7 @@
         <v>-9.5</v>
       </c>
       <c r="I100" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J100" t="n">
         <v>26.57</v>
@@ -8141,7 +8141,7 @@
         <v>-3.61</v>
       </c>
       <c r="I101" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J101" t="n">
         <v>26.45</v>
@@ -8216,7 +8216,7 @@
         <v>3.82</v>
       </c>
       <c r="I102" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J102" t="n">
         <v>26.45</v>
@@ -8291,7 +8291,7 @@
         <v>-1.92</v>
       </c>
       <c r="I103" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J103" t="n">
         <v>26.36</v>
@@ -8366,7 +8366,7 @@
         <v>-2.16</v>
       </c>
       <c r="I104" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J104" t="n">
         <v>26.23</v>
@@ -8441,7 +8441,7 @@
         <v>4.21</v>
       </c>
       <c r="I105" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J105" t="n">
         <v>26.11</v>
@@ -8516,7 +8516,7 @@
         <v>2.84</v>
       </c>
       <c r="I106" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J106" t="n">
         <v>26.03</v>
@@ -8591,7 +8591,7 @@
         <v>-0.39</v>
       </c>
       <c r="I107" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J107" t="n">
         <v>25.99</v>
@@ -8666,7 +8666,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I108" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J108" t="n">
         <v>26.02</v>
@@ -8741,7 +8741,7 @@
         <v>4.54</v>
       </c>
       <c r="I109" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J109" t="n">
         <v>26.13</v>
@@ -8816,7 +8816,7 @@
         <v>0.51</v>
       </c>
       <c r="I110" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J110" t="n">
         <v>26.24</v>
@@ -8891,7 +8891,7 @@
         <v>-6.98</v>
       </c>
       <c r="I111" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J111" t="n">
         <v>26.24</v>
@@ -8966,7 +8966,7 @@
         <v>0.59</v>
       </c>
       <c r="I112" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J112" t="n">
         <v>26.24</v>
@@ -9041,7 +9041,7 @@
         <v>-4.65</v>
       </c>
       <c r="I113" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J113" t="n">
         <v>26.24</v>
@@ -9120,7 +9120,7 @@
         <v>-1.68</v>
       </c>
       <c r="I114" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J114" t="n">
         <v>26.24</v>
@@ -9195,7 +9195,7 @@
         <v>-1.75</v>
       </c>
       <c r="I115" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J115" t="n">
         <v>26.23</v>
@@ -9270,7 +9270,7 @@
         <v>8.25</v>
       </c>
       <c r="I116" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J116" t="n">
         <v>26.32</v>
@@ -9345,7 +9345,7 @@
         <v>-0.55</v>
       </c>
       <c r="I117" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J117" t="n">
         <v>26.34</v>
@@ -9420,7 +9420,7 @@
         <v>2.35</v>
       </c>
       <c r="I118" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J118" t="n">
         <v>26.38</v>
@@ -9495,7 +9495,7 @@
         <v>0.86</v>
       </c>
       <c r="I119" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J119" t="n">
         <v>26.41</v>
@@ -9570,7 +9570,7 @@
         <v>1.24</v>
       </c>
       <c r="I120" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J120" t="n">
         <v>26.59</v>
@@ -9645,7 +9645,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J121" t="n">
         <v>26.69</v>
@@ -9724,7 +9724,7 @@
         <v>-3.04</v>
       </c>
       <c r="I122" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J122" t="n">
         <v>26.7</v>
@@ -9803,7 +9803,7 @@
         <v>-1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J123" t="n">
         <v>26.72</v>
@@ -9878,7 +9878,7 @@
         <v>2.97</v>
       </c>
       <c r="I124" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J124" t="n">
         <v>26.8</v>
@@ -9953,7 +9953,7 @@
         <v>3.08</v>
       </c>
       <c r="I125" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J125" t="n">
         <v>26.87</v>
@@ -10028,7 +10028,7 @@
         <v>2.38</v>
       </c>
       <c r="I126" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J126" t="n">
         <v>26.94</v>
@@ -10103,7 +10103,7 @@
         <v>0.37</v>
       </c>
       <c r="I127" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J127" t="n">
         <v>27.02</v>
@@ -10178,7 +10178,7 @@
         <v>5.23</v>
       </c>
       <c r="I128" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J128" t="n">
         <v>27.05</v>
@@ -10253,7 +10253,7 @@
         <v>2</v>
       </c>
       <c r="I129" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J129" t="n">
         <v>27.05</v>
@@ -10328,7 +10328,7 @@
         <v>0.45</v>
       </c>
       <c r="I130" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J130" t="n">
         <v>27.04</v>
@@ -10403,7 +10403,7 @@
         <v>2.39</v>
       </c>
       <c r="I131" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J131" t="n">
         <v>27.17</v>
@@ -10478,7 +10478,7 @@
         <v>1.6</v>
       </c>
       <c r="I132" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J132" t="n">
         <v>27.32</v>
@@ -10553,7 +10553,7 @@
         <v>-0.03</v>
       </c>
       <c r="I133" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J133" t="n">
         <v>27.53</v>
@@ -10628,7 +10628,7 @@
         <v>10.41</v>
       </c>
       <c r="I134" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J134" t="n">
         <v>27.92</v>
@@ -10703,7 +10703,7 @@
         <v>-1.84</v>
       </c>
       <c r="I135" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J135" t="n">
         <v>28.3</v>
@@ -10778,7 +10778,7 @@
         <v>4.27</v>
       </c>
       <c r="I136" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J136" t="n">
         <v>28.65</v>
@@ -10853,7 +10853,7 @@
         <v>-0.35</v>
       </c>
       <c r="I137" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J137" t="n">
         <v>29</v>
@@ -10928,7 +10928,7 @@
         <v>-0.29</v>
       </c>
       <c r="I138" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J138" t="n">
         <v>29.32</v>
@@ -11003,7 +11003,7 @@
         <v>-1.02</v>
       </c>
       <c r="I139" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J139" t="n">
         <v>29.6</v>
@@ -11078,7 +11078,7 @@
         <v>0.5</v>
       </c>
       <c r="I140" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J140" t="n">
         <v>29.88</v>
@@ -11153,7 +11153,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J141" t="n">
         <v>30.28</v>
@@ -11228,7 +11228,7 @@
         <v>2.41</v>
       </c>
       <c r="I142" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J142" t="n">
         <v>30.75</v>
@@ -11303,7 +11303,7 @@
         <v>5.8</v>
       </c>
       <c r="I143" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J143" t="n">
         <v>31.35</v>
@@ -11378,7 +11378,7 @@
         <v>6</v>
       </c>
       <c r="I144" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J144" t="n">
         <v>32.02</v>
@@ -11453,7 +11453,7 @@
         <v>-2.18</v>
       </c>
       <c r="I145" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J145" t="n">
         <v>32.61</v>
@@ -11528,7 +11528,7 @@
         <v>9.109999999999999</v>
       </c>
       <c r="I146" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J146" t="n">
         <v>33.34</v>
@@ -11603,7 +11603,7 @@
         <v>-6.91</v>
       </c>
       <c r="I147" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J147" t="n">
         <v>33.93</v>
@@ -11678,7 +11678,7 @@
         <v>10.18</v>
       </c>
       <c r="I148" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J148" t="n">
         <v>34.64</v>
@@ -11753,7 +11753,7 @@
         <v>-1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J149" t="n">
         <v>35.29</v>
@@ -11828,7 +11828,7 @@
         <v>-19</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>35.53</v>
@@ -11907,7 +11907,7 @@
         <v>14.39</v>
       </c>
       <c r="I151" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J151" t="n">
         <v>35.99</v>
@@ -11982,7 +11982,7 @@
         <v>-6.39</v>
       </c>
       <c r="I152" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J152" t="n">
         <v>36.3</v>
@@ -12057,7 +12057,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J153" t="n">
         <v>36.78</v>
@@ -12132,7 +12132,7 @@
         <v>1.48</v>
       </c>
       <c r="I154" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J154" t="n">
         <v>37.12</v>
@@ -12207,7 +12207,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J155" t="n">
         <v>37.48</v>
@@ -12282,7 +12282,7 @@
         <v>4.84</v>
       </c>
       <c r="I156" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J156" t="n">
         <v>37.88</v>
@@ -12357,7 +12357,7 @@
         <v>-1.73</v>
       </c>
       <c r="I157" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J157" t="n">
         <v>38.24</v>
@@ -12432,7 +12432,7 @@
         <v>-7.52</v>
       </c>
       <c r="I158" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J158" t="n">
         <v>38.44</v>
@@ -12511,7 +12511,7 @@
         <v>7.25</v>
       </c>
       <c r="I159" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J159" t="n">
         <v>38.81</v>
@@ -12586,7 +12586,7 @@
         <v>4.79</v>
       </c>
       <c r="I160" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J160" t="n">
         <v>39.27</v>
@@ -12661,7 +12661,7 @@
         <v>8.58</v>
       </c>
       <c r="I161" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J161" t="n">
         <v>39.91</v>
@@ -12736,7 +12736,7 @@
         <v>0.26</v>
       </c>
       <c r="I162" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J162" t="n">
         <v>40.51</v>
@@ -12811,7 +12811,7 @@
         <v>5.16</v>
       </c>
       <c r="I163" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J163" t="n">
         <v>41.14</v>
@@ -12886,7 +12886,7 @@
         <v>-4.03</v>
       </c>
       <c r="I164" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J164" t="n">
         <v>41.55</v>
@@ -12961,7 +12961,7 @@
         <v>0.82</v>
       </c>
       <c r="I165" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J165" t="n">
         <v>42.03</v>
@@ -13036,7 +13036,7 @@
         <v>1.68</v>
       </c>
       <c r="I166" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J166" t="n">
         <v>42.37</v>
@@ -13111,7 +13111,7 @@
         <v>-11.91</v>
       </c>
       <c r="I167" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J167" t="n">
         <v>42.57</v>
@@ -13186,7 +13186,7 @@
         <v>9.42</v>
       </c>
       <c r="I168" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J168" t="n">
         <v>42.77</v>
@@ -13261,7 +13261,7 @@
         <v>-8.16</v>
       </c>
       <c r="I169" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J169" t="n">
         <v>42.81</v>
@@ -13336,7 +13336,7 @@
         <v>-2.95</v>
       </c>
       <c r="I170" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J170" t="n">
         <v>43.19</v>
@@ -13415,7 +13415,7 @@
         <v>7.72</v>
       </c>
       <c r="I171" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J171" t="n">
         <v>43.48</v>
@@ -13490,7 +13490,7 @@
         <v>-7.01</v>
       </c>
       <c r="I172" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J172" t="n">
         <v>43.74</v>
@@ -13569,7 +13569,7 @@
         <v>4.55</v>
       </c>
       <c r="I173" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J173" t="n">
         <v>43.92</v>
@@ -13644,7 +13644,7 @@
         <v>-10.28</v>
       </c>
       <c r="I174" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J174" t="n">
         <v>43.86</v>
@@ -13719,7 +13719,7 @@
         <v>-0.92</v>
       </c>
       <c r="I175" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J175" t="n">
         <v>43.79</v>
@@ -13794,7 +13794,7 @@
         <v>-5.18</v>
       </c>
       <c r="I176" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J176" t="n">
         <v>43.52</v>
@@ -13869,7 +13869,7 @@
         <v>-6.76</v>
       </c>
       <c r="I177" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J177" t="n">
         <v>43.16</v>
@@ -13948,7 +13948,7 @@
         <v>4.69</v>
       </c>
       <c r="I178" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J178" t="n">
         <v>43.04</v>
@@ -13994,85 +13994,85 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>SOXL</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
         <is>
           <t>2025-11-20</t>
         </is>
       </c>
-      <c r="C179" s="4" t="n">
+      <c r="C179" t="n">
         <v>38.76</v>
       </c>
-      <c r="D179" s="4" t="n">
+      <c r="D179" t="n">
         <v>39.16</v>
       </c>
-      <c r="E179" s="4" t="n">
+      <c r="E179" t="n">
         <v>30.39</v>
       </c>
-      <c r="F179" s="4" t="n">
+      <c r="F179" t="n">
         <v>30.79</v>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" t="n">
         <v>228883600</v>
       </c>
-      <c r="H179" s="5" t="n">
+      <c r="H179" s="1" t="n">
         <v>-14.33</v>
       </c>
-      <c r="I179" s="4" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J179" s="4" t="n">
+      <c r="I179" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J179" t="n">
         <v>42.52</v>
       </c>
-      <c r="K179" s="4" t="n">
+      <c r="K179" t="n">
         <v>36.98</v>
       </c>
-      <c r="L179" s="4" t="n">
+      <c r="L179" t="n">
         <v>30.96</v>
       </c>
-      <c r="M179" s="4" t="n">
+      <c r="M179" t="n">
         <v>25.67</v>
       </c>
-      <c r="N179" s="6" t="n">
+      <c r="N179" s="2" t="n">
         <v>28.84</v>
       </c>
-      <c r="O179" s="4" t="n">
+      <c r="O179" t="n">
         <v>5</v>
       </c>
-      <c r="P179" s="4" t="inlineStr">
+      <c r="P179" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q179" s="4" t="inlineStr">
+      <c r="Q179" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R179" s="4" t="inlineStr">
+      <c r="R179" t="inlineStr">
         <is>
           <t>3rd: MA120, 50% cash, 5d</t>
         </is>
       </c>
-      <c r="S179" s="4" t="n">
+      <c r="S179" t="n">
         <v>4.11</v>
       </c>
-      <c r="T179" s="6" t="n">
+      <c r="T179" s="2" t="n">
         <v>26.4</v>
       </c>
-      <c r="U179" s="6" t="n">
+      <c r="U179" s="2" t="n">
         <v>29.2</v>
       </c>
-      <c r="V179" s="6" t="inlineStr">
+      <c r="V179" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="W179" s="7" t="n">
+      <c r="W179" s="3" t="n">
         <v>145</v>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
         <v>2.99</v>
       </c>
       <c r="I180" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J180" t="n">
         <v>41.95</v>
@@ -14181,7 +14181,7 @@
         <v>13.02</v>
       </c>
       <c r="I181" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J181" t="n">
         <v>41.4</v>
@@ -14256,7 +14256,7 @@
         <v>0.86</v>
       </c>
       <c r="I182" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J182" t="n">
         <v>40.86</v>
@@ -14331,7 +14331,7 @@
         <v>8.33</v>
       </c>
       <c r="I183" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J183" t="n">
         <v>40.35</v>
@@ -14406,7 +14406,7 @@
         <v>5.29</v>
       </c>
       <c r="I184" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J184" t="n">
         <v>40.05</v>
@@ -14481,7 +14481,7 @@
         <v>0.12</v>
       </c>
       <c r="I185" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J185" t="n">
         <v>39.72</v>
@@ -14556,7 +14556,7 @@
         <v>6.03</v>
       </c>
       <c r="I186" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J186" t="n">
         <v>39.48</v>
@@ -14631,7 +14631,7 @@
         <v>6.35</v>
       </c>
       <c r="I187" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J187" t="n">
         <v>39.67</v>
@@ -14706,7 +14706,7 @@
         <v>-3.05</v>
       </c>
       <c r="I188" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J188" t="n">
         <v>39.59</v>
@@ -14781,7 +14781,7 @@
         <v>2.97</v>
       </c>
       <c r="I189" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J189" t="n">
         <v>39.76</v>
@@ -14856,7 +14856,7 @@
         <v>3.21</v>
       </c>
       <c r="I190" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J190" t="n">
         <v>40.08</v>
@@ -14931,7 +14931,7 @@
         <v>-0.42</v>
       </c>
       <c r="I191" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J191" t="n">
         <v>40.22</v>
@@ -15006,7 +15006,7 @@
         <v>3.89</v>
       </c>
       <c r="I192" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J192" t="n">
         <v>40.61</v>
@@ -15081,7 +15081,7 @@
         <v>-1.73</v>
       </c>
       <c r="I193" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J193" t="n">
         <v>40.86</v>
@@ -15156,7 +15156,7 @@
         <v>-14.52</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>40.99</v>
@@ -15231,7 +15231,7 @@
         <v>-1.27</v>
       </c>
       <c r="I195" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J195" t="n">
         <v>41.1</v>
@@ -15306,7 +15306,7 @@
         <v>-1.68</v>
       </c>
       <c r="I196" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J196" t="n">
         <v>41.29</v>
@@ -15385,7 +15385,7 @@
         <v>-11.05</v>
       </c>
       <c r="I197" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J197" t="n">
         <v>41.37</v>
@@ -15460,7 +15460,7 @@
         <v>7.11</v>
       </c>
       <c r="I198" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J198" t="n">
         <v>41.5</v>
@@ -15535,7 +15535,7 @@
         <v>8.15</v>
       </c>
       <c r="I199" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J199" t="n">
         <v>42.05</v>
@@ -15610,7 +15610,7 @@
         <v>3.69</v>
       </c>
       <c r="I200" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J200" t="n">
         <v>42.62</v>
@@ -15685,7 +15685,7 @@
         <v>1.02</v>
       </c>
       <c r="I201" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J201" t="n">
         <v>43.01</v>
@@ -15760,7 +15760,7 @@
         <v>1.17</v>
       </c>
       <c r="I202" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J202" t="n">
         <v>43.41</v>
@@ -15835,7 +15835,7 @@
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J203" t="n">
         <v>43.67</v>
@@ -15910,7 +15910,7 @@
         <v>-0.88</v>
       </c>
       <c r="I204" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J204" t="n">
         <v>43.79</v>
@@ -15985,7 +15985,7 @@
         <v>-0.34</v>
       </c>
       <c r="I205" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J205" t="n">
         <v>43.91</v>
@@ -16064,7 +16064,7 @@
         <v>-3.76</v>
       </c>
       <c r="I206" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J206" t="n">
         <v>43.82</v>
@@ -16139,7 +16139,7 @@
         <v>12.4</v>
       </c>
       <c r="I207" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J207" t="n">
         <v>43.86</v>
@@ -16214,7 +16214,7 @@
         <v>4.19</v>
       </c>
       <c r="I208" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J208" t="n">
         <v>44.06</v>
@@ -16289,7 +16289,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="I209" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J209" t="n">
         <v>44.43</v>
@@ -16364,7 +16364,7 @@
         <v>-3.17</v>
       </c>
       <c r="I210" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J210" t="n">
         <v>44.65</v>
@@ -16439,7 +16439,7 @@
         <v>-5.05</v>
       </c>
       <c r="I211" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J211" t="n">
         <v>44.74</v>
@@ -16514,7 +16514,7 @@
         <v>8.65</v>
       </c>
       <c r="I212" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J212" t="n">
         <v>44.96</v>
@@ -16589,7 +16589,7 @@
         <v>1.3</v>
       </c>
       <c r="I213" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J213" t="n">
         <v>45.25</v>
@@ -16664,7 +16664,7 @@
         <v>2.6</v>
       </c>
       <c r="I214" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J214" t="n">
         <v>45.97</v>
@@ -16739,7 +16739,7 @@
         <v>-1.23</v>
       </c>
       <c r="I215" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J215" t="n">
         <v>46.68</v>
@@ -16814,7 +16814,7 @@
         <v>4.88</v>
       </c>
       <c r="I216" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J216" t="n">
         <v>47.56</v>
@@ -16889,7 +16889,7 @@
         <v>4.6</v>
       </c>
       <c r="I217" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J217" t="n">
         <v>48.79</v>
@@ -16964,7 +16964,7 @@
         <v>-4.63</v>
       </c>
       <c r="I218" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J218" t="n">
         <v>49.76</v>
@@ -17039,7 +17039,7 @@
         <v>9.57</v>
       </c>
       <c r="I219" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J219" t="n">
         <v>50.85</v>
@@ -17114,7 +17114,7 @@
         <v>0.38</v>
       </c>
       <c r="I220" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J220" t="n">
         <v>51.87</v>
@@ -17189,7 +17189,7 @@
         <v>-3.33</v>
       </c>
       <c r="I221" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J221" t="n">
         <v>52.76</v>
@@ -17264,7 +17264,7 @@
         <v>-1.46</v>
       </c>
       <c r="I222" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J222" t="n">
         <v>53.59</v>
@@ -17339,7 +17339,7 @@
         <v>7.02</v>
       </c>
       <c r="I223" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J223" t="n">
         <v>54.62</v>
@@ -17414,7 +17414,7 @@
         <v>7.89</v>
       </c>
       <c r="I224" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J224" t="n">
         <v>55.94</v>
@@ -17489,7 +17489,7 @@
         <v>0.54</v>
       </c>
       <c r="I225" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J225" t="n">
         <v>57.28</v>
@@ -17564,7 +17564,7 @@
         <v>-12.31</v>
       </c>
       <c r="I226" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J226" t="n">
         <v>58.26</v>
@@ -17639,7 +17639,7 @@
         <v>5.52</v>
       </c>
       <c r="I227" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J227" t="n">
         <v>59.16</v>
@@ -17714,7 +17714,7 @@
         <v>-6.14</v>
       </c>
       <c r="I228" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J228" t="n">
         <v>59.76</v>
@@ -17789,7 +17789,7 @@
         <v>-13.08</v>
       </c>
       <c r="I229" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J229" t="n">
         <v>59.72</v>
@@ -17868,7 +17868,7 @@
         <v>0.11</v>
       </c>
       <c r="I230" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J230" t="n">
         <v>59.77</v>
@@ -17943,7 +17943,7 @@
         <v>15.95</v>
       </c>
       <c r="I231" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J231" t="n">
         <v>60.37</v>
@@ -18018,7 +18018,7 @@
         <v>3.69</v>
       </c>
       <c r="I232" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J232" t="n">
         <v>60.88</v>
@@ -18093,7 +18093,7 @@
         <v>-1.08</v>
       </c>
       <c r="I233" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J233" t="n">
         <v>61.31</v>
@@ -18168,7 +18168,7 @@
         <v>7.44</v>
       </c>
       <c r="I234" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J234" t="n">
         <v>61.91</v>
@@ -18243,7 +18243,7 @@
         <v>-7.28</v>
       </c>
       <c r="I235" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J235" t="n">
         <v>62.29</v>
@@ -18318,7 +18318,7 @@
         <v>2.36</v>
       </c>
       <c r="I236" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J236" t="n">
         <v>62.62</v>
@@ -18393,7 +18393,7 @@
         <v>-0.37</v>
       </c>
       <c r="I237" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J237" t="n">
         <v>62.8</v>
@@ -18468,7 +18468,7 @@
         <v>3.02</v>
       </c>
       <c r="I238" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J238" t="n">
         <v>63.22</v>
@@ -18543,7 +18543,7 @@
         <v>-1.6</v>
       </c>
       <c r="I239" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J239" t="n">
         <v>63.31</v>
@@ -18618,7 +18618,7 @@
         <v>2.88</v>
       </c>
       <c r="I240" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J240" t="n">
         <v>63.47</v>
@@ -18693,7 +18693,7 @@
         <v>-1.86</v>
       </c>
       <c r="I241" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J241" t="n">
         <v>63.69</v>
@@ -18768,7 +18768,7 @@
         <v>4.06</v>
       </c>
       <c r="I242" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J242" t="n">
         <v>64.08</v>
@@ -18843,7 +18843,7 @@
         <v>4.85</v>
       </c>
       <c r="I243" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J243" t="n">
         <v>64.42</v>
@@ -18918,7 +18918,7 @@
         <v>-9.07</v>
       </c>
       <c r="I244" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J244" t="n">
         <v>64.19</v>
@@ -18993,7 +18993,7 @@
         <v>-3.94</v>
       </c>
       <c r="I245" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J245" t="n">
         <v>63.8</v>
@@ -19072,7 +19072,7 @@
         <v>-0.02</v>
       </c>
       <c r="I246" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J246" t="n">
         <v>63.85</v>
@@ -19147,7 +19147,7 @@
         <v>-14.89</v>
       </c>
       <c r="I247" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>63.26</v>
@@ -19226,7 +19226,7 @@
         <v>5.99</v>
       </c>
       <c r="I248" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J248" t="n">
         <v>63.03</v>
@@ -19301,7 +19301,7 @@
         <v>-3.22</v>
       </c>
       <c r="I249" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J249" t="n">
         <v>63.11</v>
@@ -19380,7 +19380,7 @@
         <v>-12.6</v>
       </c>
       <c r="I250" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J250" t="n">
         <v>62.84</v>
@@ -19459,7 +19459,7 @@
         <v>11.35</v>
       </c>
       <c r="I251" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J251" t="n">
         <v>62.42</v>
@@ -19534,7 +19534,7 @@
         <v>2.36</v>
       </c>
       <c r="I252" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J252" t="n">
         <v>61.95</v>
@@ -19609,7 +19609,7 @@
         <v>2.75</v>
       </c>
       <c r="I253" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J253" t="n">
         <v>61.59</v>
@@ -19684,7 +19684,7 @@
         <v>-10.35</v>
       </c>
       <c r="I254" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J254" t="n">
         <v>60.7</v>
@@ -19757,7 +19757,7 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J255" t="n">
         <v>60.08</v>
@@ -19836,7 +19836,7 @@
         <v>5.84</v>
       </c>
       <c r="I256" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J256" t="n">
         <v>59.54</v>
@@ -19911,7 +19911,7 @@
         <v>2.35</v>
       </c>
       <c r="I257" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J257" t="n">
         <v>59.07</v>
@@ -19986,7 +19986,7 @@
         <v>-1.69</v>
       </c>
       <c r="I258" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J258" t="n">
         <v>58.45</v>
@@ -20061,7 +20061,7 @@
         <v>1.54</v>
       </c>
       <c r="I259" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J259" t="n">
         <v>57.93</v>
@@ -20136,7 +20136,7 @@
         <v>-6.75</v>
       </c>
       <c r="I260" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J260" t="n">
         <v>57.14</v>
@@ -20215,7 +20215,7 @@
         <v>3.7</v>
       </c>
       <c r="I261" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J261" t="n">
         <v>56.5</v>
@@ -20290,7 +20290,7 @@
         <v>3.62</v>
       </c>
       <c r="I262" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J262" t="n">
         <v>55.82</v>
@@ -20365,7 +20365,7 @@
         <v>3.79</v>
       </c>
       <c r="I263" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J263" t="n">
         <v>55.08</v>
@@ -20440,7 +20440,7 @@
         <v>-14.14</v>
       </c>
       <c r="I264" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J264" t="n">
         <v>54.26</v>
@@ -20519,7 +20519,7 @@
         <v>-4.82</v>
       </c>
       <c r="I265" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J265" t="n">
         <v>53.45</v>
@@ -20598,7 +20598,7 @@
         <v>-12.86</v>
       </c>
       <c r="I266" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J266" t="n">
         <v>52.34</v>
@@ -20673,7 +20673,7 @@
         <v>17.96</v>
       </c>
       <c r="I267" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J267" t="n">
         <v>52.07</v>
@@ -20748,7 +20748,7 @@
         <v>9.09</v>
       </c>
       <c r="I268" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J268" t="n">
         <v>51.85</v>
@@ -20823,7 +20823,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I269" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J269" t="n">
         <v>51.75</v>
@@ -20898,7 +20898,7 @@
         <v>3.89</v>
       </c>
       <c r="I270" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J270" t="n">
         <v>52.1</v>
@@ -20973,7 +20973,7 @@
         <v>3.18</v>
       </c>
       <c r="I271" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J271" t="n">
         <v>52.26</v>
@@ -21052,7 +21052,7 @@
         <v>19.38</v>
       </c>
       <c r="I272" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J272" t="n">
         <v>52.9</v>
@@ -21127,7 +21127,7 @@
         <v>6.63</v>
       </c>
       <c r="I273" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J273" t="n">
         <v>53.7</v>
@@ -21202,7 +21202,7 @@
         <v>6.13</v>
       </c>
       <c r="I274" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J274" t="n">
         <v>55</v>
@@ -21277,7 +21277,7 @@
         <v>5.46</v>
       </c>
       <c r="I275" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J275" t="n">
         <v>56.49</v>
@@ -21352,7 +21352,7 @@
         <v>5.89</v>
       </c>
       <c r="I276" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J276" t="n">
         <v>58.07</v>
@@ -21427,7 +21427,7 @@
         <v>0.76</v>
       </c>
       <c r="I277" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J277" t="n">
         <v>59.62</v>
@@ -21502,7 +21502,7 @@
         <v>2.81</v>
       </c>
       <c r="I278" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J278" t="n">
         <v>61.34</v>
@@ -21577,7 +21577,7 @@
         <v>7.15</v>
       </c>
       <c r="I279" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J279" t="n">
         <v>63.33</v>
@@ -21652,7 +21652,7 @@
         <v>1.33</v>
       </c>
       <c r="I280" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J280" t="n">
         <v>65.56999999999999</v>
@@ -21727,7 +21727,7 @@
         <v>2.24</v>
       </c>
       <c r="I281" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J281" t="n">
         <v>67.81999999999999</v>
@@ -21802,7 +21802,7 @@
         <v>7.69</v>
       </c>
       <c r="I282" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J282" t="n">
         <v>70.34999999999999</v>
@@ -21877,7 +21877,7 @@
         <v>6.75</v>
       </c>
       <c r="I283" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J283" t="n">
         <v>73.14</v>
@@ -21952,7 +21952,7 @@
         <v>13.79</v>
       </c>
       <c r="I284" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J284" t="n">
         <v>77.09999999999999</v>
@@ -22027,7 +22027,7 @@
         <v>-3.84</v>
       </c>
       <c r="I285" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J285" t="n">
         <v>80.94</v>
@@ -22102,7 +22102,7 @@
         <v>-11.21</v>
       </c>
       <c r="I286" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J286" t="n">
         <v>84.38</v>
@@ -22177,7 +22177,7 @@
         <v>7.67</v>
       </c>
       <c r="I287" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J287" t="n">
         <v>87.88</v>
@@ -22252,7 +22252,7 @@
         <v>7.64</v>
       </c>
       <c r="I288" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J288" t="n">
         <v>91.62</v>
@@ -22327,7 +22327,7 @@
         <v>2.69</v>
       </c>
       <c r="I289" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J289" t="n">
         <v>95.5</v>
@@ -22402,7 +22402,7 @@
         <v>-2.18</v>
       </c>
       <c r="I290" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J290" t="n">
         <v>99.13</v>
@@ -22477,7 +22477,7 @@
         <v>13.02</v>
       </c>
       <c r="I291" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J291" t="n">
         <v>103.51</v>
@@ -22552,7 +22552,7 @@
         <v>15.04</v>
       </c>
       <c r="I292" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J292" t="n">
         <v>108.42</v>
@@ -22627,7 +22627,7 @@
         <v>-8.289999999999999</v>
       </c>
       <c r="I293" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J293" t="n">
         <v>112.43</v>
@@ -22702,7 +22702,7 @@
         <v>16.33</v>
       </c>
       <c r="I294" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J294" t="n">
         <v>117.45</v>
@@ -22777,7 +22777,7 @@
         <v>7.62</v>
       </c>
       <c r="I295" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J295" t="n">
         <v>122.94</v>
@@ -22852,7 +22852,7 @@
         <v>-9.4</v>
       </c>
       <c r="I296" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J296" t="n">
         <v>127.3</v>
@@ -22927,7 +22927,7 @@
         <v>6.79</v>
       </c>
       <c r="I297" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J297" t="n">
         <v>132.21</v>
@@ -23002,7 +23002,7 @@
         <v>1.06</v>
       </c>
       <c r="I298" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J298" t="n">
         <v>137.1</v>
@@ -23077,7 +23077,7 @@
         <v>-11.82</v>
       </c>
       <c r="I299" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J299" t="n">
         <v>140.57</v>
@@ -23152,7 +23152,7 @@
         <v>-7.57</v>
       </c>
       <c r="I300" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J300" t="n">
         <v>143.36</v>
@@ -23227,7 +23227,7 @@
         <v>0.09</v>
       </c>
       <c r="I301" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J301" t="n">
         <v>146.05</v>
@@ -23302,7 +23302,7 @@
         <v>14.03</v>
       </c>
       <c r="I302" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J302" t="n">
         <v>149.42</v>
@@ -23377,7 +23377,7 @@
         <v>2.99</v>
       </c>
       <c r="I303" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J303" t="n">
         <v>152.7</v>
@@ -23452,7 +23452,7 @@
         <v>6.83</v>
       </c>
       <c r="I304" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J304" t="n">
         <v>155.81</v>
@@ -23527,7 +23527,7 @@
         <v>18.48</v>
       </c>
       <c r="I305" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J305" t="n">
         <v>160.93</v>
@@ -23602,7 +23602,7 @@
         <v>-3.46</v>
       </c>
       <c r="I306" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J306" t="n">
         <v>166.34</v>
@@ -23677,7 +23677,7 @@
         <v>3.05</v>
       </c>
       <c r="I307" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J307" t="n">
         <v>171.67</v>
@@ -23752,7 +23752,7 @@
         <v>-0.13</v>
       </c>
       <c r="I308" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J308" t="n">
         <v>176.54</v>
@@ -23827,7 +23827,7 @@
         <v>1.2</v>
       </c>
       <c r="I309" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J309" t="n">
         <v>181.37</v>
@@ -23902,7 +23902,7 @@
         <v>17.31</v>
       </c>
       <c r="I310" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J310" t="n">
         <v>188.3</v>
@@ -23977,7 +23977,7 @@
         <v>5.34</v>
       </c>
       <c r="I311" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J311" t="n">
         <v>195.12</v>
@@ -24052,7 +24052,7 @@
         <v>-6.36</v>
       </c>
       <c r="I312" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J312" t="n">
         <v>199.96</v>
@@ -24127,7 +24127,7 @@
         <v>-30.51</v>
       </c>
       <c r="I313" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J313" s="4" t="n">
         <v>201.48</v>
@@ -24206,7 +24206,7 @@
         <v>15.83</v>
       </c>
       <c r="I314" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J314" t="n">
         <v>203.2</v>
@@ -24281,7 +24281,7 @@
         <v>-4.61</v>
       </c>
       <c r="I315" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J315" t="n">
         <v>203.76</v>
@@ -24360,7 +24360,7 @@
         <v>-10.43</v>
       </c>
       <c r="I316" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J316" t="n">
         <v>204.17</v>
@@ -24435,7 +24435,7 @@
         <v>23.99</v>
       </c>
       <c r="I317" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J317" t="n">
         <v>206.15</v>
@@ -24510,7 +24510,7 @@
         <v>4.78</v>
       </c>
       <c r="I318" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J318" t="n">
         <v>208.58</v>
@@ -24585,7 +24585,7 @@
         <v>16.11</v>
       </c>
       <c r="I319" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J319" t="n">
         <v>213.99</v>
@@ -24660,7 +24660,7 @@
         <v>-16.99</v>
       </c>
       <c r="I320" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J320" s="4" t="n">
         <v>217.71</v>
@@ -24735,7 +24735,7 @@
         <v>3.39</v>
       </c>
       <c r="I321" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J321" t="n">
         <v>221.81</v>
@@ -24810,7 +24810,7 @@
         <v>19.43</v>
       </c>
       <c r="I322" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J322" t="n">
         <v>227.11</v>
@@ -24885,7 +24885,7 @@
         <v>7.69</v>
       </c>
       <c r="I323" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J323" t="n">
         <v>233.22</v>
@@ -24960,7 +24960,7 @@
         <v>-23.06</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>235.26</v>
@@ -25039,7 +25039,7 @@
         <v>-0.8</v>
       </c>
       <c r="I325" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J325" t="n">
         <v>235.45</v>
@@ -25114,7 +25114,7 @@
         <v>10.03</v>
       </c>
       <c r="I326" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J326" t="n">
         <v>237.18</v>
@@ -25189,7 +25189,7 @@
         <v>-14.65</v>
       </c>
       <c r="I327" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J327" s="4" t="n">
         <v>236.73</v>
@@ -25268,7 +25268,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I328" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J328" t="n">
         <v>237.34</v>
@@ -25343,7 +25343,7 @@
         <v>12.76</v>
       </c>
       <c r="I329" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J329" t="n">
         <v>239.32</v>
@@ -25418,7 +25418,7 @@
         <v>-18.43</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>236.89</v>
@@ -25497,7 +25497,7 @@
         <v>-16.59</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>231.94</v>
@@ -25572,7 +25572,7 @@
         <v>7.26</v>
       </c>
       <c r="I332" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J332" t="n">
         <v>228.54</v>
@@ -25647,7 +25647,7 @@
         <v>-15.09</v>
       </c>
       <c r="I333" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J333" s="4" t="n">
         <v>227.67</v>
@@ -25726,7 +25726,7 @@
         <v>5.78</v>
       </c>
       <c r="I334" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J334" t="n">
         <v>225.84</v>
@@ -25801,7 +25801,7 @@
         <v>10.08</v>
       </c>
       <c r="I335" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J335" t="n">
         <v>225.38</v>
@@ -25876,7 +25876,7 @@
         <v>-0.1</v>
       </c>
       <c r="I336" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J336" t="n">
         <v>225.96</v>
@@ -25951,7 +25951,7 @@
         <v>-13.99</v>
       </c>
       <c r="I337" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J337" t="n">
         <v>223.03</v>
@@ -26030,7 +26030,7 @@
         <v>6.83</v>
       </c>
       <c r="I338" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J338" t="n">
         <v>220.13</v>
@@ -26105,7 +26105,7 @@
         <v>-6.29</v>
       </c>
       <c r="I339" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J339" t="n">
         <v>214.79</v>
@@ -26180,7 +26180,7 @@
         <v>-13.93</v>
       </c>
       <c r="I340" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J340" t="n">
         <v>210.61</v>
@@ -26255,7 +26255,7 @@
         <v>-4.92</v>
       </c>
       <c r="I341" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J341" t="n">
         <v>205.69</v>
@@ -26330,7 +26330,7 @@
         <v>0.99</v>
       </c>
       <c r="I342" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J342" t="n">
         <v>198.57</v>
@@ -26405,7 +26405,7 @@
         <v>15.89</v>
       </c>
       <c r="I343" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J343" t="n">
         <v>191.46</v>
@@ -26480,7 +26480,7 @@
         <v>1.54</v>
       </c>
       <c r="I344" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J344" t="n">
         <v>187.94</v>
@@ -26555,7 +26555,7 @@
         <v>-2.16</v>
       </c>
       <c r="I345" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J345" t="n">
         <v>184.34</v>
@@ -26630,7 +26630,7 @@
         <v>-13.14</v>
       </c>
       <c r="I346" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J346" t="n">
         <v>178.56</v>
@@ -26705,7 +26705,7 @@
         <v>-6.33</v>
       </c>
       <c r="I347" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J347" t="n">
         <v>174.19</v>
@@ -26784,7 +26784,7 @@
         <v>-14.52</v>
       </c>
       <c r="I348" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J348" s="4" t="n">
         <v>167.84</v>
@@ -26859,7 +26859,7 @@
         <v>-16.02</v>
       </c>
       <c r="I349" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>159.11</v>
@@ -26938,7 +26938,7 @@
         <v>24.7</v>
       </c>
       <c r="I350" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J350" t="n">
         <v>153.97</v>
@@ -27013,7 +27013,7 @@
         <v>0</v>
       </c>
       <c r="I351" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J351" t="n">
         <v>150.64</v>
@@ -27088,7 +27088,7 @@
         <v>1.74</v>
       </c>
       <c r="I352" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J352" t="n">
         <v>146.74</v>
@@ -27163,7 +27163,7 @@
         <v>19.87</v>
       </c>
       <c r="I353" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J353" t="n">
         <v>145.48</v>
@@ -27238,7 +27238,7 @@
         <v>-5.6</v>
       </c>
       <c r="I354" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J354" t="n">
         <v>143.34</v>
@@ -27317,7 +27317,7 @@
         <v>0.2</v>
       </c>
       <c r="I355" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J355" t="n">
         <v>140.34</v>
@@ -27392,7 +27392,7 @@
         <v>5.99</v>
       </c>
       <c r="I356" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J356" t="n">
         <v>137.74</v>
@@ -27467,7 +27467,7 @@
         <v>-7.31</v>
       </c>
       <c r="I357" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J357" t="n">
         <v>135.97</v>
@@ -27546,7 +27546,7 @@
         <v>2.31</v>
       </c>
       <c r="I358" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J358" t="n">
         <v>133.79</v>
@@ -27621,7 +27621,7 @@
         <v>6.89</v>
       </c>
       <c r="I359" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J359" t="n">
         <v>132.62</v>
@@ -27696,7 +27696,7 @@
         <v>2.25</v>
       </c>
       <c r="I360" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J360" t="n">
         <v>132.76</v>
@@ -27771,7 +27771,7 @@
         <v>-0.28</v>
       </c>
       <c r="I361" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J361" t="n">
         <v>133.24</v>
@@ -27846,7 +27846,7 @@
         <v>4.54</v>
       </c>
       <c r="I362" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J362" t="n">
         <v>133.97</v>
@@ -27921,7 +27921,7 @@
         <v>-14.8</v>
       </c>
       <c r="I363" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J363" s="4" t="n">
         <v>132.5</v>
@@ -28000,7 +28000,7 @@
         <v>-6.48</v>
       </c>
       <c r="I364" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J364" t="n">
         <v>130.49</v>
@@ -28075,7 +28075,7 @@
         <v>1.22</v>
       </c>
       <c r="I365" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J365" t="n">
         <v>128.73</v>
@@ -28150,7 +28150,7 @@
         <v>-1.32</v>
       </c>
       <c r="I366" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J366" t="n">
         <v>127.92</v>
@@ -28225,7 +28225,7 @@
         <v>-7.82</v>
       </c>
       <c r="I367" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J367" t="n">
         <v>127.07</v>
@@ -28300,7 +28300,7 @@
         <v>4.05</v>
       </c>
       <c r="I368" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J368" t="n">
         <v>127.37</v>
@@ -28375,7 +28375,7 @@
         <v>0.8</v>
       </c>
       <c r="I369" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J369" t="n">
         <v>128.6</v>
@@ -28450,7 +28450,7 @@
         <v>5.54</v>
       </c>
       <c r="I370" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J370" t="n">
         <v>129.02</v>
@@ -28525,7 +28525,7 @@
         <v>-9.51</v>
       </c>
       <c r="I371" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J371" t="n">
         <v>128.85</v>
@@ -28600,7 +28600,7 @@
         <v>1.3</v>
       </c>
       <c r="I372" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J372" t="n">
         <v>128.66</v>
@@ -28675,7 +28675,7 @@
         <v>-6.1</v>
       </c>
       <c r="I373" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J373" t="n">
         <v>126.96</v>
@@ -28754,7 +28754,7 @@
         <v>0.42</v>
       </c>
       <c r="I374" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J374" t="n">
         <v>125.67</v>
@@ -28833,7 +28833,7 @@
         <v>0.37</v>
       </c>
       <c r="I375" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J375" t="n">
         <v>124.39</v>
@@ -28912,7 +28912,7 @@
         <v>9.869999999999999</v>
       </c>
       <c r="I376" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J376" t="n">
         <v>123.25</v>
@@ -28987,7 +28987,7 @@
         <v>5.11</v>
       </c>
       <c r="I377" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J377" t="n">
         <v>122.91</v>
@@ -29062,7 +29062,7 @@
         <v>2.11</v>
       </c>
       <c r="I378" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J378" t="n">
         <v>122.55</v>
@@ -29137,7 +29137,7 @@
         <v>-8.039999999999999</v>
       </c>
       <c r="I379" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J379" t="n">
         <v>121.23</v>
@@ -29216,7 +29216,7 @@
         <v>5.24</v>
       </c>
       <c r="I380" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J380" t="n">
         <v>120.06</v>
@@ -29291,7 +29291,7 @@
         <v>-16.99</v>
       </c>
       <c r="I381" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J381" s="4" t="n">
         <v>117.87</v>
@@ -29370,7 +29370,7 @@
         <v>1.18</v>
       </c>
       <c r="I382" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J382" t="n">
         <v>115.41</v>
@@ -29445,7 +29445,7 @@
         <v>1.61</v>
       </c>
       <c r="I383" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J383" t="n">
         <v>114.15</v>
@@ -29520,7 +29520,7 @@
         <v>10.43</v>
       </c>
       <c r="I384" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J384" t="n">
         <v>113.86</v>
@@ -29595,7 +29595,7 @@
         <v>7.71</v>
       </c>
       <c r="I385" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J385" t="n">
         <v>113.93</v>
@@ -29670,7 +29670,7 @@
         <v>14.77</v>
       </c>
       <c r="I386" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J386" t="n">
         <v>115</v>
@@ -29745,7 +29745,7 @@
         <v>7.13</v>
       </c>
       <c r="I387" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J387" t="n">
         <v>117.04</v>
@@ -29820,7 +29820,7 @@
         <v>-3.75</v>
       </c>
       <c r="I388" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J388" t="n">
         <v>118.57</v>
@@ -29895,7 +29895,7 @@
         <v>0.05</v>
       </c>
       <c r="I389" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J389" t="n">
         <v>120.06</v>
@@ -29970,7 +29970,7 @@
         <v>3.5</v>
       </c>
       <c r="I390" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J390" t="n">
         <v>121.49</v>
@@ -30045,7 +30045,7 @@
         <v>-6.05</v>
       </c>
       <c r="I391" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J391" t="n">
         <v>123.04</v>
@@ -30120,7 +30120,7 @@
         <v>3.31</v>
       </c>
       <c r="I392" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J392" t="n">
         <v>124.75</v>
@@ -30195,7 +30195,7 @@
         <v>0.59</v>
       </c>
       <c r="I393" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J393" t="n">
         <v>126.85</v>
@@ -30270,7 +30270,7 @@
         <v>3.94</v>
       </c>
       <c r="I394" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J394" t="n">
         <v>129.22</v>
@@ -30345,7 +30345,7 @@
         <v>6.52</v>
       </c>
       <c r="I395" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J395" t="n">
         <v>132.08</v>
@@ -30420,7 +30420,7 @@
         <v>0.34</v>
       </c>
       <c r="I396" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J396" t="n">
         <v>134.43</v>
@@ -30495,7 +30495,7 @@
         <v>-0.01</v>
       </c>
       <c r="I397" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J397" t="n">
         <v>136.48</v>
@@ -30570,7 +30570,7 @@
         <v>-3.26</v>
       </c>
       <c r="I398" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J398" t="n">
         <v>138.14</v>
@@ -30649,7 +30649,7 @@
         <v>-10.31</v>
       </c>
       <c r="I399" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J399" t="n">
         <v>139.48</v>
@@ -30724,7 +30724,7 @@
         <v>-1.94</v>
       </c>
       <c r="I400" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J400" t="n">
         <v>140.38</v>
@@ -30803,7 +30803,7 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="I401" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J401" t="n">
         <v>141.75</v>
@@ -30882,7 +30882,7 @@
         <v>-0.65</v>
       </c>
       <c r="I402" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J402" t="n">
         <v>143.01</v>
@@ -30957,7 +30957,7 @@
         <v>-13.35</v>
       </c>
       <c r="I403" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J403" t="n">
         <v>143.35</v>
@@ -31032,7 +31032,7 @@
         <v>-2.89</v>
       </c>
       <c r="I404" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J404" t="n">
         <v>142.98</v>
@@ -31111,7 +31111,7 @@
         <v>-12.74</v>
       </c>
       <c r="I405" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J405" t="n">
         <v>141.48</v>
@@ -31190,7 +31190,7 @@
         <v>5.32</v>
       </c>
       <c r="I406" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J406" t="n">
         <v>139.32</v>
@@ -31269,7 +31269,7 @@
         <v>-1.12</v>
       </c>
       <c r="I407" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J407" t="n">
         <v>136.6</v>
@@ -31348,7 +31348,7 @@
         <v>5.83</v>
       </c>
       <c r="I408" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J408" t="n">
         <v>134.45</v>
@@ -31427,7 +31427,7 @@
         <v>-20.47</v>
       </c>
       <c r="I409" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>131.24</v>
@@ -31506,7 +31506,7 @@
         <v>1.77</v>
       </c>
       <c r="I410" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J410" t="n">
         <v>127.85</v>
@@ -31585,7 +31585,7 @@
         <v>8.31</v>
       </c>
       <c r="I411" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J411" t="n">
         <v>125.26</v>
@@ -31664,7 +31664,7 @@
         <v>11.69</v>
       </c>
       <c r="I412" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J412" t="n">
         <v>122.96</v>
@@ -31743,7 +31743,7 @@
         <v>6.2</v>
       </c>
       <c r="I413" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J413" t="n">
         <v>120.93</v>
@@ -31818,7 +31818,7 @@
         <v>-4.62</v>
       </c>
       <c r="I414" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="J414" t="n">
         <v>118.37</v>
@@ -31864,61 +31864,81 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>SOXL</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="n">
-        <v>199204589</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I415" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="3" t="n">
-        <v>36.71</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="C415" s="4" t="n">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>84.19</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>70.23</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>77.05</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>200613600</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-24.75</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>114.04</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>156.66</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>124.18</v>
+      </c>
+      <c r="N415" s="6" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="O415" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="P415" t="inlineStr">
+      <c r="P415" s="4" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q415" t="inlineStr">
+      <c r="Q415" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
+      <c r="R415" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" s="4" t="n">
         <v>4.93</v>
       </c>
-      <c r="T415" s="3" t="n">
+      <c r="T415" s="7" t="n">
         <v>19.4</v>
       </c>
-      <c r="U415" s="3" t="n">
+      <c r="U415" s="7" t="n">
         <v>19.3</v>
       </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="3" t="n">
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="7" t="n">
         <v>149.8</v>
       </c>
     </row>
